--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1153" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1159" uniqueCount="393">
   <si>
     <t>CUENTA</t>
   </si>
@@ -1195,6 +1195,12 @@
   </si>
   <si>
     <t>ISRAEL CORDOBA</t>
+  </si>
+  <si>
+    <t>CORRALON LAS MORADAS</t>
+  </si>
+  <si>
+    <t>FERRETERIA JULIO</t>
   </si>
 </sst>
 </file>
@@ -1547,7 +1553,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D384"/>
+  <dimension ref="A1:D386"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -6331,66 +6337,66 @@
     </row>
     <row r="342" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A342" s="6">
-        <v>60299</v>
+        <v>60296</v>
       </c>
       <c r="B342" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D342" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="343" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A343" s="6">
-        <v>61004</v>
+        <v>60297</v>
       </c>
       <c r="B343" t="s">
-        <v>293</v>
+        <v>392</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D343" s="15" t="s">
+      <c r="D343" s="12" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="344" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A344" s="6">
-        <v>61009</v>
+        <v>60299</v>
       </c>
       <c r="B344" t="s">
-        <v>294</v>
+        <v>388</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D344" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="345" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A345" s="6">
-        <v>61012</v>
+        <v>61004</v>
       </c>
       <c r="B345" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D345" s="12" t="s">
-        <v>8</v>
+      <c r="D345" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="346" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A346" s="6">
-        <v>61018</v>
+        <v>61009</v>
       </c>
       <c r="B346" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>4</v>
@@ -6401,10 +6407,10 @@
     </row>
     <row r="347" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A347" s="6">
-        <v>61102</v>
+        <v>61012</v>
       </c>
       <c r="B347" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>4</v>
@@ -6415,24 +6421,24 @@
     </row>
     <row r="348" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A348" s="6">
-        <v>61205</v>
+        <v>61018</v>
       </c>
       <c r="B348" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D348" s="15" t="s">
-        <v>5</v>
+      <c r="D348" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="349" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A349" s="6">
-        <v>70100</v>
+        <v>61102</v>
       </c>
       <c r="B349" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>4</v>
@@ -6443,10 +6449,10 @@
     </row>
     <row r="350" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A350" s="6">
-        <v>70101</v>
+        <v>61205</v>
       </c>
       <c r="B350" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>4</v>
@@ -6457,38 +6463,38 @@
     </row>
     <row r="351" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A351" s="6">
-        <v>70102</v>
+        <v>70100</v>
       </c>
       <c r="B351" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D351" s="15" t="s">
-        <v>5</v>
+      <c r="D351" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="352" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A352" s="6">
-        <v>70103</v>
+        <v>70101</v>
       </c>
       <c r="B352" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D352" s="12" t="s">
-        <v>8</v>
+      <c r="D352" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="353" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A353" s="6">
-        <v>70106</v>
+        <v>70102</v>
       </c>
       <c r="B353" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>4</v>
@@ -6499,10 +6505,10 @@
     </row>
     <row r="354" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A354" s="6">
-        <v>70109</v>
+        <v>70103</v>
       </c>
       <c r="B354" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>4</v>
@@ -6513,10 +6519,10 @@
     </row>
     <row r="355" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A355" s="6">
-        <v>70113</v>
+        <v>70106</v>
       </c>
       <c r="B355" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>4</v>
@@ -6527,66 +6533,66 @@
     </row>
     <row r="356" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A356" s="6">
-        <v>70114</v>
+        <v>70109</v>
       </c>
       <c r="B356" t="s">
-        <v>325</v>
+        <v>304</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D356" s="9" t="s">
-        <v>9</v>
+      <c r="D356" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="357" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A357" s="6">
-        <v>70115</v>
+        <v>70113</v>
       </c>
       <c r="B357" t="s">
-        <v>331</v>
+        <v>305</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D357" s="9" t="s">
-        <v>9</v>
+      <c r="D357" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="358" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A358" s="6">
-        <v>70638</v>
+        <v>70114</v>
       </c>
       <c r="B358" t="s">
-        <v>306</v>
+        <v>325</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D358" s="12" t="s">
-        <v>8</v>
+      <c r="D358" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="359" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A359" s="6">
-        <v>70639</v>
+        <v>70115</v>
       </c>
       <c r="B359" t="s">
-        <v>307</v>
+        <v>331</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D359" s="12" t="s">
-        <v>8</v>
+      <c r="D359" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="360" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A360" s="6">
-        <v>70640</v>
+        <v>70638</v>
       </c>
       <c r="B360" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>4</v>
@@ -6597,10 +6603,10 @@
     </row>
     <row r="361" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A361" s="6">
-        <v>70642</v>
+        <v>70639</v>
       </c>
       <c r="B361" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>4</v>
@@ -6611,10 +6617,10 @@
     </row>
     <row r="362" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A362" s="6">
-        <v>90504</v>
+        <v>70640</v>
       </c>
       <c r="B362" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>4</v>
@@ -6625,10 +6631,10 @@
     </row>
     <row r="363" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A363" s="6">
-        <v>90509</v>
+        <v>70642</v>
       </c>
       <c r="B363" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>4</v>
@@ -6639,24 +6645,24 @@
     </row>
     <row r="364" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A364" s="6">
-        <v>90602</v>
+        <v>90504</v>
       </c>
       <c r="B364" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D364" s="15" t="s">
-        <v>5</v>
+      <c r="D364" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="365" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A365" s="6">
-        <v>90621</v>
+        <v>90509</v>
       </c>
       <c r="B365" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>4</v>
@@ -6667,66 +6673,66 @@
     </row>
     <row r="366" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A366" s="6">
-        <v>90622</v>
+        <v>90602</v>
       </c>
       <c r="B366" t="s">
-        <v>333</v>
+        <v>312</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D366" s="9" t="s">
+      <c r="D366" s="15" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="367" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A367" s="6">
-        <v>90631</v>
-      </c>
-      <c r="B367" s="8" t="s">
-        <v>342</v>
+        <v>90621</v>
+      </c>
+      <c r="B367" t="s">
+        <v>313</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D367" s="9" t="s">
-        <v>5</v>
+      <c r="D367" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="368" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A368" s="6">
-        <v>90658</v>
+        <v>90622</v>
       </c>
       <c r="B368" t="s">
-        <v>314</v>
+        <v>333</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D368" s="12" t="s">
-        <v>8</v>
+      <c r="D368" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="369" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A369" s="6">
-        <v>90660</v>
-      </c>
-      <c r="B369" t="s">
-        <v>315</v>
+        <v>90631</v>
+      </c>
+      <c r="B369" s="8" t="s">
+        <v>342</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D369" s="12" t="s">
-        <v>8</v>
+      <c r="D369" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="370" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A370" s="6">
-        <v>90668</v>
+        <v>90658</v>
       </c>
       <c r="B370" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>4</v>
@@ -6737,10 +6743,10 @@
     </row>
     <row r="371" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A371" s="6">
-        <v>90671</v>
+        <v>90660</v>
       </c>
       <c r="B371" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>4</v>
@@ -6751,10 +6757,10 @@
     </row>
     <row r="372" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A372" s="6">
-        <v>90679</v>
+        <v>90668</v>
       </c>
       <c r="B372" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>4</v>
@@ -6765,10 +6771,10 @@
     </row>
     <row r="373" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A373" s="6">
-        <v>90683</v>
+        <v>90671</v>
       </c>
       <c r="B373" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>4</v>
@@ -6779,10 +6785,10 @@
     </row>
     <row r="374" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A374" s="6">
-        <v>90705</v>
+        <v>90679</v>
       </c>
       <c r="B374" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>4</v>
@@ -6793,10 +6799,10 @@
     </row>
     <row r="375" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A375" s="6">
-        <v>90706</v>
+        <v>90683</v>
       </c>
       <c r="B375" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>4</v>
@@ -6807,10 +6813,10 @@
     </row>
     <row r="376" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A376" s="6">
-        <v>90708</v>
+        <v>90705</v>
       </c>
       <c r="B376" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>4</v>
@@ -6821,10 +6827,10 @@
     </row>
     <row r="377" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A377" s="6">
-        <v>90709</v>
+        <v>90706</v>
       </c>
       <c r="B377" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>4</v>
@@ -6835,10 +6841,10 @@
     </row>
     <row r="378" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A378" s="6">
-        <v>1218</v>
+        <v>90708</v>
       </c>
       <c r="B378" t="s">
-        <v>382</v>
+        <v>322</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>4</v>
@@ -6849,10 +6855,10 @@
     </row>
     <row r="379" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A379" s="6">
-        <v>1959</v>
-      </c>
-      <c r="B379" s="8" t="s">
-        <v>383</v>
+        <v>90709</v>
+      </c>
+      <c r="B379" t="s">
+        <v>323</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>4</v>
@@ -6863,10 +6869,10 @@
     </row>
     <row r="380" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A380" s="6">
-        <v>5625</v>
-      </c>
-      <c r="B380" s="8" t="s">
-        <v>384</v>
+        <v>1218</v>
+      </c>
+      <c r="B380" t="s">
+        <v>382</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>4</v>
@@ -6877,10 +6883,10 @@
     </row>
     <row r="381" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A381" s="6">
-        <v>1817</v>
+        <v>1959</v>
       </c>
       <c r="B381" s="8" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>4</v>
@@ -6891,10 +6897,10 @@
     </row>
     <row r="382" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A382" s="6">
-        <v>5737</v>
+        <v>5625</v>
       </c>
       <c r="B382" s="8" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>4</v>
@@ -6905,29 +6911,57 @@
     </row>
     <row r="383" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A383" s="6">
-        <v>60295</v>
+        <v>1817</v>
       </c>
       <c r="B383" s="8" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D383" s="9" t="s">
+      <c r="D383" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="384" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A384" s="6">
+        <v>5737</v>
+      </c>
+      <c r="B384" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="C384" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D384" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A385" s="6">
+        <v>60295</v>
+      </c>
+      <c r="B385" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="C385" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D385" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A386" s="6">
         <v>1045</v>
       </c>
-      <c r="B384" s="8" t="s">
+      <c r="B386" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="C384" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D384" s="9" t="s">
+      <c r="C386" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D386" s="9" t="s">
         <v>5</v>
       </c>
     </row>

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -6948,7 +6948,7 @@
         <v>4</v>
       </c>
       <c r="D385" s="9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="386" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$334</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$336</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1159" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1165" uniqueCount="395">
   <si>
     <t>CUENTA</t>
   </si>
@@ -1201,6 +1201,12 @@
   </si>
   <si>
     <t>FERRETERIA JULIO</t>
+  </si>
+  <si>
+    <t>FERRETERIA DIONICIO</t>
+  </si>
+  <si>
+    <t>FERRETERIA LIBER</t>
   </si>
 </sst>
 </file>
@@ -1553,7 +1559,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D386"/>
+  <dimension ref="A1:D388"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -1773,52 +1779,52 @@
     </row>
     <row r="16" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
-        <v>936</v>
+        <v>921</v>
       </c>
       <c r="B16" t="s">
-        <v>86</v>
+        <v>393</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="B17" t="s">
-        <v>185</v>
+        <v>86</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>5</v>
+      <c r="D17" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B18" t="s">
-        <v>41</v>
+        <v>185</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>8</v>
+      <c r="D18" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B19" t="s">
-        <v>128</v>
+        <v>41</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>4</v>
@@ -1829,38 +1835,38 @@
     </row>
     <row r="20" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
-        <v>946</v>
+        <v>940</v>
       </c>
       <c r="B20" t="s">
-        <v>7</v>
+        <v>128</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D20" t="s">
-        <v>9</v>
+      <c r="D20" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B21" t="s">
-        <v>200</v>
+        <v>7</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>8</v>
+      <c r="D21" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="B22" t="s">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>4</v>
@@ -1871,10 +1877,10 @@
     </row>
     <row r="23" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>4</v>
@@ -1885,10 +1891,10 @@
     </row>
     <row r="24" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B24" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>4</v>
@@ -1899,38 +1905,38 @@
     </row>
     <row r="25" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B25" t="s">
-        <v>64</v>
+        <v>147</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D25" t="s">
-        <v>9</v>
+      <c r="D25" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="B26" t="s">
-        <v>129</v>
+        <v>64</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>8</v>
+      <c r="D26" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="6">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B27" t="s">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>4</v>
@@ -1941,10 +1947,10 @@
     </row>
     <row r="28" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B28" t="s">
-        <v>158</v>
+        <v>102</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>4</v>
@@ -1955,38 +1961,38 @@
     </row>
     <row r="29" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="6">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="B29" t="s">
-        <v>6</v>
+        <v>158</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>5</v>
+      <c r="D29" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="B30" t="s">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D30" s="1" t="s">
-        <v>8</v>
+      <c r="D30" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="B31" t="s">
-        <v>140</v>
+        <v>55</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>4</v>
@@ -1997,24 +2003,24 @@
     </row>
     <row r="32" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B32" t="s">
-        <v>21</v>
+        <v>140</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>5</v>
+      <c r="D32" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="6">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="B33" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>4</v>
@@ -2025,66 +2031,66 @@
     </row>
     <row r="34" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="6">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="B34" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D34" s="1" t="s">
-        <v>8</v>
+      <c r="D34" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="6">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="B35" t="s">
-        <v>226</v>
+        <v>87</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D35" t="s">
-        <v>9</v>
+      <c r="D35" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="B36" t="s">
-        <v>174</v>
+        <v>226</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D36" s="3" t="s">
-        <v>5</v>
+      <c r="D36" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="6">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B37" t="s">
-        <v>137</v>
+        <v>174</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D37" s="1" t="s">
-        <v>8</v>
+      <c r="D37" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="6">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B38" t="s">
-        <v>172</v>
+        <v>137</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>4</v>
@@ -2095,10 +2101,10 @@
     </row>
     <row r="39" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="6">
-        <v>980</v>
+        <v>974</v>
       </c>
       <c r="B39" t="s">
-        <v>133</v>
+        <v>172</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>4</v>
@@ -2109,24 +2115,24 @@
     </row>
     <row r="40" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="6">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="B40" t="s">
-        <v>197</v>
+        <v>133</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D40" s="3" t="s">
-        <v>5</v>
+      <c r="D40" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="6">
-        <v>987</v>
+        <v>982</v>
       </c>
       <c r="B41" t="s">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>4</v>
@@ -2137,24 +2143,24 @@
     </row>
     <row r="42" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="6">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B42" t="s">
-        <v>191</v>
+        <v>80</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D42" s="1" t="s">
-        <v>8</v>
+      <c r="D42" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="6">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="B43" t="s">
-        <v>66</v>
+        <v>191</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>4</v>
@@ -2165,10 +2171,10 @@
     </row>
     <row r="44" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="6">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="B44" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>4</v>
@@ -2179,10 +2185,10 @@
     </row>
     <row r="45" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="6">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B45" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>4</v>
@@ -2193,10 +2199,10 @@
     </row>
     <row r="46" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="6">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="B46" t="s">
-        <v>44</v>
+        <v>97</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>4</v>
@@ -2207,10 +2213,10 @@
     </row>
     <row r="47" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="6">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B47" t="s">
-        <v>99</v>
+        <v>44</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>4</v>
@@ -2221,38 +2227,38 @@
     </row>
     <row r="48" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="6">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B48" t="s">
-        <v>180</v>
+        <v>99</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D48" t="s">
-        <v>9</v>
+      <c r="D48" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="6">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B49" t="s">
-        <v>222</v>
+        <v>180</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D49" s="1" t="s">
-        <v>8</v>
+      <c r="D49" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="6">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B50" t="s">
-        <v>75</v>
+        <v>222</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>4</v>
@@ -2263,10 +2269,10 @@
     </row>
     <row r="51" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="6">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B51" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>4</v>
@@ -2277,10 +2283,10 @@
     </row>
     <row r="52" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="6">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="B52" t="s">
-        <v>182</v>
+        <v>46</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>4</v>
@@ -2291,38 +2297,38 @@
     </row>
     <row r="53" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="6">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B53" t="s">
-        <v>115</v>
+        <v>182</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D53" s="3" t="s">
-        <v>5</v>
+      <c r="D53" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="6">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B54" t="s">
-        <v>214</v>
+        <v>115</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D54" s="1" t="s">
-        <v>8</v>
+      <c r="D54" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="B55" t="s">
-        <v>74</v>
+        <v>214</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>4</v>
@@ -2333,24 +2339,24 @@
     </row>
     <row r="56" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="6">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B56" t="s">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D56" t="s">
-        <v>9</v>
+      <c r="D56" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="6">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="B57" t="s">
-        <v>189</v>
+        <v>109</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>4</v>
@@ -2361,24 +2367,24 @@
     </row>
     <row r="58" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="6">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B58" t="s">
-        <v>152</v>
+        <v>189</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D58" s="1" t="s">
-        <v>8</v>
+      <c r="D58" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="6">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="B59" t="s">
-        <v>35</v>
+        <v>152</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>4</v>
@@ -2389,52 +2395,52 @@
     </row>
     <row r="60" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="6">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="B60" t="s">
-        <v>362</v>
+        <v>35</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D60" s="11" t="s">
-        <v>5</v>
+      <c r="D60" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="6">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B61" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D61" s="14" t="s">
+      <c r="D61" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="6">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="B62" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D62" s="11" t="s">
+      <c r="D62" s="14" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="6">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B63" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>4</v>
@@ -2445,136 +2451,136 @@
     </row>
     <row r="64" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="6">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B64" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="6">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B65" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D65" s="14" t="s">
-        <v>5</v>
+      <c r="D65" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="6">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B66" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D66" s="11" t="s">
+      <c r="D66" s="14" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="6">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B67" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D67" s="14" t="s">
-        <v>8</v>
+      <c r="D67" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="6">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B68" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D68" s="11" t="s">
-        <v>5</v>
+      <c r="D68" s="14" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="6">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B69" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D69" s="14" t="s">
+      <c r="D69" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="6">
-        <v>1031</v>
-      </c>
-      <c r="B70" s="8" t="s">
-        <v>346</v>
+        <v>1030</v>
+      </c>
+      <c r="B70" t="s">
+        <v>356</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D70" s="14" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="6">
-        <v>1032</v>
-      </c>
-      <c r="B71" t="s">
-        <v>369</v>
+        <v>1031</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>346</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D71" s="14" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="6">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B72" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D72" s="11" t="s">
+      <c r="D72" s="14" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="6">
-        <v>1034</v>
-      </c>
-      <c r="B73" s="8" t="s">
-        <v>373</v>
+        <v>1033</v>
+      </c>
+      <c r="B73" t="s">
+        <v>357</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>4</v>
@@ -2585,10 +2591,10 @@
     </row>
     <row r="74" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="6">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>345</v>
+        <v>373</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>4</v>
@@ -2599,10 +2605,10 @@
     </row>
     <row r="75" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="6">
-        <v>1036</v>
-      </c>
-      <c r="B75" t="s">
-        <v>358</v>
+        <v>1035</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>345</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>4</v>
@@ -2613,10 +2619,10 @@
     </row>
     <row r="76" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="6">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="B76" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>4</v>
@@ -2627,10 +2633,10 @@
     </row>
     <row r="77" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="6">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B77" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>4</v>
@@ -2641,10 +2647,10 @@
     </row>
     <row r="78" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="6">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="B78" t="s">
-        <v>371</v>
+        <v>352</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>4</v>
@@ -2655,52 +2661,52 @@
     </row>
     <row r="79" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="6">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="B79" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D79" s="11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="6">
-        <v>1416</v>
+        <v>1040</v>
       </c>
       <c r="B80" t="s">
-        <v>217</v>
+        <v>372</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D80" s="1" t="s">
+      <c r="D80" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="6">
-        <v>10107</v>
+        <v>1044</v>
       </c>
       <c r="B81" t="s">
-        <v>96</v>
+        <v>394</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D81" t="s">
-        <v>9</v>
+      <c r="D81" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="6">
-        <v>10137</v>
+        <v>1416</v>
       </c>
       <c r="B82" t="s">
-        <v>123</v>
+        <v>217</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>4</v>
@@ -2711,24 +2717,24 @@
     </row>
     <row r="83" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="6">
-        <v>10157</v>
+        <v>10107</v>
       </c>
       <c r="B83" t="s">
-        <v>183</v>
+        <v>96</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D83" s="1" t="s">
-        <v>8</v>
+      <c r="D83" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="6">
-        <v>10158</v>
+        <v>10137</v>
       </c>
       <c r="B84" t="s">
-        <v>65</v>
+        <v>123</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>4</v>
@@ -2739,24 +2745,24 @@
     </row>
     <row r="85" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="6">
-        <v>10160</v>
+        <v>10157</v>
       </c>
       <c r="B85" t="s">
-        <v>125</v>
+        <v>183</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D85" s="13" t="s">
-        <v>5</v>
+      <c r="D85" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="6">
-        <v>10162</v>
+        <v>10158</v>
       </c>
       <c r="B86" t="s">
-        <v>108</v>
+        <v>65</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>4</v>
@@ -2767,10 +2773,10 @@
     </row>
     <row r="87" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="6">
-        <v>10163</v>
+        <v>10160</v>
       </c>
       <c r="B87" t="s">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>4</v>
@@ -2781,10 +2787,10 @@
     </row>
     <row r="88" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="6">
-        <v>10165</v>
+        <v>10162</v>
       </c>
       <c r="B88" t="s">
-        <v>19</v>
+        <v>108</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>4</v>
@@ -2795,136 +2801,136 @@
     </row>
     <row r="89" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="6">
-        <v>10166</v>
-      </c>
-      <c r="B89" s="8" t="s">
-        <v>348</v>
+        <v>10163</v>
+      </c>
+      <c r="B89" t="s">
+        <v>90</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D89" s="11" t="s">
-        <v>8</v>
+      <c r="D89" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="6">
-        <v>10167</v>
+        <v>10165</v>
       </c>
       <c r="B90" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D90" s="13" t="s">
-        <v>5</v>
+      <c r="D90" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="6">
-        <v>10424</v>
-      </c>
-      <c r="B91" t="s">
-        <v>12</v>
+        <v>10166</v>
+      </c>
+      <c r="B91" s="8" t="s">
+        <v>348</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D91" s="17" t="s">
-        <v>9</v>
+      <c r="D91" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="6">
-        <v>10425</v>
+        <v>10167</v>
       </c>
       <c r="B92" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D92" s="17" t="s">
-        <v>9</v>
+      <c r="D92" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="6">
-        <v>20094</v>
+        <v>10424</v>
       </c>
       <c r="B93" t="s">
-        <v>198</v>
+        <v>12</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D93" s="10" t="s">
-        <v>8</v>
+      <c r="D93" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="6">
-        <v>20095</v>
+        <v>10425</v>
       </c>
       <c r="B94" t="s">
-        <v>153</v>
+        <v>15</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D94" s="10" t="s">
-        <v>8</v>
+      <c r="D94" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="6">
-        <v>20096</v>
+        <v>20094</v>
       </c>
       <c r="B95" t="s">
-        <v>122</v>
+        <v>198</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D95" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="6">
-        <v>20100</v>
+        <v>20095</v>
       </c>
       <c r="B96" t="s">
-        <v>84</v>
+        <v>153</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D96" s="1" t="s">
+      <c r="D96" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="6">
-        <v>20101</v>
+        <v>20096</v>
       </c>
       <c r="B97" t="s">
-        <v>40</v>
+        <v>122</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D97" s="1" t="s">
+      <c r="D97" s="10" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="6">
-        <v>20103</v>
+        <v>20100</v>
       </c>
       <c r="B98" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>4</v>
@@ -2935,38 +2941,38 @@
     </row>
     <row r="99" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="6">
-        <v>20106</v>
+        <v>20101</v>
       </c>
       <c r="B99" t="s">
-        <v>155</v>
+        <v>40</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="6">
-        <v>20108</v>
+        <v>20103</v>
       </c>
       <c r="B100" t="s">
-        <v>219</v>
+        <v>81</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D100" s="10" t="s">
+      <c r="D100" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="6">
-        <v>20109</v>
+        <v>20106</v>
       </c>
       <c r="B101" t="s">
-        <v>53</v>
+        <v>155</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>4</v>
@@ -2977,66 +2983,66 @@
     </row>
     <row r="102" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="6">
-        <v>20110</v>
+        <v>20108</v>
       </c>
       <c r="B102" t="s">
-        <v>33</v>
+        <v>219</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D102" s="13" t="s">
-        <v>5</v>
+      <c r="D102" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="6">
-        <v>20113</v>
+        <v>20109</v>
       </c>
       <c r="B103" t="s">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D103" s="10" t="s">
+      <c r="D103" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="6">
-        <v>20114</v>
+        <v>20110</v>
       </c>
       <c r="B104" t="s">
-        <v>126</v>
+        <v>33</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D104" s="1" t="s">
-        <v>8</v>
+      <c r="D104" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="6">
-        <v>20116</v>
+        <v>20113</v>
       </c>
       <c r="B105" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D105" s="1" t="s">
+      <c r="D105" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="6">
-        <v>20117</v>
+        <v>20114</v>
       </c>
       <c r="B106" t="s">
-        <v>186</v>
+        <v>126</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>4</v>
@@ -3047,10 +3053,10 @@
     </row>
     <row r="107" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="6">
-        <v>20118</v>
+        <v>20116</v>
       </c>
       <c r="B107" t="s">
-        <v>160</v>
+        <v>73</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>4</v>
@@ -3061,10 +3067,10 @@
     </row>
     <row r="108" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="6">
-        <v>20120</v>
+        <v>20117</v>
       </c>
       <c r="B108" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>4</v>
@@ -3075,10 +3081,10 @@
     </row>
     <row r="109" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="6">
-        <v>20121</v>
+        <v>20118</v>
       </c>
       <c r="B109" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>4</v>
@@ -3089,24 +3095,24 @@
     </row>
     <row r="110" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="6">
-        <v>20125</v>
+        <v>20120</v>
       </c>
       <c r="B110" t="s">
-        <v>88</v>
+        <v>176</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D110" s="10" t="s">
+      <c r="D110" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="6">
-        <v>20127</v>
+        <v>20121</v>
       </c>
       <c r="B111" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>4</v>
@@ -3117,108 +3123,108 @@
     </row>
     <row r="112" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="6">
-        <v>20128</v>
+        <v>20125</v>
       </c>
       <c r="B112" t="s">
-        <v>208</v>
+        <v>88</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D112" s="1" t="s">
+      <c r="D112" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="6">
-        <v>20129</v>
+        <v>20127</v>
       </c>
       <c r="B113" t="s">
-        <v>326</v>
+        <v>168</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D113" s="10" t="s">
+      <c r="D113" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="6">
-        <v>20137</v>
+        <v>20128</v>
       </c>
       <c r="B114" t="s">
-        <v>79</v>
+        <v>208</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D114" s="3" t="s">
-        <v>5</v>
+      <c r="D114" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="6">
-        <v>20138</v>
+        <v>20129</v>
       </c>
       <c r="B115" t="s">
-        <v>113</v>
+        <v>326</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D115" s="13" t="s">
-        <v>5</v>
+      <c r="D115" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="6">
-        <v>20140</v>
+        <v>20137</v>
       </c>
       <c r="B116" t="s">
-        <v>218</v>
+        <v>79</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D116" s="13" t="s">
+      <c r="D116" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="6">
-        <v>20142</v>
+        <v>20138</v>
       </c>
       <c r="B117" t="s">
-        <v>193</v>
+        <v>113</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D117" s="1" t="s">
-        <v>8</v>
+      <c r="D117" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="6">
-        <v>20146</v>
+        <v>20140</v>
       </c>
       <c r="B118" t="s">
-        <v>148</v>
+        <v>218</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D118" s="1" t="s">
-        <v>8</v>
+      <c r="D118" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="6">
-        <v>20148</v>
+        <v>20142</v>
       </c>
       <c r="B119" t="s">
-        <v>38</v>
+        <v>193</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>4</v>
@@ -3229,38 +3235,38 @@
     </row>
     <row r="120" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="6">
-        <v>20156</v>
+        <v>20146</v>
       </c>
       <c r="B120" t="s">
-        <v>179</v>
+        <v>148</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D120" s="10" t="s">
+      <c r="D120" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="6">
-        <v>20159</v>
+        <v>20148</v>
       </c>
       <c r="B121" t="s">
-        <v>120</v>
+        <v>38</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D121" s="17" t="s">
-        <v>9</v>
+      <c r="D121" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="122" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="6">
-        <v>20160</v>
+        <v>20156</v>
       </c>
       <c r="B122" t="s">
-        <v>224</v>
+        <v>179</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>4</v>
@@ -3271,38 +3277,38 @@
     </row>
     <row r="123" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="6">
-        <v>20163</v>
+        <v>20159</v>
       </c>
       <c r="B123" t="s">
-        <v>23</v>
+        <v>120</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D123" s="10" t="s">
-        <v>8</v>
+      <c r="D123" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="6">
-        <v>20164</v>
+        <v>20160</v>
       </c>
       <c r="B124" t="s">
-        <v>18</v>
+        <v>224</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D124" t="s">
-        <v>9</v>
+      <c r="D124" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="6">
-        <v>20165</v>
+        <v>20163</v>
       </c>
       <c r="B125" t="s">
-        <v>131</v>
+        <v>23</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>4</v>
@@ -3313,52 +3319,52 @@
     </row>
     <row r="126" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="6">
-        <v>20166</v>
+        <v>20164</v>
       </c>
       <c r="B126" t="s">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D126" s="1" t="s">
-        <v>8</v>
+      <c r="D126" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="6">
-        <v>20169</v>
+        <v>20165</v>
       </c>
       <c r="B127" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D127" s="1" t="s">
+      <c r="D127" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="6">
-        <v>20173</v>
+        <v>20166</v>
       </c>
       <c r="B128" t="s">
-        <v>112</v>
+        <v>77</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D128" s="10" t="s">
+      <c r="D128" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="6">
-        <v>20174</v>
+        <v>20169</v>
       </c>
       <c r="B129" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>4</v>
@@ -3369,38 +3375,38 @@
     </row>
     <row r="130" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="6">
-        <v>20178</v>
+        <v>20173</v>
       </c>
       <c r="B130" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D130" s="1" t="s">
+      <c r="D130" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="6">
-        <v>20179</v>
+        <v>20174</v>
       </c>
       <c r="B131" t="s">
-        <v>171</v>
+        <v>132</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D131" t="s">
-        <v>9</v>
+      <c r="D131" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="6">
-        <v>20180</v>
+        <v>20178</v>
       </c>
       <c r="B132" t="s">
-        <v>149</v>
+        <v>117</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>4</v>
@@ -3411,24 +3417,24 @@
     </row>
     <row r="133" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="6">
-        <v>20183</v>
+        <v>20179</v>
       </c>
       <c r="B133" t="s">
-        <v>370</v>
+        <v>171</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D133" s="14" t="s">
-        <v>5</v>
+      <c r="D133" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="6">
-        <v>20189</v>
+        <v>20180</v>
       </c>
       <c r="B134" t="s">
-        <v>329</v>
+        <v>149</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>4</v>
@@ -3439,66 +3445,66 @@
     </row>
     <row r="135" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="6">
-        <v>20200</v>
+        <v>20183</v>
       </c>
       <c r="B135" t="s">
-        <v>83</v>
+        <v>370</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D135" s="13" t="s">
+      <c r="D135" s="14" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="6">
-        <v>20201</v>
+        <v>20189</v>
       </c>
       <c r="B136" t="s">
-        <v>145</v>
+        <v>329</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D136" s="13" t="s">
-        <v>5</v>
+      <c r="D136" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="6">
-        <v>20204</v>
+        <v>20200</v>
       </c>
       <c r="B137" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D137" s="10" t="s">
-        <v>8</v>
+      <c r="D137" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="6">
-        <v>20205</v>
+        <v>20201</v>
       </c>
       <c r="B138" t="s">
-        <v>206</v>
+        <v>145</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D138" s="1" t="s">
-        <v>9</v>
+      <c r="D138" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="6">
-        <v>20211</v>
+        <v>20204</v>
       </c>
       <c r="B139" t="s">
-        <v>190</v>
+        <v>57</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>4</v>
@@ -3509,24 +3515,24 @@
     </row>
     <row r="140" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="6">
-        <v>20224</v>
+        <v>20205</v>
       </c>
       <c r="B140" t="s">
-        <v>85</v>
+        <v>206</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="6">
-        <v>20227</v>
+        <v>20211</v>
       </c>
       <c r="B141" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>4</v>
@@ -3537,24 +3543,24 @@
     </row>
     <row r="142" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="6">
-        <v>20228</v>
+        <v>20224</v>
       </c>
       <c r="B142" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D142" s="13" t="s">
-        <v>5</v>
+      <c r="D142" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="6">
-        <v>20230</v>
+        <v>20227</v>
       </c>
       <c r="B143" t="s">
-        <v>89</v>
+        <v>192</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>4</v>
@@ -3565,10 +3571,10 @@
     </row>
     <row r="144" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="6">
-        <v>20234</v>
+        <v>20228</v>
       </c>
       <c r="B144" t="s">
-        <v>29</v>
+        <v>91</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>4</v>
@@ -3579,24 +3585,24 @@
     </row>
     <row r="145" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="6">
-        <v>20236</v>
+        <v>20230</v>
       </c>
       <c r="B145" t="s">
-        <v>31</v>
+        <v>89</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D145" s="3" t="s">
-        <v>5</v>
+      <c r="D145" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="6">
-        <v>20238</v>
+        <v>20234</v>
       </c>
       <c r="B146" t="s">
-        <v>139</v>
+        <v>29</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>4</v>
@@ -3607,66 +3613,66 @@
     </row>
     <row r="147" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="6">
-        <v>20241</v>
+        <v>20236</v>
       </c>
       <c r="B147" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D147" s="13" t="s">
+      <c r="D147" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="6">
-        <v>20242</v>
+        <v>20238</v>
       </c>
       <c r="B148" t="s">
-        <v>216</v>
+        <v>139</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D148" s="10" t="s">
-        <v>8</v>
+      <c r="D148" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="6">
-        <v>20244</v>
+        <v>20241</v>
       </c>
       <c r="B149" t="s">
-        <v>124</v>
+        <v>22</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D149" s="10" t="s">
-        <v>8</v>
+      <c r="D149" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="6">
-        <v>20246</v>
+        <v>20242</v>
       </c>
       <c r="B150" t="s">
-        <v>14</v>
+        <v>216</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D150" s="13" t="s">
-        <v>5</v>
+      <c r="D150" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="6">
-        <v>20249</v>
+        <v>20244</v>
       </c>
       <c r="B151" t="s">
-        <v>72</v>
+        <v>124</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>4</v>
@@ -3677,38 +3683,38 @@
     </row>
     <row r="152" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="6">
-        <v>20256</v>
+        <v>20246</v>
       </c>
       <c r="B152" t="s">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D152" s="1" t="s">
-        <v>8</v>
+      <c r="D152" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="6">
-        <v>20257</v>
+        <v>20249</v>
       </c>
       <c r="B153" t="s">
-        <v>150</v>
+        <v>72</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D153" s="17" t="s">
-        <v>9</v>
+      <c r="D153" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="6">
-        <v>20258</v>
+        <v>20256</v>
       </c>
       <c r="B154" t="s">
-        <v>199</v>
+        <v>50</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>4</v>
@@ -3719,80 +3725,80 @@
     </row>
     <row r="155" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="6">
-        <v>20260</v>
+        <v>20257</v>
       </c>
       <c r="B155" t="s">
-        <v>68</v>
+        <v>150</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D155" s="13" t="s">
-        <v>5</v>
+      <c r="D155" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="156" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="6">
-        <v>20261</v>
+        <v>20258</v>
       </c>
       <c r="B156" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D156" s="10" t="s">
+      <c r="D156" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="6">
-        <v>20262</v>
+        <v>20260</v>
       </c>
       <c r="B157" t="s">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D157" s="10" t="s">
-        <v>8</v>
+      <c r="D157" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="6">
-        <v>20268</v>
+        <v>20261</v>
       </c>
       <c r="B158" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D158" s="1" t="s">
+      <c r="D158" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="159" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A159" s="6">
-        <v>20271</v>
+        <v>20262</v>
       </c>
       <c r="B159" t="s">
-        <v>34</v>
+        <v>92</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D159" s="13" t="s">
-        <v>5</v>
+      <c r="D159" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="160" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="6">
-        <v>20272</v>
+        <v>20268</v>
       </c>
       <c r="B160" t="s">
-        <v>178</v>
+        <v>201</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>4</v>
@@ -3803,10 +3809,10 @@
     </row>
     <row r="161" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="6">
-        <v>20275</v>
+        <v>20271</v>
       </c>
       <c r="B161" t="s">
-        <v>166</v>
+        <v>34</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>4</v>
@@ -3817,10 +3823,10 @@
     </row>
     <row r="162" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="6">
-        <v>20277</v>
+        <v>20272</v>
       </c>
       <c r="B162" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>4</v>
@@ -3831,80 +3837,80 @@
     </row>
     <row r="163" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="6">
-        <v>20281</v>
+        <v>20275</v>
       </c>
       <c r="B163" t="s">
-        <v>105</v>
+        <v>166</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D163" s="3" t="s">
+      <c r="D163" s="13" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="6">
-        <v>20282</v>
+        <v>20277</v>
       </c>
       <c r="B164" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="165" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="6">
-        <v>20284</v>
+        <v>20281</v>
       </c>
       <c r="B165" t="s">
-        <v>17</v>
+        <v>105</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D165" s="17" t="s">
-        <v>9</v>
+      <c r="D165" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="6">
-        <v>20285</v>
+        <v>20282</v>
       </c>
       <c r="B166" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="6">
-        <v>20289</v>
+        <v>20284</v>
       </c>
       <c r="B167" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D167" s="3" t="s">
-        <v>5</v>
+      <c r="D167" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="168" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="6">
-        <v>20290</v>
+        <v>20285</v>
       </c>
       <c r="B168" t="s">
-        <v>103</v>
+        <v>146</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>4</v>
@@ -3915,66 +3921,66 @@
     </row>
     <row r="169" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="6">
-        <v>20291</v>
+        <v>20289</v>
       </c>
       <c r="B169" t="s">
-        <v>187</v>
+        <v>52</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D169" s="10" t="s">
-        <v>8</v>
+      <c r="D169" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A170" s="6">
-        <v>20292</v>
+        <v>20290</v>
       </c>
       <c r="B170" t="s">
-        <v>32</v>
+        <v>103</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D170" s="13" t="s">
-        <v>5</v>
+      <c r="D170" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="171" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="6">
-        <v>20293</v>
+        <v>20291</v>
       </c>
       <c r="B171" t="s">
-        <v>43</v>
+        <v>187</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D171" s="13" t="s">
-        <v>5</v>
+      <c r="D171" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="6">
-        <v>20294</v>
+        <v>20292</v>
       </c>
       <c r="B172" t="s">
-        <v>202</v>
+        <v>32</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D172" s="10" t="s">
-        <v>8</v>
+      <c r="D172" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="6">
-        <v>20296</v>
+        <v>20293</v>
       </c>
       <c r="B173" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>4</v>
@@ -3985,38 +3991,38 @@
     </row>
     <row r="174" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="6">
-        <v>20298</v>
+        <v>20294</v>
       </c>
       <c r="B174" t="s">
-        <v>169</v>
+        <v>202</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D174" s="1" t="s">
+      <c r="D174" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="175" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="6">
-        <v>20299</v>
+        <v>20296</v>
       </c>
       <c r="B175" t="s">
-        <v>58</v>
+        <v>144</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D175" s="1" t="s">
-        <v>8</v>
+      <c r="D175" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="6">
-        <v>20301</v>
+        <v>20298</v>
       </c>
       <c r="B176" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>4</v>
@@ -4027,10 +4033,10 @@
     </row>
     <row r="177" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A177" s="6">
-        <v>20303</v>
+        <v>20299</v>
       </c>
       <c r="B177" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>4</v>
@@ -4041,66 +4047,66 @@
     </row>
     <row r="178" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="6">
-        <v>20309</v>
+        <v>20301</v>
       </c>
       <c r="B178" t="s">
-        <v>28</v>
+        <v>134</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D178" s="13" t="s">
-        <v>5</v>
+      <c r="D178" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="179" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="6">
-        <v>20310</v>
+        <v>20303</v>
       </c>
       <c r="B179" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D179" s="13" t="s">
-        <v>5</v>
+      <c r="D179" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="6">
-        <v>20318</v>
+        <v>20309</v>
       </c>
       <c r="B180" t="s">
-        <v>209</v>
+        <v>28</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D180" s="1" t="s">
-        <v>8</v>
+      <c r="D180" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="6">
-        <v>20319</v>
+        <v>20310</v>
       </c>
       <c r="B181" t="s">
-        <v>101</v>
+        <v>59</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D181" s="10" t="s">
-        <v>8</v>
+      <c r="D181" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="182" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="6">
-        <v>20320</v>
+        <v>20318</v>
       </c>
       <c r="B182" t="s">
-        <v>130</v>
+        <v>209</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>4</v>
@@ -4111,24 +4117,24 @@
     </row>
     <row r="183" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="6">
-        <v>20324</v>
+        <v>20319</v>
       </c>
       <c r="B183" t="s">
-        <v>210</v>
+        <v>101</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D183" s="1" t="s">
+      <c r="D183" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="184" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="6">
-        <v>20331</v>
+        <v>20320</v>
       </c>
       <c r="B184" t="s">
-        <v>51</v>
+        <v>130</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>4</v>
@@ -4139,24 +4145,24 @@
     </row>
     <row r="185" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="6">
-        <v>20333</v>
+        <v>20324</v>
       </c>
       <c r="B185" t="s">
-        <v>136</v>
+        <v>210</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D185" s="13" t="s">
-        <v>5</v>
+      <c r="D185" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="186" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="6">
-        <v>20337</v>
+        <v>20331</v>
       </c>
       <c r="B186" t="s">
-        <v>104</v>
+        <v>51</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>4</v>
@@ -4167,24 +4173,24 @@
     </row>
     <row r="187" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="6">
-        <v>20343</v>
+        <v>20333</v>
       </c>
       <c r="B187" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D187" s="1" t="s">
-        <v>8</v>
+      <c r="D187" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="188" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="6">
-        <v>20344</v>
+        <v>20337</v>
       </c>
       <c r="B188" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>4</v>
@@ -4195,24 +4201,24 @@
     </row>
     <row r="189" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="6">
-        <v>20351</v>
+        <v>20343</v>
       </c>
       <c r="B189" t="s">
-        <v>26</v>
+        <v>118</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D189" s="13" t="s">
-        <v>5</v>
+      <c r="D189" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="190" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A190" s="6">
-        <v>20357</v>
+        <v>20344</v>
       </c>
       <c r="B190" t="s">
-        <v>56</v>
+        <v>127</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>4</v>
@@ -4223,10 +4229,10 @@
     </row>
     <row r="191" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="6">
-        <v>20361</v>
+        <v>20351</v>
       </c>
       <c r="B191" t="s">
-        <v>164</v>
+        <v>26</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>4</v>
@@ -4237,80 +4243,80 @@
     </row>
     <row r="192" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="6">
-        <v>20362</v>
+        <v>20357</v>
       </c>
       <c r="B192" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D192" s="10" t="s">
+      <c r="D192" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="193" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="6">
-        <v>20363</v>
+        <v>20361</v>
       </c>
       <c r="B193" t="s">
-        <v>213</v>
+        <v>164</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D193" s="10" t="s">
-        <v>8</v>
+      <c r="D193" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="194" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="6">
-        <v>20364</v>
+        <v>20362</v>
       </c>
       <c r="B194" t="s">
-        <v>196</v>
+        <v>45</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D194" s="13" t="s">
-        <v>5</v>
+      <c r="D194" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="195" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A195" s="6">
-        <v>20366</v>
+        <v>20363</v>
       </c>
       <c r="B195" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D195" s="1" t="s">
+      <c r="D195" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="196" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="6">
-        <v>20367</v>
+        <v>20364</v>
       </c>
       <c r="B196" t="s">
-        <v>47</v>
+        <v>196</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D196" s="1" t="s">
-        <v>8</v>
+      <c r="D196" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="197" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="6">
-        <v>20369</v>
+        <v>20366</v>
       </c>
       <c r="B197" t="s">
-        <v>63</v>
+        <v>220</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>4</v>
@@ -4321,10 +4327,10 @@
     </row>
     <row r="198" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A198" s="6">
-        <v>20371</v>
+        <v>20367</v>
       </c>
       <c r="B198" t="s">
-        <v>223</v>
+        <v>47</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>4</v>
@@ -4335,24 +4341,24 @@
     </row>
     <row r="199" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="6">
-        <v>20372</v>
+        <v>20369</v>
       </c>
       <c r="B199" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D199" s="10" t="s">
+      <c r="D199" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="200" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A200" s="6">
-        <v>20374</v>
+        <v>20371</v>
       </c>
       <c r="B200" t="s">
-        <v>61</v>
+        <v>223</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>4</v>
@@ -4363,10 +4369,10 @@
     </row>
     <row r="201" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="6">
-        <v>20377</v>
+        <v>20372</v>
       </c>
       <c r="B201" t="s">
-        <v>225</v>
+        <v>70</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>4</v>
@@ -4377,66 +4383,66 @@
     </row>
     <row r="202" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="6">
-        <v>20379</v>
+        <v>20374</v>
       </c>
       <c r="B202" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D202" s="10" t="s">
+      <c r="D202" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="203" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="6">
-        <v>20380</v>
+        <v>20377</v>
       </c>
       <c r="B203" t="s">
-        <v>20</v>
+        <v>225</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D203" s="13" t="s">
-        <v>5</v>
+      <c r="D203" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="204" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="6">
-        <v>20381</v>
+        <v>20379</v>
       </c>
       <c r="B204" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D204" s="1" t="s">
+      <c r="D204" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="205" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A205" s="6">
-        <v>20384</v>
+        <v>20380</v>
       </c>
       <c r="B205" t="s">
-        <v>181</v>
+        <v>20</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D205" s="10" t="s">
-        <v>8</v>
+      <c r="D205" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="206" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A206" s="6">
-        <v>20385</v>
+        <v>20381</v>
       </c>
       <c r="B206" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>4</v>
@@ -4447,38 +4453,38 @@
     </row>
     <row r="207" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A207" s="6">
-        <v>20386</v>
+        <v>20384</v>
       </c>
       <c r="B207" t="s">
-        <v>119</v>
+        <v>181</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D207" s="1" t="s">
+      <c r="D207" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="208" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A208" s="6">
-        <v>20388</v>
+        <v>20385</v>
       </c>
       <c r="B208" t="s">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D208" s="10" t="s">
+      <c r="D208" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="209" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A209" s="6">
-        <v>20391</v>
+        <v>20386</v>
       </c>
       <c r="B209" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>4</v>
@@ -4489,10 +4495,10 @@
     </row>
     <row r="210" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A210" s="6">
-        <v>20394</v>
+        <v>20388</v>
       </c>
       <c r="B210" t="s">
-        <v>173</v>
+        <v>100</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>4</v>
@@ -4503,10 +4509,10 @@
     </row>
     <row r="211" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="6">
-        <v>20395</v>
+        <v>20391</v>
       </c>
       <c r="B211" t="s">
-        <v>161</v>
+        <v>106</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>4</v>
@@ -4517,38 +4523,38 @@
     </row>
     <row r="212" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A212" s="6">
-        <v>20396</v>
+        <v>20394</v>
       </c>
       <c r="B212" t="s">
-        <v>330</v>
+        <v>173</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D212" s="1" t="s">
+      <c r="D212" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="213" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A213" s="6">
-        <v>20397</v>
-      </c>
-      <c r="B213" s="8" t="s">
-        <v>344</v>
+        <v>20395</v>
+      </c>
+      <c r="B213" t="s">
+        <v>161</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D213" s="11" t="s">
-        <v>5</v>
+      <c r="D213" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="214" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A214" s="6">
-        <v>30101</v>
+        <v>20396</v>
       </c>
       <c r="B214" t="s">
-        <v>167</v>
+        <v>330</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>4</v>
@@ -4559,136 +4565,136 @@
     </row>
     <row r="215" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A215" s="6">
-        <v>40124</v>
-      </c>
-      <c r="B215" t="s">
-        <v>24</v>
+        <v>20397</v>
+      </c>
+      <c r="B215" s="8" t="s">
+        <v>344</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D215" s="13" t="s">
+      <c r="D215" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="216" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A216" s="6">
-        <v>40125</v>
+        <v>30101</v>
       </c>
       <c r="B216" t="s">
-        <v>143</v>
+        <v>167</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D216" s="13" t="s">
-        <v>5</v>
+      <c r="D216" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="217" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A217" s="6">
-        <v>40127</v>
+        <v>40124</v>
       </c>
       <c r="B217" t="s">
-        <v>163</v>
+        <v>24</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D217" s="1" t="s">
-        <v>8</v>
+      <c r="D217" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="218" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A218" s="6">
-        <v>40129</v>
+        <v>40125</v>
       </c>
       <c r="B218" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D218" s="1" t="s">
-        <v>8</v>
+      <c r="D218" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="219" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A219" s="6">
-        <v>40137</v>
+        <v>40127</v>
       </c>
       <c r="B219" t="s">
-        <v>121</v>
+        <v>163</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D219" s="10" t="s">
+      <c r="D219" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="220" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A220" s="6">
-        <v>40139</v>
+        <v>40129</v>
       </c>
       <c r="B220" t="s">
-        <v>327</v>
+        <v>138</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D220" s="10" t="s">
+      <c r="D220" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="221" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A221" s="6">
-        <v>40140</v>
+        <v>40137</v>
       </c>
       <c r="B221" t="s">
-        <v>170</v>
+        <v>121</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D221" s="1" t="s">
+      <c r="D221" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="222" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A222" s="6">
-        <v>40141</v>
+        <v>40139</v>
       </c>
       <c r="B222" t="s">
-        <v>111</v>
+        <v>327</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D222" s="13" t="s">
-        <v>5</v>
+      <c r="D222" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="223" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223" s="6">
-        <v>40143</v>
+        <v>40140</v>
       </c>
       <c r="B223" t="s">
-        <v>94</v>
+        <v>170</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D223" s="10" t="s">
+      <c r="D223" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="224" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="6">
-        <v>40144</v>
+        <v>40141</v>
       </c>
       <c r="B224" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>4</v>
@@ -4699,66 +4705,66 @@
     </row>
     <row r="225" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A225" s="6">
-        <v>40145</v>
+        <v>40143</v>
       </c>
       <c r="B225" t="s">
-        <v>165</v>
+        <v>94</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D225" s="13" t="s">
-        <v>5</v>
+      <c r="D225" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="226" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A226" s="6">
-        <v>40150</v>
+        <v>40144</v>
       </c>
       <c r="B226" t="s">
-        <v>221</v>
+        <v>107</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D226" s="10" t="s">
-        <v>8</v>
+      <c r="D226" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="227" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A227" s="6">
-        <v>40151</v>
+        <v>40145</v>
       </c>
       <c r="B227" t="s">
-        <v>54</v>
+        <v>165</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D227" s="1" t="s">
-        <v>8</v>
+      <c r="D227" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="228" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A228" s="6">
-        <v>50102</v>
+        <v>40150</v>
       </c>
       <c r="B228" t="s">
-        <v>67</v>
+        <v>221</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D228" s="13" t="s">
-        <v>5</v>
+      <c r="D228" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="229" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A229" s="6">
-        <v>50222</v>
+        <v>40151</v>
       </c>
       <c r="B229" t="s">
-        <v>215</v>
+        <v>54</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>4</v>
@@ -4769,178 +4775,178 @@
     </row>
     <row r="230" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A230" s="6">
-        <v>50223</v>
+        <v>50102</v>
       </c>
       <c r="B230" t="s">
-        <v>194</v>
+        <v>67</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D230" s="10" t="s">
-        <v>8</v>
+      <c r="D230" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="231" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A231" s="6">
-        <v>50224</v>
+        <v>50222</v>
       </c>
       <c r="B231" t="s">
-        <v>42</v>
+        <v>215</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D231" s="3" t="s">
-        <v>5</v>
+      <c r="D231" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="232" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A232" s="6">
-        <v>50444</v>
+        <v>50223</v>
       </c>
       <c r="B232" t="s">
-        <v>116</v>
+        <v>194</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D232" s="1" t="s">
+      <c r="D232" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="233" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A233" s="6">
-        <v>50445</v>
+        <v>50224</v>
       </c>
       <c r="B233" t="s">
-        <v>354</v>
+        <v>42</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D233" s="11" t="s">
+      <c r="D233" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="234" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A234" s="6">
-        <v>50607</v>
+        <v>50444</v>
       </c>
       <c r="B234" t="s">
-        <v>76</v>
+        <v>116</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D234" s="13" t="s">
-        <v>5</v>
+      <c r="D234" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="235" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A235" s="6">
-        <v>50608</v>
+        <v>50445</v>
       </c>
       <c r="B235" t="s">
-        <v>177</v>
+        <v>354</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D235" s="1" t="s">
-        <v>8</v>
+      <c r="D235" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="236" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A236" s="6">
-        <v>50611</v>
-      </c>
-      <c r="B236" s="8" t="s">
-        <v>347</v>
+        <v>50607</v>
+      </c>
+      <c r="B236" t="s">
+        <v>76</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D236" s="14" t="s">
-        <v>8</v>
+      <c r="D236" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="237" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A237" s="6">
-        <v>50622</v>
+        <v>50608</v>
       </c>
       <c r="B237" t="s">
-        <v>95</v>
+        <v>177</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D237" s="16" t="s">
+      <c r="D237" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="238" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A238" s="6">
-        <v>50623</v>
-      </c>
-      <c r="B238" t="s">
-        <v>110</v>
+        <v>50611</v>
+      </c>
+      <c r="B238" s="8" t="s">
+        <v>347</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D238" s="10" t="s">
+      <c r="D238" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="239" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A239" s="6">
-        <v>50625</v>
+        <v>50622</v>
       </c>
       <c r="B239" t="s">
-        <v>204</v>
+        <v>95</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D239" s="10" t="s">
+      <c r="D239" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="240" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A240" s="6">
-        <v>50629</v>
+        <v>50623</v>
       </c>
       <c r="B240" t="s">
-        <v>188</v>
+        <v>110</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D240" s="1" t="s">
+      <c r="D240" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="241" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="6">
-        <v>50630</v>
+        <v>50625</v>
       </c>
       <c r="B241" t="s">
-        <v>360</v>
+        <v>204</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D241" s="14" t="s">
+      <c r="D241" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="242" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A242" s="6">
-        <v>50803</v>
+        <v>50629</v>
       </c>
       <c r="B242" t="s">
-        <v>82</v>
+        <v>188</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>4</v>
@@ -4951,24 +4957,24 @@
     </row>
     <row r="243" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A243" s="6">
-        <v>50805</v>
+        <v>50630</v>
       </c>
       <c r="B243" t="s">
-        <v>135</v>
+        <v>360</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D243" s="10" t="s">
+      <c r="D243" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="244" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A244" s="6">
-        <v>50806</v>
+        <v>50803</v>
       </c>
       <c r="B244" t="s">
-        <v>156</v>
+        <v>82</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>4</v>
@@ -4979,290 +4985,290 @@
     </row>
     <row r="245" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A245" s="6">
-        <v>50808</v>
+        <v>50805</v>
       </c>
       <c r="B245" t="s">
-        <v>16</v>
+        <v>135</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D245" s="13" t="s">
-        <v>5</v>
+      <c r="D245" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="246" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A246" s="6">
-        <v>50809</v>
+        <v>50806</v>
       </c>
       <c r="B246" t="s">
-        <v>98</v>
+        <v>156</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D246" s="13" t="s">
-        <v>5</v>
+      <c r="D246" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="247" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A247" s="6">
-        <v>50810</v>
+        <v>50808</v>
       </c>
       <c r="B247" t="s">
-        <v>175</v>
+        <v>16</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D247" s="1" t="s">
-        <v>8</v>
+      <c r="D247" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="248" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A248" s="6">
-        <v>50812</v>
+        <v>50809</v>
       </c>
       <c r="B248" t="s">
-        <v>184</v>
+        <v>98</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D248" s="1" t="s">
-        <v>8</v>
+      <c r="D248" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="249" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A249" s="6">
-        <v>50813</v>
+        <v>50810</v>
       </c>
       <c r="B249" t="s">
-        <v>71</v>
+        <v>175</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D249" s="17" t="s">
-        <v>9</v>
+      <c r="D249" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="250" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A250" s="6">
-        <v>50815</v>
+        <v>50812</v>
       </c>
       <c r="B250" t="s">
-        <v>114</v>
+        <v>184</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D250" s="10" t="s">
+      <c r="D250" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="251" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A251" s="6">
-        <v>50816</v>
+        <v>50813</v>
       </c>
       <c r="B251" t="s">
-        <v>205</v>
+        <v>71</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D251" s="1" t="s">
-        <v>8</v>
+      <c r="D251" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="252" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A252" s="6">
-        <v>50818</v>
+        <v>50815</v>
       </c>
       <c r="B252" t="s">
-        <v>227</v>
+        <v>114</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D252" s="13" t="s">
-        <v>5</v>
+      <c r="D252" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="253" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A253" s="6">
-        <v>50819</v>
+        <v>50816</v>
       </c>
       <c r="B253" t="s">
-        <v>228</v>
+        <v>205</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D253" s="10" t="s">
+      <c r="D253" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="254" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="6">
-        <v>50820</v>
+        <v>50818</v>
       </c>
       <c r="B254" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D254" s="10" t="s">
-        <v>8</v>
+      <c r="D254" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="255" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A255" s="6">
-        <v>50821</v>
+        <v>50819</v>
       </c>
       <c r="B255" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D255" s="1" t="s">
+      <c r="D255" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="256" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A256" s="6">
-        <v>50823</v>
+        <v>50820</v>
       </c>
       <c r="B256" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D256" s="17" t="s">
-        <v>9</v>
+      <c r="D256" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="257" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A257" s="6">
-        <v>50824</v>
+        <v>50821</v>
       </c>
       <c r="B257" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D257" s="13" t="s">
-        <v>5</v>
+      <c r="D257" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="258" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A258" s="6">
-        <v>50825</v>
+        <v>50823</v>
       </c>
       <c r="B258" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D258" s="10" t="s">
-        <v>8</v>
+      <c r="D258" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="259" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A259" s="6">
-        <v>50826</v>
+        <v>50824</v>
       </c>
       <c r="B259" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D259" s="10" t="s">
-        <v>8</v>
+      <c r="D259" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="260" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A260" s="6">
-        <v>50827</v>
+        <v>50825</v>
       </c>
       <c r="B260" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D260" s="1" t="s">
+      <c r="D260" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="261" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A261" s="6">
-        <v>50829</v>
+        <v>50826</v>
       </c>
       <c r="B261" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D261" s="1" t="s">
+      <c r="D261" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="262" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A262" s="6">
-        <v>50830</v>
+        <v>50827</v>
       </c>
       <c r="B262" t="s">
-        <v>366</v>
+        <v>235</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D262" s="11" t="s">
+      <c r="D262" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="263" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A263" s="6">
-        <v>50831</v>
+        <v>50829</v>
       </c>
       <c r="B263" t="s">
-        <v>351</v>
+        <v>236</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D263" s="11" t="s">
-        <v>5</v>
+      <c r="D263" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="264" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A264" s="6">
-        <v>50832</v>
-      </c>
-      <c r="B264" s="8" t="s">
-        <v>349</v>
+        <v>50830</v>
+      </c>
+      <c r="B264" t="s">
+        <v>366</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D264" s="11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="265" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A265" s="6">
-        <v>50230</v>
-      </c>
-      <c r="B265" s="8" t="s">
-        <v>379</v>
+        <v>50831</v>
+      </c>
+      <c r="B265" t="s">
+        <v>351</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>4</v>
@@ -5273,38 +5279,38 @@
     </row>
     <row r="266" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A266" s="6">
-        <v>60103</v>
-      </c>
-      <c r="B266" t="s">
-        <v>237</v>
+        <v>50832</v>
+      </c>
+      <c r="B266" s="8" t="s">
+        <v>349</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D266" s="13" t="s">
+      <c r="D266" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="267" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A267" s="6">
-        <v>60109</v>
-      </c>
-      <c r="B267" t="s">
-        <v>328</v>
+        <v>50230</v>
+      </c>
+      <c r="B267" s="8" t="s">
+        <v>379</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D267" s="11" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="268" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A268" s="6">
-        <v>60124</v>
+        <v>60103</v>
       </c>
       <c r="B268" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>4</v>
@@ -5315,80 +5321,80 @@
     </row>
     <row r="269" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A269" s="6">
-        <v>60125</v>
+        <v>60109</v>
       </c>
       <c r="B269" t="s">
-        <v>239</v>
+        <v>328</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D269" s="13" t="s">
-        <v>5</v>
+      <c r="D269" s="11" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="270" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A270" s="6">
-        <v>60126</v>
+        <v>60124</v>
       </c>
       <c r="B270" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D270" s="10" t="s">
-        <v>8</v>
+      <c r="D270" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="271" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A271" s="6">
-        <v>60128</v>
+        <v>60125</v>
       </c>
       <c r="B271" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D271" s="3" t="s">
+      <c r="D271" s="13" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="272" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A272" s="6">
-        <v>60130</v>
+        <v>60126</v>
       </c>
       <c r="B272" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D272" s="1" t="s">
+      <c r="D272" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="273" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A273" s="6">
-        <v>60133</v>
+        <v>60128</v>
       </c>
       <c r="B273" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D273" s="13" t="s">
+      <c r="D273" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="274" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A274" s="6">
-        <v>60134</v>
+        <v>60130</v>
       </c>
       <c r="B274" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>4</v>
@@ -5399,24 +5405,24 @@
     </row>
     <row r="275" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A275" s="6">
-        <v>60137</v>
+        <v>60133</v>
       </c>
       <c r="B275" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D275" s="1" t="s">
-        <v>8</v>
+      <c r="D275" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="276" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A276" s="6">
-        <v>60139</v>
+        <v>60134</v>
       </c>
       <c r="B276" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>4</v>
@@ -5427,10 +5433,10 @@
     </row>
     <row r="277" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A277" s="6">
-        <v>60142</v>
+        <v>60137</v>
       </c>
       <c r="B277" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>4</v>
@@ -5441,10 +5447,10 @@
     </row>
     <row r="278" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A278" s="6">
-        <v>60148</v>
+        <v>60139</v>
       </c>
       <c r="B278" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>4</v>
@@ -5455,10 +5461,10 @@
     </row>
     <row r="279" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A279" s="6">
-        <v>60149</v>
+        <v>60142</v>
       </c>
       <c r="B279" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>4</v>
@@ -5469,122 +5475,122 @@
     </row>
     <row r="280" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A280" s="6">
-        <v>60150</v>
+        <v>60148</v>
       </c>
       <c r="B280" t="s">
-        <v>332</v>
+        <v>248</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D280" s="13" t="s">
-        <v>5</v>
+      <c r="D280" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="281" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A281" s="6">
-        <v>60158</v>
+        <v>60149</v>
       </c>
       <c r="B281" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D281" s="10" t="s">
+      <c r="D281" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="282" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A282" s="6">
-        <v>60159</v>
+        <v>60150</v>
       </c>
       <c r="B282" t="s">
-        <v>251</v>
+        <v>332</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D282" s="1" t="s">
-        <v>8</v>
+      <c r="D282" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="283" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A283" s="6">
-        <v>60162</v>
+        <v>60158</v>
       </c>
       <c r="B283" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D283" s="13" t="s">
-        <v>5</v>
+      <c r="D283" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="284" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A284" s="6">
-        <v>60163</v>
+        <v>60159</v>
       </c>
       <c r="B284" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D284" s="13" t="s">
-        <v>5</v>
+      <c r="D284" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="285" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A285" s="6">
-        <v>60165</v>
+        <v>60162</v>
       </c>
       <c r="B285" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D285" s="1" t="s">
-        <v>8</v>
+      <c r="D285" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="286" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A286" s="6">
-        <v>60169</v>
+        <v>60163</v>
       </c>
       <c r="B286" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D286" s="1" t="s">
-        <v>8</v>
+      <c r="D286" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="287" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A287" s="6">
-        <v>60170</v>
-      </c>
-      <c r="B287" s="8" t="s">
-        <v>337</v>
+        <v>60165</v>
+      </c>
+      <c r="B287" t="s">
+        <v>254</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D287" s="11" t="s">
+      <c r="D287" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="288" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A288" s="6">
-        <v>60172</v>
+        <v>60169</v>
       </c>
       <c r="B288" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>4</v>
@@ -5595,66 +5601,66 @@
     </row>
     <row r="289" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A289" s="6">
-        <v>60174</v>
-      </c>
-      <c r="B289" t="s">
-        <v>257</v>
+        <v>60170</v>
+      </c>
+      <c r="B289" s="8" t="s">
+        <v>337</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D289" s="13" t="s">
-        <v>5</v>
+      <c r="D289" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="290" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A290" s="6">
-        <v>60176</v>
+        <v>60172</v>
       </c>
       <c r="B290" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D290" s="13" t="s">
-        <v>5</v>
+      <c r="D290" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="291" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A291" s="6">
-        <v>60178</v>
+        <v>60174</v>
       </c>
       <c r="B291" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D291" s="1" t="s">
-        <v>8</v>
+      <c r="D291" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="292" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A292" s="6">
-        <v>60180</v>
+        <v>60176</v>
       </c>
       <c r="B292" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D292" s="10" t="s">
-        <v>8</v>
+      <c r="D292" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="293" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A293" s="6">
-        <v>60184</v>
+        <v>60178</v>
       </c>
       <c r="B293" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>4</v>
@@ -5665,52 +5671,52 @@
     </row>
     <row r="294" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A294" s="6">
-        <v>60190</v>
+        <v>60180</v>
       </c>
       <c r="B294" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D294" s="1" t="s">
+      <c r="D294" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="295" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A295" s="6">
-        <v>60191</v>
+        <v>60184</v>
       </c>
       <c r="B295" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D295" s="10" t="s">
+      <c r="D295" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="296" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A296" s="6">
-        <v>60192</v>
+        <v>60190</v>
       </c>
       <c r="B296" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D296" s="10" t="s">
+      <c r="D296" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="297" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A297" s="6">
-        <v>60195</v>
+        <v>60191</v>
       </c>
       <c r="B297" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>4</v>
@@ -5721,10 +5727,10 @@
     </row>
     <row r="298" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A298" s="6">
-        <v>60196</v>
+        <v>60192</v>
       </c>
       <c r="B298" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>4</v>
@@ -5735,10 +5741,10 @@
     </row>
     <row r="299" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A299" s="6">
-        <v>60198</v>
+        <v>60195</v>
       </c>
       <c r="B299" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>4</v>
@@ -5749,66 +5755,66 @@
     </row>
     <row r="300" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A300" s="6">
-        <v>60201</v>
+        <v>60196</v>
       </c>
       <c r="B300" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D300" t="s">
-        <v>9</v>
+      <c r="D300" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="301" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A301" s="6">
-        <v>60202</v>
+        <v>60198</v>
       </c>
       <c r="B301" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D301" s="13" t="s">
-        <v>5</v>
+      <c r="D301" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="302" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A302" s="6">
-        <v>60204</v>
+        <v>60201</v>
       </c>
       <c r="B302" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D302" s="1" t="s">
-        <v>8</v>
+      <c r="D302" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="303" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A303" s="6">
-        <v>60205</v>
+        <v>60202</v>
       </c>
       <c r="B303" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D303" s="1" t="s">
-        <v>8</v>
+      <c r="D303" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="304" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A304" s="6">
-        <v>60206</v>
+        <v>60204</v>
       </c>
       <c r="B304" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>4</v>
@@ -5819,24 +5825,24 @@
     </row>
     <row r="305" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A305" s="6">
-        <v>60209</v>
+        <v>60205</v>
       </c>
       <c r="B305" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D305" s="10" t="s">
+      <c r="D305" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="306" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A306" s="6">
-        <v>60211</v>
+        <v>60206</v>
       </c>
       <c r="B306" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>4</v>
@@ -5847,10 +5853,10 @@
     </row>
     <row r="307" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A307" s="6">
-        <v>60215</v>
+        <v>60209</v>
       </c>
       <c r="B307" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>4</v>
@@ -5861,24 +5867,24 @@
     </row>
     <row r="308" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A308" s="6">
-        <v>60216</v>
+        <v>60211</v>
       </c>
       <c r="B308" t="s">
-        <v>381</v>
+        <v>274</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D308" s="10" t="s">
-        <v>9</v>
+      <c r="D308" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="309" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A309" s="6">
-        <v>60217</v>
+        <v>60215</v>
       </c>
       <c r="B309" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>4</v>
@@ -5889,24 +5895,24 @@
     </row>
     <row r="310" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A310" s="6">
-        <v>60219</v>
+        <v>60216</v>
       </c>
       <c r="B310" t="s">
-        <v>277</v>
+        <v>381</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D310" s="1" t="s">
-        <v>8</v>
+      <c r="D310" s="10" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="311" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A311" s="6">
-        <v>60222</v>
+        <v>60217</v>
       </c>
       <c r="B311" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>4</v>
@@ -5917,24 +5923,24 @@
     </row>
     <row r="312" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A312" s="6">
-        <v>60225</v>
+        <v>60219</v>
       </c>
       <c r="B312" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D312" s="17" t="s">
-        <v>9</v>
+      <c r="D312" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="313" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A313" s="6">
-        <v>60230</v>
+        <v>60222</v>
       </c>
       <c r="B313" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>4</v>
@@ -5945,94 +5951,94 @@
     </row>
     <row r="314" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A314" s="6">
-        <v>60241</v>
-      </c>
-      <c r="B314" s="8" t="s">
-        <v>338</v>
+        <v>60225</v>
+      </c>
+      <c r="B314" t="s">
+        <v>279</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D314" s="7" t="s">
+      <c r="D314" s="17" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="315" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A315" s="6">
-        <v>60242</v>
-      </c>
-      <c r="B315" s="8" t="s">
-        <v>341</v>
+        <v>60230</v>
+      </c>
+      <c r="B315" t="s">
+        <v>280</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D315" s="7" t="s">
-        <v>5</v>
+      <c r="D315" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="316" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A316" s="6">
-        <v>60245</v>
+        <v>60241</v>
       </c>
       <c r="B316" s="8" t="s">
-        <v>387</v>
+        <v>338</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D316" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="317" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A317" s="6">
-        <v>60250</v>
+        <v>60242</v>
       </c>
       <c r="B317" s="8" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D317" s="11" t="s">
-        <v>8</v>
+      <c r="D317" s="7" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="318" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A318" s="6">
-        <v>60253</v>
-      </c>
-      <c r="B318" t="s">
-        <v>281</v>
+        <v>60245</v>
+      </c>
+      <c r="B318" s="8" t="s">
+        <v>387</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D318" s="1" t="s">
-        <v>8</v>
+      <c r="D318" s="7" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="319" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A319" s="6">
-        <v>60254</v>
-      </c>
-      <c r="B319" t="s">
-        <v>282</v>
+        <v>60250</v>
+      </c>
+      <c r="B319" s="8" t="s">
+        <v>339</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D319" s="1" t="s">
+      <c r="D319" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="320" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A320" s="6">
-        <v>60257</v>
+        <v>60253</v>
       </c>
       <c r="B320" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>4</v>
@@ -6043,10 +6049,10 @@
     </row>
     <row r="321" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A321" s="6">
-        <v>60258</v>
+        <v>60254</v>
       </c>
       <c r="B321" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>4</v>
@@ -6057,66 +6063,66 @@
     </row>
     <row r="322" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A322" s="6">
-        <v>60266</v>
-      </c>
-      <c r="B322" s="8" t="s">
-        <v>343</v>
+        <v>60257</v>
+      </c>
+      <c r="B322" t="s">
+        <v>283</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D322" s="11" t="s">
+      <c r="D322" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="323" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A323" s="6">
-        <v>60269</v>
+        <v>60258</v>
       </c>
       <c r="B323" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D323" s="10" t="s">
+      <c r="D323" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="324" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A324" s="6">
-        <v>60270</v>
-      </c>
-      <c r="B324" t="s">
-        <v>286</v>
+        <v>60266</v>
+      </c>
+      <c r="B324" s="8" t="s">
+        <v>343</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D324" s="1" t="s">
+      <c r="D324" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="325" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A325" s="6">
-        <v>60272</v>
+        <v>60269</v>
       </c>
       <c r="B325" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D325" s="1" t="s">
+      <c r="D325" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="326" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A326" s="6">
-        <v>60274</v>
+        <v>60270</v>
       </c>
       <c r="B326" t="s">
-        <v>380</v>
+        <v>286</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>4</v>
@@ -6127,10 +6133,10 @@
     </row>
     <row r="327" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A327" s="6">
-        <v>60275</v>
+        <v>60272</v>
       </c>
       <c r="B327" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>4</v>
@@ -6141,10 +6147,10 @@
     </row>
     <row r="328" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A328" s="6">
-        <v>60276</v>
+        <v>60274</v>
       </c>
       <c r="B328" t="s">
-        <v>289</v>
+        <v>380</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>4</v>
@@ -6155,24 +6161,24 @@
     </row>
     <row r="329" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A329" s="6">
-        <v>60278</v>
+        <v>60275</v>
       </c>
       <c r="B329" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D329" s="13" t="s">
-        <v>9</v>
+      <c r="D329" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="330" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A330" s="6">
-        <v>60279</v>
+        <v>60276</v>
       </c>
       <c r="B330" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>4</v>
@@ -6183,94 +6189,94 @@
     </row>
     <row r="331" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A331" s="6">
-        <v>60280</v>
+        <v>60278</v>
       </c>
       <c r="B331" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D331" s="1" t="s">
-        <v>5</v>
+      <c r="D331" s="13" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="332" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A332" s="6">
-        <v>60281</v>
-      </c>
-      <c r="B332" s="8" t="s">
-        <v>336</v>
+        <v>60279</v>
+      </c>
+      <c r="B332" t="s">
+        <v>291</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D332" s="11" t="s">
-        <v>9</v>
+      <c r="D332" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="333" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A333" s="6">
-        <v>60282</v>
-      </c>
-      <c r="B333" s="8" t="s">
-        <v>340</v>
+        <v>60280</v>
+      </c>
+      <c r="B333" t="s">
+        <v>292</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D333" s="11" t="s">
+      <c r="D333" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="334" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A334" s="6">
-        <v>60283</v>
-      </c>
-      <c r="B334" t="s">
-        <v>378</v>
+        <v>60281</v>
+      </c>
+      <c r="B334" s="8" t="s">
+        <v>336</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D334" s="1" t="s">
-        <v>8</v>
+      <c r="D334" s="11" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="335" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A335" s="6">
-        <v>60284</v>
+        <v>60282</v>
       </c>
       <c r="B335" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D335" s="9" t="s">
+      <c r="D335" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="336" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A336" s="6">
-        <v>60285</v>
-      </c>
-      <c r="B336" s="8" t="s">
-        <v>350</v>
+        <v>60283</v>
+      </c>
+      <c r="B336" t="s">
+        <v>378</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D336" s="9" t="s">
-        <v>5</v>
+      <c r="D336" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="337" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A337" s="6">
-        <v>60286</v>
+        <v>60284</v>
       </c>
       <c r="B337" s="8" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>4</v>
@@ -6281,38 +6287,38 @@
     </row>
     <row r="338" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A338" s="6">
-        <v>60287</v>
-      </c>
-      <c r="B338" t="s">
-        <v>377</v>
+        <v>60285</v>
+      </c>
+      <c r="B338" s="8" t="s">
+        <v>350</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D338" s="12" t="s">
+      <c r="D338" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="339" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A339" s="6">
-        <v>60289</v>
-      </c>
-      <c r="B339" t="s">
-        <v>374</v>
+        <v>60286</v>
+      </c>
+      <c r="B339" s="8" t="s">
+        <v>334</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D339" s="12" t="s">
-        <v>9</v>
+      <c r="D339" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="340" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A340" s="6">
-        <v>60290</v>
+        <v>60287</v>
       </c>
       <c r="B340" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>4</v>
@@ -6323,38 +6329,38 @@
     </row>
     <row r="341" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A341" s="6">
-        <v>60291</v>
+        <v>60289</v>
       </c>
       <c r="B341" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D341" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="342" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A342" s="6">
-        <v>60296</v>
+        <v>60290</v>
       </c>
       <c r="B342" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D342" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="343" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A343" s="6">
-        <v>60297</v>
+        <v>60291</v>
       </c>
       <c r="B343" t="s">
-        <v>392</v>
+        <v>376</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>4</v>
@@ -6365,66 +6371,66 @@
     </row>
     <row r="344" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A344" s="6">
-        <v>60299</v>
+        <v>60296</v>
       </c>
       <c r="B344" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D344" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="345" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A345" s="6">
-        <v>61004</v>
+        <v>60297</v>
       </c>
       <c r="B345" t="s">
-        <v>293</v>
+        <v>392</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D345" s="15" t="s">
+      <c r="D345" s="12" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="346" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A346" s="6">
-        <v>61009</v>
+        <v>60299</v>
       </c>
       <c r="B346" t="s">
-        <v>294</v>
+        <v>388</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D346" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="347" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A347" s="6">
-        <v>61012</v>
+        <v>61004</v>
       </c>
       <c r="B347" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D347" s="12" t="s">
-        <v>8</v>
+      <c r="D347" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="348" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A348" s="6">
-        <v>61018</v>
+        <v>61009</v>
       </c>
       <c r="B348" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>4</v>
@@ -6435,10 +6441,10 @@
     </row>
     <row r="349" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A349" s="6">
-        <v>61102</v>
+        <v>61012</v>
       </c>
       <c r="B349" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>4</v>
@@ -6449,24 +6455,24 @@
     </row>
     <row r="350" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A350" s="6">
-        <v>61205</v>
+        <v>61018</v>
       </c>
       <c r="B350" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D350" s="15" t="s">
-        <v>5</v>
+      <c r="D350" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="351" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A351" s="6">
-        <v>70100</v>
+        <v>61102</v>
       </c>
       <c r="B351" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>4</v>
@@ -6477,10 +6483,10 @@
     </row>
     <row r="352" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A352" s="6">
-        <v>70101</v>
+        <v>61205</v>
       </c>
       <c r="B352" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>4</v>
@@ -6491,38 +6497,38 @@
     </row>
     <row r="353" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A353" s="6">
-        <v>70102</v>
+        <v>70100</v>
       </c>
       <c r="B353" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D353" s="15" t="s">
-        <v>5</v>
+      <c r="D353" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="354" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A354" s="6">
-        <v>70103</v>
+        <v>70101</v>
       </c>
       <c r="B354" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D354" s="12" t="s">
-        <v>8</v>
+      <c r="D354" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="355" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A355" s="6">
-        <v>70106</v>
+        <v>70102</v>
       </c>
       <c r="B355" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>4</v>
@@ -6533,10 +6539,10 @@
     </row>
     <row r="356" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A356" s="6">
-        <v>70109</v>
+        <v>70103</v>
       </c>
       <c r="B356" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>4</v>
@@ -6547,10 +6553,10 @@
     </row>
     <row r="357" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A357" s="6">
-        <v>70113</v>
+        <v>70106</v>
       </c>
       <c r="B357" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>4</v>
@@ -6561,66 +6567,66 @@
     </row>
     <row r="358" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A358" s="6">
-        <v>70114</v>
+        <v>70109</v>
       </c>
       <c r="B358" t="s">
-        <v>325</v>
+        <v>304</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D358" s="9" t="s">
-        <v>9</v>
+      <c r="D358" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="359" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A359" s="6">
-        <v>70115</v>
+        <v>70113</v>
       </c>
       <c r="B359" t="s">
-        <v>331</v>
+        <v>305</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D359" s="9" t="s">
-        <v>9</v>
+      <c r="D359" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="360" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A360" s="6">
-        <v>70638</v>
+        <v>70114</v>
       </c>
       <c r="B360" t="s">
-        <v>306</v>
+        <v>325</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D360" s="12" t="s">
-        <v>8</v>
+      <c r="D360" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="361" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A361" s="6">
-        <v>70639</v>
+        <v>70115</v>
       </c>
       <c r="B361" t="s">
-        <v>307</v>
+        <v>331</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D361" s="12" t="s">
-        <v>8</v>
+      <c r="D361" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="362" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A362" s="6">
-        <v>70640</v>
+        <v>70638</v>
       </c>
       <c r="B362" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>4</v>
@@ -6631,10 +6637,10 @@
     </row>
     <row r="363" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A363" s="6">
-        <v>70642</v>
+        <v>70639</v>
       </c>
       <c r="B363" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>4</v>
@@ -6645,10 +6651,10 @@
     </row>
     <row r="364" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A364" s="6">
-        <v>90504</v>
+        <v>70640</v>
       </c>
       <c r="B364" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>4</v>
@@ -6659,10 +6665,10 @@
     </row>
     <row r="365" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A365" s="6">
-        <v>90509</v>
+        <v>70642</v>
       </c>
       <c r="B365" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>4</v>
@@ -6673,24 +6679,24 @@
     </row>
     <row r="366" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A366" s="6">
-        <v>90602</v>
+        <v>90504</v>
       </c>
       <c r="B366" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D366" s="15" t="s">
-        <v>5</v>
+      <c r="D366" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="367" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A367" s="6">
-        <v>90621</v>
+        <v>90509</v>
       </c>
       <c r="B367" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>4</v>
@@ -6701,66 +6707,66 @@
     </row>
     <row r="368" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A368" s="6">
-        <v>90622</v>
+        <v>90602</v>
       </c>
       <c r="B368" t="s">
-        <v>333</v>
+        <v>312</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D368" s="9" t="s">
+      <c r="D368" s="15" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="369" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A369" s="6">
-        <v>90631</v>
-      </c>
-      <c r="B369" s="8" t="s">
-        <v>342</v>
+        <v>90621</v>
+      </c>
+      <c r="B369" t="s">
+        <v>313</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D369" s="9" t="s">
-        <v>5</v>
+      <c r="D369" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="370" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A370" s="6">
-        <v>90658</v>
+        <v>90622</v>
       </c>
       <c r="B370" t="s">
-        <v>314</v>
+        <v>333</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D370" s="12" t="s">
-        <v>8</v>
+      <c r="D370" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="371" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A371" s="6">
-        <v>90660</v>
-      </c>
-      <c r="B371" t="s">
-        <v>315</v>
+        <v>90631</v>
+      </c>
+      <c r="B371" s="8" t="s">
+        <v>342</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D371" s="12" t="s">
-        <v>8</v>
+      <c r="D371" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="372" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A372" s="6">
-        <v>90668</v>
+        <v>90658</v>
       </c>
       <c r="B372" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>4</v>
@@ -6771,10 +6777,10 @@
     </row>
     <row r="373" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A373" s="6">
-        <v>90671</v>
+        <v>90660</v>
       </c>
       <c r="B373" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>4</v>
@@ -6785,10 +6791,10 @@
     </row>
     <row r="374" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A374" s="6">
-        <v>90679</v>
+        <v>90668</v>
       </c>
       <c r="B374" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>4</v>
@@ -6799,10 +6805,10 @@
     </row>
     <row r="375" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A375" s="6">
-        <v>90683</v>
+        <v>90671</v>
       </c>
       <c r="B375" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>4</v>
@@ -6813,10 +6819,10 @@
     </row>
     <row r="376" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A376" s="6">
-        <v>90705</v>
+        <v>90679</v>
       </c>
       <c r="B376" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>4</v>
@@ -6827,10 +6833,10 @@
     </row>
     <row r="377" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A377" s="6">
-        <v>90706</v>
+        <v>90683</v>
       </c>
       <c r="B377" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>4</v>
@@ -6841,10 +6847,10 @@
     </row>
     <row r="378" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A378" s="6">
-        <v>90708</v>
+        <v>90705</v>
       </c>
       <c r="B378" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>4</v>
@@ -6855,10 +6861,10 @@
     </row>
     <row r="379" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A379" s="6">
-        <v>90709</v>
+        <v>90706</v>
       </c>
       <c r="B379" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>4</v>
@@ -6869,10 +6875,10 @@
     </row>
     <row r="380" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A380" s="6">
-        <v>1218</v>
+        <v>90708</v>
       </c>
       <c r="B380" t="s">
-        <v>382</v>
+        <v>322</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>4</v>
@@ -6883,10 +6889,10 @@
     </row>
     <row r="381" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A381" s="6">
-        <v>1959</v>
-      </c>
-      <c r="B381" s="8" t="s">
-        <v>383</v>
+        <v>90709</v>
+      </c>
+      <c r="B381" t="s">
+        <v>323</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>4</v>
@@ -6897,10 +6903,10 @@
     </row>
     <row r="382" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A382" s="6">
-        <v>5625</v>
-      </c>
-      <c r="B382" s="8" t="s">
-        <v>384</v>
+        <v>1218</v>
+      </c>
+      <c r="B382" t="s">
+        <v>382</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>4</v>
@@ -6911,10 +6917,10 @@
     </row>
     <row r="383" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A383" s="6">
-        <v>1817</v>
+        <v>1959</v>
       </c>
       <c r="B383" s="8" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>4</v>
@@ -6925,10 +6931,10 @@
     </row>
     <row r="384" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A384" s="6">
-        <v>5737</v>
+        <v>5625</v>
       </c>
       <c r="B384" s="8" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>4</v>
@@ -6939,34 +6945,62 @@
     </row>
     <row r="385" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A385" s="6">
-        <v>60295</v>
+        <v>1817</v>
       </c>
       <c r="B385" s="8" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D385" s="9" t="s">
-        <v>9</v>
+      <c r="D385" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="386" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A386" s="6">
+        <v>5737</v>
+      </c>
+      <c r="B386" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="C386" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D386" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A387" s="6">
+        <v>60295</v>
+      </c>
+      <c r="B387" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="C387" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D387" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="388" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A388" s="6">
         <v>1045</v>
       </c>
-      <c r="B386" s="8" t="s">
+      <c r="B388" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="C386" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D386" s="9" t="s">
+      <c r="C388" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D388" s="9" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D334"/>
+  <autoFilter ref="A1:D336"/>
   <sortState ref="A2:D374">
     <sortCondition ref="A277"/>
   </sortState>

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$336</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$338</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1165" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1171" uniqueCount="398">
   <si>
     <t>CUENTA</t>
   </si>
@@ -1207,6 +1207,15 @@
   </si>
   <si>
     <t>FERRETERIA LIBER</t>
+  </si>
+  <si>
+    <t>FERRETERIA GRACIELA</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>DEPOSITO</t>
   </si>
 </sst>
 </file>
@@ -1559,7 +1568,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D388"/>
+  <dimension ref="A1:D390"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -1583,38 +1592,38 @@
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B3" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4">
-        <v>5</v>
-      </c>
-      <c r="B3" s="1" t="s">
+      <c r="C3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
+        <v>5</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="5">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
@@ -1625,10 +1634,10 @@
     </row>
     <row r="5" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
-        <v>12</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>211</v>
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>4</v>
@@ -1639,24 +1648,24 @@
     </row>
     <row r="6" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
+        <v>12</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <v>20</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B7" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="6">
-        <v>27</v>
-      </c>
-      <c r="B7" t="s">
-        <v>142</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>4</v>
@@ -1667,10 +1676,10 @@
     </row>
     <row r="8" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>142</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>4</v>
@@ -1681,10 +1690,10 @@
     </row>
     <row r="9" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
-        <v>233</v>
+        <v>33</v>
       </c>
       <c r="B9" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>4</v>
@@ -1695,10 +1704,10 @@
     </row>
     <row r="10" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>4</v>
@@ -1709,10 +1718,10 @@
     </row>
     <row r="11" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="B11" t="s">
-        <v>157</v>
+        <v>62</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>4</v>
@@ -1723,10 +1732,10 @@
     </row>
     <row r="12" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>157</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>4</v>
@@ -1737,10 +1746,10 @@
     </row>
     <row r="13" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="B13" t="s">
-        <v>212</v>
+        <v>25</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>4</v>
@@ -1751,10 +1760,10 @@
     </row>
     <row r="14" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
-        <v>308</v>
+        <v>265</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>212</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>4</v>
@@ -1765,10 +1774,10 @@
     </row>
     <row r="15" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
-        <v>920</v>
+        <v>308</v>
       </c>
       <c r="B15" t="s">
-        <v>195</v>
+        <v>27</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>4</v>
@@ -1779,66 +1788,66 @@
     </row>
     <row r="16" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B16" t="s">
-        <v>393</v>
+        <v>195</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
-        <v>936</v>
+        <v>921</v>
       </c>
       <c r="B17" t="s">
-        <v>86</v>
+        <v>393</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="B18" t="s">
-        <v>185</v>
+        <v>86</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>5</v>
+      <c r="D18" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B19" t="s">
-        <v>41</v>
+        <v>185</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>8</v>
+      <c r="D19" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B20" t="s">
-        <v>128</v>
+        <v>41</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>4</v>
@@ -1849,38 +1858,38 @@
     </row>
     <row r="21" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
-        <v>946</v>
+        <v>940</v>
       </c>
       <c r="B21" t="s">
-        <v>7</v>
+        <v>128</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D21" t="s">
-        <v>9</v>
+      <c r="D21" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B22" t="s">
-        <v>200</v>
+        <v>7</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D22" s="1" t="s">
-        <v>8</v>
+      <c r="D22" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="B23" t="s">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>4</v>
@@ -1891,10 +1900,10 @@
     </row>
     <row r="24" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="B24" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>4</v>
@@ -1905,10 +1914,10 @@
     </row>
     <row r="25" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B25" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>4</v>
@@ -1919,38 +1928,38 @@
     </row>
     <row r="26" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B26" t="s">
-        <v>64</v>
+        <v>147</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D26" t="s">
-        <v>9</v>
+      <c r="D26" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="6">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="B27" t="s">
-        <v>129</v>
+        <v>64</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>8</v>
+      <c r="D27" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B28" t="s">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>4</v>
@@ -1961,10 +1970,10 @@
     </row>
     <row r="29" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="6">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B29" t="s">
-        <v>158</v>
+        <v>102</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>4</v>
@@ -1975,38 +1984,38 @@
     </row>
     <row r="30" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="B30" t="s">
-        <v>6</v>
+        <v>158</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>5</v>
+      <c r="D30" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="B31" t="s">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D31" s="1" t="s">
-        <v>8</v>
+      <c r="D31" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="B32" t="s">
-        <v>140</v>
+        <v>55</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>4</v>
@@ -2017,24 +2026,24 @@
     </row>
     <row r="33" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="6">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B33" t="s">
-        <v>21</v>
+        <v>140</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>5</v>
+      <c r="D33" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="6">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="B34" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>4</v>
@@ -2045,66 +2054,66 @@
     </row>
     <row r="35" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="6">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="B35" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D35" s="1" t="s">
-        <v>8</v>
+      <c r="D35" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="B36" t="s">
-        <v>226</v>
+        <v>87</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D36" t="s">
-        <v>9</v>
+      <c r="D36" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="6">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="B37" t="s">
-        <v>174</v>
+        <v>226</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D37" s="3" t="s">
-        <v>5</v>
+      <c r="D37" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="6">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B38" t="s">
-        <v>137</v>
+        <v>174</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D38" s="1" t="s">
-        <v>8</v>
+      <c r="D38" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="6">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B39" t="s">
-        <v>172</v>
+        <v>137</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>4</v>
@@ -2115,10 +2124,10 @@
     </row>
     <row r="40" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="6">
-        <v>980</v>
+        <v>974</v>
       </c>
       <c r="B40" t="s">
-        <v>133</v>
+        <v>172</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>4</v>
@@ -2129,24 +2138,24 @@
     </row>
     <row r="41" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="6">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="B41" t="s">
-        <v>197</v>
+        <v>133</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>5</v>
+      <c r="D41" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="6">
-        <v>987</v>
+        <v>982</v>
       </c>
       <c r="B42" t="s">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>4</v>
@@ -2157,24 +2166,24 @@
     </row>
     <row r="43" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="6">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B43" t="s">
-        <v>191</v>
+        <v>80</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D43" s="1" t="s">
-        <v>8</v>
+      <c r="D43" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="6">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="B44" t="s">
-        <v>66</v>
+        <v>191</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>4</v>
@@ -2185,10 +2194,10 @@
     </row>
     <row r="45" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="6">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="B45" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>4</v>
@@ -2199,10 +2208,10 @@
     </row>
     <row r="46" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="6">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B46" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>4</v>
@@ -2213,10 +2222,10 @@
     </row>
     <row r="47" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="6">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="B47" t="s">
-        <v>44</v>
+        <v>97</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>4</v>
@@ -2227,10 +2236,10 @@
     </row>
     <row r="48" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="6">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B48" t="s">
-        <v>99</v>
+        <v>44</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>4</v>
@@ -2241,38 +2250,38 @@
     </row>
     <row r="49" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="6">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B49" t="s">
-        <v>180</v>
+        <v>99</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D49" t="s">
-        <v>9</v>
+      <c r="D49" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="6">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B50" t="s">
-        <v>222</v>
+        <v>180</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D50" s="1" t="s">
-        <v>8</v>
+      <c r="D50" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="6">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B51" t="s">
-        <v>75</v>
+        <v>222</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>4</v>
@@ -2283,10 +2292,10 @@
     </row>
     <row r="52" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="6">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B52" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>4</v>
@@ -2297,10 +2306,10 @@
     </row>
     <row r="53" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="6">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="B53" t="s">
-        <v>182</v>
+        <v>46</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>4</v>
@@ -2311,38 +2320,38 @@
     </row>
     <row r="54" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="6">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B54" t="s">
-        <v>115</v>
+        <v>182</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>5</v>
+      <c r="D54" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B55" t="s">
-        <v>214</v>
+        <v>115</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D55" s="1" t="s">
-        <v>8</v>
+      <c r="D55" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="6">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="B56" t="s">
-        <v>74</v>
+        <v>214</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>4</v>
@@ -2353,24 +2362,24 @@
     </row>
     <row r="57" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="6">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B57" t="s">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D57" t="s">
-        <v>9</v>
+      <c r="D57" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="6">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="B58" t="s">
-        <v>189</v>
+        <v>109</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>4</v>
@@ -2381,24 +2390,24 @@
     </row>
     <row r="59" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="6">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B59" t="s">
-        <v>152</v>
+        <v>189</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D59" s="1" t="s">
-        <v>8</v>
+      <c r="D59" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="6">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="B60" t="s">
-        <v>35</v>
+        <v>152</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>4</v>
@@ -2409,52 +2418,52 @@
     </row>
     <row r="61" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="6">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="B61" t="s">
-        <v>362</v>
+        <v>35</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D61" s="11" t="s">
-        <v>5</v>
+      <c r="D61" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="6">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B62" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D62" s="14" t="s">
+      <c r="D62" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="6">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="B63" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D63" s="11" t="s">
+      <c r="D63" s="14" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="6">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B64" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>4</v>
@@ -2465,136 +2474,136 @@
     </row>
     <row r="65" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="6">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B65" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="6">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B66" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D66" s="14" t="s">
-        <v>5</v>
+      <c r="D66" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="6">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B67" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D67" s="11" t="s">
+      <c r="D67" s="14" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="6">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B68" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D68" s="14" t="s">
-        <v>8</v>
+      <c r="D68" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="6">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B69" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D69" s="11" t="s">
-        <v>5</v>
+      <c r="D69" s="14" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="6">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B70" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D70" s="14" t="s">
+      <c r="D70" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="6">
-        <v>1031</v>
-      </c>
-      <c r="B71" s="8" t="s">
-        <v>346</v>
+        <v>1030</v>
+      </c>
+      <c r="B71" t="s">
+        <v>356</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D71" s="14" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="6">
-        <v>1032</v>
-      </c>
-      <c r="B72" t="s">
-        <v>369</v>
+        <v>1031</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>346</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="6">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B73" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D73" s="11" t="s">
+      <c r="D73" s="14" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="6">
-        <v>1034</v>
-      </c>
-      <c r="B74" s="8" t="s">
-        <v>373</v>
+        <v>1033</v>
+      </c>
+      <c r="B74" t="s">
+        <v>357</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>4</v>
@@ -2605,10 +2614,10 @@
     </row>
     <row r="75" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="6">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>345</v>
+        <v>373</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>4</v>
@@ -2619,10 +2628,10 @@
     </row>
     <row r="76" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="6">
-        <v>1036</v>
-      </c>
-      <c r="B76" t="s">
-        <v>358</v>
+        <v>1035</v>
+      </c>
+      <c r="B76" s="8" t="s">
+        <v>345</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>4</v>
@@ -2633,10 +2642,10 @@
     </row>
     <row r="77" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="6">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="B77" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>4</v>
@@ -2647,10 +2656,10 @@
     </row>
     <row r="78" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="6">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B78" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>4</v>
@@ -2661,10 +2670,10 @@
     </row>
     <row r="79" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="6">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="B79" t="s">
-        <v>371</v>
+        <v>352</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>4</v>
@@ -2675,80 +2684,80 @@
     </row>
     <row r="80" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="6">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="B80" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D80" s="11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="6">
-        <v>1044</v>
+        <v>1040</v>
       </c>
       <c r="B81" t="s">
-        <v>394</v>
+        <v>372</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D81" s="11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="6">
-        <v>1416</v>
+        <v>1044</v>
       </c>
       <c r="B82" t="s">
-        <v>217</v>
+        <v>394</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D82" s="1" t="s">
-        <v>8</v>
+      <c r="D82" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="6">
-        <v>10107</v>
+        <v>1416</v>
       </c>
       <c r="B83" t="s">
-        <v>96</v>
+        <v>217</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D83" t="s">
-        <v>9</v>
+      <c r="D83" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="6">
-        <v>10137</v>
+        <v>10107</v>
       </c>
       <c r="B84" t="s">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D84" s="1" t="s">
-        <v>8</v>
+      <c r="D84" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="6">
-        <v>10157</v>
+        <v>10137</v>
       </c>
       <c r="B85" t="s">
-        <v>183</v>
+        <v>123</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>4</v>
@@ -2759,10 +2768,10 @@
     </row>
     <row r="86" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="6">
-        <v>10158</v>
+        <v>10157</v>
       </c>
       <c r="B86" t="s">
-        <v>65</v>
+        <v>183</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>4</v>
@@ -2773,108 +2782,108 @@
     </row>
     <row r="87" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="6">
-        <v>10160</v>
+        <v>10158</v>
       </c>
       <c r="B87" t="s">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D87" s="13" t="s">
-        <v>5</v>
+      <c r="D87" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="6">
-        <v>10162</v>
+        <v>10160</v>
       </c>
       <c r="B88" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D88" s="1" t="s">
-        <v>8</v>
+      <c r="D88" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="6">
-        <v>10163</v>
+        <v>10162</v>
       </c>
       <c r="B89" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D89" s="13" t="s">
-        <v>5</v>
+      <c r="D89" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="6">
-        <v>10165</v>
+        <v>10163</v>
       </c>
       <c r="B90" t="s">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D90" s="1" t="s">
-        <v>8</v>
+      <c r="D90" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="6">
-        <v>10166</v>
-      </c>
-      <c r="B91" s="8" t="s">
-        <v>348</v>
+        <v>10165</v>
+      </c>
+      <c r="B91" t="s">
+        <v>19</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D91" s="11" t="s">
+      <c r="D91" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="6">
-        <v>10167</v>
-      </c>
-      <c r="B92" t="s">
-        <v>39</v>
+        <v>10166</v>
+      </c>
+      <c r="B92" s="8" t="s">
+        <v>348</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D92" s="13" t="s">
-        <v>5</v>
+      <c r="D92" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="6">
-        <v>10424</v>
+        <v>10167</v>
       </c>
       <c r="B93" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D93" s="17" t="s">
-        <v>9</v>
+      <c r="D93" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="6">
-        <v>10425</v>
+        <v>10424</v>
       </c>
       <c r="B94" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>4</v>
@@ -2885,24 +2894,24 @@
     </row>
     <row r="95" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="6">
-        <v>20094</v>
+        <v>10425</v>
       </c>
       <c r="B95" t="s">
-        <v>198</v>
+        <v>15</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D95" s="10" t="s">
-        <v>8</v>
+      <c r="D95" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="6">
-        <v>20095</v>
+        <v>20094</v>
       </c>
       <c r="B96" t="s">
-        <v>153</v>
+        <v>198</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>4</v>
@@ -2913,66 +2922,66 @@
     </row>
     <row r="97" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="6">
-        <v>20096</v>
+        <v>20095</v>
       </c>
       <c r="B97" t="s">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D97" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="6">
-        <v>20100</v>
+        <v>20096</v>
       </c>
       <c r="B98" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D98" s="1" t="s">
-        <v>8</v>
+      <c r="D98" s="10" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="6">
-        <v>20101</v>
+        <v>20100</v>
       </c>
       <c r="B99" t="s">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="6">
-        <v>20103</v>
+        <v>20101</v>
       </c>
       <c r="B100" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="6">
-        <v>20106</v>
+        <v>20103</v>
       </c>
       <c r="B101" t="s">
-        <v>155</v>
+        <v>81</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>4</v>
@@ -2983,80 +2992,80 @@
     </row>
     <row r="102" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="6">
-        <v>20108</v>
+        <v>20106</v>
       </c>
       <c r="B102" t="s">
-        <v>219</v>
+        <v>155</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D102" s="10" t="s">
+      <c r="D102" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="6">
-        <v>20109</v>
+        <v>20108</v>
       </c>
       <c r="B103" t="s">
-        <v>53</v>
+        <v>219</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D103" s="1" t="s">
+      <c r="D103" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="6">
-        <v>20110</v>
+        <v>20109</v>
       </c>
       <c r="B104" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D104" s="13" t="s">
-        <v>5</v>
+      <c r="D104" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="6">
-        <v>20113</v>
+        <v>20110</v>
       </c>
       <c r="B105" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D105" s="10" t="s">
-        <v>8</v>
+      <c r="D105" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="6">
-        <v>20114</v>
+        <v>20113</v>
       </c>
       <c r="B106" t="s">
-        <v>126</v>
+        <v>93</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D106" s="1" t="s">
+      <c r="D106" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="6">
-        <v>20116</v>
+        <v>20114</v>
       </c>
       <c r="B107" t="s">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>4</v>
@@ -3067,10 +3076,10 @@
     </row>
     <row r="108" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="6">
-        <v>20117</v>
+        <v>20116</v>
       </c>
       <c r="B108" t="s">
-        <v>186</v>
+        <v>73</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>4</v>
@@ -3081,10 +3090,10 @@
     </row>
     <row r="109" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="6">
-        <v>20118</v>
+        <v>20117</v>
       </c>
       <c r="B109" t="s">
-        <v>160</v>
+        <v>186</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>4</v>
@@ -3095,10 +3104,10 @@
     </row>
     <row r="110" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="6">
-        <v>20120</v>
+        <v>20118</v>
       </c>
       <c r="B110" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>4</v>
@@ -3109,10 +3118,10 @@
     </row>
     <row r="111" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="6">
-        <v>20121</v>
+        <v>20120</v>
       </c>
       <c r="B111" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>4</v>
@@ -3123,38 +3132,38 @@
     </row>
     <row r="112" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="6">
-        <v>20125</v>
+        <v>20121</v>
       </c>
       <c r="B112" t="s">
-        <v>88</v>
+        <v>159</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D112" s="10" t="s">
+      <c r="D112" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="6">
-        <v>20127</v>
+        <v>20125</v>
       </c>
       <c r="B113" t="s">
-        <v>168</v>
+        <v>88</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D113" s="1" t="s">
+      <c r="D113" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="6">
-        <v>20128</v>
+        <v>20127</v>
       </c>
       <c r="B114" t="s">
-        <v>208</v>
+        <v>168</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>4</v>
@@ -3165,52 +3174,52 @@
     </row>
     <row r="115" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="6">
-        <v>20129</v>
+        <v>20128</v>
       </c>
       <c r="B115" t="s">
-        <v>326</v>
+        <v>208</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D115" s="10" t="s">
+      <c r="D115" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="6">
-        <v>20137</v>
+        <v>20129</v>
       </c>
       <c r="B116" t="s">
-        <v>79</v>
+        <v>326</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D116" s="3" t="s">
-        <v>5</v>
+      <c r="D116" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="6">
-        <v>20138</v>
+        <v>20137</v>
       </c>
       <c r="B117" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D117" s="13" t="s">
+      <c r="D117" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="6">
-        <v>20140</v>
+        <v>20138</v>
       </c>
       <c r="B118" t="s">
-        <v>218</v>
+        <v>113</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>4</v>
@@ -3221,24 +3230,24 @@
     </row>
     <row r="119" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="6">
-        <v>20142</v>
+        <v>20140</v>
       </c>
       <c r="B119" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D119" s="1" t="s">
-        <v>8</v>
+      <c r="D119" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="6">
-        <v>20146</v>
+        <v>20142</v>
       </c>
       <c r="B120" t="s">
-        <v>148</v>
+        <v>193</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>4</v>
@@ -3249,10 +3258,10 @@
     </row>
     <row r="121" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="6">
-        <v>20148</v>
+        <v>20146</v>
       </c>
       <c r="B121" t="s">
-        <v>38</v>
+        <v>148</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>4</v>
@@ -3263,52 +3272,52 @@
     </row>
     <row r="122" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="6">
-        <v>20156</v>
+        <v>20148</v>
       </c>
       <c r="B122" t="s">
-        <v>179</v>
+        <v>38</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D122" s="10" t="s">
+      <c r="D122" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="6">
-        <v>20159</v>
+        <v>20156</v>
       </c>
       <c r="B123" t="s">
-        <v>120</v>
+        <v>179</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D123" s="17" t="s">
-        <v>9</v>
+      <c r="D123" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="6">
-        <v>20160</v>
+        <v>20159</v>
       </c>
       <c r="B124" t="s">
-        <v>224</v>
+        <v>120</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D124" s="10" t="s">
-        <v>8</v>
+      <c r="D124" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="6">
-        <v>20163</v>
+        <v>20160</v>
       </c>
       <c r="B125" t="s">
-        <v>23</v>
+        <v>224</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>4</v>
@@ -3319,52 +3328,52 @@
     </row>
     <row r="126" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="6">
-        <v>20164</v>
+        <v>20163</v>
       </c>
       <c r="B126" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D126" t="s">
-        <v>9</v>
+      <c r="D126" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="6">
-        <v>20165</v>
+        <v>20164</v>
       </c>
       <c r="B127" t="s">
-        <v>131</v>
+        <v>18</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D127" s="10" t="s">
-        <v>8</v>
+      <c r="D127" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="6">
-        <v>20166</v>
+        <v>20165</v>
       </c>
       <c r="B128" t="s">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D128" s="1" t="s">
+      <c r="D128" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="6">
-        <v>20169</v>
+        <v>20166</v>
       </c>
       <c r="B129" t="s">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>4</v>
@@ -3375,38 +3384,38 @@
     </row>
     <row r="130" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="6">
-        <v>20173</v>
+        <v>20169</v>
       </c>
       <c r="B130" t="s">
-        <v>112</v>
+        <v>151</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D130" s="10" t="s">
+      <c r="D130" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="6">
-        <v>20174</v>
+        <v>20173</v>
       </c>
       <c r="B131" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D131" s="1" t="s">
+      <c r="D131" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="6">
-        <v>20178</v>
+        <v>20174</v>
       </c>
       <c r="B132" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>4</v>
@@ -3417,80 +3426,80 @@
     </row>
     <row r="133" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="6">
-        <v>20179</v>
+        <v>20178</v>
       </c>
       <c r="B133" t="s">
-        <v>171</v>
+        <v>117</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D133" t="s">
-        <v>9</v>
+      <c r="D133" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="6">
-        <v>20180</v>
+        <v>20179</v>
       </c>
       <c r="B134" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D134" s="1" t="s">
-        <v>8</v>
+      <c r="D134" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="6">
-        <v>20183</v>
+        <v>20180</v>
       </c>
       <c r="B135" t="s">
-        <v>370</v>
+        <v>149</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D135" s="14" t="s">
-        <v>5</v>
+      <c r="D135" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="6">
-        <v>20189</v>
+        <v>20183</v>
       </c>
       <c r="B136" t="s">
-        <v>329</v>
+        <v>370</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D136" s="1" t="s">
-        <v>8</v>
+      <c r="D136" s="14" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="6">
-        <v>20200</v>
+        <v>20189</v>
       </c>
       <c r="B137" t="s">
-        <v>83</v>
+        <v>329</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D137" s="13" t="s">
-        <v>5</v>
+      <c r="D137" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="6">
-        <v>20201</v>
+        <v>20200</v>
       </c>
       <c r="B138" t="s">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>4</v>
@@ -3501,150 +3510,150 @@
     </row>
     <row r="139" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="6">
-        <v>20204</v>
+        <v>20201</v>
       </c>
       <c r="B139" t="s">
-        <v>57</v>
+        <v>145</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D139" s="10" t="s">
-        <v>8</v>
+      <c r="D139" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="6">
-        <v>20205</v>
+        <v>20204</v>
       </c>
       <c r="B140" t="s">
-        <v>206</v>
+        <v>57</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D140" s="1" t="s">
-        <v>9</v>
+      <c r="D140" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="6">
-        <v>20211</v>
+        <v>20205</v>
       </c>
       <c r="B141" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D141" s="10" t="s">
-        <v>8</v>
+      <c r="D141" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="6">
-        <v>20224</v>
+        <v>20211</v>
       </c>
       <c r="B142" t="s">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D142" s="1" t="s">
+      <c r="D142" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="6">
-        <v>20227</v>
+        <v>20224</v>
       </c>
       <c r="B143" t="s">
-        <v>192</v>
+        <v>85</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D143" s="10" t="s">
+      <c r="D143" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="6">
-        <v>20228</v>
+        <v>20227</v>
       </c>
       <c r="B144" t="s">
-        <v>91</v>
+        <v>192</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D144" s="13" t="s">
-        <v>5</v>
+      <c r="D144" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="6">
-        <v>20230</v>
+        <v>20228</v>
       </c>
       <c r="B145" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D145" s="10" t="s">
-        <v>8</v>
+      <c r="D145" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="6">
-        <v>20234</v>
+        <v>20230</v>
       </c>
       <c r="B146" t="s">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D146" s="13" t="s">
-        <v>5</v>
+      <c r="D146" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="6">
-        <v>20236</v>
+        <v>20234</v>
       </c>
       <c r="B147" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D147" s="3" t="s">
+      <c r="D147" s="13" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="6">
-        <v>20238</v>
+        <v>20236</v>
       </c>
       <c r="B148" t="s">
-        <v>139</v>
+        <v>31</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D148" s="13" t="s">
+      <c r="D148" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="6">
-        <v>20241</v>
+        <v>20238</v>
       </c>
       <c r="B149" t="s">
-        <v>22</v>
+        <v>139</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>4</v>
@@ -3655,24 +3664,24 @@
     </row>
     <row r="150" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="6">
-        <v>20242</v>
+        <v>20241</v>
       </c>
       <c r="B150" t="s">
-        <v>216</v>
+        <v>22</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D150" s="10" t="s">
-        <v>8</v>
+      <c r="D150" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="6">
-        <v>20244</v>
+        <v>20242</v>
       </c>
       <c r="B151" t="s">
-        <v>124</v>
+        <v>216</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>4</v>
@@ -3683,108 +3692,108 @@
     </row>
     <row r="152" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="6">
-        <v>20246</v>
+        <v>20244</v>
       </c>
       <c r="B152" t="s">
-        <v>14</v>
+        <v>124</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D152" s="13" t="s">
-        <v>5</v>
+      <c r="D152" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="6">
-        <v>20249</v>
+        <v>20246</v>
       </c>
       <c r="B153" t="s">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D153" s="10" t="s">
-        <v>8</v>
+      <c r="D153" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="6">
-        <v>20256</v>
+        <v>20249</v>
       </c>
       <c r="B154" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D154" s="1" t="s">
+      <c r="D154" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="155" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="6">
-        <v>20257</v>
+        <v>20256</v>
       </c>
       <c r="B155" t="s">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D155" s="17" t="s">
-        <v>9</v>
+      <c r="D155" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="156" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="6">
-        <v>20258</v>
+        <v>20257</v>
       </c>
       <c r="B156" t="s">
-        <v>199</v>
+        <v>150</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D156" s="1" t="s">
-        <v>8</v>
+      <c r="D156" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="6">
-        <v>20260</v>
+        <v>20258</v>
       </c>
       <c r="B157" t="s">
-        <v>68</v>
+        <v>199</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D157" s="13" t="s">
-        <v>5</v>
+      <c r="D157" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="6">
-        <v>20261</v>
+        <v>20260</v>
       </c>
       <c r="B158" t="s">
-        <v>207</v>
+        <v>68</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D158" s="10" t="s">
-        <v>8</v>
+      <c r="D158" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="159" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A159" s="6">
-        <v>20262</v>
+        <v>20261</v>
       </c>
       <c r="B159" t="s">
-        <v>92</v>
+        <v>207</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>4</v>
@@ -3795,192 +3804,192 @@
     </row>
     <row r="160" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="6">
-        <v>20268</v>
+        <v>20262</v>
       </c>
       <c r="B160" t="s">
-        <v>201</v>
+        <v>92</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D160" s="1" t="s">
+      <c r="D160" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="161" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="6">
-        <v>20271</v>
+        <v>20268</v>
       </c>
       <c r="B161" t="s">
-        <v>34</v>
+        <v>201</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D161" s="13" t="s">
-        <v>5</v>
+      <c r="D161" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="6">
-        <v>20272</v>
+        <v>20271</v>
       </c>
       <c r="B162" t="s">
-        <v>178</v>
+        <v>34</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D162" s="1" t="s">
-        <v>8</v>
+      <c r="D162" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="163" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="6">
-        <v>20275</v>
+        <v>20272</v>
       </c>
       <c r="B163" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D163" s="13" t="s">
-        <v>5</v>
+      <c r="D163" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="6">
-        <v>20277</v>
+        <v>20275</v>
       </c>
       <c r="B164" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D164" s="1" t="s">
-        <v>8</v>
+      <c r="D164" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="165" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="6">
-        <v>20281</v>
+        <v>20277</v>
       </c>
       <c r="B165" t="s">
-        <v>105</v>
+        <v>154</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D165" s="3" t="s">
-        <v>5</v>
+      <c r="D165" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="6">
-        <v>20282</v>
+        <v>20281</v>
       </c>
       <c r="B166" t="s">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D166" s="1" t="s">
-        <v>9</v>
+      <c r="D166" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="6">
-        <v>20284</v>
+        <v>20282</v>
       </c>
       <c r="B167" t="s">
-        <v>17</v>
+        <v>141</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D167" s="17" t="s">
+      <c r="D167" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="168" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="6">
-        <v>20285</v>
+        <v>20284</v>
       </c>
       <c r="B168" t="s">
-        <v>146</v>
+        <v>17</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D168" s="1" t="s">
-        <v>8</v>
+      <c r="D168" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="6">
-        <v>20289</v>
+        <v>20285</v>
       </c>
       <c r="B169" t="s">
-        <v>52</v>
+        <v>146</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D169" s="3" t="s">
-        <v>5</v>
+      <c r="D169" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A170" s="6">
-        <v>20290</v>
+        <v>20289</v>
       </c>
       <c r="B170" t="s">
-        <v>103</v>
+        <v>52</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D170" s="1" t="s">
-        <v>8</v>
+      <c r="D170" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="171" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="6">
-        <v>20291</v>
+        <v>20290</v>
       </c>
       <c r="B171" t="s">
-        <v>187</v>
+        <v>103</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D171" s="10" t="s">
+      <c r="D171" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="6">
-        <v>20292</v>
+        <v>20291</v>
       </c>
       <c r="B172" t="s">
-        <v>32</v>
+        <v>187</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D172" s="13" t="s">
-        <v>5</v>
+      <c r="D172" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="6">
-        <v>20293</v>
+        <v>20292</v>
       </c>
       <c r="B173" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>4</v>
@@ -3991,52 +4000,52 @@
     </row>
     <row r="174" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="6">
-        <v>20294</v>
+        <v>20293</v>
       </c>
       <c r="B174" t="s">
-        <v>202</v>
+        <v>43</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D174" s="10" t="s">
-        <v>8</v>
+      <c r="D174" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="175" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="6">
-        <v>20296</v>
+        <v>20294</v>
       </c>
       <c r="B175" t="s">
-        <v>144</v>
+        <v>202</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D175" s="13" t="s">
-        <v>5</v>
+      <c r="D175" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="6">
-        <v>20298</v>
+        <v>20296</v>
       </c>
       <c r="B176" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D176" s="1" t="s">
-        <v>8</v>
+      <c r="D176" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="177" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A177" s="6">
-        <v>20299</v>
+        <v>20298</v>
       </c>
       <c r="B177" t="s">
-        <v>58</v>
+        <v>169</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>4</v>
@@ -4047,10 +4056,10 @@
     </row>
     <row r="178" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="6">
-        <v>20301</v>
+        <v>20299</v>
       </c>
       <c r="B178" t="s">
-        <v>134</v>
+        <v>58</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>4</v>
@@ -4061,10 +4070,10 @@
     </row>
     <row r="179" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="6">
-        <v>20303</v>
+        <v>20301</v>
       </c>
       <c r="B179" t="s">
-        <v>37</v>
+        <v>134</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>4</v>
@@ -4075,24 +4084,24 @@
     </row>
     <row r="180" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="6">
-        <v>20309</v>
+        <v>20303</v>
       </c>
       <c r="B180" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D180" s="13" t="s">
-        <v>5</v>
+      <c r="D180" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="6">
-        <v>20310</v>
+        <v>20309</v>
       </c>
       <c r="B181" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>4</v>
@@ -4103,52 +4112,52 @@
     </row>
     <row r="182" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="6">
-        <v>20318</v>
+        <v>20310</v>
       </c>
       <c r="B182" t="s">
-        <v>209</v>
+        <v>59</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D182" s="1" t="s">
-        <v>8</v>
+      <c r="D182" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="183" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="6">
-        <v>20319</v>
+        <v>20318</v>
       </c>
       <c r="B183" t="s">
-        <v>101</v>
+        <v>209</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D183" s="10" t="s">
+      <c r="D183" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="184" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="6">
-        <v>20320</v>
+        <v>20319</v>
       </c>
       <c r="B184" t="s">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D184" s="1" t="s">
+      <c r="D184" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="185" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="6">
-        <v>20324</v>
+        <v>20320</v>
       </c>
       <c r="B185" t="s">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>4</v>
@@ -4159,10 +4168,10 @@
     </row>
     <row r="186" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="6">
-        <v>20331</v>
+        <v>20324</v>
       </c>
       <c r="B186" t="s">
-        <v>51</v>
+        <v>210</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>4</v>
@@ -4173,38 +4182,38 @@
     </row>
     <row r="187" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="6">
-        <v>20333</v>
+        <v>20331</v>
       </c>
       <c r="B187" t="s">
-        <v>136</v>
+        <v>51</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D187" s="13" t="s">
-        <v>5</v>
+      <c r="D187" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="188" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="6">
-        <v>20337</v>
+        <v>20333</v>
       </c>
       <c r="B188" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D188" s="1" t="s">
-        <v>8</v>
+      <c r="D188" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="189" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="6">
-        <v>20343</v>
+        <v>20337</v>
       </c>
       <c r="B189" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>4</v>
@@ -4215,10 +4224,10 @@
     </row>
     <row r="190" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A190" s="6">
-        <v>20344</v>
+        <v>20343</v>
       </c>
       <c r="B190" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>4</v>
@@ -4229,66 +4238,66 @@
     </row>
     <row r="191" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="6">
-        <v>20351</v>
+        <v>20344</v>
       </c>
       <c r="B191" t="s">
-        <v>26</v>
+        <v>127</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D191" s="13" t="s">
-        <v>5</v>
+      <c r="D191" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="192" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="6">
-        <v>20357</v>
+        <v>20351</v>
       </c>
       <c r="B192" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D192" s="1" t="s">
-        <v>8</v>
+      <c r="D192" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="193" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="6">
-        <v>20361</v>
+        <v>20357</v>
       </c>
       <c r="B193" t="s">
-        <v>164</v>
+        <v>56</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D193" s="13" t="s">
-        <v>5</v>
+      <c r="D193" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="194" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="6">
-        <v>20362</v>
+        <v>20361</v>
       </c>
       <c r="B194" t="s">
-        <v>45</v>
+        <v>164</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D194" s="10" t="s">
-        <v>8</v>
+      <c r="D194" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="195" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A195" s="6">
-        <v>20363</v>
+        <v>20362</v>
       </c>
       <c r="B195" t="s">
-        <v>213</v>
+        <v>45</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>4</v>
@@ -4299,38 +4308,38 @@
     </row>
     <row r="196" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="6">
-        <v>20364</v>
+        <v>20363</v>
       </c>
       <c r="B196" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D196" s="13" t="s">
-        <v>5</v>
+      <c r="D196" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="197" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="6">
-        <v>20366</v>
+        <v>20364</v>
       </c>
       <c r="B197" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D197" s="1" t="s">
-        <v>8</v>
+      <c r="D197" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="198" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A198" s="6">
-        <v>20367</v>
+        <v>20366</v>
       </c>
       <c r="B198" t="s">
-        <v>47</v>
+        <v>220</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>4</v>
@@ -4341,10 +4350,10 @@
     </row>
     <row r="199" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="6">
-        <v>20369</v>
+        <v>20367</v>
       </c>
       <c r="B199" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>4</v>
@@ -4355,10 +4364,10 @@
     </row>
     <row r="200" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A200" s="6">
-        <v>20371</v>
+        <v>20369</v>
       </c>
       <c r="B200" t="s">
-        <v>223</v>
+        <v>63</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>4</v>
@@ -4369,52 +4378,52 @@
     </row>
     <row r="201" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="6">
-        <v>20372</v>
+        <v>20371</v>
       </c>
       <c r="B201" t="s">
-        <v>70</v>
+        <v>223</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D201" s="10" t="s">
+      <c r="D201" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="202" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="6">
-        <v>20374</v>
+        <v>20372</v>
       </c>
       <c r="B202" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D202" s="1" t="s">
+      <c r="D202" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="203" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="6">
-        <v>20377</v>
+        <v>20374</v>
       </c>
       <c r="B203" t="s">
-        <v>225</v>
+        <v>61</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D203" s="10" t="s">
+      <c r="D203" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="204" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="6">
-        <v>20379</v>
+        <v>20377</v>
       </c>
       <c r="B204" t="s">
-        <v>49</v>
+        <v>225</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>4</v>
@@ -4425,66 +4434,66 @@
     </row>
     <row r="205" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A205" s="6">
-        <v>20380</v>
+        <v>20379</v>
       </c>
       <c r="B205" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D205" s="13" t="s">
-        <v>5</v>
+      <c r="D205" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="206" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A206" s="6">
-        <v>20381</v>
+        <v>20380</v>
       </c>
       <c r="B206" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D206" s="1" t="s">
-        <v>8</v>
+      <c r="D206" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="207" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A207" s="6">
-        <v>20384</v>
+        <v>20381</v>
       </c>
       <c r="B207" t="s">
-        <v>181</v>
+        <v>60</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D207" s="10" t="s">
+      <c r="D207" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="208" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A208" s="6">
-        <v>20385</v>
+        <v>20384</v>
       </c>
       <c r="B208" t="s">
-        <v>36</v>
+        <v>181</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D208" s="1" t="s">
+      <c r="D208" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="209" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A209" s="6">
-        <v>20386</v>
+        <v>20385</v>
       </c>
       <c r="B209" t="s">
-        <v>119</v>
+        <v>36</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>4</v>
@@ -4495,66 +4504,66 @@
     </row>
     <row r="210" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A210" s="6">
-        <v>20388</v>
+        <v>20386</v>
       </c>
       <c r="B210" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D210" s="10" t="s">
+      <c r="D210" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="211" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="6">
-        <v>20391</v>
+        <v>20388</v>
       </c>
       <c r="B211" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D211" s="1" t="s">
+      <c r="D211" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="212" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A212" s="6">
-        <v>20394</v>
+        <v>20391</v>
       </c>
       <c r="B212" t="s">
-        <v>173</v>
+        <v>106</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D212" s="10" t="s">
+      <c r="D212" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="213" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A213" s="6">
-        <v>20395</v>
+        <v>20394</v>
       </c>
       <c r="B213" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D213" s="1" t="s">
+      <c r="D213" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="214" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A214" s="6">
-        <v>20396</v>
+        <v>20395</v>
       </c>
       <c r="B214" t="s">
-        <v>330</v>
+        <v>161</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>4</v>
@@ -4565,52 +4574,52 @@
     </row>
     <row r="215" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A215" s="6">
-        <v>20397</v>
-      </c>
-      <c r="B215" s="8" t="s">
-        <v>344</v>
+        <v>20396</v>
+      </c>
+      <c r="B215" t="s">
+        <v>330</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D215" s="11" t="s">
-        <v>5</v>
+      <c r="D215" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="216" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A216" s="6">
-        <v>30101</v>
-      </c>
-      <c r="B216" t="s">
-        <v>167</v>
+        <v>20397</v>
+      </c>
+      <c r="B216" s="8" t="s">
+        <v>344</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D216" s="1" t="s">
-        <v>8</v>
+      <c r="D216" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="217" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A217" s="6">
-        <v>40124</v>
+        <v>30101</v>
       </c>
       <c r="B217" t="s">
-        <v>24</v>
+        <v>167</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D217" s="13" t="s">
-        <v>5</v>
+      <c r="D217" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="218" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A218" s="6">
-        <v>40125</v>
+        <v>40124</v>
       </c>
       <c r="B218" t="s">
-        <v>143</v>
+        <v>24</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>4</v>
@@ -4621,24 +4630,24 @@
     </row>
     <row r="219" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A219" s="6">
-        <v>40127</v>
+        <v>40125</v>
       </c>
       <c r="B219" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D219" s="1" t="s">
-        <v>8</v>
+      <c r="D219" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="220" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A220" s="6">
-        <v>40129</v>
+        <v>40127</v>
       </c>
       <c r="B220" t="s">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>4</v>
@@ -4649,24 +4658,24 @@
     </row>
     <row r="221" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A221" s="6">
-        <v>40137</v>
+        <v>40129</v>
       </c>
       <c r="B221" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D221" s="10" t="s">
+      <c r="D221" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="222" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A222" s="6">
-        <v>40139</v>
+        <v>40137</v>
       </c>
       <c r="B222" t="s">
-        <v>327</v>
+        <v>121</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>4</v>
@@ -4677,66 +4686,66 @@
     </row>
     <row r="223" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223" s="6">
-        <v>40140</v>
+        <v>40139</v>
       </c>
       <c r="B223" t="s">
-        <v>170</v>
+        <v>327</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D223" s="1" t="s">
+      <c r="D223" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="224" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="6">
-        <v>40141</v>
+        <v>40140</v>
       </c>
       <c r="B224" t="s">
-        <v>111</v>
+        <v>170</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D224" s="13" t="s">
-        <v>5</v>
+      <c r="D224" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="225" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A225" s="6">
-        <v>40143</v>
+        <v>40141</v>
       </c>
       <c r="B225" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D225" s="10" t="s">
-        <v>8</v>
+      <c r="D225" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="226" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A226" s="6">
-        <v>40144</v>
+        <v>40143</v>
       </c>
       <c r="B226" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D226" s="13" t="s">
-        <v>5</v>
+      <c r="D226" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="227" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A227" s="6">
-        <v>40145</v>
+        <v>40144</v>
       </c>
       <c r="B227" t="s">
-        <v>165</v>
+        <v>107</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>4</v>
@@ -4747,192 +4756,192 @@
     </row>
     <row r="228" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A228" s="6">
-        <v>40150</v>
+        <v>40145</v>
       </c>
       <c r="B228" t="s">
-        <v>221</v>
+        <v>165</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D228" s="10" t="s">
-        <v>8</v>
+      <c r="D228" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="229" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A229" s="6">
-        <v>40151</v>
+        <v>40150</v>
       </c>
       <c r="B229" t="s">
-        <v>54</v>
+        <v>221</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D229" s="1" t="s">
+      <c r="D229" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="230" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A230" s="6">
-        <v>50102</v>
+        <v>40151</v>
       </c>
       <c r="B230" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D230" s="13" t="s">
-        <v>5</v>
+      <c r="D230" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="231" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A231" s="6">
-        <v>50222</v>
+        <v>50102</v>
       </c>
       <c r="B231" t="s">
-        <v>215</v>
+        <v>67</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D231" s="1" t="s">
-        <v>8</v>
+      <c r="D231" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="232" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A232" s="6">
-        <v>50223</v>
+        <v>50222</v>
       </c>
       <c r="B232" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D232" s="10" t="s">
+      <c r="D232" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="233" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A233" s="6">
-        <v>50224</v>
+        <v>50223</v>
       </c>
       <c r="B233" t="s">
-        <v>42</v>
+        <v>194</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D233" s="3" t="s">
-        <v>5</v>
+      <c r="D233" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="234" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A234" s="6">
-        <v>50444</v>
+        <v>50224</v>
       </c>
       <c r="B234" t="s">
-        <v>116</v>
+        <v>42</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D234" s="1" t="s">
-        <v>8</v>
+      <c r="D234" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="235" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A235" s="6">
-        <v>50445</v>
+        <v>50444</v>
       </c>
       <c r="B235" t="s">
-        <v>354</v>
+        <v>116</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D235" s="11" t="s">
-        <v>5</v>
+      <c r="D235" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="236" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A236" s="6">
-        <v>50607</v>
+        <v>50445</v>
       </c>
       <c r="B236" t="s">
-        <v>76</v>
+        <v>354</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D236" s="13" t="s">
+      <c r="D236" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="237" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A237" s="6">
-        <v>50608</v>
+        <v>50607</v>
       </c>
       <c r="B237" t="s">
-        <v>177</v>
+        <v>76</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D237" s="1" t="s">
-        <v>8</v>
+      <c r="D237" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="238" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A238" s="6">
-        <v>50611</v>
-      </c>
-      <c r="B238" s="8" t="s">
-        <v>347</v>
+        <v>50608</v>
+      </c>
+      <c r="B238" t="s">
+        <v>177</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D238" s="14" t="s">
+      <c r="D238" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="239" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A239" s="6">
-        <v>50622</v>
-      </c>
-      <c r="B239" t="s">
-        <v>95</v>
+        <v>50611</v>
+      </c>
+      <c r="B239" s="8" t="s">
+        <v>347</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D239" s="16" t="s">
+      <c r="D239" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="240" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A240" s="6">
-        <v>50623</v>
+        <v>50622</v>
       </c>
       <c r="B240" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D240" s="10" t="s">
+      <c r="D240" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="241" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="6">
-        <v>50625</v>
+        <v>50623</v>
       </c>
       <c r="B241" t="s">
-        <v>204</v>
+        <v>110</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>4</v>
@@ -4943,94 +4952,94 @@
     </row>
     <row r="242" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A242" s="6">
-        <v>50629</v>
+        <v>50625</v>
       </c>
       <c r="B242" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D242" s="1" t="s">
+      <c r="D242" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="243" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A243" s="6">
-        <v>50630</v>
+        <v>50629</v>
       </c>
       <c r="B243" t="s">
-        <v>360</v>
+        <v>188</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D243" s="14" t="s">
+      <c r="D243" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="244" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A244" s="6">
-        <v>50803</v>
+        <v>50630</v>
       </c>
       <c r="B244" t="s">
-        <v>82</v>
+        <v>360</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D244" s="1" t="s">
+      <c r="D244" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="245" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A245" s="6">
-        <v>50805</v>
+        <v>50803</v>
       </c>
       <c r="B245" t="s">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D245" s="10" t="s">
+      <c r="D245" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="246" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A246" s="6">
-        <v>50806</v>
+        <v>50805</v>
       </c>
       <c r="B246" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D246" s="1" t="s">
+      <c r="D246" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="247" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A247" s="6">
-        <v>50808</v>
+        <v>50806</v>
       </c>
       <c r="B247" t="s">
-        <v>16</v>
+        <v>156</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D247" s="13" t="s">
-        <v>5</v>
+      <c r="D247" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="248" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A248" s="6">
-        <v>50809</v>
+        <v>50808</v>
       </c>
       <c r="B248" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>4</v>
@@ -5041,24 +5050,24 @@
     </row>
     <row r="249" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A249" s="6">
-        <v>50810</v>
+        <v>50809</v>
       </c>
       <c r="B249" t="s">
-        <v>175</v>
+        <v>98</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D249" s="1" t="s">
-        <v>8</v>
+      <c r="D249" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="250" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A250" s="6">
-        <v>50812</v>
+        <v>50810</v>
       </c>
       <c r="B250" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>4</v>
@@ -5069,80 +5078,80 @@
     </row>
     <row r="251" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A251" s="6">
-        <v>50813</v>
+        <v>50812</v>
       </c>
       <c r="B251" t="s">
-        <v>71</v>
+        <v>184</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D251" s="17" t="s">
-        <v>9</v>
+      <c r="D251" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="252" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A252" s="6">
-        <v>50815</v>
+        <v>50813</v>
       </c>
       <c r="B252" t="s">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D252" s="10" t="s">
-        <v>8</v>
+      <c r="D252" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="253" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A253" s="6">
-        <v>50816</v>
+        <v>50815</v>
       </c>
       <c r="B253" t="s">
-        <v>205</v>
+        <v>114</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D253" s="1" t="s">
+      <c r="D253" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="254" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="6">
-        <v>50818</v>
+        <v>50816</v>
       </c>
       <c r="B254" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D254" s="13" t="s">
-        <v>5</v>
+      <c r="D254" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="255" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A255" s="6">
-        <v>50819</v>
+        <v>50818</v>
       </c>
       <c r="B255" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D255" s="10" t="s">
-        <v>8</v>
+      <c r="D255" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="256" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A256" s="6">
-        <v>50820</v>
+        <v>50819</v>
       </c>
       <c r="B256" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>4</v>
@@ -5153,66 +5162,66 @@
     </row>
     <row r="257" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A257" s="6">
-        <v>50821</v>
+        <v>50820</v>
       </c>
       <c r="B257" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D257" s="1" t="s">
+      <c r="D257" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="258" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A258" s="6">
-        <v>50823</v>
+        <v>50821</v>
       </c>
       <c r="B258" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D258" s="17" t="s">
-        <v>9</v>
+      <c r="D258" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="259" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A259" s="6">
-        <v>50824</v>
+        <v>50823</v>
       </c>
       <c r="B259" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D259" s="13" t="s">
-        <v>5</v>
+      <c r="D259" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="260" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A260" s="6">
-        <v>50825</v>
+        <v>50824</v>
       </c>
       <c r="B260" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D260" s="10" t="s">
-        <v>8</v>
+      <c r="D260" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="261" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A261" s="6">
-        <v>50826</v>
+        <v>50825</v>
       </c>
       <c r="B261" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>4</v>
@@ -5223,24 +5232,24 @@
     </row>
     <row r="262" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A262" s="6">
-        <v>50827</v>
+        <v>50826</v>
       </c>
       <c r="B262" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D262" s="1" t="s">
+      <c r="D262" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="263" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A263" s="6">
-        <v>50829</v>
+        <v>50827</v>
       </c>
       <c r="B263" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>4</v>
@@ -5251,38 +5260,38 @@
     </row>
     <row r="264" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A264" s="6">
-        <v>50830</v>
+        <v>50829</v>
       </c>
       <c r="B264" t="s">
-        <v>366</v>
+        <v>236</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D264" s="11" t="s">
+      <c r="D264" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="265" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A265" s="6">
-        <v>50831</v>
+        <v>50830</v>
       </c>
       <c r="B265" t="s">
-        <v>351</v>
+        <v>366</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D265" s="11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="266" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A266" s="6">
-        <v>50832</v>
-      </c>
-      <c r="B266" s="8" t="s">
-        <v>349</v>
+        <v>50831</v>
+      </c>
+      <c r="B266" t="s">
+        <v>351</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>4</v>
@@ -5293,10 +5302,10 @@
     </row>
     <row r="267" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A267" s="6">
-        <v>50230</v>
+        <v>50832</v>
       </c>
       <c r="B267" s="8" t="s">
-        <v>379</v>
+        <v>349</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>4</v>
@@ -5307,52 +5316,52 @@
     </row>
     <row r="268" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A268" s="6">
-        <v>60103</v>
-      </c>
-      <c r="B268" t="s">
-        <v>237</v>
+        <v>50230</v>
+      </c>
+      <c r="B268" s="8" t="s">
+        <v>379</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D268" s="13" t="s">
+      <c r="D268" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="269" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A269" s="6">
-        <v>60109</v>
+        <v>60103</v>
       </c>
       <c r="B269" t="s">
-        <v>328</v>
+        <v>237</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D269" s="11" t="s">
-        <v>9</v>
+      <c r="D269" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="270" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A270" s="6">
-        <v>60124</v>
+        <v>60109</v>
       </c>
       <c r="B270" t="s">
-        <v>238</v>
+        <v>328</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D270" s="13" t="s">
-        <v>5</v>
+      <c r="D270" s="11" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="271" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A271" s="6">
-        <v>60125</v>
+        <v>60124</v>
       </c>
       <c r="B271" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>4</v>
@@ -5363,80 +5372,80 @@
     </row>
     <row r="272" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A272" s="6">
-        <v>60126</v>
+        <v>60125</v>
       </c>
       <c r="B272" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D272" s="10" t="s">
-        <v>8</v>
+      <c r="D272" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="273" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A273" s="6">
-        <v>60128</v>
+        <v>60126</v>
       </c>
       <c r="B273" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D273" s="3" t="s">
-        <v>5</v>
+      <c r="D273" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="274" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A274" s="6">
-        <v>60130</v>
+        <v>60128</v>
       </c>
       <c r="B274" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D274" s="1" t="s">
-        <v>8</v>
+      <c r="D274" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="275" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A275" s="6">
-        <v>60133</v>
+        <v>60130</v>
       </c>
       <c r="B275" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D275" s="13" t="s">
-        <v>5</v>
+      <c r="D275" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="276" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A276" s="6">
-        <v>60134</v>
+        <v>60133</v>
       </c>
       <c r="B276" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D276" s="1" t="s">
-        <v>8</v>
+      <c r="D276" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="277" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A277" s="6">
-        <v>60137</v>
+        <v>60134</v>
       </c>
       <c r="B277" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>4</v>
@@ -5447,10 +5456,10 @@
     </row>
     <row r="278" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A278" s="6">
-        <v>60139</v>
+        <v>60137</v>
       </c>
       <c r="B278" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>4</v>
@@ -5461,10 +5470,10 @@
     </row>
     <row r="279" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A279" s="6">
-        <v>60142</v>
+        <v>60139</v>
       </c>
       <c r="B279" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>4</v>
@@ -5475,10 +5484,10 @@
     </row>
     <row r="280" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A280" s="6">
-        <v>60148</v>
+        <v>60142</v>
       </c>
       <c r="B280" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>4</v>
@@ -5489,10 +5498,10 @@
     </row>
     <row r="281" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A281" s="6">
-        <v>60149</v>
+        <v>60148</v>
       </c>
       <c r="B281" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>4</v>
@@ -5503,66 +5512,66 @@
     </row>
     <row r="282" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A282" s="6">
-        <v>60150</v>
+        <v>60149</v>
       </c>
       <c r="B282" t="s">
-        <v>332</v>
+        <v>249</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D282" s="13" t="s">
-        <v>5</v>
+      <c r="D282" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="283" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A283" s="6">
-        <v>60158</v>
+        <v>60150</v>
       </c>
       <c r="B283" t="s">
-        <v>250</v>
+        <v>332</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D283" s="10" t="s">
-        <v>8</v>
+      <c r="D283" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="284" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A284" s="6">
-        <v>60159</v>
+        <v>60158</v>
       </c>
       <c r="B284" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D284" s="1" t="s">
+      <c r="D284" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="285" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A285" s="6">
-        <v>60162</v>
+        <v>60159</v>
       </c>
       <c r="B285" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D285" s="13" t="s">
-        <v>5</v>
+      <c r="D285" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="286" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A286" s="6">
-        <v>60163</v>
+        <v>60162</v>
       </c>
       <c r="B286" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>4</v>
@@ -5573,24 +5582,24 @@
     </row>
     <row r="287" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A287" s="6">
-        <v>60165</v>
+        <v>60163</v>
       </c>
       <c r="B287" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D287" s="1" t="s">
-        <v>8</v>
+      <c r="D287" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="288" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A288" s="6">
-        <v>60169</v>
+        <v>60165</v>
       </c>
       <c r="B288" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>4</v>
@@ -5601,52 +5610,52 @@
     </row>
     <row r="289" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A289" s="6">
-        <v>60170</v>
-      </c>
-      <c r="B289" s="8" t="s">
-        <v>337</v>
+        <v>60169</v>
+      </c>
+      <c r="B289" t="s">
+        <v>255</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D289" s="11" t="s">
+      <c r="D289" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="290" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A290" s="6">
-        <v>60172</v>
-      </c>
-      <c r="B290" t="s">
-        <v>256</v>
+        <v>60170</v>
+      </c>
+      <c r="B290" s="8" t="s">
+        <v>337</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D290" s="1" t="s">
+      <c r="D290" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="291" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A291" s="6">
-        <v>60174</v>
+        <v>60172</v>
       </c>
       <c r="B291" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D291" s="13" t="s">
-        <v>5</v>
+      <c r="D291" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="292" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A292" s="6">
-        <v>60176</v>
+        <v>60174</v>
       </c>
       <c r="B292" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>4</v>
@@ -5657,52 +5666,52 @@
     </row>
     <row r="293" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A293" s="6">
-        <v>60178</v>
+        <v>60176</v>
       </c>
       <c r="B293" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D293" s="1" t="s">
-        <v>8</v>
+      <c r="D293" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="294" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A294" s="6">
-        <v>60180</v>
+        <v>60178</v>
       </c>
       <c r="B294" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D294" s="10" t="s">
+      <c r="D294" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="295" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A295" s="6">
-        <v>60184</v>
+        <v>60180</v>
       </c>
       <c r="B295" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D295" s="1" t="s">
+      <c r="D295" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="296" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A296" s="6">
-        <v>60190</v>
+        <v>60184</v>
       </c>
       <c r="B296" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>4</v>
@@ -5713,24 +5722,24 @@
     </row>
     <row r="297" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A297" s="6">
-        <v>60191</v>
+        <v>60190</v>
       </c>
       <c r="B297" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D297" s="10" t="s">
+      <c r="D297" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="298" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A298" s="6">
-        <v>60192</v>
+        <v>60191</v>
       </c>
       <c r="B298" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>4</v>
@@ -5741,10 +5750,10 @@
     </row>
     <row r="299" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A299" s="6">
-        <v>60195</v>
+        <v>60192</v>
       </c>
       <c r="B299" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>4</v>
@@ -5755,10 +5764,10 @@
     </row>
     <row r="300" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A300" s="6">
-        <v>60196</v>
+        <v>60195</v>
       </c>
       <c r="B300" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>4</v>
@@ -5769,10 +5778,10 @@
     </row>
     <row r="301" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A301" s="6">
-        <v>60198</v>
+        <v>60196</v>
       </c>
       <c r="B301" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>4</v>
@@ -5783,52 +5792,52 @@
     </row>
     <row r="302" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A302" s="6">
-        <v>60201</v>
+        <v>60198</v>
       </c>
       <c r="B302" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D302" t="s">
-        <v>9</v>
+      <c r="D302" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="303" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A303" s="6">
-        <v>60202</v>
+        <v>60201</v>
       </c>
       <c r="B303" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D303" s="13" t="s">
-        <v>5</v>
+      <c r="D303" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="304" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A304" s="6">
-        <v>60204</v>
+        <v>60202</v>
       </c>
       <c r="B304" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D304" s="1" t="s">
-        <v>8</v>
+      <c r="D304" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="305" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A305" s="6">
-        <v>60205</v>
+        <v>60204</v>
       </c>
       <c r="B305" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>4</v>
@@ -5839,10 +5848,10 @@
     </row>
     <row r="306" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A306" s="6">
-        <v>60206</v>
+        <v>60205</v>
       </c>
       <c r="B306" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>4</v>
@@ -5853,164 +5862,164 @@
     </row>
     <row r="307" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A307" s="6">
-        <v>60209</v>
+        <v>60206</v>
       </c>
       <c r="B307" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D307" s="10" t="s">
+      <c r="D307" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="308" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A308" s="6">
-        <v>60211</v>
+        <v>60209</v>
       </c>
       <c r="B308" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D308" s="1" t="s">
+      <c r="D308" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="309" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A309" s="6">
-        <v>60215</v>
+        <v>60211</v>
       </c>
       <c r="B309" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D309" s="10" t="s">
+      <c r="D309" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="310" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A310" s="6">
-        <v>60216</v>
+        <v>60215</v>
       </c>
       <c r="B310" t="s">
-        <v>381</v>
+        <v>275</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D310" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="311" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A311" s="6">
-        <v>60217</v>
+        <v>60216</v>
       </c>
       <c r="B311" t="s">
-        <v>276</v>
+        <v>381</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D311" s="10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="312" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A312" s="6">
-        <v>60219</v>
+        <v>60217</v>
       </c>
       <c r="B312" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D312" s="1" t="s">
+      <c r="D312" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="313" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A313" s="6">
-        <v>60222</v>
+        <v>60219</v>
       </c>
       <c r="B313" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D313" s="10" t="s">
+      <c r="D313" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="314" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A314" s="6">
-        <v>60225</v>
+        <v>60222</v>
       </c>
       <c r="B314" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D314" s="17" t="s">
-        <v>9</v>
+      <c r="D314" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="315" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A315" s="6">
-        <v>60230</v>
+        <v>60225</v>
       </c>
       <c r="B315" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D315" s="10" t="s">
-        <v>8</v>
+      <c r="D315" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="316" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A316" s="6">
-        <v>60241</v>
-      </c>
-      <c r="B316" s="8" t="s">
-        <v>338</v>
+        <v>60230</v>
+      </c>
+      <c r="B316" t="s">
+        <v>280</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D316" s="7" t="s">
-        <v>9</v>
+      <c r="D316" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="317" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A317" s="6">
-        <v>60242</v>
+        <v>60241</v>
       </c>
       <c r="B317" s="8" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D317" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="318" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A318" s="6">
-        <v>60245</v>
+        <v>60242</v>
       </c>
       <c r="B318" s="8" t="s">
-        <v>387</v>
+        <v>341</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>4</v>
@@ -6021,52 +6030,52 @@
     </row>
     <row r="319" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A319" s="6">
-        <v>60250</v>
+        <v>60243</v>
       </c>
       <c r="B319" s="8" t="s">
-        <v>339</v>
+        <v>395</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D319" s="11" t="s">
-        <v>8</v>
+      <c r="D319" s="7" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="320" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A320" s="6">
-        <v>60253</v>
-      </c>
-      <c r="B320" t="s">
-        <v>281</v>
+        <v>60245</v>
+      </c>
+      <c r="B320" s="8" t="s">
+        <v>387</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D320" s="1" t="s">
-        <v>8</v>
+      <c r="D320" s="7" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="321" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A321" s="6">
-        <v>60254</v>
-      </c>
-      <c r="B321" t="s">
-        <v>282</v>
+        <v>60250</v>
+      </c>
+      <c r="B321" s="8" t="s">
+        <v>339</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D321" s="1" t="s">
+      <c r="D321" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="322" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A322" s="6">
-        <v>60257</v>
+        <v>60253</v>
       </c>
       <c r="B322" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>4</v>
@@ -6077,10 +6086,10 @@
     </row>
     <row r="323" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A323" s="6">
-        <v>60258</v>
+        <v>60254</v>
       </c>
       <c r="B323" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>4</v>
@@ -6091,66 +6100,66 @@
     </row>
     <row r="324" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A324" s="6">
-        <v>60266</v>
-      </c>
-      <c r="B324" s="8" t="s">
-        <v>343</v>
+        <v>60257</v>
+      </c>
+      <c r="B324" t="s">
+        <v>283</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D324" s="11" t="s">
+      <c r="D324" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="325" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A325" s="6">
-        <v>60269</v>
+        <v>60258</v>
       </c>
       <c r="B325" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D325" s="10" t="s">
+      <c r="D325" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="326" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A326" s="6">
-        <v>60270</v>
-      </c>
-      <c r="B326" t="s">
-        <v>286</v>
+        <v>60266</v>
+      </c>
+      <c r="B326" s="8" t="s">
+        <v>343</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D326" s="1" t="s">
+      <c r="D326" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="327" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A327" s="6">
-        <v>60272</v>
+        <v>60269</v>
       </c>
       <c r="B327" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D327" s="1" t="s">
+      <c r="D327" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="328" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A328" s="6">
-        <v>60274</v>
+        <v>60270</v>
       </c>
       <c r="B328" t="s">
-        <v>380</v>
+        <v>286</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>4</v>
@@ -6161,10 +6170,10 @@
     </row>
     <row r="329" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A329" s="6">
-        <v>60275</v>
+        <v>60272</v>
       </c>
       <c r="B329" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>4</v>
@@ -6175,10 +6184,10 @@
     </row>
     <row r="330" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A330" s="6">
-        <v>60276</v>
+        <v>60274</v>
       </c>
       <c r="B330" t="s">
-        <v>289</v>
+        <v>380</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>4</v>
@@ -6189,24 +6198,24 @@
     </row>
     <row r="331" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A331" s="6">
-        <v>60278</v>
+        <v>60275</v>
       </c>
       <c r="B331" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D331" s="13" t="s">
+      <c r="D331" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="332" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A332" s="6">
-        <v>60279</v>
+        <v>60276</v>
       </c>
       <c r="B332" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>4</v>
@@ -6217,94 +6226,94 @@
     </row>
     <row r="333" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A333" s="6">
-        <v>60280</v>
+        <v>60278</v>
       </c>
       <c r="B333" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D333" s="1" t="s">
-        <v>5</v>
+      <c r="D333" s="13" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="334" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A334" s="6">
-        <v>60281</v>
-      </c>
-      <c r="B334" s="8" t="s">
-        <v>336</v>
+        <v>60279</v>
+      </c>
+      <c r="B334" t="s">
+        <v>291</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D334" s="11" t="s">
-        <v>9</v>
+      <c r="D334" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="335" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A335" s="6">
-        <v>60282</v>
-      </c>
-      <c r="B335" s="8" t="s">
-        <v>340</v>
+        <v>60280</v>
+      </c>
+      <c r="B335" t="s">
+        <v>292</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D335" s="11" t="s">
+      <c r="D335" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="336" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A336" s="6">
-        <v>60283</v>
-      </c>
-      <c r="B336" t="s">
-        <v>378</v>
+        <v>60281</v>
+      </c>
+      <c r="B336" s="8" t="s">
+        <v>336</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D336" s="1" t="s">
-        <v>8</v>
+      <c r="D336" s="11" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="337" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A337" s="6">
-        <v>60284</v>
+        <v>60282</v>
       </c>
       <c r="B337" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D337" s="9" t="s">
+      <c r="D337" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="338" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A338" s="6">
-        <v>60285</v>
-      </c>
-      <c r="B338" s="8" t="s">
-        <v>350</v>
+        <v>60283</v>
+      </c>
+      <c r="B338" t="s">
+        <v>378</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D338" s="9" t="s">
-        <v>5</v>
+      <c r="D338" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="339" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A339" s="6">
-        <v>60286</v>
+        <v>60284</v>
       </c>
       <c r="B339" s="8" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>4</v>
@@ -6315,38 +6324,38 @@
     </row>
     <row r="340" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A340" s="6">
-        <v>60287</v>
-      </c>
-      <c r="B340" t="s">
-        <v>377</v>
+        <v>60285</v>
+      </c>
+      <c r="B340" s="8" t="s">
+        <v>350</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D340" s="12" t="s">
+      <c r="D340" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="341" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A341" s="6">
-        <v>60289</v>
-      </c>
-      <c r="B341" t="s">
-        <v>374</v>
+        <v>60286</v>
+      </c>
+      <c r="B341" s="8" t="s">
+        <v>334</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D341" s="12" t="s">
-        <v>9</v>
+      <c r="D341" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="342" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A342" s="6">
-        <v>60290</v>
+        <v>60287</v>
       </c>
       <c r="B342" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>4</v>
@@ -6357,38 +6366,38 @@
     </row>
     <row r="343" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A343" s="6">
-        <v>60291</v>
+        <v>60289</v>
       </c>
       <c r="B343" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D343" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="344" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A344" s="6">
-        <v>60296</v>
+        <v>60290</v>
       </c>
       <c r="B344" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D344" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="345" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A345" s="6">
-        <v>60297</v>
+        <v>60291</v>
       </c>
       <c r="B345" t="s">
-        <v>392</v>
+        <v>376</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>4</v>
@@ -6399,66 +6408,66 @@
     </row>
     <row r="346" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A346" s="6">
-        <v>60299</v>
+        <v>60296</v>
       </c>
       <c r="B346" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D346" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="347" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A347" s="6">
-        <v>61004</v>
+        <v>60297</v>
       </c>
       <c r="B347" t="s">
-        <v>293</v>
+        <v>392</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D347" s="15" t="s">
+      <c r="D347" s="12" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="348" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A348" s="6">
-        <v>61009</v>
+        <v>60299</v>
       </c>
       <c r="B348" t="s">
-        <v>294</v>
+        <v>388</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D348" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="349" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A349" s="6">
-        <v>61012</v>
+        <v>61004</v>
       </c>
       <c r="B349" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D349" s="12" t="s">
-        <v>8</v>
+      <c r="D349" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="350" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A350" s="6">
-        <v>61018</v>
+        <v>61009</v>
       </c>
       <c r="B350" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>4</v>
@@ -6469,10 +6478,10 @@
     </row>
     <row r="351" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A351" s="6">
-        <v>61102</v>
+        <v>61012</v>
       </c>
       <c r="B351" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>4</v>
@@ -6483,24 +6492,24 @@
     </row>
     <row r="352" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A352" s="6">
-        <v>61205</v>
+        <v>61018</v>
       </c>
       <c r="B352" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D352" s="15" t="s">
-        <v>5</v>
+      <c r="D352" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="353" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A353" s="6">
-        <v>70100</v>
+        <v>61102</v>
       </c>
       <c r="B353" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>4</v>
@@ -6511,10 +6520,10 @@
     </row>
     <row r="354" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A354" s="6">
-        <v>70101</v>
+        <v>61205</v>
       </c>
       <c r="B354" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>4</v>
@@ -6525,38 +6534,38 @@
     </row>
     <row r="355" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A355" s="6">
-        <v>70102</v>
+        <v>70100</v>
       </c>
       <c r="B355" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D355" s="15" t="s">
-        <v>5</v>
+      <c r="D355" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="356" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A356" s="6">
-        <v>70103</v>
+        <v>70101</v>
       </c>
       <c r="B356" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D356" s="12" t="s">
-        <v>8</v>
+      <c r="D356" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="357" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A357" s="6">
-        <v>70106</v>
+        <v>70102</v>
       </c>
       <c r="B357" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>4</v>
@@ -6567,10 +6576,10 @@
     </row>
     <row r="358" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A358" s="6">
-        <v>70109</v>
+        <v>70103</v>
       </c>
       <c r="B358" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>4</v>
@@ -6581,10 +6590,10 @@
     </row>
     <row r="359" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A359" s="6">
-        <v>70113</v>
+        <v>70106</v>
       </c>
       <c r="B359" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>4</v>
@@ -6595,66 +6604,66 @@
     </row>
     <row r="360" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A360" s="6">
-        <v>70114</v>
+        <v>70109</v>
       </c>
       <c r="B360" t="s">
-        <v>325</v>
+        <v>304</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D360" s="9" t="s">
-        <v>9</v>
+      <c r="D360" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="361" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A361" s="6">
-        <v>70115</v>
+        <v>70113</v>
       </c>
       <c r="B361" t="s">
-        <v>331</v>
+        <v>305</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D361" s="9" t="s">
-        <v>9</v>
+      <c r="D361" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="362" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A362" s="6">
-        <v>70638</v>
+        <v>70114</v>
       </c>
       <c r="B362" t="s">
-        <v>306</v>
+        <v>325</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D362" s="12" t="s">
-        <v>8</v>
+      <c r="D362" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="363" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A363" s="6">
-        <v>70639</v>
+        <v>70115</v>
       </c>
       <c r="B363" t="s">
-        <v>307</v>
+        <v>331</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D363" s="12" t="s">
-        <v>8</v>
+      <c r="D363" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="364" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A364" s="6">
-        <v>70640</v>
+        <v>70638</v>
       </c>
       <c r="B364" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>4</v>
@@ -6665,10 +6674,10 @@
     </row>
     <row r="365" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A365" s="6">
-        <v>70642</v>
+        <v>70639</v>
       </c>
       <c r="B365" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>4</v>
@@ -6679,10 +6688,10 @@
     </row>
     <row r="366" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A366" s="6">
-        <v>90504</v>
+        <v>70640</v>
       </c>
       <c r="B366" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>4</v>
@@ -6693,10 +6702,10 @@
     </row>
     <row r="367" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A367" s="6">
-        <v>90509</v>
+        <v>70642</v>
       </c>
       <c r="B367" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>4</v>
@@ -6707,24 +6716,24 @@
     </row>
     <row r="368" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A368" s="6">
-        <v>90602</v>
+        <v>90504</v>
       </c>
       <c r="B368" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D368" s="15" t="s">
-        <v>5</v>
+      <c r="D368" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="369" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A369" s="6">
-        <v>90621</v>
+        <v>90509</v>
       </c>
       <c r="B369" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>4</v>
@@ -6735,66 +6744,66 @@
     </row>
     <row r="370" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A370" s="6">
-        <v>90622</v>
+        <v>90602</v>
       </c>
       <c r="B370" t="s">
-        <v>333</v>
+        <v>312</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D370" s="9" t="s">
+      <c r="D370" s="15" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="371" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A371" s="6">
-        <v>90631</v>
-      </c>
-      <c r="B371" s="8" t="s">
-        <v>342</v>
+        <v>90621</v>
+      </c>
+      <c r="B371" t="s">
+        <v>313</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D371" s="9" t="s">
-        <v>5</v>
+      <c r="D371" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="372" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A372" s="6">
-        <v>90658</v>
+        <v>90622</v>
       </c>
       <c r="B372" t="s">
-        <v>314</v>
+        <v>333</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D372" s="12" t="s">
-        <v>8</v>
+      <c r="D372" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="373" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A373" s="6">
-        <v>90660</v>
-      </c>
-      <c r="B373" t="s">
-        <v>315</v>
+        <v>90631</v>
+      </c>
+      <c r="B373" s="8" t="s">
+        <v>342</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D373" s="12" t="s">
-        <v>8</v>
+      <c r="D373" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="374" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A374" s="6">
-        <v>90668</v>
+        <v>90658</v>
       </c>
       <c r="B374" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>4</v>
@@ -6805,10 +6814,10 @@
     </row>
     <row r="375" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A375" s="6">
-        <v>90671</v>
+        <v>90660</v>
       </c>
       <c r="B375" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>4</v>
@@ -6819,10 +6828,10 @@
     </row>
     <row r="376" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A376" s="6">
-        <v>90679</v>
+        <v>90668</v>
       </c>
       <c r="B376" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>4</v>
@@ -6833,10 +6842,10 @@
     </row>
     <row r="377" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A377" s="6">
-        <v>90683</v>
+        <v>90671</v>
       </c>
       <c r="B377" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>4</v>
@@ -6847,10 +6856,10 @@
     </row>
     <row r="378" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A378" s="6">
-        <v>90705</v>
+        <v>90679</v>
       </c>
       <c r="B378" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>4</v>
@@ -6861,10 +6870,10 @@
     </row>
     <row r="379" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A379" s="6">
-        <v>90706</v>
+        <v>90683</v>
       </c>
       <c r="B379" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>4</v>
@@ -6875,10 +6884,10 @@
     </row>
     <row r="380" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A380" s="6">
-        <v>90708</v>
+        <v>90705</v>
       </c>
       <c r="B380" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>4</v>
@@ -6889,10 +6898,10 @@
     </row>
     <row r="381" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A381" s="6">
-        <v>90709</v>
+        <v>90706</v>
       </c>
       <c r="B381" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>4</v>
@@ -6903,10 +6912,10 @@
     </row>
     <row r="382" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A382" s="6">
-        <v>1218</v>
+        <v>90708</v>
       </c>
       <c r="B382" t="s">
-        <v>382</v>
+        <v>322</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>4</v>
@@ -6917,10 +6926,10 @@
     </row>
     <row r="383" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A383" s="6">
-        <v>1959</v>
-      </c>
-      <c r="B383" s="8" t="s">
-        <v>383</v>
+        <v>90709</v>
+      </c>
+      <c r="B383" t="s">
+        <v>323</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>4</v>
@@ -6931,10 +6940,10 @@
     </row>
     <row r="384" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A384" s="6">
-        <v>5625</v>
-      </c>
-      <c r="B384" s="8" t="s">
-        <v>384</v>
+        <v>1218</v>
+      </c>
+      <c r="B384" t="s">
+        <v>382</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>4</v>
@@ -6945,10 +6954,10 @@
     </row>
     <row r="385" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A385" s="6">
-        <v>1817</v>
+        <v>1959</v>
       </c>
       <c r="B385" s="8" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>4</v>
@@ -6959,10 +6968,10 @@
     </row>
     <row r="386" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A386" s="6">
-        <v>5737</v>
+        <v>5625</v>
       </c>
       <c r="B386" s="8" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>4</v>
@@ -6973,34 +6982,62 @@
     </row>
     <row r="387" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A387" s="6">
-        <v>60295</v>
+        <v>1817</v>
       </c>
       <c r="B387" s="8" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D387" s="9" t="s">
-        <v>9</v>
+      <c r="D387" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="388" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A388" s="6">
+        <v>5737</v>
+      </c>
+      <c r="B388" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="C388" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D388" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A389" s="6">
+        <v>60295</v>
+      </c>
+      <c r="B389" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="C389" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D389" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A390" s="6">
         <v>1045</v>
       </c>
-      <c r="B388" s="8" t="s">
+      <c r="B390" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="C388" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D388" s="9" t="s">
+      <c r="C390" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D390" s="9" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D336"/>
+  <autoFilter ref="A1:D338"/>
   <sortState ref="A2:D374">
     <sortCondition ref="A277"/>
   </sortState>

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1171" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1171" uniqueCount="397">
   <si>
     <t>CUENTA</t>
   </si>
@@ -1210,9 +1210,6 @@
   </si>
   <si>
     <t>FERRETERIA GRACIELA</t>
-  </si>
-  <si>
-    <t>C</t>
   </si>
   <si>
     <t>DEPOSITO</t>
@@ -1595,7 +1592,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>4</v>
@@ -6039,7 +6036,7 @@
         <v>4</v>
       </c>
       <c r="D319" s="7" t="s">
-        <v>396</v>
+        <v>9</v>
       </c>
     </row>
     <row r="320" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -6162,7 +6162,7 @@
         <v>4</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="329" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$338</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$339</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1171" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1174" uniqueCount="398">
   <si>
     <t>CUENTA</t>
   </si>
@@ -1213,6 +1213,9 @@
   </si>
   <si>
     <t>DEPOSITO</t>
+  </si>
+  <si>
+    <t>FERRETERIA NOR-CINTI</t>
   </si>
 </sst>
 </file>
@@ -1565,7 +1568,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D390"/>
+  <dimension ref="A1:D391"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -5313,66 +5316,66 @@
     </row>
     <row r="268" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A268" s="6">
-        <v>50230</v>
+        <v>50833</v>
       </c>
       <c r="B268" s="8" t="s">
-        <v>379</v>
+        <v>397</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D268" s="11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="269" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A269" s="6">
-        <v>60103</v>
-      </c>
-      <c r="B269" t="s">
-        <v>237</v>
+        <v>50230</v>
+      </c>
+      <c r="B269" s="8" t="s">
+        <v>379</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D269" s="13" t="s">
+      <c r="D269" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="270" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A270" s="6">
-        <v>60109</v>
+        <v>60103</v>
       </c>
       <c r="B270" t="s">
-        <v>328</v>
+        <v>237</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D270" s="11" t="s">
-        <v>9</v>
+      <c r="D270" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="271" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A271" s="6">
-        <v>60124</v>
+        <v>60109</v>
       </c>
       <c r="B271" t="s">
-        <v>238</v>
+        <v>328</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D271" s="13" t="s">
-        <v>5</v>
+      <c r="D271" s="11" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="272" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A272" s="6">
-        <v>60125</v>
+        <v>60124</v>
       </c>
       <c r="B272" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>4</v>
@@ -5383,80 +5386,80 @@
     </row>
     <row r="273" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A273" s="6">
-        <v>60126</v>
+        <v>60125</v>
       </c>
       <c r="B273" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D273" s="10" t="s">
-        <v>8</v>
+      <c r="D273" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="274" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A274" s="6">
-        <v>60128</v>
+        <v>60126</v>
       </c>
       <c r="B274" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D274" s="3" t="s">
-        <v>5</v>
+      <c r="D274" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="275" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A275" s="6">
-        <v>60130</v>
+        <v>60128</v>
       </c>
       <c r="B275" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D275" s="1" t="s">
-        <v>8</v>
+      <c r="D275" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="276" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A276" s="6">
-        <v>60133</v>
+        <v>60130</v>
       </c>
       <c r="B276" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D276" s="13" t="s">
-        <v>5</v>
+      <c r="D276" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="277" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A277" s="6">
-        <v>60134</v>
+        <v>60133</v>
       </c>
       <c r="B277" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D277" s="1" t="s">
-        <v>8</v>
+      <c r="D277" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="278" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A278" s="6">
-        <v>60137</v>
+        <v>60134</v>
       </c>
       <c r="B278" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>4</v>
@@ -5467,10 +5470,10 @@
     </row>
     <row r="279" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A279" s="6">
-        <v>60139</v>
+        <v>60137</v>
       </c>
       <c r="B279" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>4</v>
@@ -5481,10 +5484,10 @@
     </row>
     <row r="280" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A280" s="6">
-        <v>60142</v>
+        <v>60139</v>
       </c>
       <c r="B280" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>4</v>
@@ -5495,10 +5498,10 @@
     </row>
     <row r="281" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A281" s="6">
-        <v>60148</v>
+        <v>60142</v>
       </c>
       <c r="B281" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>4</v>
@@ -5509,10 +5512,10 @@
     </row>
     <row r="282" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A282" s="6">
-        <v>60149</v>
+        <v>60148</v>
       </c>
       <c r="B282" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>4</v>
@@ -5523,66 +5526,66 @@
     </row>
     <row r="283" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A283" s="6">
-        <v>60150</v>
+        <v>60149</v>
       </c>
       <c r="B283" t="s">
-        <v>332</v>
+        <v>249</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D283" s="13" t="s">
-        <v>5</v>
+      <c r="D283" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="284" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A284" s="6">
-        <v>60158</v>
+        <v>60150</v>
       </c>
       <c r="B284" t="s">
-        <v>250</v>
+        <v>332</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D284" s="10" t="s">
-        <v>8</v>
+      <c r="D284" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="285" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A285" s="6">
-        <v>60159</v>
+        <v>60158</v>
       </c>
       <c r="B285" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D285" s="1" t="s">
+      <c r="D285" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="286" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A286" s="6">
-        <v>60162</v>
+        <v>60159</v>
       </c>
       <c r="B286" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D286" s="13" t="s">
-        <v>5</v>
+      <c r="D286" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="287" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A287" s="6">
-        <v>60163</v>
+        <v>60162</v>
       </c>
       <c r="B287" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>4</v>
@@ -5593,24 +5596,24 @@
     </row>
     <row r="288" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A288" s="6">
-        <v>60165</v>
+        <v>60163</v>
       </c>
       <c r="B288" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D288" s="1" t="s">
-        <v>8</v>
+      <c r="D288" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="289" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A289" s="6">
-        <v>60169</v>
+        <v>60165</v>
       </c>
       <c r="B289" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>4</v>
@@ -5621,52 +5624,52 @@
     </row>
     <row r="290" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A290" s="6">
-        <v>60170</v>
-      </c>
-      <c r="B290" s="8" t="s">
-        <v>337</v>
+        <v>60169</v>
+      </c>
+      <c r="B290" t="s">
+        <v>255</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D290" s="11" t="s">
+      <c r="D290" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="291" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A291" s="6">
-        <v>60172</v>
-      </c>
-      <c r="B291" t="s">
-        <v>256</v>
+        <v>60170</v>
+      </c>
+      <c r="B291" s="8" t="s">
+        <v>337</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D291" s="1" t="s">
+      <c r="D291" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="292" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A292" s="6">
-        <v>60174</v>
+        <v>60172</v>
       </c>
       <c r="B292" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D292" s="13" t="s">
-        <v>5</v>
+      <c r="D292" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="293" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A293" s="6">
-        <v>60176</v>
+        <v>60174</v>
       </c>
       <c r="B293" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>4</v>
@@ -5677,52 +5680,52 @@
     </row>
     <row r="294" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A294" s="6">
-        <v>60178</v>
+        <v>60176</v>
       </c>
       <c r="B294" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D294" s="1" t="s">
-        <v>8</v>
+      <c r="D294" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="295" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A295" s="6">
-        <v>60180</v>
+        <v>60178</v>
       </c>
       <c r="B295" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D295" s="10" t="s">
+      <c r="D295" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="296" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A296" s="6">
-        <v>60184</v>
+        <v>60180</v>
       </c>
       <c r="B296" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D296" s="1" t="s">
+      <c r="D296" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="297" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A297" s="6">
-        <v>60190</v>
+        <v>60184</v>
       </c>
       <c r="B297" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>4</v>
@@ -5733,24 +5736,24 @@
     </row>
     <row r="298" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A298" s="6">
-        <v>60191</v>
+        <v>60190</v>
       </c>
       <c r="B298" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D298" s="10" t="s">
+      <c r="D298" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="299" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A299" s="6">
-        <v>60192</v>
+        <v>60191</v>
       </c>
       <c r="B299" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>4</v>
@@ -5761,10 +5764,10 @@
     </row>
     <row r="300" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A300" s="6">
-        <v>60195</v>
+        <v>60192</v>
       </c>
       <c r="B300" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>4</v>
@@ -5775,10 +5778,10 @@
     </row>
     <row r="301" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A301" s="6">
-        <v>60196</v>
+        <v>60195</v>
       </c>
       <c r="B301" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>4</v>
@@ -5789,10 +5792,10 @@
     </row>
     <row r="302" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A302" s="6">
-        <v>60198</v>
+        <v>60196</v>
       </c>
       <c r="B302" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>4</v>
@@ -5803,52 +5806,52 @@
     </row>
     <row r="303" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A303" s="6">
-        <v>60201</v>
+        <v>60198</v>
       </c>
       <c r="B303" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D303" t="s">
-        <v>9</v>
+      <c r="D303" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="304" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A304" s="6">
-        <v>60202</v>
+        <v>60201</v>
       </c>
       <c r="B304" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D304" s="13" t="s">
-        <v>5</v>
+      <c r="D304" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="305" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A305" s="6">
-        <v>60204</v>
+        <v>60202</v>
       </c>
       <c r="B305" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D305" s="1" t="s">
-        <v>8</v>
+      <c r="D305" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="306" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A306" s="6">
-        <v>60205</v>
+        <v>60204</v>
       </c>
       <c r="B306" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>4</v>
@@ -5859,10 +5862,10 @@
     </row>
     <row r="307" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A307" s="6">
-        <v>60206</v>
+        <v>60205</v>
       </c>
       <c r="B307" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>4</v>
@@ -5873,220 +5876,220 @@
     </row>
     <row r="308" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A308" s="6">
-        <v>60209</v>
+        <v>60206</v>
       </c>
       <c r="B308" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D308" s="10" t="s">
+      <c r="D308" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="309" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A309" s="6">
-        <v>60211</v>
+        <v>60209</v>
       </c>
       <c r="B309" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D309" s="1" t="s">
+      <c r="D309" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="310" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A310" s="6">
-        <v>60215</v>
+        <v>60211</v>
       </c>
       <c r="B310" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D310" s="10" t="s">
+      <c r="D310" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="311" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A311" s="6">
-        <v>60216</v>
+        <v>60215</v>
       </c>
       <c r="B311" t="s">
-        <v>381</v>
+        <v>275</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D311" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="312" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A312" s="6">
-        <v>60217</v>
+        <v>60216</v>
       </c>
       <c r="B312" t="s">
-        <v>276</v>
+        <v>381</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D312" s="10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="313" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A313" s="6">
-        <v>60219</v>
+        <v>60217</v>
       </c>
       <c r="B313" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D313" s="1" t="s">
+      <c r="D313" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="314" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A314" s="6">
-        <v>60222</v>
+        <v>60219</v>
       </c>
       <c r="B314" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D314" s="10" t="s">
+      <c r="D314" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="315" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A315" s="6">
-        <v>60225</v>
+        <v>60222</v>
       </c>
       <c r="B315" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D315" s="17" t="s">
-        <v>9</v>
+      <c r="D315" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="316" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A316" s="6">
-        <v>60230</v>
+        <v>60225</v>
       </c>
       <c r="B316" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D316" s="10" t="s">
-        <v>8</v>
+      <c r="D316" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="317" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A317" s="6">
-        <v>60241</v>
-      </c>
-      <c r="B317" s="8" t="s">
-        <v>338</v>
+        <v>60230</v>
+      </c>
+      <c r="B317" t="s">
+        <v>280</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D317" s="7" t="s">
-        <v>9</v>
+      <c r="D317" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="318" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A318" s="6">
-        <v>60242</v>
+        <v>60241</v>
       </c>
       <c r="B318" s="8" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D318" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="319" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A319" s="6">
-        <v>60243</v>
+        <v>60242</v>
       </c>
       <c r="B319" s="8" t="s">
-        <v>395</v>
+        <v>341</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D319" s="7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="320" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A320" s="6">
-        <v>60245</v>
+        <v>60243</v>
       </c>
       <c r="B320" s="8" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D320" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="321" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A321" s="6">
-        <v>60250</v>
+        <v>60245</v>
       </c>
       <c r="B321" s="8" t="s">
-        <v>339</v>
+        <v>387</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D321" s="11" t="s">
-        <v>8</v>
+      <c r="D321" s="7" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="322" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A322" s="6">
-        <v>60253</v>
-      </c>
-      <c r="B322" t="s">
-        <v>281</v>
+        <v>60250</v>
+      </c>
+      <c r="B322" s="8" t="s">
+        <v>339</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D322" s="1" t="s">
+      <c r="D322" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="323" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A323" s="6">
-        <v>60254</v>
+        <v>60253</v>
       </c>
       <c r="B323" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>4</v>
@@ -6097,10 +6100,10 @@
     </row>
     <row r="324" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A324" s="6">
-        <v>60257</v>
+        <v>60254</v>
       </c>
       <c r="B324" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>4</v>
@@ -6111,10 +6114,10 @@
     </row>
     <row r="325" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A325" s="6">
-        <v>60258</v>
+        <v>60257</v>
       </c>
       <c r="B325" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>4</v>
@@ -6125,66 +6128,66 @@
     </row>
     <row r="326" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A326" s="6">
-        <v>60266</v>
-      </c>
-      <c r="B326" s="8" t="s">
-        <v>343</v>
+        <v>60258</v>
+      </c>
+      <c r="B326" t="s">
+        <v>284</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D326" s="11" t="s">
+      <c r="D326" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="327" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A327" s="6">
-        <v>60269</v>
-      </c>
-      <c r="B327" t="s">
-        <v>285</v>
+        <v>60266</v>
+      </c>
+      <c r="B327" s="8" t="s">
+        <v>343</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D327" s="10" t="s">
+      <c r="D327" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="328" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A328" s="6">
-        <v>60270</v>
+        <v>60269</v>
       </c>
       <c r="B328" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D328" s="1" t="s">
-        <v>9</v>
+      <c r="D328" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="329" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A329" s="6">
-        <v>60272</v>
+        <v>60270</v>
       </c>
       <c r="B329" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="330" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A330" s="6">
-        <v>60274</v>
+        <v>60272</v>
       </c>
       <c r="B330" t="s">
-        <v>380</v>
+        <v>287</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>4</v>
@@ -6195,10 +6198,10 @@
     </row>
     <row r="331" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A331" s="6">
-        <v>60275</v>
+        <v>60274</v>
       </c>
       <c r="B331" t="s">
-        <v>288</v>
+        <v>380</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>4</v>
@@ -6209,10 +6212,10 @@
     </row>
     <row r="332" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A332" s="6">
-        <v>60276</v>
+        <v>60275</v>
       </c>
       <c r="B332" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>4</v>
@@ -6223,108 +6226,108 @@
     </row>
     <row r="333" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A333" s="6">
-        <v>60278</v>
+        <v>60276</v>
       </c>
       <c r="B333" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D333" s="13" t="s">
+      <c r="D333" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="334" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A334" s="6">
-        <v>60279</v>
+        <v>60278</v>
       </c>
       <c r="B334" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D334" s="1" t="s">
+      <c r="D334" s="13" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="335" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A335" s="6">
-        <v>60280</v>
+        <v>60279</v>
       </c>
       <c r="B335" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="336" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A336" s="6">
-        <v>60281</v>
-      </c>
-      <c r="B336" s="8" t="s">
-        <v>336</v>
+        <v>60280</v>
+      </c>
+      <c r="B336" t="s">
+        <v>292</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D336" s="11" t="s">
-        <v>9</v>
+      <c r="D336" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="337" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A337" s="6">
-        <v>60282</v>
+        <v>60281</v>
       </c>
       <c r="B337" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D337" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="338" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A338" s="6">
-        <v>60283</v>
-      </c>
-      <c r="B338" t="s">
-        <v>378</v>
+        <v>60282</v>
+      </c>
+      <c r="B338" s="8" t="s">
+        <v>340</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D338" s="1" t="s">
-        <v>8</v>
+      <c r="D338" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="339" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A339" s="6">
-        <v>60284</v>
-      </c>
-      <c r="B339" s="8" t="s">
-        <v>335</v>
+        <v>60283</v>
+      </c>
+      <c r="B339" t="s">
+        <v>378</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D339" s="9" t="s">
-        <v>5</v>
+      <c r="D339" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="340" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A340" s="6">
-        <v>60285</v>
+        <v>60284</v>
       </c>
       <c r="B340" s="8" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>4</v>
@@ -6335,10 +6338,10 @@
     </row>
     <row r="341" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A341" s="6">
-        <v>60286</v>
+        <v>60285</v>
       </c>
       <c r="B341" s="8" t="s">
-        <v>334</v>
+        <v>350</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>4</v>
@@ -6349,52 +6352,52 @@
     </row>
     <row r="342" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A342" s="6">
-        <v>60287</v>
-      </c>
-      <c r="B342" t="s">
-        <v>377</v>
+        <v>60286</v>
+      </c>
+      <c r="B342" s="8" t="s">
+        <v>334</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D342" s="12" t="s">
+      <c r="D342" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="343" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A343" s="6">
-        <v>60289</v>
+        <v>60287</v>
       </c>
       <c r="B343" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D343" s="12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="344" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A344" s="6">
-        <v>60290</v>
+        <v>60289</v>
       </c>
       <c r="B344" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D344" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="345" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A345" s="6">
-        <v>60291</v>
+        <v>60290</v>
       </c>
       <c r="B345" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>4</v>
@@ -6405,38 +6408,38 @@
     </row>
     <row r="346" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A346" s="6">
-        <v>60296</v>
+        <v>60291</v>
       </c>
       <c r="B346" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D346" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="347" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A347" s="6">
-        <v>60297</v>
+        <v>60296</v>
       </c>
       <c r="B347" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D347" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="348" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A348" s="6">
-        <v>60299</v>
+        <v>60297</v>
       </c>
       <c r="B348" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>4</v>
@@ -6447,38 +6450,38 @@
     </row>
     <row r="349" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A349" s="6">
-        <v>61004</v>
+        <v>60299</v>
       </c>
       <c r="B349" t="s">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D349" s="15" t="s">
+      <c r="D349" s="12" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="350" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A350" s="6">
-        <v>61009</v>
+        <v>61004</v>
       </c>
       <c r="B350" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D350" s="12" t="s">
-        <v>8</v>
+      <c r="D350" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="351" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A351" s="6">
-        <v>61012</v>
+        <v>61009</v>
       </c>
       <c r="B351" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>4</v>
@@ -6489,10 +6492,10 @@
     </row>
     <row r="352" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A352" s="6">
-        <v>61018</v>
+        <v>61012</v>
       </c>
       <c r="B352" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>4</v>
@@ -6503,10 +6506,10 @@
     </row>
     <row r="353" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A353" s="6">
-        <v>61102</v>
+        <v>61018</v>
       </c>
       <c r="B353" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>4</v>
@@ -6517,52 +6520,52 @@
     </row>
     <row r="354" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A354" s="6">
-        <v>61205</v>
+        <v>61102</v>
       </c>
       <c r="B354" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D354" s="15" t="s">
-        <v>5</v>
+      <c r="D354" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="355" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A355" s="6">
-        <v>70100</v>
+        <v>61205</v>
       </c>
       <c r="B355" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D355" s="12" t="s">
-        <v>8</v>
+      <c r="D355" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="356" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A356" s="6">
-        <v>70101</v>
+        <v>70100</v>
       </c>
       <c r="B356" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D356" s="15" t="s">
-        <v>5</v>
+      <c r="D356" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="357" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A357" s="6">
-        <v>70102</v>
+        <v>70101</v>
       </c>
       <c r="B357" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>4</v>
@@ -6573,80 +6576,80 @@
     </row>
     <row r="358" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A358" s="6">
-        <v>70103</v>
+        <v>70102</v>
       </c>
       <c r="B358" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D358" s="12" t="s">
-        <v>8</v>
+      <c r="D358" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="359" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A359" s="6">
-        <v>70106</v>
+        <v>70103</v>
       </c>
       <c r="B359" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D359" s="15" t="s">
-        <v>5</v>
+      <c r="D359" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="360" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A360" s="6">
-        <v>70109</v>
+        <v>70106</v>
       </c>
       <c r="B360" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D360" s="12" t="s">
-        <v>8</v>
+      <c r="D360" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="361" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A361" s="6">
-        <v>70113</v>
+        <v>70109</v>
       </c>
       <c r="B361" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D361" s="15" t="s">
-        <v>5</v>
+      <c r="D361" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="362" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A362" s="6">
-        <v>70114</v>
+        <v>70113</v>
       </c>
       <c r="B362" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D362" s="9" t="s">
-        <v>9</v>
+      <c r="D362" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="363" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A363" s="6">
-        <v>70115</v>
+        <v>70114</v>
       </c>
       <c r="B363" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>4</v>
@@ -6657,24 +6660,24 @@
     </row>
     <row r="364" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A364" s="6">
-        <v>70638</v>
+        <v>70115</v>
       </c>
       <c r="B364" t="s">
-        <v>306</v>
+        <v>331</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D364" s="12" t="s">
-        <v>8</v>
+      <c r="D364" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="365" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A365" s="6">
-        <v>70639</v>
+        <v>70638</v>
       </c>
       <c r="B365" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>4</v>
@@ -6685,10 +6688,10 @@
     </row>
     <row r="366" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A366" s="6">
-        <v>70640</v>
+        <v>70639</v>
       </c>
       <c r="B366" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>4</v>
@@ -6699,10 +6702,10 @@
     </row>
     <row r="367" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A367" s="6">
-        <v>70642</v>
+        <v>70640</v>
       </c>
       <c r="B367" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>4</v>
@@ -6713,10 +6716,10 @@
     </row>
     <row r="368" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A368" s="6">
-        <v>90504</v>
+        <v>70642</v>
       </c>
       <c r="B368" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>4</v>
@@ -6727,10 +6730,10 @@
     </row>
     <row r="369" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A369" s="6">
-        <v>90509</v>
+        <v>90504</v>
       </c>
       <c r="B369" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>4</v>
@@ -6741,52 +6744,52 @@
     </row>
     <row r="370" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A370" s="6">
-        <v>90602</v>
+        <v>90509</v>
       </c>
       <c r="B370" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D370" s="15" t="s">
-        <v>5</v>
+      <c r="D370" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="371" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A371" s="6">
-        <v>90621</v>
+        <v>90602</v>
       </c>
       <c r="B371" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D371" s="12" t="s">
-        <v>8</v>
+      <c r="D371" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="372" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A372" s="6">
-        <v>90622</v>
+        <v>90621</v>
       </c>
       <c r="B372" t="s">
-        <v>333</v>
+        <v>313</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D372" s="9" t="s">
-        <v>5</v>
+      <c r="D372" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="373" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A373" s="6">
-        <v>90631</v>
-      </c>
-      <c r="B373" s="8" t="s">
-        <v>342</v>
+        <v>90622</v>
+      </c>
+      <c r="B373" t="s">
+        <v>333</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>4</v>
@@ -6797,24 +6800,24 @@
     </row>
     <row r="374" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A374" s="6">
-        <v>90658</v>
-      </c>
-      <c r="B374" t="s">
-        <v>314</v>
+        <v>90631</v>
+      </c>
+      <c r="B374" s="8" t="s">
+        <v>342</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D374" s="12" t="s">
-        <v>8</v>
+      <c r="D374" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="375" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A375" s="6">
-        <v>90660</v>
+        <v>90658</v>
       </c>
       <c r="B375" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>4</v>
@@ -6825,10 +6828,10 @@
     </row>
     <row r="376" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A376" s="6">
-        <v>90668</v>
+        <v>90660</v>
       </c>
       <c r="B376" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>4</v>
@@ -6839,10 +6842,10 @@
     </row>
     <row r="377" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A377" s="6">
-        <v>90671</v>
+        <v>90668</v>
       </c>
       <c r="B377" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>4</v>
@@ -6853,10 +6856,10 @@
     </row>
     <row r="378" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A378" s="6">
-        <v>90679</v>
+        <v>90671</v>
       </c>
       <c r="B378" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>4</v>
@@ -6867,10 +6870,10 @@
     </row>
     <row r="379" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A379" s="6">
-        <v>90683</v>
+        <v>90679</v>
       </c>
       <c r="B379" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>4</v>
@@ -6881,10 +6884,10 @@
     </row>
     <row r="380" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A380" s="6">
-        <v>90705</v>
+        <v>90683</v>
       </c>
       <c r="B380" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>4</v>
@@ -6895,10 +6898,10 @@
     </row>
     <row r="381" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A381" s="6">
-        <v>90706</v>
+        <v>90705</v>
       </c>
       <c r="B381" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>4</v>
@@ -6909,10 +6912,10 @@
     </row>
     <row r="382" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A382" s="6">
-        <v>90708</v>
+        <v>90706</v>
       </c>
       <c r="B382" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>4</v>
@@ -6923,10 +6926,10 @@
     </row>
     <row r="383" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A383" s="6">
-        <v>90709</v>
+        <v>90708</v>
       </c>
       <c r="B383" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>4</v>
@@ -6937,10 +6940,10 @@
     </row>
     <row r="384" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A384" s="6">
-        <v>1218</v>
+        <v>90709</v>
       </c>
       <c r="B384" t="s">
-        <v>382</v>
+        <v>323</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>4</v>
@@ -6951,10 +6954,10 @@
     </row>
     <row r="385" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A385" s="6">
-        <v>1959</v>
-      </c>
-      <c r="B385" s="8" t="s">
-        <v>383</v>
+        <v>1218</v>
+      </c>
+      <c r="B385" t="s">
+        <v>382</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>4</v>
@@ -6965,10 +6968,10 @@
     </row>
     <row r="386" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A386" s="6">
-        <v>5625</v>
+        <v>1959</v>
       </c>
       <c r="B386" s="8" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>4</v>
@@ -6979,10 +6982,10 @@
     </row>
     <row r="387" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A387" s="6">
-        <v>1817</v>
+        <v>5625</v>
       </c>
       <c r="B387" s="8" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>4</v>
@@ -6993,10 +6996,10 @@
     </row>
     <row r="388" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A388" s="6">
-        <v>5737</v>
+        <v>1817</v>
       </c>
       <c r="B388" s="8" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>4</v>
@@ -7007,34 +7010,48 @@
     </row>
     <row r="389" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A389" s="6">
-        <v>60295</v>
+        <v>5737</v>
       </c>
       <c r="B389" s="8" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D389" s="9" t="s">
-        <v>9</v>
+      <c r="D389" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="390" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A390" s="6">
+        <v>60295</v>
+      </c>
+      <c r="B390" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="C390" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D390" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A391" s="6">
         <v>1045</v>
       </c>
-      <c r="B390" s="8" t="s">
+      <c r="B391" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="C390" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D390" s="9" t="s">
+      <c r="C391" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D391" s="9" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D338"/>
+  <autoFilter ref="A1:D339"/>
   <sortState ref="A2:D374">
     <sortCondition ref="A277"/>
   </sortState>

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$339</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$340</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1174" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1177" uniqueCount="399">
   <si>
     <t>CUENTA</t>
   </si>
@@ -1216,6 +1216,9 @@
   </si>
   <si>
     <t>FERRETERIA NOR-CINTI</t>
+  </si>
+  <si>
+    <t>BELISARIO FERRETERIA</t>
   </si>
 </sst>
 </file>
@@ -1568,7 +1571,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D391"/>
+  <dimension ref="A1:D392"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -2726,52 +2729,52 @@
     </row>
     <row r="83" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="6">
-        <v>1416</v>
+        <v>1046</v>
       </c>
       <c r="B83" t="s">
-        <v>217</v>
+        <v>398</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D83" s="1" t="s">
-        <v>8</v>
+      <c r="D83" s="11" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="6">
-        <v>10107</v>
+        <v>1416</v>
       </c>
       <c r="B84" t="s">
-        <v>96</v>
+        <v>217</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D84" t="s">
-        <v>9</v>
+      <c r="D84" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="6">
-        <v>10137</v>
+        <v>10107</v>
       </c>
       <c r="B85" t="s">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D85" s="1" t="s">
-        <v>8</v>
+      <c r="D85" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="6">
-        <v>10157</v>
+        <v>10137</v>
       </c>
       <c r="B86" t="s">
-        <v>183</v>
+        <v>123</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>4</v>
@@ -2782,10 +2785,10 @@
     </row>
     <row r="87" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="6">
-        <v>10158</v>
+        <v>10157</v>
       </c>
       <c r="B87" t="s">
-        <v>65</v>
+        <v>183</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>4</v>
@@ -2796,108 +2799,108 @@
     </row>
     <row r="88" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="6">
-        <v>10160</v>
+        <v>10158</v>
       </c>
       <c r="B88" t="s">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D88" s="13" t="s">
-        <v>5</v>
+      <c r="D88" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="6">
-        <v>10162</v>
+        <v>10160</v>
       </c>
       <c r="B89" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D89" s="1" t="s">
-        <v>8</v>
+      <c r="D89" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="6">
-        <v>10163</v>
+        <v>10162</v>
       </c>
       <c r="B90" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D90" s="13" t="s">
-        <v>5</v>
+      <c r="D90" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="6">
-        <v>10165</v>
+        <v>10163</v>
       </c>
       <c r="B91" t="s">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D91" s="1" t="s">
-        <v>8</v>
+      <c r="D91" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="6">
-        <v>10166</v>
-      </c>
-      <c r="B92" s="8" t="s">
-        <v>348</v>
+        <v>10165</v>
+      </c>
+      <c r="B92" t="s">
+        <v>19</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D92" s="11" t="s">
+      <c r="D92" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="6">
-        <v>10167</v>
-      </c>
-      <c r="B93" t="s">
-        <v>39</v>
+        <v>10166</v>
+      </c>
+      <c r="B93" s="8" t="s">
+        <v>348</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D93" s="13" t="s">
-        <v>5</v>
+      <c r="D93" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="6">
-        <v>10424</v>
+        <v>10167</v>
       </c>
       <c r="B94" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D94" s="17" t="s">
-        <v>9</v>
+      <c r="D94" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="6">
-        <v>10425</v>
+        <v>10424</v>
       </c>
       <c r="B95" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>4</v>
@@ -2908,24 +2911,24 @@
     </row>
     <row r="96" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="6">
-        <v>20094</v>
+        <v>10425</v>
       </c>
       <c r="B96" t="s">
-        <v>198</v>
+        <v>15</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D96" s="10" t="s">
-        <v>8</v>
+      <c r="D96" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="6">
-        <v>20095</v>
+        <v>20094</v>
       </c>
       <c r="B97" t="s">
-        <v>153</v>
+        <v>198</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>4</v>
@@ -2936,66 +2939,66 @@
     </row>
     <row r="98" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="6">
-        <v>20096</v>
+        <v>20095</v>
       </c>
       <c r="B98" t="s">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D98" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="6">
-        <v>20100</v>
+        <v>20096</v>
       </c>
       <c r="B99" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D99" s="1" t="s">
-        <v>8</v>
+      <c r="D99" s="10" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="6">
-        <v>20101</v>
+        <v>20100</v>
       </c>
       <c r="B100" t="s">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="6">
-        <v>20103</v>
+        <v>20101</v>
       </c>
       <c r="B101" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="6">
-        <v>20106</v>
+        <v>20103</v>
       </c>
       <c r="B102" t="s">
-        <v>155</v>
+        <v>81</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>4</v>
@@ -3006,80 +3009,80 @@
     </row>
     <row r="103" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="6">
-        <v>20108</v>
+        <v>20106</v>
       </c>
       <c r="B103" t="s">
-        <v>219</v>
+        <v>155</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D103" s="10" t="s">
+      <c r="D103" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="6">
-        <v>20109</v>
+        <v>20108</v>
       </c>
       <c r="B104" t="s">
-        <v>53</v>
+        <v>219</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D104" s="1" t="s">
+      <c r="D104" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="6">
-        <v>20110</v>
+        <v>20109</v>
       </c>
       <c r="B105" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D105" s="13" t="s">
-        <v>5</v>
+      <c r="D105" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="6">
-        <v>20113</v>
+        <v>20110</v>
       </c>
       <c r="B106" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D106" s="10" t="s">
-        <v>8</v>
+      <c r="D106" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="6">
-        <v>20114</v>
+        <v>20113</v>
       </c>
       <c r="B107" t="s">
-        <v>126</v>
+        <v>93</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D107" s="1" t="s">
+      <c r="D107" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="6">
-        <v>20116</v>
+        <v>20114</v>
       </c>
       <c r="B108" t="s">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>4</v>
@@ -3090,10 +3093,10 @@
     </row>
     <row r="109" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="6">
-        <v>20117</v>
+        <v>20116</v>
       </c>
       <c r="B109" t="s">
-        <v>186</v>
+        <v>73</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>4</v>
@@ -3104,10 +3107,10 @@
     </row>
     <row r="110" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="6">
-        <v>20118</v>
+        <v>20117</v>
       </c>
       <c r="B110" t="s">
-        <v>160</v>
+        <v>186</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>4</v>
@@ -3118,10 +3121,10 @@
     </row>
     <row r="111" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="6">
-        <v>20120</v>
+        <v>20118</v>
       </c>
       <c r="B111" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>4</v>
@@ -3132,10 +3135,10 @@
     </row>
     <row r="112" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="6">
-        <v>20121</v>
+        <v>20120</v>
       </c>
       <c r="B112" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>4</v>
@@ -3146,38 +3149,38 @@
     </row>
     <row r="113" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="6">
-        <v>20125</v>
+        <v>20121</v>
       </c>
       <c r="B113" t="s">
-        <v>88</v>
+        <v>159</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D113" s="10" t="s">
+      <c r="D113" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="6">
-        <v>20127</v>
+        <v>20125</v>
       </c>
       <c r="B114" t="s">
-        <v>168</v>
+        <v>88</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D114" s="1" t="s">
+      <c r="D114" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="6">
-        <v>20128</v>
+        <v>20127</v>
       </c>
       <c r="B115" t="s">
-        <v>208</v>
+        <v>168</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>4</v>
@@ -3188,52 +3191,52 @@
     </row>
     <row r="116" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="6">
-        <v>20129</v>
+        <v>20128</v>
       </c>
       <c r="B116" t="s">
-        <v>326</v>
+        <v>208</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D116" s="10" t="s">
+      <c r="D116" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="6">
-        <v>20137</v>
+        <v>20129</v>
       </c>
       <c r="B117" t="s">
-        <v>79</v>
+        <v>326</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D117" s="3" t="s">
-        <v>5</v>
+      <c r="D117" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="6">
-        <v>20138</v>
+        <v>20137</v>
       </c>
       <c r="B118" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D118" s="13" t="s">
+      <c r="D118" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="6">
-        <v>20140</v>
+        <v>20138</v>
       </c>
       <c r="B119" t="s">
-        <v>218</v>
+        <v>113</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>4</v>
@@ -3244,24 +3247,24 @@
     </row>
     <row r="120" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="6">
-        <v>20142</v>
+        <v>20140</v>
       </c>
       <c r="B120" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D120" s="1" t="s">
-        <v>8</v>
+      <c r="D120" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="6">
-        <v>20146</v>
+        <v>20142</v>
       </c>
       <c r="B121" t="s">
-        <v>148</v>
+        <v>193</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>4</v>
@@ -3272,10 +3275,10 @@
     </row>
     <row r="122" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="6">
-        <v>20148</v>
+        <v>20146</v>
       </c>
       <c r="B122" t="s">
-        <v>38</v>
+        <v>148</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>4</v>
@@ -3286,52 +3289,52 @@
     </row>
     <row r="123" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="6">
-        <v>20156</v>
+        <v>20148</v>
       </c>
       <c r="B123" t="s">
-        <v>179</v>
+        <v>38</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D123" s="10" t="s">
+      <c r="D123" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="6">
-        <v>20159</v>
+        <v>20156</v>
       </c>
       <c r="B124" t="s">
-        <v>120</v>
+        <v>179</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D124" s="17" t="s">
-        <v>9</v>
+      <c r="D124" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="6">
-        <v>20160</v>
+        <v>20159</v>
       </c>
       <c r="B125" t="s">
-        <v>224</v>
+        <v>120</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D125" s="10" t="s">
-        <v>8</v>
+      <c r="D125" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="6">
-        <v>20163</v>
+        <v>20160</v>
       </c>
       <c r="B126" t="s">
-        <v>23</v>
+        <v>224</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>4</v>
@@ -3342,52 +3345,52 @@
     </row>
     <row r="127" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="6">
-        <v>20164</v>
+        <v>20163</v>
       </c>
       <c r="B127" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D127" t="s">
-        <v>9</v>
+      <c r="D127" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="6">
-        <v>20165</v>
+        <v>20164</v>
       </c>
       <c r="B128" t="s">
-        <v>131</v>
+        <v>18</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D128" s="10" t="s">
-        <v>8</v>
+      <c r="D128" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="6">
-        <v>20166</v>
+        <v>20165</v>
       </c>
       <c r="B129" t="s">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D129" s="1" t="s">
+      <c r="D129" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="6">
-        <v>20169</v>
+        <v>20166</v>
       </c>
       <c r="B130" t="s">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>4</v>
@@ -3398,38 +3401,38 @@
     </row>
     <row r="131" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="6">
-        <v>20173</v>
+        <v>20169</v>
       </c>
       <c r="B131" t="s">
-        <v>112</v>
+        <v>151</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D131" s="10" t="s">
+      <c r="D131" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="6">
-        <v>20174</v>
+        <v>20173</v>
       </c>
       <c r="B132" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D132" s="1" t="s">
+      <c r="D132" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="6">
-        <v>20178</v>
+        <v>20174</v>
       </c>
       <c r="B133" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>4</v>
@@ -3440,80 +3443,80 @@
     </row>
     <row r="134" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="6">
-        <v>20179</v>
+        <v>20178</v>
       </c>
       <c r="B134" t="s">
-        <v>171</v>
+        <v>117</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D134" t="s">
-        <v>9</v>
+      <c r="D134" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="6">
-        <v>20180</v>
+        <v>20179</v>
       </c>
       <c r="B135" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D135" s="1" t="s">
-        <v>8</v>
+      <c r="D135" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="6">
-        <v>20183</v>
+        <v>20180</v>
       </c>
       <c r="B136" t="s">
-        <v>370</v>
+        <v>149</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D136" s="14" t="s">
-        <v>5</v>
+      <c r="D136" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="6">
-        <v>20189</v>
+        <v>20183</v>
       </c>
       <c r="B137" t="s">
-        <v>329</v>
+        <v>370</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D137" s="1" t="s">
-        <v>8</v>
+      <c r="D137" s="14" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="6">
-        <v>20200</v>
+        <v>20189</v>
       </c>
       <c r="B138" t="s">
-        <v>83</v>
+        <v>329</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D138" s="13" t="s">
-        <v>5</v>
+      <c r="D138" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="6">
-        <v>20201</v>
+        <v>20200</v>
       </c>
       <c r="B139" t="s">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>4</v>
@@ -3524,150 +3527,150 @@
     </row>
     <row r="140" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="6">
-        <v>20204</v>
+        <v>20201</v>
       </c>
       <c r="B140" t="s">
-        <v>57</v>
+        <v>145</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D140" s="10" t="s">
-        <v>8</v>
+      <c r="D140" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="6">
-        <v>20205</v>
+        <v>20204</v>
       </c>
       <c r="B141" t="s">
-        <v>206</v>
+        <v>57</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D141" s="1" t="s">
-        <v>9</v>
+      <c r="D141" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="6">
-        <v>20211</v>
+        <v>20205</v>
       </c>
       <c r="B142" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D142" s="10" t="s">
-        <v>8</v>
+      <c r="D142" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="6">
-        <v>20224</v>
+        <v>20211</v>
       </c>
       <c r="B143" t="s">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D143" s="1" t="s">
+      <c r="D143" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="6">
-        <v>20227</v>
+        <v>20224</v>
       </c>
       <c r="B144" t="s">
-        <v>192</v>
+        <v>85</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D144" s="10" t="s">
+      <c r="D144" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="6">
-        <v>20228</v>
+        <v>20227</v>
       </c>
       <c r="B145" t="s">
-        <v>91</v>
+        <v>192</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D145" s="13" t="s">
-        <v>5</v>
+      <c r="D145" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="6">
-        <v>20230</v>
+        <v>20228</v>
       </c>
       <c r="B146" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D146" s="10" t="s">
-        <v>8</v>
+      <c r="D146" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="6">
-        <v>20234</v>
+        <v>20230</v>
       </c>
       <c r="B147" t="s">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D147" s="13" t="s">
-        <v>5</v>
+      <c r="D147" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="6">
-        <v>20236</v>
+        <v>20234</v>
       </c>
       <c r="B148" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D148" s="3" t="s">
+      <c r="D148" s="13" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="6">
-        <v>20238</v>
+        <v>20236</v>
       </c>
       <c r="B149" t="s">
-        <v>139</v>
+        <v>31</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D149" s="13" t="s">
+      <c r="D149" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="6">
-        <v>20241</v>
+        <v>20238</v>
       </c>
       <c r="B150" t="s">
-        <v>22</v>
+        <v>139</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>4</v>
@@ -3678,24 +3681,24 @@
     </row>
     <row r="151" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="6">
-        <v>20242</v>
+        <v>20241</v>
       </c>
       <c r="B151" t="s">
-        <v>216</v>
+        <v>22</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D151" s="10" t="s">
-        <v>8</v>
+      <c r="D151" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="6">
-        <v>20244</v>
+        <v>20242</v>
       </c>
       <c r="B152" t="s">
-        <v>124</v>
+        <v>216</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>4</v>
@@ -3706,108 +3709,108 @@
     </row>
     <row r="153" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="6">
-        <v>20246</v>
+        <v>20244</v>
       </c>
       <c r="B153" t="s">
-        <v>14</v>
+        <v>124</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D153" s="13" t="s">
-        <v>5</v>
+      <c r="D153" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="6">
-        <v>20249</v>
+        <v>20246</v>
       </c>
       <c r="B154" t="s">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D154" s="10" t="s">
-        <v>8</v>
+      <c r="D154" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="155" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="6">
-        <v>20256</v>
+        <v>20249</v>
       </c>
       <c r="B155" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D155" s="1" t="s">
+      <c r="D155" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="156" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="6">
-        <v>20257</v>
+        <v>20256</v>
       </c>
       <c r="B156" t="s">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D156" s="17" t="s">
-        <v>9</v>
+      <c r="D156" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="6">
-        <v>20258</v>
+        <v>20257</v>
       </c>
       <c r="B157" t="s">
-        <v>199</v>
+        <v>150</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D157" s="1" t="s">
-        <v>8</v>
+      <c r="D157" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="6">
-        <v>20260</v>
+        <v>20258</v>
       </c>
       <c r="B158" t="s">
-        <v>68</v>
+        <v>199</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D158" s="13" t="s">
-        <v>5</v>
+      <c r="D158" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="159" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A159" s="6">
-        <v>20261</v>
+        <v>20260</v>
       </c>
       <c r="B159" t="s">
-        <v>207</v>
+        <v>68</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D159" s="10" t="s">
-        <v>8</v>
+      <c r="D159" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="160" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="6">
-        <v>20262</v>
+        <v>20261</v>
       </c>
       <c r="B160" t="s">
-        <v>92</v>
+        <v>207</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>4</v>
@@ -3818,192 +3821,192 @@
     </row>
     <row r="161" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="6">
-        <v>20268</v>
+        <v>20262</v>
       </c>
       <c r="B161" t="s">
-        <v>201</v>
+        <v>92</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D161" s="1" t="s">
+      <c r="D161" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="6">
-        <v>20271</v>
+        <v>20268</v>
       </c>
       <c r="B162" t="s">
-        <v>34</v>
+        <v>201</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D162" s="13" t="s">
-        <v>5</v>
+      <c r="D162" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="163" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="6">
-        <v>20272</v>
+        <v>20271</v>
       </c>
       <c r="B163" t="s">
-        <v>178</v>
+        <v>34</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D163" s="1" t="s">
-        <v>8</v>
+      <c r="D163" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="6">
-        <v>20275</v>
+        <v>20272</v>
       </c>
       <c r="B164" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D164" s="13" t="s">
-        <v>5</v>
+      <c r="D164" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="165" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="6">
-        <v>20277</v>
+        <v>20275</v>
       </c>
       <c r="B165" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D165" s="1" t="s">
-        <v>8</v>
+      <c r="D165" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="6">
-        <v>20281</v>
+        <v>20277</v>
       </c>
       <c r="B166" t="s">
-        <v>105</v>
+        <v>154</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D166" s="3" t="s">
-        <v>5</v>
+      <c r="D166" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="6">
-        <v>20282</v>
+        <v>20281</v>
       </c>
       <c r="B167" t="s">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D167" s="1" t="s">
-        <v>9</v>
+      <c r="D167" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="168" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="6">
-        <v>20284</v>
+        <v>20282</v>
       </c>
       <c r="B168" t="s">
-        <v>17</v>
+        <v>141</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D168" s="17" t="s">
+      <c r="D168" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="6">
-        <v>20285</v>
+        <v>20284</v>
       </c>
       <c r="B169" t="s">
-        <v>146</v>
+        <v>17</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D169" s="1" t="s">
-        <v>8</v>
+      <c r="D169" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A170" s="6">
-        <v>20289</v>
+        <v>20285</v>
       </c>
       <c r="B170" t="s">
-        <v>52</v>
+        <v>146</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D170" s="3" t="s">
-        <v>5</v>
+      <c r="D170" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="171" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="6">
-        <v>20290</v>
+        <v>20289</v>
       </c>
       <c r="B171" t="s">
-        <v>103</v>
+        <v>52</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D171" s="1" t="s">
-        <v>8</v>
+      <c r="D171" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="6">
-        <v>20291</v>
+        <v>20290</v>
       </c>
       <c r="B172" t="s">
-        <v>187</v>
+        <v>103</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D172" s="10" t="s">
+      <c r="D172" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="6">
-        <v>20292</v>
+        <v>20291</v>
       </c>
       <c r="B173" t="s">
-        <v>32</v>
+        <v>187</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D173" s="13" t="s">
-        <v>5</v>
+      <c r="D173" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="174" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="6">
-        <v>20293</v>
+        <v>20292</v>
       </c>
       <c r="B174" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>4</v>
@@ -4014,52 +4017,52 @@
     </row>
     <row r="175" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="6">
-        <v>20294</v>
+        <v>20293</v>
       </c>
       <c r="B175" t="s">
-        <v>202</v>
+        <v>43</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D175" s="10" t="s">
-        <v>8</v>
+      <c r="D175" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="6">
-        <v>20296</v>
+        <v>20294</v>
       </c>
       <c r="B176" t="s">
-        <v>144</v>
+        <v>202</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D176" s="13" t="s">
-        <v>5</v>
+      <c r="D176" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="177" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A177" s="6">
-        <v>20298</v>
+        <v>20296</v>
       </c>
       <c r="B177" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D177" s="1" t="s">
-        <v>8</v>
+      <c r="D177" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="6">
-        <v>20299</v>
+        <v>20298</v>
       </c>
       <c r="B178" t="s">
-        <v>58</v>
+        <v>169</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>4</v>
@@ -4070,10 +4073,10 @@
     </row>
     <row r="179" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="6">
-        <v>20301</v>
+        <v>20299</v>
       </c>
       <c r="B179" t="s">
-        <v>134</v>
+        <v>58</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>4</v>
@@ -4084,10 +4087,10 @@
     </row>
     <row r="180" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="6">
-        <v>20303</v>
+        <v>20301</v>
       </c>
       <c r="B180" t="s">
-        <v>37</v>
+        <v>134</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>4</v>
@@ -4098,24 +4101,24 @@
     </row>
     <row r="181" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="6">
-        <v>20309</v>
+        <v>20303</v>
       </c>
       <c r="B181" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D181" s="13" t="s">
-        <v>5</v>
+      <c r="D181" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="182" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="6">
-        <v>20310</v>
+        <v>20309</v>
       </c>
       <c r="B182" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>4</v>
@@ -4126,52 +4129,52 @@
     </row>
     <row r="183" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="6">
-        <v>20318</v>
+        <v>20310</v>
       </c>
       <c r="B183" t="s">
-        <v>209</v>
+        <v>59</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D183" s="1" t="s">
-        <v>8</v>
+      <c r="D183" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="184" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="6">
-        <v>20319</v>
+        <v>20318</v>
       </c>
       <c r="B184" t="s">
-        <v>101</v>
+        <v>209</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D184" s="10" t="s">
+      <c r="D184" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="185" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="6">
-        <v>20320</v>
+        <v>20319</v>
       </c>
       <c r="B185" t="s">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D185" s="1" t="s">
+      <c r="D185" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="186" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="6">
-        <v>20324</v>
+        <v>20320</v>
       </c>
       <c r="B186" t="s">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>4</v>
@@ -4182,10 +4185,10 @@
     </row>
     <row r="187" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="6">
-        <v>20331</v>
+        <v>20324</v>
       </c>
       <c r="B187" t="s">
-        <v>51</v>
+        <v>210</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>4</v>
@@ -4196,38 +4199,38 @@
     </row>
     <row r="188" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="6">
-        <v>20333</v>
+        <v>20331</v>
       </c>
       <c r="B188" t="s">
-        <v>136</v>
+        <v>51</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D188" s="13" t="s">
-        <v>5</v>
+      <c r="D188" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="189" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="6">
-        <v>20337</v>
+        <v>20333</v>
       </c>
       <c r="B189" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D189" s="1" t="s">
-        <v>8</v>
+      <c r="D189" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="190" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A190" s="6">
-        <v>20343</v>
+        <v>20337</v>
       </c>
       <c r="B190" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>4</v>
@@ -4238,10 +4241,10 @@
     </row>
     <row r="191" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="6">
-        <v>20344</v>
+        <v>20343</v>
       </c>
       <c r="B191" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>4</v>
@@ -4252,66 +4255,66 @@
     </row>
     <row r="192" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="6">
-        <v>20351</v>
+        <v>20344</v>
       </c>
       <c r="B192" t="s">
-        <v>26</v>
+        <v>127</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D192" s="13" t="s">
-        <v>5</v>
+      <c r="D192" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="193" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="6">
-        <v>20357</v>
+        <v>20351</v>
       </c>
       <c r="B193" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D193" s="1" t="s">
-        <v>8</v>
+      <c r="D193" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="194" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="6">
-        <v>20361</v>
+        <v>20357</v>
       </c>
       <c r="B194" t="s">
-        <v>164</v>
+        <v>56</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D194" s="13" t="s">
-        <v>5</v>
+      <c r="D194" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="195" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A195" s="6">
-        <v>20362</v>
+        <v>20361</v>
       </c>
       <c r="B195" t="s">
-        <v>45</v>
+        <v>164</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D195" s="10" t="s">
-        <v>8</v>
+      <c r="D195" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="196" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="6">
-        <v>20363</v>
+        <v>20362</v>
       </c>
       <c r="B196" t="s">
-        <v>213</v>
+        <v>45</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>4</v>
@@ -4322,38 +4325,38 @@
     </row>
     <row r="197" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="6">
-        <v>20364</v>
+        <v>20363</v>
       </c>
       <c r="B197" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D197" s="13" t="s">
-        <v>5</v>
+      <c r="D197" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="198" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A198" s="6">
-        <v>20366</v>
+        <v>20364</v>
       </c>
       <c r="B198" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D198" s="1" t="s">
-        <v>8</v>
+      <c r="D198" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="199" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="6">
-        <v>20367</v>
+        <v>20366</v>
       </c>
       <c r="B199" t="s">
-        <v>47</v>
+        <v>220</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>4</v>
@@ -4364,10 +4367,10 @@
     </row>
     <row r="200" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A200" s="6">
-        <v>20369</v>
+        <v>20367</v>
       </c>
       <c r="B200" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>4</v>
@@ -4378,10 +4381,10 @@
     </row>
     <row r="201" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="6">
-        <v>20371</v>
+        <v>20369</v>
       </c>
       <c r="B201" t="s">
-        <v>223</v>
+        <v>63</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>4</v>
@@ -4392,52 +4395,52 @@
     </row>
     <row r="202" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="6">
-        <v>20372</v>
+        <v>20371</v>
       </c>
       <c r="B202" t="s">
-        <v>70</v>
+        <v>223</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D202" s="10" t="s">
+      <c r="D202" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="203" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="6">
-        <v>20374</v>
+        <v>20372</v>
       </c>
       <c r="B203" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D203" s="1" t="s">
+      <c r="D203" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="204" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="6">
-        <v>20377</v>
+        <v>20374</v>
       </c>
       <c r="B204" t="s">
-        <v>225</v>
+        <v>61</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D204" s="10" t="s">
+      <c r="D204" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="205" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A205" s="6">
-        <v>20379</v>
+        <v>20377</v>
       </c>
       <c r="B205" t="s">
-        <v>49</v>
+        <v>225</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>4</v>
@@ -4448,66 +4451,66 @@
     </row>
     <row r="206" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A206" s="6">
-        <v>20380</v>
+        <v>20379</v>
       </c>
       <c r="B206" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D206" s="13" t="s">
-        <v>5</v>
+      <c r="D206" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="207" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A207" s="6">
-        <v>20381</v>
+        <v>20380</v>
       </c>
       <c r="B207" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D207" s="1" t="s">
-        <v>8</v>
+      <c r="D207" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="208" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A208" s="6">
-        <v>20384</v>
+        <v>20381</v>
       </c>
       <c r="B208" t="s">
-        <v>181</v>
+        <v>60</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D208" s="10" t="s">
+      <c r="D208" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="209" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A209" s="6">
-        <v>20385</v>
+        <v>20384</v>
       </c>
       <c r="B209" t="s">
-        <v>36</v>
+        <v>181</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D209" s="1" t="s">
+      <c r="D209" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="210" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A210" s="6">
-        <v>20386</v>
+        <v>20385</v>
       </c>
       <c r="B210" t="s">
-        <v>119</v>
+        <v>36</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>4</v>
@@ -4518,66 +4521,66 @@
     </row>
     <row r="211" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="6">
-        <v>20388</v>
+        <v>20386</v>
       </c>
       <c r="B211" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D211" s="10" t="s">
+      <c r="D211" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="212" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A212" s="6">
-        <v>20391</v>
+        <v>20388</v>
       </c>
       <c r="B212" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D212" s="1" t="s">
+      <c r="D212" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="213" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A213" s="6">
-        <v>20394</v>
+        <v>20391</v>
       </c>
       <c r="B213" t="s">
-        <v>173</v>
+        <v>106</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D213" s="10" t="s">
+      <c r="D213" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="214" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A214" s="6">
-        <v>20395</v>
+        <v>20394</v>
       </c>
       <c r="B214" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D214" s="1" t="s">
+      <c r="D214" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="215" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A215" s="6">
-        <v>20396</v>
+        <v>20395</v>
       </c>
       <c r="B215" t="s">
-        <v>330</v>
+        <v>161</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>4</v>
@@ -4588,52 +4591,52 @@
     </row>
     <row r="216" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A216" s="6">
-        <v>20397</v>
-      </c>
-      <c r="B216" s="8" t="s">
-        <v>344</v>
+        <v>20396</v>
+      </c>
+      <c r="B216" t="s">
+        <v>330</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D216" s="11" t="s">
-        <v>5</v>
+      <c r="D216" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="217" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A217" s="6">
-        <v>30101</v>
-      </c>
-      <c r="B217" t="s">
-        <v>167</v>
+        <v>20397</v>
+      </c>
+      <c r="B217" s="8" t="s">
+        <v>344</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D217" s="1" t="s">
-        <v>8</v>
+      <c r="D217" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="218" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A218" s="6">
-        <v>40124</v>
+        <v>30101</v>
       </c>
       <c r="B218" t="s">
-        <v>24</v>
+        <v>167</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D218" s="13" t="s">
-        <v>5</v>
+      <c r="D218" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="219" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A219" s="6">
-        <v>40125</v>
+        <v>40124</v>
       </c>
       <c r="B219" t="s">
-        <v>143</v>
+        <v>24</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>4</v>
@@ -4644,24 +4647,24 @@
     </row>
     <row r="220" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A220" s="6">
-        <v>40127</v>
+        <v>40125</v>
       </c>
       <c r="B220" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D220" s="1" t="s">
-        <v>8</v>
+      <c r="D220" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="221" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A221" s="6">
-        <v>40129</v>
+        <v>40127</v>
       </c>
       <c r="B221" t="s">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>4</v>
@@ -4672,24 +4675,24 @@
     </row>
     <row r="222" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A222" s="6">
-        <v>40137</v>
+        <v>40129</v>
       </c>
       <c r="B222" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D222" s="10" t="s">
+      <c r="D222" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="223" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223" s="6">
-        <v>40139</v>
+        <v>40137</v>
       </c>
       <c r="B223" t="s">
-        <v>327</v>
+        <v>121</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>4</v>
@@ -4700,66 +4703,66 @@
     </row>
     <row r="224" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="6">
-        <v>40140</v>
+        <v>40139</v>
       </c>
       <c r="B224" t="s">
-        <v>170</v>
+        <v>327</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D224" s="1" t="s">
+      <c r="D224" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="225" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A225" s="6">
-        <v>40141</v>
+        <v>40140</v>
       </c>
       <c r="B225" t="s">
-        <v>111</v>
+        <v>170</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D225" s="13" t="s">
-        <v>5</v>
+      <c r="D225" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="226" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A226" s="6">
-        <v>40143</v>
+        <v>40141</v>
       </c>
       <c r="B226" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D226" s="10" t="s">
-        <v>8</v>
+      <c r="D226" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="227" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A227" s="6">
-        <v>40144</v>
+        <v>40143</v>
       </c>
       <c r="B227" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D227" s="13" t="s">
-        <v>5</v>
+      <c r="D227" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="228" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A228" s="6">
-        <v>40145</v>
+        <v>40144</v>
       </c>
       <c r="B228" t="s">
-        <v>165</v>
+        <v>107</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>4</v>
@@ -4770,192 +4773,192 @@
     </row>
     <row r="229" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A229" s="6">
-        <v>40150</v>
+        <v>40145</v>
       </c>
       <c r="B229" t="s">
-        <v>221</v>
+        <v>165</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D229" s="10" t="s">
-        <v>8</v>
+      <c r="D229" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="230" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A230" s="6">
-        <v>40151</v>
+        <v>40150</v>
       </c>
       <c r="B230" t="s">
-        <v>54</v>
+        <v>221</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D230" s="1" t="s">
+      <c r="D230" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="231" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A231" s="6">
-        <v>50102</v>
+        <v>40151</v>
       </c>
       <c r="B231" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D231" s="13" t="s">
-        <v>5</v>
+      <c r="D231" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="232" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A232" s="6">
-        <v>50222</v>
+        <v>50102</v>
       </c>
       <c r="B232" t="s">
-        <v>215</v>
+        <v>67</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D232" s="1" t="s">
-        <v>8</v>
+      <c r="D232" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="233" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A233" s="6">
-        <v>50223</v>
+        <v>50222</v>
       </c>
       <c r="B233" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D233" s="10" t="s">
+      <c r="D233" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="234" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A234" s="6">
-        <v>50224</v>
+        <v>50223</v>
       </c>
       <c r="B234" t="s">
-        <v>42</v>
+        <v>194</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D234" s="3" t="s">
-        <v>5</v>
+      <c r="D234" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="235" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A235" s="6">
-        <v>50444</v>
+        <v>50224</v>
       </c>
       <c r="B235" t="s">
-        <v>116</v>
+        <v>42</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D235" s="1" t="s">
-        <v>8</v>
+      <c r="D235" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="236" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A236" s="6">
-        <v>50445</v>
+        <v>50444</v>
       </c>
       <c r="B236" t="s">
-        <v>354</v>
+        <v>116</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D236" s="11" t="s">
-        <v>5</v>
+      <c r="D236" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="237" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A237" s="6">
-        <v>50607</v>
+        <v>50445</v>
       </c>
       <c r="B237" t="s">
-        <v>76</v>
+        <v>354</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D237" s="13" t="s">
+      <c r="D237" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="238" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A238" s="6">
-        <v>50608</v>
+        <v>50607</v>
       </c>
       <c r="B238" t="s">
-        <v>177</v>
+        <v>76</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D238" s="1" t="s">
-        <v>8</v>
+      <c r="D238" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="239" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A239" s="6">
-        <v>50611</v>
-      </c>
-      <c r="B239" s="8" t="s">
-        <v>347</v>
+        <v>50608</v>
+      </c>
+      <c r="B239" t="s">
+        <v>177</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D239" s="14" t="s">
+      <c r="D239" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="240" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A240" s="6">
-        <v>50622</v>
-      </c>
-      <c r="B240" t="s">
-        <v>95</v>
+        <v>50611</v>
+      </c>
+      <c r="B240" s="8" t="s">
+        <v>347</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D240" s="16" t="s">
+      <c r="D240" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="241" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="6">
-        <v>50623</v>
+        <v>50622</v>
       </c>
       <c r="B241" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D241" s="10" t="s">
+      <c r="D241" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="242" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A242" s="6">
-        <v>50625</v>
+        <v>50623</v>
       </c>
       <c r="B242" t="s">
-        <v>204</v>
+        <v>110</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>4</v>
@@ -4966,94 +4969,94 @@
     </row>
     <row r="243" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A243" s="6">
-        <v>50629</v>
+        <v>50625</v>
       </c>
       <c r="B243" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D243" s="1" t="s">
+      <c r="D243" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="244" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A244" s="6">
-        <v>50630</v>
+        <v>50629</v>
       </c>
       <c r="B244" t="s">
-        <v>360</v>
+        <v>188</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D244" s="14" t="s">
+      <c r="D244" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="245" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A245" s="6">
-        <v>50803</v>
+        <v>50630</v>
       </c>
       <c r="B245" t="s">
-        <v>82</v>
+        <v>360</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D245" s="1" t="s">
+      <c r="D245" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="246" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A246" s="6">
-        <v>50805</v>
+        <v>50803</v>
       </c>
       <c r="B246" t="s">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D246" s="10" t="s">
+      <c r="D246" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="247" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A247" s="6">
-        <v>50806</v>
+        <v>50805</v>
       </c>
       <c r="B247" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D247" s="1" t="s">
+      <c r="D247" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="248" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A248" s="6">
-        <v>50808</v>
+        <v>50806</v>
       </c>
       <c r="B248" t="s">
-        <v>16</v>
+        <v>156</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D248" s="13" t="s">
-        <v>5</v>
+      <c r="D248" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="249" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A249" s="6">
-        <v>50809</v>
+        <v>50808</v>
       </c>
       <c r="B249" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>4</v>
@@ -5064,24 +5067,24 @@
     </row>
     <row r="250" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A250" s="6">
-        <v>50810</v>
+        <v>50809</v>
       </c>
       <c r="B250" t="s">
-        <v>175</v>
+        <v>98</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D250" s="1" t="s">
-        <v>8</v>
+      <c r="D250" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="251" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A251" s="6">
-        <v>50812</v>
+        <v>50810</v>
       </c>
       <c r="B251" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>4</v>
@@ -5092,80 +5095,80 @@
     </row>
     <row r="252" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A252" s="6">
-        <v>50813</v>
+        <v>50812</v>
       </c>
       <c r="B252" t="s">
-        <v>71</v>
+        <v>184</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D252" s="17" t="s">
-        <v>9</v>
+      <c r="D252" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="253" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A253" s="6">
-        <v>50815</v>
+        <v>50813</v>
       </c>
       <c r="B253" t="s">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D253" s="10" t="s">
-        <v>8</v>
+      <c r="D253" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="254" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="6">
-        <v>50816</v>
+        <v>50815</v>
       </c>
       <c r="B254" t="s">
-        <v>205</v>
+        <v>114</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D254" s="1" t="s">
+      <c r="D254" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="255" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A255" s="6">
-        <v>50818</v>
+        <v>50816</v>
       </c>
       <c r="B255" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D255" s="13" t="s">
-        <v>5</v>
+      <c r="D255" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="256" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A256" s="6">
-        <v>50819</v>
+        <v>50818</v>
       </c>
       <c r="B256" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D256" s="10" t="s">
-        <v>8</v>
+      <c r="D256" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="257" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A257" s="6">
-        <v>50820</v>
+        <v>50819</v>
       </c>
       <c r="B257" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>4</v>
@@ -5176,66 +5179,66 @@
     </row>
     <row r="258" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A258" s="6">
-        <v>50821</v>
+        <v>50820</v>
       </c>
       <c r="B258" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D258" s="1" t="s">
+      <c r="D258" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="259" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A259" s="6">
-        <v>50823</v>
+        <v>50821</v>
       </c>
       <c r="B259" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D259" s="17" t="s">
-        <v>9</v>
+      <c r="D259" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="260" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A260" s="6">
-        <v>50824</v>
+        <v>50823</v>
       </c>
       <c r="B260" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D260" s="13" t="s">
-        <v>5</v>
+      <c r="D260" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="261" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A261" s="6">
-        <v>50825</v>
+        <v>50824</v>
       </c>
       <c r="B261" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D261" s="10" t="s">
-        <v>8</v>
+      <c r="D261" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="262" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A262" s="6">
-        <v>50826</v>
+        <v>50825</v>
       </c>
       <c r="B262" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>4</v>
@@ -5246,24 +5249,24 @@
     </row>
     <row r="263" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A263" s="6">
-        <v>50827</v>
+        <v>50826</v>
       </c>
       <c r="B263" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D263" s="1" t="s">
+      <c r="D263" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="264" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A264" s="6">
-        <v>50829</v>
+        <v>50827</v>
       </c>
       <c r="B264" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>4</v>
@@ -5274,38 +5277,38 @@
     </row>
     <row r="265" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A265" s="6">
-        <v>50830</v>
+        <v>50829</v>
       </c>
       <c r="B265" t="s">
-        <v>366</v>
+        <v>236</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D265" s="11" t="s">
+      <c r="D265" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="266" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A266" s="6">
-        <v>50831</v>
+        <v>50830</v>
       </c>
       <c r="B266" t="s">
-        <v>351</v>
+        <v>366</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D266" s="11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="267" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A267" s="6">
-        <v>50832</v>
-      </c>
-      <c r="B267" s="8" t="s">
-        <v>349</v>
+        <v>50831</v>
+      </c>
+      <c r="B267" t="s">
+        <v>351</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>4</v>
@@ -5316,80 +5319,80 @@
     </row>
     <row r="268" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A268" s="6">
-        <v>50833</v>
+        <v>50832</v>
       </c>
       <c r="B268" s="8" t="s">
-        <v>397</v>
+        <v>349</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D268" s="11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="269" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A269" s="6">
-        <v>50230</v>
+        <v>50833</v>
       </c>
       <c r="B269" s="8" t="s">
-        <v>379</v>
+        <v>397</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D269" s="11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="270" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A270" s="6">
-        <v>60103</v>
-      </c>
-      <c r="B270" t="s">
-        <v>237</v>
+        <v>50230</v>
+      </c>
+      <c r="B270" s="8" t="s">
+        <v>379</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D270" s="13" t="s">
+      <c r="D270" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="271" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A271" s="6">
-        <v>60109</v>
+        <v>60103</v>
       </c>
       <c r="B271" t="s">
-        <v>328</v>
+        <v>237</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D271" s="11" t="s">
-        <v>9</v>
+      <c r="D271" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="272" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A272" s="6">
-        <v>60124</v>
+        <v>60109</v>
       </c>
       <c r="B272" t="s">
-        <v>238</v>
+        <v>328</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D272" s="13" t="s">
-        <v>5</v>
+      <c r="D272" s="11" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="273" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A273" s="6">
-        <v>60125</v>
+        <v>60124</v>
       </c>
       <c r="B273" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>4</v>
@@ -5400,80 +5403,80 @@
     </row>
     <row r="274" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A274" s="6">
-        <v>60126</v>
+        <v>60125</v>
       </c>
       <c r="B274" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D274" s="10" t="s">
-        <v>8</v>
+      <c r="D274" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="275" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A275" s="6">
-        <v>60128</v>
+        <v>60126</v>
       </c>
       <c r="B275" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D275" s="3" t="s">
-        <v>5</v>
+      <c r="D275" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="276" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A276" s="6">
-        <v>60130</v>
+        <v>60128</v>
       </c>
       <c r="B276" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D276" s="1" t="s">
-        <v>8</v>
+      <c r="D276" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="277" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A277" s="6">
-        <v>60133</v>
+        <v>60130</v>
       </c>
       <c r="B277" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D277" s="13" t="s">
-        <v>5</v>
+      <c r="D277" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="278" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A278" s="6">
-        <v>60134</v>
+        <v>60133</v>
       </c>
       <c r="B278" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D278" s="1" t="s">
-        <v>8</v>
+      <c r="D278" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="279" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A279" s="6">
-        <v>60137</v>
+        <v>60134</v>
       </c>
       <c r="B279" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>4</v>
@@ -5484,10 +5487,10 @@
     </row>
     <row r="280" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A280" s="6">
-        <v>60139</v>
+        <v>60137</v>
       </c>
       <c r="B280" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>4</v>
@@ -5498,10 +5501,10 @@
     </row>
     <row r="281" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A281" s="6">
-        <v>60142</v>
+        <v>60139</v>
       </c>
       <c r="B281" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>4</v>
@@ -5512,10 +5515,10 @@
     </row>
     <row r="282" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A282" s="6">
-        <v>60148</v>
+        <v>60142</v>
       </c>
       <c r="B282" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>4</v>
@@ -5526,10 +5529,10 @@
     </row>
     <row r="283" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A283" s="6">
-        <v>60149</v>
+        <v>60148</v>
       </c>
       <c r="B283" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>4</v>
@@ -5540,66 +5543,66 @@
     </row>
     <row r="284" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A284" s="6">
-        <v>60150</v>
+        <v>60149</v>
       </c>
       <c r="B284" t="s">
-        <v>332</v>
+        <v>249</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D284" s="13" t="s">
-        <v>5</v>
+      <c r="D284" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="285" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A285" s="6">
-        <v>60158</v>
+        <v>60150</v>
       </c>
       <c r="B285" t="s">
-        <v>250</v>
+        <v>332</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D285" s="10" t="s">
-        <v>8</v>
+      <c r="D285" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="286" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A286" s="6">
-        <v>60159</v>
+        <v>60158</v>
       </c>
       <c r="B286" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D286" s="1" t="s">
+      <c r="D286" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="287" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A287" s="6">
-        <v>60162</v>
+        <v>60159</v>
       </c>
       <c r="B287" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D287" s="13" t="s">
-        <v>5</v>
+      <c r="D287" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="288" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A288" s="6">
-        <v>60163</v>
+        <v>60162</v>
       </c>
       <c r="B288" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>4</v>
@@ -5610,24 +5613,24 @@
     </row>
     <row r="289" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A289" s="6">
-        <v>60165</v>
+        <v>60163</v>
       </c>
       <c r="B289" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D289" s="1" t="s">
-        <v>8</v>
+      <c r="D289" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="290" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A290" s="6">
-        <v>60169</v>
+        <v>60165</v>
       </c>
       <c r="B290" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>4</v>
@@ -5638,52 +5641,52 @@
     </row>
     <row r="291" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A291" s="6">
-        <v>60170</v>
-      </c>
-      <c r="B291" s="8" t="s">
-        <v>337</v>
+        <v>60169</v>
+      </c>
+      <c r="B291" t="s">
+        <v>255</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D291" s="11" t="s">
+      <c r="D291" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="292" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A292" s="6">
-        <v>60172</v>
-      </c>
-      <c r="B292" t="s">
-        <v>256</v>
+        <v>60170</v>
+      </c>
+      <c r="B292" s="8" t="s">
+        <v>337</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D292" s="1" t="s">
+      <c r="D292" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="293" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A293" s="6">
-        <v>60174</v>
+        <v>60172</v>
       </c>
       <c r="B293" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D293" s="13" t="s">
-        <v>5</v>
+      <c r="D293" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="294" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A294" s="6">
-        <v>60176</v>
+        <v>60174</v>
       </c>
       <c r="B294" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>4</v>
@@ -5694,52 +5697,52 @@
     </row>
     <row r="295" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A295" s="6">
-        <v>60178</v>
+        <v>60176</v>
       </c>
       <c r="B295" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D295" s="1" t="s">
-        <v>8</v>
+      <c r="D295" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="296" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A296" s="6">
-        <v>60180</v>
+        <v>60178</v>
       </c>
       <c r="B296" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D296" s="10" t="s">
+      <c r="D296" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="297" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A297" s="6">
-        <v>60184</v>
+        <v>60180</v>
       </c>
       <c r="B297" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D297" s="1" t="s">
+      <c r="D297" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="298" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A298" s="6">
-        <v>60190</v>
+        <v>60184</v>
       </c>
       <c r="B298" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>4</v>
@@ -5750,24 +5753,24 @@
     </row>
     <row r="299" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A299" s="6">
-        <v>60191</v>
+        <v>60190</v>
       </c>
       <c r="B299" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D299" s="10" t="s">
+      <c r="D299" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="300" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A300" s="6">
-        <v>60192</v>
+        <v>60191</v>
       </c>
       <c r="B300" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>4</v>
@@ -5778,10 +5781,10 @@
     </row>
     <row r="301" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A301" s="6">
-        <v>60195</v>
+        <v>60192</v>
       </c>
       <c r="B301" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>4</v>
@@ -5792,10 +5795,10 @@
     </row>
     <row r="302" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A302" s="6">
-        <v>60196</v>
+        <v>60195</v>
       </c>
       <c r="B302" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>4</v>
@@ -5806,10 +5809,10 @@
     </row>
     <row r="303" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A303" s="6">
-        <v>60198</v>
+        <v>60196</v>
       </c>
       <c r="B303" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>4</v>
@@ -5820,52 +5823,52 @@
     </row>
     <row r="304" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A304" s="6">
-        <v>60201</v>
+        <v>60198</v>
       </c>
       <c r="B304" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D304" t="s">
-        <v>9</v>
+      <c r="D304" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="305" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A305" s="6">
-        <v>60202</v>
+        <v>60201</v>
       </c>
       <c r="B305" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D305" s="13" t="s">
-        <v>5</v>
+      <c r="D305" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="306" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A306" s="6">
-        <v>60204</v>
+        <v>60202</v>
       </c>
       <c r="B306" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D306" s="1" t="s">
-        <v>8</v>
+      <c r="D306" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="307" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A307" s="6">
-        <v>60205</v>
+        <v>60204</v>
       </c>
       <c r="B307" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>4</v>
@@ -5876,10 +5879,10 @@
     </row>
     <row r="308" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A308" s="6">
-        <v>60206</v>
+        <v>60205</v>
       </c>
       <c r="B308" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>4</v>
@@ -5890,220 +5893,220 @@
     </row>
     <row r="309" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A309" s="6">
-        <v>60209</v>
+        <v>60206</v>
       </c>
       <c r="B309" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D309" s="10" t="s">
+      <c r="D309" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="310" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A310" s="6">
-        <v>60211</v>
+        <v>60209</v>
       </c>
       <c r="B310" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D310" s="1" t="s">
+      <c r="D310" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="311" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A311" s="6">
-        <v>60215</v>
+        <v>60211</v>
       </c>
       <c r="B311" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D311" s="10" t="s">
+      <c r="D311" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="312" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A312" s="6">
-        <v>60216</v>
+        <v>60215</v>
       </c>
       <c r="B312" t="s">
-        <v>381</v>
+        <v>275</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D312" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="313" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A313" s="6">
-        <v>60217</v>
+        <v>60216</v>
       </c>
       <c r="B313" t="s">
-        <v>276</v>
+        <v>381</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D313" s="10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="314" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A314" s="6">
-        <v>60219</v>
+        <v>60217</v>
       </c>
       <c r="B314" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D314" s="1" t="s">
+      <c r="D314" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="315" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A315" s="6">
-        <v>60222</v>
+        <v>60219</v>
       </c>
       <c r="B315" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D315" s="10" t="s">
+      <c r="D315" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="316" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A316" s="6">
-        <v>60225</v>
+        <v>60222</v>
       </c>
       <c r="B316" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D316" s="17" t="s">
-        <v>9</v>
+      <c r="D316" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="317" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A317" s="6">
-        <v>60230</v>
+        <v>60225</v>
       </c>
       <c r="B317" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D317" s="10" t="s">
-        <v>8</v>
+      <c r="D317" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="318" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A318" s="6">
-        <v>60241</v>
-      </c>
-      <c r="B318" s="8" t="s">
-        <v>338</v>
+        <v>60230</v>
+      </c>
+      <c r="B318" t="s">
+        <v>280</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D318" s="7" t="s">
-        <v>9</v>
+      <c r="D318" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="319" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A319" s="6">
-        <v>60242</v>
+        <v>60241</v>
       </c>
       <c r="B319" s="8" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D319" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="320" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A320" s="6">
-        <v>60243</v>
+        <v>60242</v>
       </c>
       <c r="B320" s="8" t="s">
-        <v>395</v>
+        <v>341</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D320" s="7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="321" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A321" s="6">
-        <v>60245</v>
+        <v>60243</v>
       </c>
       <c r="B321" s="8" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D321" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="322" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A322" s="6">
-        <v>60250</v>
+        <v>60245</v>
       </c>
       <c r="B322" s="8" t="s">
-        <v>339</v>
+        <v>387</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D322" s="11" t="s">
-        <v>8</v>
+      <c r="D322" s="7" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="323" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A323" s="6">
-        <v>60253</v>
-      </c>
-      <c r="B323" t="s">
-        <v>281</v>
+        <v>60250</v>
+      </c>
+      <c r="B323" s="8" t="s">
+        <v>339</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D323" s="1" t="s">
+      <c r="D323" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="324" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A324" s="6">
-        <v>60254</v>
+        <v>60253</v>
       </c>
       <c r="B324" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>4</v>
@@ -6114,10 +6117,10 @@
     </row>
     <row r="325" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A325" s="6">
-        <v>60257</v>
+        <v>60254</v>
       </c>
       <c r="B325" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>4</v>
@@ -6128,10 +6131,10 @@
     </row>
     <row r="326" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A326" s="6">
-        <v>60258</v>
+        <v>60257</v>
       </c>
       <c r="B326" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>4</v>
@@ -6142,66 +6145,66 @@
     </row>
     <row r="327" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A327" s="6">
-        <v>60266</v>
-      </c>
-      <c r="B327" s="8" t="s">
-        <v>343</v>
+        <v>60258</v>
+      </c>
+      <c r="B327" t="s">
+        <v>284</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D327" s="11" t="s">
+      <c r="D327" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="328" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A328" s="6">
-        <v>60269</v>
-      </c>
-      <c r="B328" t="s">
-        <v>285</v>
+        <v>60266</v>
+      </c>
+      <c r="B328" s="8" t="s">
+        <v>343</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D328" s="10" t="s">
+      <c r="D328" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="329" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A329" s="6">
-        <v>60270</v>
+        <v>60269</v>
       </c>
       <c r="B329" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D329" s="1" t="s">
-        <v>9</v>
+      <c r="D329" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="330" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A330" s="6">
-        <v>60272</v>
+        <v>60270</v>
       </c>
       <c r="B330" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="331" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A331" s="6">
-        <v>60274</v>
+        <v>60272</v>
       </c>
       <c r="B331" t="s">
-        <v>380</v>
+        <v>287</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>4</v>
@@ -6212,10 +6215,10 @@
     </row>
     <row r="332" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A332" s="6">
-        <v>60275</v>
+        <v>60274</v>
       </c>
       <c r="B332" t="s">
-        <v>288</v>
+        <v>380</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>4</v>
@@ -6226,10 +6229,10 @@
     </row>
     <row r="333" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A333" s="6">
-        <v>60276</v>
+        <v>60275</v>
       </c>
       <c r="B333" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>4</v>
@@ -6240,108 +6243,108 @@
     </row>
     <row r="334" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A334" s="6">
-        <v>60278</v>
+        <v>60276</v>
       </c>
       <c r="B334" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D334" s="13" t="s">
+      <c r="D334" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="335" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A335" s="6">
-        <v>60279</v>
+        <v>60278</v>
       </c>
       <c r="B335" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D335" s="1" t="s">
+      <c r="D335" s="13" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="336" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A336" s="6">
-        <v>60280</v>
+        <v>60279</v>
       </c>
       <c r="B336" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="337" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A337" s="6">
-        <v>60281</v>
-      </c>
-      <c r="B337" s="8" t="s">
-        <v>336</v>
+        <v>60280</v>
+      </c>
+      <c r="B337" t="s">
+        <v>292</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D337" s="11" t="s">
-        <v>9</v>
+      <c r="D337" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="338" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A338" s="6">
-        <v>60282</v>
+        <v>60281</v>
       </c>
       <c r="B338" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D338" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="339" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A339" s="6">
-        <v>60283</v>
-      </c>
-      <c r="B339" t="s">
-        <v>378</v>
+        <v>60282</v>
+      </c>
+      <c r="B339" s="8" t="s">
+        <v>340</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D339" s="1" t="s">
-        <v>8</v>
+      <c r="D339" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="340" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A340" s="6">
-        <v>60284</v>
-      </c>
-      <c r="B340" s="8" t="s">
-        <v>335</v>
+        <v>60283</v>
+      </c>
+      <c r="B340" t="s">
+        <v>378</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D340" s="9" t="s">
-        <v>5</v>
+      <c r="D340" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="341" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A341" s="6">
-        <v>60285</v>
+        <v>60284</v>
       </c>
       <c r="B341" s="8" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>4</v>
@@ -6352,10 +6355,10 @@
     </row>
     <row r="342" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A342" s="6">
-        <v>60286</v>
+        <v>60285</v>
       </c>
       <c r="B342" s="8" t="s">
-        <v>334</v>
+        <v>350</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>4</v>
@@ -6366,52 +6369,52 @@
     </row>
     <row r="343" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A343" s="6">
-        <v>60287</v>
-      </c>
-      <c r="B343" t="s">
-        <v>377</v>
+        <v>60286</v>
+      </c>
+      <c r="B343" s="8" t="s">
+        <v>334</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D343" s="12" t="s">
+      <c r="D343" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="344" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A344" s="6">
-        <v>60289</v>
+        <v>60287</v>
       </c>
       <c r="B344" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D344" s="12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="345" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A345" s="6">
-        <v>60290</v>
+        <v>60289</v>
       </c>
       <c r="B345" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D345" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="346" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A346" s="6">
-        <v>60291</v>
+        <v>60290</v>
       </c>
       <c r="B346" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>4</v>
@@ -6422,38 +6425,38 @@
     </row>
     <row r="347" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A347" s="6">
-        <v>60296</v>
+        <v>60291</v>
       </c>
       <c r="B347" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D347" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="348" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A348" s="6">
-        <v>60297</v>
+        <v>60296</v>
       </c>
       <c r="B348" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D348" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="349" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A349" s="6">
-        <v>60299</v>
+        <v>60297</v>
       </c>
       <c r="B349" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>4</v>
@@ -6464,38 +6467,38 @@
     </row>
     <row r="350" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A350" s="6">
-        <v>61004</v>
+        <v>60299</v>
       </c>
       <c r="B350" t="s">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D350" s="15" t="s">
+      <c r="D350" s="12" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="351" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A351" s="6">
-        <v>61009</v>
+        <v>61004</v>
       </c>
       <c r="B351" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D351" s="12" t="s">
-        <v>8</v>
+      <c r="D351" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="352" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A352" s="6">
-        <v>61012</v>
+        <v>61009</v>
       </c>
       <c r="B352" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>4</v>
@@ -6506,10 +6509,10 @@
     </row>
     <row r="353" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A353" s="6">
-        <v>61018</v>
+        <v>61012</v>
       </c>
       <c r="B353" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>4</v>
@@ -6520,10 +6523,10 @@
     </row>
     <row r="354" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A354" s="6">
-        <v>61102</v>
+        <v>61018</v>
       </c>
       <c r="B354" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>4</v>
@@ -6534,52 +6537,52 @@
     </row>
     <row r="355" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A355" s="6">
-        <v>61205</v>
+        <v>61102</v>
       </c>
       <c r="B355" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D355" s="15" t="s">
-        <v>5</v>
+      <c r="D355" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="356" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A356" s="6">
-        <v>70100</v>
+        <v>61205</v>
       </c>
       <c r="B356" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D356" s="12" t="s">
-        <v>8</v>
+      <c r="D356" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="357" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A357" s="6">
-        <v>70101</v>
+        <v>70100</v>
       </c>
       <c r="B357" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D357" s="15" t="s">
-        <v>5</v>
+      <c r="D357" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="358" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A358" s="6">
-        <v>70102</v>
+        <v>70101</v>
       </c>
       <c r="B358" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>4</v>
@@ -6590,80 +6593,80 @@
     </row>
     <row r="359" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A359" s="6">
-        <v>70103</v>
+        <v>70102</v>
       </c>
       <c r="B359" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D359" s="12" t="s">
-        <v>8</v>
+      <c r="D359" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="360" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A360" s="6">
-        <v>70106</v>
+        <v>70103</v>
       </c>
       <c r="B360" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D360" s="15" t="s">
-        <v>5</v>
+      <c r="D360" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="361" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A361" s="6">
-        <v>70109</v>
+        <v>70106</v>
       </c>
       <c r="B361" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D361" s="12" t="s">
-        <v>8</v>
+      <c r="D361" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="362" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A362" s="6">
-        <v>70113</v>
+        <v>70109</v>
       </c>
       <c r="B362" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D362" s="15" t="s">
-        <v>5</v>
+      <c r="D362" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="363" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A363" s="6">
-        <v>70114</v>
+        <v>70113</v>
       </c>
       <c r="B363" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D363" s="9" t="s">
-        <v>9</v>
+      <c r="D363" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="364" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A364" s="6">
-        <v>70115</v>
+        <v>70114</v>
       </c>
       <c r="B364" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>4</v>
@@ -6674,24 +6677,24 @@
     </row>
     <row r="365" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A365" s="6">
-        <v>70638</v>
+        <v>70115</v>
       </c>
       <c r="B365" t="s">
-        <v>306</v>
+        <v>331</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D365" s="12" t="s">
-        <v>8</v>
+      <c r="D365" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="366" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A366" s="6">
-        <v>70639</v>
+        <v>70638</v>
       </c>
       <c r="B366" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>4</v>
@@ -6702,10 +6705,10 @@
     </row>
     <row r="367" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A367" s="6">
-        <v>70640</v>
+        <v>70639</v>
       </c>
       <c r="B367" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>4</v>
@@ -6716,10 +6719,10 @@
     </row>
     <row r="368" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A368" s="6">
-        <v>70642</v>
+        <v>70640</v>
       </c>
       <c r="B368" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>4</v>
@@ -6730,10 +6733,10 @@
     </row>
     <row r="369" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A369" s="6">
-        <v>90504</v>
+        <v>70642</v>
       </c>
       <c r="B369" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>4</v>
@@ -6744,10 +6747,10 @@
     </row>
     <row r="370" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A370" s="6">
-        <v>90509</v>
+        <v>90504</v>
       </c>
       <c r="B370" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>4</v>
@@ -6758,52 +6761,52 @@
     </row>
     <row r="371" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A371" s="6">
-        <v>90602</v>
+        <v>90509</v>
       </c>
       <c r="B371" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D371" s="15" t="s">
-        <v>5</v>
+      <c r="D371" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="372" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A372" s="6">
-        <v>90621</v>
+        <v>90602</v>
       </c>
       <c r="B372" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D372" s="12" t="s">
-        <v>8</v>
+      <c r="D372" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="373" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A373" s="6">
-        <v>90622</v>
+        <v>90621</v>
       </c>
       <c r="B373" t="s">
-        <v>333</v>
+        <v>313</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D373" s="9" t="s">
-        <v>5</v>
+      <c r="D373" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="374" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A374" s="6">
-        <v>90631</v>
-      </c>
-      <c r="B374" s="8" t="s">
-        <v>342</v>
+        <v>90622</v>
+      </c>
+      <c r="B374" t="s">
+        <v>333</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>4</v>
@@ -6814,24 +6817,24 @@
     </row>
     <row r="375" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A375" s="6">
-        <v>90658</v>
-      </c>
-      <c r="B375" t="s">
-        <v>314</v>
+        <v>90631</v>
+      </c>
+      <c r="B375" s="8" t="s">
+        <v>342</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D375" s="12" t="s">
-        <v>8</v>
+      <c r="D375" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="376" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A376" s="6">
-        <v>90660</v>
+        <v>90658</v>
       </c>
       <c r="B376" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>4</v>
@@ -6842,10 +6845,10 @@
     </row>
     <row r="377" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A377" s="6">
-        <v>90668</v>
+        <v>90660</v>
       </c>
       <c r="B377" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>4</v>
@@ -6856,10 +6859,10 @@
     </row>
     <row r="378" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A378" s="6">
-        <v>90671</v>
+        <v>90668</v>
       </c>
       <c r="B378" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>4</v>
@@ -6870,10 +6873,10 @@
     </row>
     <row r="379" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A379" s="6">
-        <v>90679</v>
+        <v>90671</v>
       </c>
       <c r="B379" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>4</v>
@@ -6884,10 +6887,10 @@
     </row>
     <row r="380" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A380" s="6">
-        <v>90683</v>
+        <v>90679</v>
       </c>
       <c r="B380" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>4</v>
@@ -6898,10 +6901,10 @@
     </row>
     <row r="381" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A381" s="6">
-        <v>90705</v>
+        <v>90683</v>
       </c>
       <c r="B381" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>4</v>
@@ -6912,10 +6915,10 @@
     </row>
     <row r="382" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A382" s="6">
-        <v>90706</v>
+        <v>90705</v>
       </c>
       <c r="B382" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>4</v>
@@ -6926,10 +6929,10 @@
     </row>
     <row r="383" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A383" s="6">
-        <v>90708</v>
+        <v>90706</v>
       </c>
       <c r="B383" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>4</v>
@@ -6940,10 +6943,10 @@
     </row>
     <row r="384" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A384" s="6">
-        <v>90709</v>
+        <v>90708</v>
       </c>
       <c r="B384" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>4</v>
@@ -6954,10 +6957,10 @@
     </row>
     <row r="385" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A385" s="6">
-        <v>1218</v>
+        <v>90709</v>
       </c>
       <c r="B385" t="s">
-        <v>382</v>
+        <v>323</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>4</v>
@@ -6968,10 +6971,10 @@
     </row>
     <row r="386" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A386" s="6">
-        <v>1959</v>
-      </c>
-      <c r="B386" s="8" t="s">
-        <v>383</v>
+        <v>1218</v>
+      </c>
+      <c r="B386" t="s">
+        <v>382</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>4</v>
@@ -6982,10 +6985,10 @@
     </row>
     <row r="387" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A387" s="6">
-        <v>5625</v>
+        <v>1959</v>
       </c>
       <c r="B387" s="8" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>4</v>
@@ -6996,10 +6999,10 @@
     </row>
     <row r="388" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A388" s="6">
-        <v>1817</v>
+        <v>5625</v>
       </c>
       <c r="B388" s="8" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>4</v>
@@ -7010,10 +7013,10 @@
     </row>
     <row r="389" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A389" s="6">
-        <v>5737</v>
+        <v>1817</v>
       </c>
       <c r="B389" s="8" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>4</v>
@@ -7024,34 +7027,48 @@
     </row>
     <row r="390" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A390" s="6">
-        <v>60295</v>
+        <v>5737</v>
       </c>
       <c r="B390" s="8" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D390" s="9" t="s">
-        <v>9</v>
+      <c r="D390" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="391" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A391" s="6">
+        <v>60295</v>
+      </c>
+      <c r="B391" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="C391" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D391" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="392" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A392" s="6">
         <v>1045</v>
       </c>
-      <c r="B391" s="8" t="s">
+      <c r="B392" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="C391" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D391" s="9" t="s">
+      <c r="C392" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D392" s="9" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D339"/>
+  <autoFilter ref="A1:D340"/>
   <sortState ref="A2:D374">
     <sortCondition ref="A277"/>
   </sortState>

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$340</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$341</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1177" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1183" uniqueCount="401">
   <si>
     <t>CUENTA</t>
   </si>
@@ -1219,6 +1219,12 @@
   </si>
   <si>
     <t>BELISARIO FERRETERIA</t>
+  </si>
+  <si>
+    <t>EL CORDOBES FERRETERIA</t>
+  </si>
+  <si>
+    <t>FERRETERIA ALFA</t>
   </si>
 </sst>
 </file>
@@ -1301,7 +1307,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1342,6 +1348,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1571,7 +1578,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D392"/>
+  <dimension ref="A1:D394"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -2435,52 +2442,52 @@
     </row>
     <row r="62" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="6">
-        <v>1020</v>
-      </c>
-      <c r="B62" t="s">
-        <v>362</v>
+        <v>1018</v>
+      </c>
+      <c r="B62" s="18" t="s">
+        <v>399</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D62" s="11" t="s">
-        <v>5</v>
+      <c r="D62" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="6">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B63" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D63" s="14" t="s">
+      <c r="D63" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="6">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="B64" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D64" s="11" t="s">
+      <c r="D64" s="14" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="6">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B65" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>4</v>
@@ -2491,136 +2498,136 @@
     </row>
     <row r="66" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="6">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B66" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="6">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B67" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D67" s="14" t="s">
-        <v>5</v>
+      <c r="D67" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="6">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B68" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D68" s="11" t="s">
+      <c r="D68" s="14" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="6">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B69" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D69" s="14" t="s">
-        <v>8</v>
+      <c r="D69" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="6">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B70" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D70" s="11" t="s">
-        <v>5</v>
+      <c r="D70" s="14" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="6">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B71" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D71" s="14" t="s">
+      <c r="D71" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="6">
-        <v>1031</v>
-      </c>
-      <c r="B72" s="8" t="s">
-        <v>346</v>
+        <v>1030</v>
+      </c>
+      <c r="B72" t="s">
+        <v>356</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="6">
-        <v>1032</v>
-      </c>
-      <c r="B73" t="s">
-        <v>369</v>
+        <v>1031</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>346</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D73" s="14" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="6">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B74" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D74" s="11" t="s">
+      <c r="D74" s="14" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="6">
-        <v>1034</v>
-      </c>
-      <c r="B75" s="8" t="s">
-        <v>373</v>
+        <v>1033</v>
+      </c>
+      <c r="B75" t="s">
+        <v>357</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>4</v>
@@ -2631,10 +2638,10 @@
     </row>
     <row r="76" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="6">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>345</v>
+        <v>373</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>4</v>
@@ -2645,10 +2652,10 @@
     </row>
     <row r="77" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="6">
-        <v>1036</v>
-      </c>
-      <c r="B77" t="s">
-        <v>358</v>
+        <v>1035</v>
+      </c>
+      <c r="B77" s="8" t="s">
+        <v>345</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>4</v>
@@ -2659,10 +2666,10 @@
     </row>
     <row r="78" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="6">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="B78" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>4</v>
@@ -2673,10 +2680,10 @@
     </row>
     <row r="79" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="6">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B79" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>4</v>
@@ -2687,10 +2694,10 @@
     </row>
     <row r="80" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="6">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="B80" t="s">
-        <v>371</v>
+        <v>352</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>4</v>
@@ -2701,94 +2708,94 @@
     </row>
     <row r="81" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="6">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="B81" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D81" s="11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="6">
-        <v>1044</v>
+        <v>1040</v>
       </c>
       <c r="B82" t="s">
-        <v>394</v>
+        <v>372</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="6">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="B83" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D83" s="11" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="6">
-        <v>1416</v>
+        <v>1046</v>
       </c>
       <c r="B84" t="s">
-        <v>217</v>
+        <v>398</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D84" s="1" t="s">
-        <v>8</v>
+      <c r="D84" s="11" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="6">
-        <v>10107</v>
+        <v>1416</v>
       </c>
       <c r="B85" t="s">
-        <v>96</v>
+        <v>217</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D85" t="s">
-        <v>9</v>
+      <c r="D85" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="6">
-        <v>10137</v>
+        <v>10107</v>
       </c>
       <c r="B86" t="s">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D86" s="1" t="s">
-        <v>8</v>
+      <c r="D86" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="6">
-        <v>10157</v>
+        <v>10137</v>
       </c>
       <c r="B87" t="s">
-        <v>183</v>
+        <v>123</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>4</v>
@@ -2799,10 +2806,10 @@
     </row>
     <row r="88" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="6">
-        <v>10158</v>
+        <v>10157</v>
       </c>
       <c r="B88" t="s">
-        <v>65</v>
+        <v>183</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>4</v>
@@ -2813,108 +2820,108 @@
     </row>
     <row r="89" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="6">
-        <v>10160</v>
+        <v>10158</v>
       </c>
       <c r="B89" t="s">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D89" s="13" t="s">
-        <v>5</v>
+      <c r="D89" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="6">
-        <v>10162</v>
+        <v>10160</v>
       </c>
       <c r="B90" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D90" s="1" t="s">
-        <v>8</v>
+      <c r="D90" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="6">
-        <v>10163</v>
+        <v>10162</v>
       </c>
       <c r="B91" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D91" s="13" t="s">
-        <v>5</v>
+      <c r="D91" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="6">
-        <v>10165</v>
+        <v>10163</v>
       </c>
       <c r="B92" t="s">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D92" s="1" t="s">
-        <v>8</v>
+      <c r="D92" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="6">
-        <v>10166</v>
-      </c>
-      <c r="B93" s="8" t="s">
-        <v>348</v>
+        <v>10165</v>
+      </c>
+      <c r="B93" t="s">
+        <v>19</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D93" s="11" t="s">
+      <c r="D93" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="6">
-        <v>10167</v>
-      </c>
-      <c r="B94" t="s">
-        <v>39</v>
+        <v>10166</v>
+      </c>
+      <c r="B94" s="8" t="s">
+        <v>348</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D94" s="13" t="s">
-        <v>5</v>
+      <c r="D94" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="6">
-        <v>10424</v>
+        <v>10167</v>
       </c>
       <c r="B95" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D95" s="17" t="s">
-        <v>9</v>
+      <c r="D95" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="6">
-        <v>10425</v>
+        <v>10424</v>
       </c>
       <c r="B96" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>4</v>
@@ -2925,24 +2932,24 @@
     </row>
     <row r="97" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="6">
-        <v>20094</v>
+        <v>10425</v>
       </c>
       <c r="B97" t="s">
-        <v>198</v>
+        <v>15</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D97" s="10" t="s">
-        <v>8</v>
+      <c r="D97" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="6">
-        <v>20095</v>
+        <v>20094</v>
       </c>
       <c r="B98" t="s">
-        <v>153</v>
+        <v>198</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>4</v>
@@ -2953,66 +2960,66 @@
     </row>
     <row r="99" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="6">
-        <v>20096</v>
+        <v>20095</v>
       </c>
       <c r="B99" t="s">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D99" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="6">
-        <v>20100</v>
+        <v>20096</v>
       </c>
       <c r="B100" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D100" s="1" t="s">
-        <v>8</v>
+      <c r="D100" s="10" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="6">
-        <v>20101</v>
+        <v>20100</v>
       </c>
       <c r="B101" t="s">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="6">
-        <v>20103</v>
+        <v>20101</v>
       </c>
       <c r="B102" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="6">
-        <v>20106</v>
+        <v>20103</v>
       </c>
       <c r="B103" t="s">
-        <v>155</v>
+        <v>81</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>4</v>
@@ -3023,80 +3030,80 @@
     </row>
     <row r="104" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="6">
-        <v>20108</v>
+        <v>20106</v>
       </c>
       <c r="B104" t="s">
-        <v>219</v>
+        <v>155</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D104" s="10" t="s">
+      <c r="D104" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="6">
-        <v>20109</v>
+        <v>20108</v>
       </c>
       <c r="B105" t="s">
-        <v>53</v>
+        <v>219</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D105" s="1" t="s">
+      <c r="D105" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="6">
-        <v>20110</v>
+        <v>20109</v>
       </c>
       <c r="B106" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D106" s="13" t="s">
-        <v>5</v>
+      <c r="D106" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="6">
-        <v>20113</v>
+        <v>20110</v>
       </c>
       <c r="B107" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D107" s="10" t="s">
-        <v>8</v>
+      <c r="D107" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="6">
-        <v>20114</v>
+        <v>20113</v>
       </c>
       <c r="B108" t="s">
-        <v>126</v>
+        <v>93</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D108" s="1" t="s">
+      <c r="D108" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="6">
-        <v>20116</v>
+        <v>20114</v>
       </c>
       <c r="B109" t="s">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>4</v>
@@ -3107,10 +3114,10 @@
     </row>
     <row r="110" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="6">
-        <v>20117</v>
+        <v>20116</v>
       </c>
       <c r="B110" t="s">
-        <v>186</v>
+        <v>73</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>4</v>
@@ -3121,10 +3128,10 @@
     </row>
     <row r="111" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="6">
-        <v>20118</v>
+        <v>20117</v>
       </c>
       <c r="B111" t="s">
-        <v>160</v>
+        <v>186</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>4</v>
@@ -3135,10 +3142,10 @@
     </row>
     <row r="112" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="6">
-        <v>20120</v>
+        <v>20118</v>
       </c>
       <c r="B112" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>4</v>
@@ -3149,10 +3156,10 @@
     </row>
     <row r="113" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="6">
-        <v>20121</v>
+        <v>20120</v>
       </c>
       <c r="B113" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>4</v>
@@ -3163,38 +3170,38 @@
     </row>
     <row r="114" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="6">
-        <v>20125</v>
+        <v>20121</v>
       </c>
       <c r="B114" t="s">
-        <v>88</v>
+        <v>159</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D114" s="10" t="s">
+      <c r="D114" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="6">
-        <v>20127</v>
+        <v>20125</v>
       </c>
       <c r="B115" t="s">
-        <v>168</v>
+        <v>88</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D115" s="1" t="s">
+      <c r="D115" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="6">
-        <v>20128</v>
+        <v>20127</v>
       </c>
       <c r="B116" t="s">
-        <v>208</v>
+        <v>168</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>4</v>
@@ -3205,52 +3212,52 @@
     </row>
     <row r="117" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="6">
-        <v>20129</v>
+        <v>20128</v>
       </c>
       <c r="B117" t="s">
-        <v>326</v>
+        <v>208</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D117" s="10" t="s">
+      <c r="D117" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="6">
-        <v>20137</v>
+        <v>20129</v>
       </c>
       <c r="B118" t="s">
-        <v>79</v>
+        <v>326</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D118" s="3" t="s">
-        <v>5</v>
+      <c r="D118" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="6">
-        <v>20138</v>
+        <v>20137</v>
       </c>
       <c r="B119" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D119" s="13" t="s">
+      <c r="D119" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="6">
-        <v>20140</v>
+        <v>20138</v>
       </c>
       <c r="B120" t="s">
-        <v>218</v>
+        <v>113</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>4</v>
@@ -3261,24 +3268,24 @@
     </row>
     <row r="121" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="6">
-        <v>20142</v>
+        <v>20140</v>
       </c>
       <c r="B121" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D121" s="1" t="s">
-        <v>8</v>
+      <c r="D121" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="6">
-        <v>20146</v>
+        <v>20142</v>
       </c>
       <c r="B122" t="s">
-        <v>148</v>
+        <v>193</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>4</v>
@@ -3289,10 +3296,10 @@
     </row>
     <row r="123" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="6">
-        <v>20148</v>
+        <v>20146</v>
       </c>
       <c r="B123" t="s">
-        <v>38</v>
+        <v>148</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>4</v>
@@ -3303,52 +3310,52 @@
     </row>
     <row r="124" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="6">
-        <v>20156</v>
+        <v>20148</v>
       </c>
       <c r="B124" t="s">
-        <v>179</v>
+        <v>38</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D124" s="10" t="s">
+      <c r="D124" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="6">
-        <v>20159</v>
+        <v>20156</v>
       </c>
       <c r="B125" t="s">
-        <v>120</v>
+        <v>179</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D125" s="17" t="s">
-        <v>9</v>
+      <c r="D125" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="6">
-        <v>20160</v>
+        <v>20159</v>
       </c>
       <c r="B126" t="s">
-        <v>224</v>
+        <v>120</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D126" s="10" t="s">
-        <v>8</v>
+      <c r="D126" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="6">
-        <v>20163</v>
+        <v>20160</v>
       </c>
       <c r="B127" t="s">
-        <v>23</v>
+        <v>224</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>4</v>
@@ -3359,52 +3366,52 @@
     </row>
     <row r="128" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="6">
-        <v>20164</v>
+        <v>20163</v>
       </c>
       <c r="B128" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D128" t="s">
-        <v>9</v>
+      <c r="D128" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="6">
-        <v>20165</v>
+        <v>20164</v>
       </c>
       <c r="B129" t="s">
-        <v>131</v>
+        <v>18</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D129" s="10" t="s">
-        <v>8</v>
+      <c r="D129" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="6">
-        <v>20166</v>
+        <v>20165</v>
       </c>
       <c r="B130" t="s">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D130" s="1" t="s">
+      <c r="D130" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="6">
-        <v>20169</v>
+        <v>20166</v>
       </c>
       <c r="B131" t="s">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>4</v>
@@ -3415,38 +3422,38 @@
     </row>
     <row r="132" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="6">
-        <v>20173</v>
+        <v>20169</v>
       </c>
       <c r="B132" t="s">
-        <v>112</v>
+        <v>151</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D132" s="10" t="s">
+      <c r="D132" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="6">
-        <v>20174</v>
+        <v>20173</v>
       </c>
       <c r="B133" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D133" s="1" t="s">
+      <c r="D133" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="6">
-        <v>20178</v>
+        <v>20174</v>
       </c>
       <c r="B134" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>4</v>
@@ -3457,80 +3464,80 @@
     </row>
     <row r="135" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="6">
-        <v>20179</v>
+        <v>20178</v>
       </c>
       <c r="B135" t="s">
-        <v>171</v>
+        <v>117</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D135" t="s">
-        <v>9</v>
+      <c r="D135" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="6">
-        <v>20180</v>
+        <v>20179</v>
       </c>
       <c r="B136" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D136" s="1" t="s">
-        <v>8</v>
+      <c r="D136" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="6">
-        <v>20183</v>
+        <v>20180</v>
       </c>
       <c r="B137" t="s">
-        <v>370</v>
+        <v>149</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D137" s="14" t="s">
-        <v>5</v>
+      <c r="D137" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="6">
-        <v>20189</v>
+        <v>20183</v>
       </c>
       <c r="B138" t="s">
-        <v>329</v>
+        <v>370</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D138" s="1" t="s">
-        <v>8</v>
+      <c r="D138" s="14" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="6">
-        <v>20200</v>
+        <v>20189</v>
       </c>
       <c r="B139" t="s">
-        <v>83</v>
+        <v>329</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D139" s="13" t="s">
-        <v>5</v>
+      <c r="D139" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="6">
-        <v>20201</v>
+        <v>20200</v>
       </c>
       <c r="B140" t="s">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>4</v>
@@ -3541,150 +3548,150 @@
     </row>
     <row r="141" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="6">
-        <v>20204</v>
+        <v>20201</v>
       </c>
       <c r="B141" t="s">
-        <v>57</v>
+        <v>145</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D141" s="10" t="s">
-        <v>8</v>
+      <c r="D141" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="6">
-        <v>20205</v>
+        <v>20204</v>
       </c>
       <c r="B142" t="s">
-        <v>206</v>
+        <v>57</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D142" s="1" t="s">
-        <v>9</v>
+      <c r="D142" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="6">
-        <v>20211</v>
+        <v>20205</v>
       </c>
       <c r="B143" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D143" s="10" t="s">
-        <v>8</v>
+      <c r="D143" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="6">
-        <v>20224</v>
+        <v>20211</v>
       </c>
       <c r="B144" t="s">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D144" s="1" t="s">
+      <c r="D144" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="6">
-        <v>20227</v>
+        <v>20224</v>
       </c>
       <c r="B145" t="s">
-        <v>192</v>
+        <v>85</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D145" s="10" t="s">
+      <c r="D145" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="6">
-        <v>20228</v>
+        <v>20227</v>
       </c>
       <c r="B146" t="s">
-        <v>91</v>
+        <v>192</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D146" s="13" t="s">
-        <v>5</v>
+      <c r="D146" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="6">
-        <v>20230</v>
+        <v>20228</v>
       </c>
       <c r="B147" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D147" s="10" t="s">
-        <v>8</v>
+      <c r="D147" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="6">
-        <v>20234</v>
+        <v>20230</v>
       </c>
       <c r="B148" t="s">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D148" s="13" t="s">
-        <v>5</v>
+      <c r="D148" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="6">
-        <v>20236</v>
+        <v>20234</v>
       </c>
       <c r="B149" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D149" s="3" t="s">
+      <c r="D149" s="13" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="6">
-        <v>20238</v>
+        <v>20236</v>
       </c>
       <c r="B150" t="s">
-        <v>139</v>
+        <v>31</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D150" s="13" t="s">
+      <c r="D150" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="6">
-        <v>20241</v>
+        <v>20238</v>
       </c>
       <c r="B151" t="s">
-        <v>22</v>
+        <v>139</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>4</v>
@@ -3695,24 +3702,24 @@
     </row>
     <row r="152" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="6">
-        <v>20242</v>
+        <v>20241</v>
       </c>
       <c r="B152" t="s">
-        <v>216</v>
+        <v>22</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D152" s="10" t="s">
-        <v>8</v>
+      <c r="D152" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="6">
-        <v>20244</v>
+        <v>20242</v>
       </c>
       <c r="B153" t="s">
-        <v>124</v>
+        <v>216</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>4</v>
@@ -3723,108 +3730,108 @@
     </row>
     <row r="154" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="6">
-        <v>20246</v>
+        <v>20244</v>
       </c>
       <c r="B154" t="s">
-        <v>14</v>
+        <v>124</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D154" s="13" t="s">
-        <v>5</v>
+      <c r="D154" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="155" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="6">
-        <v>20249</v>
+        <v>20246</v>
       </c>
       <c r="B155" t="s">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D155" s="10" t="s">
-        <v>8</v>
+      <c r="D155" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="156" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="6">
-        <v>20256</v>
+        <v>20249</v>
       </c>
       <c r="B156" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D156" s="1" t="s">
+      <c r="D156" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="6">
-        <v>20257</v>
+        <v>20256</v>
       </c>
       <c r="B157" t="s">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D157" s="17" t="s">
-        <v>9</v>
+      <c r="D157" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="6">
-        <v>20258</v>
+        <v>20257</v>
       </c>
       <c r="B158" t="s">
-        <v>199</v>
+        <v>150</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D158" s="1" t="s">
-        <v>8</v>
+      <c r="D158" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="159" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A159" s="6">
-        <v>20260</v>
+        <v>20258</v>
       </c>
       <c r="B159" t="s">
-        <v>68</v>
+        <v>199</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D159" s="13" t="s">
-        <v>5</v>
+      <c r="D159" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="160" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="6">
-        <v>20261</v>
+        <v>20260</v>
       </c>
       <c r="B160" t="s">
-        <v>207</v>
+        <v>68</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D160" s="10" t="s">
-        <v>8</v>
+      <c r="D160" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="161" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="6">
-        <v>20262</v>
+        <v>20261</v>
       </c>
       <c r="B161" t="s">
-        <v>92</v>
+        <v>207</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>4</v>
@@ -3835,192 +3842,192 @@
     </row>
     <row r="162" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="6">
-        <v>20268</v>
+        <v>20262</v>
       </c>
       <c r="B162" t="s">
-        <v>201</v>
+        <v>92</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D162" s="1" t="s">
+      <c r="D162" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="163" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="6">
-        <v>20271</v>
+        <v>20268</v>
       </c>
       <c r="B163" t="s">
-        <v>34</v>
+        <v>201</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D163" s="13" t="s">
-        <v>5</v>
+      <c r="D163" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="6">
-        <v>20272</v>
+        <v>20271</v>
       </c>
       <c r="B164" t="s">
-        <v>178</v>
+        <v>34</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D164" s="1" t="s">
-        <v>8</v>
+      <c r="D164" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="165" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="6">
-        <v>20275</v>
+        <v>20272</v>
       </c>
       <c r="B165" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D165" s="13" t="s">
-        <v>5</v>
+      <c r="D165" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="6">
-        <v>20277</v>
+        <v>20275</v>
       </c>
       <c r="B166" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D166" s="1" t="s">
-        <v>8</v>
+      <c r="D166" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="6">
-        <v>20281</v>
+        <v>20277</v>
       </c>
       <c r="B167" t="s">
-        <v>105</v>
+        <v>154</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D167" s="3" t="s">
-        <v>5</v>
+      <c r="D167" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="168" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="6">
-        <v>20282</v>
+        <v>20281</v>
       </c>
       <c r="B168" t="s">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D168" s="1" t="s">
-        <v>9</v>
+      <c r="D168" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="6">
-        <v>20284</v>
+        <v>20282</v>
       </c>
       <c r="B169" t="s">
-        <v>17</v>
+        <v>141</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D169" s="17" t="s">
+      <c r="D169" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A170" s="6">
-        <v>20285</v>
+        <v>20284</v>
       </c>
       <c r="B170" t="s">
-        <v>146</v>
+        <v>17</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D170" s="1" t="s">
-        <v>8</v>
+      <c r="D170" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="171" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="6">
-        <v>20289</v>
+        <v>20285</v>
       </c>
       <c r="B171" t="s">
-        <v>52</v>
+        <v>146</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D171" s="3" t="s">
-        <v>5</v>
+      <c r="D171" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="6">
-        <v>20290</v>
+        <v>20289</v>
       </c>
       <c r="B172" t="s">
-        <v>103</v>
+        <v>52</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D172" s="1" t="s">
-        <v>8</v>
+      <c r="D172" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="6">
-        <v>20291</v>
+        <v>20290</v>
       </c>
       <c r="B173" t="s">
-        <v>187</v>
+        <v>103</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D173" s="10" t="s">
+      <c r="D173" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="174" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="6">
-        <v>20292</v>
+        <v>20291</v>
       </c>
       <c r="B174" t="s">
-        <v>32</v>
+        <v>187</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D174" s="13" t="s">
-        <v>5</v>
+      <c r="D174" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="175" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="6">
-        <v>20293</v>
+        <v>20292</v>
       </c>
       <c r="B175" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>4</v>
@@ -4031,52 +4038,52 @@
     </row>
     <row r="176" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="6">
-        <v>20294</v>
+        <v>20293</v>
       </c>
       <c r="B176" t="s">
-        <v>202</v>
+        <v>43</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D176" s="10" t="s">
-        <v>8</v>
+      <c r="D176" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="177" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A177" s="6">
-        <v>20296</v>
+        <v>20294</v>
       </c>
       <c r="B177" t="s">
-        <v>144</v>
+        <v>202</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D177" s="13" t="s">
-        <v>5</v>
+      <c r="D177" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="6">
-        <v>20298</v>
+        <v>20296</v>
       </c>
       <c r="B178" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D178" s="1" t="s">
-        <v>8</v>
+      <c r="D178" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="179" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="6">
-        <v>20299</v>
+        <v>20298</v>
       </c>
       <c r="B179" t="s">
-        <v>58</v>
+        <v>169</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>4</v>
@@ -4087,10 +4094,10 @@
     </row>
     <row r="180" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="6">
-        <v>20301</v>
+        <v>20299</v>
       </c>
       <c r="B180" t="s">
-        <v>134</v>
+        <v>58</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>4</v>
@@ -4101,10 +4108,10 @@
     </row>
     <row r="181" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="6">
-        <v>20303</v>
+        <v>20301</v>
       </c>
       <c r="B181" t="s">
-        <v>37</v>
+        <v>134</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>4</v>
@@ -4115,24 +4122,24 @@
     </row>
     <row r="182" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="6">
-        <v>20309</v>
+        <v>20303</v>
       </c>
       <c r="B182" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D182" s="13" t="s">
-        <v>5</v>
+      <c r="D182" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="183" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="6">
-        <v>20310</v>
+        <v>20309</v>
       </c>
       <c r="B183" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>4</v>
@@ -4143,52 +4150,52 @@
     </row>
     <row r="184" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="6">
-        <v>20318</v>
+        <v>20310</v>
       </c>
       <c r="B184" t="s">
-        <v>209</v>
+        <v>59</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D184" s="1" t="s">
-        <v>8</v>
+      <c r="D184" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="185" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="6">
-        <v>20319</v>
+        <v>20318</v>
       </c>
       <c r="B185" t="s">
-        <v>101</v>
+        <v>209</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D185" s="10" t="s">
+      <c r="D185" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="186" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="6">
-        <v>20320</v>
+        <v>20319</v>
       </c>
       <c r="B186" t="s">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D186" s="1" t="s">
+      <c r="D186" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="187" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="6">
-        <v>20324</v>
+        <v>20320</v>
       </c>
       <c r="B187" t="s">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>4</v>
@@ -4199,10 +4206,10 @@
     </row>
     <row r="188" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="6">
-        <v>20331</v>
+        <v>20324</v>
       </c>
       <c r="B188" t="s">
-        <v>51</v>
+        <v>210</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>4</v>
@@ -4213,38 +4220,38 @@
     </row>
     <row r="189" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="6">
-        <v>20333</v>
+        <v>20331</v>
       </c>
       <c r="B189" t="s">
-        <v>136</v>
+        <v>51</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D189" s="13" t="s">
-        <v>5</v>
+      <c r="D189" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="190" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A190" s="6">
-        <v>20337</v>
+        <v>20333</v>
       </c>
       <c r="B190" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D190" s="1" t="s">
-        <v>8</v>
+      <c r="D190" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="191" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="6">
-        <v>20343</v>
+        <v>20337</v>
       </c>
       <c r="B191" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>4</v>
@@ -4255,10 +4262,10 @@
     </row>
     <row r="192" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="6">
-        <v>20344</v>
+        <v>20343</v>
       </c>
       <c r="B192" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>4</v>
@@ -4269,66 +4276,66 @@
     </row>
     <row r="193" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="6">
-        <v>20351</v>
+        <v>20344</v>
       </c>
       <c r="B193" t="s">
-        <v>26</v>
+        <v>127</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D193" s="13" t="s">
-        <v>5</v>
+      <c r="D193" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="194" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="6">
-        <v>20357</v>
+        <v>20351</v>
       </c>
       <c r="B194" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D194" s="1" t="s">
-        <v>8</v>
+      <c r="D194" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="195" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A195" s="6">
-        <v>20361</v>
+        <v>20357</v>
       </c>
       <c r="B195" t="s">
-        <v>164</v>
+        <v>56</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D195" s="13" t="s">
-        <v>5</v>
+      <c r="D195" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="196" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="6">
-        <v>20362</v>
+        <v>20361</v>
       </c>
       <c r="B196" t="s">
-        <v>45</v>
+        <v>164</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D196" s="10" t="s">
-        <v>8</v>
+      <c r="D196" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="197" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="6">
-        <v>20363</v>
+        <v>20362</v>
       </c>
       <c r="B197" t="s">
-        <v>213</v>
+        <v>45</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>4</v>
@@ -4339,38 +4346,38 @@
     </row>
     <row r="198" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A198" s="6">
-        <v>20364</v>
+        <v>20363</v>
       </c>
       <c r="B198" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D198" s="13" t="s">
-        <v>5</v>
+      <c r="D198" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="199" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="6">
-        <v>20366</v>
+        <v>20364</v>
       </c>
       <c r="B199" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D199" s="1" t="s">
-        <v>8</v>
+      <c r="D199" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="200" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A200" s="6">
-        <v>20367</v>
+        <v>20366</v>
       </c>
       <c r="B200" t="s">
-        <v>47</v>
+        <v>220</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>4</v>
@@ -4381,10 +4388,10 @@
     </row>
     <row r="201" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="6">
-        <v>20369</v>
+        <v>20367</v>
       </c>
       <c r="B201" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>4</v>
@@ -4395,10 +4402,10 @@
     </row>
     <row r="202" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="6">
-        <v>20371</v>
+        <v>20369</v>
       </c>
       <c r="B202" t="s">
-        <v>223</v>
+        <v>63</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>4</v>
@@ -4409,52 +4416,52 @@
     </row>
     <row r="203" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="6">
-        <v>20372</v>
+        <v>20371</v>
       </c>
       <c r="B203" t="s">
-        <v>70</v>
+        <v>223</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D203" s="10" t="s">
+      <c r="D203" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="204" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="6">
-        <v>20374</v>
+        <v>20372</v>
       </c>
       <c r="B204" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D204" s="1" t="s">
+      <c r="D204" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="205" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A205" s="6">
-        <v>20377</v>
+        <v>20374</v>
       </c>
       <c r="B205" t="s">
-        <v>225</v>
+        <v>61</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D205" s="10" t="s">
+      <c r="D205" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="206" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A206" s="6">
-        <v>20379</v>
+        <v>20377</v>
       </c>
       <c r="B206" t="s">
-        <v>49</v>
+        <v>225</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>4</v>
@@ -4465,66 +4472,66 @@
     </row>
     <row r="207" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A207" s="6">
-        <v>20380</v>
+        <v>20379</v>
       </c>
       <c r="B207" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D207" s="13" t="s">
-        <v>5</v>
+      <c r="D207" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="208" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A208" s="6">
-        <v>20381</v>
+        <v>20380</v>
       </c>
       <c r="B208" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D208" s="1" t="s">
-        <v>8</v>
+      <c r="D208" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="209" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A209" s="6">
-        <v>20384</v>
+        <v>20381</v>
       </c>
       <c r="B209" t="s">
-        <v>181</v>
+        <v>60</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D209" s="10" t="s">
+      <c r="D209" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="210" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A210" s="6">
-        <v>20385</v>
+        <v>20384</v>
       </c>
       <c r="B210" t="s">
-        <v>36</v>
+        <v>181</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D210" s="1" t="s">
+      <c r="D210" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="211" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="6">
-        <v>20386</v>
+        <v>20385</v>
       </c>
       <c r="B211" t="s">
-        <v>119</v>
+        <v>36</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>4</v>
@@ -4535,66 +4542,66 @@
     </row>
     <row r="212" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A212" s="6">
-        <v>20388</v>
+        <v>20386</v>
       </c>
       <c r="B212" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D212" s="10" t="s">
+      <c r="D212" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="213" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A213" s="6">
-        <v>20391</v>
+        <v>20388</v>
       </c>
       <c r="B213" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D213" s="1" t="s">
+      <c r="D213" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="214" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A214" s="6">
-        <v>20394</v>
+        <v>20391</v>
       </c>
       <c r="B214" t="s">
-        <v>173</v>
+        <v>106</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D214" s="10" t="s">
+      <c r="D214" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="215" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A215" s="6">
-        <v>20395</v>
+        <v>20394</v>
       </c>
       <c r="B215" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D215" s="1" t="s">
+      <c r="D215" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="216" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A216" s="6">
-        <v>20396</v>
+        <v>20395</v>
       </c>
       <c r="B216" t="s">
-        <v>330</v>
+        <v>161</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>4</v>
@@ -4605,52 +4612,52 @@
     </row>
     <row r="217" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A217" s="6">
-        <v>20397</v>
-      </c>
-      <c r="B217" s="8" t="s">
-        <v>344</v>
+        <v>20396</v>
+      </c>
+      <c r="B217" t="s">
+        <v>330</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D217" s="11" t="s">
-        <v>5</v>
+      <c r="D217" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="218" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A218" s="6">
-        <v>30101</v>
-      </c>
-      <c r="B218" t="s">
-        <v>167</v>
+        <v>20397</v>
+      </c>
+      <c r="B218" s="8" t="s">
+        <v>344</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D218" s="1" t="s">
-        <v>8</v>
+      <c r="D218" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="219" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A219" s="6">
-        <v>40124</v>
+        <v>30101</v>
       </c>
       <c r="B219" t="s">
-        <v>24</v>
+        <v>167</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D219" s="13" t="s">
-        <v>5</v>
+      <c r="D219" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="220" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A220" s="6">
-        <v>40125</v>
+        <v>40124</v>
       </c>
       <c r="B220" t="s">
-        <v>143</v>
+        <v>24</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>4</v>
@@ -4661,24 +4668,24 @@
     </row>
     <row r="221" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A221" s="6">
-        <v>40127</v>
+        <v>40125</v>
       </c>
       <c r="B221" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D221" s="1" t="s">
-        <v>8</v>
+      <c r="D221" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="222" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A222" s="6">
-        <v>40129</v>
+        <v>40127</v>
       </c>
       <c r="B222" t="s">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>4</v>
@@ -4689,24 +4696,24 @@
     </row>
     <row r="223" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223" s="6">
-        <v>40137</v>
+        <v>40129</v>
       </c>
       <c r="B223" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D223" s="10" t="s">
+      <c r="D223" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="224" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="6">
-        <v>40139</v>
+        <v>40137</v>
       </c>
       <c r="B224" t="s">
-        <v>327</v>
+        <v>121</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>4</v>
@@ -4717,66 +4724,66 @@
     </row>
     <row r="225" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A225" s="6">
-        <v>40140</v>
+        <v>40139</v>
       </c>
       <c r="B225" t="s">
-        <v>170</v>
+        <v>327</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D225" s="1" t="s">
+      <c r="D225" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="226" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A226" s="6">
-        <v>40141</v>
+        <v>40140</v>
       </c>
       <c r="B226" t="s">
-        <v>111</v>
+        <v>170</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D226" s="13" t="s">
-        <v>5</v>
+      <c r="D226" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="227" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A227" s="6">
-        <v>40143</v>
+        <v>40141</v>
       </c>
       <c r="B227" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D227" s="10" t="s">
-        <v>8</v>
+      <c r="D227" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="228" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A228" s="6">
-        <v>40144</v>
+        <v>40143</v>
       </c>
       <c r="B228" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D228" s="13" t="s">
-        <v>5</v>
+      <c r="D228" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="229" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A229" s="6">
-        <v>40145</v>
+        <v>40144</v>
       </c>
       <c r="B229" t="s">
-        <v>165</v>
+        <v>107</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>4</v>
@@ -4787,192 +4794,192 @@
     </row>
     <row r="230" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A230" s="6">
-        <v>40150</v>
+        <v>40145</v>
       </c>
       <c r="B230" t="s">
-        <v>221</v>
+        <v>165</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D230" s="10" t="s">
-        <v>8</v>
+      <c r="D230" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="231" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A231" s="6">
-        <v>40151</v>
+        <v>40150</v>
       </c>
       <c r="B231" t="s">
-        <v>54</v>
+        <v>221</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D231" s="1" t="s">
+      <c r="D231" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="232" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A232" s="6">
-        <v>50102</v>
+        <v>40151</v>
       </c>
       <c r="B232" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D232" s="13" t="s">
-        <v>5</v>
+      <c r="D232" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="233" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A233" s="6">
-        <v>50222</v>
+        <v>50102</v>
       </c>
       <c r="B233" t="s">
-        <v>215</v>
+        <v>67</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D233" s="1" t="s">
-        <v>8</v>
+      <c r="D233" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="234" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A234" s="6">
-        <v>50223</v>
+        <v>50222</v>
       </c>
       <c r="B234" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D234" s="10" t="s">
+      <c r="D234" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="235" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A235" s="6">
-        <v>50224</v>
+        <v>50223</v>
       </c>
       <c r="B235" t="s">
-        <v>42</v>
+        <v>194</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D235" s="3" t="s">
-        <v>5</v>
+      <c r="D235" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="236" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A236" s="6">
-        <v>50444</v>
+        <v>50224</v>
       </c>
       <c r="B236" t="s">
-        <v>116</v>
+        <v>42</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D236" s="1" t="s">
-        <v>8</v>
+      <c r="D236" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="237" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A237" s="6">
-        <v>50445</v>
+        <v>50444</v>
       </c>
       <c r="B237" t="s">
-        <v>354</v>
+        <v>116</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D237" s="11" t="s">
-        <v>5</v>
+      <c r="D237" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="238" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A238" s="6">
-        <v>50607</v>
+        <v>50445</v>
       </c>
       <c r="B238" t="s">
-        <v>76</v>
+        <v>354</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D238" s="13" t="s">
+      <c r="D238" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="239" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A239" s="6">
-        <v>50608</v>
+        <v>50607</v>
       </c>
       <c r="B239" t="s">
-        <v>177</v>
+        <v>76</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D239" s="1" t="s">
-        <v>8</v>
+      <c r="D239" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="240" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A240" s="6">
-        <v>50611</v>
-      </c>
-      <c r="B240" s="8" t="s">
-        <v>347</v>
+        <v>50608</v>
+      </c>
+      <c r="B240" t="s">
+        <v>177</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D240" s="14" t="s">
+      <c r="D240" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="241" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="6">
-        <v>50622</v>
-      </c>
-      <c r="B241" t="s">
-        <v>95</v>
+        <v>50611</v>
+      </c>
+      <c r="B241" s="8" t="s">
+        <v>347</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D241" s="16" t="s">
+      <c r="D241" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="242" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A242" s="6">
-        <v>50623</v>
+        <v>50622</v>
       </c>
       <c r="B242" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D242" s="10" t="s">
+      <c r="D242" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="243" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A243" s="6">
-        <v>50625</v>
+        <v>50623</v>
       </c>
       <c r="B243" t="s">
-        <v>204</v>
+        <v>110</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>4</v>
@@ -4983,94 +4990,94 @@
     </row>
     <row r="244" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A244" s="6">
-        <v>50629</v>
+        <v>50625</v>
       </c>
       <c r="B244" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D244" s="1" t="s">
+      <c r="D244" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="245" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A245" s="6">
-        <v>50630</v>
+        <v>50629</v>
       </c>
       <c r="B245" t="s">
-        <v>360</v>
+        <v>188</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D245" s="14" t="s">
+      <c r="D245" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="246" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A246" s="6">
-        <v>50803</v>
+        <v>50630</v>
       </c>
       <c r="B246" t="s">
-        <v>82</v>
+        <v>360</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D246" s="1" t="s">
+      <c r="D246" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="247" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A247" s="6">
-        <v>50805</v>
+        <v>50803</v>
       </c>
       <c r="B247" t="s">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D247" s="10" t="s">
+      <c r="D247" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="248" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A248" s="6">
-        <v>50806</v>
+        <v>50805</v>
       </c>
       <c r="B248" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D248" s="1" t="s">
+      <c r="D248" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="249" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A249" s="6">
-        <v>50808</v>
+        <v>50806</v>
       </c>
       <c r="B249" t="s">
-        <v>16</v>
+        <v>156</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D249" s="13" t="s">
-        <v>5</v>
+      <c r="D249" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="250" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A250" s="6">
-        <v>50809</v>
+        <v>50808</v>
       </c>
       <c r="B250" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>4</v>
@@ -5081,24 +5088,24 @@
     </row>
     <row r="251" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A251" s="6">
-        <v>50810</v>
+        <v>50809</v>
       </c>
       <c r="B251" t="s">
-        <v>175</v>
+        <v>98</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D251" s="1" t="s">
-        <v>8</v>
+      <c r="D251" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="252" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A252" s="6">
-        <v>50812</v>
+        <v>50810</v>
       </c>
       <c r="B252" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>4</v>
@@ -5109,80 +5116,80 @@
     </row>
     <row r="253" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A253" s="6">
-        <v>50813</v>
+        <v>50812</v>
       </c>
       <c r="B253" t="s">
-        <v>71</v>
+        <v>184</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D253" s="17" t="s">
-        <v>9</v>
+      <c r="D253" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="254" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="6">
-        <v>50815</v>
+        <v>50813</v>
       </c>
       <c r="B254" t="s">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D254" s="10" t="s">
-        <v>8</v>
+      <c r="D254" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="255" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A255" s="6">
-        <v>50816</v>
+        <v>50815</v>
       </c>
       <c r="B255" t="s">
-        <v>205</v>
+        <v>114</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D255" s="1" t="s">
+      <c r="D255" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="256" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A256" s="6">
-        <v>50818</v>
+        <v>50816</v>
       </c>
       <c r="B256" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D256" s="13" t="s">
-        <v>5</v>
+      <c r="D256" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="257" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A257" s="6">
-        <v>50819</v>
+        <v>50818</v>
       </c>
       <c r="B257" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D257" s="10" t="s">
-        <v>8</v>
+      <c r="D257" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="258" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A258" s="6">
-        <v>50820</v>
+        <v>50819</v>
       </c>
       <c r="B258" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>4</v>
@@ -5193,66 +5200,66 @@
     </row>
     <row r="259" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A259" s="6">
-        <v>50821</v>
+        <v>50820</v>
       </c>
       <c r="B259" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D259" s="1" t="s">
+      <c r="D259" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="260" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A260" s="6">
-        <v>50823</v>
+        <v>50821</v>
       </c>
       <c r="B260" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D260" s="17" t="s">
-        <v>9</v>
+      <c r="D260" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="261" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A261" s="6">
-        <v>50824</v>
+        <v>50823</v>
       </c>
       <c r="B261" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D261" s="13" t="s">
-        <v>5</v>
+      <c r="D261" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="262" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A262" s="6">
-        <v>50825</v>
+        <v>50824</v>
       </c>
       <c r="B262" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D262" s="10" t="s">
-        <v>8</v>
+      <c r="D262" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="263" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A263" s="6">
-        <v>50826</v>
+        <v>50825</v>
       </c>
       <c r="B263" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>4</v>
@@ -5263,24 +5270,24 @@
     </row>
     <row r="264" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A264" s="6">
-        <v>50827</v>
+        <v>50826</v>
       </c>
       <c r="B264" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D264" s="1" t="s">
+      <c r="D264" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="265" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A265" s="6">
-        <v>50829</v>
+        <v>50827</v>
       </c>
       <c r="B265" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>4</v>
@@ -5291,38 +5298,38 @@
     </row>
     <row r="266" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A266" s="6">
-        <v>50830</v>
+        <v>50829</v>
       </c>
       <c r="B266" t="s">
-        <v>366</v>
+        <v>236</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D266" s="11" t="s">
+      <c r="D266" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="267" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A267" s="6">
-        <v>50831</v>
+        <v>50830</v>
       </c>
       <c r="B267" t="s">
-        <v>351</v>
+        <v>366</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D267" s="11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="268" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A268" s="6">
-        <v>50832</v>
-      </c>
-      <c r="B268" s="8" t="s">
-        <v>349</v>
+        <v>50831</v>
+      </c>
+      <c r="B268" t="s">
+        <v>351</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>4</v>
@@ -5333,80 +5340,80 @@
     </row>
     <row r="269" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A269" s="6">
-        <v>50833</v>
+        <v>50832</v>
       </c>
       <c r="B269" s="8" t="s">
-        <v>397</v>
+        <v>349</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D269" s="11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="270" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A270" s="6">
-        <v>50230</v>
+        <v>50833</v>
       </c>
       <c r="B270" s="8" t="s">
-        <v>379</v>
+        <v>397</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D270" s="11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="271" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A271" s="6">
-        <v>60103</v>
-      </c>
-      <c r="B271" t="s">
-        <v>237</v>
+        <v>50230</v>
+      </c>
+      <c r="B271" s="8" t="s">
+        <v>379</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D271" s="13" t="s">
+      <c r="D271" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="272" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A272" s="6">
-        <v>60109</v>
+        <v>60103</v>
       </c>
       <c r="B272" t="s">
-        <v>328</v>
+        <v>237</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D272" s="11" t="s">
-        <v>9</v>
+      <c r="D272" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="273" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A273" s="6">
-        <v>60124</v>
+        <v>60109</v>
       </c>
       <c r="B273" t="s">
-        <v>238</v>
+        <v>328</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D273" s="13" t="s">
-        <v>5</v>
+      <c r="D273" s="11" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="274" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A274" s="6">
-        <v>60125</v>
+        <v>60124</v>
       </c>
       <c r="B274" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>4</v>
@@ -5417,80 +5424,80 @@
     </row>
     <row r="275" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A275" s="6">
-        <v>60126</v>
+        <v>60125</v>
       </c>
       <c r="B275" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D275" s="10" t="s">
-        <v>8</v>
+      <c r="D275" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="276" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A276" s="6">
-        <v>60128</v>
+        <v>60126</v>
       </c>
       <c r="B276" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D276" s="3" t="s">
-        <v>5</v>
+      <c r="D276" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="277" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A277" s="6">
-        <v>60130</v>
+        <v>60128</v>
       </c>
       <c r="B277" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D277" s="1" t="s">
-        <v>8</v>
+      <c r="D277" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="278" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A278" s="6">
-        <v>60133</v>
+        <v>60130</v>
       </c>
       <c r="B278" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D278" s="13" t="s">
-        <v>5</v>
+      <c r="D278" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="279" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A279" s="6">
-        <v>60134</v>
+        <v>60133</v>
       </c>
       <c r="B279" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D279" s="1" t="s">
-        <v>8</v>
+      <c r="D279" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="280" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A280" s="6">
-        <v>60137</v>
+        <v>60134</v>
       </c>
       <c r="B280" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>4</v>
@@ -5501,10 +5508,10 @@
     </row>
     <row r="281" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A281" s="6">
-        <v>60139</v>
+        <v>60137</v>
       </c>
       <c r="B281" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>4</v>
@@ -5515,10 +5522,10 @@
     </row>
     <row r="282" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A282" s="6">
-        <v>60142</v>
+        <v>60139</v>
       </c>
       <c r="B282" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>4</v>
@@ -5529,10 +5536,10 @@
     </row>
     <row r="283" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A283" s="6">
-        <v>60148</v>
+        <v>60142</v>
       </c>
       <c r="B283" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>4</v>
@@ -5543,10 +5550,10 @@
     </row>
     <row r="284" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A284" s="6">
-        <v>60149</v>
+        <v>60148</v>
       </c>
       <c r="B284" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>4</v>
@@ -5557,66 +5564,66 @@
     </row>
     <row r="285" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A285" s="6">
-        <v>60150</v>
+        <v>60149</v>
       </c>
       <c r="B285" t="s">
-        <v>332</v>
+        <v>249</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D285" s="13" t="s">
-        <v>5</v>
+      <c r="D285" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="286" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A286" s="6">
-        <v>60158</v>
+        <v>60150</v>
       </c>
       <c r="B286" t="s">
-        <v>250</v>
+        <v>332</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D286" s="10" t="s">
-        <v>8</v>
+      <c r="D286" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="287" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A287" s="6">
-        <v>60159</v>
+        <v>60158</v>
       </c>
       <c r="B287" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D287" s="1" t="s">
+      <c r="D287" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="288" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A288" s="6">
-        <v>60162</v>
+        <v>60159</v>
       </c>
       <c r="B288" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D288" s="13" t="s">
-        <v>5</v>
+      <c r="D288" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="289" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A289" s="6">
-        <v>60163</v>
+        <v>60162</v>
       </c>
       <c r="B289" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>4</v>
@@ -5627,24 +5634,24 @@
     </row>
     <row r="290" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A290" s="6">
-        <v>60165</v>
+        <v>60163</v>
       </c>
       <c r="B290" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D290" s="1" t="s">
-        <v>8</v>
+      <c r="D290" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="291" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A291" s="6">
-        <v>60169</v>
+        <v>60165</v>
       </c>
       <c r="B291" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>4</v>
@@ -5655,52 +5662,52 @@
     </row>
     <row r="292" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A292" s="6">
-        <v>60170</v>
-      </c>
-      <c r="B292" s="8" t="s">
-        <v>337</v>
+        <v>60169</v>
+      </c>
+      <c r="B292" t="s">
+        <v>255</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D292" s="11" t="s">
+      <c r="D292" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="293" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A293" s="6">
-        <v>60172</v>
-      </c>
-      <c r="B293" t="s">
-        <v>256</v>
+        <v>60170</v>
+      </c>
+      <c r="B293" s="8" t="s">
+        <v>337</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D293" s="1" t="s">
+      <c r="D293" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="294" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A294" s="6">
-        <v>60174</v>
+        <v>60172</v>
       </c>
       <c r="B294" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D294" s="13" t="s">
-        <v>5</v>
+      <c r="D294" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="295" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A295" s="6">
-        <v>60176</v>
+        <v>60174</v>
       </c>
       <c r="B295" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>4</v>
@@ -5711,52 +5718,52 @@
     </row>
     <row r="296" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A296" s="6">
-        <v>60178</v>
+        <v>60176</v>
       </c>
       <c r="B296" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D296" s="1" t="s">
-        <v>8</v>
+      <c r="D296" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="297" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A297" s="6">
-        <v>60180</v>
+        <v>60178</v>
       </c>
       <c r="B297" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D297" s="10" t="s">
+      <c r="D297" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="298" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A298" s="6">
-        <v>60184</v>
+        <v>60180</v>
       </c>
       <c r="B298" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D298" s="1" t="s">
+      <c r="D298" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="299" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A299" s="6">
-        <v>60190</v>
+        <v>60184</v>
       </c>
       <c r="B299" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>4</v>
@@ -5767,24 +5774,24 @@
     </row>
     <row r="300" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A300" s="6">
-        <v>60191</v>
+        <v>60190</v>
       </c>
       <c r="B300" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D300" s="10" t="s">
+      <c r="D300" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="301" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A301" s="6">
-        <v>60192</v>
+        <v>60191</v>
       </c>
       <c r="B301" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>4</v>
@@ -5795,10 +5802,10 @@
     </row>
     <row r="302" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A302" s="6">
-        <v>60195</v>
+        <v>60192</v>
       </c>
       <c r="B302" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>4</v>
@@ -5809,10 +5816,10 @@
     </row>
     <row r="303" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A303" s="6">
-        <v>60196</v>
+        <v>60195</v>
       </c>
       <c r="B303" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>4</v>
@@ -5823,10 +5830,10 @@
     </row>
     <row r="304" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A304" s="6">
-        <v>60198</v>
+        <v>60196</v>
       </c>
       <c r="B304" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>4</v>
@@ -5837,52 +5844,52 @@
     </row>
     <row r="305" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A305" s="6">
-        <v>60201</v>
+        <v>60198</v>
       </c>
       <c r="B305" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D305" t="s">
-        <v>9</v>
+      <c r="D305" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="306" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A306" s="6">
-        <v>60202</v>
+        <v>60201</v>
       </c>
       <c r="B306" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D306" s="13" t="s">
-        <v>5</v>
+      <c r="D306" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="307" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A307" s="6">
-        <v>60204</v>
+        <v>60202</v>
       </c>
       <c r="B307" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D307" s="1" t="s">
-        <v>8</v>
+      <c r="D307" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="308" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A308" s="6">
-        <v>60205</v>
+        <v>60204</v>
       </c>
       <c r="B308" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>4</v>
@@ -5893,10 +5900,10 @@
     </row>
     <row r="309" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A309" s="6">
-        <v>60206</v>
+        <v>60205</v>
       </c>
       <c r="B309" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>4</v>
@@ -5907,220 +5914,220 @@
     </row>
     <row r="310" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A310" s="6">
-        <v>60209</v>
+        <v>60206</v>
       </c>
       <c r="B310" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D310" s="10" t="s">
+      <c r="D310" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="311" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A311" s="6">
-        <v>60211</v>
+        <v>60209</v>
       </c>
       <c r="B311" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D311" s="1" t="s">
+      <c r="D311" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="312" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A312" s="6">
-        <v>60215</v>
+        <v>60211</v>
       </c>
       <c r="B312" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D312" s="10" t="s">
+      <c r="D312" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="313" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A313" s="6">
-        <v>60216</v>
+        <v>60215</v>
       </c>
       <c r="B313" t="s">
-        <v>381</v>
+        <v>275</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D313" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="314" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A314" s="6">
-        <v>60217</v>
+        <v>60216</v>
       </c>
       <c r="B314" t="s">
-        <v>276</v>
+        <v>381</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D314" s="10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="315" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A315" s="6">
-        <v>60219</v>
+        <v>60217</v>
       </c>
       <c r="B315" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D315" s="1" t="s">
+      <c r="D315" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="316" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A316" s="6">
-        <v>60222</v>
+        <v>60219</v>
       </c>
       <c r="B316" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D316" s="10" t="s">
+      <c r="D316" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="317" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A317" s="6">
-        <v>60225</v>
+        <v>60222</v>
       </c>
       <c r="B317" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D317" s="17" t="s">
-        <v>9</v>
+      <c r="D317" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="318" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A318" s="6">
-        <v>60230</v>
+        <v>60225</v>
       </c>
       <c r="B318" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D318" s="10" t="s">
-        <v>8</v>
+      <c r="D318" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="319" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A319" s="6">
-        <v>60241</v>
-      </c>
-      <c r="B319" s="8" t="s">
-        <v>338</v>
+        <v>60230</v>
+      </c>
+      <c r="B319" t="s">
+        <v>280</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D319" s="7" t="s">
-        <v>9</v>
+      <c r="D319" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="320" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A320" s="6">
-        <v>60242</v>
+        <v>60241</v>
       </c>
       <c r="B320" s="8" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D320" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="321" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A321" s="6">
-        <v>60243</v>
+        <v>60242</v>
       </c>
       <c r="B321" s="8" t="s">
-        <v>395</v>
+        <v>341</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D321" s="7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="322" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A322" s="6">
-        <v>60245</v>
+        <v>60243</v>
       </c>
       <c r="B322" s="8" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D322" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="323" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A323" s="6">
-        <v>60250</v>
+        <v>60245</v>
       </c>
       <c r="B323" s="8" t="s">
-        <v>339</v>
+        <v>387</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D323" s="11" t="s">
-        <v>8</v>
+      <c r="D323" s="7" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="324" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A324" s="6">
-        <v>60253</v>
-      </c>
-      <c r="B324" t="s">
-        <v>281</v>
+        <v>60250</v>
+      </c>
+      <c r="B324" s="8" t="s">
+        <v>339</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D324" s="1" t="s">
+      <c r="D324" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="325" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A325" s="6">
-        <v>60254</v>
+        <v>60253</v>
       </c>
       <c r="B325" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>4</v>
@@ -6131,10 +6138,10 @@
     </row>
     <row r="326" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A326" s="6">
-        <v>60257</v>
+        <v>60254</v>
       </c>
       <c r="B326" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>4</v>
@@ -6145,10 +6152,10 @@
     </row>
     <row r="327" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A327" s="6">
-        <v>60258</v>
+        <v>60257</v>
       </c>
       <c r="B327" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>4</v>
@@ -6159,66 +6166,66 @@
     </row>
     <row r="328" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A328" s="6">
-        <v>60266</v>
-      </c>
-      <c r="B328" s="8" t="s">
-        <v>343</v>
+        <v>60258</v>
+      </c>
+      <c r="B328" t="s">
+        <v>284</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D328" s="11" t="s">
+      <c r="D328" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="329" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A329" s="6">
-        <v>60269</v>
-      </c>
-      <c r="B329" t="s">
-        <v>285</v>
+        <v>60266</v>
+      </c>
+      <c r="B329" s="8" t="s">
+        <v>343</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D329" s="10" t="s">
+      <c r="D329" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="330" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A330" s="6">
-        <v>60270</v>
+        <v>60269</v>
       </c>
       <c r="B330" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D330" s="1" t="s">
-        <v>9</v>
+      <c r="D330" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="331" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A331" s="6">
-        <v>60272</v>
+        <v>60270</v>
       </c>
       <c r="B331" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="332" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A332" s="6">
-        <v>60274</v>
+        <v>60272</v>
       </c>
       <c r="B332" t="s">
-        <v>380</v>
+        <v>287</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>4</v>
@@ -6229,10 +6236,10 @@
     </row>
     <row r="333" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A333" s="6">
-        <v>60275</v>
+        <v>60274</v>
       </c>
       <c r="B333" t="s">
-        <v>288</v>
+        <v>380</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>4</v>
@@ -6243,10 +6250,10 @@
     </row>
     <row r="334" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A334" s="6">
-        <v>60276</v>
+        <v>60275</v>
       </c>
       <c r="B334" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>4</v>
@@ -6257,108 +6264,108 @@
     </row>
     <row r="335" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A335" s="6">
-        <v>60278</v>
+        <v>60276</v>
       </c>
       <c r="B335" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D335" s="13" t="s">
+      <c r="D335" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="336" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A336" s="6">
-        <v>60279</v>
+        <v>60278</v>
       </c>
       <c r="B336" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D336" s="1" t="s">
+      <c r="D336" s="13" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="337" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A337" s="6">
-        <v>60280</v>
+        <v>60279</v>
       </c>
       <c r="B337" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="338" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A338" s="6">
-        <v>60281</v>
-      </c>
-      <c r="B338" s="8" t="s">
-        <v>336</v>
+        <v>60280</v>
+      </c>
+      <c r="B338" t="s">
+        <v>292</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D338" s="11" t="s">
-        <v>9</v>
+      <c r="D338" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="339" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A339" s="6">
-        <v>60282</v>
+        <v>60281</v>
       </c>
       <c r="B339" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D339" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="340" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A340" s="6">
-        <v>60283</v>
-      </c>
-      <c r="B340" t="s">
-        <v>378</v>
+        <v>60282</v>
+      </c>
+      <c r="B340" s="8" t="s">
+        <v>340</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D340" s="1" t="s">
-        <v>8</v>
+      <c r="D340" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="341" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A341" s="6">
-        <v>60284</v>
-      </c>
-      <c r="B341" s="8" t="s">
-        <v>335</v>
+        <v>60283</v>
+      </c>
+      <c r="B341" t="s">
+        <v>378</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D341" s="9" t="s">
-        <v>5</v>
+      <c r="D341" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="342" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A342" s="6">
-        <v>60285</v>
+        <v>60284</v>
       </c>
       <c r="B342" s="8" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>4</v>
@@ -6369,10 +6376,10 @@
     </row>
     <row r="343" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A343" s="6">
-        <v>60286</v>
+        <v>60285</v>
       </c>
       <c r="B343" s="8" t="s">
-        <v>334</v>
+        <v>350</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>4</v>
@@ -6383,52 +6390,52 @@
     </row>
     <row r="344" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A344" s="6">
-        <v>60287</v>
-      </c>
-      <c r="B344" t="s">
-        <v>377</v>
+        <v>60286</v>
+      </c>
+      <c r="B344" s="8" t="s">
+        <v>334</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D344" s="12" t="s">
+      <c r="D344" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="345" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A345" s="6">
-        <v>60289</v>
+        <v>60287</v>
       </c>
       <c r="B345" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D345" s="12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="346" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A346" s="6">
-        <v>60290</v>
+        <v>60289</v>
       </c>
       <c r="B346" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D346" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="347" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A347" s="6">
-        <v>60291</v>
+        <v>60290</v>
       </c>
       <c r="B347" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>4</v>
@@ -6439,94 +6446,94 @@
     </row>
     <row r="348" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A348" s="6">
-        <v>60296</v>
+        <v>60291</v>
       </c>
       <c r="B348" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D348" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="349" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A349" s="6">
-        <v>60297</v>
-      </c>
-      <c r="B349" t="s">
-        <v>392</v>
+        <v>60292</v>
+      </c>
+      <c r="B349" s="18" t="s">
+        <v>400</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D349" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="350" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A350" s="6">
-        <v>60299</v>
+        <v>60296</v>
       </c>
       <c r="B350" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D350" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="351" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A351" s="6">
-        <v>61004</v>
+        <v>60297</v>
       </c>
       <c r="B351" t="s">
-        <v>293</v>
+        <v>392</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D351" s="15" t="s">
+      <c r="D351" s="12" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="352" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A352" s="6">
-        <v>61009</v>
+        <v>60299</v>
       </c>
       <c r="B352" t="s">
-        <v>294</v>
+        <v>388</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D352" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="353" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A353" s="6">
-        <v>61012</v>
+        <v>61004</v>
       </c>
       <c r="B353" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D353" s="12" t="s">
-        <v>8</v>
+      <c r="D353" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="354" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A354" s="6">
-        <v>61018</v>
+        <v>61009</v>
       </c>
       <c r="B354" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>4</v>
@@ -6537,10 +6544,10 @@
     </row>
     <row r="355" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A355" s="6">
-        <v>61102</v>
+        <v>61012</v>
       </c>
       <c r="B355" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>4</v>
@@ -6551,24 +6558,24 @@
     </row>
     <row r="356" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A356" s="6">
-        <v>61205</v>
+        <v>61018</v>
       </c>
       <c r="B356" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D356" s="15" t="s">
-        <v>5</v>
+      <c r="D356" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="357" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A357" s="6">
-        <v>70100</v>
+        <v>61102</v>
       </c>
       <c r="B357" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>4</v>
@@ -6579,10 +6586,10 @@
     </row>
     <row r="358" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A358" s="6">
-        <v>70101</v>
+        <v>61205</v>
       </c>
       <c r="B358" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>4</v>
@@ -6593,38 +6600,38 @@
     </row>
     <row r="359" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A359" s="6">
-        <v>70102</v>
+        <v>70100</v>
       </c>
       <c r="B359" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D359" s="15" t="s">
-        <v>5</v>
+      <c r="D359" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="360" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A360" s="6">
-        <v>70103</v>
+        <v>70101</v>
       </c>
       <c r="B360" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D360" s="12" t="s">
-        <v>8</v>
+      <c r="D360" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="361" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A361" s="6">
-        <v>70106</v>
+        <v>70102</v>
       </c>
       <c r="B361" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>4</v>
@@ -6635,10 +6642,10 @@
     </row>
     <row r="362" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A362" s="6">
-        <v>70109</v>
+        <v>70103</v>
       </c>
       <c r="B362" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>4</v>
@@ -6649,10 +6656,10 @@
     </row>
     <row r="363" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A363" s="6">
-        <v>70113</v>
+        <v>70106</v>
       </c>
       <c r="B363" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>4</v>
@@ -6663,66 +6670,66 @@
     </row>
     <row r="364" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A364" s="6">
-        <v>70114</v>
+        <v>70109</v>
       </c>
       <c r="B364" t="s">
-        <v>325</v>
+        <v>304</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D364" s="9" t="s">
-        <v>9</v>
+      <c r="D364" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="365" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A365" s="6">
-        <v>70115</v>
+        <v>70113</v>
       </c>
       <c r="B365" t="s">
-        <v>331</v>
+        <v>305</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D365" s="9" t="s">
-        <v>9</v>
+      <c r="D365" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="366" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A366" s="6">
-        <v>70638</v>
+        <v>70114</v>
       </c>
       <c r="B366" t="s">
-        <v>306</v>
+        <v>325</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D366" s="12" t="s">
-        <v>8</v>
+      <c r="D366" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="367" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A367" s="6">
-        <v>70639</v>
+        <v>70115</v>
       </c>
       <c r="B367" t="s">
-        <v>307</v>
+        <v>331</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D367" s="12" t="s">
-        <v>8</v>
+      <c r="D367" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="368" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A368" s="6">
-        <v>70640</v>
+        <v>70638</v>
       </c>
       <c r="B368" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>4</v>
@@ -6733,10 +6740,10 @@
     </row>
     <row r="369" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A369" s="6">
-        <v>70642</v>
+        <v>70639</v>
       </c>
       <c r="B369" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>4</v>
@@ -6747,10 +6754,10 @@
     </row>
     <row r="370" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A370" s="6">
-        <v>90504</v>
+        <v>70640</v>
       </c>
       <c r="B370" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>4</v>
@@ -6761,10 +6768,10 @@
     </row>
     <row r="371" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A371" s="6">
-        <v>90509</v>
+        <v>70642</v>
       </c>
       <c r="B371" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>4</v>
@@ -6775,24 +6782,24 @@
     </row>
     <row r="372" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A372" s="6">
-        <v>90602</v>
+        <v>90504</v>
       </c>
       <c r="B372" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D372" s="15" t="s">
-        <v>5</v>
+      <c r="D372" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="373" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A373" s="6">
-        <v>90621</v>
+        <v>90509</v>
       </c>
       <c r="B373" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>4</v>
@@ -6803,66 +6810,66 @@
     </row>
     <row r="374" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A374" s="6">
-        <v>90622</v>
+        <v>90602</v>
       </c>
       <c r="B374" t="s">
-        <v>333</v>
+        <v>312</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D374" s="9" t="s">
+      <c r="D374" s="15" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="375" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A375" s="6">
-        <v>90631</v>
-      </c>
-      <c r="B375" s="8" t="s">
-        <v>342</v>
+        <v>90621</v>
+      </c>
+      <c r="B375" t="s">
+        <v>313</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D375" s="9" t="s">
-        <v>5</v>
+      <c r="D375" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="376" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A376" s="6">
-        <v>90658</v>
+        <v>90622</v>
       </c>
       <c r="B376" t="s">
-        <v>314</v>
+        <v>333</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D376" s="12" t="s">
-        <v>8</v>
+      <c r="D376" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="377" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A377" s="6">
-        <v>90660</v>
-      </c>
-      <c r="B377" t="s">
-        <v>315</v>
+        <v>90631</v>
+      </c>
+      <c r="B377" s="8" t="s">
+        <v>342</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D377" s="12" t="s">
-        <v>8</v>
+      <c r="D377" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="378" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A378" s="6">
-        <v>90668</v>
+        <v>90658</v>
       </c>
       <c r="B378" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>4</v>
@@ -6873,10 +6880,10 @@
     </row>
     <row r="379" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A379" s="6">
-        <v>90671</v>
+        <v>90660</v>
       </c>
       <c r="B379" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>4</v>
@@ -6887,10 +6894,10 @@
     </row>
     <row r="380" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A380" s="6">
-        <v>90679</v>
+        <v>90668</v>
       </c>
       <c r="B380" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>4</v>
@@ -6901,10 +6908,10 @@
     </row>
     <row r="381" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A381" s="6">
-        <v>90683</v>
+        <v>90671</v>
       </c>
       <c r="B381" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>4</v>
@@ -6915,10 +6922,10 @@
     </row>
     <row r="382" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A382" s="6">
-        <v>90705</v>
+        <v>90679</v>
       </c>
       <c r="B382" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>4</v>
@@ -6929,10 +6936,10 @@
     </row>
     <row r="383" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A383" s="6">
-        <v>90706</v>
+        <v>90683</v>
       </c>
       <c r="B383" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>4</v>
@@ -6943,10 +6950,10 @@
     </row>
     <row r="384" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A384" s="6">
-        <v>90708</v>
+        <v>90705</v>
       </c>
       <c r="B384" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>4</v>
@@ -6957,10 +6964,10 @@
     </row>
     <row r="385" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A385" s="6">
-        <v>90709</v>
+        <v>90706</v>
       </c>
       <c r="B385" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>4</v>
@@ -6971,10 +6978,10 @@
     </row>
     <row r="386" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A386" s="6">
-        <v>1218</v>
+        <v>90708</v>
       </c>
       <c r="B386" t="s">
-        <v>382</v>
+        <v>322</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>4</v>
@@ -6985,10 +6992,10 @@
     </row>
     <row r="387" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A387" s="6">
-        <v>1959</v>
-      </c>
-      <c r="B387" s="8" t="s">
-        <v>383</v>
+        <v>90709</v>
+      </c>
+      <c r="B387" t="s">
+        <v>323</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>4</v>
@@ -6999,10 +7006,10 @@
     </row>
     <row r="388" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A388" s="6">
-        <v>5625</v>
-      </c>
-      <c r="B388" s="8" t="s">
-        <v>384</v>
+        <v>1218</v>
+      </c>
+      <c r="B388" t="s">
+        <v>382</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>4</v>
@@ -7013,10 +7020,10 @@
     </row>
     <row r="389" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A389" s="6">
-        <v>1817</v>
+        <v>1959</v>
       </c>
       <c r="B389" s="8" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>4</v>
@@ -7027,10 +7034,10 @@
     </row>
     <row r="390" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A390" s="6">
-        <v>5737</v>
+        <v>5625</v>
       </c>
       <c r="B390" s="8" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>4</v>
@@ -7041,34 +7048,62 @@
     </row>
     <row r="391" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A391" s="6">
-        <v>60295</v>
+        <v>1817</v>
       </c>
       <c r="B391" s="8" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D391" s="9" t="s">
-        <v>9</v>
+      <c r="D391" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="392" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A392" s="6">
+        <v>5737</v>
+      </c>
+      <c r="B392" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="C392" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D392" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A393" s="6">
+        <v>60295</v>
+      </c>
+      <c r="B393" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="C393" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D393" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A394" s="6">
         <v>1045</v>
       </c>
-      <c r="B392" s="8" t="s">
+      <c r="B394" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="C392" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D392" s="9" t="s">
+      <c r="C394" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D394" s="9" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D340"/>
+  <autoFilter ref="A1:D341"/>
   <sortState ref="A2:D374">
     <sortCondition ref="A277"/>
   </sortState>

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1183" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1183" uniqueCount="402">
   <si>
     <t>CUENTA</t>
   </si>
@@ -1225,6 +1225,9 @@
   </si>
   <si>
     <t>FERRETERIA ALFA</t>
+  </si>
+  <si>
+    <t>C</t>
   </si>
 </sst>
 </file>
@@ -5335,7 +5338,7 @@
         <v>4</v>
       </c>
       <c r="D268" s="11" t="s">
-        <v>5</v>
+        <v>401</v>
       </c>
     </row>
     <row r="269" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1183" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1183" uniqueCount="401">
   <si>
     <t>CUENTA</t>
   </si>
@@ -1225,9 +1225,6 @@
   </si>
   <si>
     <t>FERRETERIA ALFA</t>
-  </si>
-  <si>
-    <t>C</t>
   </si>
 </sst>
 </file>
@@ -5338,7 +5335,7 @@
         <v>4</v>
       </c>
       <c r="D268" s="11" t="s">
-        <v>401</v>
+        <v>8</v>
       </c>
     </row>
     <row r="269" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$341</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$342</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1183" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1186" uniqueCount="402">
   <si>
     <t>CUENTA</t>
   </si>
@@ -1225,6 +1225,9 @@
   </si>
   <si>
     <t>FERRETERIA ALFA</t>
+  </si>
+  <si>
+    <t>FERRETERIA VIGO</t>
   </si>
 </sst>
 </file>
@@ -1578,7 +1581,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D394"/>
+  <dimension ref="A1:D395"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -3856,192 +3859,192 @@
     </row>
     <row r="163" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="6">
-        <v>20268</v>
+        <v>20267</v>
       </c>
       <c r="B163" t="s">
-        <v>201</v>
+        <v>401</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D163" s="1" t="s">
-        <v>8</v>
+      <c r="D163" s="10" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="6">
-        <v>20271</v>
+        <v>20268</v>
       </c>
       <c r="B164" t="s">
-        <v>34</v>
+        <v>201</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D164" s="13" t="s">
-        <v>5</v>
+      <c r="D164" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="165" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="6">
-        <v>20272</v>
+        <v>20271</v>
       </c>
       <c r="B165" t="s">
-        <v>178</v>
+        <v>34</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D165" s="1" t="s">
-        <v>8</v>
+      <c r="D165" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="6">
-        <v>20275</v>
+        <v>20272</v>
       </c>
       <c r="B166" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D166" s="13" t="s">
-        <v>5</v>
+      <c r="D166" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="6">
-        <v>20277</v>
+        <v>20275</v>
       </c>
       <c r="B167" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D167" s="1" t="s">
-        <v>8</v>
+      <c r="D167" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="168" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="6">
-        <v>20281</v>
+        <v>20277</v>
       </c>
       <c r="B168" t="s">
-        <v>105</v>
+        <v>154</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D168" s="3" t="s">
-        <v>5</v>
+      <c r="D168" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="6">
-        <v>20282</v>
+        <v>20281</v>
       </c>
       <c r="B169" t="s">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D169" s="1" t="s">
-        <v>9</v>
+      <c r="D169" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A170" s="6">
-        <v>20284</v>
+        <v>20282</v>
       </c>
       <c r="B170" t="s">
-        <v>17</v>
+        <v>141</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D170" s="17" t="s">
+      <c r="D170" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="171" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="6">
-        <v>20285</v>
+        <v>20284</v>
       </c>
       <c r="B171" t="s">
-        <v>146</v>
+        <v>17</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D171" s="1" t="s">
-        <v>8</v>
+      <c r="D171" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="6">
-        <v>20289</v>
+        <v>20285</v>
       </c>
       <c r="B172" t="s">
-        <v>52</v>
+        <v>146</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D172" s="3" t="s">
-        <v>5</v>
+      <c r="D172" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="6">
-        <v>20290</v>
+        <v>20289</v>
       </c>
       <c r="B173" t="s">
-        <v>103</v>
+        <v>52</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D173" s="1" t="s">
-        <v>8</v>
+      <c r="D173" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="174" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="6">
-        <v>20291</v>
+        <v>20290</v>
       </c>
       <c r="B174" t="s">
-        <v>187</v>
+        <v>103</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D174" s="10" t="s">
+      <c r="D174" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="175" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="6">
-        <v>20292</v>
+        <v>20291</v>
       </c>
       <c r="B175" t="s">
-        <v>32</v>
+        <v>187</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D175" s="13" t="s">
-        <v>5</v>
+      <c r="D175" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="6">
-        <v>20293</v>
+        <v>20292</v>
       </c>
       <c r="B176" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>4</v>
@@ -4052,52 +4055,52 @@
     </row>
     <row r="177" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A177" s="6">
-        <v>20294</v>
+        <v>20293</v>
       </c>
       <c r="B177" t="s">
-        <v>202</v>
+        <v>43</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D177" s="10" t="s">
-        <v>8</v>
+      <c r="D177" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="6">
-        <v>20296</v>
+        <v>20294</v>
       </c>
       <c r="B178" t="s">
-        <v>144</v>
+        <v>202</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D178" s="13" t="s">
-        <v>5</v>
+      <c r="D178" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="179" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="6">
-        <v>20298</v>
+        <v>20296</v>
       </c>
       <c r="B179" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D179" s="1" t="s">
-        <v>8</v>
+      <c r="D179" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="6">
-        <v>20299</v>
+        <v>20298</v>
       </c>
       <c r="B180" t="s">
-        <v>58</v>
+        <v>169</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>4</v>
@@ -4108,10 +4111,10 @@
     </row>
     <row r="181" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="6">
-        <v>20301</v>
+        <v>20299</v>
       </c>
       <c r="B181" t="s">
-        <v>134</v>
+        <v>58</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>4</v>
@@ -4122,10 +4125,10 @@
     </row>
     <row r="182" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="6">
-        <v>20303</v>
+        <v>20301</v>
       </c>
       <c r="B182" t="s">
-        <v>37</v>
+        <v>134</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>4</v>
@@ -4136,24 +4139,24 @@
     </row>
     <row r="183" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="6">
-        <v>20309</v>
+        <v>20303</v>
       </c>
       <c r="B183" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D183" s="13" t="s">
-        <v>5</v>
+      <c r="D183" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="184" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="6">
-        <v>20310</v>
+        <v>20309</v>
       </c>
       <c r="B184" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>4</v>
@@ -4164,52 +4167,52 @@
     </row>
     <row r="185" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="6">
-        <v>20318</v>
+        <v>20310</v>
       </c>
       <c r="B185" t="s">
-        <v>209</v>
+        <v>59</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D185" s="1" t="s">
-        <v>8</v>
+      <c r="D185" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="186" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="6">
-        <v>20319</v>
+        <v>20318</v>
       </c>
       <c r="B186" t="s">
-        <v>101</v>
+        <v>209</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D186" s="10" t="s">
+      <c r="D186" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="187" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="6">
-        <v>20320</v>
+        <v>20319</v>
       </c>
       <c r="B187" t="s">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D187" s="1" t="s">
+      <c r="D187" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="188" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="6">
-        <v>20324</v>
+        <v>20320</v>
       </c>
       <c r="B188" t="s">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>4</v>
@@ -4220,10 +4223,10 @@
     </row>
     <row r="189" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="6">
-        <v>20331</v>
+        <v>20324</v>
       </c>
       <c r="B189" t="s">
-        <v>51</v>
+        <v>210</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>4</v>
@@ -4234,38 +4237,38 @@
     </row>
     <row r="190" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A190" s="6">
-        <v>20333</v>
+        <v>20331</v>
       </c>
       <c r="B190" t="s">
-        <v>136</v>
+        <v>51</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D190" s="13" t="s">
-        <v>5</v>
+      <c r="D190" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="191" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="6">
-        <v>20337</v>
+        <v>20333</v>
       </c>
       <c r="B191" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D191" s="1" t="s">
-        <v>8</v>
+      <c r="D191" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="192" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="6">
-        <v>20343</v>
+        <v>20337</v>
       </c>
       <c r="B192" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>4</v>
@@ -4276,10 +4279,10 @@
     </row>
     <row r="193" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="6">
-        <v>20344</v>
+        <v>20343</v>
       </c>
       <c r="B193" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>4</v>
@@ -4290,66 +4293,66 @@
     </row>
     <row r="194" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="6">
-        <v>20351</v>
+        <v>20344</v>
       </c>
       <c r="B194" t="s">
-        <v>26</v>
+        <v>127</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D194" s="13" t="s">
-        <v>5</v>
+      <c r="D194" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="195" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A195" s="6">
-        <v>20357</v>
+        <v>20351</v>
       </c>
       <c r="B195" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D195" s="1" t="s">
-        <v>8</v>
+      <c r="D195" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="196" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="6">
-        <v>20361</v>
+        <v>20357</v>
       </c>
       <c r="B196" t="s">
-        <v>164</v>
+        <v>56</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D196" s="13" t="s">
-        <v>5</v>
+      <c r="D196" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="197" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="6">
-        <v>20362</v>
+        <v>20361</v>
       </c>
       <c r="B197" t="s">
-        <v>45</v>
+        <v>164</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D197" s="10" t="s">
-        <v>8</v>
+      <c r="D197" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="198" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A198" s="6">
-        <v>20363</v>
+        <v>20362</v>
       </c>
       <c r="B198" t="s">
-        <v>213</v>
+        <v>45</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>4</v>
@@ -4360,38 +4363,38 @@
     </row>
     <row r="199" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="6">
-        <v>20364</v>
+        <v>20363</v>
       </c>
       <c r="B199" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D199" s="13" t="s">
-        <v>5</v>
+      <c r="D199" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="200" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A200" s="6">
-        <v>20366</v>
+        <v>20364</v>
       </c>
       <c r="B200" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D200" s="1" t="s">
-        <v>8</v>
+      <c r="D200" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="201" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="6">
-        <v>20367</v>
+        <v>20366</v>
       </c>
       <c r="B201" t="s">
-        <v>47</v>
+        <v>220</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>4</v>
@@ -4402,10 +4405,10 @@
     </row>
     <row r="202" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="6">
-        <v>20369</v>
+        <v>20367</v>
       </c>
       <c r="B202" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>4</v>
@@ -4416,10 +4419,10 @@
     </row>
     <row r="203" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="6">
-        <v>20371</v>
+        <v>20369</v>
       </c>
       <c r="B203" t="s">
-        <v>223</v>
+        <v>63</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>4</v>
@@ -4430,52 +4433,52 @@
     </row>
     <row r="204" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="6">
-        <v>20372</v>
+        <v>20371</v>
       </c>
       <c r="B204" t="s">
-        <v>70</v>
+        <v>223</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D204" s="10" t="s">
+      <c r="D204" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="205" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A205" s="6">
-        <v>20374</v>
+        <v>20372</v>
       </c>
       <c r="B205" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D205" s="1" t="s">
+      <c r="D205" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="206" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A206" s="6">
-        <v>20377</v>
+        <v>20374</v>
       </c>
       <c r="B206" t="s">
-        <v>225</v>
+        <v>61</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D206" s="10" t="s">
+      <c r="D206" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="207" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A207" s="6">
-        <v>20379</v>
+        <v>20377</v>
       </c>
       <c r="B207" t="s">
-        <v>49</v>
+        <v>225</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>4</v>
@@ -4486,66 +4489,66 @@
     </row>
     <row r="208" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A208" s="6">
-        <v>20380</v>
+        <v>20379</v>
       </c>
       <c r="B208" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D208" s="13" t="s">
-        <v>5</v>
+      <c r="D208" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="209" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A209" s="6">
-        <v>20381</v>
+        <v>20380</v>
       </c>
       <c r="B209" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D209" s="1" t="s">
-        <v>8</v>
+      <c r="D209" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="210" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A210" s="6">
-        <v>20384</v>
+        <v>20381</v>
       </c>
       <c r="B210" t="s">
-        <v>181</v>
+        <v>60</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D210" s="10" t="s">
+      <c r="D210" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="211" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="6">
-        <v>20385</v>
+        <v>20384</v>
       </c>
       <c r="B211" t="s">
-        <v>36</v>
+        <v>181</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D211" s="1" t="s">
+      <c r="D211" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="212" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A212" s="6">
-        <v>20386</v>
+        <v>20385</v>
       </c>
       <c r="B212" t="s">
-        <v>119</v>
+        <v>36</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>4</v>
@@ -4556,66 +4559,66 @@
     </row>
     <row r="213" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A213" s="6">
-        <v>20388</v>
+        <v>20386</v>
       </c>
       <c r="B213" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D213" s="10" t="s">
+      <c r="D213" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="214" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A214" s="6">
-        <v>20391</v>
+        <v>20388</v>
       </c>
       <c r="B214" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D214" s="1" t="s">
+      <c r="D214" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="215" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A215" s="6">
-        <v>20394</v>
+        <v>20391</v>
       </c>
       <c r="B215" t="s">
-        <v>173</v>
+        <v>106</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D215" s="10" t="s">
+      <c r="D215" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="216" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A216" s="6">
-        <v>20395</v>
+        <v>20394</v>
       </c>
       <c r="B216" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D216" s="1" t="s">
+      <c r="D216" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="217" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A217" s="6">
-        <v>20396</v>
+        <v>20395</v>
       </c>
       <c r="B217" t="s">
-        <v>330</v>
+        <v>161</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>4</v>
@@ -4626,52 +4629,52 @@
     </row>
     <row r="218" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A218" s="6">
-        <v>20397</v>
-      </c>
-      <c r="B218" s="8" t="s">
-        <v>344</v>
+        <v>20396</v>
+      </c>
+      <c r="B218" t="s">
+        <v>330</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D218" s="11" t="s">
-        <v>5</v>
+      <c r="D218" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="219" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A219" s="6">
-        <v>30101</v>
-      </c>
-      <c r="B219" t="s">
-        <v>167</v>
+        <v>20397</v>
+      </c>
+      <c r="B219" s="8" t="s">
+        <v>344</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D219" s="1" t="s">
-        <v>8</v>
+      <c r="D219" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="220" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A220" s="6">
-        <v>40124</v>
+        <v>30101</v>
       </c>
       <c r="B220" t="s">
-        <v>24</v>
+        <v>167</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D220" s="13" t="s">
-        <v>5</v>
+      <c r="D220" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="221" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A221" s="6">
-        <v>40125</v>
+        <v>40124</v>
       </c>
       <c r="B221" t="s">
-        <v>143</v>
+        <v>24</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>4</v>
@@ -4682,24 +4685,24 @@
     </row>
     <row r="222" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A222" s="6">
-        <v>40127</v>
+        <v>40125</v>
       </c>
       <c r="B222" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D222" s="1" t="s">
-        <v>8</v>
+      <c r="D222" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="223" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223" s="6">
-        <v>40129</v>
+        <v>40127</v>
       </c>
       <c r="B223" t="s">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>4</v>
@@ -4710,24 +4713,24 @@
     </row>
     <row r="224" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="6">
-        <v>40137</v>
+        <v>40129</v>
       </c>
       <c r="B224" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D224" s="10" t="s">
+      <c r="D224" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="225" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A225" s="6">
-        <v>40139</v>
+        <v>40137</v>
       </c>
       <c r="B225" t="s">
-        <v>327</v>
+        <v>121</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>4</v>
@@ -4738,66 +4741,66 @@
     </row>
     <row r="226" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A226" s="6">
-        <v>40140</v>
+        <v>40139</v>
       </c>
       <c r="B226" t="s">
-        <v>170</v>
+        <v>327</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D226" s="1" t="s">
+      <c r="D226" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="227" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A227" s="6">
-        <v>40141</v>
+        <v>40140</v>
       </c>
       <c r="B227" t="s">
-        <v>111</v>
+        <v>170</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D227" s="13" t="s">
-        <v>5</v>
+      <c r="D227" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="228" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A228" s="6">
-        <v>40143</v>
+        <v>40141</v>
       </c>
       <c r="B228" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D228" s="10" t="s">
-        <v>8</v>
+      <c r="D228" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="229" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A229" s="6">
-        <v>40144</v>
+        <v>40143</v>
       </c>
       <c r="B229" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D229" s="13" t="s">
-        <v>5</v>
+      <c r="D229" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="230" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A230" s="6">
-        <v>40145</v>
+        <v>40144</v>
       </c>
       <c r="B230" t="s">
-        <v>165</v>
+        <v>107</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>4</v>
@@ -4808,192 +4811,192 @@
     </row>
     <row r="231" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A231" s="6">
-        <v>40150</v>
+        <v>40145</v>
       </c>
       <c r="B231" t="s">
-        <v>221</v>
+        <v>165</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D231" s="10" t="s">
-        <v>8</v>
+      <c r="D231" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="232" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A232" s="6">
-        <v>40151</v>
+        <v>40150</v>
       </c>
       <c r="B232" t="s">
-        <v>54</v>
+        <v>221</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D232" s="1" t="s">
+      <c r="D232" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="233" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A233" s="6">
-        <v>50102</v>
+        <v>40151</v>
       </c>
       <c r="B233" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D233" s="13" t="s">
-        <v>5</v>
+      <c r="D233" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="234" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A234" s="6">
-        <v>50222</v>
+        <v>50102</v>
       </c>
       <c r="B234" t="s">
-        <v>215</v>
+        <v>67</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D234" s="1" t="s">
-        <v>8</v>
+      <c r="D234" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="235" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A235" s="6">
-        <v>50223</v>
+        <v>50222</v>
       </c>
       <c r="B235" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D235" s="10" t="s">
+      <c r="D235" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="236" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A236" s="6">
-        <v>50224</v>
+        <v>50223</v>
       </c>
       <c r="B236" t="s">
-        <v>42</v>
+        <v>194</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D236" s="3" t="s">
-        <v>5</v>
+      <c r="D236" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="237" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A237" s="6">
-        <v>50444</v>
+        <v>50224</v>
       </c>
       <c r="B237" t="s">
-        <v>116</v>
+        <v>42</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D237" s="1" t="s">
-        <v>8</v>
+      <c r="D237" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="238" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A238" s="6">
-        <v>50445</v>
+        <v>50444</v>
       </c>
       <c r="B238" t="s">
-        <v>354</v>
+        <v>116</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D238" s="11" t="s">
-        <v>5</v>
+      <c r="D238" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="239" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A239" s="6">
-        <v>50607</v>
+        <v>50445</v>
       </c>
       <c r="B239" t="s">
-        <v>76</v>
+        <v>354</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D239" s="13" t="s">
+      <c r="D239" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="240" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A240" s="6">
-        <v>50608</v>
+        <v>50607</v>
       </c>
       <c r="B240" t="s">
-        <v>177</v>
+        <v>76</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D240" s="1" t="s">
-        <v>8</v>
+      <c r="D240" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="241" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="6">
-        <v>50611</v>
-      </c>
-      <c r="B241" s="8" t="s">
-        <v>347</v>
+        <v>50608</v>
+      </c>
+      <c r="B241" t="s">
+        <v>177</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D241" s="14" t="s">
+      <c r="D241" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="242" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A242" s="6">
-        <v>50622</v>
-      </c>
-      <c r="B242" t="s">
-        <v>95</v>
+        <v>50611</v>
+      </c>
+      <c r="B242" s="8" t="s">
+        <v>347</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D242" s="16" t="s">
+      <c r="D242" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="243" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A243" s="6">
-        <v>50623</v>
+        <v>50622</v>
       </c>
       <c r="B243" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D243" s="10" t="s">
+      <c r="D243" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="244" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A244" s="6">
-        <v>50625</v>
+        <v>50623</v>
       </c>
       <c r="B244" t="s">
-        <v>204</v>
+        <v>110</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>4</v>
@@ -5004,94 +5007,94 @@
     </row>
     <row r="245" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A245" s="6">
-        <v>50629</v>
+        <v>50625</v>
       </c>
       <c r="B245" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D245" s="1" t="s">
+      <c r="D245" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="246" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A246" s="6">
-        <v>50630</v>
+        <v>50629</v>
       </c>
       <c r="B246" t="s">
-        <v>360</v>
+        <v>188</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D246" s="14" t="s">
+      <c r="D246" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="247" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A247" s="6">
-        <v>50803</v>
+        <v>50630</v>
       </c>
       <c r="B247" t="s">
-        <v>82</v>
+        <v>360</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D247" s="1" t="s">
+      <c r="D247" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="248" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A248" s="6">
-        <v>50805</v>
+        <v>50803</v>
       </c>
       <c r="B248" t="s">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D248" s="10" t="s">
+      <c r="D248" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="249" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A249" s="6">
-        <v>50806</v>
+        <v>50805</v>
       </c>
       <c r="B249" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D249" s="1" t="s">
+      <c r="D249" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="250" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A250" s="6">
-        <v>50808</v>
+        <v>50806</v>
       </c>
       <c r="B250" t="s">
-        <v>16</v>
+        <v>156</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D250" s="13" t="s">
-        <v>5</v>
+      <c r="D250" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="251" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A251" s="6">
-        <v>50809</v>
+        <v>50808</v>
       </c>
       <c r="B251" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>4</v>
@@ -5102,24 +5105,24 @@
     </row>
     <row r="252" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A252" s="6">
-        <v>50810</v>
+        <v>50809</v>
       </c>
       <c r="B252" t="s">
-        <v>175</v>
+        <v>98</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D252" s="1" t="s">
-        <v>8</v>
+      <c r="D252" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="253" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A253" s="6">
-        <v>50812</v>
+        <v>50810</v>
       </c>
       <c r="B253" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>4</v>
@@ -5130,80 +5133,80 @@
     </row>
     <row r="254" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="6">
-        <v>50813</v>
+        <v>50812</v>
       </c>
       <c r="B254" t="s">
-        <v>71</v>
+        <v>184</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D254" s="17" t="s">
-        <v>9</v>
+      <c r="D254" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="255" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A255" s="6">
-        <v>50815</v>
+        <v>50813</v>
       </c>
       <c r="B255" t="s">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D255" s="10" t="s">
-        <v>8</v>
+      <c r="D255" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="256" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A256" s="6">
-        <v>50816</v>
+        <v>50815</v>
       </c>
       <c r="B256" t="s">
-        <v>205</v>
+        <v>114</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D256" s="1" t="s">
+      <c r="D256" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="257" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A257" s="6">
-        <v>50818</v>
+        <v>50816</v>
       </c>
       <c r="B257" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D257" s="13" t="s">
-        <v>5</v>
+      <c r="D257" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="258" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A258" s="6">
-        <v>50819</v>
+        <v>50818</v>
       </c>
       <c r="B258" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D258" s="10" t="s">
-        <v>8</v>
+      <c r="D258" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="259" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A259" s="6">
-        <v>50820</v>
+        <v>50819</v>
       </c>
       <c r="B259" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>4</v>
@@ -5214,66 +5217,66 @@
     </row>
     <row r="260" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A260" s="6">
-        <v>50821</v>
+        <v>50820</v>
       </c>
       <c r="B260" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D260" s="1" t="s">
+      <c r="D260" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="261" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A261" s="6">
-        <v>50823</v>
+        <v>50821</v>
       </c>
       <c r="B261" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D261" s="17" t="s">
-        <v>9</v>
+      <c r="D261" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="262" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A262" s="6">
-        <v>50824</v>
+        <v>50823</v>
       </c>
       <c r="B262" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D262" s="13" t="s">
-        <v>5</v>
+      <c r="D262" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="263" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A263" s="6">
-        <v>50825</v>
+        <v>50824</v>
       </c>
       <c r="B263" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D263" s="10" t="s">
-        <v>8</v>
+      <c r="D263" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="264" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A264" s="6">
-        <v>50826</v>
+        <v>50825</v>
       </c>
       <c r="B264" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>4</v>
@@ -5284,24 +5287,24 @@
     </row>
     <row r="265" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A265" s="6">
-        <v>50827</v>
+        <v>50826</v>
       </c>
       <c r="B265" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D265" s="1" t="s">
+      <c r="D265" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="266" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A266" s="6">
-        <v>50829</v>
+        <v>50827</v>
       </c>
       <c r="B266" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>4</v>
@@ -5312,24 +5315,24 @@
     </row>
     <row r="267" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A267" s="6">
-        <v>50830</v>
+        <v>50829</v>
       </c>
       <c r="B267" t="s">
-        <v>366</v>
+        <v>236</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D267" s="11" t="s">
+      <c r="D267" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="268" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A268" s="6">
-        <v>50831</v>
+        <v>50830</v>
       </c>
       <c r="B268" t="s">
-        <v>351</v>
+        <v>366</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>4</v>
@@ -5340,94 +5343,94 @@
     </row>
     <row r="269" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A269" s="6">
-        <v>50832</v>
-      </c>
-      <c r="B269" s="8" t="s">
-        <v>349</v>
+        <v>50831</v>
+      </c>
+      <c r="B269" t="s">
+        <v>351</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D269" s="11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="270" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A270" s="6">
-        <v>50833</v>
+        <v>50832</v>
       </c>
       <c r="B270" s="8" t="s">
-        <v>397</v>
+        <v>349</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D270" s="11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="271" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A271" s="6">
-        <v>50230</v>
+        <v>50833</v>
       </c>
       <c r="B271" s="8" t="s">
-        <v>379</v>
+        <v>397</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D271" s="11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="272" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A272" s="6">
-        <v>60103</v>
-      </c>
-      <c r="B272" t="s">
-        <v>237</v>
+        <v>50230</v>
+      </c>
+      <c r="B272" s="8" t="s">
+        <v>379</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D272" s="13" t="s">
+      <c r="D272" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="273" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A273" s="6">
-        <v>60109</v>
+        <v>60103</v>
       </c>
       <c r="B273" t="s">
-        <v>328</v>
+        <v>237</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D273" s="11" t="s">
-        <v>9</v>
+      <c r="D273" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="274" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A274" s="6">
-        <v>60124</v>
+        <v>60109</v>
       </c>
       <c r="B274" t="s">
-        <v>238</v>
+        <v>328</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D274" s="13" t="s">
-        <v>5</v>
+      <c r="D274" s="11" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="275" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A275" s="6">
-        <v>60125</v>
+        <v>60124</v>
       </c>
       <c r="B275" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>4</v>
@@ -5438,80 +5441,80 @@
     </row>
     <row r="276" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A276" s="6">
-        <v>60126</v>
+        <v>60125</v>
       </c>
       <c r="B276" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D276" s="10" t="s">
-        <v>8</v>
+      <c r="D276" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="277" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A277" s="6">
-        <v>60128</v>
+        <v>60126</v>
       </c>
       <c r="B277" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D277" s="3" t="s">
-        <v>5</v>
+      <c r="D277" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="278" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A278" s="6">
-        <v>60130</v>
+        <v>60128</v>
       </c>
       <c r="B278" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D278" s="1" t="s">
-        <v>8</v>
+      <c r="D278" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="279" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A279" s="6">
-        <v>60133</v>
+        <v>60130</v>
       </c>
       <c r="B279" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D279" s="13" t="s">
-        <v>5</v>
+      <c r="D279" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="280" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A280" s="6">
-        <v>60134</v>
+        <v>60133</v>
       </c>
       <c r="B280" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D280" s="1" t="s">
-        <v>8</v>
+      <c r="D280" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="281" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A281" s="6">
-        <v>60137</v>
+        <v>60134</v>
       </c>
       <c r="B281" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>4</v>
@@ -5522,10 +5525,10 @@
     </row>
     <row r="282" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A282" s="6">
-        <v>60139</v>
+        <v>60137</v>
       </c>
       <c r="B282" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>4</v>
@@ -5536,10 +5539,10 @@
     </row>
     <row r="283" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A283" s="6">
-        <v>60142</v>
+        <v>60139</v>
       </c>
       <c r="B283" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>4</v>
@@ -5550,10 +5553,10 @@
     </row>
     <row r="284" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A284" s="6">
-        <v>60148</v>
+        <v>60142</v>
       </c>
       <c r="B284" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>4</v>
@@ -5564,10 +5567,10 @@
     </row>
     <row r="285" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A285" s="6">
-        <v>60149</v>
+        <v>60148</v>
       </c>
       <c r="B285" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>4</v>
@@ -5578,66 +5581,66 @@
     </row>
     <row r="286" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A286" s="6">
-        <v>60150</v>
+        <v>60149</v>
       </c>
       <c r="B286" t="s">
-        <v>332</v>
+        <v>249</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D286" s="13" t="s">
-        <v>5</v>
+      <c r="D286" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="287" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A287" s="6">
-        <v>60158</v>
+        <v>60150</v>
       </c>
       <c r="B287" t="s">
-        <v>250</v>
+        <v>332</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D287" s="10" t="s">
-        <v>8</v>
+      <c r="D287" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="288" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A288" s="6">
-        <v>60159</v>
+        <v>60158</v>
       </c>
       <c r="B288" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D288" s="1" t="s">
+      <c r="D288" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="289" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A289" s="6">
-        <v>60162</v>
+        <v>60159</v>
       </c>
       <c r="B289" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D289" s="13" t="s">
-        <v>5</v>
+      <c r="D289" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="290" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A290" s="6">
-        <v>60163</v>
+        <v>60162</v>
       </c>
       <c r="B290" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>4</v>
@@ -5648,24 +5651,24 @@
     </row>
     <row r="291" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A291" s="6">
-        <v>60165</v>
+        <v>60163</v>
       </c>
       <c r="B291" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D291" s="1" t="s">
-        <v>8</v>
+      <c r="D291" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="292" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A292" s="6">
-        <v>60169</v>
+        <v>60165</v>
       </c>
       <c r="B292" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>4</v>
@@ -5676,52 +5679,52 @@
     </row>
     <row r="293" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A293" s="6">
-        <v>60170</v>
-      </c>
-      <c r="B293" s="8" t="s">
-        <v>337</v>
+        <v>60169</v>
+      </c>
+      <c r="B293" t="s">
+        <v>255</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D293" s="11" t="s">
+      <c r="D293" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="294" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A294" s="6">
-        <v>60172</v>
-      </c>
-      <c r="B294" t="s">
-        <v>256</v>
+        <v>60170</v>
+      </c>
+      <c r="B294" s="8" t="s">
+        <v>337</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D294" s="1" t="s">
+      <c r="D294" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="295" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A295" s="6">
-        <v>60174</v>
+        <v>60172</v>
       </c>
       <c r="B295" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D295" s="13" t="s">
-        <v>5</v>
+      <c r="D295" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="296" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A296" s="6">
-        <v>60176</v>
+        <v>60174</v>
       </c>
       <c r="B296" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>4</v>
@@ -5732,52 +5735,52 @@
     </row>
     <row r="297" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A297" s="6">
-        <v>60178</v>
+        <v>60176</v>
       </c>
       <c r="B297" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D297" s="1" t="s">
-        <v>8</v>
+      <c r="D297" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="298" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A298" s="6">
-        <v>60180</v>
+        <v>60178</v>
       </c>
       <c r="B298" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D298" s="10" t="s">
+      <c r="D298" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="299" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A299" s="6">
-        <v>60184</v>
+        <v>60180</v>
       </c>
       <c r="B299" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D299" s="1" t="s">
+      <c r="D299" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="300" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A300" s="6">
-        <v>60190</v>
+        <v>60184</v>
       </c>
       <c r="B300" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>4</v>
@@ -5788,24 +5791,24 @@
     </row>
     <row r="301" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A301" s="6">
-        <v>60191</v>
+        <v>60190</v>
       </c>
       <c r="B301" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D301" s="10" t="s">
+      <c r="D301" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="302" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A302" s="6">
-        <v>60192</v>
+        <v>60191</v>
       </c>
       <c r="B302" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>4</v>
@@ -5816,10 +5819,10 @@
     </row>
     <row r="303" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A303" s="6">
-        <v>60195</v>
+        <v>60192</v>
       </c>
       <c r="B303" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>4</v>
@@ -5830,10 +5833,10 @@
     </row>
     <row r="304" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A304" s="6">
-        <v>60196</v>
+        <v>60195</v>
       </c>
       <c r="B304" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>4</v>
@@ -5844,10 +5847,10 @@
     </row>
     <row r="305" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A305" s="6">
-        <v>60198</v>
+        <v>60196</v>
       </c>
       <c r="B305" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>4</v>
@@ -5858,52 +5861,52 @@
     </row>
     <row r="306" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A306" s="6">
-        <v>60201</v>
+        <v>60198</v>
       </c>
       <c r="B306" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D306" t="s">
-        <v>9</v>
+      <c r="D306" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="307" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A307" s="6">
-        <v>60202</v>
+        <v>60201</v>
       </c>
       <c r="B307" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D307" s="13" t="s">
-        <v>5</v>
+      <c r="D307" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="308" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A308" s="6">
-        <v>60204</v>
+        <v>60202</v>
       </c>
       <c r="B308" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D308" s="1" t="s">
-        <v>8</v>
+      <c r="D308" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="309" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A309" s="6">
-        <v>60205</v>
+        <v>60204</v>
       </c>
       <c r="B309" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>4</v>
@@ -5914,10 +5917,10 @@
     </row>
     <row r="310" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A310" s="6">
-        <v>60206</v>
+        <v>60205</v>
       </c>
       <c r="B310" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>4</v>
@@ -5928,220 +5931,220 @@
     </row>
     <row r="311" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A311" s="6">
-        <v>60209</v>
+        <v>60206</v>
       </c>
       <c r="B311" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D311" s="10" t="s">
+      <c r="D311" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="312" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A312" s="6">
-        <v>60211</v>
+        <v>60209</v>
       </c>
       <c r="B312" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D312" s="1" t="s">
+      <c r="D312" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="313" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A313" s="6">
-        <v>60215</v>
+        <v>60211</v>
       </c>
       <c r="B313" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D313" s="10" t="s">
+      <c r="D313" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="314" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A314" s="6">
-        <v>60216</v>
+        <v>60215</v>
       </c>
       <c r="B314" t="s">
-        <v>381</v>
+        <v>275</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D314" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="315" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A315" s="6">
-        <v>60217</v>
+        <v>60216</v>
       </c>
       <c r="B315" t="s">
-        <v>276</v>
+        <v>381</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D315" s="10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="316" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A316" s="6">
-        <v>60219</v>
+        <v>60217</v>
       </c>
       <c r="B316" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D316" s="1" t="s">
+      <c r="D316" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="317" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A317" s="6">
-        <v>60222</v>
+        <v>60219</v>
       </c>
       <c r="B317" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D317" s="10" t="s">
+      <c r="D317" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="318" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A318" s="6">
-        <v>60225</v>
+        <v>60222</v>
       </c>
       <c r="B318" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D318" s="17" t="s">
-        <v>9</v>
+      <c r="D318" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="319" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A319" s="6">
-        <v>60230</v>
+        <v>60225</v>
       </c>
       <c r="B319" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D319" s="10" t="s">
-        <v>8</v>
+      <c r="D319" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="320" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A320" s="6">
-        <v>60241</v>
-      </c>
-      <c r="B320" s="8" t="s">
-        <v>338</v>
+        <v>60230</v>
+      </c>
+      <c r="B320" t="s">
+        <v>280</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D320" s="7" t="s">
-        <v>9</v>
+      <c r="D320" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="321" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A321" s="6">
-        <v>60242</v>
+        <v>60241</v>
       </c>
       <c r="B321" s="8" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D321" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="322" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A322" s="6">
-        <v>60243</v>
+        <v>60242</v>
       </c>
       <c r="B322" s="8" t="s">
-        <v>395</v>
+        <v>341</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D322" s="7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="323" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A323" s="6">
-        <v>60245</v>
+        <v>60243</v>
       </c>
       <c r="B323" s="8" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D323" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="324" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A324" s="6">
-        <v>60250</v>
+        <v>60245</v>
       </c>
       <c r="B324" s="8" t="s">
-        <v>339</v>
+        <v>387</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D324" s="11" t="s">
-        <v>8</v>
+      <c r="D324" s="7" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="325" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A325" s="6">
-        <v>60253</v>
-      </c>
-      <c r="B325" t="s">
-        <v>281</v>
+        <v>60250</v>
+      </c>
+      <c r="B325" s="8" t="s">
+        <v>339</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D325" s="1" t="s">
+      <c r="D325" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="326" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A326" s="6">
-        <v>60254</v>
+        <v>60253</v>
       </c>
       <c r="B326" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>4</v>
@@ -6152,10 +6155,10 @@
     </row>
     <row r="327" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A327" s="6">
-        <v>60257</v>
+        <v>60254</v>
       </c>
       <c r="B327" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>4</v>
@@ -6166,10 +6169,10 @@
     </row>
     <row r="328" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A328" s="6">
-        <v>60258</v>
+        <v>60257</v>
       </c>
       <c r="B328" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>4</v>
@@ -6180,66 +6183,66 @@
     </row>
     <row r="329" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A329" s="6">
-        <v>60266</v>
-      </c>
-      <c r="B329" s="8" t="s">
-        <v>343</v>
+        <v>60258</v>
+      </c>
+      <c r="B329" t="s">
+        <v>284</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D329" s="11" t="s">
+      <c r="D329" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="330" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A330" s="6">
-        <v>60269</v>
-      </c>
-      <c r="B330" t="s">
-        <v>285</v>
+        <v>60266</v>
+      </c>
+      <c r="B330" s="8" t="s">
+        <v>343</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D330" s="10" t="s">
+      <c r="D330" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="331" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A331" s="6">
-        <v>60270</v>
+        <v>60269</v>
       </c>
       <c r="B331" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D331" s="1" t="s">
-        <v>9</v>
+      <c r="D331" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="332" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A332" s="6">
-        <v>60272</v>
+        <v>60270</v>
       </c>
       <c r="B332" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="333" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A333" s="6">
-        <v>60274</v>
+        <v>60272</v>
       </c>
       <c r="B333" t="s">
-        <v>380</v>
+        <v>287</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>4</v>
@@ -6250,10 +6253,10 @@
     </row>
     <row r="334" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A334" s="6">
-        <v>60275</v>
+        <v>60274</v>
       </c>
       <c r="B334" t="s">
-        <v>288</v>
+        <v>380</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>4</v>
@@ -6264,10 +6267,10 @@
     </row>
     <row r="335" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A335" s="6">
-        <v>60276</v>
+        <v>60275</v>
       </c>
       <c r="B335" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>4</v>
@@ -6278,108 +6281,108 @@
     </row>
     <row r="336" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A336" s="6">
-        <v>60278</v>
+        <v>60276</v>
       </c>
       <c r="B336" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D336" s="13" t="s">
+      <c r="D336" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="337" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A337" s="6">
-        <v>60279</v>
+        <v>60278</v>
       </c>
       <c r="B337" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D337" s="1" t="s">
+      <c r="D337" s="13" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="338" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A338" s="6">
-        <v>60280</v>
+        <v>60279</v>
       </c>
       <c r="B338" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="339" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A339" s="6">
-        <v>60281</v>
-      </c>
-      <c r="B339" s="8" t="s">
-        <v>336</v>
+        <v>60280</v>
+      </c>
+      <c r="B339" t="s">
+        <v>292</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D339" s="11" t="s">
-        <v>9</v>
+      <c r="D339" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="340" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A340" s="6">
-        <v>60282</v>
+        <v>60281</v>
       </c>
       <c r="B340" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D340" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="341" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A341" s="6">
-        <v>60283</v>
-      </c>
-      <c r="B341" t="s">
-        <v>378</v>
+        <v>60282</v>
+      </c>
+      <c r="B341" s="8" t="s">
+        <v>340</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D341" s="1" t="s">
-        <v>8</v>
+      <c r="D341" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="342" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A342" s="6">
-        <v>60284</v>
-      </c>
-      <c r="B342" s="8" t="s">
-        <v>335</v>
+        <v>60283</v>
+      </c>
+      <c r="B342" t="s">
+        <v>378</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D342" s="9" t="s">
-        <v>5</v>
+      <c r="D342" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="343" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A343" s="6">
-        <v>60285</v>
+        <v>60284</v>
       </c>
       <c r="B343" s="8" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>4</v>
@@ -6390,10 +6393,10 @@
     </row>
     <row r="344" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A344" s="6">
-        <v>60286</v>
+        <v>60285</v>
       </c>
       <c r="B344" s="8" t="s">
-        <v>334</v>
+        <v>350</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>4</v>
@@ -6404,52 +6407,52 @@
     </row>
     <row r="345" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A345" s="6">
-        <v>60287</v>
-      </c>
-      <c r="B345" t="s">
-        <v>377</v>
+        <v>60286</v>
+      </c>
+      <c r="B345" s="8" t="s">
+        <v>334</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D345" s="12" t="s">
+      <c r="D345" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="346" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A346" s="6">
-        <v>60289</v>
+        <v>60287</v>
       </c>
       <c r="B346" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D346" s="12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="347" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A347" s="6">
-        <v>60290</v>
+        <v>60289</v>
       </c>
       <c r="B347" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D347" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="348" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A348" s="6">
-        <v>60291</v>
+        <v>60290</v>
       </c>
       <c r="B348" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>4</v>
@@ -6460,24 +6463,24 @@
     </row>
     <row r="349" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A349" s="6">
-        <v>60292</v>
-      </c>
-      <c r="B349" s="18" t="s">
-        <v>400</v>
+        <v>60291</v>
+      </c>
+      <c r="B349" t="s">
+        <v>376</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D349" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="350" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A350" s="6">
-        <v>60296</v>
-      </c>
-      <c r="B350" t="s">
-        <v>391</v>
+        <v>60292</v>
+      </c>
+      <c r="B350" s="18" t="s">
+        <v>400</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>4</v>
@@ -6488,24 +6491,24 @@
     </row>
     <row r="351" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A351" s="6">
-        <v>60297</v>
+        <v>60296</v>
       </c>
       <c r="B351" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D351" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="352" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A352" s="6">
-        <v>60299</v>
+        <v>60297</v>
       </c>
       <c r="B352" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>4</v>
@@ -6516,38 +6519,38 @@
     </row>
     <row r="353" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A353" s="6">
-        <v>61004</v>
+        <v>60299</v>
       </c>
       <c r="B353" t="s">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D353" s="15" t="s">
+      <c r="D353" s="12" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="354" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A354" s="6">
-        <v>61009</v>
+        <v>61004</v>
       </c>
       <c r="B354" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D354" s="12" t="s">
-        <v>8</v>
+      <c r="D354" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="355" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A355" s="6">
-        <v>61012</v>
+        <v>61009</v>
       </c>
       <c r="B355" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>4</v>
@@ -6558,10 +6561,10 @@
     </row>
     <row r="356" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A356" s="6">
-        <v>61018</v>
+        <v>61012</v>
       </c>
       <c r="B356" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>4</v>
@@ -6572,10 +6575,10 @@
     </row>
     <row r="357" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A357" s="6">
-        <v>61102</v>
+        <v>61018</v>
       </c>
       <c r="B357" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>4</v>
@@ -6586,52 +6589,52 @@
     </row>
     <row r="358" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A358" s="6">
-        <v>61205</v>
+        <v>61102</v>
       </c>
       <c r="B358" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D358" s="15" t="s">
-        <v>5</v>
+      <c r="D358" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="359" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A359" s="6">
-        <v>70100</v>
+        <v>61205</v>
       </c>
       <c r="B359" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D359" s="12" t="s">
-        <v>8</v>
+      <c r="D359" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="360" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A360" s="6">
-        <v>70101</v>
+        <v>70100</v>
       </c>
       <c r="B360" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D360" s="15" t="s">
-        <v>5</v>
+      <c r="D360" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="361" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A361" s="6">
-        <v>70102</v>
+        <v>70101</v>
       </c>
       <c r="B361" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>4</v>
@@ -6642,80 +6645,80 @@
     </row>
     <row r="362" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A362" s="6">
-        <v>70103</v>
+        <v>70102</v>
       </c>
       <c r="B362" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D362" s="12" t="s">
-        <v>8</v>
+      <c r="D362" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="363" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A363" s="6">
-        <v>70106</v>
+        <v>70103</v>
       </c>
       <c r="B363" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D363" s="15" t="s">
-        <v>5</v>
+      <c r="D363" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="364" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A364" s="6">
-        <v>70109</v>
+        <v>70106</v>
       </c>
       <c r="B364" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D364" s="12" t="s">
-        <v>8</v>
+      <c r="D364" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="365" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A365" s="6">
-        <v>70113</v>
+        <v>70109</v>
       </c>
       <c r="B365" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D365" s="15" t="s">
-        <v>5</v>
+      <c r="D365" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="366" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A366" s="6">
-        <v>70114</v>
+        <v>70113</v>
       </c>
       <c r="B366" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D366" s="9" t="s">
-        <v>9</v>
+      <c r="D366" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="367" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A367" s="6">
-        <v>70115</v>
+        <v>70114</v>
       </c>
       <c r="B367" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>4</v>
@@ -6726,24 +6729,24 @@
     </row>
     <row r="368" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A368" s="6">
-        <v>70638</v>
+        <v>70115</v>
       </c>
       <c r="B368" t="s">
-        <v>306</v>
+        <v>331</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D368" s="12" t="s">
-        <v>8</v>
+      <c r="D368" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="369" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A369" s="6">
-        <v>70639</v>
+        <v>70638</v>
       </c>
       <c r="B369" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>4</v>
@@ -6754,10 +6757,10 @@
     </row>
     <row r="370" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A370" s="6">
-        <v>70640</v>
+        <v>70639</v>
       </c>
       <c r="B370" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>4</v>
@@ -6768,10 +6771,10 @@
     </row>
     <row r="371" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A371" s="6">
-        <v>70642</v>
+        <v>70640</v>
       </c>
       <c r="B371" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>4</v>
@@ -6782,10 +6785,10 @@
     </row>
     <row r="372" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A372" s="6">
-        <v>90504</v>
+        <v>70642</v>
       </c>
       <c r="B372" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>4</v>
@@ -6796,10 +6799,10 @@
     </row>
     <row r="373" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A373" s="6">
-        <v>90509</v>
+        <v>90504</v>
       </c>
       <c r="B373" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>4</v>
@@ -6810,52 +6813,52 @@
     </row>
     <row r="374" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A374" s="6">
-        <v>90602</v>
+        <v>90509</v>
       </c>
       <c r="B374" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D374" s="15" t="s">
-        <v>5</v>
+      <c r="D374" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="375" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A375" s="6">
-        <v>90621</v>
+        <v>90602</v>
       </c>
       <c r="B375" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D375" s="12" t="s">
-        <v>8</v>
+      <c r="D375" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="376" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A376" s="6">
-        <v>90622</v>
+        <v>90621</v>
       </c>
       <c r="B376" t="s">
-        <v>333</v>
+        <v>313</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D376" s="9" t="s">
-        <v>5</v>
+      <c r="D376" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="377" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A377" s="6">
-        <v>90631</v>
-      </c>
-      <c r="B377" s="8" t="s">
-        <v>342</v>
+        <v>90622</v>
+      </c>
+      <c r="B377" t="s">
+        <v>333</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>4</v>
@@ -6866,24 +6869,24 @@
     </row>
     <row r="378" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A378" s="6">
-        <v>90658</v>
-      </c>
-      <c r="B378" t="s">
-        <v>314</v>
+        <v>90631</v>
+      </c>
+      <c r="B378" s="8" t="s">
+        <v>342</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D378" s="12" t="s">
-        <v>8</v>
+      <c r="D378" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="379" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A379" s="6">
-        <v>90660</v>
+        <v>90658</v>
       </c>
       <c r="B379" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>4</v>
@@ -6894,10 +6897,10 @@
     </row>
     <row r="380" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A380" s="6">
-        <v>90668</v>
+        <v>90660</v>
       </c>
       <c r="B380" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>4</v>
@@ -6908,10 +6911,10 @@
     </row>
     <row r="381" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A381" s="6">
-        <v>90671</v>
+        <v>90668</v>
       </c>
       <c r="B381" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>4</v>
@@ -6922,10 +6925,10 @@
     </row>
     <row r="382" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A382" s="6">
-        <v>90679</v>
+        <v>90671</v>
       </c>
       <c r="B382" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>4</v>
@@ -6936,10 +6939,10 @@
     </row>
     <row r="383" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A383" s="6">
-        <v>90683</v>
+        <v>90679</v>
       </c>
       <c r="B383" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>4</v>
@@ -6950,10 +6953,10 @@
     </row>
     <row r="384" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A384" s="6">
-        <v>90705</v>
+        <v>90683</v>
       </c>
       <c r="B384" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>4</v>
@@ -6964,10 +6967,10 @@
     </row>
     <row r="385" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A385" s="6">
-        <v>90706</v>
+        <v>90705</v>
       </c>
       <c r="B385" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>4</v>
@@ -6978,10 +6981,10 @@
     </row>
     <row r="386" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A386" s="6">
-        <v>90708</v>
+        <v>90706</v>
       </c>
       <c r="B386" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>4</v>
@@ -6992,10 +6995,10 @@
     </row>
     <row r="387" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A387" s="6">
-        <v>90709</v>
+        <v>90708</v>
       </c>
       <c r="B387" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>4</v>
@@ -7006,10 +7009,10 @@
     </row>
     <row r="388" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A388" s="6">
-        <v>1218</v>
+        <v>90709</v>
       </c>
       <c r="B388" t="s">
-        <v>382</v>
+        <v>323</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>4</v>
@@ -7020,10 +7023,10 @@
     </row>
     <row r="389" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A389" s="6">
-        <v>1959</v>
-      </c>
-      <c r="B389" s="8" t="s">
-        <v>383</v>
+        <v>1218</v>
+      </c>
+      <c r="B389" t="s">
+        <v>382</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>4</v>
@@ -7034,10 +7037,10 @@
     </row>
     <row r="390" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A390" s="6">
-        <v>5625</v>
+        <v>1959</v>
       </c>
       <c r="B390" s="8" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>4</v>
@@ -7048,10 +7051,10 @@
     </row>
     <row r="391" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A391" s="6">
-        <v>1817</v>
+        <v>5625</v>
       </c>
       <c r="B391" s="8" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>4</v>
@@ -7062,10 +7065,10 @@
     </row>
     <row r="392" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A392" s="6">
-        <v>5737</v>
+        <v>1817</v>
       </c>
       <c r="B392" s="8" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>4</v>
@@ -7076,34 +7079,48 @@
     </row>
     <row r="393" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A393" s="6">
-        <v>60295</v>
+        <v>5737</v>
       </c>
       <c r="B393" s="8" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D393" s="9" t="s">
-        <v>9</v>
+      <c r="D393" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="394" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A394" s="6">
+        <v>60295</v>
+      </c>
+      <c r="B394" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="C394" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D394" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A395" s="6">
         <v>1045</v>
       </c>
-      <c r="B394" s="8" t="s">
+      <c r="B395" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="C394" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D394" s="9" t="s">
+      <c r="C395" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D395" s="9" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D341"/>
+  <autoFilter ref="A1:D342"/>
   <sortState ref="A2:D374">
     <sortCondition ref="A277"/>
   </sortState>

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -5352,7 +5352,7 @@
         <v>4</v>
       </c>
       <c r="D269" s="11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="270" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1186" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1189" uniqueCount="403">
   <si>
     <t>CUENTA</t>
   </si>
@@ -1228,6 +1228,9 @@
   </si>
   <si>
     <t>FERRETERIA VIGO</t>
+  </si>
+  <si>
+    <t>SANTO DOMINGO</t>
   </si>
 </sst>
 </file>
@@ -1581,7 +1584,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D395"/>
+  <dimension ref="A1:D396"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -7023,24 +7026,24 @@
     </row>
     <row r="389" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A389" s="6">
-        <v>1218</v>
+        <v>90713</v>
       </c>
       <c r="B389" t="s">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D389" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="390" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A390" s="6">
-        <v>1959</v>
-      </c>
-      <c r="B390" s="8" t="s">
-        <v>383</v>
+        <v>1218</v>
+      </c>
+      <c r="B390" t="s">
+        <v>382</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>4</v>
@@ -7051,10 +7054,10 @@
     </row>
     <row r="391" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A391" s="6">
-        <v>5625</v>
+        <v>1959</v>
       </c>
       <c r="B391" s="8" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>4</v>
@@ -7065,10 +7068,10 @@
     </row>
     <row r="392" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A392" s="6">
-        <v>1817</v>
+        <v>5625</v>
       </c>
       <c r="B392" s="8" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>4</v>
@@ -7079,10 +7082,10 @@
     </row>
     <row r="393" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A393" s="6">
-        <v>5737</v>
+        <v>1817</v>
       </c>
       <c r="B393" s="8" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>4</v>
@@ -7093,29 +7096,43 @@
     </row>
     <row r="394" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A394" s="6">
-        <v>60295</v>
+        <v>5737</v>
       </c>
       <c r="B394" s="8" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D394" s="9" t="s">
-        <v>9</v>
+      <c r="D394" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="395" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A395" s="6">
+        <v>60295</v>
+      </c>
+      <c r="B395" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="C395" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D395" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A396" s="6">
         <v>1045</v>
       </c>
-      <c r="B395" s="8" t="s">
+      <c r="B396" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="C395" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D395" s="9" t="s">
+      <c r="C396" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D396" s="9" t="s">
         <v>5</v>
       </c>
     </row>

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -5355,7 +5355,7 @@
         <v>4</v>
       </c>
       <c r="D269" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="270" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1189" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1192" uniqueCount="404">
   <si>
     <t>CUENTA</t>
   </si>
@@ -1231,6 +1231,9 @@
   </si>
   <si>
     <t>SANTO DOMINGO</t>
+  </si>
+  <si>
+    <t>FERRIYAN 2</t>
   </si>
 </sst>
 </file>
@@ -1584,7 +1587,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D396"/>
+  <dimension ref="A1:D397"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -6536,38 +6539,38 @@
     </row>
     <row r="354" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A354" s="6">
-        <v>61004</v>
+        <v>61001</v>
       </c>
       <c r="B354" t="s">
-        <v>293</v>
+        <v>403</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D354" s="15" t="s">
-        <v>5</v>
+      <c r="D354" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="355" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A355" s="6">
-        <v>61009</v>
+        <v>61004</v>
       </c>
       <c r="B355" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D355" s="12" t="s">
-        <v>8</v>
+      <c r="D355" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="356" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A356" s="6">
-        <v>61012</v>
+        <v>61009</v>
       </c>
       <c r="B356" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>4</v>
@@ -6578,10 +6581,10 @@
     </row>
     <row r="357" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A357" s="6">
-        <v>61018</v>
+        <v>61012</v>
       </c>
       <c r="B357" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>4</v>
@@ -6592,10 +6595,10 @@
     </row>
     <row r="358" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A358" s="6">
-        <v>61102</v>
+        <v>61018</v>
       </c>
       <c r="B358" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>4</v>
@@ -6606,52 +6609,52 @@
     </row>
     <row r="359" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A359" s="6">
-        <v>61205</v>
+        <v>61102</v>
       </c>
       <c r="B359" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D359" s="15" t="s">
-        <v>5</v>
+      <c r="D359" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="360" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A360" s="6">
-        <v>70100</v>
+        <v>61205</v>
       </c>
       <c r="B360" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D360" s="12" t="s">
-        <v>8</v>
+      <c r="D360" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="361" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A361" s="6">
-        <v>70101</v>
+        <v>70100</v>
       </c>
       <c r="B361" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D361" s="15" t="s">
-        <v>5</v>
+      <c r="D361" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="362" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A362" s="6">
-        <v>70102</v>
+        <v>70101</v>
       </c>
       <c r="B362" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>4</v>
@@ -6662,80 +6665,80 @@
     </row>
     <row r="363" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A363" s="6">
-        <v>70103</v>
+        <v>70102</v>
       </c>
       <c r="B363" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D363" s="12" t="s">
-        <v>8</v>
+      <c r="D363" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="364" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A364" s="6">
-        <v>70106</v>
+        <v>70103</v>
       </c>
       <c r="B364" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D364" s="15" t="s">
-        <v>5</v>
+      <c r="D364" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="365" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A365" s="6">
-        <v>70109</v>
+        <v>70106</v>
       </c>
       <c r="B365" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D365" s="12" t="s">
-        <v>8</v>
+      <c r="D365" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="366" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A366" s="6">
-        <v>70113</v>
+        <v>70109</v>
       </c>
       <c r="B366" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D366" s="15" t="s">
-        <v>5</v>
+      <c r="D366" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="367" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A367" s="6">
-        <v>70114</v>
+        <v>70113</v>
       </c>
       <c r="B367" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D367" s="9" t="s">
-        <v>9</v>
+      <c r="D367" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="368" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A368" s="6">
-        <v>70115</v>
+        <v>70114</v>
       </c>
       <c r="B368" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>4</v>
@@ -6746,24 +6749,24 @@
     </row>
     <row r="369" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A369" s="6">
-        <v>70638</v>
+        <v>70115</v>
       </c>
       <c r="B369" t="s">
-        <v>306</v>
+        <v>331</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D369" s="12" t="s">
-        <v>8</v>
+      <c r="D369" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="370" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A370" s="6">
-        <v>70639</v>
+        <v>70638</v>
       </c>
       <c r="B370" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>4</v>
@@ -6774,10 +6777,10 @@
     </row>
     <row r="371" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A371" s="6">
-        <v>70640</v>
+        <v>70639</v>
       </c>
       <c r="B371" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>4</v>
@@ -6788,10 +6791,10 @@
     </row>
     <row r="372" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A372" s="6">
-        <v>70642</v>
+        <v>70640</v>
       </c>
       <c r="B372" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>4</v>
@@ -6802,10 +6805,10 @@
     </row>
     <row r="373" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A373" s="6">
-        <v>90504</v>
+        <v>70642</v>
       </c>
       <c r="B373" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>4</v>
@@ -6816,10 +6819,10 @@
     </row>
     <row r="374" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A374" s="6">
-        <v>90509</v>
+        <v>90504</v>
       </c>
       <c r="B374" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>4</v>
@@ -6830,52 +6833,52 @@
     </row>
     <row r="375" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A375" s="6">
-        <v>90602</v>
+        <v>90509</v>
       </c>
       <c r="B375" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D375" s="15" t="s">
-        <v>5</v>
+      <c r="D375" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="376" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A376" s="6">
-        <v>90621</v>
+        <v>90602</v>
       </c>
       <c r="B376" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D376" s="12" t="s">
-        <v>8</v>
+      <c r="D376" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="377" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A377" s="6">
-        <v>90622</v>
+        <v>90621</v>
       </c>
       <c r="B377" t="s">
-        <v>333</v>
+        <v>313</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D377" s="9" t="s">
-        <v>5</v>
+      <c r="D377" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="378" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A378" s="6">
-        <v>90631</v>
-      </c>
-      <c r="B378" s="8" t="s">
-        <v>342</v>
+        <v>90622</v>
+      </c>
+      <c r="B378" t="s">
+        <v>333</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>4</v>
@@ -6886,24 +6889,24 @@
     </row>
     <row r="379" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A379" s="6">
-        <v>90658</v>
-      </c>
-      <c r="B379" t="s">
-        <v>314</v>
+        <v>90631</v>
+      </c>
+      <c r="B379" s="8" t="s">
+        <v>342</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D379" s="12" t="s">
-        <v>8</v>
+      <c r="D379" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="380" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A380" s="6">
-        <v>90660</v>
+        <v>90658</v>
       </c>
       <c r="B380" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>4</v>
@@ -6914,10 +6917,10 @@
     </row>
     <row r="381" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A381" s="6">
-        <v>90668</v>
+        <v>90660</v>
       </c>
       <c r="B381" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>4</v>
@@ -6928,10 +6931,10 @@
     </row>
     <row r="382" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A382" s="6">
-        <v>90671</v>
+        <v>90668</v>
       </c>
       <c r="B382" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>4</v>
@@ -6942,10 +6945,10 @@
     </row>
     <row r="383" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A383" s="6">
-        <v>90679</v>
+        <v>90671</v>
       </c>
       <c r="B383" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>4</v>
@@ -6956,10 +6959,10 @@
     </row>
     <row r="384" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A384" s="6">
-        <v>90683</v>
+        <v>90679</v>
       </c>
       <c r="B384" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>4</v>
@@ -6970,10 +6973,10 @@
     </row>
     <row r="385" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A385" s="6">
-        <v>90705</v>
+        <v>90683</v>
       </c>
       <c r="B385" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>4</v>
@@ -6984,10 +6987,10 @@
     </row>
     <row r="386" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A386" s="6">
-        <v>90706</v>
+        <v>90705</v>
       </c>
       <c r="B386" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>4</v>
@@ -6998,10 +7001,10 @@
     </row>
     <row r="387" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A387" s="6">
-        <v>90708</v>
+        <v>90706</v>
       </c>
       <c r="B387" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>4</v>
@@ -7012,10 +7015,10 @@
     </row>
     <row r="388" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A388" s="6">
-        <v>90709</v>
+        <v>90708</v>
       </c>
       <c r="B388" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>4</v>
@@ -7026,38 +7029,38 @@
     </row>
     <row r="389" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A389" s="6">
-        <v>90713</v>
+        <v>90709</v>
       </c>
       <c r="B389" t="s">
-        <v>402</v>
+        <v>323</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D389" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="390" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A390" s="6">
-        <v>1218</v>
+        <v>90713</v>
       </c>
       <c r="B390" t="s">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D390" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="391" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A391" s="6">
-        <v>1959</v>
-      </c>
-      <c r="B391" s="8" t="s">
-        <v>383</v>
+        <v>1218</v>
+      </c>
+      <c r="B391" t="s">
+        <v>382</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>4</v>
@@ -7068,10 +7071,10 @@
     </row>
     <row r="392" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A392" s="6">
-        <v>5625</v>
+        <v>1959</v>
       </c>
       <c r="B392" s="8" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>4</v>
@@ -7082,10 +7085,10 @@
     </row>
     <row r="393" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A393" s="6">
-        <v>1817</v>
+        <v>5625</v>
       </c>
       <c r="B393" s="8" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>4</v>
@@ -7096,10 +7099,10 @@
     </row>
     <row r="394" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A394" s="6">
-        <v>5737</v>
+        <v>1817</v>
       </c>
       <c r="B394" s="8" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>4</v>
@@ -7110,29 +7113,43 @@
     </row>
     <row r="395" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A395" s="6">
-        <v>60295</v>
+        <v>5737</v>
       </c>
       <c r="B395" s="8" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D395" s="9" t="s">
-        <v>9</v>
+      <c r="D395" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="396" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A396" s="6">
+        <v>60295</v>
+      </c>
+      <c r="B396" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="C396" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D396" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A397" s="6">
         <v>1045</v>
       </c>
-      <c r="B396" s="8" t="s">
+      <c r="B397" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="C396" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D396" s="9" t="s">
+      <c r="C397" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D397" s="9" t="s">
         <v>5</v>
       </c>
     </row>

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$342</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$343</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1192" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1195" uniqueCount="405">
   <si>
     <t>CUENTA</t>
   </si>
@@ -1234,6 +1234,9 @@
   </si>
   <si>
     <t>FERRIYAN 2</t>
+  </si>
+  <si>
+    <t>FERRETERIA BAUPI</t>
   </si>
 </sst>
 </file>
@@ -1587,7 +1590,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D397"/>
+  <dimension ref="A1:D398"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -2773,52 +2776,52 @@
     </row>
     <row r="85" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="6">
-        <v>1416</v>
+        <v>1048</v>
       </c>
       <c r="B85" t="s">
-        <v>217</v>
+        <v>404</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D85" s="1" t="s">
+      <c r="D85" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="6">
-        <v>10107</v>
+        <v>1416</v>
       </c>
       <c r="B86" t="s">
-        <v>96</v>
+        <v>217</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D86" t="s">
-        <v>9</v>
+      <c r="D86" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="6">
-        <v>10137</v>
+        <v>10107</v>
       </c>
       <c r="B87" t="s">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D87" s="1" t="s">
-        <v>8</v>
+      <c r="D87" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="6">
-        <v>10157</v>
+        <v>10137</v>
       </c>
       <c r="B88" t="s">
-        <v>183</v>
+        <v>123</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>4</v>
@@ -2829,10 +2832,10 @@
     </row>
     <row r="89" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="6">
-        <v>10158</v>
+        <v>10157</v>
       </c>
       <c r="B89" t="s">
-        <v>65</v>
+        <v>183</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>4</v>
@@ -2843,108 +2846,108 @@
     </row>
     <row r="90" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="6">
-        <v>10160</v>
+        <v>10158</v>
       </c>
       <c r="B90" t="s">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D90" s="13" t="s">
-        <v>5</v>
+      <c r="D90" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="6">
-        <v>10162</v>
+        <v>10160</v>
       </c>
       <c r="B91" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D91" s="1" t="s">
-        <v>8</v>
+      <c r="D91" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="6">
-        <v>10163</v>
+        <v>10162</v>
       </c>
       <c r="B92" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D92" s="13" t="s">
-        <v>5</v>
+      <c r="D92" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="6">
-        <v>10165</v>
+        <v>10163</v>
       </c>
       <c r="B93" t="s">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D93" s="1" t="s">
-        <v>8</v>
+      <c r="D93" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="6">
-        <v>10166</v>
-      </c>
-      <c r="B94" s="8" t="s">
-        <v>348</v>
+        <v>10165</v>
+      </c>
+      <c r="B94" t="s">
+        <v>19</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D94" s="11" t="s">
+      <c r="D94" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="6">
-        <v>10167</v>
-      </c>
-      <c r="B95" t="s">
-        <v>39</v>
+        <v>10166</v>
+      </c>
+      <c r="B95" s="8" t="s">
+        <v>348</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D95" s="13" t="s">
-        <v>5</v>
+      <c r="D95" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="6">
-        <v>10424</v>
+        <v>10167</v>
       </c>
       <c r="B96" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D96" s="17" t="s">
-        <v>9</v>
+      <c r="D96" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="6">
-        <v>10425</v>
+        <v>10424</v>
       </c>
       <c r="B97" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>4</v>
@@ -2955,24 +2958,24 @@
     </row>
     <row r="98" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="6">
-        <v>20094</v>
+        <v>10425</v>
       </c>
       <c r="B98" t="s">
-        <v>198</v>
+        <v>15</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D98" s="10" t="s">
-        <v>8</v>
+      <c r="D98" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="6">
-        <v>20095</v>
+        <v>20094</v>
       </c>
       <c r="B99" t="s">
-        <v>153</v>
+        <v>198</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>4</v>
@@ -2983,66 +2986,66 @@
     </row>
     <row r="100" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="6">
-        <v>20096</v>
+        <v>20095</v>
       </c>
       <c r="B100" t="s">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D100" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="6">
-        <v>20100</v>
+        <v>20096</v>
       </c>
       <c r="B101" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D101" s="1" t="s">
-        <v>8</v>
+      <c r="D101" s="10" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="6">
-        <v>20101</v>
+        <v>20100</v>
       </c>
       <c r="B102" t="s">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="6">
-        <v>20103</v>
+        <v>20101</v>
       </c>
       <c r="B103" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="6">
-        <v>20106</v>
+        <v>20103</v>
       </c>
       <c r="B104" t="s">
-        <v>155</v>
+        <v>81</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>4</v>
@@ -3053,80 +3056,80 @@
     </row>
     <row r="105" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="6">
-        <v>20108</v>
+        <v>20106</v>
       </c>
       <c r="B105" t="s">
-        <v>219</v>
+        <v>155</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D105" s="10" t="s">
+      <c r="D105" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="6">
-        <v>20109</v>
+        <v>20108</v>
       </c>
       <c r="B106" t="s">
-        <v>53</v>
+        <v>219</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D106" s="1" t="s">
+      <c r="D106" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="6">
-        <v>20110</v>
+        <v>20109</v>
       </c>
       <c r="B107" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D107" s="13" t="s">
-        <v>5</v>
+      <c r="D107" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="6">
-        <v>20113</v>
+        <v>20110</v>
       </c>
       <c r="B108" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D108" s="10" t="s">
-        <v>8</v>
+      <c r="D108" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="6">
-        <v>20114</v>
+        <v>20113</v>
       </c>
       <c r="B109" t="s">
-        <v>126</v>
+        <v>93</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D109" s="1" t="s">
+      <c r="D109" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="6">
-        <v>20116</v>
+        <v>20114</v>
       </c>
       <c r="B110" t="s">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>4</v>
@@ -3137,10 +3140,10 @@
     </row>
     <row r="111" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="6">
-        <v>20117</v>
+        <v>20116</v>
       </c>
       <c r="B111" t="s">
-        <v>186</v>
+        <v>73</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>4</v>
@@ -3151,10 +3154,10 @@
     </row>
     <row r="112" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="6">
-        <v>20118</v>
+        <v>20117</v>
       </c>
       <c r="B112" t="s">
-        <v>160</v>
+        <v>186</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>4</v>
@@ -3165,10 +3168,10 @@
     </row>
     <row r="113" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="6">
-        <v>20120</v>
+        <v>20118</v>
       </c>
       <c r="B113" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>4</v>
@@ -3179,10 +3182,10 @@
     </row>
     <row r="114" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="6">
-        <v>20121</v>
+        <v>20120</v>
       </c>
       <c r="B114" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>4</v>
@@ -3193,38 +3196,38 @@
     </row>
     <row r="115" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="6">
-        <v>20125</v>
+        <v>20121</v>
       </c>
       <c r="B115" t="s">
-        <v>88</v>
+        <v>159</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D115" s="10" t="s">
+      <c r="D115" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="6">
-        <v>20127</v>
+        <v>20125</v>
       </c>
       <c r="B116" t="s">
-        <v>168</v>
+        <v>88</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D116" s="1" t="s">
+      <c r="D116" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="6">
-        <v>20128</v>
+        <v>20127</v>
       </c>
       <c r="B117" t="s">
-        <v>208</v>
+        <v>168</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>4</v>
@@ -3235,52 +3238,52 @@
     </row>
     <row r="118" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="6">
-        <v>20129</v>
+        <v>20128</v>
       </c>
       <c r="B118" t="s">
-        <v>326</v>
+        <v>208</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D118" s="10" t="s">
+      <c r="D118" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="6">
-        <v>20137</v>
+        <v>20129</v>
       </c>
       <c r="B119" t="s">
-        <v>79</v>
+        <v>326</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D119" s="3" t="s">
-        <v>5</v>
+      <c r="D119" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="6">
-        <v>20138</v>
+        <v>20137</v>
       </c>
       <c r="B120" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D120" s="13" t="s">
+      <c r="D120" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="6">
-        <v>20140</v>
+        <v>20138</v>
       </c>
       <c r="B121" t="s">
-        <v>218</v>
+        <v>113</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>4</v>
@@ -3291,24 +3294,24 @@
     </row>
     <row r="122" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="6">
-        <v>20142</v>
+        <v>20140</v>
       </c>
       <c r="B122" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D122" s="1" t="s">
-        <v>8</v>
+      <c r="D122" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="6">
-        <v>20146</v>
+        <v>20142</v>
       </c>
       <c r="B123" t="s">
-        <v>148</v>
+        <v>193</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>4</v>
@@ -3319,10 +3322,10 @@
     </row>
     <row r="124" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="6">
-        <v>20148</v>
+        <v>20146</v>
       </c>
       <c r="B124" t="s">
-        <v>38</v>
+        <v>148</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>4</v>
@@ -3333,52 +3336,52 @@
     </row>
     <row r="125" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="6">
-        <v>20156</v>
+        <v>20148</v>
       </c>
       <c r="B125" t="s">
-        <v>179</v>
+        <v>38</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D125" s="10" t="s">
+      <c r="D125" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="6">
-        <v>20159</v>
+        <v>20156</v>
       </c>
       <c r="B126" t="s">
-        <v>120</v>
+        <v>179</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D126" s="17" t="s">
-        <v>9</v>
+      <c r="D126" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="6">
-        <v>20160</v>
+        <v>20159</v>
       </c>
       <c r="B127" t="s">
-        <v>224</v>
+        <v>120</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D127" s="10" t="s">
-        <v>8</v>
+      <c r="D127" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="6">
-        <v>20163</v>
+        <v>20160</v>
       </c>
       <c r="B128" t="s">
-        <v>23</v>
+        <v>224</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>4</v>
@@ -3389,52 +3392,52 @@
     </row>
     <row r="129" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="6">
-        <v>20164</v>
+        <v>20163</v>
       </c>
       <c r="B129" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D129" t="s">
-        <v>9</v>
+      <c r="D129" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="6">
-        <v>20165</v>
+        <v>20164</v>
       </c>
       <c r="B130" t="s">
-        <v>131</v>
+        <v>18</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D130" s="10" t="s">
-        <v>8</v>
+      <c r="D130" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="6">
-        <v>20166</v>
+        <v>20165</v>
       </c>
       <c r="B131" t="s">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D131" s="1" t="s">
+      <c r="D131" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="6">
-        <v>20169</v>
+        <v>20166</v>
       </c>
       <c r="B132" t="s">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>4</v>
@@ -3445,38 +3448,38 @@
     </row>
     <row r="133" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="6">
-        <v>20173</v>
+        <v>20169</v>
       </c>
       <c r="B133" t="s">
-        <v>112</v>
+        <v>151</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D133" s="10" t="s">
+      <c r="D133" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="6">
-        <v>20174</v>
+        <v>20173</v>
       </c>
       <c r="B134" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D134" s="1" t="s">
+      <c r="D134" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="6">
-        <v>20178</v>
+        <v>20174</v>
       </c>
       <c r="B135" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>4</v>
@@ -3487,80 +3490,80 @@
     </row>
     <row r="136" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="6">
-        <v>20179</v>
+        <v>20178</v>
       </c>
       <c r="B136" t="s">
-        <v>171</v>
+        <v>117</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D136" t="s">
-        <v>9</v>
+      <c r="D136" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="6">
-        <v>20180</v>
+        <v>20179</v>
       </c>
       <c r="B137" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D137" s="1" t="s">
-        <v>8</v>
+      <c r="D137" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="6">
-        <v>20183</v>
+        <v>20180</v>
       </c>
       <c r="B138" t="s">
-        <v>370</v>
+        <v>149</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D138" s="14" t="s">
-        <v>5</v>
+      <c r="D138" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="6">
-        <v>20189</v>
+        <v>20183</v>
       </c>
       <c r="B139" t="s">
-        <v>329</v>
+        <v>370</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D139" s="1" t="s">
-        <v>8</v>
+      <c r="D139" s="14" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="6">
-        <v>20200</v>
+        <v>20189</v>
       </c>
       <c r="B140" t="s">
-        <v>83</v>
+        <v>329</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D140" s="13" t="s">
-        <v>5</v>
+      <c r="D140" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="6">
-        <v>20201</v>
+        <v>20200</v>
       </c>
       <c r="B141" t="s">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>4</v>
@@ -3571,150 +3574,150 @@
     </row>
     <row r="142" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="6">
-        <v>20204</v>
+        <v>20201</v>
       </c>
       <c r="B142" t="s">
-        <v>57</v>
+        <v>145</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D142" s="10" t="s">
-        <v>8</v>
+      <c r="D142" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="6">
-        <v>20205</v>
+        <v>20204</v>
       </c>
       <c r="B143" t="s">
-        <v>206</v>
+        <v>57</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D143" s="1" t="s">
-        <v>9</v>
+      <c r="D143" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="6">
-        <v>20211</v>
+        <v>20205</v>
       </c>
       <c r="B144" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D144" s="10" t="s">
-        <v>8</v>
+      <c r="D144" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="6">
-        <v>20224</v>
+        <v>20211</v>
       </c>
       <c r="B145" t="s">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D145" s="1" t="s">
+      <c r="D145" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="6">
-        <v>20227</v>
+        <v>20224</v>
       </c>
       <c r="B146" t="s">
-        <v>192</v>
+        <v>85</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D146" s="10" t="s">
+      <c r="D146" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="6">
-        <v>20228</v>
+        <v>20227</v>
       </c>
       <c r="B147" t="s">
-        <v>91</v>
+        <v>192</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D147" s="13" t="s">
-        <v>5</v>
+      <c r="D147" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="6">
-        <v>20230</v>
+        <v>20228</v>
       </c>
       <c r="B148" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D148" s="10" t="s">
-        <v>8</v>
+      <c r="D148" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="6">
-        <v>20234</v>
+        <v>20230</v>
       </c>
       <c r="B149" t="s">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D149" s="13" t="s">
-        <v>5</v>
+      <c r="D149" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="6">
-        <v>20236</v>
+        <v>20234</v>
       </c>
       <c r="B150" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D150" s="3" t="s">
+      <c r="D150" s="13" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="6">
-        <v>20238</v>
+        <v>20236</v>
       </c>
       <c r="B151" t="s">
-        <v>139</v>
+        <v>31</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D151" s="13" t="s">
+      <c r="D151" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="6">
-        <v>20241</v>
+        <v>20238</v>
       </c>
       <c r="B152" t="s">
-        <v>22</v>
+        <v>139</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>4</v>
@@ -3725,24 +3728,24 @@
     </row>
     <row r="153" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="6">
-        <v>20242</v>
+        <v>20241</v>
       </c>
       <c r="B153" t="s">
-        <v>216</v>
+        <v>22</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D153" s="10" t="s">
-        <v>8</v>
+      <c r="D153" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="6">
-        <v>20244</v>
+        <v>20242</v>
       </c>
       <c r="B154" t="s">
-        <v>124</v>
+        <v>216</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>4</v>
@@ -3753,108 +3756,108 @@
     </row>
     <row r="155" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="6">
-        <v>20246</v>
+        <v>20244</v>
       </c>
       <c r="B155" t="s">
-        <v>14</v>
+        <v>124</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D155" s="13" t="s">
-        <v>5</v>
+      <c r="D155" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="156" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="6">
-        <v>20249</v>
+        <v>20246</v>
       </c>
       <c r="B156" t="s">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D156" s="10" t="s">
-        <v>8</v>
+      <c r="D156" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="6">
-        <v>20256</v>
+        <v>20249</v>
       </c>
       <c r="B157" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D157" s="1" t="s">
+      <c r="D157" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="6">
-        <v>20257</v>
+        <v>20256</v>
       </c>
       <c r="B158" t="s">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D158" s="17" t="s">
-        <v>9</v>
+      <c r="D158" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="159" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A159" s="6">
-        <v>20258</v>
+        <v>20257</v>
       </c>
       <c r="B159" t="s">
-        <v>199</v>
+        <v>150</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D159" s="1" t="s">
-        <v>8</v>
+      <c r="D159" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="160" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="6">
-        <v>20260</v>
+        <v>20258</v>
       </c>
       <c r="B160" t="s">
-        <v>68</v>
+        <v>199</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D160" s="13" t="s">
-        <v>5</v>
+      <c r="D160" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="161" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="6">
-        <v>20261</v>
+        <v>20260</v>
       </c>
       <c r="B161" t="s">
-        <v>207</v>
+        <v>68</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D161" s="10" t="s">
-        <v>8</v>
+      <c r="D161" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="6">
-        <v>20262</v>
+        <v>20261</v>
       </c>
       <c r="B162" t="s">
-        <v>92</v>
+        <v>207</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>4</v>
@@ -3865,206 +3868,206 @@
     </row>
     <row r="163" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="6">
-        <v>20267</v>
+        <v>20262</v>
       </c>
       <c r="B163" t="s">
-        <v>401</v>
+        <v>92</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D163" s="10" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="6">
-        <v>20268</v>
+        <v>20267</v>
       </c>
       <c r="B164" t="s">
-        <v>201</v>
+        <v>401</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D164" s="1" t="s">
-        <v>8</v>
+      <c r="D164" s="10" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="165" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="6">
-        <v>20271</v>
+        <v>20268</v>
       </c>
       <c r="B165" t="s">
-        <v>34</v>
+        <v>201</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D165" s="13" t="s">
-        <v>5</v>
+      <c r="D165" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="6">
-        <v>20272</v>
+        <v>20271</v>
       </c>
       <c r="B166" t="s">
-        <v>178</v>
+        <v>34</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D166" s="1" t="s">
-        <v>8</v>
+      <c r="D166" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="6">
-        <v>20275</v>
+        <v>20272</v>
       </c>
       <c r="B167" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D167" s="13" t="s">
-        <v>5</v>
+      <c r="D167" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="168" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="6">
-        <v>20277</v>
+        <v>20275</v>
       </c>
       <c r="B168" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D168" s="1" t="s">
-        <v>8</v>
+      <c r="D168" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="6">
-        <v>20281</v>
+        <v>20277</v>
       </c>
       <c r="B169" t="s">
-        <v>105</v>
+        <v>154</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D169" s="3" t="s">
-        <v>5</v>
+      <c r="D169" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A170" s="6">
-        <v>20282</v>
+        <v>20281</v>
       </c>
       <c r="B170" t="s">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D170" s="1" t="s">
-        <v>9</v>
+      <c r="D170" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="171" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="6">
-        <v>20284</v>
+        <v>20282</v>
       </c>
       <c r="B171" t="s">
-        <v>17</v>
+        <v>141</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D171" s="17" t="s">
+      <c r="D171" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="6">
-        <v>20285</v>
+        <v>20284</v>
       </c>
       <c r="B172" t="s">
-        <v>146</v>
+        <v>17</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D172" s="1" t="s">
-        <v>8</v>
+      <c r="D172" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="6">
-        <v>20289</v>
+        <v>20285</v>
       </c>
       <c r="B173" t="s">
-        <v>52</v>
+        <v>146</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D173" s="3" t="s">
-        <v>5</v>
+      <c r="D173" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="174" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="6">
-        <v>20290</v>
+        <v>20289</v>
       </c>
       <c r="B174" t="s">
-        <v>103</v>
+        <v>52</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D174" s="1" t="s">
-        <v>8</v>
+      <c r="D174" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="175" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="6">
-        <v>20291</v>
+        <v>20290</v>
       </c>
       <c r="B175" t="s">
-        <v>187</v>
+        <v>103</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D175" s="10" t="s">
+      <c r="D175" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="6">
-        <v>20292</v>
+        <v>20291</v>
       </c>
       <c r="B176" t="s">
-        <v>32</v>
+        <v>187</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D176" s="13" t="s">
-        <v>5</v>
+      <c r="D176" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="177" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A177" s="6">
-        <v>20293</v>
+        <v>20292</v>
       </c>
       <c r="B177" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>4</v>
@@ -4075,52 +4078,52 @@
     </row>
     <row r="178" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="6">
-        <v>20294</v>
+        <v>20293</v>
       </c>
       <c r="B178" t="s">
-        <v>202</v>
+        <v>43</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D178" s="10" t="s">
-        <v>8</v>
+      <c r="D178" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="179" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="6">
-        <v>20296</v>
+        <v>20294</v>
       </c>
       <c r="B179" t="s">
-        <v>144</v>
+        <v>202</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D179" s="13" t="s">
-        <v>5</v>
+      <c r="D179" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="6">
-        <v>20298</v>
+        <v>20296</v>
       </c>
       <c r="B180" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D180" s="1" t="s">
-        <v>8</v>
+      <c r="D180" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="6">
-        <v>20299</v>
+        <v>20298</v>
       </c>
       <c r="B181" t="s">
-        <v>58</v>
+        <v>169</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>4</v>
@@ -4131,10 +4134,10 @@
     </row>
     <row r="182" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="6">
-        <v>20301</v>
+        <v>20299</v>
       </c>
       <c r="B182" t="s">
-        <v>134</v>
+        <v>58</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>4</v>
@@ -4145,10 +4148,10 @@
     </row>
     <row r="183" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="6">
-        <v>20303</v>
+        <v>20301</v>
       </c>
       <c r="B183" t="s">
-        <v>37</v>
+        <v>134</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>4</v>
@@ -4159,24 +4162,24 @@
     </row>
     <row r="184" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="6">
-        <v>20309</v>
+        <v>20303</v>
       </c>
       <c r="B184" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D184" s="13" t="s">
-        <v>5</v>
+      <c r="D184" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="185" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="6">
-        <v>20310</v>
+        <v>20309</v>
       </c>
       <c r="B185" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>4</v>
@@ -4187,52 +4190,52 @@
     </row>
     <row r="186" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="6">
-        <v>20318</v>
+        <v>20310</v>
       </c>
       <c r="B186" t="s">
-        <v>209</v>
+        <v>59</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D186" s="1" t="s">
-        <v>8</v>
+      <c r="D186" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="187" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="6">
-        <v>20319</v>
+        <v>20318</v>
       </c>
       <c r="B187" t="s">
-        <v>101</v>
+        <v>209</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D187" s="10" t="s">
+      <c r="D187" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="188" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="6">
-        <v>20320</v>
+        <v>20319</v>
       </c>
       <c r="B188" t="s">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D188" s="1" t="s">
+      <c r="D188" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="189" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="6">
-        <v>20324</v>
+        <v>20320</v>
       </c>
       <c r="B189" t="s">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>4</v>
@@ -4243,10 +4246,10 @@
     </row>
     <row r="190" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A190" s="6">
-        <v>20331</v>
+        <v>20324</v>
       </c>
       <c r="B190" t="s">
-        <v>51</v>
+        <v>210</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>4</v>
@@ -4257,38 +4260,38 @@
     </row>
     <row r="191" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="6">
-        <v>20333</v>
+        <v>20331</v>
       </c>
       <c r="B191" t="s">
-        <v>136</v>
+        <v>51</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D191" s="13" t="s">
-        <v>5</v>
+      <c r="D191" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="192" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="6">
-        <v>20337</v>
+        <v>20333</v>
       </c>
       <c r="B192" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D192" s="1" t="s">
-        <v>8</v>
+      <c r="D192" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="193" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="6">
-        <v>20343</v>
+        <v>20337</v>
       </c>
       <c r="B193" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>4</v>
@@ -4299,10 +4302,10 @@
     </row>
     <row r="194" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="6">
-        <v>20344</v>
+        <v>20343</v>
       </c>
       <c r="B194" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>4</v>
@@ -4313,66 +4316,66 @@
     </row>
     <row r="195" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A195" s="6">
-        <v>20351</v>
+        <v>20344</v>
       </c>
       <c r="B195" t="s">
-        <v>26</v>
+        <v>127</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D195" s="13" t="s">
-        <v>5</v>
+      <c r="D195" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="196" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="6">
-        <v>20357</v>
+        <v>20351</v>
       </c>
       <c r="B196" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D196" s="1" t="s">
-        <v>8</v>
+      <c r="D196" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="197" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="6">
-        <v>20361</v>
+        <v>20357</v>
       </c>
       <c r="B197" t="s">
-        <v>164</v>
+        <v>56</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D197" s="13" t="s">
-        <v>5</v>
+      <c r="D197" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="198" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A198" s="6">
-        <v>20362</v>
+        <v>20361</v>
       </c>
       <c r="B198" t="s">
-        <v>45</v>
+        <v>164</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D198" s="10" t="s">
-        <v>8</v>
+      <c r="D198" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="199" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="6">
-        <v>20363</v>
+        <v>20362</v>
       </c>
       <c r="B199" t="s">
-        <v>213</v>
+        <v>45</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>4</v>
@@ -4383,38 +4386,38 @@
     </row>
     <row r="200" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A200" s="6">
-        <v>20364</v>
+        <v>20363</v>
       </c>
       <c r="B200" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D200" s="13" t="s">
-        <v>5</v>
+      <c r="D200" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="201" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="6">
-        <v>20366</v>
+        <v>20364</v>
       </c>
       <c r="B201" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D201" s="1" t="s">
-        <v>8</v>
+      <c r="D201" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="202" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="6">
-        <v>20367</v>
+        <v>20366</v>
       </c>
       <c r="B202" t="s">
-        <v>47</v>
+        <v>220</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>4</v>
@@ -4425,10 +4428,10 @@
     </row>
     <row r="203" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="6">
-        <v>20369</v>
+        <v>20367</v>
       </c>
       <c r="B203" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>4</v>
@@ -4439,10 +4442,10 @@
     </row>
     <row r="204" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="6">
-        <v>20371</v>
+        <v>20369</v>
       </c>
       <c r="B204" t="s">
-        <v>223</v>
+        <v>63</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>4</v>
@@ -4453,52 +4456,52 @@
     </row>
     <row r="205" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A205" s="6">
-        <v>20372</v>
+        <v>20371</v>
       </c>
       <c r="B205" t="s">
-        <v>70</v>
+        <v>223</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D205" s="10" t="s">
+      <c r="D205" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="206" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A206" s="6">
-        <v>20374</v>
+        <v>20372</v>
       </c>
       <c r="B206" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D206" s="1" t="s">
+      <c r="D206" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="207" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A207" s="6">
-        <v>20377</v>
+        <v>20374</v>
       </c>
       <c r="B207" t="s">
-        <v>225</v>
+        <v>61</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D207" s="10" t="s">
+      <c r="D207" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="208" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A208" s="6">
-        <v>20379</v>
+        <v>20377</v>
       </c>
       <c r="B208" t="s">
-        <v>49</v>
+        <v>225</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>4</v>
@@ -4509,66 +4512,66 @@
     </row>
     <row r="209" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A209" s="6">
-        <v>20380</v>
+        <v>20379</v>
       </c>
       <c r="B209" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D209" s="13" t="s">
-        <v>5</v>
+      <c r="D209" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="210" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A210" s="6">
-        <v>20381</v>
+        <v>20380</v>
       </c>
       <c r="B210" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D210" s="1" t="s">
-        <v>8</v>
+      <c r="D210" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="211" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="6">
-        <v>20384</v>
+        <v>20381</v>
       </c>
       <c r="B211" t="s">
-        <v>181</v>
+        <v>60</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D211" s="10" t="s">
+      <c r="D211" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="212" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A212" s="6">
-        <v>20385</v>
+        <v>20384</v>
       </c>
       <c r="B212" t="s">
-        <v>36</v>
+        <v>181</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D212" s="1" t="s">
+      <c r="D212" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="213" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A213" s="6">
-        <v>20386</v>
+        <v>20385</v>
       </c>
       <c r="B213" t="s">
-        <v>119</v>
+        <v>36</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>4</v>
@@ -4579,66 +4582,66 @@
     </row>
     <row r="214" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A214" s="6">
-        <v>20388</v>
+        <v>20386</v>
       </c>
       <c r="B214" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D214" s="10" t="s">
+      <c r="D214" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="215" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A215" s="6">
-        <v>20391</v>
+        <v>20388</v>
       </c>
       <c r="B215" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D215" s="1" t="s">
+      <c r="D215" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="216" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A216" s="6">
-        <v>20394</v>
+        <v>20391</v>
       </c>
       <c r="B216" t="s">
-        <v>173</v>
+        <v>106</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D216" s="10" t="s">
+      <c r="D216" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="217" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A217" s="6">
-        <v>20395</v>
+        <v>20394</v>
       </c>
       <c r="B217" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D217" s="1" t="s">
+      <c r="D217" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="218" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A218" s="6">
-        <v>20396</v>
+        <v>20395</v>
       </c>
       <c r="B218" t="s">
-        <v>330</v>
+        <v>161</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>4</v>
@@ -4649,52 +4652,52 @@
     </row>
     <row r="219" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A219" s="6">
-        <v>20397</v>
-      </c>
-      <c r="B219" s="8" t="s">
-        <v>344</v>
+        <v>20396</v>
+      </c>
+      <c r="B219" t="s">
+        <v>330</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D219" s="11" t="s">
-        <v>5</v>
+      <c r="D219" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="220" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A220" s="6">
-        <v>30101</v>
-      </c>
-      <c r="B220" t="s">
-        <v>167</v>
+        <v>20397</v>
+      </c>
+      <c r="B220" s="8" t="s">
+        <v>344</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D220" s="1" t="s">
-        <v>8</v>
+      <c r="D220" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="221" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A221" s="6">
-        <v>40124</v>
+        <v>30101</v>
       </c>
       <c r="B221" t="s">
-        <v>24</v>
+        <v>167</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D221" s="13" t="s">
-        <v>5</v>
+      <c r="D221" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="222" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A222" s="6">
-        <v>40125</v>
+        <v>40124</v>
       </c>
       <c r="B222" t="s">
-        <v>143</v>
+        <v>24</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>4</v>
@@ -4705,24 +4708,24 @@
     </row>
     <row r="223" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223" s="6">
-        <v>40127</v>
+        <v>40125</v>
       </c>
       <c r="B223" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D223" s="1" t="s">
-        <v>8</v>
+      <c r="D223" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="224" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="6">
-        <v>40129</v>
+        <v>40127</v>
       </c>
       <c r="B224" t="s">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>4</v>
@@ -4733,24 +4736,24 @@
     </row>
     <row r="225" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A225" s="6">
-        <v>40137</v>
+        <v>40129</v>
       </c>
       <c r="B225" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D225" s="10" t="s">
+      <c r="D225" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="226" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A226" s="6">
-        <v>40139</v>
+        <v>40137</v>
       </c>
       <c r="B226" t="s">
-        <v>327</v>
+        <v>121</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>4</v>
@@ -4761,66 +4764,66 @@
     </row>
     <row r="227" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A227" s="6">
-        <v>40140</v>
+        <v>40139</v>
       </c>
       <c r="B227" t="s">
-        <v>170</v>
+        <v>327</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D227" s="1" t="s">
+      <c r="D227" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="228" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A228" s="6">
-        <v>40141</v>
+        <v>40140</v>
       </c>
       <c r="B228" t="s">
-        <v>111</v>
+        <v>170</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D228" s="13" t="s">
-        <v>5</v>
+      <c r="D228" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="229" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A229" s="6">
-        <v>40143</v>
+        <v>40141</v>
       </c>
       <c r="B229" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D229" s="10" t="s">
-        <v>8</v>
+      <c r="D229" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="230" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A230" s="6">
-        <v>40144</v>
+        <v>40143</v>
       </c>
       <c r="B230" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D230" s="13" t="s">
-        <v>5</v>
+      <c r="D230" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="231" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A231" s="6">
-        <v>40145</v>
+        <v>40144</v>
       </c>
       <c r="B231" t="s">
-        <v>165</v>
+        <v>107</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>4</v>
@@ -4831,192 +4834,192 @@
     </row>
     <row r="232" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A232" s="6">
-        <v>40150</v>
+        <v>40145</v>
       </c>
       <c r="B232" t="s">
-        <v>221</v>
+        <v>165</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D232" s="10" t="s">
-        <v>8</v>
+      <c r="D232" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="233" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A233" s="6">
-        <v>40151</v>
+        <v>40150</v>
       </c>
       <c r="B233" t="s">
-        <v>54</v>
+        <v>221</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D233" s="1" t="s">
+      <c r="D233" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="234" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A234" s="6">
-        <v>50102</v>
+        <v>40151</v>
       </c>
       <c r="B234" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D234" s="13" t="s">
-        <v>5</v>
+      <c r="D234" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="235" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A235" s="6">
-        <v>50222</v>
+        <v>50102</v>
       </c>
       <c r="B235" t="s">
-        <v>215</v>
+        <v>67</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D235" s="1" t="s">
-        <v>8</v>
+      <c r="D235" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="236" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A236" s="6">
-        <v>50223</v>
+        <v>50222</v>
       </c>
       <c r="B236" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D236" s="10" t="s">
+      <c r="D236" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="237" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A237" s="6">
-        <v>50224</v>
+        <v>50223</v>
       </c>
       <c r="B237" t="s">
-        <v>42</v>
+        <v>194</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D237" s="3" t="s">
-        <v>5</v>
+      <c r="D237" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="238" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A238" s="6">
-        <v>50444</v>
+        <v>50224</v>
       </c>
       <c r="B238" t="s">
-        <v>116</v>
+        <v>42</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D238" s="1" t="s">
-        <v>8</v>
+      <c r="D238" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="239" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A239" s="6">
-        <v>50445</v>
+        <v>50444</v>
       </c>
       <c r="B239" t="s">
-        <v>354</v>
+        <v>116</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D239" s="11" t="s">
-        <v>5</v>
+      <c r="D239" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="240" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A240" s="6">
-        <v>50607</v>
+        <v>50445</v>
       </c>
       <c r="B240" t="s">
-        <v>76</v>
+        <v>354</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D240" s="13" t="s">
+      <c r="D240" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="241" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="6">
-        <v>50608</v>
+        <v>50607</v>
       </c>
       <c r="B241" t="s">
-        <v>177</v>
+        <v>76</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D241" s="1" t="s">
-        <v>8</v>
+      <c r="D241" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="242" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A242" s="6">
-        <v>50611</v>
-      </c>
-      <c r="B242" s="8" t="s">
-        <v>347</v>
+        <v>50608</v>
+      </c>
+      <c r="B242" t="s">
+        <v>177</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D242" s="14" t="s">
+      <c r="D242" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="243" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A243" s="6">
-        <v>50622</v>
-      </c>
-      <c r="B243" t="s">
-        <v>95</v>
+        <v>50611</v>
+      </c>
+      <c r="B243" s="8" t="s">
+        <v>347</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D243" s="16" t="s">
+      <c r="D243" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="244" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A244" s="6">
-        <v>50623</v>
+        <v>50622</v>
       </c>
       <c r="B244" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D244" s="10" t="s">
+      <c r="D244" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="245" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A245" s="6">
-        <v>50625</v>
+        <v>50623</v>
       </c>
       <c r="B245" t="s">
-        <v>204</v>
+        <v>110</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>4</v>
@@ -5027,94 +5030,94 @@
     </row>
     <row r="246" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A246" s="6">
-        <v>50629</v>
+        <v>50625</v>
       </c>
       <c r="B246" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D246" s="1" t="s">
+      <c r="D246" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="247" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A247" s="6">
-        <v>50630</v>
+        <v>50629</v>
       </c>
       <c r="B247" t="s">
-        <v>360</v>
+        <v>188</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D247" s="14" t="s">
+      <c r="D247" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="248" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A248" s="6">
-        <v>50803</v>
+        <v>50630</v>
       </c>
       <c r="B248" t="s">
-        <v>82</v>
+        <v>360</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D248" s="1" t="s">
+      <c r="D248" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="249" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A249" s="6">
-        <v>50805</v>
+        <v>50803</v>
       </c>
       <c r="B249" t="s">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D249" s="10" t="s">
+      <c r="D249" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="250" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A250" s="6">
-        <v>50806</v>
+        <v>50805</v>
       </c>
       <c r="B250" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D250" s="1" t="s">
+      <c r="D250" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="251" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A251" s="6">
-        <v>50808</v>
+        <v>50806</v>
       </c>
       <c r="B251" t="s">
-        <v>16</v>
+        <v>156</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D251" s="13" t="s">
-        <v>5</v>
+      <c r="D251" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="252" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A252" s="6">
-        <v>50809</v>
+        <v>50808</v>
       </c>
       <c r="B252" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>4</v>
@@ -5125,24 +5128,24 @@
     </row>
     <row r="253" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A253" s="6">
-        <v>50810</v>
+        <v>50809</v>
       </c>
       <c r="B253" t="s">
-        <v>175</v>
+        <v>98</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D253" s="1" t="s">
-        <v>8</v>
+      <c r="D253" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="254" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="6">
-        <v>50812</v>
+        <v>50810</v>
       </c>
       <c r="B254" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>4</v>
@@ -5153,80 +5156,80 @@
     </row>
     <row r="255" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A255" s="6">
-        <v>50813</v>
+        <v>50812</v>
       </c>
       <c r="B255" t="s">
-        <v>71</v>
+        <v>184</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D255" s="17" t="s">
-        <v>9</v>
+      <c r="D255" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="256" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A256" s="6">
-        <v>50815</v>
+        <v>50813</v>
       </c>
       <c r="B256" t="s">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D256" s="10" t="s">
-        <v>8</v>
+      <c r="D256" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="257" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A257" s="6">
-        <v>50816</v>
+        <v>50815</v>
       </c>
       <c r="B257" t="s">
-        <v>205</v>
+        <v>114</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D257" s="1" t="s">
+      <c r="D257" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="258" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A258" s="6">
-        <v>50818</v>
+        <v>50816</v>
       </c>
       <c r="B258" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D258" s="13" t="s">
-        <v>5</v>
+      <c r="D258" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="259" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A259" s="6">
-        <v>50819</v>
+        <v>50818</v>
       </c>
       <c r="B259" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D259" s="10" t="s">
-        <v>8</v>
+      <c r="D259" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="260" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A260" s="6">
-        <v>50820</v>
+        <v>50819</v>
       </c>
       <c r="B260" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>4</v>
@@ -5237,66 +5240,66 @@
     </row>
     <row r="261" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A261" s="6">
-        <v>50821</v>
+        <v>50820</v>
       </c>
       <c r="B261" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D261" s="1" t="s">
+      <c r="D261" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="262" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A262" s="6">
-        <v>50823</v>
+        <v>50821</v>
       </c>
       <c r="B262" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D262" s="17" t="s">
-        <v>9</v>
+      <c r="D262" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="263" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A263" s="6">
-        <v>50824</v>
+        <v>50823</v>
       </c>
       <c r="B263" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D263" s="13" t="s">
-        <v>5</v>
+      <c r="D263" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="264" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A264" s="6">
-        <v>50825</v>
+        <v>50824</v>
       </c>
       <c r="B264" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D264" s="10" t="s">
-        <v>8</v>
+      <c r="D264" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="265" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A265" s="6">
-        <v>50826</v>
+        <v>50825</v>
       </c>
       <c r="B265" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>4</v>
@@ -5307,24 +5310,24 @@
     </row>
     <row r="266" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A266" s="6">
-        <v>50827</v>
+        <v>50826</v>
       </c>
       <c r="B266" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D266" s="1" t="s">
+      <c r="D266" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="267" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A267" s="6">
-        <v>50829</v>
+        <v>50827</v>
       </c>
       <c r="B267" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>4</v>
@@ -5335,122 +5338,122 @@
     </row>
     <row r="268" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A268" s="6">
-        <v>50830</v>
+        <v>50829</v>
       </c>
       <c r="B268" t="s">
-        <v>366</v>
+        <v>236</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D268" s="11" t="s">
+      <c r="D268" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="269" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A269" s="6">
-        <v>50831</v>
+        <v>50830</v>
       </c>
       <c r="B269" t="s">
-        <v>351</v>
+        <v>366</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D269" s="11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="270" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A270" s="6">
-        <v>50832</v>
-      </c>
-      <c r="B270" s="8" t="s">
-        <v>349</v>
+        <v>50831</v>
+      </c>
+      <c r="B270" t="s">
+        <v>351</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D270" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="271" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A271" s="6">
-        <v>50833</v>
+        <v>50832</v>
       </c>
       <c r="B271" s="8" t="s">
-        <v>397</v>
+        <v>349</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D271" s="11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="272" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A272" s="6">
-        <v>50230</v>
+        <v>50833</v>
       </c>
       <c r="B272" s="8" t="s">
-        <v>379</v>
+        <v>397</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D272" s="11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="273" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A273" s="6">
-        <v>60103</v>
-      </c>
-      <c r="B273" t="s">
-        <v>237</v>
+        <v>50230</v>
+      </c>
+      <c r="B273" s="8" t="s">
+        <v>379</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D273" s="13" t="s">
+      <c r="D273" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="274" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A274" s="6">
-        <v>60109</v>
+        <v>60103</v>
       </c>
       <c r="B274" t="s">
-        <v>328</v>
+        <v>237</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D274" s="11" t="s">
-        <v>9</v>
+      <c r="D274" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="275" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A275" s="6">
-        <v>60124</v>
+        <v>60109</v>
       </c>
       <c r="B275" t="s">
-        <v>238</v>
+        <v>328</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D275" s="13" t="s">
-        <v>5</v>
+      <c r="D275" s="11" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="276" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A276" s="6">
-        <v>60125</v>
+        <v>60124</v>
       </c>
       <c r="B276" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>4</v>
@@ -5461,80 +5464,80 @@
     </row>
     <row r="277" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A277" s="6">
-        <v>60126</v>
+        <v>60125</v>
       </c>
       <c r="B277" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D277" s="10" t="s">
-        <v>8</v>
+      <c r="D277" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="278" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A278" s="6">
-        <v>60128</v>
+        <v>60126</v>
       </c>
       <c r="B278" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D278" s="3" t="s">
-        <v>5</v>
+      <c r="D278" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="279" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A279" s="6">
-        <v>60130</v>
+        <v>60128</v>
       </c>
       <c r="B279" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D279" s="1" t="s">
-        <v>8</v>
+      <c r="D279" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="280" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A280" s="6">
-        <v>60133</v>
+        <v>60130</v>
       </c>
       <c r="B280" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D280" s="13" t="s">
-        <v>5</v>
+      <c r="D280" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="281" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A281" s="6">
-        <v>60134</v>
+        <v>60133</v>
       </c>
       <c r="B281" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D281" s="1" t="s">
-        <v>8</v>
+      <c r="D281" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="282" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A282" s="6">
-        <v>60137</v>
+        <v>60134</v>
       </c>
       <c r="B282" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>4</v>
@@ -5545,10 +5548,10 @@
     </row>
     <row r="283" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A283" s="6">
-        <v>60139</v>
+        <v>60137</v>
       </c>
       <c r="B283" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>4</v>
@@ -5559,10 +5562,10 @@
     </row>
     <row r="284" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A284" s="6">
-        <v>60142</v>
+        <v>60139</v>
       </c>
       <c r="B284" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>4</v>
@@ -5573,10 +5576,10 @@
     </row>
     <row r="285" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A285" s="6">
-        <v>60148</v>
+        <v>60142</v>
       </c>
       <c r="B285" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>4</v>
@@ -5587,10 +5590,10 @@
     </row>
     <row r="286" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A286" s="6">
-        <v>60149</v>
+        <v>60148</v>
       </c>
       <c r="B286" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>4</v>
@@ -5601,66 +5604,66 @@
     </row>
     <row r="287" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A287" s="6">
-        <v>60150</v>
+        <v>60149</v>
       </c>
       <c r="B287" t="s">
-        <v>332</v>
+        <v>249</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D287" s="13" t="s">
-        <v>5</v>
+      <c r="D287" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="288" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A288" s="6">
-        <v>60158</v>
+        <v>60150</v>
       </c>
       <c r="B288" t="s">
-        <v>250</v>
+        <v>332</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D288" s="10" t="s">
-        <v>8</v>
+      <c r="D288" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="289" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A289" s="6">
-        <v>60159</v>
+        <v>60158</v>
       </c>
       <c r="B289" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D289" s="1" t="s">
+      <c r="D289" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="290" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A290" s="6">
-        <v>60162</v>
+        <v>60159</v>
       </c>
       <c r="B290" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D290" s="13" t="s">
-        <v>5</v>
+      <c r="D290" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="291" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A291" s="6">
-        <v>60163</v>
+        <v>60162</v>
       </c>
       <c r="B291" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>4</v>
@@ -5671,24 +5674,24 @@
     </row>
     <row r="292" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A292" s="6">
-        <v>60165</v>
+        <v>60163</v>
       </c>
       <c r="B292" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D292" s="1" t="s">
-        <v>8</v>
+      <c r="D292" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="293" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A293" s="6">
-        <v>60169</v>
+        <v>60165</v>
       </c>
       <c r="B293" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>4</v>
@@ -5699,52 +5702,52 @@
     </row>
     <row r="294" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A294" s="6">
-        <v>60170</v>
-      </c>
-      <c r="B294" s="8" t="s">
-        <v>337</v>
+        <v>60169</v>
+      </c>
+      <c r="B294" t="s">
+        <v>255</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D294" s="11" t="s">
+      <c r="D294" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="295" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A295" s="6">
-        <v>60172</v>
-      </c>
-      <c r="B295" t="s">
-        <v>256</v>
+        <v>60170</v>
+      </c>
+      <c r="B295" s="8" t="s">
+        <v>337</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D295" s="1" t="s">
+      <c r="D295" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="296" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A296" s="6">
-        <v>60174</v>
+        <v>60172</v>
       </c>
       <c r="B296" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D296" s="13" t="s">
-        <v>5</v>
+      <c r="D296" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="297" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A297" s="6">
-        <v>60176</v>
+        <v>60174</v>
       </c>
       <c r="B297" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>4</v>
@@ -5755,52 +5758,52 @@
     </row>
     <row r="298" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A298" s="6">
-        <v>60178</v>
+        <v>60176</v>
       </c>
       <c r="B298" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D298" s="1" t="s">
-        <v>8</v>
+      <c r="D298" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="299" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A299" s="6">
-        <v>60180</v>
+        <v>60178</v>
       </c>
       <c r="B299" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D299" s="10" t="s">
+      <c r="D299" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="300" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A300" s="6">
-        <v>60184</v>
+        <v>60180</v>
       </c>
       <c r="B300" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D300" s="1" t="s">
+      <c r="D300" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="301" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A301" s="6">
-        <v>60190</v>
+        <v>60184</v>
       </c>
       <c r="B301" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>4</v>
@@ -5811,24 +5814,24 @@
     </row>
     <row r="302" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A302" s="6">
-        <v>60191</v>
+        <v>60190</v>
       </c>
       <c r="B302" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D302" s="10" t="s">
+      <c r="D302" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="303" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A303" s="6">
-        <v>60192</v>
+        <v>60191</v>
       </c>
       <c r="B303" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>4</v>
@@ -5839,10 +5842,10 @@
     </row>
     <row r="304" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A304" s="6">
-        <v>60195</v>
+        <v>60192</v>
       </c>
       <c r="B304" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>4</v>
@@ -5853,10 +5856,10 @@
     </row>
     <row r="305" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A305" s="6">
-        <v>60196</v>
+        <v>60195</v>
       </c>
       <c r="B305" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>4</v>
@@ -5867,10 +5870,10 @@
     </row>
     <row r="306" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A306" s="6">
-        <v>60198</v>
+        <v>60196</v>
       </c>
       <c r="B306" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>4</v>
@@ -5881,52 +5884,52 @@
     </row>
     <row r="307" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A307" s="6">
-        <v>60201</v>
+        <v>60198</v>
       </c>
       <c r="B307" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D307" t="s">
-        <v>9</v>
+      <c r="D307" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="308" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A308" s="6">
-        <v>60202</v>
+        <v>60201</v>
       </c>
       <c r="B308" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D308" s="13" t="s">
-        <v>5</v>
+      <c r="D308" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="309" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A309" s="6">
-        <v>60204</v>
+        <v>60202</v>
       </c>
       <c r="B309" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D309" s="1" t="s">
-        <v>8</v>
+      <c r="D309" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="310" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A310" s="6">
-        <v>60205</v>
+        <v>60204</v>
       </c>
       <c r="B310" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>4</v>
@@ -5937,10 +5940,10 @@
     </row>
     <row r="311" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A311" s="6">
-        <v>60206</v>
+        <v>60205</v>
       </c>
       <c r="B311" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>4</v>
@@ -5951,220 +5954,220 @@
     </row>
     <row r="312" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A312" s="6">
-        <v>60209</v>
+        <v>60206</v>
       </c>
       <c r="B312" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D312" s="10" t="s">
+      <c r="D312" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="313" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A313" s="6">
-        <v>60211</v>
+        <v>60209</v>
       </c>
       <c r="B313" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D313" s="1" t="s">
+      <c r="D313" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="314" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A314" s="6">
-        <v>60215</v>
+        <v>60211</v>
       </c>
       <c r="B314" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D314" s="10" t="s">
+      <c r="D314" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="315" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A315" s="6">
-        <v>60216</v>
+        <v>60215</v>
       </c>
       <c r="B315" t="s">
-        <v>381</v>
+        <v>275</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D315" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="316" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A316" s="6">
-        <v>60217</v>
+        <v>60216</v>
       </c>
       <c r="B316" t="s">
-        <v>276</v>
+        <v>381</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D316" s="10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="317" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A317" s="6">
-        <v>60219</v>
+        <v>60217</v>
       </c>
       <c r="B317" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D317" s="1" t="s">
+      <c r="D317" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="318" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A318" s="6">
-        <v>60222</v>
+        <v>60219</v>
       </c>
       <c r="B318" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D318" s="10" t="s">
+      <c r="D318" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="319" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A319" s="6">
-        <v>60225</v>
+        <v>60222</v>
       </c>
       <c r="B319" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D319" s="17" t="s">
-        <v>9</v>
+      <c r="D319" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="320" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A320" s="6">
-        <v>60230</v>
+        <v>60225</v>
       </c>
       <c r="B320" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D320" s="10" t="s">
-        <v>8</v>
+      <c r="D320" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="321" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A321" s="6">
-        <v>60241</v>
-      </c>
-      <c r="B321" s="8" t="s">
-        <v>338</v>
+        <v>60230</v>
+      </c>
+      <c r="B321" t="s">
+        <v>280</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D321" s="7" t="s">
-        <v>9</v>
+      <c r="D321" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="322" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A322" s="6">
-        <v>60242</v>
+        <v>60241</v>
       </c>
       <c r="B322" s="8" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D322" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="323" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A323" s="6">
-        <v>60243</v>
+        <v>60242</v>
       </c>
       <c r="B323" s="8" t="s">
-        <v>395</v>
+        <v>341</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D323" s="7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="324" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A324" s="6">
-        <v>60245</v>
+        <v>60243</v>
       </c>
       <c r="B324" s="8" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D324" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="325" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A325" s="6">
-        <v>60250</v>
+        <v>60245</v>
       </c>
       <c r="B325" s="8" t="s">
-        <v>339</v>
+        <v>387</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D325" s="11" t="s">
-        <v>8</v>
+      <c r="D325" s="7" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="326" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A326" s="6">
-        <v>60253</v>
-      </c>
-      <c r="B326" t="s">
-        <v>281</v>
+        <v>60250</v>
+      </c>
+      <c r="B326" s="8" t="s">
+        <v>339</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D326" s="1" t="s">
+      <c r="D326" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="327" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A327" s="6">
-        <v>60254</v>
+        <v>60253</v>
       </c>
       <c r="B327" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>4</v>
@@ -6175,10 +6178,10 @@
     </row>
     <row r="328" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A328" s="6">
-        <v>60257</v>
+        <v>60254</v>
       </c>
       <c r="B328" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>4</v>
@@ -6189,10 +6192,10 @@
     </row>
     <row r="329" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A329" s="6">
-        <v>60258</v>
+        <v>60257</v>
       </c>
       <c r="B329" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>4</v>
@@ -6203,66 +6206,66 @@
     </row>
     <row r="330" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A330" s="6">
-        <v>60266</v>
-      </c>
-      <c r="B330" s="8" t="s">
-        <v>343</v>
+        <v>60258</v>
+      </c>
+      <c r="B330" t="s">
+        <v>284</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D330" s="11" t="s">
+      <c r="D330" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="331" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A331" s="6">
-        <v>60269</v>
-      </c>
-      <c r="B331" t="s">
-        <v>285</v>
+        <v>60266</v>
+      </c>
+      <c r="B331" s="8" t="s">
+        <v>343</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D331" s="10" t="s">
+      <c r="D331" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="332" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A332" s="6">
-        <v>60270</v>
+        <v>60269</v>
       </c>
       <c r="B332" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D332" s="1" t="s">
-        <v>9</v>
+      <c r="D332" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="333" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A333" s="6">
-        <v>60272</v>
+        <v>60270</v>
       </c>
       <c r="B333" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="334" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A334" s="6">
-        <v>60274</v>
+        <v>60272</v>
       </c>
       <c r="B334" t="s">
-        <v>380</v>
+        <v>287</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>4</v>
@@ -6273,10 +6276,10 @@
     </row>
     <row r="335" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A335" s="6">
-        <v>60275</v>
+        <v>60274</v>
       </c>
       <c r="B335" t="s">
-        <v>288</v>
+        <v>380</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>4</v>
@@ -6287,10 +6290,10 @@
     </row>
     <row r="336" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A336" s="6">
-        <v>60276</v>
+        <v>60275</v>
       </c>
       <c r="B336" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>4</v>
@@ -6301,108 +6304,108 @@
     </row>
     <row r="337" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A337" s="6">
-        <v>60278</v>
+        <v>60276</v>
       </c>
       <c r="B337" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D337" s="13" t="s">
+      <c r="D337" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="338" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A338" s="6">
-        <v>60279</v>
+        <v>60278</v>
       </c>
       <c r="B338" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D338" s="1" t="s">
+      <c r="D338" s="13" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="339" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A339" s="6">
-        <v>60280</v>
+        <v>60279</v>
       </c>
       <c r="B339" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="340" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A340" s="6">
-        <v>60281</v>
-      </c>
-      <c r="B340" s="8" t="s">
-        <v>336</v>
+        <v>60280</v>
+      </c>
+      <c r="B340" t="s">
+        <v>292</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D340" s="11" t="s">
-        <v>9</v>
+      <c r="D340" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="341" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A341" s="6">
-        <v>60282</v>
+        <v>60281</v>
       </c>
       <c r="B341" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D341" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="342" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A342" s="6">
-        <v>60283</v>
-      </c>
-      <c r="B342" t="s">
-        <v>378</v>
+        <v>60282</v>
+      </c>
+      <c r="B342" s="8" t="s">
+        <v>340</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D342" s="1" t="s">
-        <v>8</v>
+      <c r="D342" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="343" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A343" s="6">
-        <v>60284</v>
-      </c>
-      <c r="B343" s="8" t="s">
-        <v>335</v>
+        <v>60283</v>
+      </c>
+      <c r="B343" t="s">
+        <v>378</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D343" s="9" t="s">
-        <v>5</v>
+      <c r="D343" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="344" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A344" s="6">
-        <v>60285</v>
+        <v>60284</v>
       </c>
       <c r="B344" s="8" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>4</v>
@@ -6413,10 +6416,10 @@
     </row>
     <row r="345" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A345" s="6">
-        <v>60286</v>
+        <v>60285</v>
       </c>
       <c r="B345" s="8" t="s">
-        <v>334</v>
+        <v>350</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>4</v>
@@ -6427,52 +6430,52 @@
     </row>
     <row r="346" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A346" s="6">
-        <v>60287</v>
-      </c>
-      <c r="B346" t="s">
-        <v>377</v>
+        <v>60286</v>
+      </c>
+      <c r="B346" s="8" t="s">
+        <v>334</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D346" s="12" t="s">
+      <c r="D346" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="347" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A347" s="6">
-        <v>60289</v>
+        <v>60287</v>
       </c>
       <c r="B347" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D347" s="12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="348" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A348" s="6">
-        <v>60290</v>
+        <v>60289</v>
       </c>
       <c r="B348" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D348" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="349" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A349" s="6">
-        <v>60291</v>
+        <v>60290</v>
       </c>
       <c r="B349" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>4</v>
@@ -6483,24 +6486,24 @@
     </row>
     <row r="350" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A350" s="6">
-        <v>60292</v>
-      </c>
-      <c r="B350" s="18" t="s">
-        <v>400</v>
+        <v>60291</v>
+      </c>
+      <c r="B350" t="s">
+        <v>376</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D350" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="351" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A351" s="6">
-        <v>60296</v>
-      </c>
-      <c r="B351" t="s">
-        <v>391</v>
+        <v>60292</v>
+      </c>
+      <c r="B351" s="18" t="s">
+        <v>400</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>4</v>
@@ -6511,24 +6514,24 @@
     </row>
     <row r="352" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A352" s="6">
-        <v>60297</v>
+        <v>60296</v>
       </c>
       <c r="B352" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D352" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="353" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A353" s="6">
-        <v>60299</v>
+        <v>60297</v>
       </c>
       <c r="B353" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>4</v>
@@ -6539,52 +6542,52 @@
     </row>
     <row r="354" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A354" s="6">
-        <v>61001</v>
+        <v>60299</v>
       </c>
       <c r="B354" t="s">
-        <v>403</v>
+        <v>388</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D354" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="355" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A355" s="6">
-        <v>61004</v>
+        <v>61001</v>
       </c>
       <c r="B355" t="s">
-        <v>293</v>
+        <v>403</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D355" s="15" t="s">
-        <v>5</v>
+      <c r="D355" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="356" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A356" s="6">
-        <v>61009</v>
+        <v>61004</v>
       </c>
       <c r="B356" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D356" s="12" t="s">
-        <v>8</v>
+      <c r="D356" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="357" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A357" s="6">
-        <v>61012</v>
+        <v>61009</v>
       </c>
       <c r="B357" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>4</v>
@@ -6595,10 +6598,10 @@
     </row>
     <row r="358" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A358" s="6">
-        <v>61018</v>
+        <v>61012</v>
       </c>
       <c r="B358" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>4</v>
@@ -6609,10 +6612,10 @@
     </row>
     <row r="359" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A359" s="6">
-        <v>61102</v>
+        <v>61018</v>
       </c>
       <c r="B359" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>4</v>
@@ -6623,52 +6626,52 @@
     </row>
     <row r="360" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A360" s="6">
-        <v>61205</v>
+        <v>61102</v>
       </c>
       <c r="B360" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D360" s="15" t="s">
-        <v>5</v>
+      <c r="D360" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="361" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A361" s="6">
-        <v>70100</v>
+        <v>61205</v>
       </c>
       <c r="B361" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D361" s="12" t="s">
-        <v>8</v>
+      <c r="D361" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="362" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A362" s="6">
-        <v>70101</v>
+        <v>70100</v>
       </c>
       <c r="B362" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D362" s="15" t="s">
-        <v>5</v>
+      <c r="D362" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="363" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A363" s="6">
-        <v>70102</v>
+        <v>70101</v>
       </c>
       <c r="B363" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>4</v>
@@ -6679,80 +6682,80 @@
     </row>
     <row r="364" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A364" s="6">
-        <v>70103</v>
+        <v>70102</v>
       </c>
       <c r="B364" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D364" s="12" t="s">
-        <v>8</v>
+      <c r="D364" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="365" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A365" s="6">
-        <v>70106</v>
+        <v>70103</v>
       </c>
       <c r="B365" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D365" s="15" t="s">
-        <v>5</v>
+      <c r="D365" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="366" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A366" s="6">
-        <v>70109</v>
+        <v>70106</v>
       </c>
       <c r="B366" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D366" s="12" t="s">
-        <v>8</v>
+      <c r="D366" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="367" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A367" s="6">
-        <v>70113</v>
+        <v>70109</v>
       </c>
       <c r="B367" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D367" s="15" t="s">
-        <v>5</v>
+      <c r="D367" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="368" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A368" s="6">
-        <v>70114</v>
+        <v>70113</v>
       </c>
       <c r="B368" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D368" s="9" t="s">
-        <v>9</v>
+      <c r="D368" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="369" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A369" s="6">
-        <v>70115</v>
+        <v>70114</v>
       </c>
       <c r="B369" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>4</v>
@@ -6763,24 +6766,24 @@
     </row>
     <row r="370" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A370" s="6">
-        <v>70638</v>
+        <v>70115</v>
       </c>
       <c r="B370" t="s">
-        <v>306</v>
+        <v>331</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D370" s="12" t="s">
-        <v>8</v>
+      <c r="D370" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="371" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A371" s="6">
-        <v>70639</v>
+        <v>70638</v>
       </c>
       <c r="B371" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>4</v>
@@ -6791,10 +6794,10 @@
     </row>
     <row r="372" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A372" s="6">
-        <v>70640</v>
+        <v>70639</v>
       </c>
       <c r="B372" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>4</v>
@@ -6805,10 +6808,10 @@
     </row>
     <row r="373" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A373" s="6">
-        <v>70642</v>
+        <v>70640</v>
       </c>
       <c r="B373" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>4</v>
@@ -6819,10 +6822,10 @@
     </row>
     <row r="374" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A374" s="6">
-        <v>90504</v>
+        <v>70642</v>
       </c>
       <c r="B374" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>4</v>
@@ -6833,10 +6836,10 @@
     </row>
     <row r="375" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A375" s="6">
-        <v>90509</v>
+        <v>90504</v>
       </c>
       <c r="B375" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>4</v>
@@ -6847,52 +6850,52 @@
     </row>
     <row r="376" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A376" s="6">
-        <v>90602</v>
+        <v>90509</v>
       </c>
       <c r="B376" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D376" s="15" t="s">
-        <v>5</v>
+      <c r="D376" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="377" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A377" s="6">
-        <v>90621</v>
+        <v>90602</v>
       </c>
       <c r="B377" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D377" s="12" t="s">
-        <v>8</v>
+      <c r="D377" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="378" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A378" s="6">
-        <v>90622</v>
+        <v>90621</v>
       </c>
       <c r="B378" t="s">
-        <v>333</v>
+        <v>313</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D378" s="9" t="s">
-        <v>5</v>
+      <c r="D378" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="379" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A379" s="6">
-        <v>90631</v>
-      </c>
-      <c r="B379" s="8" t="s">
-        <v>342</v>
+        <v>90622</v>
+      </c>
+      <c r="B379" t="s">
+        <v>333</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>4</v>
@@ -6903,24 +6906,24 @@
     </row>
     <row r="380" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A380" s="6">
-        <v>90658</v>
-      </c>
-      <c r="B380" t="s">
-        <v>314</v>
+        <v>90631</v>
+      </c>
+      <c r="B380" s="8" t="s">
+        <v>342</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D380" s="12" t="s">
-        <v>8</v>
+      <c r="D380" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="381" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A381" s="6">
-        <v>90660</v>
+        <v>90658</v>
       </c>
       <c r="B381" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>4</v>
@@ -6931,10 +6934,10 @@
     </row>
     <row r="382" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A382" s="6">
-        <v>90668</v>
+        <v>90660</v>
       </c>
       <c r="B382" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>4</v>
@@ -6945,10 +6948,10 @@
     </row>
     <row r="383" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A383" s="6">
-        <v>90671</v>
+        <v>90668</v>
       </c>
       <c r="B383" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>4</v>
@@ -6959,10 +6962,10 @@
     </row>
     <row r="384" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A384" s="6">
-        <v>90679</v>
+        <v>90671</v>
       </c>
       <c r="B384" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>4</v>
@@ -6973,10 +6976,10 @@
     </row>
     <row r="385" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A385" s="6">
-        <v>90683</v>
+        <v>90679</v>
       </c>
       <c r="B385" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>4</v>
@@ -6987,10 +6990,10 @@
     </row>
     <row r="386" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A386" s="6">
-        <v>90705</v>
+        <v>90683</v>
       </c>
       <c r="B386" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>4</v>
@@ -7001,10 +7004,10 @@
     </row>
     <row r="387" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A387" s="6">
-        <v>90706</v>
+        <v>90705</v>
       </c>
       <c r="B387" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>4</v>
@@ -7015,10 +7018,10 @@
     </row>
     <row r="388" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A388" s="6">
-        <v>90708</v>
+        <v>90706</v>
       </c>
       <c r="B388" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>4</v>
@@ -7029,10 +7032,10 @@
     </row>
     <row r="389" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A389" s="6">
-        <v>90709</v>
+        <v>90708</v>
       </c>
       <c r="B389" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>4</v>
@@ -7043,38 +7046,38 @@
     </row>
     <row r="390" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A390" s="6">
-        <v>90713</v>
+        <v>90709</v>
       </c>
       <c r="B390" t="s">
-        <v>402</v>
+        <v>323</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D390" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="391" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A391" s="6">
-        <v>1218</v>
+        <v>90713</v>
       </c>
       <c r="B391" t="s">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D391" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="392" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A392" s="6">
-        <v>1959</v>
-      </c>
-      <c r="B392" s="8" t="s">
-        <v>383</v>
+        <v>1218</v>
+      </c>
+      <c r="B392" t="s">
+        <v>382</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>4</v>
@@ -7085,10 +7088,10 @@
     </row>
     <row r="393" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A393" s="6">
-        <v>5625</v>
+        <v>1959</v>
       </c>
       <c r="B393" s="8" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>4</v>
@@ -7099,10 +7102,10 @@
     </row>
     <row r="394" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A394" s="6">
-        <v>1817</v>
+        <v>5625</v>
       </c>
       <c r="B394" s="8" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>4</v>
@@ -7113,10 +7116,10 @@
     </row>
     <row r="395" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A395" s="6">
-        <v>5737</v>
+        <v>1817</v>
       </c>
       <c r="B395" s="8" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>4</v>
@@ -7127,34 +7130,48 @@
     </row>
     <row r="396" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A396" s="6">
-        <v>60295</v>
+        <v>5737</v>
       </c>
       <c r="B396" s="8" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D396" s="9" t="s">
-        <v>9</v>
+      <c r="D396" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="397" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A397" s="6">
+        <v>60295</v>
+      </c>
+      <c r="B397" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="C397" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D397" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A398" s="6">
         <v>1045</v>
       </c>
-      <c r="B397" s="8" t="s">
+      <c r="B398" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="C397" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D397" s="9" t="s">
+      <c r="C398" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D398" s="9" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D342"/>
+  <autoFilter ref="A1:D343"/>
   <sortState ref="A2:D374">
     <sortCondition ref="A277"/>
   </sortState>

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$343</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$344</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1195" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1198" uniqueCount="406">
   <si>
     <t>CUENTA</t>
   </si>
@@ -1237,6 +1237,9 @@
   </si>
   <si>
     <t>FERRETERIA BAUPI</t>
+  </si>
+  <si>
+    <t>ATR FERRETERIA</t>
   </si>
 </sst>
 </file>
@@ -1319,7 +1322,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1361,6 +1364,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1590,7 +1594,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D398"/>
+  <dimension ref="A1:D399"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -4848,192 +4852,192 @@
     </row>
     <row r="233" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A233" s="6">
-        <v>40150</v>
+        <v>40147</v>
       </c>
       <c r="B233" t="s">
-        <v>221</v>
+        <v>405</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D233" s="10" t="s">
+      <c r="D233" s="19" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="234" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A234" s="6">
-        <v>40151</v>
+        <v>40150</v>
       </c>
       <c r="B234" t="s">
-        <v>54</v>
+        <v>221</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D234" s="1" t="s">
+      <c r="D234" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="235" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A235" s="6">
-        <v>50102</v>
+        <v>40151</v>
       </c>
       <c r="B235" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D235" s="13" t="s">
-        <v>5</v>
+      <c r="D235" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="236" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A236" s="6">
-        <v>50222</v>
+        <v>50102</v>
       </c>
       <c r="B236" t="s">
-        <v>215</v>
+        <v>67</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D236" s="1" t="s">
-        <v>8</v>
+      <c r="D236" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="237" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A237" s="6">
-        <v>50223</v>
+        <v>50222</v>
       </c>
       <c r="B237" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D237" s="10" t="s">
+      <c r="D237" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="238" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A238" s="6">
-        <v>50224</v>
+        <v>50223</v>
       </c>
       <c r="B238" t="s">
-        <v>42</v>
+        <v>194</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D238" s="3" t="s">
-        <v>5</v>
+      <c r="D238" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="239" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A239" s="6">
-        <v>50444</v>
+        <v>50224</v>
       </c>
       <c r="B239" t="s">
-        <v>116</v>
+        <v>42</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D239" s="1" t="s">
-        <v>8</v>
+      <c r="D239" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="240" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A240" s="6">
-        <v>50445</v>
+        <v>50444</v>
       </c>
       <c r="B240" t="s">
-        <v>354</v>
+        <v>116</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D240" s="11" t="s">
-        <v>5</v>
+      <c r="D240" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="241" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="6">
-        <v>50607</v>
+        <v>50445</v>
       </c>
       <c r="B241" t="s">
-        <v>76</v>
+        <v>354</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D241" s="13" t="s">
+      <c r="D241" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="242" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A242" s="6">
-        <v>50608</v>
+        <v>50607</v>
       </c>
       <c r="B242" t="s">
-        <v>177</v>
+        <v>76</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D242" s="1" t="s">
-        <v>8</v>
+      <c r="D242" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="243" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A243" s="6">
-        <v>50611</v>
-      </c>
-      <c r="B243" s="8" t="s">
-        <v>347</v>
+        <v>50608</v>
+      </c>
+      <c r="B243" t="s">
+        <v>177</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D243" s="14" t="s">
+      <c r="D243" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="244" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A244" s="6">
-        <v>50622</v>
-      </c>
-      <c r="B244" t="s">
-        <v>95</v>
+        <v>50611</v>
+      </c>
+      <c r="B244" s="8" t="s">
+        <v>347</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D244" s="16" t="s">
+      <c r="D244" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="245" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A245" s="6">
-        <v>50623</v>
+        <v>50622</v>
       </c>
       <c r="B245" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D245" s="10" t="s">
+      <c r="D245" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="246" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A246" s="6">
-        <v>50625</v>
+        <v>50623</v>
       </c>
       <c r="B246" t="s">
-        <v>204</v>
+        <v>110</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>4</v>
@@ -5044,94 +5048,94 @@
     </row>
     <row r="247" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A247" s="6">
-        <v>50629</v>
+        <v>50625</v>
       </c>
       <c r="B247" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D247" s="1" t="s">
+      <c r="D247" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="248" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A248" s="6">
-        <v>50630</v>
+        <v>50629</v>
       </c>
       <c r="B248" t="s">
-        <v>360</v>
+        <v>188</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D248" s="14" t="s">
+      <c r="D248" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="249" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A249" s="6">
-        <v>50803</v>
+        <v>50630</v>
       </c>
       <c r="B249" t="s">
-        <v>82</v>
+        <v>360</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D249" s="1" t="s">
+      <c r="D249" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="250" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A250" s="6">
-        <v>50805</v>
+        <v>50803</v>
       </c>
       <c r="B250" t="s">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D250" s="10" t="s">
+      <c r="D250" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="251" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A251" s="6">
-        <v>50806</v>
+        <v>50805</v>
       </c>
       <c r="B251" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D251" s="1" t="s">
+      <c r="D251" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="252" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A252" s="6">
-        <v>50808</v>
+        <v>50806</v>
       </c>
       <c r="B252" t="s">
-        <v>16</v>
+        <v>156</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D252" s="13" t="s">
-        <v>5</v>
+      <c r="D252" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="253" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A253" s="6">
-        <v>50809</v>
+        <v>50808</v>
       </c>
       <c r="B253" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>4</v>
@@ -5142,24 +5146,24 @@
     </row>
     <row r="254" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="6">
-        <v>50810</v>
+        <v>50809</v>
       </c>
       <c r="B254" t="s">
-        <v>175</v>
+        <v>98</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D254" s="1" t="s">
-        <v>8</v>
+      <c r="D254" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="255" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A255" s="6">
-        <v>50812</v>
+        <v>50810</v>
       </c>
       <c r="B255" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>4</v>
@@ -5170,80 +5174,80 @@
     </row>
     <row r="256" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A256" s="6">
-        <v>50813</v>
+        <v>50812</v>
       </c>
       <c r="B256" t="s">
-        <v>71</v>
+        <v>184</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D256" s="17" t="s">
-        <v>9</v>
+      <c r="D256" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="257" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A257" s="6">
-        <v>50815</v>
+        <v>50813</v>
       </c>
       <c r="B257" t="s">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D257" s="10" t="s">
-        <v>8</v>
+      <c r="D257" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="258" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A258" s="6">
-        <v>50816</v>
+        <v>50815</v>
       </c>
       <c r="B258" t="s">
-        <v>205</v>
+        <v>114</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D258" s="1" t="s">
+      <c r="D258" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="259" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A259" s="6">
-        <v>50818</v>
+        <v>50816</v>
       </c>
       <c r="B259" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D259" s="13" t="s">
-        <v>5</v>
+      <c r="D259" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="260" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A260" s="6">
-        <v>50819</v>
+        <v>50818</v>
       </c>
       <c r="B260" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D260" s="10" t="s">
-        <v>8</v>
+      <c r="D260" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="261" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A261" s="6">
-        <v>50820</v>
+        <v>50819</v>
       </c>
       <c r="B261" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>4</v>
@@ -5254,66 +5258,66 @@
     </row>
     <row r="262" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A262" s="6">
-        <v>50821</v>
+        <v>50820</v>
       </c>
       <c r="B262" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D262" s="1" t="s">
+      <c r="D262" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="263" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A263" s="6">
-        <v>50823</v>
+        <v>50821</v>
       </c>
       <c r="B263" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D263" s="17" t="s">
-        <v>9</v>
+      <c r="D263" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="264" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A264" s="6">
-        <v>50824</v>
+        <v>50823</v>
       </c>
       <c r="B264" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D264" s="13" t="s">
-        <v>5</v>
+      <c r="D264" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="265" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A265" s="6">
-        <v>50825</v>
+        <v>50824</v>
       </c>
       <c r="B265" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D265" s="10" t="s">
-        <v>8</v>
+      <c r="D265" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="266" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A266" s="6">
-        <v>50826</v>
+        <v>50825</v>
       </c>
       <c r="B266" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>4</v>
@@ -5324,24 +5328,24 @@
     </row>
     <row r="267" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A267" s="6">
-        <v>50827</v>
+        <v>50826</v>
       </c>
       <c r="B267" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D267" s="1" t="s">
+      <c r="D267" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="268" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A268" s="6">
-        <v>50829</v>
+        <v>50827</v>
       </c>
       <c r="B268" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>4</v>
@@ -5352,122 +5356,122 @@
     </row>
     <row r="269" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A269" s="6">
-        <v>50830</v>
+        <v>50829</v>
       </c>
       <c r="B269" t="s">
-        <v>366</v>
+        <v>236</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D269" s="11" t="s">
+      <c r="D269" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="270" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A270" s="6">
-        <v>50831</v>
+        <v>50830</v>
       </c>
       <c r="B270" t="s">
-        <v>351</v>
+        <v>366</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D270" s="11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="271" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A271" s="6">
-        <v>50832</v>
-      </c>
-      <c r="B271" s="8" t="s">
-        <v>349</v>
+        <v>50831</v>
+      </c>
+      <c r="B271" t="s">
+        <v>351</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D271" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="272" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A272" s="6">
-        <v>50833</v>
+        <v>50832</v>
       </c>
       <c r="B272" s="8" t="s">
-        <v>397</v>
+        <v>349</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D272" s="11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="273" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A273" s="6">
-        <v>50230</v>
+        <v>50833</v>
       </c>
       <c r="B273" s="8" t="s">
-        <v>379</v>
+        <v>397</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D273" s="11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="274" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A274" s="6">
-        <v>60103</v>
-      </c>
-      <c r="B274" t="s">
-        <v>237</v>
+        <v>50230</v>
+      </c>
+      <c r="B274" s="8" t="s">
+        <v>379</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D274" s="13" t="s">
+      <c r="D274" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="275" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A275" s="6">
-        <v>60109</v>
+        <v>60103</v>
       </c>
       <c r="B275" t="s">
-        <v>328</v>
+        <v>237</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D275" s="11" t="s">
-        <v>9</v>
+      <c r="D275" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="276" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A276" s="6">
-        <v>60124</v>
+        <v>60109</v>
       </c>
       <c r="B276" t="s">
-        <v>238</v>
+        <v>328</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D276" s="13" t="s">
-        <v>5</v>
+      <c r="D276" s="11" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="277" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A277" s="6">
-        <v>60125</v>
+        <v>60124</v>
       </c>
       <c r="B277" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>4</v>
@@ -5478,80 +5482,80 @@
     </row>
     <row r="278" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A278" s="6">
-        <v>60126</v>
+        <v>60125</v>
       </c>
       <c r="B278" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D278" s="10" t="s">
-        <v>8</v>
+      <c r="D278" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="279" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A279" s="6">
-        <v>60128</v>
+        <v>60126</v>
       </c>
       <c r="B279" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D279" s="3" t="s">
-        <v>5</v>
+      <c r="D279" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="280" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A280" s="6">
-        <v>60130</v>
+        <v>60128</v>
       </c>
       <c r="B280" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D280" s="1" t="s">
-        <v>8</v>
+      <c r="D280" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="281" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A281" s="6">
-        <v>60133</v>
+        <v>60130</v>
       </c>
       <c r="B281" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D281" s="13" t="s">
-        <v>5</v>
+      <c r="D281" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="282" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A282" s="6">
-        <v>60134</v>
+        <v>60133</v>
       </c>
       <c r="B282" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D282" s="1" t="s">
-        <v>8</v>
+      <c r="D282" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="283" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A283" s="6">
-        <v>60137</v>
+        <v>60134</v>
       </c>
       <c r="B283" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>4</v>
@@ -5562,10 +5566,10 @@
     </row>
     <row r="284" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A284" s="6">
-        <v>60139</v>
+        <v>60137</v>
       </c>
       <c r="B284" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>4</v>
@@ -5576,10 +5580,10 @@
     </row>
     <row r="285" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A285" s="6">
-        <v>60142</v>
+        <v>60139</v>
       </c>
       <c r="B285" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>4</v>
@@ -5590,10 +5594,10 @@
     </row>
     <row r="286" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A286" s="6">
-        <v>60148</v>
+        <v>60142</v>
       </c>
       <c r="B286" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>4</v>
@@ -5604,10 +5608,10 @@
     </row>
     <row r="287" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A287" s="6">
-        <v>60149</v>
+        <v>60148</v>
       </c>
       <c r="B287" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>4</v>
@@ -5618,66 +5622,66 @@
     </row>
     <row r="288" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A288" s="6">
-        <v>60150</v>
+        <v>60149</v>
       </c>
       <c r="B288" t="s">
-        <v>332</v>
+        <v>249</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D288" s="13" t="s">
-        <v>5</v>
+      <c r="D288" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="289" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A289" s="6">
-        <v>60158</v>
+        <v>60150</v>
       </c>
       <c r="B289" t="s">
-        <v>250</v>
+        <v>332</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D289" s="10" t="s">
-        <v>8</v>
+      <c r="D289" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="290" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A290" s="6">
-        <v>60159</v>
+        <v>60158</v>
       </c>
       <c r="B290" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D290" s="1" t="s">
+      <c r="D290" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="291" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A291" s="6">
-        <v>60162</v>
+        <v>60159</v>
       </c>
       <c r="B291" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D291" s="13" t="s">
-        <v>5</v>
+      <c r="D291" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="292" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A292" s="6">
-        <v>60163</v>
+        <v>60162</v>
       </c>
       <c r="B292" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>4</v>
@@ -5688,24 +5692,24 @@
     </row>
     <row r="293" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A293" s="6">
-        <v>60165</v>
+        <v>60163</v>
       </c>
       <c r="B293" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D293" s="1" t="s">
-        <v>8</v>
+      <c r="D293" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="294" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A294" s="6">
-        <v>60169</v>
+        <v>60165</v>
       </c>
       <c r="B294" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>4</v>
@@ -5716,52 +5720,52 @@
     </row>
     <row r="295" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A295" s="6">
-        <v>60170</v>
-      </c>
-      <c r="B295" s="8" t="s">
-        <v>337</v>
+        <v>60169</v>
+      </c>
+      <c r="B295" t="s">
+        <v>255</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D295" s="11" t="s">
+      <c r="D295" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="296" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A296" s="6">
-        <v>60172</v>
-      </c>
-      <c r="B296" t="s">
-        <v>256</v>
+        <v>60170</v>
+      </c>
+      <c r="B296" s="8" t="s">
+        <v>337</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D296" s="1" t="s">
+      <c r="D296" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="297" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A297" s="6">
-        <v>60174</v>
+        <v>60172</v>
       </c>
       <c r="B297" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D297" s="13" t="s">
-        <v>5</v>
+      <c r="D297" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="298" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A298" s="6">
-        <v>60176</v>
+        <v>60174</v>
       </c>
       <c r="B298" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>4</v>
@@ -5772,52 +5776,52 @@
     </row>
     <row r="299" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A299" s="6">
-        <v>60178</v>
+        <v>60176</v>
       </c>
       <c r="B299" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D299" s="1" t="s">
-        <v>8</v>
+      <c r="D299" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="300" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A300" s="6">
-        <v>60180</v>
+        <v>60178</v>
       </c>
       <c r="B300" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D300" s="10" t="s">
+      <c r="D300" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="301" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A301" s="6">
-        <v>60184</v>
+        <v>60180</v>
       </c>
       <c r="B301" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D301" s="1" t="s">
+      <c r="D301" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="302" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A302" s="6">
-        <v>60190</v>
+        <v>60184</v>
       </c>
       <c r="B302" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>4</v>
@@ -5828,24 +5832,24 @@
     </row>
     <row r="303" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A303" s="6">
-        <v>60191</v>
+        <v>60190</v>
       </c>
       <c r="B303" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D303" s="10" t="s">
+      <c r="D303" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="304" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A304" s="6">
-        <v>60192</v>
+        <v>60191</v>
       </c>
       <c r="B304" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>4</v>
@@ -5856,10 +5860,10 @@
     </row>
     <row r="305" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A305" s="6">
-        <v>60195</v>
+        <v>60192</v>
       </c>
       <c r="B305" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>4</v>
@@ -5870,10 +5874,10 @@
     </row>
     <row r="306" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A306" s="6">
-        <v>60196</v>
+        <v>60195</v>
       </c>
       <c r="B306" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>4</v>
@@ -5884,10 +5888,10 @@
     </row>
     <row r="307" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A307" s="6">
-        <v>60198</v>
+        <v>60196</v>
       </c>
       <c r="B307" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>4</v>
@@ -5898,52 +5902,52 @@
     </row>
     <row r="308" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A308" s="6">
-        <v>60201</v>
+        <v>60198</v>
       </c>
       <c r="B308" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D308" t="s">
-        <v>9</v>
+      <c r="D308" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="309" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A309" s="6">
-        <v>60202</v>
+        <v>60201</v>
       </c>
       <c r="B309" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D309" s="13" t="s">
-        <v>5</v>
+      <c r="D309" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="310" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A310" s="6">
-        <v>60204</v>
+        <v>60202</v>
       </c>
       <c r="B310" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D310" s="1" t="s">
-        <v>8</v>
+      <c r="D310" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="311" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A311" s="6">
-        <v>60205</v>
+        <v>60204</v>
       </c>
       <c r="B311" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>4</v>
@@ -5954,10 +5958,10 @@
     </row>
     <row r="312" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A312" s="6">
-        <v>60206</v>
+        <v>60205</v>
       </c>
       <c r="B312" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>4</v>
@@ -5968,220 +5972,220 @@
     </row>
     <row r="313" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A313" s="6">
-        <v>60209</v>
+        <v>60206</v>
       </c>
       <c r="B313" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D313" s="10" t="s">
+      <c r="D313" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="314" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A314" s="6">
-        <v>60211</v>
+        <v>60209</v>
       </c>
       <c r="B314" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D314" s="1" t="s">
+      <c r="D314" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="315" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A315" s="6">
-        <v>60215</v>
+        <v>60211</v>
       </c>
       <c r="B315" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D315" s="10" t="s">
+      <c r="D315" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="316" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A316" s="6">
-        <v>60216</v>
+        <v>60215</v>
       </c>
       <c r="B316" t="s">
-        <v>381</v>
+        <v>275</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D316" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="317" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A317" s="6">
-        <v>60217</v>
+        <v>60216</v>
       </c>
       <c r="B317" t="s">
-        <v>276</v>
+        <v>381</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D317" s="10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="318" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A318" s="6">
-        <v>60219</v>
+        <v>60217</v>
       </c>
       <c r="B318" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D318" s="1" t="s">
+      <c r="D318" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="319" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A319" s="6">
-        <v>60222</v>
+        <v>60219</v>
       </c>
       <c r="B319" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D319" s="10" t="s">
+      <c r="D319" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="320" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A320" s="6">
-        <v>60225</v>
+        <v>60222</v>
       </c>
       <c r="B320" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D320" s="17" t="s">
-        <v>9</v>
+      <c r="D320" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="321" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A321" s="6">
-        <v>60230</v>
+        <v>60225</v>
       </c>
       <c r="B321" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D321" s="10" t="s">
-        <v>8</v>
+      <c r="D321" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="322" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A322" s="6">
-        <v>60241</v>
-      </c>
-      <c r="B322" s="8" t="s">
-        <v>338</v>
+        <v>60230</v>
+      </c>
+      <c r="B322" t="s">
+        <v>280</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D322" s="7" t="s">
-        <v>9</v>
+      <c r="D322" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="323" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A323" s="6">
-        <v>60242</v>
+        <v>60241</v>
       </c>
       <c r="B323" s="8" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D323" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="324" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A324" s="6">
-        <v>60243</v>
+        <v>60242</v>
       </c>
       <c r="B324" s="8" t="s">
-        <v>395</v>
+        <v>341</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D324" s="7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="325" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A325" s="6">
-        <v>60245</v>
+        <v>60243</v>
       </c>
       <c r="B325" s="8" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D325" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="326" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A326" s="6">
-        <v>60250</v>
+        <v>60245</v>
       </c>
       <c r="B326" s="8" t="s">
-        <v>339</v>
+        <v>387</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D326" s="11" t="s">
-        <v>8</v>
+      <c r="D326" s="7" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="327" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A327" s="6">
-        <v>60253</v>
-      </c>
-      <c r="B327" t="s">
-        <v>281</v>
+        <v>60250</v>
+      </c>
+      <c r="B327" s="8" t="s">
+        <v>339</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D327" s="1" t="s">
+      <c r="D327" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="328" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A328" s="6">
-        <v>60254</v>
+        <v>60253</v>
       </c>
       <c r="B328" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>4</v>
@@ -6192,10 +6196,10 @@
     </row>
     <row r="329" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A329" s="6">
-        <v>60257</v>
+        <v>60254</v>
       </c>
       <c r="B329" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>4</v>
@@ -6206,10 +6210,10 @@
     </row>
     <row r="330" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A330" s="6">
-        <v>60258</v>
+        <v>60257</v>
       </c>
       <c r="B330" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>4</v>
@@ -6220,66 +6224,66 @@
     </row>
     <row r="331" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A331" s="6">
-        <v>60266</v>
-      </c>
-      <c r="B331" s="8" t="s">
-        <v>343</v>
+        <v>60258</v>
+      </c>
+      <c r="B331" t="s">
+        <v>284</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D331" s="11" t="s">
+      <c r="D331" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="332" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A332" s="6">
-        <v>60269</v>
-      </c>
-      <c r="B332" t="s">
-        <v>285</v>
+        <v>60266</v>
+      </c>
+      <c r="B332" s="8" t="s">
+        <v>343</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D332" s="10" t="s">
+      <c r="D332" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="333" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A333" s="6">
-        <v>60270</v>
+        <v>60269</v>
       </c>
       <c r="B333" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D333" s="1" t="s">
-        <v>9</v>
+      <c r="D333" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="334" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A334" s="6">
-        <v>60272</v>
+        <v>60270</v>
       </c>
       <c r="B334" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="335" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A335" s="6">
-        <v>60274</v>
+        <v>60272</v>
       </c>
       <c r="B335" t="s">
-        <v>380</v>
+        <v>287</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>4</v>
@@ -6290,10 +6294,10 @@
     </row>
     <row r="336" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A336" s="6">
-        <v>60275</v>
+        <v>60274</v>
       </c>
       <c r="B336" t="s">
-        <v>288</v>
+        <v>380</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>4</v>
@@ -6304,10 +6308,10 @@
     </row>
     <row r="337" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A337" s="6">
-        <v>60276</v>
+        <v>60275</v>
       </c>
       <c r="B337" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>4</v>
@@ -6318,108 +6322,108 @@
     </row>
     <row r="338" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A338" s="6">
-        <v>60278</v>
+        <v>60276</v>
       </c>
       <c r="B338" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D338" s="13" t="s">
+      <c r="D338" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="339" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A339" s="6">
-        <v>60279</v>
+        <v>60278</v>
       </c>
       <c r="B339" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D339" s="1" t="s">
+      <c r="D339" s="13" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="340" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A340" s="6">
-        <v>60280</v>
+        <v>60279</v>
       </c>
       <c r="B340" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="341" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A341" s="6">
-        <v>60281</v>
-      </c>
-      <c r="B341" s="8" t="s">
-        <v>336</v>
+        <v>60280</v>
+      </c>
+      <c r="B341" t="s">
+        <v>292</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D341" s="11" t="s">
-        <v>9</v>
+      <c r="D341" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="342" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A342" s="6">
-        <v>60282</v>
+        <v>60281</v>
       </c>
       <c r="B342" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D342" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="343" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A343" s="6">
-        <v>60283</v>
-      </c>
-      <c r="B343" t="s">
-        <v>378</v>
+        <v>60282</v>
+      </c>
+      <c r="B343" s="8" t="s">
+        <v>340</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D343" s="1" t="s">
-        <v>8</v>
+      <c r="D343" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="344" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A344" s="6">
-        <v>60284</v>
-      </c>
-      <c r="B344" s="8" t="s">
-        <v>335</v>
+        <v>60283</v>
+      </c>
+      <c r="B344" t="s">
+        <v>378</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D344" s="9" t="s">
-        <v>5</v>
+      <c r="D344" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="345" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A345" s="6">
-        <v>60285</v>
+        <v>60284</v>
       </c>
       <c r="B345" s="8" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>4</v>
@@ -6430,10 +6434,10 @@
     </row>
     <row r="346" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A346" s="6">
-        <v>60286</v>
+        <v>60285</v>
       </c>
       <c r="B346" s="8" t="s">
-        <v>334</v>
+        <v>350</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>4</v>
@@ -6444,52 +6448,52 @@
     </row>
     <row r="347" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A347" s="6">
-        <v>60287</v>
-      </c>
-      <c r="B347" t="s">
-        <v>377</v>
+        <v>60286</v>
+      </c>
+      <c r="B347" s="8" t="s">
+        <v>334</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D347" s="12" t="s">
+      <c r="D347" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="348" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A348" s="6">
-        <v>60289</v>
+        <v>60287</v>
       </c>
       <c r="B348" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D348" s="12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="349" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A349" s="6">
-        <v>60290</v>
+        <v>60289</v>
       </c>
       <c r="B349" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D349" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="350" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A350" s="6">
-        <v>60291</v>
+        <v>60290</v>
       </c>
       <c r="B350" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>4</v>
@@ -6500,24 +6504,24 @@
     </row>
     <row r="351" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A351" s="6">
-        <v>60292</v>
-      </c>
-      <c r="B351" s="18" t="s">
-        <v>400</v>
+        <v>60291</v>
+      </c>
+      <c r="B351" t="s">
+        <v>376</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D351" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="352" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A352" s="6">
-        <v>60296</v>
-      </c>
-      <c r="B352" t="s">
-        <v>391</v>
+        <v>60292</v>
+      </c>
+      <c r="B352" s="18" t="s">
+        <v>400</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>4</v>
@@ -6528,24 +6532,24 @@
     </row>
     <row r="353" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A353" s="6">
-        <v>60297</v>
+        <v>60296</v>
       </c>
       <c r="B353" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D353" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="354" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A354" s="6">
-        <v>60299</v>
+        <v>60297</v>
       </c>
       <c r="B354" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>4</v>
@@ -6556,52 +6560,52 @@
     </row>
     <row r="355" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A355" s="6">
-        <v>61001</v>
+        <v>60299</v>
       </c>
       <c r="B355" t="s">
-        <v>403</v>
+        <v>388</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D355" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="356" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A356" s="6">
-        <v>61004</v>
+        <v>61001</v>
       </c>
       <c r="B356" t="s">
-        <v>293</v>
+        <v>403</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D356" s="15" t="s">
-        <v>5</v>
+      <c r="D356" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="357" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A357" s="6">
-        <v>61009</v>
+        <v>61004</v>
       </c>
       <c r="B357" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D357" s="12" t="s">
-        <v>8</v>
+      <c r="D357" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="358" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A358" s="6">
-        <v>61012</v>
+        <v>61009</v>
       </c>
       <c r="B358" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>4</v>
@@ -6612,10 +6616,10 @@
     </row>
     <row r="359" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A359" s="6">
-        <v>61018</v>
+        <v>61012</v>
       </c>
       <c r="B359" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>4</v>
@@ -6626,10 +6630,10 @@
     </row>
     <row r="360" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A360" s="6">
-        <v>61102</v>
+        <v>61018</v>
       </c>
       <c r="B360" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>4</v>
@@ -6640,52 +6644,52 @@
     </row>
     <row r="361" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A361" s="6">
-        <v>61205</v>
+        <v>61102</v>
       </c>
       <c r="B361" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D361" s="15" t="s">
-        <v>5</v>
+      <c r="D361" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="362" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A362" s="6">
-        <v>70100</v>
+        <v>61205</v>
       </c>
       <c r="B362" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D362" s="12" t="s">
-        <v>8</v>
+      <c r="D362" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="363" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A363" s="6">
-        <v>70101</v>
+        <v>70100</v>
       </c>
       <c r="B363" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D363" s="15" t="s">
-        <v>5</v>
+      <c r="D363" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="364" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A364" s="6">
-        <v>70102</v>
+        <v>70101</v>
       </c>
       <c r="B364" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>4</v>
@@ -6696,80 +6700,80 @@
     </row>
     <row r="365" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A365" s="6">
-        <v>70103</v>
+        <v>70102</v>
       </c>
       <c r="B365" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D365" s="12" t="s">
-        <v>8</v>
+      <c r="D365" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="366" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A366" s="6">
-        <v>70106</v>
+        <v>70103</v>
       </c>
       <c r="B366" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D366" s="15" t="s">
-        <v>5</v>
+      <c r="D366" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="367" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A367" s="6">
-        <v>70109</v>
+        <v>70106</v>
       </c>
       <c r="B367" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D367" s="12" t="s">
-        <v>8</v>
+      <c r="D367" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="368" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A368" s="6">
-        <v>70113</v>
+        <v>70109</v>
       </c>
       <c r="B368" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D368" s="15" t="s">
-        <v>5</v>
+      <c r="D368" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="369" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A369" s="6">
-        <v>70114</v>
+        <v>70113</v>
       </c>
       <c r="B369" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D369" s="9" t="s">
-        <v>9</v>
+      <c r="D369" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="370" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A370" s="6">
-        <v>70115</v>
+        <v>70114</v>
       </c>
       <c r="B370" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>4</v>
@@ -6780,24 +6784,24 @@
     </row>
     <row r="371" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A371" s="6">
-        <v>70638</v>
+        <v>70115</v>
       </c>
       <c r="B371" t="s">
-        <v>306</v>
+        <v>331</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D371" s="12" t="s">
-        <v>8</v>
+      <c r="D371" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="372" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A372" s="6">
-        <v>70639</v>
+        <v>70638</v>
       </c>
       <c r="B372" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>4</v>
@@ -6808,10 +6812,10 @@
     </row>
     <row r="373" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A373" s="6">
-        <v>70640</v>
+        <v>70639</v>
       </c>
       <c r="B373" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>4</v>
@@ -6822,10 +6826,10 @@
     </row>
     <row r="374" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A374" s="6">
-        <v>70642</v>
+        <v>70640</v>
       </c>
       <c r="B374" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>4</v>
@@ -6836,10 +6840,10 @@
     </row>
     <row r="375" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A375" s="6">
-        <v>90504</v>
+        <v>70642</v>
       </c>
       <c r="B375" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>4</v>
@@ -6850,10 +6854,10 @@
     </row>
     <row r="376" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A376" s="6">
-        <v>90509</v>
+        <v>90504</v>
       </c>
       <c r="B376" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>4</v>
@@ -6864,52 +6868,52 @@
     </row>
     <row r="377" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A377" s="6">
-        <v>90602</v>
+        <v>90509</v>
       </c>
       <c r="B377" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D377" s="15" t="s">
-        <v>5</v>
+      <c r="D377" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="378" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A378" s="6">
-        <v>90621</v>
+        <v>90602</v>
       </c>
       <c r="B378" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D378" s="12" t="s">
-        <v>8</v>
+      <c r="D378" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="379" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A379" s="6">
-        <v>90622</v>
+        <v>90621</v>
       </c>
       <c r="B379" t="s">
-        <v>333</v>
+        <v>313</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D379" s="9" t="s">
-        <v>5</v>
+      <c r="D379" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="380" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A380" s="6">
-        <v>90631</v>
-      </c>
-      <c r="B380" s="8" t="s">
-        <v>342</v>
+        <v>90622</v>
+      </c>
+      <c r="B380" t="s">
+        <v>333</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>4</v>
@@ -6920,24 +6924,24 @@
     </row>
     <row r="381" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A381" s="6">
-        <v>90658</v>
-      </c>
-      <c r="B381" t="s">
-        <v>314</v>
+        <v>90631</v>
+      </c>
+      <c r="B381" s="8" t="s">
+        <v>342</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D381" s="12" t="s">
-        <v>8</v>
+      <c r="D381" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="382" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A382" s="6">
-        <v>90660</v>
+        <v>90658</v>
       </c>
       <c r="B382" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>4</v>
@@ -6948,10 +6952,10 @@
     </row>
     <row r="383" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A383" s="6">
-        <v>90668</v>
+        <v>90660</v>
       </c>
       <c r="B383" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>4</v>
@@ -6962,10 +6966,10 @@
     </row>
     <row r="384" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A384" s="6">
-        <v>90671</v>
+        <v>90668</v>
       </c>
       <c r="B384" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>4</v>
@@ -6976,10 +6980,10 @@
     </row>
     <row r="385" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A385" s="6">
-        <v>90679</v>
+        <v>90671</v>
       </c>
       <c r="B385" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>4</v>
@@ -6990,10 +6994,10 @@
     </row>
     <row r="386" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A386" s="6">
-        <v>90683</v>
+        <v>90679</v>
       </c>
       <c r="B386" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>4</v>
@@ -7004,10 +7008,10 @@
     </row>
     <row r="387" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A387" s="6">
-        <v>90705</v>
+        <v>90683</v>
       </c>
       <c r="B387" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>4</v>
@@ -7018,10 +7022,10 @@
     </row>
     <row r="388" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A388" s="6">
-        <v>90706</v>
+        <v>90705</v>
       </c>
       <c r="B388" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>4</v>
@@ -7032,10 +7036,10 @@
     </row>
     <row r="389" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A389" s="6">
-        <v>90708</v>
+        <v>90706</v>
       </c>
       <c r="B389" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>4</v>
@@ -7046,10 +7050,10 @@
     </row>
     <row r="390" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A390" s="6">
-        <v>90709</v>
+        <v>90708</v>
       </c>
       <c r="B390" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>4</v>
@@ -7060,38 +7064,38 @@
     </row>
     <row r="391" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A391" s="6">
-        <v>90713</v>
+        <v>90709</v>
       </c>
       <c r="B391" t="s">
-        <v>402</v>
+        <v>323</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D391" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="392" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A392" s="6">
-        <v>1218</v>
+        <v>90713</v>
       </c>
       <c r="B392" t="s">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D392" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="393" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A393" s="6">
-        <v>1959</v>
-      </c>
-      <c r="B393" s="8" t="s">
-        <v>383</v>
+        <v>1218</v>
+      </c>
+      <c r="B393" t="s">
+        <v>382</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>4</v>
@@ -7102,10 +7106,10 @@
     </row>
     <row r="394" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A394" s="6">
-        <v>5625</v>
+        <v>1959</v>
       </c>
       <c r="B394" s="8" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>4</v>
@@ -7116,10 +7120,10 @@
     </row>
     <row r="395" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A395" s="6">
-        <v>1817</v>
+        <v>5625</v>
       </c>
       <c r="B395" s="8" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>4</v>
@@ -7130,10 +7134,10 @@
     </row>
     <row r="396" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A396" s="6">
-        <v>5737</v>
+        <v>1817</v>
       </c>
       <c r="B396" s="8" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>4</v>
@@ -7144,34 +7148,48 @@
     </row>
     <row r="397" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A397" s="6">
-        <v>60295</v>
+        <v>5737</v>
       </c>
       <c r="B397" s="8" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D397" s="9" t="s">
-        <v>9</v>
+      <c r="D397" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="398" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A398" s="6">
+        <v>60295</v>
+      </c>
+      <c r="B398" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="C398" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D398" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A399" s="6">
         <v>1045</v>
       </c>
-      <c r="B398" s="8" t="s">
+      <c r="B399" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="C398" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D398" s="9" t="s">
+      <c r="C399" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D399" s="9" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D343"/>
+  <autoFilter ref="A1:D344"/>
   <sortState ref="A2:D374">
     <sortCondition ref="A277"/>
   </sortState>

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$344</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$345</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1198" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1201" uniqueCount="407">
   <si>
     <t>CUENTA</t>
   </si>
@@ -1240,6 +1240,9 @@
   </si>
   <si>
     <t>ATR FERRETERIA</t>
+  </si>
+  <si>
+    <t>FERRETERIA MONCHO</t>
   </si>
 </sst>
 </file>
@@ -1594,7 +1597,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D399"/>
+  <dimension ref="A1:D400"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -2794,52 +2797,52 @@
     </row>
     <row r="86" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="6">
-        <v>1416</v>
+        <v>1049</v>
       </c>
       <c r="B86" t="s">
-        <v>217</v>
+        <v>406</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D86" s="1" t="s">
+      <c r="D86" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="6">
-        <v>10107</v>
+        <v>1416</v>
       </c>
       <c r="B87" t="s">
-        <v>96</v>
+        <v>217</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D87" t="s">
-        <v>9</v>
+      <c r="D87" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="6">
-        <v>10137</v>
+        <v>10107</v>
       </c>
       <c r="B88" t="s">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D88" s="1" t="s">
-        <v>8</v>
+      <c r="D88" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="6">
-        <v>10157</v>
+        <v>10137</v>
       </c>
       <c r="B89" t="s">
-        <v>183</v>
+        <v>123</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>4</v>
@@ -2850,10 +2853,10 @@
     </row>
     <row r="90" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="6">
-        <v>10158</v>
+        <v>10157</v>
       </c>
       <c r="B90" t="s">
-        <v>65</v>
+        <v>183</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>4</v>
@@ -2864,108 +2867,108 @@
     </row>
     <row r="91" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="6">
-        <v>10160</v>
+        <v>10158</v>
       </c>
       <c r="B91" t="s">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D91" s="13" t="s">
-        <v>5</v>
+      <c r="D91" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="6">
-        <v>10162</v>
+        <v>10160</v>
       </c>
       <c r="B92" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D92" s="1" t="s">
-        <v>8</v>
+      <c r="D92" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="6">
-        <v>10163</v>
+        <v>10162</v>
       </c>
       <c r="B93" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D93" s="13" t="s">
-        <v>5</v>
+      <c r="D93" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="6">
-        <v>10165</v>
+        <v>10163</v>
       </c>
       <c r="B94" t="s">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D94" s="1" t="s">
-        <v>8</v>
+      <c r="D94" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="6">
-        <v>10166</v>
-      </c>
-      <c r="B95" s="8" t="s">
-        <v>348</v>
+        <v>10165</v>
+      </c>
+      <c r="B95" t="s">
+        <v>19</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D95" s="11" t="s">
+      <c r="D95" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="6">
-        <v>10167</v>
-      </c>
-      <c r="B96" t="s">
-        <v>39</v>
+        <v>10166</v>
+      </c>
+      <c r="B96" s="8" t="s">
+        <v>348</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D96" s="13" t="s">
-        <v>5</v>
+      <c r="D96" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="6">
-        <v>10424</v>
+        <v>10167</v>
       </c>
       <c r="B97" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D97" s="17" t="s">
-        <v>9</v>
+      <c r="D97" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="6">
-        <v>10425</v>
+        <v>10424</v>
       </c>
       <c r="B98" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>4</v>
@@ -2976,24 +2979,24 @@
     </row>
     <row r="99" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="6">
-        <v>20094</v>
+        <v>10425</v>
       </c>
       <c r="B99" t="s">
-        <v>198</v>
+        <v>15</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D99" s="10" t="s">
-        <v>8</v>
+      <c r="D99" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="6">
-        <v>20095</v>
+        <v>20094</v>
       </c>
       <c r="B100" t="s">
-        <v>153</v>
+        <v>198</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>4</v>
@@ -3004,66 +3007,66 @@
     </row>
     <row r="101" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="6">
-        <v>20096</v>
+        <v>20095</v>
       </c>
       <c r="B101" t="s">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D101" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="6">
-        <v>20100</v>
+        <v>20096</v>
       </c>
       <c r="B102" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D102" s="1" t="s">
-        <v>8</v>
+      <c r="D102" s="10" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="6">
-        <v>20101</v>
+        <v>20100</v>
       </c>
       <c r="B103" t="s">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="6">
-        <v>20103</v>
+        <v>20101</v>
       </c>
       <c r="B104" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="6">
-        <v>20106</v>
+        <v>20103</v>
       </c>
       <c r="B105" t="s">
-        <v>155</v>
+        <v>81</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>4</v>
@@ -3074,80 +3077,80 @@
     </row>
     <row r="106" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="6">
-        <v>20108</v>
+        <v>20106</v>
       </c>
       <c r="B106" t="s">
-        <v>219</v>
+        <v>155</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D106" s="10" t="s">
+      <c r="D106" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="6">
-        <v>20109</v>
+        <v>20108</v>
       </c>
       <c r="B107" t="s">
-        <v>53</v>
+        <v>219</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D107" s="1" t="s">
+      <c r="D107" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="6">
-        <v>20110</v>
+        <v>20109</v>
       </c>
       <c r="B108" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D108" s="13" t="s">
-        <v>5</v>
+      <c r="D108" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="6">
-        <v>20113</v>
+        <v>20110</v>
       </c>
       <c r="B109" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D109" s="10" t="s">
-        <v>8</v>
+      <c r="D109" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="6">
-        <v>20114</v>
+        <v>20113</v>
       </c>
       <c r="B110" t="s">
-        <v>126</v>
+        <v>93</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D110" s="1" t="s">
+      <c r="D110" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="6">
-        <v>20116</v>
+        <v>20114</v>
       </c>
       <c r="B111" t="s">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>4</v>
@@ -3158,10 +3161,10 @@
     </row>
     <row r="112" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="6">
-        <v>20117</v>
+        <v>20116</v>
       </c>
       <c r="B112" t="s">
-        <v>186</v>
+        <v>73</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>4</v>
@@ -3172,10 +3175,10 @@
     </row>
     <row r="113" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="6">
-        <v>20118</v>
+        <v>20117</v>
       </c>
       <c r="B113" t="s">
-        <v>160</v>
+        <v>186</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>4</v>
@@ -3186,10 +3189,10 @@
     </row>
     <row r="114" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="6">
-        <v>20120</v>
+        <v>20118</v>
       </c>
       <c r="B114" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>4</v>
@@ -3200,10 +3203,10 @@
     </row>
     <row r="115" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="6">
-        <v>20121</v>
+        <v>20120</v>
       </c>
       <c r="B115" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>4</v>
@@ -3214,38 +3217,38 @@
     </row>
     <row r="116" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="6">
-        <v>20125</v>
+        <v>20121</v>
       </c>
       <c r="B116" t="s">
-        <v>88</v>
+        <v>159</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D116" s="10" t="s">
+      <c r="D116" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="6">
-        <v>20127</v>
+        <v>20125</v>
       </c>
       <c r="B117" t="s">
-        <v>168</v>
+        <v>88</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D117" s="1" t="s">
+      <c r="D117" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="6">
-        <v>20128</v>
+        <v>20127</v>
       </c>
       <c r="B118" t="s">
-        <v>208</v>
+        <v>168</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>4</v>
@@ -3256,52 +3259,52 @@
     </row>
     <row r="119" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="6">
-        <v>20129</v>
+        <v>20128</v>
       </c>
       <c r="B119" t="s">
-        <v>326</v>
+        <v>208</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D119" s="10" t="s">
+      <c r="D119" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="6">
-        <v>20137</v>
+        <v>20129</v>
       </c>
       <c r="B120" t="s">
-        <v>79</v>
+        <v>326</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D120" s="3" t="s">
-        <v>5</v>
+      <c r="D120" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="6">
-        <v>20138</v>
+        <v>20137</v>
       </c>
       <c r="B121" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D121" s="13" t="s">
+      <c r="D121" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="6">
-        <v>20140</v>
+        <v>20138</v>
       </c>
       <c r="B122" t="s">
-        <v>218</v>
+        <v>113</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>4</v>
@@ -3312,24 +3315,24 @@
     </row>
     <row r="123" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="6">
-        <v>20142</v>
+        <v>20140</v>
       </c>
       <c r="B123" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D123" s="1" t="s">
-        <v>8</v>
+      <c r="D123" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="6">
-        <v>20146</v>
+        <v>20142</v>
       </c>
       <c r="B124" t="s">
-        <v>148</v>
+        <v>193</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>4</v>
@@ -3340,10 +3343,10 @@
     </row>
     <row r="125" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="6">
-        <v>20148</v>
+        <v>20146</v>
       </c>
       <c r="B125" t="s">
-        <v>38</v>
+        <v>148</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>4</v>
@@ -3354,52 +3357,52 @@
     </row>
     <row r="126" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="6">
-        <v>20156</v>
+        <v>20148</v>
       </c>
       <c r="B126" t="s">
-        <v>179</v>
+        <v>38</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D126" s="10" t="s">
+      <c r="D126" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="6">
-        <v>20159</v>
+        <v>20156</v>
       </c>
       <c r="B127" t="s">
-        <v>120</v>
+        <v>179</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D127" s="17" t="s">
-        <v>9</v>
+      <c r="D127" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="6">
-        <v>20160</v>
+        <v>20159</v>
       </c>
       <c r="B128" t="s">
-        <v>224</v>
+        <v>120</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D128" s="10" t="s">
-        <v>8</v>
+      <c r="D128" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="6">
-        <v>20163</v>
+        <v>20160</v>
       </c>
       <c r="B129" t="s">
-        <v>23</v>
+        <v>224</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>4</v>
@@ -3410,52 +3413,52 @@
     </row>
     <row r="130" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="6">
-        <v>20164</v>
+        <v>20163</v>
       </c>
       <c r="B130" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D130" t="s">
-        <v>9</v>
+      <c r="D130" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="6">
-        <v>20165</v>
+        <v>20164</v>
       </c>
       <c r="B131" t="s">
-        <v>131</v>
+        <v>18</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D131" s="10" t="s">
-        <v>8</v>
+      <c r="D131" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="6">
-        <v>20166</v>
+        <v>20165</v>
       </c>
       <c r="B132" t="s">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D132" s="1" t="s">
+      <c r="D132" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="6">
-        <v>20169</v>
+        <v>20166</v>
       </c>
       <c r="B133" t="s">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>4</v>
@@ -3466,38 +3469,38 @@
     </row>
     <row r="134" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="6">
-        <v>20173</v>
+        <v>20169</v>
       </c>
       <c r="B134" t="s">
-        <v>112</v>
+        <v>151</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D134" s="10" t="s">
+      <c r="D134" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="6">
-        <v>20174</v>
+        <v>20173</v>
       </c>
       <c r="B135" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D135" s="1" t="s">
+      <c r="D135" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="6">
-        <v>20178</v>
+        <v>20174</v>
       </c>
       <c r="B136" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>4</v>
@@ -3508,80 +3511,80 @@
     </row>
     <row r="137" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="6">
-        <v>20179</v>
+        <v>20178</v>
       </c>
       <c r="B137" t="s">
-        <v>171</v>
+        <v>117</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D137" t="s">
-        <v>9</v>
+      <c r="D137" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="6">
-        <v>20180</v>
+        <v>20179</v>
       </c>
       <c r="B138" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D138" s="1" t="s">
-        <v>8</v>
+      <c r="D138" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="6">
-        <v>20183</v>
+        <v>20180</v>
       </c>
       <c r="B139" t="s">
-        <v>370</v>
+        <v>149</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D139" s="14" t="s">
-        <v>5</v>
+      <c r="D139" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="6">
-        <v>20189</v>
+        <v>20183</v>
       </c>
       <c r="B140" t="s">
-        <v>329</v>
+        <v>370</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D140" s="1" t="s">
-        <v>8</v>
+      <c r="D140" s="14" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="6">
-        <v>20200</v>
+        <v>20189</v>
       </c>
       <c r="B141" t="s">
-        <v>83</v>
+        <v>329</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D141" s="13" t="s">
-        <v>5</v>
+      <c r="D141" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="6">
-        <v>20201</v>
+        <v>20200</v>
       </c>
       <c r="B142" t="s">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>4</v>
@@ -3592,150 +3595,150 @@
     </row>
     <row r="143" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="6">
-        <v>20204</v>
+        <v>20201</v>
       </c>
       <c r="B143" t="s">
-        <v>57</v>
+        <v>145</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D143" s="10" t="s">
-        <v>8</v>
+      <c r="D143" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="6">
-        <v>20205</v>
+        <v>20204</v>
       </c>
       <c r="B144" t="s">
-        <v>206</v>
+        <v>57</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D144" s="1" t="s">
-        <v>9</v>
+      <c r="D144" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="6">
-        <v>20211</v>
+        <v>20205</v>
       </c>
       <c r="B145" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D145" s="10" t="s">
-        <v>8</v>
+      <c r="D145" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="6">
-        <v>20224</v>
+        <v>20211</v>
       </c>
       <c r="B146" t="s">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D146" s="1" t="s">
+      <c r="D146" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="6">
-        <v>20227</v>
+        <v>20224</v>
       </c>
       <c r="B147" t="s">
-        <v>192</v>
+        <v>85</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D147" s="10" t="s">
+      <c r="D147" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="6">
-        <v>20228</v>
+        <v>20227</v>
       </c>
       <c r="B148" t="s">
-        <v>91</v>
+        <v>192</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D148" s="13" t="s">
-        <v>5</v>
+      <c r="D148" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="6">
-        <v>20230</v>
+        <v>20228</v>
       </c>
       <c r="B149" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D149" s="10" t="s">
-        <v>8</v>
+      <c r="D149" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="6">
-        <v>20234</v>
+        <v>20230</v>
       </c>
       <c r="B150" t="s">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D150" s="13" t="s">
-        <v>5</v>
+      <c r="D150" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="6">
-        <v>20236</v>
+        <v>20234</v>
       </c>
       <c r="B151" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D151" s="3" t="s">
+      <c r="D151" s="13" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="6">
-        <v>20238</v>
+        <v>20236</v>
       </c>
       <c r="B152" t="s">
-        <v>139</v>
+        <v>31</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D152" s="13" t="s">
+      <c r="D152" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="6">
-        <v>20241</v>
+        <v>20238</v>
       </c>
       <c r="B153" t="s">
-        <v>22</v>
+        <v>139</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>4</v>
@@ -3746,24 +3749,24 @@
     </row>
     <row r="154" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="6">
-        <v>20242</v>
+        <v>20241</v>
       </c>
       <c r="B154" t="s">
-        <v>216</v>
+        <v>22</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D154" s="10" t="s">
-        <v>8</v>
+      <c r="D154" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="155" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="6">
-        <v>20244</v>
+        <v>20242</v>
       </c>
       <c r="B155" t="s">
-        <v>124</v>
+        <v>216</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>4</v>
@@ -3774,108 +3777,108 @@
     </row>
     <row r="156" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="6">
-        <v>20246</v>
+        <v>20244</v>
       </c>
       <c r="B156" t="s">
-        <v>14</v>
+        <v>124</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D156" s="13" t="s">
-        <v>5</v>
+      <c r="D156" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="6">
-        <v>20249</v>
+        <v>20246</v>
       </c>
       <c r="B157" t="s">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D157" s="10" t="s">
-        <v>8</v>
+      <c r="D157" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="6">
-        <v>20256</v>
+        <v>20249</v>
       </c>
       <c r="B158" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D158" s="1" t="s">
+      <c r="D158" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="159" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A159" s="6">
-        <v>20257</v>
+        <v>20256</v>
       </c>
       <c r="B159" t="s">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D159" s="17" t="s">
-        <v>9</v>
+      <c r="D159" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="160" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="6">
-        <v>20258</v>
+        <v>20257</v>
       </c>
       <c r="B160" t="s">
-        <v>199</v>
+        <v>150</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D160" s="1" t="s">
-        <v>8</v>
+      <c r="D160" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="161" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="6">
-        <v>20260</v>
+        <v>20258</v>
       </c>
       <c r="B161" t="s">
-        <v>68</v>
+        <v>199</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D161" s="13" t="s">
-        <v>5</v>
+      <c r="D161" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="6">
-        <v>20261</v>
+        <v>20260</v>
       </c>
       <c r="B162" t="s">
-        <v>207</v>
+        <v>68</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D162" s="10" t="s">
-        <v>8</v>
+      <c r="D162" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="163" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="6">
-        <v>20262</v>
+        <v>20261</v>
       </c>
       <c r="B163" t="s">
-        <v>92</v>
+        <v>207</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>4</v>
@@ -3886,206 +3889,206 @@
     </row>
     <row r="164" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="6">
-        <v>20267</v>
+        <v>20262</v>
       </c>
       <c r="B164" t="s">
-        <v>401</v>
+        <v>92</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D164" s="10" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="165" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="6">
-        <v>20268</v>
+        <v>20267</v>
       </c>
       <c r="B165" t="s">
-        <v>201</v>
+        <v>401</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D165" s="1" t="s">
-        <v>8</v>
+      <c r="D165" s="10" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="6">
-        <v>20271</v>
+        <v>20268</v>
       </c>
       <c r="B166" t="s">
-        <v>34</v>
+        <v>201</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D166" s="13" t="s">
-        <v>5</v>
+      <c r="D166" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="6">
-        <v>20272</v>
+        <v>20271</v>
       </c>
       <c r="B167" t="s">
-        <v>178</v>
+        <v>34</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D167" s="1" t="s">
-        <v>8</v>
+      <c r="D167" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="168" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="6">
-        <v>20275</v>
+        <v>20272</v>
       </c>
       <c r="B168" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D168" s="13" t="s">
-        <v>5</v>
+      <c r="D168" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="6">
-        <v>20277</v>
+        <v>20275</v>
       </c>
       <c r="B169" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D169" s="1" t="s">
-        <v>8</v>
+      <c r="D169" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A170" s="6">
-        <v>20281</v>
+        <v>20277</v>
       </c>
       <c r="B170" t="s">
-        <v>105</v>
+        <v>154</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D170" s="3" t="s">
-        <v>5</v>
+      <c r="D170" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="171" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="6">
-        <v>20282</v>
+        <v>20281</v>
       </c>
       <c r="B171" t="s">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D171" s="1" t="s">
-        <v>9</v>
+      <c r="D171" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="6">
-        <v>20284</v>
+        <v>20282</v>
       </c>
       <c r="B172" t="s">
-        <v>17</v>
+        <v>141</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D172" s="17" t="s">
+      <c r="D172" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="6">
-        <v>20285</v>
+        <v>20284</v>
       </c>
       <c r="B173" t="s">
-        <v>146</v>
+        <v>17</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D173" s="1" t="s">
-        <v>8</v>
+      <c r="D173" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="174" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="6">
-        <v>20289</v>
+        <v>20285</v>
       </c>
       <c r="B174" t="s">
-        <v>52</v>
+        <v>146</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D174" s="3" t="s">
-        <v>5</v>
+      <c r="D174" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="175" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="6">
-        <v>20290</v>
+        <v>20289</v>
       </c>
       <c r="B175" t="s">
-        <v>103</v>
+        <v>52</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D175" s="1" t="s">
-        <v>8</v>
+      <c r="D175" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="6">
-        <v>20291</v>
+        <v>20290</v>
       </c>
       <c r="B176" t="s">
-        <v>187</v>
+        <v>103</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D176" s="10" t="s">
+      <c r="D176" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="177" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A177" s="6">
-        <v>20292</v>
+        <v>20291</v>
       </c>
       <c r="B177" t="s">
-        <v>32</v>
+        <v>187</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D177" s="13" t="s">
-        <v>5</v>
+      <c r="D177" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="6">
-        <v>20293</v>
+        <v>20292</v>
       </c>
       <c r="B178" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>4</v>
@@ -4096,52 +4099,52 @@
     </row>
     <row r="179" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="6">
-        <v>20294</v>
+        <v>20293</v>
       </c>
       <c r="B179" t="s">
-        <v>202</v>
+        <v>43</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D179" s="10" t="s">
-        <v>8</v>
+      <c r="D179" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="6">
-        <v>20296</v>
+        <v>20294</v>
       </c>
       <c r="B180" t="s">
-        <v>144</v>
+        <v>202</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D180" s="13" t="s">
-        <v>5</v>
+      <c r="D180" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="6">
-        <v>20298</v>
+        <v>20296</v>
       </c>
       <c r="B181" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D181" s="1" t="s">
-        <v>8</v>
+      <c r="D181" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="182" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="6">
-        <v>20299</v>
+        <v>20298</v>
       </c>
       <c r="B182" t="s">
-        <v>58</v>
+        <v>169</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>4</v>
@@ -4152,10 +4155,10 @@
     </row>
     <row r="183" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="6">
-        <v>20301</v>
+        <v>20299</v>
       </c>
       <c r="B183" t="s">
-        <v>134</v>
+        <v>58</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>4</v>
@@ -4166,10 +4169,10 @@
     </row>
     <row r="184" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="6">
-        <v>20303</v>
+        <v>20301</v>
       </c>
       <c r="B184" t="s">
-        <v>37</v>
+        <v>134</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>4</v>
@@ -4180,24 +4183,24 @@
     </row>
     <row r="185" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="6">
-        <v>20309</v>
+        <v>20303</v>
       </c>
       <c r="B185" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D185" s="13" t="s">
-        <v>5</v>
+      <c r="D185" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="186" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="6">
-        <v>20310</v>
+        <v>20309</v>
       </c>
       <c r="B186" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>4</v>
@@ -4208,52 +4211,52 @@
     </row>
     <row r="187" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="6">
-        <v>20318</v>
+        <v>20310</v>
       </c>
       <c r="B187" t="s">
-        <v>209</v>
+        <v>59</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D187" s="1" t="s">
-        <v>8</v>
+      <c r="D187" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="188" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="6">
-        <v>20319</v>
+        <v>20318</v>
       </c>
       <c r="B188" t="s">
-        <v>101</v>
+        <v>209</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D188" s="10" t="s">
+      <c r="D188" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="189" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="6">
-        <v>20320</v>
+        <v>20319</v>
       </c>
       <c r="B189" t="s">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D189" s="1" t="s">
+      <c r="D189" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="190" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A190" s="6">
-        <v>20324</v>
+        <v>20320</v>
       </c>
       <c r="B190" t="s">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>4</v>
@@ -4264,10 +4267,10 @@
     </row>
     <row r="191" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="6">
-        <v>20331</v>
+        <v>20324</v>
       </c>
       <c r="B191" t="s">
-        <v>51</v>
+        <v>210</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>4</v>
@@ -4278,38 +4281,38 @@
     </row>
     <row r="192" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="6">
-        <v>20333</v>
+        <v>20331</v>
       </c>
       <c r="B192" t="s">
-        <v>136</v>
+        <v>51</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D192" s="13" t="s">
-        <v>5</v>
+      <c r="D192" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="193" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="6">
-        <v>20337</v>
+        <v>20333</v>
       </c>
       <c r="B193" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D193" s="1" t="s">
-        <v>8</v>
+      <c r="D193" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="194" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="6">
-        <v>20343</v>
+        <v>20337</v>
       </c>
       <c r="B194" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>4</v>
@@ -4320,10 +4323,10 @@
     </row>
     <row r="195" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A195" s="6">
-        <v>20344</v>
+        <v>20343</v>
       </c>
       <c r="B195" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>4</v>
@@ -4334,66 +4337,66 @@
     </row>
     <row r="196" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="6">
-        <v>20351</v>
+        <v>20344</v>
       </c>
       <c r="B196" t="s">
-        <v>26</v>
+        <v>127</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D196" s="13" t="s">
-        <v>5</v>
+      <c r="D196" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="197" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="6">
-        <v>20357</v>
+        <v>20351</v>
       </c>
       <c r="B197" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D197" s="1" t="s">
-        <v>8</v>
+      <c r="D197" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="198" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A198" s="6">
-        <v>20361</v>
+        <v>20357</v>
       </c>
       <c r="B198" t="s">
-        <v>164</v>
+        <v>56</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D198" s="13" t="s">
-        <v>5</v>
+      <c r="D198" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="199" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="6">
-        <v>20362</v>
+        <v>20361</v>
       </c>
       <c r="B199" t="s">
-        <v>45</v>
+        <v>164</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D199" s="10" t="s">
-        <v>8</v>
+      <c r="D199" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="200" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A200" s="6">
-        <v>20363</v>
+        <v>20362</v>
       </c>
       <c r="B200" t="s">
-        <v>213</v>
+        <v>45</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>4</v>
@@ -4404,38 +4407,38 @@
     </row>
     <row r="201" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="6">
-        <v>20364</v>
+        <v>20363</v>
       </c>
       <c r="B201" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D201" s="13" t="s">
-        <v>5</v>
+      <c r="D201" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="202" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="6">
-        <v>20366</v>
+        <v>20364</v>
       </c>
       <c r="B202" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D202" s="1" t="s">
-        <v>8</v>
+      <c r="D202" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="203" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="6">
-        <v>20367</v>
+        <v>20366</v>
       </c>
       <c r="B203" t="s">
-        <v>47</v>
+        <v>220</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>4</v>
@@ -4446,10 +4449,10 @@
     </row>
     <row r="204" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="6">
-        <v>20369</v>
+        <v>20367</v>
       </c>
       <c r="B204" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>4</v>
@@ -4460,10 +4463,10 @@
     </row>
     <row r="205" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A205" s="6">
-        <v>20371</v>
+        <v>20369</v>
       </c>
       <c r="B205" t="s">
-        <v>223</v>
+        <v>63</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>4</v>
@@ -4474,52 +4477,52 @@
     </row>
     <row r="206" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A206" s="6">
-        <v>20372</v>
+        <v>20371</v>
       </c>
       <c r="B206" t="s">
-        <v>70</v>
+        <v>223</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D206" s="10" t="s">
+      <c r="D206" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="207" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A207" s="6">
-        <v>20374</v>
+        <v>20372</v>
       </c>
       <c r="B207" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D207" s="1" t="s">
+      <c r="D207" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="208" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A208" s="6">
-        <v>20377</v>
+        <v>20374</v>
       </c>
       <c r="B208" t="s">
-        <v>225</v>
+        <v>61</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D208" s="10" t="s">
+      <c r="D208" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="209" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A209" s="6">
-        <v>20379</v>
+        <v>20377</v>
       </c>
       <c r="B209" t="s">
-        <v>49</v>
+        <v>225</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>4</v>
@@ -4530,66 +4533,66 @@
     </row>
     <row r="210" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A210" s="6">
-        <v>20380</v>
+        <v>20379</v>
       </c>
       <c r="B210" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D210" s="13" t="s">
-        <v>5</v>
+      <c r="D210" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="211" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="6">
-        <v>20381</v>
+        <v>20380</v>
       </c>
       <c r="B211" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D211" s="1" t="s">
-        <v>8</v>
+      <c r="D211" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="212" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A212" s="6">
-        <v>20384</v>
+        <v>20381</v>
       </c>
       <c r="B212" t="s">
-        <v>181</v>
+        <v>60</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D212" s="10" t="s">
+      <c r="D212" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="213" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A213" s="6">
-        <v>20385</v>
+        <v>20384</v>
       </c>
       <c r="B213" t="s">
-        <v>36</v>
+        <v>181</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D213" s="1" t="s">
+      <c r="D213" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="214" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A214" s="6">
-        <v>20386</v>
+        <v>20385</v>
       </c>
       <c r="B214" t="s">
-        <v>119</v>
+        <v>36</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>4</v>
@@ -4600,66 +4603,66 @@
     </row>
     <row r="215" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A215" s="6">
-        <v>20388</v>
+        <v>20386</v>
       </c>
       <c r="B215" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D215" s="10" t="s">
+      <c r="D215" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="216" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A216" s="6">
-        <v>20391</v>
+        <v>20388</v>
       </c>
       <c r="B216" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D216" s="1" t="s">
+      <c r="D216" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="217" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A217" s="6">
-        <v>20394</v>
+        <v>20391</v>
       </c>
       <c r="B217" t="s">
-        <v>173</v>
+        <v>106</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D217" s="10" t="s">
+      <c r="D217" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="218" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A218" s="6">
-        <v>20395</v>
+        <v>20394</v>
       </c>
       <c r="B218" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D218" s="1" t="s">
+      <c r="D218" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="219" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A219" s="6">
-        <v>20396</v>
+        <v>20395</v>
       </c>
       <c r="B219" t="s">
-        <v>330</v>
+        <v>161</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>4</v>
@@ -4670,52 +4673,52 @@
     </row>
     <row r="220" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A220" s="6">
-        <v>20397</v>
-      </c>
-      <c r="B220" s="8" t="s">
-        <v>344</v>
+        <v>20396</v>
+      </c>
+      <c r="B220" t="s">
+        <v>330</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D220" s="11" t="s">
-        <v>5</v>
+      <c r="D220" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="221" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A221" s="6">
-        <v>30101</v>
-      </c>
-      <c r="B221" t="s">
-        <v>167</v>
+        <v>20397</v>
+      </c>
+      <c r="B221" s="8" t="s">
+        <v>344</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D221" s="1" t="s">
-        <v>8</v>
+      <c r="D221" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="222" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A222" s="6">
-        <v>40124</v>
+        <v>30101</v>
       </c>
       <c r="B222" t="s">
-        <v>24</v>
+        <v>167</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D222" s="13" t="s">
-        <v>5</v>
+      <c r="D222" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="223" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223" s="6">
-        <v>40125</v>
+        <v>40124</v>
       </c>
       <c r="B223" t="s">
-        <v>143</v>
+        <v>24</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>4</v>
@@ -4726,24 +4729,24 @@
     </row>
     <row r="224" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="6">
-        <v>40127</v>
+        <v>40125</v>
       </c>
       <c r="B224" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D224" s="1" t="s">
-        <v>8</v>
+      <c r="D224" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="225" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A225" s="6">
-        <v>40129</v>
+        <v>40127</v>
       </c>
       <c r="B225" t="s">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>4</v>
@@ -4754,24 +4757,24 @@
     </row>
     <row r="226" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A226" s="6">
-        <v>40137</v>
+        <v>40129</v>
       </c>
       <c r="B226" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D226" s="10" t="s">
+      <c r="D226" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="227" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A227" s="6">
-        <v>40139</v>
+        <v>40137</v>
       </c>
       <c r="B227" t="s">
-        <v>327</v>
+        <v>121</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>4</v>
@@ -4782,66 +4785,66 @@
     </row>
     <row r="228" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A228" s="6">
-        <v>40140</v>
+        <v>40139</v>
       </c>
       <c r="B228" t="s">
-        <v>170</v>
+        <v>327</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D228" s="1" t="s">
+      <c r="D228" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="229" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A229" s="6">
-        <v>40141</v>
+        <v>40140</v>
       </c>
       <c r="B229" t="s">
-        <v>111</v>
+        <v>170</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D229" s="13" t="s">
-        <v>5</v>
+      <c r="D229" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="230" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A230" s="6">
-        <v>40143</v>
+        <v>40141</v>
       </c>
       <c r="B230" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D230" s="10" t="s">
-        <v>8</v>
+      <c r="D230" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="231" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A231" s="6">
-        <v>40144</v>
+        <v>40143</v>
       </c>
       <c r="B231" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D231" s="13" t="s">
-        <v>5</v>
+      <c r="D231" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="232" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A232" s="6">
-        <v>40145</v>
+        <v>40144</v>
       </c>
       <c r="B232" t="s">
-        <v>165</v>
+        <v>107</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>4</v>
@@ -4852,206 +4855,206 @@
     </row>
     <row r="233" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A233" s="6">
-        <v>40147</v>
+        <v>40145</v>
       </c>
       <c r="B233" t="s">
-        <v>405</v>
+        <v>165</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D233" s="19" t="s">
-        <v>8</v>
+      <c r="D233" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="234" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A234" s="6">
-        <v>40150</v>
+        <v>40147</v>
       </c>
       <c r="B234" t="s">
-        <v>221</v>
+        <v>405</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D234" s="10" t="s">
+      <c r="D234" s="19" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="235" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A235" s="6">
-        <v>40151</v>
+        <v>40150</v>
       </c>
       <c r="B235" t="s">
-        <v>54</v>
+        <v>221</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D235" s="1" t="s">
+      <c r="D235" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="236" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A236" s="6">
-        <v>50102</v>
+        <v>40151</v>
       </c>
       <c r="B236" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D236" s="13" t="s">
-        <v>5</v>
+      <c r="D236" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="237" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A237" s="6">
-        <v>50222</v>
+        <v>50102</v>
       </c>
       <c r="B237" t="s">
-        <v>215</v>
+        <v>67</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D237" s="1" t="s">
-        <v>8</v>
+      <c r="D237" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="238" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A238" s="6">
-        <v>50223</v>
+        <v>50222</v>
       </c>
       <c r="B238" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D238" s="10" t="s">
+      <c r="D238" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="239" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A239" s="6">
-        <v>50224</v>
+        <v>50223</v>
       </c>
       <c r="B239" t="s">
-        <v>42</v>
+        <v>194</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D239" s="3" t="s">
-        <v>5</v>
+      <c r="D239" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="240" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A240" s="6">
-        <v>50444</v>
+        <v>50224</v>
       </c>
       <c r="B240" t="s">
-        <v>116</v>
+        <v>42</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D240" s="1" t="s">
-        <v>8</v>
+      <c r="D240" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="241" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="6">
-        <v>50445</v>
+        <v>50444</v>
       </c>
       <c r="B241" t="s">
-        <v>354</v>
+        <v>116</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D241" s="11" t="s">
-        <v>5</v>
+      <c r="D241" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="242" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A242" s="6">
-        <v>50607</v>
+        <v>50445</v>
       </c>
       <c r="B242" t="s">
-        <v>76</v>
+        <v>354</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D242" s="13" t="s">
+      <c r="D242" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="243" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A243" s="6">
-        <v>50608</v>
+        <v>50607</v>
       </c>
       <c r="B243" t="s">
-        <v>177</v>
+        <v>76</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D243" s="1" t="s">
-        <v>8</v>
+      <c r="D243" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="244" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A244" s="6">
-        <v>50611</v>
-      </c>
-      <c r="B244" s="8" t="s">
-        <v>347</v>
+        <v>50608</v>
+      </c>
+      <c r="B244" t="s">
+        <v>177</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D244" s="14" t="s">
+      <c r="D244" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="245" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A245" s="6">
-        <v>50622</v>
-      </c>
-      <c r="B245" t="s">
-        <v>95</v>
+        <v>50611</v>
+      </c>
+      <c r="B245" s="8" t="s">
+        <v>347</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D245" s="16" t="s">
+      <c r="D245" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="246" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A246" s="6">
-        <v>50623</v>
+        <v>50622</v>
       </c>
       <c r="B246" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D246" s="10" t="s">
+      <c r="D246" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="247" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A247" s="6">
-        <v>50625</v>
+        <v>50623</v>
       </c>
       <c r="B247" t="s">
-        <v>204</v>
+        <v>110</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>4</v>
@@ -5062,94 +5065,94 @@
     </row>
     <row r="248" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A248" s="6">
-        <v>50629</v>
+        <v>50625</v>
       </c>
       <c r="B248" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D248" s="1" t="s">
+      <c r="D248" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="249" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A249" s="6">
-        <v>50630</v>
+        <v>50629</v>
       </c>
       <c r="B249" t="s">
-        <v>360</v>
+        <v>188</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D249" s="14" t="s">
+      <c r="D249" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="250" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A250" s="6">
-        <v>50803</v>
+        <v>50630</v>
       </c>
       <c r="B250" t="s">
-        <v>82</v>
+        <v>360</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D250" s="1" t="s">
+      <c r="D250" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="251" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A251" s="6">
-        <v>50805</v>
+        <v>50803</v>
       </c>
       <c r="B251" t="s">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D251" s="10" t="s">
+      <c r="D251" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="252" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A252" s="6">
-        <v>50806</v>
+        <v>50805</v>
       </c>
       <c r="B252" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D252" s="1" t="s">
+      <c r="D252" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="253" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A253" s="6">
-        <v>50808</v>
+        <v>50806</v>
       </c>
       <c r="B253" t="s">
-        <v>16</v>
+        <v>156</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D253" s="13" t="s">
-        <v>5</v>
+      <c r="D253" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="254" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="6">
-        <v>50809</v>
+        <v>50808</v>
       </c>
       <c r="B254" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>4</v>
@@ -5160,24 +5163,24 @@
     </row>
     <row r="255" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A255" s="6">
-        <v>50810</v>
+        <v>50809</v>
       </c>
       <c r="B255" t="s">
-        <v>175</v>
+        <v>98</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D255" s="1" t="s">
-        <v>8</v>
+      <c r="D255" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="256" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A256" s="6">
-        <v>50812</v>
+        <v>50810</v>
       </c>
       <c r="B256" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>4</v>
@@ -5188,80 +5191,80 @@
     </row>
     <row r="257" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A257" s="6">
-        <v>50813</v>
+        <v>50812</v>
       </c>
       <c r="B257" t="s">
-        <v>71</v>
+        <v>184</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D257" s="17" t="s">
-        <v>9</v>
+      <c r="D257" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="258" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A258" s="6">
-        <v>50815</v>
+        <v>50813</v>
       </c>
       <c r="B258" t="s">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D258" s="10" t="s">
-        <v>8</v>
+      <c r="D258" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="259" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A259" s="6">
-        <v>50816</v>
+        <v>50815</v>
       </c>
       <c r="B259" t="s">
-        <v>205</v>
+        <v>114</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D259" s="1" t="s">
+      <c r="D259" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="260" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A260" s="6">
-        <v>50818</v>
+        <v>50816</v>
       </c>
       <c r="B260" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D260" s="13" t="s">
-        <v>5</v>
+      <c r="D260" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="261" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A261" s="6">
-        <v>50819</v>
+        <v>50818</v>
       </c>
       <c r="B261" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D261" s="10" t="s">
-        <v>8</v>
+      <c r="D261" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="262" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A262" s="6">
-        <v>50820</v>
+        <v>50819</v>
       </c>
       <c r="B262" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>4</v>
@@ -5272,66 +5275,66 @@
     </row>
     <row r="263" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A263" s="6">
-        <v>50821</v>
+        <v>50820</v>
       </c>
       <c r="B263" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D263" s="1" t="s">
+      <c r="D263" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="264" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A264" s="6">
-        <v>50823</v>
+        <v>50821</v>
       </c>
       <c r="B264" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D264" s="17" t="s">
-        <v>9</v>
+      <c r="D264" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="265" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A265" s="6">
-        <v>50824</v>
+        <v>50823</v>
       </c>
       <c r="B265" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D265" s="13" t="s">
-        <v>5</v>
+      <c r="D265" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="266" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A266" s="6">
-        <v>50825</v>
+        <v>50824</v>
       </c>
       <c r="B266" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D266" s="10" t="s">
-        <v>8</v>
+      <c r="D266" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="267" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A267" s="6">
-        <v>50826</v>
+        <v>50825</v>
       </c>
       <c r="B267" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>4</v>
@@ -5342,24 +5345,24 @@
     </row>
     <row r="268" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A268" s="6">
-        <v>50827</v>
+        <v>50826</v>
       </c>
       <c r="B268" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D268" s="1" t="s">
+      <c r="D268" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="269" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A269" s="6">
-        <v>50829</v>
+        <v>50827</v>
       </c>
       <c r="B269" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>4</v>
@@ -5370,122 +5373,122 @@
     </row>
     <row r="270" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A270" s="6">
-        <v>50830</v>
+        <v>50829</v>
       </c>
       <c r="B270" t="s">
-        <v>366</v>
+        <v>236</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D270" s="11" t="s">
+      <c r="D270" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="271" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A271" s="6">
-        <v>50831</v>
+        <v>50830</v>
       </c>
       <c r="B271" t="s">
-        <v>351</v>
+        <v>366</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D271" s="11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="272" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A272" s="6">
-        <v>50832</v>
-      </c>
-      <c r="B272" s="8" t="s">
-        <v>349</v>
+        <v>50831</v>
+      </c>
+      <c r="B272" t="s">
+        <v>351</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D272" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="273" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A273" s="6">
-        <v>50833</v>
+        <v>50832</v>
       </c>
       <c r="B273" s="8" t="s">
-        <v>397</v>
+        <v>349</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D273" s="11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="274" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A274" s="6">
-        <v>50230</v>
+        <v>50833</v>
       </c>
       <c r="B274" s="8" t="s">
-        <v>379</v>
+        <v>397</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D274" s="11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="275" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A275" s="6">
-        <v>60103</v>
-      </c>
-      <c r="B275" t="s">
-        <v>237</v>
+        <v>50230</v>
+      </c>
+      <c r="B275" s="8" t="s">
+        <v>379</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D275" s="13" t="s">
+      <c r="D275" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="276" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A276" s="6">
-        <v>60109</v>
+        <v>60103</v>
       </c>
       <c r="B276" t="s">
-        <v>328</v>
+        <v>237</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D276" s="11" t="s">
-        <v>9</v>
+      <c r="D276" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="277" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A277" s="6">
-        <v>60124</v>
+        <v>60109</v>
       </c>
       <c r="B277" t="s">
-        <v>238</v>
+        <v>328</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D277" s="13" t="s">
-        <v>5</v>
+      <c r="D277" s="11" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="278" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A278" s="6">
-        <v>60125</v>
+        <v>60124</v>
       </c>
       <c r="B278" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>4</v>
@@ -5496,80 +5499,80 @@
     </row>
     <row r="279" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A279" s="6">
-        <v>60126</v>
+        <v>60125</v>
       </c>
       <c r="B279" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D279" s="10" t="s">
-        <v>8</v>
+      <c r="D279" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="280" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A280" s="6">
-        <v>60128</v>
+        <v>60126</v>
       </c>
       <c r="B280" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D280" s="3" t="s">
-        <v>5</v>
+      <c r="D280" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="281" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A281" s="6">
-        <v>60130</v>
+        <v>60128</v>
       </c>
       <c r="B281" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D281" s="1" t="s">
-        <v>8</v>
+      <c r="D281" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="282" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A282" s="6">
-        <v>60133</v>
+        <v>60130</v>
       </c>
       <c r="B282" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D282" s="13" t="s">
-        <v>5</v>
+      <c r="D282" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="283" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A283" s="6">
-        <v>60134</v>
+        <v>60133</v>
       </c>
       <c r="B283" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D283" s="1" t="s">
-        <v>8</v>
+      <c r="D283" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="284" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A284" s="6">
-        <v>60137</v>
+        <v>60134</v>
       </c>
       <c r="B284" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>4</v>
@@ -5580,10 +5583,10 @@
     </row>
     <row r="285" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A285" s="6">
-        <v>60139</v>
+        <v>60137</v>
       </c>
       <c r="B285" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>4</v>
@@ -5594,10 +5597,10 @@
     </row>
     <row r="286" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A286" s="6">
-        <v>60142</v>
+        <v>60139</v>
       </c>
       <c r="B286" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>4</v>
@@ -5608,10 +5611,10 @@
     </row>
     <row r="287" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A287" s="6">
-        <v>60148</v>
+        <v>60142</v>
       </c>
       <c r="B287" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>4</v>
@@ -5622,10 +5625,10 @@
     </row>
     <row r="288" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A288" s="6">
-        <v>60149</v>
+        <v>60148</v>
       </c>
       <c r="B288" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>4</v>
@@ -5636,66 +5639,66 @@
     </row>
     <row r="289" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A289" s="6">
-        <v>60150</v>
+        <v>60149</v>
       </c>
       <c r="B289" t="s">
-        <v>332</v>
+        <v>249</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D289" s="13" t="s">
-        <v>5</v>
+      <c r="D289" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="290" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A290" s="6">
-        <v>60158</v>
+        <v>60150</v>
       </c>
       <c r="B290" t="s">
-        <v>250</v>
+        <v>332</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D290" s="10" t="s">
-        <v>8</v>
+      <c r="D290" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="291" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A291" s="6">
-        <v>60159</v>
+        <v>60158</v>
       </c>
       <c r="B291" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D291" s="1" t="s">
+      <c r="D291" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="292" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A292" s="6">
-        <v>60162</v>
+        <v>60159</v>
       </c>
       <c r="B292" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D292" s="13" t="s">
-        <v>5</v>
+      <c r="D292" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="293" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A293" s="6">
-        <v>60163</v>
+        <v>60162</v>
       </c>
       <c r="B293" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>4</v>
@@ -5706,24 +5709,24 @@
     </row>
     <row r="294" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A294" s="6">
-        <v>60165</v>
+        <v>60163</v>
       </c>
       <c r="B294" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D294" s="1" t="s">
-        <v>8</v>
+      <c r="D294" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="295" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A295" s="6">
-        <v>60169</v>
+        <v>60165</v>
       </c>
       <c r="B295" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>4</v>
@@ -5734,52 +5737,52 @@
     </row>
     <row r="296" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A296" s="6">
-        <v>60170</v>
-      </c>
-      <c r="B296" s="8" t="s">
-        <v>337</v>
+        <v>60169</v>
+      </c>
+      <c r="B296" t="s">
+        <v>255</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D296" s="11" t="s">
+      <c r="D296" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="297" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A297" s="6">
-        <v>60172</v>
-      </c>
-      <c r="B297" t="s">
-        <v>256</v>
+        <v>60170</v>
+      </c>
+      <c r="B297" s="8" t="s">
+        <v>337</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D297" s="1" t="s">
+      <c r="D297" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="298" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A298" s="6">
-        <v>60174</v>
+        <v>60172</v>
       </c>
       <c r="B298" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D298" s="13" t="s">
-        <v>5</v>
+      <c r="D298" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="299" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A299" s="6">
-        <v>60176</v>
+        <v>60174</v>
       </c>
       <c r="B299" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>4</v>
@@ -5790,52 +5793,52 @@
     </row>
     <row r="300" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A300" s="6">
-        <v>60178</v>
+        <v>60176</v>
       </c>
       <c r="B300" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D300" s="1" t="s">
-        <v>8</v>
+      <c r="D300" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="301" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A301" s="6">
-        <v>60180</v>
+        <v>60178</v>
       </c>
       <c r="B301" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D301" s="10" t="s">
+      <c r="D301" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="302" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A302" s="6">
-        <v>60184</v>
+        <v>60180</v>
       </c>
       <c r="B302" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D302" s="1" t="s">
+      <c r="D302" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="303" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A303" s="6">
-        <v>60190</v>
+        <v>60184</v>
       </c>
       <c r="B303" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>4</v>
@@ -5846,24 +5849,24 @@
     </row>
     <row r="304" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A304" s="6">
-        <v>60191</v>
+        <v>60190</v>
       </c>
       <c r="B304" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D304" s="10" t="s">
+      <c r="D304" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="305" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A305" s="6">
-        <v>60192</v>
+        <v>60191</v>
       </c>
       <c r="B305" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>4</v>
@@ -5874,10 +5877,10 @@
     </row>
     <row r="306" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A306" s="6">
-        <v>60195</v>
+        <v>60192</v>
       </c>
       <c r="B306" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>4</v>
@@ -5888,10 +5891,10 @@
     </row>
     <row r="307" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A307" s="6">
-        <v>60196</v>
+        <v>60195</v>
       </c>
       <c r="B307" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>4</v>
@@ -5902,10 +5905,10 @@
     </row>
     <row r="308" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A308" s="6">
-        <v>60198</v>
+        <v>60196</v>
       </c>
       <c r="B308" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>4</v>
@@ -5916,52 +5919,52 @@
     </row>
     <row r="309" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A309" s="6">
-        <v>60201</v>
+        <v>60198</v>
       </c>
       <c r="B309" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D309" t="s">
-        <v>9</v>
+      <c r="D309" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="310" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A310" s="6">
-        <v>60202</v>
+        <v>60201</v>
       </c>
       <c r="B310" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D310" s="13" t="s">
-        <v>5</v>
+      <c r="D310" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="311" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A311" s="6">
-        <v>60204</v>
+        <v>60202</v>
       </c>
       <c r="B311" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D311" s="1" t="s">
-        <v>8</v>
+      <c r="D311" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="312" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A312" s="6">
-        <v>60205</v>
+        <v>60204</v>
       </c>
       <c r="B312" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>4</v>
@@ -5972,10 +5975,10 @@
     </row>
     <row r="313" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A313" s="6">
-        <v>60206</v>
+        <v>60205</v>
       </c>
       <c r="B313" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>4</v>
@@ -5986,220 +5989,220 @@
     </row>
     <row r="314" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A314" s="6">
-        <v>60209</v>
+        <v>60206</v>
       </c>
       <c r="B314" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D314" s="10" t="s">
+      <c r="D314" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="315" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A315" s="6">
-        <v>60211</v>
+        <v>60209</v>
       </c>
       <c r="B315" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D315" s="1" t="s">
+      <c r="D315" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="316" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A316" s="6">
-        <v>60215</v>
+        <v>60211</v>
       </c>
       <c r="B316" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D316" s="10" t="s">
+      <c r="D316" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="317" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A317" s="6">
-        <v>60216</v>
+        <v>60215</v>
       </c>
       <c r="B317" t="s">
-        <v>381</v>
+        <v>275</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D317" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="318" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A318" s="6">
-        <v>60217</v>
+        <v>60216</v>
       </c>
       <c r="B318" t="s">
-        <v>276</v>
+        <v>381</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D318" s="10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="319" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A319" s="6">
-        <v>60219</v>
+        <v>60217</v>
       </c>
       <c r="B319" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D319" s="1" t="s">
+      <c r="D319" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="320" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A320" s="6">
-        <v>60222</v>
+        <v>60219</v>
       </c>
       <c r="B320" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D320" s="10" t="s">
+      <c r="D320" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="321" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A321" s="6">
-        <v>60225</v>
+        <v>60222</v>
       </c>
       <c r="B321" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D321" s="17" t="s">
-        <v>9</v>
+      <c r="D321" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="322" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A322" s="6">
-        <v>60230</v>
+        <v>60225</v>
       </c>
       <c r="B322" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D322" s="10" t="s">
-        <v>8</v>
+      <c r="D322" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="323" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A323" s="6">
-        <v>60241</v>
-      </c>
-      <c r="B323" s="8" t="s">
-        <v>338</v>
+        <v>60230</v>
+      </c>
+      <c r="B323" t="s">
+        <v>280</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D323" s="7" t="s">
-        <v>9</v>
+      <c r="D323" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="324" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A324" s="6">
-        <v>60242</v>
+        <v>60241</v>
       </c>
       <c r="B324" s="8" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D324" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="325" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A325" s="6">
-        <v>60243</v>
+        <v>60242</v>
       </c>
       <c r="B325" s="8" t="s">
-        <v>395</v>
+        <v>341</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D325" s="7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="326" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A326" s="6">
-        <v>60245</v>
+        <v>60243</v>
       </c>
       <c r="B326" s="8" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D326" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="327" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A327" s="6">
-        <v>60250</v>
+        <v>60245</v>
       </c>
       <c r="B327" s="8" t="s">
-        <v>339</v>
+        <v>387</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D327" s="11" t="s">
-        <v>8</v>
+      <c r="D327" s="7" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="328" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A328" s="6">
-        <v>60253</v>
-      </c>
-      <c r="B328" t="s">
-        <v>281</v>
+        <v>60250</v>
+      </c>
+      <c r="B328" s="8" t="s">
+        <v>339</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D328" s="1" t="s">
+      <c r="D328" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="329" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A329" s="6">
-        <v>60254</v>
+        <v>60253</v>
       </c>
       <c r="B329" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>4</v>
@@ -6210,10 +6213,10 @@
     </row>
     <row r="330" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A330" s="6">
-        <v>60257</v>
+        <v>60254</v>
       </c>
       <c r="B330" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>4</v>
@@ -6224,10 +6227,10 @@
     </row>
     <row r="331" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A331" s="6">
-        <v>60258</v>
+        <v>60257</v>
       </c>
       <c r="B331" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>4</v>
@@ -6238,66 +6241,66 @@
     </row>
     <row r="332" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A332" s="6">
-        <v>60266</v>
-      </c>
-      <c r="B332" s="8" t="s">
-        <v>343</v>
+        <v>60258</v>
+      </c>
+      <c r="B332" t="s">
+        <v>284</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D332" s="11" t="s">
+      <c r="D332" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="333" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A333" s="6">
-        <v>60269</v>
-      </c>
-      <c r="B333" t="s">
-        <v>285</v>
+        <v>60266</v>
+      </c>
+      <c r="B333" s="8" t="s">
+        <v>343</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D333" s="10" t="s">
+      <c r="D333" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="334" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A334" s="6">
-        <v>60270</v>
+        <v>60269</v>
       </c>
       <c r="B334" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D334" s="1" t="s">
-        <v>9</v>
+      <c r="D334" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="335" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A335" s="6">
-        <v>60272</v>
+        <v>60270</v>
       </c>
       <c r="B335" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="336" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A336" s="6">
-        <v>60274</v>
+        <v>60272</v>
       </c>
       <c r="B336" t="s">
-        <v>380</v>
+        <v>287</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>4</v>
@@ -6308,10 +6311,10 @@
     </row>
     <row r="337" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A337" s="6">
-        <v>60275</v>
+        <v>60274</v>
       </c>
       <c r="B337" t="s">
-        <v>288</v>
+        <v>380</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>4</v>
@@ -6322,10 +6325,10 @@
     </row>
     <row r="338" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A338" s="6">
-        <v>60276</v>
+        <v>60275</v>
       </c>
       <c r="B338" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>4</v>
@@ -6336,108 +6339,108 @@
     </row>
     <row r="339" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A339" s="6">
-        <v>60278</v>
+        <v>60276</v>
       </c>
       <c r="B339" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D339" s="13" t="s">
+      <c r="D339" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="340" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A340" s="6">
-        <v>60279</v>
+        <v>60278</v>
       </c>
       <c r="B340" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D340" s="1" t="s">
+      <c r="D340" s="13" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="341" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A341" s="6">
-        <v>60280</v>
+        <v>60279</v>
       </c>
       <c r="B341" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="342" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A342" s="6">
-        <v>60281</v>
-      </c>
-      <c r="B342" s="8" t="s">
-        <v>336</v>
+        <v>60280</v>
+      </c>
+      <c r="B342" t="s">
+        <v>292</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D342" s="11" t="s">
-        <v>9</v>
+      <c r="D342" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="343" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A343" s="6">
-        <v>60282</v>
+        <v>60281</v>
       </c>
       <c r="B343" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D343" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="344" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A344" s="6">
-        <v>60283</v>
-      </c>
-      <c r="B344" t="s">
-        <v>378</v>
+        <v>60282</v>
+      </c>
+      <c r="B344" s="8" t="s">
+        <v>340</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D344" s="1" t="s">
-        <v>8</v>
+      <c r="D344" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="345" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A345" s="6">
-        <v>60284</v>
-      </c>
-      <c r="B345" s="8" t="s">
-        <v>335</v>
+        <v>60283</v>
+      </c>
+      <c r="B345" t="s">
+        <v>378</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D345" s="9" t="s">
-        <v>5</v>
+      <c r="D345" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="346" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A346" s="6">
-        <v>60285</v>
+        <v>60284</v>
       </c>
       <c r="B346" s="8" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>4</v>
@@ -6448,10 +6451,10 @@
     </row>
     <row r="347" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A347" s="6">
-        <v>60286</v>
+        <v>60285</v>
       </c>
       <c r="B347" s="8" t="s">
-        <v>334</v>
+        <v>350</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>4</v>
@@ -6462,52 +6465,52 @@
     </row>
     <row r="348" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A348" s="6">
-        <v>60287</v>
-      </c>
-      <c r="B348" t="s">
-        <v>377</v>
+        <v>60286</v>
+      </c>
+      <c r="B348" s="8" t="s">
+        <v>334</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D348" s="12" t="s">
+      <c r="D348" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="349" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A349" s="6">
-        <v>60289</v>
+        <v>60287</v>
       </c>
       <c r="B349" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D349" s="12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="350" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A350" s="6">
-        <v>60290</v>
+        <v>60289</v>
       </c>
       <c r="B350" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D350" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="351" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A351" s="6">
-        <v>60291</v>
+        <v>60290</v>
       </c>
       <c r="B351" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>4</v>
@@ -6518,24 +6521,24 @@
     </row>
     <row r="352" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A352" s="6">
-        <v>60292</v>
-      </c>
-      <c r="B352" s="18" t="s">
-        <v>400</v>
+        <v>60291</v>
+      </c>
+      <c r="B352" t="s">
+        <v>376</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D352" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="353" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A353" s="6">
-        <v>60296</v>
-      </c>
-      <c r="B353" t="s">
-        <v>391</v>
+        <v>60292</v>
+      </c>
+      <c r="B353" s="18" t="s">
+        <v>400</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>4</v>
@@ -6546,24 +6549,24 @@
     </row>
     <row r="354" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A354" s="6">
-        <v>60297</v>
+        <v>60296</v>
       </c>
       <c r="B354" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D354" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="355" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A355" s="6">
-        <v>60299</v>
+        <v>60297</v>
       </c>
       <c r="B355" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>4</v>
@@ -6574,52 +6577,52 @@
     </row>
     <row r="356" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A356" s="6">
-        <v>61001</v>
+        <v>60299</v>
       </c>
       <c r="B356" t="s">
-        <v>403</v>
+        <v>388</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D356" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="357" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A357" s="6">
-        <v>61004</v>
+        <v>61001</v>
       </c>
       <c r="B357" t="s">
-        <v>293</v>
+        <v>403</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D357" s="15" t="s">
-        <v>5</v>
+      <c r="D357" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="358" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A358" s="6">
-        <v>61009</v>
+        <v>61004</v>
       </c>
       <c r="B358" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D358" s="12" t="s">
-        <v>8</v>
+      <c r="D358" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="359" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A359" s="6">
-        <v>61012</v>
+        <v>61009</v>
       </c>
       <c r="B359" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>4</v>
@@ -6630,10 +6633,10 @@
     </row>
     <row r="360" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A360" s="6">
-        <v>61018</v>
+        <v>61012</v>
       </c>
       <c r="B360" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>4</v>
@@ -6644,10 +6647,10 @@
     </row>
     <row r="361" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A361" s="6">
-        <v>61102</v>
+        <v>61018</v>
       </c>
       <c r="B361" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>4</v>
@@ -6658,52 +6661,52 @@
     </row>
     <row r="362" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A362" s="6">
-        <v>61205</v>
+        <v>61102</v>
       </c>
       <c r="B362" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D362" s="15" t="s">
-        <v>5</v>
+      <c r="D362" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="363" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A363" s="6">
-        <v>70100</v>
+        <v>61205</v>
       </c>
       <c r="B363" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D363" s="12" t="s">
-        <v>8</v>
+      <c r="D363" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="364" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A364" s="6">
-        <v>70101</v>
+        <v>70100</v>
       </c>
       <c r="B364" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D364" s="15" t="s">
-        <v>5</v>
+      <c r="D364" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="365" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A365" s="6">
-        <v>70102</v>
+        <v>70101</v>
       </c>
       <c r="B365" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>4</v>
@@ -6714,80 +6717,80 @@
     </row>
     <row r="366" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A366" s="6">
-        <v>70103</v>
+        <v>70102</v>
       </c>
       <c r="B366" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D366" s="12" t="s">
-        <v>8</v>
+      <c r="D366" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="367" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A367" s="6">
-        <v>70106</v>
+        <v>70103</v>
       </c>
       <c r="B367" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D367" s="15" t="s">
-        <v>5</v>
+      <c r="D367" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="368" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A368" s="6">
-        <v>70109</v>
+        <v>70106</v>
       </c>
       <c r="B368" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D368" s="12" t="s">
-        <v>8</v>
+      <c r="D368" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="369" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A369" s="6">
-        <v>70113</v>
+        <v>70109</v>
       </c>
       <c r="B369" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D369" s="15" t="s">
-        <v>5</v>
+      <c r="D369" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="370" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A370" s="6">
-        <v>70114</v>
+        <v>70113</v>
       </c>
       <c r="B370" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D370" s="9" t="s">
-        <v>9</v>
+      <c r="D370" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="371" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A371" s="6">
-        <v>70115</v>
+        <v>70114</v>
       </c>
       <c r="B371" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>4</v>
@@ -6798,24 +6801,24 @@
     </row>
     <row r="372" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A372" s="6">
-        <v>70638</v>
+        <v>70115</v>
       </c>
       <c r="B372" t="s">
-        <v>306</v>
+        <v>331</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D372" s="12" t="s">
-        <v>8</v>
+      <c r="D372" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="373" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A373" s="6">
-        <v>70639</v>
+        <v>70638</v>
       </c>
       <c r="B373" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>4</v>
@@ -6826,10 +6829,10 @@
     </row>
     <row r="374" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A374" s="6">
-        <v>70640</v>
+        <v>70639</v>
       </c>
       <c r="B374" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>4</v>
@@ -6840,10 +6843,10 @@
     </row>
     <row r="375" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A375" s="6">
-        <v>70642</v>
+        <v>70640</v>
       </c>
       <c r="B375" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>4</v>
@@ -6854,10 +6857,10 @@
     </row>
     <row r="376" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A376" s="6">
-        <v>90504</v>
+        <v>70642</v>
       </c>
       <c r="B376" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>4</v>
@@ -6868,10 +6871,10 @@
     </row>
     <row r="377" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A377" s="6">
-        <v>90509</v>
+        <v>90504</v>
       </c>
       <c r="B377" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>4</v>
@@ -6882,52 +6885,52 @@
     </row>
     <row r="378" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A378" s="6">
-        <v>90602</v>
+        <v>90509</v>
       </c>
       <c r="B378" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D378" s="15" t="s">
-        <v>5</v>
+      <c r="D378" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="379" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A379" s="6">
-        <v>90621</v>
+        <v>90602</v>
       </c>
       <c r="B379" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D379" s="12" t="s">
-        <v>8</v>
+      <c r="D379" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="380" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A380" s="6">
-        <v>90622</v>
+        <v>90621</v>
       </c>
       <c r="B380" t="s">
-        <v>333</v>
+        <v>313</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D380" s="9" t="s">
-        <v>5</v>
+      <c r="D380" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="381" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A381" s="6">
-        <v>90631</v>
-      </c>
-      <c r="B381" s="8" t="s">
-        <v>342</v>
+        <v>90622</v>
+      </c>
+      <c r="B381" t="s">
+        <v>333</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>4</v>
@@ -6938,24 +6941,24 @@
     </row>
     <row r="382" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A382" s="6">
-        <v>90658</v>
-      </c>
-      <c r="B382" t="s">
-        <v>314</v>
+        <v>90631</v>
+      </c>
+      <c r="B382" s="8" t="s">
+        <v>342</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D382" s="12" t="s">
-        <v>8</v>
+      <c r="D382" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="383" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A383" s="6">
-        <v>90660</v>
+        <v>90658</v>
       </c>
       <c r="B383" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>4</v>
@@ -6966,10 +6969,10 @@
     </row>
     <row r="384" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A384" s="6">
-        <v>90668</v>
+        <v>90660</v>
       </c>
       <c r="B384" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>4</v>
@@ -6980,10 +6983,10 @@
     </row>
     <row r="385" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A385" s="6">
-        <v>90671</v>
+        <v>90668</v>
       </c>
       <c r="B385" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>4</v>
@@ -6994,10 +6997,10 @@
     </row>
     <row r="386" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A386" s="6">
-        <v>90679</v>
+        <v>90671</v>
       </c>
       <c r="B386" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>4</v>
@@ -7008,10 +7011,10 @@
     </row>
     <row r="387" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A387" s="6">
-        <v>90683</v>
+        <v>90679</v>
       </c>
       <c r="B387" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>4</v>
@@ -7022,10 +7025,10 @@
     </row>
     <row r="388" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A388" s="6">
-        <v>90705</v>
+        <v>90683</v>
       </c>
       <c r="B388" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>4</v>
@@ -7036,10 +7039,10 @@
     </row>
     <row r="389" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A389" s="6">
-        <v>90706</v>
+        <v>90705</v>
       </c>
       <c r="B389" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>4</v>
@@ -7050,10 +7053,10 @@
     </row>
     <row r="390" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A390" s="6">
-        <v>90708</v>
+        <v>90706</v>
       </c>
       <c r="B390" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>4</v>
@@ -7064,10 +7067,10 @@
     </row>
     <row r="391" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A391" s="6">
-        <v>90709</v>
+        <v>90708</v>
       </c>
       <c r="B391" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>4</v>
@@ -7078,38 +7081,38 @@
     </row>
     <row r="392" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A392" s="6">
-        <v>90713</v>
+        <v>90709</v>
       </c>
       <c r="B392" t="s">
-        <v>402</v>
+        <v>323</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D392" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="393" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A393" s="6">
-        <v>1218</v>
+        <v>90713</v>
       </c>
       <c r="B393" t="s">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D393" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="394" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A394" s="6">
-        <v>1959</v>
-      </c>
-      <c r="B394" s="8" t="s">
-        <v>383</v>
+        <v>1218</v>
+      </c>
+      <c r="B394" t="s">
+        <v>382</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>4</v>
@@ -7120,10 +7123,10 @@
     </row>
     <row r="395" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A395" s="6">
-        <v>5625</v>
+        <v>1959</v>
       </c>
       <c r="B395" s="8" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>4</v>
@@ -7134,10 +7137,10 @@
     </row>
     <row r="396" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A396" s="6">
-        <v>1817</v>
+        <v>5625</v>
       </c>
       <c r="B396" s="8" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>4</v>
@@ -7148,10 +7151,10 @@
     </row>
     <row r="397" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A397" s="6">
-        <v>5737</v>
+        <v>1817</v>
       </c>
       <c r="B397" s="8" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>4</v>
@@ -7162,34 +7165,48 @@
     </row>
     <row r="398" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A398" s="6">
-        <v>60295</v>
+        <v>5737</v>
       </c>
       <c r="B398" s="8" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D398" s="9" t="s">
-        <v>9</v>
+      <c r="D398" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="399" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A399" s="6">
+        <v>60295</v>
+      </c>
+      <c r="B399" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="C399" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D399" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A400" s="6">
         <v>1045</v>
       </c>
-      <c r="B399" s="8" t="s">
+      <c r="B400" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="C399" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D399" s="9" t="s">
+      <c r="C400" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D400" s="9" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D344"/>
+  <autoFilter ref="A1:D345"/>
   <sortState ref="A2:D374">
     <sortCondition ref="A277"/>
   </sortState>

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$345</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$346</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1201" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="408">
   <si>
     <t>CUENTA</t>
   </si>
@@ -1243,6 +1243,9 @@
   </si>
   <si>
     <t>FERRETERIA MONCHO</t>
+  </si>
+  <si>
+    <t>FERRETERIA PEPITO</t>
   </si>
 </sst>
 </file>
@@ -1597,7 +1600,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D400"/>
+  <dimension ref="A1:D401"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -6185,38 +6188,38 @@
     </row>
     <row r="328" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A328" s="6">
-        <v>60250</v>
+        <v>60246</v>
       </c>
       <c r="B328" s="8" t="s">
-        <v>339</v>
+        <v>407</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D328" s="11" t="s">
-        <v>8</v>
+      <c r="D328" s="7" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="329" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A329" s="6">
-        <v>60253</v>
-      </c>
-      <c r="B329" t="s">
-        <v>281</v>
+        <v>60250</v>
+      </c>
+      <c r="B329" s="8" t="s">
+        <v>339</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D329" s="1" t="s">
+      <c r="D329" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="330" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A330" s="6">
-        <v>60254</v>
+        <v>60253</v>
       </c>
       <c r="B330" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>4</v>
@@ -6227,10 +6230,10 @@
     </row>
     <row r="331" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A331" s="6">
-        <v>60257</v>
+        <v>60254</v>
       </c>
       <c r="B331" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>4</v>
@@ -6241,10 +6244,10 @@
     </row>
     <row r="332" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A332" s="6">
-        <v>60258</v>
+        <v>60257</v>
       </c>
       <c r="B332" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>4</v>
@@ -6255,66 +6258,66 @@
     </row>
     <row r="333" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A333" s="6">
-        <v>60266</v>
-      </c>
-      <c r="B333" s="8" t="s">
-        <v>343</v>
+        <v>60258</v>
+      </c>
+      <c r="B333" t="s">
+        <v>284</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D333" s="11" t="s">
+      <c r="D333" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="334" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A334" s="6">
-        <v>60269</v>
-      </c>
-      <c r="B334" t="s">
-        <v>285</v>
+        <v>60266</v>
+      </c>
+      <c r="B334" s="8" t="s">
+        <v>343</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D334" s="10" t="s">
+      <c r="D334" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="335" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A335" s="6">
-        <v>60270</v>
+        <v>60269</v>
       </c>
       <c r="B335" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D335" s="1" t="s">
-        <v>9</v>
+      <c r="D335" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="336" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A336" s="6">
-        <v>60272</v>
+        <v>60270</v>
       </c>
       <c r="B336" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="337" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A337" s="6">
-        <v>60274</v>
+        <v>60272</v>
       </c>
       <c r="B337" t="s">
-        <v>380</v>
+        <v>287</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>4</v>
@@ -6325,10 +6328,10 @@
     </row>
     <row r="338" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A338" s="6">
-        <v>60275</v>
+        <v>60274</v>
       </c>
       <c r="B338" t="s">
-        <v>288</v>
+        <v>380</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>4</v>
@@ -6339,10 +6342,10 @@
     </row>
     <row r="339" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A339" s="6">
-        <v>60276</v>
+        <v>60275</v>
       </c>
       <c r="B339" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>4</v>
@@ -6353,108 +6356,108 @@
     </row>
     <row r="340" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A340" s="6">
-        <v>60278</v>
+        <v>60276</v>
       </c>
       <c r="B340" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D340" s="13" t="s">
+      <c r="D340" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="341" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A341" s="6">
-        <v>60279</v>
+        <v>60278</v>
       </c>
       <c r="B341" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D341" s="1" t="s">
+      <c r="D341" s="13" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="342" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A342" s="6">
-        <v>60280</v>
+        <v>60279</v>
       </c>
       <c r="B342" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="343" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A343" s="6">
-        <v>60281</v>
-      </c>
-      <c r="B343" s="8" t="s">
-        <v>336</v>
+        <v>60280</v>
+      </c>
+      <c r="B343" t="s">
+        <v>292</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D343" s="11" t="s">
-        <v>9</v>
+      <c r="D343" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="344" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A344" s="6">
-        <v>60282</v>
+        <v>60281</v>
       </c>
       <c r="B344" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D344" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="345" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A345" s="6">
-        <v>60283</v>
-      </c>
-      <c r="B345" t="s">
-        <v>378</v>
+        <v>60282</v>
+      </c>
+      <c r="B345" s="8" t="s">
+        <v>340</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D345" s="1" t="s">
-        <v>8</v>
+      <c r="D345" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="346" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A346" s="6">
-        <v>60284</v>
-      </c>
-      <c r="B346" s="8" t="s">
-        <v>335</v>
+        <v>60283</v>
+      </c>
+      <c r="B346" t="s">
+        <v>378</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D346" s="9" t="s">
-        <v>5</v>
+      <c r="D346" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="347" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A347" s="6">
-        <v>60285</v>
+        <v>60284</v>
       </c>
       <c r="B347" s="8" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>4</v>
@@ -6465,10 +6468,10 @@
     </row>
     <row r="348" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A348" s="6">
-        <v>60286</v>
+        <v>60285</v>
       </c>
       <c r="B348" s="8" t="s">
-        <v>334</v>
+        <v>350</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>4</v>
@@ -6479,52 +6482,52 @@
     </row>
     <row r="349" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A349" s="6">
-        <v>60287</v>
-      </c>
-      <c r="B349" t="s">
-        <v>377</v>
+        <v>60286</v>
+      </c>
+      <c r="B349" s="8" t="s">
+        <v>334</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D349" s="12" t="s">
+      <c r="D349" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="350" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A350" s="6">
-        <v>60289</v>
+        <v>60287</v>
       </c>
       <c r="B350" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D350" s="12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="351" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A351" s="6">
-        <v>60290</v>
+        <v>60289</v>
       </c>
       <c r="B351" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D351" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="352" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A352" s="6">
-        <v>60291</v>
+        <v>60290</v>
       </c>
       <c r="B352" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>4</v>
@@ -6535,24 +6538,24 @@
     </row>
     <row r="353" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A353" s="6">
-        <v>60292</v>
-      </c>
-      <c r="B353" s="18" t="s">
-        <v>400</v>
+        <v>60291</v>
+      </c>
+      <c r="B353" t="s">
+        <v>376</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D353" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="354" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A354" s="6">
-        <v>60296</v>
-      </c>
-      <c r="B354" t="s">
-        <v>391</v>
+        <v>60292</v>
+      </c>
+      <c r="B354" s="18" t="s">
+        <v>400</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>4</v>
@@ -6563,24 +6566,24 @@
     </row>
     <row r="355" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A355" s="6">
-        <v>60297</v>
+        <v>60296</v>
       </c>
       <c r="B355" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D355" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="356" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A356" s="6">
-        <v>60299</v>
+        <v>60297</v>
       </c>
       <c r="B356" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>4</v>
@@ -6591,52 +6594,52 @@
     </row>
     <row r="357" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A357" s="6">
-        <v>61001</v>
+        <v>60299</v>
       </c>
       <c r="B357" t="s">
-        <v>403</v>
+        <v>388</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D357" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="358" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A358" s="6">
-        <v>61004</v>
+        <v>61001</v>
       </c>
       <c r="B358" t="s">
-        <v>293</v>
+        <v>403</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D358" s="15" t="s">
-        <v>5</v>
+      <c r="D358" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="359" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A359" s="6">
-        <v>61009</v>
+        <v>61004</v>
       </c>
       <c r="B359" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D359" s="12" t="s">
-        <v>8</v>
+      <c r="D359" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="360" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A360" s="6">
-        <v>61012</v>
+        <v>61009</v>
       </c>
       <c r="B360" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>4</v>
@@ -6647,10 +6650,10 @@
     </row>
     <row r="361" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A361" s="6">
-        <v>61018</v>
+        <v>61012</v>
       </c>
       <c r="B361" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>4</v>
@@ -6661,10 +6664,10 @@
     </row>
     <row r="362" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A362" s="6">
-        <v>61102</v>
+        <v>61018</v>
       </c>
       <c r="B362" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>4</v>
@@ -6675,52 +6678,52 @@
     </row>
     <row r="363" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A363" s="6">
-        <v>61205</v>
+        <v>61102</v>
       </c>
       <c r="B363" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D363" s="15" t="s">
-        <v>5</v>
+      <c r="D363" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="364" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A364" s="6">
-        <v>70100</v>
+        <v>61205</v>
       </c>
       <c r="B364" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D364" s="12" t="s">
-        <v>8</v>
+      <c r="D364" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="365" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A365" s="6">
-        <v>70101</v>
+        <v>70100</v>
       </c>
       <c r="B365" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D365" s="15" t="s">
-        <v>5</v>
+      <c r="D365" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="366" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A366" s="6">
-        <v>70102</v>
+        <v>70101</v>
       </c>
       <c r="B366" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>4</v>
@@ -6731,80 +6734,80 @@
     </row>
     <row r="367" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A367" s="6">
-        <v>70103</v>
+        <v>70102</v>
       </c>
       <c r="B367" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D367" s="12" t="s">
-        <v>8</v>
+      <c r="D367" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="368" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A368" s="6">
-        <v>70106</v>
+        <v>70103</v>
       </c>
       <c r="B368" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D368" s="15" t="s">
-        <v>5</v>
+      <c r="D368" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="369" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A369" s="6">
-        <v>70109</v>
+        <v>70106</v>
       </c>
       <c r="B369" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D369" s="12" t="s">
-        <v>8</v>
+      <c r="D369" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="370" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A370" s="6">
-        <v>70113</v>
+        <v>70109</v>
       </c>
       <c r="B370" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D370" s="15" t="s">
-        <v>5</v>
+      <c r="D370" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="371" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A371" s="6">
-        <v>70114</v>
+        <v>70113</v>
       </c>
       <c r="B371" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D371" s="9" t="s">
-        <v>9</v>
+      <c r="D371" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="372" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A372" s="6">
-        <v>70115</v>
+        <v>70114</v>
       </c>
       <c r="B372" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>4</v>
@@ -6815,24 +6818,24 @@
     </row>
     <row r="373" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A373" s="6">
-        <v>70638</v>
+        <v>70115</v>
       </c>
       <c r="B373" t="s">
-        <v>306</v>
+        <v>331</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D373" s="12" t="s">
-        <v>8</v>
+      <c r="D373" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="374" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A374" s="6">
-        <v>70639</v>
+        <v>70638</v>
       </c>
       <c r="B374" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>4</v>
@@ -6843,10 +6846,10 @@
     </row>
     <row r="375" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A375" s="6">
-        <v>70640</v>
+        <v>70639</v>
       </c>
       <c r="B375" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>4</v>
@@ -6857,10 +6860,10 @@
     </row>
     <row r="376" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A376" s="6">
-        <v>70642</v>
+        <v>70640</v>
       </c>
       <c r="B376" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>4</v>
@@ -6871,10 +6874,10 @@
     </row>
     <row r="377" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A377" s="6">
-        <v>90504</v>
+        <v>70642</v>
       </c>
       <c r="B377" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>4</v>
@@ -6885,10 +6888,10 @@
     </row>
     <row r="378" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A378" s="6">
-        <v>90509</v>
+        <v>90504</v>
       </c>
       <c r="B378" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>4</v>
@@ -6899,52 +6902,52 @@
     </row>
     <row r="379" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A379" s="6">
-        <v>90602</v>
+        <v>90509</v>
       </c>
       <c r="B379" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D379" s="15" t="s">
-        <v>5</v>
+      <c r="D379" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="380" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A380" s="6">
-        <v>90621</v>
+        <v>90602</v>
       </c>
       <c r="B380" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D380" s="12" t="s">
-        <v>8</v>
+      <c r="D380" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="381" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A381" s="6">
-        <v>90622</v>
+        <v>90621</v>
       </c>
       <c r="B381" t="s">
-        <v>333</v>
+        <v>313</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D381" s="9" t="s">
-        <v>5</v>
+      <c r="D381" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="382" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A382" s="6">
-        <v>90631</v>
-      </c>
-      <c r="B382" s="8" t="s">
-        <v>342</v>
+        <v>90622</v>
+      </c>
+      <c r="B382" t="s">
+        <v>333</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>4</v>
@@ -6955,24 +6958,24 @@
     </row>
     <row r="383" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A383" s="6">
-        <v>90658</v>
-      </c>
-      <c r="B383" t="s">
-        <v>314</v>
+        <v>90631</v>
+      </c>
+      <c r="B383" s="8" t="s">
+        <v>342</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D383" s="12" t="s">
-        <v>8</v>
+      <c r="D383" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="384" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A384" s="6">
-        <v>90660</v>
+        <v>90658</v>
       </c>
       <c r="B384" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>4</v>
@@ -6983,10 +6986,10 @@
     </row>
     <row r="385" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A385" s="6">
-        <v>90668</v>
+        <v>90660</v>
       </c>
       <c r="B385" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>4</v>
@@ -6997,10 +7000,10 @@
     </row>
     <row r="386" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A386" s="6">
-        <v>90671</v>
+        <v>90668</v>
       </c>
       <c r="B386" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>4</v>
@@ -7011,10 +7014,10 @@
     </row>
     <row r="387" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A387" s="6">
-        <v>90679</v>
+        <v>90671</v>
       </c>
       <c r="B387" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>4</v>
@@ -7025,10 +7028,10 @@
     </row>
     <row r="388" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A388" s="6">
-        <v>90683</v>
+        <v>90679</v>
       </c>
       <c r="B388" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>4</v>
@@ -7039,10 +7042,10 @@
     </row>
     <row r="389" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A389" s="6">
-        <v>90705</v>
+        <v>90683</v>
       </c>
       <c r="B389" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>4</v>
@@ -7053,10 +7056,10 @@
     </row>
     <row r="390" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A390" s="6">
-        <v>90706</v>
+        <v>90705</v>
       </c>
       <c r="B390" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>4</v>
@@ -7067,10 +7070,10 @@
     </row>
     <row r="391" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A391" s="6">
-        <v>90708</v>
+        <v>90706</v>
       </c>
       <c r="B391" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>4</v>
@@ -7081,10 +7084,10 @@
     </row>
     <row r="392" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A392" s="6">
-        <v>90709</v>
+        <v>90708</v>
       </c>
       <c r="B392" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>4</v>
@@ -7095,38 +7098,38 @@
     </row>
     <row r="393" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A393" s="6">
-        <v>90713</v>
+        <v>90709</v>
       </c>
       <c r="B393" t="s">
-        <v>402</v>
+        <v>323</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D393" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="394" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A394" s="6">
-        <v>1218</v>
+        <v>90713</v>
       </c>
       <c r="B394" t="s">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D394" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="395" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A395" s="6">
-        <v>1959</v>
-      </c>
-      <c r="B395" s="8" t="s">
-        <v>383</v>
+        <v>1218</v>
+      </c>
+      <c r="B395" t="s">
+        <v>382</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>4</v>
@@ -7137,10 +7140,10 @@
     </row>
     <row r="396" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A396" s="6">
-        <v>5625</v>
+        <v>1959</v>
       </c>
       <c r="B396" s="8" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>4</v>
@@ -7151,10 +7154,10 @@
     </row>
     <row r="397" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A397" s="6">
-        <v>1817</v>
+        <v>5625</v>
       </c>
       <c r="B397" s="8" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>4</v>
@@ -7165,10 +7168,10 @@
     </row>
     <row r="398" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A398" s="6">
-        <v>5737</v>
+        <v>1817</v>
       </c>
       <c r="B398" s="8" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>4</v>
@@ -7179,34 +7182,48 @@
     </row>
     <row r="399" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A399" s="6">
-        <v>60295</v>
+        <v>5737</v>
       </c>
       <c r="B399" s="8" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D399" s="9" t="s">
-        <v>9</v>
+      <c r="D399" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="400" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A400" s="6">
+        <v>60295</v>
+      </c>
+      <c r="B400" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="C400" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D400" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A401" s="6">
         <v>1045</v>
       </c>
-      <c r="B400" s="8" t="s">
+      <c r="B401" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="C400" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D400" s="9" t="s">
+      <c r="C401" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D401" s="9" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D345"/>
+  <autoFilter ref="A1:D346"/>
   <sortState ref="A2:D374">
     <sortCondition ref="A277"/>
   </sortState>

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$346</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$347</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1207" uniqueCount="409">
   <si>
     <t>CUENTA</t>
   </si>
@@ -1246,6 +1246,9 @@
   </si>
   <si>
     <t>FERRETERIA PEPITO</t>
+  </si>
+  <si>
+    <t>FERRETERIA GUATEMALA</t>
   </si>
 </sst>
 </file>
@@ -1600,7 +1603,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D401"/>
+  <dimension ref="A1:D402"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -6202,38 +6205,38 @@
     </row>
     <row r="329" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A329" s="6">
-        <v>60250</v>
-      </c>
-      <c r="B329" s="8" t="s">
-        <v>339</v>
+        <v>60249</v>
+      </c>
+      <c r="B329" s="18" t="s">
+        <v>408</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D329" s="11" t="s">
-        <v>8</v>
+      <c r="D329" s="7" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="330" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A330" s="6">
-        <v>60253</v>
-      </c>
-      <c r="B330" t="s">
-        <v>281</v>
+        <v>60250</v>
+      </c>
+      <c r="B330" s="8" t="s">
+        <v>339</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D330" s="1" t="s">
+      <c r="D330" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="331" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A331" s="6">
-        <v>60254</v>
+        <v>60253</v>
       </c>
       <c r="B331" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>4</v>
@@ -6244,10 +6247,10 @@
     </row>
     <row r="332" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A332" s="6">
-        <v>60257</v>
+        <v>60254</v>
       </c>
       <c r="B332" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>4</v>
@@ -6258,10 +6261,10 @@
     </row>
     <row r="333" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A333" s="6">
-        <v>60258</v>
+        <v>60257</v>
       </c>
       <c r="B333" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>4</v>
@@ -6272,66 +6275,66 @@
     </row>
     <row r="334" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A334" s="6">
-        <v>60266</v>
-      </c>
-      <c r="B334" s="8" t="s">
-        <v>343</v>
+        <v>60258</v>
+      </c>
+      <c r="B334" t="s">
+        <v>284</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D334" s="11" t="s">
+      <c r="D334" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="335" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A335" s="6">
-        <v>60269</v>
-      </c>
-      <c r="B335" t="s">
-        <v>285</v>
+        <v>60266</v>
+      </c>
+      <c r="B335" s="8" t="s">
+        <v>343</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D335" s="10" t="s">
+      <c r="D335" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="336" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A336" s="6">
-        <v>60270</v>
+        <v>60269</v>
       </c>
       <c r="B336" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D336" s="1" t="s">
-        <v>9</v>
+      <c r="D336" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="337" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A337" s="6">
-        <v>60272</v>
+        <v>60270</v>
       </c>
       <c r="B337" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="338" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A338" s="6">
-        <v>60274</v>
+        <v>60272</v>
       </c>
       <c r="B338" t="s">
-        <v>380</v>
+        <v>287</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>4</v>
@@ -6342,10 +6345,10 @@
     </row>
     <row r="339" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A339" s="6">
-        <v>60275</v>
+        <v>60274</v>
       </c>
       <c r="B339" t="s">
-        <v>288</v>
+        <v>380</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>4</v>
@@ -6356,10 +6359,10 @@
     </row>
     <row r="340" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A340" s="6">
-        <v>60276</v>
+        <v>60275</v>
       </c>
       <c r="B340" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>4</v>
@@ -6370,108 +6373,108 @@
     </row>
     <row r="341" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A341" s="6">
-        <v>60278</v>
+        <v>60276</v>
       </c>
       <c r="B341" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D341" s="13" t="s">
+      <c r="D341" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="342" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A342" s="6">
-        <v>60279</v>
+        <v>60278</v>
       </c>
       <c r="B342" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D342" s="1" t="s">
+      <c r="D342" s="13" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="343" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A343" s="6">
-        <v>60280</v>
+        <v>60279</v>
       </c>
       <c r="B343" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="344" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A344" s="6">
-        <v>60281</v>
-      </c>
-      <c r="B344" s="8" t="s">
-        <v>336</v>
+        <v>60280</v>
+      </c>
+      <c r="B344" t="s">
+        <v>292</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D344" s="11" t="s">
-        <v>9</v>
+      <c r="D344" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="345" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A345" s="6">
-        <v>60282</v>
+        <v>60281</v>
       </c>
       <c r="B345" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D345" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="346" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A346" s="6">
-        <v>60283</v>
-      </c>
-      <c r="B346" t="s">
-        <v>378</v>
+        <v>60282</v>
+      </c>
+      <c r="B346" s="8" t="s">
+        <v>340</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D346" s="1" t="s">
-        <v>8</v>
+      <c r="D346" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="347" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A347" s="6">
-        <v>60284</v>
-      </c>
-      <c r="B347" s="8" t="s">
-        <v>335</v>
+        <v>60283</v>
+      </c>
+      <c r="B347" t="s">
+        <v>378</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D347" s="9" t="s">
-        <v>5</v>
+      <c r="D347" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="348" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A348" s="6">
-        <v>60285</v>
+        <v>60284</v>
       </c>
       <c r="B348" s="8" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>4</v>
@@ -6482,10 +6485,10 @@
     </row>
     <row r="349" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A349" s="6">
-        <v>60286</v>
+        <v>60285</v>
       </c>
       <c r="B349" s="8" t="s">
-        <v>334</v>
+        <v>350</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>4</v>
@@ -6496,52 +6499,52 @@
     </row>
     <row r="350" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A350" s="6">
-        <v>60287</v>
-      </c>
-      <c r="B350" t="s">
-        <v>377</v>
+        <v>60286</v>
+      </c>
+      <c r="B350" s="8" t="s">
+        <v>334</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D350" s="12" t="s">
+      <c r="D350" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="351" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A351" s="6">
-        <v>60289</v>
+        <v>60287</v>
       </c>
       <c r="B351" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D351" s="12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="352" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A352" s="6">
-        <v>60290</v>
+        <v>60289</v>
       </c>
       <c r="B352" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D352" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="353" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A353" s="6">
-        <v>60291</v>
+        <v>60290</v>
       </c>
       <c r="B353" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>4</v>
@@ -6552,24 +6555,24 @@
     </row>
     <row r="354" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A354" s="6">
-        <v>60292</v>
-      </c>
-      <c r="B354" s="18" t="s">
-        <v>400</v>
+        <v>60291</v>
+      </c>
+      <c r="B354" t="s">
+        <v>376</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D354" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="355" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A355" s="6">
-        <v>60296</v>
-      </c>
-      <c r="B355" t="s">
-        <v>391</v>
+        <v>60292</v>
+      </c>
+      <c r="B355" s="18" t="s">
+        <v>400</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>4</v>
@@ -6580,24 +6583,24 @@
     </row>
     <row r="356" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A356" s="6">
-        <v>60297</v>
+        <v>60296</v>
       </c>
       <c r="B356" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D356" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="357" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A357" s="6">
-        <v>60299</v>
+        <v>60297</v>
       </c>
       <c r="B357" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>4</v>
@@ -6608,52 +6611,52 @@
     </row>
     <row r="358" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A358" s="6">
-        <v>61001</v>
+        <v>60299</v>
       </c>
       <c r="B358" t="s">
-        <v>403</v>
+        <v>388</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D358" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="359" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A359" s="6">
-        <v>61004</v>
+        <v>61001</v>
       </c>
       <c r="B359" t="s">
-        <v>293</v>
+        <v>403</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D359" s="15" t="s">
-        <v>5</v>
+      <c r="D359" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="360" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A360" s="6">
-        <v>61009</v>
+        <v>61004</v>
       </c>
       <c r="B360" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D360" s="12" t="s">
-        <v>8</v>
+      <c r="D360" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="361" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A361" s="6">
-        <v>61012</v>
+        <v>61009</v>
       </c>
       <c r="B361" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>4</v>
@@ -6664,10 +6667,10 @@
     </row>
     <row r="362" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A362" s="6">
-        <v>61018</v>
+        <v>61012</v>
       </c>
       <c r="B362" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>4</v>
@@ -6678,10 +6681,10 @@
     </row>
     <row r="363" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A363" s="6">
-        <v>61102</v>
+        <v>61018</v>
       </c>
       <c r="B363" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>4</v>
@@ -6692,52 +6695,52 @@
     </row>
     <row r="364" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A364" s="6">
-        <v>61205</v>
+        <v>61102</v>
       </c>
       <c r="B364" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D364" s="15" t="s">
-        <v>5</v>
+      <c r="D364" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="365" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A365" s="6">
-        <v>70100</v>
+        <v>61205</v>
       </c>
       <c r="B365" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D365" s="12" t="s">
-        <v>8</v>
+      <c r="D365" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="366" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A366" s="6">
-        <v>70101</v>
+        <v>70100</v>
       </c>
       <c r="B366" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D366" s="15" t="s">
-        <v>5</v>
+      <c r="D366" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="367" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A367" s="6">
-        <v>70102</v>
+        <v>70101</v>
       </c>
       <c r="B367" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>4</v>
@@ -6748,80 +6751,80 @@
     </row>
     <row r="368" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A368" s="6">
-        <v>70103</v>
+        <v>70102</v>
       </c>
       <c r="B368" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D368" s="12" t="s">
-        <v>8</v>
+      <c r="D368" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="369" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A369" s="6">
-        <v>70106</v>
+        <v>70103</v>
       </c>
       <c r="B369" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D369" s="15" t="s">
-        <v>5</v>
+      <c r="D369" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="370" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A370" s="6">
-        <v>70109</v>
+        <v>70106</v>
       </c>
       <c r="B370" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D370" s="12" t="s">
-        <v>8</v>
+      <c r="D370" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="371" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A371" s="6">
-        <v>70113</v>
+        <v>70109</v>
       </c>
       <c r="B371" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D371" s="15" t="s">
-        <v>5</v>
+      <c r="D371" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="372" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A372" s="6">
-        <v>70114</v>
+        <v>70113</v>
       </c>
       <c r="B372" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D372" s="9" t="s">
-        <v>9</v>
+      <c r="D372" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="373" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A373" s="6">
-        <v>70115</v>
+        <v>70114</v>
       </c>
       <c r="B373" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>4</v>
@@ -6832,24 +6835,24 @@
     </row>
     <row r="374" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A374" s="6">
-        <v>70638</v>
+        <v>70115</v>
       </c>
       <c r="B374" t="s">
-        <v>306</v>
+        <v>331</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D374" s="12" t="s">
-        <v>8</v>
+      <c r="D374" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="375" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A375" s="6">
-        <v>70639</v>
+        <v>70638</v>
       </c>
       <c r="B375" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>4</v>
@@ -6860,10 +6863,10 @@
     </row>
     <row r="376" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A376" s="6">
-        <v>70640</v>
+        <v>70639</v>
       </c>
       <c r="B376" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>4</v>
@@ -6874,10 +6877,10 @@
     </row>
     <row r="377" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A377" s="6">
-        <v>70642</v>
+        <v>70640</v>
       </c>
       <c r="B377" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>4</v>
@@ -6888,10 +6891,10 @@
     </row>
     <row r="378" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A378" s="6">
-        <v>90504</v>
+        <v>70642</v>
       </c>
       <c r="B378" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>4</v>
@@ -6902,10 +6905,10 @@
     </row>
     <row r="379" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A379" s="6">
-        <v>90509</v>
+        <v>90504</v>
       </c>
       <c r="B379" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>4</v>
@@ -6916,52 +6919,52 @@
     </row>
     <row r="380" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A380" s="6">
-        <v>90602</v>
+        <v>90509</v>
       </c>
       <c r="B380" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D380" s="15" t="s">
-        <v>5</v>
+      <c r="D380" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="381" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A381" s="6">
-        <v>90621</v>
+        <v>90602</v>
       </c>
       <c r="B381" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D381" s="12" t="s">
-        <v>8</v>
+      <c r="D381" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="382" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A382" s="6">
-        <v>90622</v>
+        <v>90621</v>
       </c>
       <c r="B382" t="s">
-        <v>333</v>
+        <v>313</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D382" s="9" t="s">
-        <v>5</v>
+      <c r="D382" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="383" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A383" s="6">
-        <v>90631</v>
-      </c>
-      <c r="B383" s="8" t="s">
-        <v>342</v>
+        <v>90622</v>
+      </c>
+      <c r="B383" t="s">
+        <v>333</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>4</v>
@@ -6972,24 +6975,24 @@
     </row>
     <row r="384" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A384" s="6">
-        <v>90658</v>
-      </c>
-      <c r="B384" t="s">
-        <v>314</v>
+        <v>90631</v>
+      </c>
+      <c r="B384" s="8" t="s">
+        <v>342</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D384" s="12" t="s">
-        <v>8</v>
+      <c r="D384" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="385" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A385" s="6">
-        <v>90660</v>
+        <v>90658</v>
       </c>
       <c r="B385" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>4</v>
@@ -7000,10 +7003,10 @@
     </row>
     <row r="386" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A386" s="6">
-        <v>90668</v>
+        <v>90660</v>
       </c>
       <c r="B386" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>4</v>
@@ -7014,10 +7017,10 @@
     </row>
     <row r="387" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A387" s="6">
-        <v>90671</v>
+        <v>90668</v>
       </c>
       <c r="B387" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>4</v>
@@ -7028,10 +7031,10 @@
     </row>
     <row r="388" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A388" s="6">
-        <v>90679</v>
+        <v>90671</v>
       </c>
       <c r="B388" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>4</v>
@@ -7042,10 +7045,10 @@
     </row>
     <row r="389" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A389" s="6">
-        <v>90683</v>
+        <v>90679</v>
       </c>
       <c r="B389" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>4</v>
@@ -7056,10 +7059,10 @@
     </row>
     <row r="390" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A390" s="6">
-        <v>90705</v>
+        <v>90683</v>
       </c>
       <c r="B390" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>4</v>
@@ -7070,10 +7073,10 @@
     </row>
     <row r="391" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A391" s="6">
-        <v>90706</v>
+        <v>90705</v>
       </c>
       <c r="B391" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>4</v>
@@ -7084,10 +7087,10 @@
     </row>
     <row r="392" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A392" s="6">
-        <v>90708</v>
+        <v>90706</v>
       </c>
       <c r="B392" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>4</v>
@@ -7098,10 +7101,10 @@
     </row>
     <row r="393" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A393" s="6">
-        <v>90709</v>
+        <v>90708</v>
       </c>
       <c r="B393" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>4</v>
@@ -7112,38 +7115,38 @@
     </row>
     <row r="394" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A394" s="6">
-        <v>90713</v>
+        <v>90709</v>
       </c>
       <c r="B394" t="s">
-        <v>402</v>
+        <v>323</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D394" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="395" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A395" s="6">
-        <v>1218</v>
+        <v>90713</v>
       </c>
       <c r="B395" t="s">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D395" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="396" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A396" s="6">
-        <v>1959</v>
-      </c>
-      <c r="B396" s="8" t="s">
-        <v>383</v>
+        <v>1218</v>
+      </c>
+      <c r="B396" t="s">
+        <v>382</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>4</v>
@@ -7154,10 +7157,10 @@
     </row>
     <row r="397" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A397" s="6">
-        <v>5625</v>
+        <v>1959</v>
       </c>
       <c r="B397" s="8" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>4</v>
@@ -7168,10 +7171,10 @@
     </row>
     <row r="398" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A398" s="6">
-        <v>1817</v>
+        <v>5625</v>
       </c>
       <c r="B398" s="8" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>4</v>
@@ -7182,10 +7185,10 @@
     </row>
     <row r="399" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A399" s="6">
-        <v>5737</v>
+        <v>1817</v>
       </c>
       <c r="B399" s="8" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>4</v>
@@ -7196,34 +7199,48 @@
     </row>
     <row r="400" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A400" s="6">
-        <v>60295</v>
+        <v>5737</v>
       </c>
       <c r="B400" s="8" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C400" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D400" s="9" t="s">
-        <v>9</v>
+      <c r="D400" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="401" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A401" s="6">
+        <v>60295</v>
+      </c>
+      <c r="B401" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="C401" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D401" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A402" s="6">
         <v>1045</v>
       </c>
-      <c r="B401" s="8" t="s">
+      <c r="B402" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="C401" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D401" s="9" t="s">
+      <c r="C402" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D402" s="9" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D346"/>
+  <autoFilter ref="A1:D347"/>
   <sortState ref="A2:D374">
     <sortCondition ref="A277"/>
   </sortState>

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$347</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$348</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1207" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1210" uniqueCount="410">
   <si>
     <t>CUENTA</t>
   </si>
@@ -1249,6 +1249,9 @@
   </si>
   <si>
     <t>FERRETERIA GUATEMALA</t>
+  </si>
+  <si>
+    <t>FERRETERIA BM</t>
   </si>
 </sst>
 </file>
@@ -1603,7 +1606,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D402"/>
+  <dimension ref="A1:D403"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -2817,52 +2820,52 @@
     </row>
     <row r="87" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="6">
-        <v>1416</v>
-      </c>
-      <c r="B87" t="s">
-        <v>217</v>
+        <v>1050</v>
+      </c>
+      <c r="B87" s="18" t="s">
+        <v>409</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D87" s="1" t="s">
-        <v>8</v>
+      <c r="D87" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="6">
-        <v>10107</v>
+        <v>1416</v>
       </c>
       <c r="B88" t="s">
-        <v>96</v>
+        <v>217</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D88" t="s">
-        <v>9</v>
+      <c r="D88" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="6">
-        <v>10137</v>
+        <v>10107</v>
       </c>
       <c r="B89" t="s">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D89" s="1" t="s">
-        <v>8</v>
+      <c r="D89" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="6">
-        <v>10157</v>
+        <v>10137</v>
       </c>
       <c r="B90" t="s">
-        <v>183</v>
+        <v>123</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>4</v>
@@ -2873,10 +2876,10 @@
     </row>
     <row r="91" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="6">
-        <v>10158</v>
+        <v>10157</v>
       </c>
       <c r="B91" t="s">
-        <v>65</v>
+        <v>183</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>4</v>
@@ -2887,108 +2890,108 @@
     </row>
     <row r="92" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="6">
-        <v>10160</v>
+        <v>10158</v>
       </c>
       <c r="B92" t="s">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D92" s="13" t="s">
-        <v>5</v>
+      <c r="D92" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="6">
-        <v>10162</v>
+        <v>10160</v>
       </c>
       <c r="B93" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D93" s="1" t="s">
-        <v>8</v>
+      <c r="D93" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="6">
-        <v>10163</v>
+        <v>10162</v>
       </c>
       <c r="B94" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D94" s="13" t="s">
-        <v>5</v>
+      <c r="D94" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="6">
-        <v>10165</v>
+        <v>10163</v>
       </c>
       <c r="B95" t="s">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D95" s="1" t="s">
-        <v>8</v>
+      <c r="D95" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="6">
-        <v>10166</v>
-      </c>
-      <c r="B96" s="8" t="s">
-        <v>348</v>
+        <v>10165</v>
+      </c>
+      <c r="B96" t="s">
+        <v>19</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D96" s="11" t="s">
+      <c r="D96" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="6">
-        <v>10167</v>
-      </c>
-      <c r="B97" t="s">
-        <v>39</v>
+        <v>10166</v>
+      </c>
+      <c r="B97" s="8" t="s">
+        <v>348</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D97" s="13" t="s">
-        <v>5</v>
+      <c r="D97" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="6">
-        <v>10424</v>
+        <v>10167</v>
       </c>
       <c r="B98" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D98" s="17" t="s">
-        <v>9</v>
+      <c r="D98" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="6">
-        <v>10425</v>
+        <v>10424</v>
       </c>
       <c r="B99" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>4</v>
@@ -2999,24 +3002,24 @@
     </row>
     <row r="100" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="6">
-        <v>20094</v>
+        <v>10425</v>
       </c>
       <c r="B100" t="s">
-        <v>198</v>
+        <v>15</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D100" s="10" t="s">
-        <v>8</v>
+      <c r="D100" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="6">
-        <v>20095</v>
+        <v>20094</v>
       </c>
       <c r="B101" t="s">
-        <v>153</v>
+        <v>198</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>4</v>
@@ -3027,66 +3030,66 @@
     </row>
     <row r="102" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="6">
-        <v>20096</v>
+        <v>20095</v>
       </c>
       <c r="B102" t="s">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D102" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="6">
-        <v>20100</v>
+        <v>20096</v>
       </c>
       <c r="B103" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D103" s="1" t="s">
-        <v>8</v>
+      <c r="D103" s="10" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="6">
-        <v>20101</v>
+        <v>20100</v>
       </c>
       <c r="B104" t="s">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="6">
-        <v>20103</v>
+        <v>20101</v>
       </c>
       <c r="B105" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="6">
-        <v>20106</v>
+        <v>20103</v>
       </c>
       <c r="B106" t="s">
-        <v>155</v>
+        <v>81</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>4</v>
@@ -3097,80 +3100,80 @@
     </row>
     <row r="107" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="6">
-        <v>20108</v>
+        <v>20106</v>
       </c>
       <c r="B107" t="s">
-        <v>219</v>
+        <v>155</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D107" s="10" t="s">
+      <c r="D107" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="6">
-        <v>20109</v>
+        <v>20108</v>
       </c>
       <c r="B108" t="s">
-        <v>53</v>
+        <v>219</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D108" s="1" t="s">
+      <c r="D108" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="6">
-        <v>20110</v>
+        <v>20109</v>
       </c>
       <c r="B109" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D109" s="13" t="s">
-        <v>5</v>
+      <c r="D109" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="6">
-        <v>20113</v>
+        <v>20110</v>
       </c>
       <c r="B110" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D110" s="10" t="s">
-        <v>8</v>
+      <c r="D110" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="6">
-        <v>20114</v>
+        <v>20113</v>
       </c>
       <c r="B111" t="s">
-        <v>126</v>
+        <v>93</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D111" s="1" t="s">
+      <c r="D111" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="6">
-        <v>20116</v>
+        <v>20114</v>
       </c>
       <c r="B112" t="s">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>4</v>
@@ -3181,10 +3184,10 @@
     </row>
     <row r="113" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="6">
-        <v>20117</v>
+        <v>20116</v>
       </c>
       <c r="B113" t="s">
-        <v>186</v>
+        <v>73</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>4</v>
@@ -3195,10 +3198,10 @@
     </row>
     <row r="114" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="6">
-        <v>20118</v>
+        <v>20117</v>
       </c>
       <c r="B114" t="s">
-        <v>160</v>
+        <v>186</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>4</v>
@@ -3209,10 +3212,10 @@
     </row>
     <row r="115" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="6">
-        <v>20120</v>
+        <v>20118</v>
       </c>
       <c r="B115" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>4</v>
@@ -3223,10 +3226,10 @@
     </row>
     <row r="116" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="6">
-        <v>20121</v>
+        <v>20120</v>
       </c>
       <c r="B116" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>4</v>
@@ -3237,38 +3240,38 @@
     </row>
     <row r="117" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="6">
-        <v>20125</v>
+        <v>20121</v>
       </c>
       <c r="B117" t="s">
-        <v>88</v>
+        <v>159</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D117" s="10" t="s">
+      <c r="D117" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="6">
-        <v>20127</v>
+        <v>20125</v>
       </c>
       <c r="B118" t="s">
-        <v>168</v>
+        <v>88</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D118" s="1" t="s">
+      <c r="D118" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="6">
-        <v>20128</v>
+        <v>20127</v>
       </c>
       <c r="B119" t="s">
-        <v>208</v>
+        <v>168</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>4</v>
@@ -3279,52 +3282,52 @@
     </row>
     <row r="120" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="6">
-        <v>20129</v>
+        <v>20128</v>
       </c>
       <c r="B120" t="s">
-        <v>326</v>
+        <v>208</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D120" s="10" t="s">
+      <c r="D120" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="6">
-        <v>20137</v>
+        <v>20129</v>
       </c>
       <c r="B121" t="s">
-        <v>79</v>
+        <v>326</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D121" s="3" t="s">
-        <v>5</v>
+      <c r="D121" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="122" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="6">
-        <v>20138</v>
+        <v>20137</v>
       </c>
       <c r="B122" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D122" s="13" t="s">
+      <c r="D122" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="6">
-        <v>20140</v>
+        <v>20138</v>
       </c>
       <c r="B123" t="s">
-        <v>218</v>
+        <v>113</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>4</v>
@@ -3335,24 +3338,24 @@
     </row>
     <row r="124" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="6">
-        <v>20142</v>
+        <v>20140</v>
       </c>
       <c r="B124" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D124" s="1" t="s">
-        <v>8</v>
+      <c r="D124" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="6">
-        <v>20146</v>
+        <v>20142</v>
       </c>
       <c r="B125" t="s">
-        <v>148</v>
+        <v>193</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>4</v>
@@ -3363,10 +3366,10 @@
     </row>
     <row r="126" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="6">
-        <v>20148</v>
+        <v>20146</v>
       </c>
       <c r="B126" t="s">
-        <v>38</v>
+        <v>148</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>4</v>
@@ -3377,52 +3380,52 @@
     </row>
     <row r="127" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="6">
-        <v>20156</v>
+        <v>20148</v>
       </c>
       <c r="B127" t="s">
-        <v>179</v>
+        <v>38</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D127" s="10" t="s">
+      <c r="D127" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="6">
-        <v>20159</v>
+        <v>20156</v>
       </c>
       <c r="B128" t="s">
-        <v>120</v>
+        <v>179</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D128" s="17" t="s">
-        <v>9</v>
+      <c r="D128" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="6">
-        <v>20160</v>
+        <v>20159</v>
       </c>
       <c r="B129" t="s">
-        <v>224</v>
+        <v>120</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D129" s="10" t="s">
-        <v>8</v>
+      <c r="D129" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="6">
-        <v>20163</v>
+        <v>20160</v>
       </c>
       <c r="B130" t="s">
-        <v>23</v>
+        <v>224</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>4</v>
@@ -3433,52 +3436,52 @@
     </row>
     <row r="131" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="6">
-        <v>20164</v>
+        <v>20163</v>
       </c>
       <c r="B131" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D131" t="s">
-        <v>9</v>
+      <c r="D131" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="6">
-        <v>20165</v>
+        <v>20164</v>
       </c>
       <c r="B132" t="s">
-        <v>131</v>
+        <v>18</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D132" s="10" t="s">
-        <v>8</v>
+      <c r="D132" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="6">
-        <v>20166</v>
+        <v>20165</v>
       </c>
       <c r="B133" t="s">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D133" s="1" t="s">
+      <c r="D133" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="6">
-        <v>20169</v>
+        <v>20166</v>
       </c>
       <c r="B134" t="s">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>4</v>
@@ -3489,38 +3492,38 @@
     </row>
     <row r="135" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="6">
-        <v>20173</v>
+        <v>20169</v>
       </c>
       <c r="B135" t="s">
-        <v>112</v>
+        <v>151</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D135" s="10" t="s">
+      <c r="D135" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="6">
-        <v>20174</v>
+        <v>20173</v>
       </c>
       <c r="B136" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D136" s="1" t="s">
+      <c r="D136" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="6">
-        <v>20178</v>
+        <v>20174</v>
       </c>
       <c r="B137" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>4</v>
@@ -3531,80 +3534,80 @@
     </row>
     <row r="138" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="6">
-        <v>20179</v>
+        <v>20178</v>
       </c>
       <c r="B138" t="s">
-        <v>171</v>
+        <v>117</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D138" t="s">
-        <v>9</v>
+      <c r="D138" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="6">
-        <v>20180</v>
+        <v>20179</v>
       </c>
       <c r="B139" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D139" s="1" t="s">
-        <v>8</v>
+      <c r="D139" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="6">
-        <v>20183</v>
+        <v>20180</v>
       </c>
       <c r="B140" t="s">
-        <v>370</v>
+        <v>149</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D140" s="14" t="s">
-        <v>5</v>
+      <c r="D140" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="6">
-        <v>20189</v>
+        <v>20183</v>
       </c>
       <c r="B141" t="s">
-        <v>329</v>
+        <v>370</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D141" s="1" t="s">
-        <v>8</v>
+      <c r="D141" s="14" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="6">
-        <v>20200</v>
+        <v>20189</v>
       </c>
       <c r="B142" t="s">
-        <v>83</v>
+        <v>329</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D142" s="13" t="s">
-        <v>5</v>
+      <c r="D142" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="6">
-        <v>20201</v>
+        <v>20200</v>
       </c>
       <c r="B143" t="s">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>4</v>
@@ -3615,150 +3618,150 @@
     </row>
     <row r="144" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="6">
-        <v>20204</v>
+        <v>20201</v>
       </c>
       <c r="B144" t="s">
-        <v>57</v>
+        <v>145</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D144" s="10" t="s">
-        <v>8</v>
+      <c r="D144" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="6">
-        <v>20205</v>
+        <v>20204</v>
       </c>
       <c r="B145" t="s">
-        <v>206</v>
+        <v>57</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D145" s="1" t="s">
-        <v>9</v>
+      <c r="D145" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="6">
-        <v>20211</v>
+        <v>20205</v>
       </c>
       <c r="B146" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D146" s="10" t="s">
-        <v>8</v>
+      <c r="D146" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="6">
-        <v>20224</v>
+        <v>20211</v>
       </c>
       <c r="B147" t="s">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D147" s="1" t="s">
+      <c r="D147" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="6">
-        <v>20227</v>
+        <v>20224</v>
       </c>
       <c r="B148" t="s">
-        <v>192</v>
+        <v>85</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D148" s="10" t="s">
+      <c r="D148" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="6">
-        <v>20228</v>
+        <v>20227</v>
       </c>
       <c r="B149" t="s">
-        <v>91</v>
+        <v>192</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D149" s="13" t="s">
-        <v>5</v>
+      <c r="D149" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="6">
-        <v>20230</v>
+        <v>20228</v>
       </c>
       <c r="B150" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D150" s="10" t="s">
-        <v>8</v>
+      <c r="D150" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="6">
-        <v>20234</v>
+        <v>20230</v>
       </c>
       <c r="B151" t="s">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D151" s="13" t="s">
-        <v>5</v>
+      <c r="D151" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="6">
-        <v>20236</v>
+        <v>20234</v>
       </c>
       <c r="B152" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D152" s="3" t="s">
+      <c r="D152" s="13" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="6">
-        <v>20238</v>
+        <v>20236</v>
       </c>
       <c r="B153" t="s">
-        <v>139</v>
+        <v>31</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D153" s="13" t="s">
+      <c r="D153" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="6">
-        <v>20241</v>
+        <v>20238</v>
       </c>
       <c r="B154" t="s">
-        <v>22</v>
+        <v>139</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>4</v>
@@ -3769,24 +3772,24 @@
     </row>
     <row r="155" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="6">
-        <v>20242</v>
+        <v>20241</v>
       </c>
       <c r="B155" t="s">
-        <v>216</v>
+        <v>22</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D155" s="10" t="s">
-        <v>8</v>
+      <c r="D155" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="156" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="6">
-        <v>20244</v>
+        <v>20242</v>
       </c>
       <c r="B156" t="s">
-        <v>124</v>
+        <v>216</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>4</v>
@@ -3797,108 +3800,108 @@
     </row>
     <row r="157" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="6">
-        <v>20246</v>
+        <v>20244</v>
       </c>
       <c r="B157" t="s">
-        <v>14</v>
+        <v>124</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D157" s="13" t="s">
-        <v>5</v>
+      <c r="D157" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="6">
-        <v>20249</v>
+        <v>20246</v>
       </c>
       <c r="B158" t="s">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D158" s="10" t="s">
-        <v>8</v>
+      <c r="D158" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="159" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A159" s="6">
-        <v>20256</v>
+        <v>20249</v>
       </c>
       <c r="B159" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D159" s="1" t="s">
+      <c r="D159" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="160" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="6">
-        <v>20257</v>
+        <v>20256</v>
       </c>
       <c r="B160" t="s">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D160" s="17" t="s">
-        <v>9</v>
+      <c r="D160" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="161" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="6">
-        <v>20258</v>
+        <v>20257</v>
       </c>
       <c r="B161" t="s">
-        <v>199</v>
+        <v>150</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D161" s="1" t="s">
-        <v>8</v>
+      <c r="D161" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="6">
-        <v>20260</v>
+        <v>20258</v>
       </c>
       <c r="B162" t="s">
-        <v>68</v>
+        <v>199</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D162" s="13" t="s">
-        <v>5</v>
+      <c r="D162" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="163" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="6">
-        <v>20261</v>
+        <v>20260</v>
       </c>
       <c r="B163" t="s">
-        <v>207</v>
+        <v>68</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D163" s="10" t="s">
-        <v>8</v>
+      <c r="D163" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="6">
-        <v>20262</v>
+        <v>20261</v>
       </c>
       <c r="B164" t="s">
-        <v>92</v>
+        <v>207</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>4</v>
@@ -3909,206 +3912,206 @@
     </row>
     <row r="165" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="6">
-        <v>20267</v>
+        <v>20262</v>
       </c>
       <c r="B165" t="s">
-        <v>401</v>
+        <v>92</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D165" s="10" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="6">
-        <v>20268</v>
+        <v>20267</v>
       </c>
       <c r="B166" t="s">
-        <v>201</v>
+        <v>401</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D166" s="1" t="s">
-        <v>8</v>
+      <c r="D166" s="10" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="6">
-        <v>20271</v>
+        <v>20268</v>
       </c>
       <c r="B167" t="s">
-        <v>34</v>
+        <v>201</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D167" s="13" t="s">
-        <v>5</v>
+      <c r="D167" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="168" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="6">
-        <v>20272</v>
+        <v>20271</v>
       </c>
       <c r="B168" t="s">
-        <v>178</v>
+        <v>34</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D168" s="1" t="s">
-        <v>8</v>
+      <c r="D168" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="6">
-        <v>20275</v>
+        <v>20272</v>
       </c>
       <c r="B169" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D169" s="13" t="s">
-        <v>5</v>
+      <c r="D169" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A170" s="6">
-        <v>20277</v>
+        <v>20275</v>
       </c>
       <c r="B170" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D170" s="1" t="s">
-        <v>8</v>
+      <c r="D170" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="171" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="6">
-        <v>20281</v>
+        <v>20277</v>
       </c>
       <c r="B171" t="s">
-        <v>105</v>
+        <v>154</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D171" s="3" t="s">
-        <v>5</v>
+      <c r="D171" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="6">
-        <v>20282</v>
+        <v>20281</v>
       </c>
       <c r="B172" t="s">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D172" s="1" t="s">
-        <v>9</v>
+      <c r="D172" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="6">
-        <v>20284</v>
+        <v>20282</v>
       </c>
       <c r="B173" t="s">
-        <v>17</v>
+        <v>141</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D173" s="17" t="s">
+      <c r="D173" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="174" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="6">
-        <v>20285</v>
+        <v>20284</v>
       </c>
       <c r="B174" t="s">
-        <v>146</v>
+        <v>17</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D174" s="1" t="s">
-        <v>8</v>
+      <c r="D174" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="175" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="6">
-        <v>20289</v>
+        <v>20285</v>
       </c>
       <c r="B175" t="s">
-        <v>52</v>
+        <v>146</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D175" s="3" t="s">
-        <v>5</v>
+      <c r="D175" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="6">
-        <v>20290</v>
+        <v>20289</v>
       </c>
       <c r="B176" t="s">
-        <v>103</v>
+        <v>52</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D176" s="1" t="s">
-        <v>8</v>
+      <c r="D176" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="177" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A177" s="6">
-        <v>20291</v>
+        <v>20290</v>
       </c>
       <c r="B177" t="s">
-        <v>187</v>
+        <v>103</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D177" s="10" t="s">
+      <c r="D177" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="6">
-        <v>20292</v>
+        <v>20291</v>
       </c>
       <c r="B178" t="s">
-        <v>32</v>
+        <v>187</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D178" s="13" t="s">
-        <v>5</v>
+      <c r="D178" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="179" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="6">
-        <v>20293</v>
+        <v>20292</v>
       </c>
       <c r="B179" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>4</v>
@@ -4119,52 +4122,52 @@
     </row>
     <row r="180" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="6">
-        <v>20294</v>
+        <v>20293</v>
       </c>
       <c r="B180" t="s">
-        <v>202</v>
+        <v>43</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D180" s="10" t="s">
-        <v>8</v>
+      <c r="D180" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="6">
-        <v>20296</v>
+        <v>20294</v>
       </c>
       <c r="B181" t="s">
-        <v>144</v>
+        <v>202</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D181" s="13" t="s">
-        <v>5</v>
+      <c r="D181" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="182" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="6">
-        <v>20298</v>
+        <v>20296</v>
       </c>
       <c r="B182" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D182" s="1" t="s">
-        <v>8</v>
+      <c r="D182" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="183" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="6">
-        <v>20299</v>
+        <v>20298</v>
       </c>
       <c r="B183" t="s">
-        <v>58</v>
+        <v>169</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>4</v>
@@ -4175,10 +4178,10 @@
     </row>
     <row r="184" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="6">
-        <v>20301</v>
+        <v>20299</v>
       </c>
       <c r="B184" t="s">
-        <v>134</v>
+        <v>58</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>4</v>
@@ -4189,10 +4192,10 @@
     </row>
     <row r="185" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="6">
-        <v>20303</v>
+        <v>20301</v>
       </c>
       <c r="B185" t="s">
-        <v>37</v>
+        <v>134</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>4</v>
@@ -4203,24 +4206,24 @@
     </row>
     <row r="186" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="6">
-        <v>20309</v>
+        <v>20303</v>
       </c>
       <c r="B186" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D186" s="13" t="s">
-        <v>5</v>
+      <c r="D186" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="187" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="6">
-        <v>20310</v>
+        <v>20309</v>
       </c>
       <c r="B187" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>4</v>
@@ -4231,52 +4234,52 @@
     </row>
     <row r="188" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="6">
-        <v>20318</v>
+        <v>20310</v>
       </c>
       <c r="B188" t="s">
-        <v>209</v>
+        <v>59</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D188" s="1" t="s">
-        <v>8</v>
+      <c r="D188" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="189" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="6">
-        <v>20319</v>
+        <v>20318</v>
       </c>
       <c r="B189" t="s">
-        <v>101</v>
+        <v>209</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D189" s="10" t="s">
+      <c r="D189" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="190" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A190" s="6">
-        <v>20320</v>
+        <v>20319</v>
       </c>
       <c r="B190" t="s">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D190" s="1" t="s">
+      <c r="D190" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="191" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="6">
-        <v>20324</v>
+        <v>20320</v>
       </c>
       <c r="B191" t="s">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>4</v>
@@ -4287,10 +4290,10 @@
     </row>
     <row r="192" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="6">
-        <v>20331</v>
+        <v>20324</v>
       </c>
       <c r="B192" t="s">
-        <v>51</v>
+        <v>210</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>4</v>
@@ -4301,38 +4304,38 @@
     </row>
     <row r="193" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="6">
-        <v>20333</v>
+        <v>20331</v>
       </c>
       <c r="B193" t="s">
-        <v>136</v>
+        <v>51</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D193" s="13" t="s">
-        <v>5</v>
+      <c r="D193" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="194" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="6">
-        <v>20337</v>
+        <v>20333</v>
       </c>
       <c r="B194" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D194" s="1" t="s">
-        <v>8</v>
+      <c r="D194" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="195" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A195" s="6">
-        <v>20343</v>
+        <v>20337</v>
       </c>
       <c r="B195" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>4</v>
@@ -4343,10 +4346,10 @@
     </row>
     <row r="196" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="6">
-        <v>20344</v>
+        <v>20343</v>
       </c>
       <c r="B196" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>4</v>
@@ -4357,66 +4360,66 @@
     </row>
     <row r="197" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="6">
-        <v>20351</v>
+        <v>20344</v>
       </c>
       <c r="B197" t="s">
-        <v>26</v>
+        <v>127</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D197" s="13" t="s">
-        <v>5</v>
+      <c r="D197" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="198" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A198" s="6">
-        <v>20357</v>
+        <v>20351</v>
       </c>
       <c r="B198" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D198" s="1" t="s">
-        <v>8</v>
+      <c r="D198" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="199" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="6">
-        <v>20361</v>
+        <v>20357</v>
       </c>
       <c r="B199" t="s">
-        <v>164</v>
+        <v>56</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D199" s="13" t="s">
-        <v>5</v>
+      <c r="D199" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="200" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A200" s="6">
-        <v>20362</v>
+        <v>20361</v>
       </c>
       <c r="B200" t="s">
-        <v>45</v>
+        <v>164</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D200" s="10" t="s">
-        <v>8</v>
+      <c r="D200" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="201" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="6">
-        <v>20363</v>
+        <v>20362</v>
       </c>
       <c r="B201" t="s">
-        <v>213</v>
+        <v>45</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>4</v>
@@ -4427,38 +4430,38 @@
     </row>
     <row r="202" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="6">
-        <v>20364</v>
+        <v>20363</v>
       </c>
       <c r="B202" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D202" s="13" t="s">
-        <v>5</v>
+      <c r="D202" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="203" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="6">
-        <v>20366</v>
+        <v>20364</v>
       </c>
       <c r="B203" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D203" s="1" t="s">
-        <v>8</v>
+      <c r="D203" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="204" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="6">
-        <v>20367</v>
+        <v>20366</v>
       </c>
       <c r="B204" t="s">
-        <v>47</v>
+        <v>220</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>4</v>
@@ -4469,10 +4472,10 @@
     </row>
     <row r="205" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A205" s="6">
-        <v>20369</v>
+        <v>20367</v>
       </c>
       <c r="B205" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>4</v>
@@ -4483,10 +4486,10 @@
     </row>
     <row r="206" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A206" s="6">
-        <v>20371</v>
+        <v>20369</v>
       </c>
       <c r="B206" t="s">
-        <v>223</v>
+        <v>63</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>4</v>
@@ -4497,52 +4500,52 @@
     </row>
     <row r="207" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A207" s="6">
-        <v>20372</v>
+        <v>20371</v>
       </c>
       <c r="B207" t="s">
-        <v>70</v>
+        <v>223</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D207" s="10" t="s">
+      <c r="D207" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="208" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A208" s="6">
-        <v>20374</v>
+        <v>20372</v>
       </c>
       <c r="B208" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D208" s="1" t="s">
+      <c r="D208" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="209" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A209" s="6">
-        <v>20377</v>
+        <v>20374</v>
       </c>
       <c r="B209" t="s">
-        <v>225</v>
+        <v>61</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D209" s="10" t="s">
+      <c r="D209" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="210" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A210" s="6">
-        <v>20379</v>
+        <v>20377</v>
       </c>
       <c r="B210" t="s">
-        <v>49</v>
+        <v>225</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>4</v>
@@ -4553,66 +4556,66 @@
     </row>
     <row r="211" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="6">
-        <v>20380</v>
+        <v>20379</v>
       </c>
       <c r="B211" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D211" s="13" t="s">
-        <v>5</v>
+      <c r="D211" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="212" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A212" s="6">
-        <v>20381</v>
+        <v>20380</v>
       </c>
       <c r="B212" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D212" s="1" t="s">
-        <v>8</v>
+      <c r="D212" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="213" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A213" s="6">
-        <v>20384</v>
+        <v>20381</v>
       </c>
       <c r="B213" t="s">
-        <v>181</v>
+        <v>60</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D213" s="10" t="s">
+      <c r="D213" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="214" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A214" s="6">
-        <v>20385</v>
+        <v>20384</v>
       </c>
       <c r="B214" t="s">
-        <v>36</v>
+        <v>181</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D214" s="1" t="s">
+      <c r="D214" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="215" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A215" s="6">
-        <v>20386</v>
+        <v>20385</v>
       </c>
       <c r="B215" t="s">
-        <v>119</v>
+        <v>36</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>4</v>
@@ -4623,66 +4626,66 @@
     </row>
     <row r="216" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A216" s="6">
-        <v>20388</v>
+        <v>20386</v>
       </c>
       <c r="B216" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D216" s="10" t="s">
+      <c r="D216" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="217" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A217" s="6">
-        <v>20391</v>
+        <v>20388</v>
       </c>
       <c r="B217" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D217" s="1" t="s">
+      <c r="D217" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="218" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A218" s="6">
-        <v>20394</v>
+        <v>20391</v>
       </c>
       <c r="B218" t="s">
-        <v>173</v>
+        <v>106</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D218" s="10" t="s">
+      <c r="D218" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="219" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A219" s="6">
-        <v>20395</v>
+        <v>20394</v>
       </c>
       <c r="B219" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D219" s="1" t="s">
+      <c r="D219" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="220" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A220" s="6">
-        <v>20396</v>
+        <v>20395</v>
       </c>
       <c r="B220" t="s">
-        <v>330</v>
+        <v>161</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>4</v>
@@ -4693,52 +4696,52 @@
     </row>
     <row r="221" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A221" s="6">
-        <v>20397</v>
-      </c>
-      <c r="B221" s="8" t="s">
-        <v>344</v>
+        <v>20396</v>
+      </c>
+      <c r="B221" t="s">
+        <v>330</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D221" s="11" t="s">
-        <v>5</v>
+      <c r="D221" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="222" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A222" s="6">
-        <v>30101</v>
-      </c>
-      <c r="B222" t="s">
-        <v>167</v>
+        <v>20397</v>
+      </c>
+      <c r="B222" s="8" t="s">
+        <v>344</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D222" s="1" t="s">
-        <v>8</v>
+      <c r="D222" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="223" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223" s="6">
-        <v>40124</v>
+        <v>30101</v>
       </c>
       <c r="B223" t="s">
-        <v>24</v>
+        <v>167</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D223" s="13" t="s">
-        <v>5</v>
+      <c r="D223" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="224" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="6">
-        <v>40125</v>
+        <v>40124</v>
       </c>
       <c r="B224" t="s">
-        <v>143</v>
+        <v>24</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>4</v>
@@ -4749,24 +4752,24 @@
     </row>
     <row r="225" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A225" s="6">
-        <v>40127</v>
+        <v>40125</v>
       </c>
       <c r="B225" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D225" s="1" t="s">
-        <v>8</v>
+      <c r="D225" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="226" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A226" s="6">
-        <v>40129</v>
+        <v>40127</v>
       </c>
       <c r="B226" t="s">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>4</v>
@@ -4777,24 +4780,24 @@
     </row>
     <row r="227" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A227" s="6">
-        <v>40137</v>
+        <v>40129</v>
       </c>
       <c r="B227" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D227" s="10" t="s">
+      <c r="D227" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="228" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A228" s="6">
-        <v>40139</v>
+        <v>40137</v>
       </c>
       <c r="B228" t="s">
-        <v>327</v>
+        <v>121</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>4</v>
@@ -4805,66 +4808,66 @@
     </row>
     <row r="229" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A229" s="6">
-        <v>40140</v>
+        <v>40139</v>
       </c>
       <c r="B229" t="s">
-        <v>170</v>
+        <v>327</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D229" s="1" t="s">
+      <c r="D229" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="230" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A230" s="6">
-        <v>40141</v>
+        <v>40140</v>
       </c>
       <c r="B230" t="s">
-        <v>111</v>
+        <v>170</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D230" s="13" t="s">
-        <v>5</v>
+      <c r="D230" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="231" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A231" s="6">
-        <v>40143</v>
+        <v>40141</v>
       </c>
       <c r="B231" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D231" s="10" t="s">
-        <v>8</v>
+      <c r="D231" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="232" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A232" s="6">
-        <v>40144</v>
+        <v>40143</v>
       </c>
       <c r="B232" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D232" s="13" t="s">
-        <v>5</v>
+      <c r="D232" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="233" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A233" s="6">
-        <v>40145</v>
+        <v>40144</v>
       </c>
       <c r="B233" t="s">
-        <v>165</v>
+        <v>107</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>4</v>
@@ -4875,206 +4878,206 @@
     </row>
     <row r="234" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A234" s="6">
-        <v>40147</v>
+        <v>40145</v>
       </c>
       <c r="B234" t="s">
-        <v>405</v>
+        <v>165</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D234" s="19" t="s">
-        <v>8</v>
+      <c r="D234" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="235" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A235" s="6">
-        <v>40150</v>
+        <v>40147</v>
       </c>
       <c r="B235" t="s">
-        <v>221</v>
+        <v>405</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D235" s="10" t="s">
+      <c r="D235" s="19" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="236" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A236" s="6">
-        <v>40151</v>
+        <v>40150</v>
       </c>
       <c r="B236" t="s">
-        <v>54</v>
+        <v>221</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D236" s="1" t="s">
+      <c r="D236" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="237" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A237" s="6">
-        <v>50102</v>
+        <v>40151</v>
       </c>
       <c r="B237" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D237" s="13" t="s">
-        <v>5</v>
+      <c r="D237" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="238" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A238" s="6">
-        <v>50222</v>
+        <v>50102</v>
       </c>
       <c r="B238" t="s">
-        <v>215</v>
+        <v>67</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D238" s="1" t="s">
-        <v>8</v>
+      <c r="D238" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="239" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A239" s="6">
-        <v>50223</v>
+        <v>50222</v>
       </c>
       <c r="B239" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D239" s="10" t="s">
+      <c r="D239" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="240" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A240" s="6">
-        <v>50224</v>
+        <v>50223</v>
       </c>
       <c r="B240" t="s">
-        <v>42</v>
+        <v>194</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D240" s="3" t="s">
-        <v>5</v>
+      <c r="D240" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="241" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="6">
-        <v>50444</v>
+        <v>50224</v>
       </c>
       <c r="B241" t="s">
-        <v>116</v>
+        <v>42</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D241" s="1" t="s">
-        <v>8</v>
+      <c r="D241" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="242" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A242" s="6">
-        <v>50445</v>
+        <v>50444</v>
       </c>
       <c r="B242" t="s">
-        <v>354</v>
+        <v>116</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D242" s="11" t="s">
-        <v>5</v>
+      <c r="D242" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="243" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A243" s="6">
-        <v>50607</v>
+        <v>50445</v>
       </c>
       <c r="B243" t="s">
-        <v>76</v>
+        <v>354</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D243" s="13" t="s">
+      <c r="D243" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="244" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A244" s="6">
-        <v>50608</v>
+        <v>50607</v>
       </c>
       <c r="B244" t="s">
-        <v>177</v>
+        <v>76</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D244" s="1" t="s">
-        <v>8</v>
+      <c r="D244" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="245" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A245" s="6">
-        <v>50611</v>
-      </c>
-      <c r="B245" s="8" t="s">
-        <v>347</v>
+        <v>50608</v>
+      </c>
+      <c r="B245" t="s">
+        <v>177</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D245" s="14" t="s">
+      <c r="D245" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="246" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A246" s="6">
-        <v>50622</v>
-      </c>
-      <c r="B246" t="s">
-        <v>95</v>
+        <v>50611</v>
+      </c>
+      <c r="B246" s="8" t="s">
+        <v>347</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D246" s="16" t="s">
+      <c r="D246" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="247" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A247" s="6">
-        <v>50623</v>
+        <v>50622</v>
       </c>
       <c r="B247" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D247" s="10" t="s">
+      <c r="D247" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="248" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A248" s="6">
-        <v>50625</v>
+        <v>50623</v>
       </c>
       <c r="B248" t="s">
-        <v>204</v>
+        <v>110</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>4</v>
@@ -5085,94 +5088,94 @@
     </row>
     <row r="249" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A249" s="6">
-        <v>50629</v>
+        <v>50625</v>
       </c>
       <c r="B249" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D249" s="1" t="s">
+      <c r="D249" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="250" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A250" s="6">
-        <v>50630</v>
+        <v>50629</v>
       </c>
       <c r="B250" t="s">
-        <v>360</v>
+        <v>188</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D250" s="14" t="s">
+      <c r="D250" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="251" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A251" s="6">
-        <v>50803</v>
+        <v>50630</v>
       </c>
       <c r="B251" t="s">
-        <v>82</v>
+        <v>360</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D251" s="1" t="s">
+      <c r="D251" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="252" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A252" s="6">
-        <v>50805</v>
+        <v>50803</v>
       </c>
       <c r="B252" t="s">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D252" s="10" t="s">
+      <c r="D252" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="253" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A253" s="6">
-        <v>50806</v>
+        <v>50805</v>
       </c>
       <c r="B253" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D253" s="1" t="s">
+      <c r="D253" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="254" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="6">
-        <v>50808</v>
+        <v>50806</v>
       </c>
       <c r="B254" t="s">
-        <v>16</v>
+        <v>156</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D254" s="13" t="s">
-        <v>5</v>
+      <c r="D254" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="255" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A255" s="6">
-        <v>50809</v>
+        <v>50808</v>
       </c>
       <c r="B255" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>4</v>
@@ -5183,24 +5186,24 @@
     </row>
     <row r="256" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A256" s="6">
-        <v>50810</v>
+        <v>50809</v>
       </c>
       <c r="B256" t="s">
-        <v>175</v>
+        <v>98</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D256" s="1" t="s">
-        <v>8</v>
+      <c r="D256" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="257" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A257" s="6">
-        <v>50812</v>
+        <v>50810</v>
       </c>
       <c r="B257" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>4</v>
@@ -5211,80 +5214,80 @@
     </row>
     <row r="258" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A258" s="6">
-        <v>50813</v>
+        <v>50812</v>
       </c>
       <c r="B258" t="s">
-        <v>71</v>
+        <v>184</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D258" s="17" t="s">
-        <v>9</v>
+      <c r="D258" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="259" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A259" s="6">
-        <v>50815</v>
+        <v>50813</v>
       </c>
       <c r="B259" t="s">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D259" s="10" t="s">
-        <v>8</v>
+      <c r="D259" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="260" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A260" s="6">
-        <v>50816</v>
+        <v>50815</v>
       </c>
       <c r="B260" t="s">
-        <v>205</v>
+        <v>114</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D260" s="1" t="s">
+      <c r="D260" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="261" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A261" s="6">
-        <v>50818</v>
+        <v>50816</v>
       </c>
       <c r="B261" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D261" s="13" t="s">
-        <v>5</v>
+      <c r="D261" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="262" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A262" s="6">
-        <v>50819</v>
+        <v>50818</v>
       </c>
       <c r="B262" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D262" s="10" t="s">
-        <v>8</v>
+      <c r="D262" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="263" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A263" s="6">
-        <v>50820</v>
+        <v>50819</v>
       </c>
       <c r="B263" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>4</v>
@@ -5295,66 +5298,66 @@
     </row>
     <row r="264" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A264" s="6">
-        <v>50821</v>
+        <v>50820</v>
       </c>
       <c r="B264" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D264" s="1" t="s">
+      <c r="D264" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="265" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A265" s="6">
-        <v>50823</v>
+        <v>50821</v>
       </c>
       <c r="B265" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D265" s="17" t="s">
-        <v>9</v>
+      <c r="D265" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="266" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A266" s="6">
-        <v>50824</v>
+        <v>50823</v>
       </c>
       <c r="B266" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D266" s="13" t="s">
-        <v>5</v>
+      <c r="D266" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="267" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A267" s="6">
-        <v>50825</v>
+        <v>50824</v>
       </c>
       <c r="B267" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D267" s="10" t="s">
-        <v>8</v>
+      <c r="D267" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="268" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A268" s="6">
-        <v>50826</v>
+        <v>50825</v>
       </c>
       <c r="B268" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>4</v>
@@ -5365,24 +5368,24 @@
     </row>
     <row r="269" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A269" s="6">
-        <v>50827</v>
+        <v>50826</v>
       </c>
       <c r="B269" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D269" s="1" t="s">
+      <c r="D269" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="270" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A270" s="6">
-        <v>50829</v>
+        <v>50827</v>
       </c>
       <c r="B270" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>4</v>
@@ -5393,122 +5396,122 @@
     </row>
     <row r="271" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A271" s="6">
-        <v>50830</v>
+        <v>50829</v>
       </c>
       <c r="B271" t="s">
-        <v>366</v>
+        <v>236</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D271" s="11" t="s">
+      <c r="D271" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="272" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A272" s="6">
-        <v>50831</v>
+        <v>50830</v>
       </c>
       <c r="B272" t="s">
-        <v>351</v>
+        <v>366</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D272" s="11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="273" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A273" s="6">
-        <v>50832</v>
-      </c>
-      <c r="B273" s="8" t="s">
-        <v>349</v>
+        <v>50831</v>
+      </c>
+      <c r="B273" t="s">
+        <v>351</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D273" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="274" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A274" s="6">
-        <v>50833</v>
+        <v>50832</v>
       </c>
       <c r="B274" s="8" t="s">
-        <v>397</v>
+        <v>349</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D274" s="11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="275" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A275" s="6">
-        <v>50230</v>
+        <v>50833</v>
       </c>
       <c r="B275" s="8" t="s">
-        <v>379</v>
+        <v>397</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D275" s="11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="276" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A276" s="6">
-        <v>60103</v>
-      </c>
-      <c r="B276" t="s">
-        <v>237</v>
+        <v>50230</v>
+      </c>
+      <c r="B276" s="8" t="s">
+        <v>379</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D276" s="13" t="s">
+      <c r="D276" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="277" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A277" s="6">
-        <v>60109</v>
+        <v>60103</v>
       </c>
       <c r="B277" t="s">
-        <v>328</v>
+        <v>237</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D277" s="11" t="s">
-        <v>9</v>
+      <c r="D277" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="278" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A278" s="6">
-        <v>60124</v>
+        <v>60109</v>
       </c>
       <c r="B278" t="s">
-        <v>238</v>
+        <v>328</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D278" s="13" t="s">
-        <v>5</v>
+      <c r="D278" s="11" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="279" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A279" s="6">
-        <v>60125</v>
+        <v>60124</v>
       </c>
       <c r="B279" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>4</v>
@@ -5519,80 +5522,80 @@
     </row>
     <row r="280" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A280" s="6">
-        <v>60126</v>
+        <v>60125</v>
       </c>
       <c r="B280" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D280" s="10" t="s">
-        <v>8</v>
+      <c r="D280" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="281" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A281" s="6">
-        <v>60128</v>
+        <v>60126</v>
       </c>
       <c r="B281" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D281" s="3" t="s">
-        <v>5</v>
+      <c r="D281" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="282" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A282" s="6">
-        <v>60130</v>
+        <v>60128</v>
       </c>
       <c r="B282" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D282" s="1" t="s">
-        <v>8</v>
+      <c r="D282" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="283" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A283" s="6">
-        <v>60133</v>
+        <v>60130</v>
       </c>
       <c r="B283" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D283" s="13" t="s">
-        <v>5</v>
+      <c r="D283" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="284" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A284" s="6">
-        <v>60134</v>
+        <v>60133</v>
       </c>
       <c r="B284" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D284" s="1" t="s">
-        <v>8</v>
+      <c r="D284" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="285" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A285" s="6">
-        <v>60137</v>
+        <v>60134</v>
       </c>
       <c r="B285" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>4</v>
@@ -5603,10 +5606,10 @@
     </row>
     <row r="286" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A286" s="6">
-        <v>60139</v>
+        <v>60137</v>
       </c>
       <c r="B286" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>4</v>
@@ -5617,10 +5620,10 @@
     </row>
     <row r="287" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A287" s="6">
-        <v>60142</v>
+        <v>60139</v>
       </c>
       <c r="B287" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>4</v>
@@ -5631,10 +5634,10 @@
     </row>
     <row r="288" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A288" s="6">
-        <v>60148</v>
+        <v>60142</v>
       </c>
       <c r="B288" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>4</v>
@@ -5645,10 +5648,10 @@
     </row>
     <row r="289" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A289" s="6">
-        <v>60149</v>
+        <v>60148</v>
       </c>
       <c r="B289" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>4</v>
@@ -5659,66 +5662,66 @@
     </row>
     <row r="290" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A290" s="6">
-        <v>60150</v>
+        <v>60149</v>
       </c>
       <c r="B290" t="s">
-        <v>332</v>
+        <v>249</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D290" s="13" t="s">
-        <v>5</v>
+      <c r="D290" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="291" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A291" s="6">
-        <v>60158</v>
+        <v>60150</v>
       </c>
       <c r="B291" t="s">
-        <v>250</v>
+        <v>332</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D291" s="10" t="s">
-        <v>8</v>
+      <c r="D291" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="292" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A292" s="6">
-        <v>60159</v>
+        <v>60158</v>
       </c>
       <c r="B292" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D292" s="1" t="s">
+      <c r="D292" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="293" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A293" s="6">
-        <v>60162</v>
+        <v>60159</v>
       </c>
       <c r="B293" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D293" s="13" t="s">
-        <v>5</v>
+      <c r="D293" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="294" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A294" s="6">
-        <v>60163</v>
+        <v>60162</v>
       </c>
       <c r="B294" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>4</v>
@@ -5729,24 +5732,24 @@
     </row>
     <row r="295" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A295" s="6">
-        <v>60165</v>
+        <v>60163</v>
       </c>
       <c r="B295" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D295" s="1" t="s">
-        <v>8</v>
+      <c r="D295" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="296" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A296" s="6">
-        <v>60169</v>
+        <v>60165</v>
       </c>
       <c r="B296" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>4</v>
@@ -5757,52 +5760,52 @@
     </row>
     <row r="297" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A297" s="6">
-        <v>60170</v>
-      </c>
-      <c r="B297" s="8" t="s">
-        <v>337</v>
+        <v>60169</v>
+      </c>
+      <c r="B297" t="s">
+        <v>255</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D297" s="11" t="s">
+      <c r="D297" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="298" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A298" s="6">
-        <v>60172</v>
-      </c>
-      <c r="B298" t="s">
-        <v>256</v>
+        <v>60170</v>
+      </c>
+      <c r="B298" s="8" t="s">
+        <v>337</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D298" s="1" t="s">
+      <c r="D298" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="299" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A299" s="6">
-        <v>60174</v>
+        <v>60172</v>
       </c>
       <c r="B299" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D299" s="13" t="s">
-        <v>5</v>
+      <c r="D299" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="300" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A300" s="6">
-        <v>60176</v>
+        <v>60174</v>
       </c>
       <c r="B300" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>4</v>
@@ -5813,52 +5816,52 @@
     </row>
     <row r="301" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A301" s="6">
-        <v>60178</v>
+        <v>60176</v>
       </c>
       <c r="B301" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D301" s="1" t="s">
-        <v>8</v>
+      <c r="D301" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="302" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A302" s="6">
-        <v>60180</v>
+        <v>60178</v>
       </c>
       <c r="B302" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D302" s="10" t="s">
+      <c r="D302" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="303" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A303" s="6">
-        <v>60184</v>
+        <v>60180</v>
       </c>
       <c r="B303" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D303" s="1" t="s">
+      <c r="D303" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="304" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A304" s="6">
-        <v>60190</v>
+        <v>60184</v>
       </c>
       <c r="B304" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>4</v>
@@ -5869,24 +5872,24 @@
     </row>
     <row r="305" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A305" s="6">
-        <v>60191</v>
+        <v>60190</v>
       </c>
       <c r="B305" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D305" s="10" t="s">
+      <c r="D305" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="306" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A306" s="6">
-        <v>60192</v>
+        <v>60191</v>
       </c>
       <c r="B306" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>4</v>
@@ -5897,10 +5900,10 @@
     </row>
     <row r="307" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A307" s="6">
-        <v>60195</v>
+        <v>60192</v>
       </c>
       <c r="B307" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>4</v>
@@ -5911,10 +5914,10 @@
     </row>
     <row r="308" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A308" s="6">
-        <v>60196</v>
+        <v>60195</v>
       </c>
       <c r="B308" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>4</v>
@@ -5925,10 +5928,10 @@
     </row>
     <row r="309" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A309" s="6">
-        <v>60198</v>
+        <v>60196</v>
       </c>
       <c r="B309" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>4</v>
@@ -5939,52 +5942,52 @@
     </row>
     <row r="310" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A310" s="6">
-        <v>60201</v>
+        <v>60198</v>
       </c>
       <c r="B310" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D310" t="s">
-        <v>9</v>
+      <c r="D310" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="311" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A311" s="6">
-        <v>60202</v>
+        <v>60201</v>
       </c>
       <c r="B311" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D311" s="13" t="s">
-        <v>5</v>
+      <c r="D311" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="312" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A312" s="6">
-        <v>60204</v>
+        <v>60202</v>
       </c>
       <c r="B312" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D312" s="1" t="s">
-        <v>8</v>
+      <c r="D312" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="313" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A313" s="6">
-        <v>60205</v>
+        <v>60204</v>
       </c>
       <c r="B313" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>4</v>
@@ -5995,10 +5998,10 @@
     </row>
     <row r="314" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A314" s="6">
-        <v>60206</v>
+        <v>60205</v>
       </c>
       <c r="B314" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>4</v>
@@ -6009,192 +6012,192 @@
     </row>
     <row r="315" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A315" s="6">
-        <v>60209</v>
+        <v>60206</v>
       </c>
       <c r="B315" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D315" s="10" t="s">
+      <c r="D315" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="316" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A316" s="6">
-        <v>60211</v>
+        <v>60209</v>
       </c>
       <c r="B316" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D316" s="1" t="s">
+      <c r="D316" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="317" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A317" s="6">
-        <v>60215</v>
+        <v>60211</v>
       </c>
       <c r="B317" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D317" s="10" t="s">
+      <c r="D317" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="318" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A318" s="6">
-        <v>60216</v>
+        <v>60215</v>
       </c>
       <c r="B318" t="s">
-        <v>381</v>
+        <v>275</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D318" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="319" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A319" s="6">
-        <v>60217</v>
+        <v>60216</v>
       </c>
       <c r="B319" t="s">
-        <v>276</v>
+        <v>381</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D319" s="10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="320" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A320" s="6">
-        <v>60219</v>
+        <v>60217</v>
       </c>
       <c r="B320" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D320" s="1" t="s">
+      <c r="D320" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="321" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A321" s="6">
-        <v>60222</v>
+        <v>60219</v>
       </c>
       <c r="B321" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D321" s="10" t="s">
+      <c r="D321" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="322" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A322" s="6">
-        <v>60225</v>
+        <v>60222</v>
       </c>
       <c r="B322" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D322" s="17" t="s">
-        <v>9</v>
+      <c r="D322" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="323" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A323" s="6">
-        <v>60230</v>
+        <v>60225</v>
       </c>
       <c r="B323" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D323" s="10" t="s">
-        <v>8</v>
+      <c r="D323" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="324" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A324" s="6">
-        <v>60241</v>
-      </c>
-      <c r="B324" s="8" t="s">
-        <v>338</v>
+        <v>60230</v>
+      </c>
+      <c r="B324" t="s">
+        <v>280</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D324" s="7" t="s">
-        <v>9</v>
+      <c r="D324" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="325" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A325" s="6">
-        <v>60242</v>
+        <v>60241</v>
       </c>
       <c r="B325" s="8" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D325" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="326" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A326" s="6">
-        <v>60243</v>
+        <v>60242</v>
       </c>
       <c r="B326" s="8" t="s">
-        <v>395</v>
+        <v>341</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D326" s="7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="327" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A327" s="6">
-        <v>60245</v>
+        <v>60243</v>
       </c>
       <c r="B327" s="8" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D327" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="328" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A328" s="6">
-        <v>60246</v>
+        <v>60245</v>
       </c>
       <c r="B328" s="8" t="s">
-        <v>407</v>
+        <v>387</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>4</v>
@@ -6205,10 +6208,10 @@
     </row>
     <row r="329" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A329" s="6">
-        <v>60249</v>
-      </c>
-      <c r="B329" s="18" t="s">
-        <v>408</v>
+        <v>60246</v>
+      </c>
+      <c r="B329" s="8" t="s">
+        <v>407</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>4</v>
@@ -6219,38 +6222,38 @@
     </row>
     <row r="330" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A330" s="6">
-        <v>60250</v>
-      </c>
-      <c r="B330" s="8" t="s">
-        <v>339</v>
+        <v>60249</v>
+      </c>
+      <c r="B330" s="18" t="s">
+        <v>408</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D330" s="11" t="s">
-        <v>8</v>
+      <c r="D330" s="7" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="331" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A331" s="6">
-        <v>60253</v>
-      </c>
-      <c r="B331" t="s">
-        <v>281</v>
+        <v>60250</v>
+      </c>
+      <c r="B331" s="8" t="s">
+        <v>339</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D331" s="1" t="s">
+      <c r="D331" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="332" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A332" s="6">
-        <v>60254</v>
+        <v>60253</v>
       </c>
       <c r="B332" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>4</v>
@@ -6261,10 +6264,10 @@
     </row>
     <row r="333" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A333" s="6">
-        <v>60257</v>
+        <v>60254</v>
       </c>
       <c r="B333" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>4</v>
@@ -6275,10 +6278,10 @@
     </row>
     <row r="334" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A334" s="6">
-        <v>60258</v>
+        <v>60257</v>
       </c>
       <c r="B334" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>4</v>
@@ -6289,66 +6292,66 @@
     </row>
     <row r="335" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A335" s="6">
-        <v>60266</v>
-      </c>
-      <c r="B335" s="8" t="s">
-        <v>343</v>
+        <v>60258</v>
+      </c>
+      <c r="B335" t="s">
+        <v>284</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D335" s="11" t="s">
+      <c r="D335" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="336" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A336" s="6">
-        <v>60269</v>
-      </c>
-      <c r="B336" t="s">
-        <v>285</v>
+        <v>60266</v>
+      </c>
+      <c r="B336" s="8" t="s">
+        <v>343</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D336" s="10" t="s">
+      <c r="D336" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="337" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A337" s="6">
-        <v>60270</v>
+        <v>60269</v>
       </c>
       <c r="B337" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D337" s="1" t="s">
-        <v>9</v>
+      <c r="D337" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="338" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A338" s="6">
-        <v>60272</v>
+        <v>60270</v>
       </c>
       <c r="B338" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="339" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A339" s="6">
-        <v>60274</v>
+        <v>60272</v>
       </c>
       <c r="B339" t="s">
-        <v>380</v>
+        <v>287</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>4</v>
@@ -6359,10 +6362,10 @@
     </row>
     <row r="340" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A340" s="6">
-        <v>60275</v>
+        <v>60274</v>
       </c>
       <c r="B340" t="s">
-        <v>288</v>
+        <v>380</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>4</v>
@@ -6373,10 +6376,10 @@
     </row>
     <row r="341" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A341" s="6">
-        <v>60276</v>
+        <v>60275</v>
       </c>
       <c r="B341" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>4</v>
@@ -6387,108 +6390,108 @@
     </row>
     <row r="342" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A342" s="6">
-        <v>60278</v>
+        <v>60276</v>
       </c>
       <c r="B342" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D342" s="13" t="s">
+      <c r="D342" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="343" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A343" s="6">
-        <v>60279</v>
+        <v>60278</v>
       </c>
       <c r="B343" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D343" s="1" t="s">
+      <c r="D343" s="13" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="344" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A344" s="6">
-        <v>60280</v>
+        <v>60279</v>
       </c>
       <c r="B344" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="345" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A345" s="6">
-        <v>60281</v>
-      </c>
-      <c r="B345" s="8" t="s">
-        <v>336</v>
+        <v>60280</v>
+      </c>
+      <c r="B345" t="s">
+        <v>292</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D345" s="11" t="s">
-        <v>9</v>
+      <c r="D345" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="346" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A346" s="6">
-        <v>60282</v>
+        <v>60281</v>
       </c>
       <c r="B346" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D346" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="347" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A347" s="6">
-        <v>60283</v>
-      </c>
-      <c r="B347" t="s">
-        <v>378</v>
+        <v>60282</v>
+      </c>
+      <c r="B347" s="8" t="s">
+        <v>340</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D347" s="1" t="s">
-        <v>8</v>
+      <c r="D347" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="348" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A348" s="6">
-        <v>60284</v>
-      </c>
-      <c r="B348" s="8" t="s">
-        <v>335</v>
+        <v>60283</v>
+      </c>
+      <c r="B348" t="s">
+        <v>378</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D348" s="9" t="s">
-        <v>5</v>
+      <c r="D348" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="349" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A349" s="6">
-        <v>60285</v>
+        <v>60284</v>
       </c>
       <c r="B349" s="8" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>4</v>
@@ -6499,10 +6502,10 @@
     </row>
     <row r="350" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A350" s="6">
-        <v>60286</v>
+        <v>60285</v>
       </c>
       <c r="B350" s="8" t="s">
-        <v>334</v>
+        <v>350</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>4</v>
@@ -6513,52 +6516,52 @@
     </row>
     <row r="351" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A351" s="6">
-        <v>60287</v>
-      </c>
-      <c r="B351" t="s">
-        <v>377</v>
+        <v>60286</v>
+      </c>
+      <c r="B351" s="8" t="s">
+        <v>334</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D351" s="12" t="s">
+      <c r="D351" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="352" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A352" s="6">
-        <v>60289</v>
+        <v>60287</v>
       </c>
       <c r="B352" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D352" s="12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="353" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A353" s="6">
-        <v>60290</v>
+        <v>60289</v>
       </c>
       <c r="B353" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D353" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="354" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A354" s="6">
-        <v>60291</v>
+        <v>60290</v>
       </c>
       <c r="B354" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>4</v>
@@ -6569,24 +6572,24 @@
     </row>
     <row r="355" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A355" s="6">
-        <v>60292</v>
-      </c>
-      <c r="B355" s="18" t="s">
-        <v>400</v>
+        <v>60291</v>
+      </c>
+      <c r="B355" t="s">
+        <v>376</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D355" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="356" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A356" s="6">
-        <v>60296</v>
-      </c>
-      <c r="B356" t="s">
-        <v>391</v>
+        <v>60292</v>
+      </c>
+      <c r="B356" s="18" t="s">
+        <v>400</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>4</v>
@@ -6597,24 +6600,24 @@
     </row>
     <row r="357" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A357" s="6">
-        <v>60297</v>
+        <v>60296</v>
       </c>
       <c r="B357" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D357" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="358" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A358" s="6">
-        <v>60299</v>
+        <v>60297</v>
       </c>
       <c r="B358" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>4</v>
@@ -6625,52 +6628,52 @@
     </row>
     <row r="359" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A359" s="6">
-        <v>61001</v>
+        <v>60299</v>
       </c>
       <c r="B359" t="s">
-        <v>403</v>
+        <v>388</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D359" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="360" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A360" s="6">
-        <v>61004</v>
+        <v>61001</v>
       </c>
       <c r="B360" t="s">
-        <v>293</v>
+        <v>403</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D360" s="15" t="s">
-        <v>5</v>
+      <c r="D360" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="361" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A361" s="6">
-        <v>61009</v>
+        <v>61004</v>
       </c>
       <c r="B361" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D361" s="12" t="s">
-        <v>8</v>
+      <c r="D361" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="362" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A362" s="6">
-        <v>61012</v>
+        <v>61009</v>
       </c>
       <c r="B362" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>4</v>
@@ -6681,10 +6684,10 @@
     </row>
     <row r="363" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A363" s="6">
-        <v>61018</v>
+        <v>61012</v>
       </c>
       <c r="B363" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>4</v>
@@ -6695,10 +6698,10 @@
     </row>
     <row r="364" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A364" s="6">
-        <v>61102</v>
+        <v>61018</v>
       </c>
       <c r="B364" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>4</v>
@@ -6709,52 +6712,52 @@
     </row>
     <row r="365" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A365" s="6">
-        <v>61205</v>
+        <v>61102</v>
       </c>
       <c r="B365" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D365" s="15" t="s">
-        <v>5</v>
+      <c r="D365" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="366" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A366" s="6">
-        <v>70100</v>
+        <v>61205</v>
       </c>
       <c r="B366" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D366" s="12" t="s">
-        <v>8</v>
+      <c r="D366" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="367" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A367" s="6">
-        <v>70101</v>
+        <v>70100</v>
       </c>
       <c r="B367" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D367" s="15" t="s">
-        <v>5</v>
+      <c r="D367" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="368" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A368" s="6">
-        <v>70102</v>
+        <v>70101</v>
       </c>
       <c r="B368" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>4</v>
@@ -6765,80 +6768,80 @@
     </row>
     <row r="369" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A369" s="6">
-        <v>70103</v>
+        <v>70102</v>
       </c>
       <c r="B369" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D369" s="12" t="s">
-        <v>8</v>
+      <c r="D369" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="370" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A370" s="6">
-        <v>70106</v>
+        <v>70103</v>
       </c>
       <c r="B370" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D370" s="15" t="s">
-        <v>5</v>
+      <c r="D370" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="371" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A371" s="6">
-        <v>70109</v>
+        <v>70106</v>
       </c>
       <c r="B371" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D371" s="12" t="s">
-        <v>8</v>
+      <c r="D371" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="372" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A372" s="6">
-        <v>70113</v>
+        <v>70109</v>
       </c>
       <c r="B372" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D372" s="15" t="s">
-        <v>5</v>
+      <c r="D372" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="373" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A373" s="6">
-        <v>70114</v>
+        <v>70113</v>
       </c>
       <c r="B373" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D373" s="9" t="s">
-        <v>9</v>
+      <c r="D373" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="374" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A374" s="6">
-        <v>70115</v>
+        <v>70114</v>
       </c>
       <c r="B374" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>4</v>
@@ -6849,24 +6852,24 @@
     </row>
     <row r="375" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A375" s="6">
-        <v>70638</v>
+        <v>70115</v>
       </c>
       <c r="B375" t="s">
-        <v>306</v>
+        <v>331</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D375" s="12" t="s">
-        <v>8</v>
+      <c r="D375" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="376" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A376" s="6">
-        <v>70639</v>
+        <v>70638</v>
       </c>
       <c r="B376" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>4</v>
@@ -6877,10 +6880,10 @@
     </row>
     <row r="377" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A377" s="6">
-        <v>70640</v>
+        <v>70639</v>
       </c>
       <c r="B377" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>4</v>
@@ -6891,10 +6894,10 @@
     </row>
     <row r="378" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A378" s="6">
-        <v>70642</v>
+        <v>70640</v>
       </c>
       <c r="B378" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>4</v>
@@ -6905,10 +6908,10 @@
     </row>
     <row r="379" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A379" s="6">
-        <v>90504</v>
+        <v>70642</v>
       </c>
       <c r="B379" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>4</v>
@@ -6919,10 +6922,10 @@
     </row>
     <row r="380" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A380" s="6">
-        <v>90509</v>
+        <v>90504</v>
       </c>
       <c r="B380" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>4</v>
@@ -6933,52 +6936,52 @@
     </row>
     <row r="381" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A381" s="6">
-        <v>90602</v>
+        <v>90509</v>
       </c>
       <c r="B381" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D381" s="15" t="s">
-        <v>5</v>
+      <c r="D381" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="382" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A382" s="6">
-        <v>90621</v>
+        <v>90602</v>
       </c>
       <c r="B382" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D382" s="12" t="s">
-        <v>8</v>
+      <c r="D382" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="383" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A383" s="6">
-        <v>90622</v>
+        <v>90621</v>
       </c>
       <c r="B383" t="s">
-        <v>333</v>
+        <v>313</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D383" s="9" t="s">
-        <v>5</v>
+      <c r="D383" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="384" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A384" s="6">
-        <v>90631</v>
-      </c>
-      <c r="B384" s="8" t="s">
-        <v>342</v>
+        <v>90622</v>
+      </c>
+      <c r="B384" t="s">
+        <v>333</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>4</v>
@@ -6989,24 +6992,24 @@
     </row>
     <row r="385" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A385" s="6">
-        <v>90658</v>
-      </c>
-      <c r="B385" t="s">
-        <v>314</v>
+        <v>90631</v>
+      </c>
+      <c r="B385" s="8" t="s">
+        <v>342</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D385" s="12" t="s">
-        <v>8</v>
+      <c r="D385" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="386" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A386" s="6">
-        <v>90660</v>
+        <v>90658</v>
       </c>
       <c r="B386" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>4</v>
@@ -7017,10 +7020,10 @@
     </row>
     <row r="387" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A387" s="6">
-        <v>90668</v>
+        <v>90660</v>
       </c>
       <c r="B387" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>4</v>
@@ -7031,10 +7034,10 @@
     </row>
     <row r="388" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A388" s="6">
-        <v>90671</v>
+        <v>90668</v>
       </c>
       <c r="B388" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>4</v>
@@ -7045,10 +7048,10 @@
     </row>
     <row r="389" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A389" s="6">
-        <v>90679</v>
+        <v>90671</v>
       </c>
       <c r="B389" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>4</v>
@@ -7059,10 +7062,10 @@
     </row>
     <row r="390" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A390" s="6">
-        <v>90683</v>
+        <v>90679</v>
       </c>
       <c r="B390" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>4</v>
@@ -7073,10 +7076,10 @@
     </row>
     <row r="391" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A391" s="6">
-        <v>90705</v>
+        <v>90683</v>
       </c>
       <c r="B391" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>4</v>
@@ -7087,10 +7090,10 @@
     </row>
     <row r="392" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A392" s="6">
-        <v>90706</v>
+        <v>90705</v>
       </c>
       <c r="B392" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>4</v>
@@ -7101,10 +7104,10 @@
     </row>
     <row r="393" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A393" s="6">
-        <v>90708</v>
+        <v>90706</v>
       </c>
       <c r="B393" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>4</v>
@@ -7115,10 +7118,10 @@
     </row>
     <row r="394" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A394" s="6">
-        <v>90709</v>
+        <v>90708</v>
       </c>
       <c r="B394" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>4</v>
@@ -7129,38 +7132,38 @@
     </row>
     <row r="395" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A395" s="6">
-        <v>90713</v>
+        <v>90709</v>
       </c>
       <c r="B395" t="s">
-        <v>402</v>
+        <v>323</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D395" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="396" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A396" s="6">
-        <v>1218</v>
+        <v>90713</v>
       </c>
       <c r="B396" t="s">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D396" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="397" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A397" s="6">
-        <v>1959</v>
-      </c>
-      <c r="B397" s="8" t="s">
-        <v>383</v>
+        <v>1218</v>
+      </c>
+      <c r="B397" t="s">
+        <v>382</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>4</v>
@@ -7171,10 +7174,10 @@
     </row>
     <row r="398" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A398" s="6">
-        <v>5625</v>
+        <v>1959</v>
       </c>
       <c r="B398" s="8" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>4</v>
@@ -7185,10 +7188,10 @@
     </row>
     <row r="399" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A399" s="6">
-        <v>1817</v>
+        <v>5625</v>
       </c>
       <c r="B399" s="8" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>4</v>
@@ -7199,10 +7202,10 @@
     </row>
     <row r="400" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A400" s="6">
-        <v>5737</v>
+        <v>1817</v>
       </c>
       <c r="B400" s="8" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C400" s="1" t="s">
         <v>4</v>
@@ -7213,34 +7216,48 @@
     </row>
     <row r="401" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A401" s="6">
-        <v>60295</v>
+        <v>5737</v>
       </c>
       <c r="B401" s="8" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C401" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D401" s="9" t="s">
-        <v>9</v>
+      <c r="D401" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="402" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A402" s="6">
+        <v>60295</v>
+      </c>
+      <c r="B402" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="C402" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D402" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A403" s="6">
         <v>1045</v>
       </c>
-      <c r="B402" s="8" t="s">
+      <c r="B403" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="C402" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D402" s="9" t="s">
+      <c r="C403" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D403" s="9" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D347"/>
+  <autoFilter ref="A1:D348"/>
   <sortState ref="A2:D374">
     <sortCondition ref="A277"/>
   </sortState>

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$348</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$349</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1210" uniqueCount="410">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="411">
   <si>
     <t>CUENTA</t>
   </si>
@@ -1252,6 +1252,9 @@
   </si>
   <si>
     <t>FERRETERIA BM</t>
+  </si>
+  <si>
+    <t>EL BUHO FERRETERIA</t>
   </si>
 </sst>
 </file>
@@ -1606,7 +1609,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D403"/>
+  <dimension ref="A1:D404"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -5914,10 +5917,10 @@
     </row>
     <row r="308" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A308" s="6">
-        <v>60195</v>
-      </c>
-      <c r="B308" t="s">
-        <v>265</v>
+        <v>60194</v>
+      </c>
+      <c r="B308" s="18" t="s">
+        <v>410</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>4</v>
@@ -5928,10 +5931,10 @@
     </row>
     <row r="309" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A309" s="6">
-        <v>60196</v>
+        <v>60195</v>
       </c>
       <c r="B309" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>4</v>
@@ -5942,10 +5945,10 @@
     </row>
     <row r="310" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A310" s="6">
-        <v>60198</v>
+        <v>60196</v>
       </c>
       <c r="B310" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>4</v>
@@ -5956,52 +5959,52 @@
     </row>
     <row r="311" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A311" s="6">
-        <v>60201</v>
+        <v>60198</v>
       </c>
       <c r="B311" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D311" t="s">
-        <v>9</v>
+      <c r="D311" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="312" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A312" s="6">
-        <v>60202</v>
+        <v>60201</v>
       </c>
       <c r="B312" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D312" s="13" t="s">
-        <v>5</v>
+      <c r="D312" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="313" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A313" s="6">
-        <v>60204</v>
+        <v>60202</v>
       </c>
       <c r="B313" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D313" s="1" t="s">
-        <v>8</v>
+      <c r="D313" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="314" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A314" s="6">
-        <v>60205</v>
+        <v>60204</v>
       </c>
       <c r="B314" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>4</v>
@@ -6012,10 +6015,10 @@
     </row>
     <row r="315" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A315" s="6">
-        <v>60206</v>
+        <v>60205</v>
       </c>
       <c r="B315" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>4</v>
@@ -6026,192 +6029,192 @@
     </row>
     <row r="316" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A316" s="6">
-        <v>60209</v>
+        <v>60206</v>
       </c>
       <c r="B316" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D316" s="10" t="s">
+      <c r="D316" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="317" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A317" s="6">
-        <v>60211</v>
+        <v>60209</v>
       </c>
       <c r="B317" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D317" s="1" t="s">
+      <c r="D317" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="318" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A318" s="6">
-        <v>60215</v>
+        <v>60211</v>
       </c>
       <c r="B318" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D318" s="10" t="s">
+      <c r="D318" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="319" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A319" s="6">
-        <v>60216</v>
+        <v>60215</v>
       </c>
       <c r="B319" t="s">
-        <v>381</v>
+        <v>275</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D319" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="320" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A320" s="6">
-        <v>60217</v>
+        <v>60216</v>
       </c>
       <c r="B320" t="s">
-        <v>276</v>
+        <v>381</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D320" s="10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="321" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A321" s="6">
-        <v>60219</v>
+        <v>60217</v>
       </c>
       <c r="B321" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D321" s="1" t="s">
+      <c r="D321" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="322" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A322" s="6">
-        <v>60222</v>
+        <v>60219</v>
       </c>
       <c r="B322" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D322" s="10" t="s">
+      <c r="D322" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="323" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A323" s="6">
-        <v>60225</v>
+        <v>60222</v>
       </c>
       <c r="B323" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D323" s="17" t="s">
-        <v>9</v>
+      <c r="D323" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="324" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A324" s="6">
-        <v>60230</v>
+        <v>60225</v>
       </c>
       <c r="B324" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D324" s="10" t="s">
-        <v>8</v>
+      <c r="D324" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="325" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A325" s="6">
-        <v>60241</v>
-      </c>
-      <c r="B325" s="8" t="s">
-        <v>338</v>
+        <v>60230</v>
+      </c>
+      <c r="B325" t="s">
+        <v>280</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D325" s="7" t="s">
-        <v>9</v>
+      <c r="D325" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="326" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A326" s="6">
-        <v>60242</v>
+        <v>60241</v>
       </c>
       <c r="B326" s="8" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D326" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="327" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A327" s="6">
-        <v>60243</v>
+        <v>60242</v>
       </c>
       <c r="B327" s="8" t="s">
-        <v>395</v>
+        <v>341</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D327" s="7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="328" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A328" s="6">
-        <v>60245</v>
+        <v>60243</v>
       </c>
       <c r="B328" s="8" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D328" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="329" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A329" s="6">
-        <v>60246</v>
+        <v>60245</v>
       </c>
       <c r="B329" s="8" t="s">
-        <v>407</v>
+        <v>387</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>4</v>
@@ -6222,10 +6225,10 @@
     </row>
     <row r="330" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A330" s="6">
-        <v>60249</v>
-      </c>
-      <c r="B330" s="18" t="s">
-        <v>408</v>
+        <v>60246</v>
+      </c>
+      <c r="B330" s="8" t="s">
+        <v>407</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>4</v>
@@ -6236,38 +6239,38 @@
     </row>
     <row r="331" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A331" s="6">
-        <v>60250</v>
-      </c>
-      <c r="B331" s="8" t="s">
-        <v>339</v>
+        <v>60249</v>
+      </c>
+      <c r="B331" s="18" t="s">
+        <v>408</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D331" s="11" t="s">
-        <v>8</v>
+      <c r="D331" s="7" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="332" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A332" s="6">
-        <v>60253</v>
-      </c>
-      <c r="B332" t="s">
-        <v>281</v>
+        <v>60250</v>
+      </c>
+      <c r="B332" s="8" t="s">
+        <v>339</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D332" s="1" t="s">
+      <c r="D332" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="333" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A333" s="6">
-        <v>60254</v>
+        <v>60253</v>
       </c>
       <c r="B333" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>4</v>
@@ -6278,10 +6281,10 @@
     </row>
     <row r="334" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A334" s="6">
-        <v>60257</v>
+        <v>60254</v>
       </c>
       <c r="B334" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>4</v>
@@ -6292,10 +6295,10 @@
     </row>
     <row r="335" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A335" s="6">
-        <v>60258</v>
+        <v>60257</v>
       </c>
       <c r="B335" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>4</v>
@@ -6306,66 +6309,66 @@
     </row>
     <row r="336" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A336" s="6">
-        <v>60266</v>
-      </c>
-      <c r="B336" s="8" t="s">
-        <v>343</v>
+        <v>60258</v>
+      </c>
+      <c r="B336" t="s">
+        <v>284</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D336" s="11" t="s">
+      <c r="D336" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="337" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A337" s="6">
-        <v>60269</v>
-      </c>
-      <c r="B337" t="s">
-        <v>285</v>
+        <v>60266</v>
+      </c>
+      <c r="B337" s="8" t="s">
+        <v>343</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D337" s="10" t="s">
+      <c r="D337" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="338" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A338" s="6">
-        <v>60270</v>
+        <v>60269</v>
       </c>
       <c r="B338" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D338" s="1" t="s">
-        <v>9</v>
+      <c r="D338" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="339" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A339" s="6">
-        <v>60272</v>
+        <v>60270</v>
       </c>
       <c r="B339" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="340" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A340" s="6">
-        <v>60274</v>
+        <v>60272</v>
       </c>
       <c r="B340" t="s">
-        <v>380</v>
+        <v>287</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>4</v>
@@ -6376,10 +6379,10 @@
     </row>
     <row r="341" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A341" s="6">
-        <v>60275</v>
+        <v>60274</v>
       </c>
       <c r="B341" t="s">
-        <v>288</v>
+        <v>380</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>4</v>
@@ -6390,10 +6393,10 @@
     </row>
     <row r="342" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A342" s="6">
-        <v>60276</v>
+        <v>60275</v>
       </c>
       <c r="B342" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>4</v>
@@ -6404,108 +6407,108 @@
     </row>
     <row r="343" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A343" s="6">
-        <v>60278</v>
+        <v>60276</v>
       </c>
       <c r="B343" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D343" s="13" t="s">
+      <c r="D343" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="344" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A344" s="6">
-        <v>60279</v>
+        <v>60278</v>
       </c>
       <c r="B344" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D344" s="1" t="s">
+      <c r="D344" s="13" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="345" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A345" s="6">
-        <v>60280</v>
+        <v>60279</v>
       </c>
       <c r="B345" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="346" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A346" s="6">
-        <v>60281</v>
-      </c>
-      <c r="B346" s="8" t="s">
-        <v>336</v>
+        <v>60280</v>
+      </c>
+      <c r="B346" t="s">
+        <v>292</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D346" s="11" t="s">
-        <v>9</v>
+      <c r="D346" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="347" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A347" s="6">
-        <v>60282</v>
+        <v>60281</v>
       </c>
       <c r="B347" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D347" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="348" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A348" s="6">
-        <v>60283</v>
-      </c>
-      <c r="B348" t="s">
-        <v>378</v>
+        <v>60282</v>
+      </c>
+      <c r="B348" s="8" t="s">
+        <v>340</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D348" s="1" t="s">
-        <v>8</v>
+      <c r="D348" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="349" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A349" s="6">
-        <v>60284</v>
-      </c>
-      <c r="B349" s="8" t="s">
-        <v>335</v>
+        <v>60283</v>
+      </c>
+      <c r="B349" t="s">
+        <v>378</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D349" s="9" t="s">
-        <v>5</v>
+      <c r="D349" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="350" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A350" s="6">
-        <v>60285</v>
+        <v>60284</v>
       </c>
       <c r="B350" s="8" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>4</v>
@@ -6516,10 +6519,10 @@
     </row>
     <row r="351" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A351" s="6">
-        <v>60286</v>
+        <v>60285</v>
       </c>
       <c r="B351" s="8" t="s">
-        <v>334</v>
+        <v>350</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>4</v>
@@ -6530,52 +6533,52 @@
     </row>
     <row r="352" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A352" s="6">
-        <v>60287</v>
-      </c>
-      <c r="B352" t="s">
-        <v>377</v>
+        <v>60286</v>
+      </c>
+      <c r="B352" s="8" t="s">
+        <v>334</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D352" s="12" t="s">
+      <c r="D352" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="353" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A353" s="6">
-        <v>60289</v>
+        <v>60287</v>
       </c>
       <c r="B353" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D353" s="12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="354" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A354" s="6">
-        <v>60290</v>
+        <v>60289</v>
       </c>
       <c r="B354" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D354" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="355" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A355" s="6">
-        <v>60291</v>
+        <v>60290</v>
       </c>
       <c r="B355" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>4</v>
@@ -6586,24 +6589,24 @@
     </row>
     <row r="356" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A356" s="6">
-        <v>60292</v>
-      </c>
-      <c r="B356" s="18" t="s">
-        <v>400</v>
+        <v>60291</v>
+      </c>
+      <c r="B356" t="s">
+        <v>376</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D356" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="357" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A357" s="6">
-        <v>60296</v>
-      </c>
-      <c r="B357" t="s">
-        <v>391</v>
+        <v>60292</v>
+      </c>
+      <c r="B357" s="18" t="s">
+        <v>400</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>4</v>
@@ -6614,24 +6617,24 @@
     </row>
     <row r="358" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A358" s="6">
-        <v>60297</v>
+        <v>60296</v>
       </c>
       <c r="B358" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D358" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="359" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A359" s="6">
-        <v>60299</v>
+        <v>60297</v>
       </c>
       <c r="B359" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>4</v>
@@ -6642,52 +6645,52 @@
     </row>
     <row r="360" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A360" s="6">
-        <v>61001</v>
+        <v>60299</v>
       </c>
       <c r="B360" t="s">
-        <v>403</v>
+        <v>388</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D360" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="361" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A361" s="6">
-        <v>61004</v>
+        <v>61001</v>
       </c>
       <c r="B361" t="s">
-        <v>293</v>
+        <v>403</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D361" s="15" t="s">
-        <v>5</v>
+      <c r="D361" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="362" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A362" s="6">
-        <v>61009</v>
+        <v>61004</v>
       </c>
       <c r="B362" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D362" s="12" t="s">
-        <v>8</v>
+      <c r="D362" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="363" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A363" s="6">
-        <v>61012</v>
+        <v>61009</v>
       </c>
       <c r="B363" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>4</v>
@@ -6698,10 +6701,10 @@
     </row>
     <row r="364" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A364" s="6">
-        <v>61018</v>
+        <v>61012</v>
       </c>
       <c r="B364" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>4</v>
@@ -6712,10 +6715,10 @@
     </row>
     <row r="365" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A365" s="6">
-        <v>61102</v>
+        <v>61018</v>
       </c>
       <c r="B365" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>4</v>
@@ -6726,52 +6729,52 @@
     </row>
     <row r="366" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A366" s="6">
-        <v>61205</v>
+        <v>61102</v>
       </c>
       <c r="B366" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D366" s="15" t="s">
-        <v>5</v>
+      <c r="D366" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="367" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A367" s="6">
-        <v>70100</v>
+        <v>61205</v>
       </c>
       <c r="B367" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D367" s="12" t="s">
-        <v>8</v>
+      <c r="D367" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="368" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A368" s="6">
-        <v>70101</v>
+        <v>70100</v>
       </c>
       <c r="B368" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D368" s="15" t="s">
-        <v>5</v>
+      <c r="D368" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="369" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A369" s="6">
-        <v>70102</v>
+        <v>70101</v>
       </c>
       <c r="B369" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>4</v>
@@ -6782,80 +6785,80 @@
     </row>
     <row r="370" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A370" s="6">
-        <v>70103</v>
+        <v>70102</v>
       </c>
       <c r="B370" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D370" s="12" t="s">
-        <v>8</v>
+      <c r="D370" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="371" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A371" s="6">
-        <v>70106</v>
+        <v>70103</v>
       </c>
       <c r="B371" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D371" s="15" t="s">
-        <v>5</v>
+      <c r="D371" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="372" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A372" s="6">
-        <v>70109</v>
+        <v>70106</v>
       </c>
       <c r="B372" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D372" s="12" t="s">
-        <v>8</v>
+      <c r="D372" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="373" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A373" s="6">
-        <v>70113</v>
+        <v>70109</v>
       </c>
       <c r="B373" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D373" s="15" t="s">
-        <v>5</v>
+      <c r="D373" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="374" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A374" s="6">
-        <v>70114</v>
+        <v>70113</v>
       </c>
       <c r="B374" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D374" s="9" t="s">
-        <v>9</v>
+      <c r="D374" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="375" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A375" s="6">
-        <v>70115</v>
+        <v>70114</v>
       </c>
       <c r="B375" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>4</v>
@@ -6866,24 +6869,24 @@
     </row>
     <row r="376" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A376" s="6">
-        <v>70638</v>
+        <v>70115</v>
       </c>
       <c r="B376" t="s">
-        <v>306</v>
+        <v>331</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D376" s="12" t="s">
-        <v>8</v>
+      <c r="D376" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="377" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A377" s="6">
-        <v>70639</v>
+        <v>70638</v>
       </c>
       <c r="B377" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>4</v>
@@ -6894,10 +6897,10 @@
     </row>
     <row r="378" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A378" s="6">
-        <v>70640</v>
+        <v>70639</v>
       </c>
       <c r="B378" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>4</v>
@@ -6908,10 +6911,10 @@
     </row>
     <row r="379" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A379" s="6">
-        <v>70642</v>
+        <v>70640</v>
       </c>
       <c r="B379" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>4</v>
@@ -6922,10 +6925,10 @@
     </row>
     <row r="380" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A380" s="6">
-        <v>90504</v>
+        <v>70642</v>
       </c>
       <c r="B380" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>4</v>
@@ -6936,10 +6939,10 @@
     </row>
     <row r="381" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A381" s="6">
-        <v>90509</v>
+        <v>90504</v>
       </c>
       <c r="B381" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>4</v>
@@ -6950,52 +6953,52 @@
     </row>
     <row r="382" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A382" s="6">
-        <v>90602</v>
+        <v>90509</v>
       </c>
       <c r="B382" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D382" s="15" t="s">
-        <v>5</v>
+      <c r="D382" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="383" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A383" s="6">
-        <v>90621</v>
+        <v>90602</v>
       </c>
       <c r="B383" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D383" s="12" t="s">
-        <v>8</v>
+      <c r="D383" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="384" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A384" s="6">
-        <v>90622</v>
+        <v>90621</v>
       </c>
       <c r="B384" t="s">
-        <v>333</v>
+        <v>313</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D384" s="9" t="s">
-        <v>5</v>
+      <c r="D384" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="385" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A385" s="6">
-        <v>90631</v>
-      </c>
-      <c r="B385" s="8" t="s">
-        <v>342</v>
+        <v>90622</v>
+      </c>
+      <c r="B385" t="s">
+        <v>333</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>4</v>
@@ -7006,24 +7009,24 @@
     </row>
     <row r="386" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A386" s="6">
-        <v>90658</v>
-      </c>
-      <c r="B386" t="s">
-        <v>314</v>
+        <v>90631</v>
+      </c>
+      <c r="B386" s="8" t="s">
+        <v>342</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D386" s="12" t="s">
-        <v>8</v>
+      <c r="D386" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="387" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A387" s="6">
-        <v>90660</v>
+        <v>90658</v>
       </c>
       <c r="B387" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>4</v>
@@ -7034,10 +7037,10 @@
     </row>
     <row r="388" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A388" s="6">
-        <v>90668</v>
+        <v>90660</v>
       </c>
       <c r="B388" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>4</v>
@@ -7048,10 +7051,10 @@
     </row>
     <row r="389" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A389" s="6">
-        <v>90671</v>
+        <v>90668</v>
       </c>
       <c r="B389" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>4</v>
@@ -7062,10 +7065,10 @@
     </row>
     <row r="390" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A390" s="6">
-        <v>90679</v>
+        <v>90671</v>
       </c>
       <c r="B390" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>4</v>
@@ -7076,10 +7079,10 @@
     </row>
     <row r="391" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A391" s="6">
-        <v>90683</v>
+        <v>90679</v>
       </c>
       <c r="B391" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>4</v>
@@ -7090,10 +7093,10 @@
     </row>
     <row r="392" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A392" s="6">
-        <v>90705</v>
+        <v>90683</v>
       </c>
       <c r="B392" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>4</v>
@@ -7104,10 +7107,10 @@
     </row>
     <row r="393" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A393" s="6">
-        <v>90706</v>
+        <v>90705</v>
       </c>
       <c r="B393" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>4</v>
@@ -7118,10 +7121,10 @@
     </row>
     <row r="394" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A394" s="6">
-        <v>90708</v>
+        <v>90706</v>
       </c>
       <c r="B394" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>4</v>
@@ -7132,10 +7135,10 @@
     </row>
     <row r="395" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A395" s="6">
-        <v>90709</v>
+        <v>90708</v>
       </c>
       <c r="B395" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>4</v>
@@ -7146,38 +7149,38 @@
     </row>
     <row r="396" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A396" s="6">
-        <v>90713</v>
+        <v>90709</v>
       </c>
       <c r="B396" t="s">
-        <v>402</v>
+        <v>323</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D396" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="397" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A397" s="6">
-        <v>1218</v>
+        <v>90713</v>
       </c>
       <c r="B397" t="s">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D397" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="398" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A398" s="6">
-        <v>1959</v>
-      </c>
-      <c r="B398" s="8" t="s">
-        <v>383</v>
+        <v>1218</v>
+      </c>
+      <c r="B398" t="s">
+        <v>382</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>4</v>
@@ -7188,10 +7191,10 @@
     </row>
     <row r="399" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A399" s="6">
-        <v>5625</v>
+        <v>1959</v>
       </c>
       <c r="B399" s="8" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>4</v>
@@ -7202,10 +7205,10 @@
     </row>
     <row r="400" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A400" s="6">
-        <v>1817</v>
+        <v>5625</v>
       </c>
       <c r="B400" s="8" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="C400" s="1" t="s">
         <v>4</v>
@@ -7216,10 +7219,10 @@
     </row>
     <row r="401" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A401" s="6">
-        <v>5737</v>
+        <v>1817</v>
       </c>
       <c r="B401" s="8" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C401" s="1" t="s">
         <v>4</v>
@@ -7230,34 +7233,48 @@
     </row>
     <row r="402" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A402" s="6">
-        <v>60295</v>
+        <v>5737</v>
       </c>
       <c r="B402" s="8" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C402" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D402" s="9" t="s">
-        <v>9</v>
+      <c r="D402" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="403" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A403" s="6">
+        <v>60295</v>
+      </c>
+      <c r="B403" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="C403" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D403" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="404" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A404" s="6">
         <v>1045</v>
       </c>
-      <c r="B403" s="8" t="s">
+      <c r="B404" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="C403" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D403" s="9" t="s">
+      <c r="C404" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D404" s="9" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D348"/>
+  <autoFilter ref="A1:D349"/>
   <sortState ref="A2:D374">
     <sortCondition ref="A277"/>
   </sortState>

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1219" uniqueCount="413">
   <si>
     <t>CUENTA</t>
   </si>
@@ -1255,6 +1255,12 @@
   </si>
   <si>
     <t>EL BUHO FERRETERIA</t>
+  </si>
+  <si>
+    <t>FERRETERIA L y C</t>
+  </si>
+  <si>
+    <t>FERRETERIA EBER</t>
   </si>
 </sst>
 </file>
@@ -1609,7 +1615,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D404"/>
+  <dimension ref="A1:D406"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -6659,38 +6665,38 @@
     </row>
     <row r="361" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A361" s="6">
-        <v>61001</v>
-      </c>
-      <c r="B361" t="s">
-        <v>403</v>
+        <v>60302</v>
+      </c>
+      <c r="B361" s="18" t="s">
+        <v>411</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D361" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="362" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A362" s="6">
-        <v>61004</v>
-      </c>
-      <c r="B362" t="s">
-        <v>293</v>
+        <v>60303</v>
+      </c>
+      <c r="B362" s="18" t="s">
+        <v>412</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D362" s="15" t="s">
+      <c r="D362" s="12" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="363" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A363" s="6">
-        <v>61009</v>
+        <v>61001</v>
       </c>
       <c r="B363" t="s">
-        <v>294</v>
+        <v>403</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>4</v>
@@ -6701,24 +6707,24 @@
     </row>
     <row r="364" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A364" s="6">
-        <v>61012</v>
+        <v>61004</v>
       </c>
       <c r="B364" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D364" s="12" t="s">
-        <v>8</v>
+      <c r="D364" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="365" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A365" s="6">
-        <v>61018</v>
+        <v>61009</v>
       </c>
       <c r="B365" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>4</v>
@@ -6729,10 +6735,10 @@
     </row>
     <row r="366" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A366" s="6">
-        <v>61102</v>
+        <v>61012</v>
       </c>
       <c r="B366" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>4</v>
@@ -6743,24 +6749,24 @@
     </row>
     <row r="367" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A367" s="6">
-        <v>61205</v>
+        <v>61018</v>
       </c>
       <c r="B367" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D367" s="15" t="s">
-        <v>5</v>
+      <c r="D367" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="368" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A368" s="6">
-        <v>70100</v>
+        <v>61102</v>
       </c>
       <c r="B368" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>4</v>
@@ -6771,10 +6777,10 @@
     </row>
     <row r="369" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A369" s="6">
-        <v>70101</v>
+        <v>61205</v>
       </c>
       <c r="B369" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>4</v>
@@ -6785,38 +6791,38 @@
     </row>
     <row r="370" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A370" s="6">
-        <v>70102</v>
+        <v>70100</v>
       </c>
       <c r="B370" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D370" s="15" t="s">
-        <v>5</v>
+      <c r="D370" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="371" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A371" s="6">
-        <v>70103</v>
+        <v>70101</v>
       </c>
       <c r="B371" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D371" s="12" t="s">
-        <v>8</v>
+      <c r="D371" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="372" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A372" s="6">
-        <v>70106</v>
+        <v>70102</v>
       </c>
       <c r="B372" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>4</v>
@@ -6827,10 +6833,10 @@
     </row>
     <row r="373" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A373" s="6">
-        <v>70109</v>
+        <v>70103</v>
       </c>
       <c r="B373" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>4</v>
@@ -6841,10 +6847,10 @@
     </row>
     <row r="374" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A374" s="6">
-        <v>70113</v>
+        <v>70106</v>
       </c>
       <c r="B374" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>4</v>
@@ -6855,66 +6861,66 @@
     </row>
     <row r="375" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A375" s="6">
-        <v>70114</v>
+        <v>70109</v>
       </c>
       <c r="B375" t="s">
-        <v>325</v>
+        <v>304</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D375" s="9" t="s">
-        <v>9</v>
+      <c r="D375" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="376" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A376" s="6">
-        <v>70115</v>
+        <v>70113</v>
       </c>
       <c r="B376" t="s">
-        <v>331</v>
+        <v>305</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D376" s="9" t="s">
-        <v>9</v>
+      <c r="D376" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="377" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A377" s="6">
-        <v>70638</v>
+        <v>70114</v>
       </c>
       <c r="B377" t="s">
-        <v>306</v>
+        <v>325</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D377" s="12" t="s">
-        <v>8</v>
+      <c r="D377" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="378" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A378" s="6">
-        <v>70639</v>
+        <v>70115</v>
       </c>
       <c r="B378" t="s">
-        <v>307</v>
+        <v>331</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D378" s="12" t="s">
-        <v>8</v>
+      <c r="D378" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="379" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A379" s="6">
-        <v>70640</v>
+        <v>70638</v>
       </c>
       <c r="B379" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>4</v>
@@ -6925,10 +6931,10 @@
     </row>
     <row r="380" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A380" s="6">
-        <v>70642</v>
+        <v>70639</v>
       </c>
       <c r="B380" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>4</v>
@@ -6939,10 +6945,10 @@
     </row>
     <row r="381" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A381" s="6">
-        <v>90504</v>
+        <v>70640</v>
       </c>
       <c r="B381" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>4</v>
@@ -6953,10 +6959,10 @@
     </row>
     <row r="382" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A382" s="6">
-        <v>90509</v>
+        <v>70642</v>
       </c>
       <c r="B382" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>4</v>
@@ -6967,24 +6973,24 @@
     </row>
     <row r="383" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A383" s="6">
-        <v>90602</v>
+        <v>90504</v>
       </c>
       <c r="B383" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D383" s="15" t="s">
-        <v>5</v>
+      <c r="D383" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="384" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A384" s="6">
-        <v>90621</v>
+        <v>90509</v>
       </c>
       <c r="B384" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>4</v>
@@ -6995,66 +7001,66 @@
     </row>
     <row r="385" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A385" s="6">
-        <v>90622</v>
+        <v>90602</v>
       </c>
       <c r="B385" t="s">
-        <v>333</v>
+        <v>312</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D385" s="9" t="s">
+      <c r="D385" s="15" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="386" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A386" s="6">
-        <v>90631</v>
-      </c>
-      <c r="B386" s="8" t="s">
-        <v>342</v>
+        <v>90621</v>
+      </c>
+      <c r="B386" t="s">
+        <v>313</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D386" s="9" t="s">
-        <v>5</v>
+      <c r="D386" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="387" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A387" s="6">
-        <v>90658</v>
+        <v>90622</v>
       </c>
       <c r="B387" t="s">
-        <v>314</v>
+        <v>333</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D387" s="12" t="s">
-        <v>8</v>
+      <c r="D387" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="388" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A388" s="6">
-        <v>90660</v>
-      </c>
-      <c r="B388" t="s">
-        <v>315</v>
+        <v>90631</v>
+      </c>
+      <c r="B388" s="8" t="s">
+        <v>342</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D388" s="12" t="s">
-        <v>8</v>
+      <c r="D388" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="389" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A389" s="6">
-        <v>90668</v>
+        <v>90658</v>
       </c>
       <c r="B389" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>4</v>
@@ -7065,10 +7071,10 @@
     </row>
     <row r="390" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A390" s="6">
-        <v>90671</v>
+        <v>90660</v>
       </c>
       <c r="B390" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>4</v>
@@ -7079,10 +7085,10 @@
     </row>
     <row r="391" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A391" s="6">
-        <v>90679</v>
+        <v>90668</v>
       </c>
       <c r="B391" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>4</v>
@@ -7093,10 +7099,10 @@
     </row>
     <row r="392" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A392" s="6">
-        <v>90683</v>
+        <v>90671</v>
       </c>
       <c r="B392" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>4</v>
@@ -7107,10 +7113,10 @@
     </row>
     <row r="393" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A393" s="6">
-        <v>90705</v>
+        <v>90679</v>
       </c>
       <c r="B393" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>4</v>
@@ -7121,10 +7127,10 @@
     </row>
     <row r="394" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A394" s="6">
-        <v>90706</v>
+        <v>90683</v>
       </c>
       <c r="B394" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>4</v>
@@ -7135,10 +7141,10 @@
     </row>
     <row r="395" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A395" s="6">
-        <v>90708</v>
+        <v>90705</v>
       </c>
       <c r="B395" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>4</v>
@@ -7149,10 +7155,10 @@
     </row>
     <row r="396" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A396" s="6">
-        <v>90709</v>
+        <v>90706</v>
       </c>
       <c r="B396" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>4</v>
@@ -7163,24 +7169,24 @@
     </row>
     <row r="397" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A397" s="6">
-        <v>90713</v>
+        <v>90708</v>
       </c>
       <c r="B397" t="s">
-        <v>402</v>
+        <v>322</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D397" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="398" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A398" s="6">
-        <v>1218</v>
+        <v>90709</v>
       </c>
       <c r="B398" t="s">
-        <v>382</v>
+        <v>323</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>4</v>
@@ -7191,24 +7197,24 @@
     </row>
     <row r="399" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A399" s="6">
-        <v>1959</v>
-      </c>
-      <c r="B399" s="8" t="s">
-        <v>383</v>
+        <v>90713</v>
+      </c>
+      <c r="B399" t="s">
+        <v>402</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D399" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="400" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A400" s="6">
-        <v>5625</v>
-      </c>
-      <c r="B400" s="8" t="s">
-        <v>384</v>
+        <v>1218</v>
+      </c>
+      <c r="B400" t="s">
+        <v>382</v>
       </c>
       <c r="C400" s="1" t="s">
         <v>4</v>
@@ -7219,10 +7225,10 @@
     </row>
     <row r="401" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A401" s="6">
-        <v>1817</v>
+        <v>1959</v>
       </c>
       <c r="B401" s="8" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="C401" s="1" t="s">
         <v>4</v>
@@ -7233,10 +7239,10 @@
     </row>
     <row r="402" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A402" s="6">
-        <v>5737</v>
+        <v>5625</v>
       </c>
       <c r="B402" s="8" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="C402" s="1" t="s">
         <v>4</v>
@@ -7247,29 +7253,57 @@
     </row>
     <row r="403" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A403" s="6">
-        <v>60295</v>
+        <v>1817</v>
       </c>
       <c r="B403" s="8" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="C403" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D403" s="9" t="s">
-        <v>9</v>
+      <c r="D403" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="404" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A404" s="6">
+        <v>5737</v>
+      </c>
+      <c r="B404" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="C404" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D404" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A405" s="6">
+        <v>60295</v>
+      </c>
+      <c r="B405" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="C405" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D405" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A406" s="6">
         <v>1045</v>
       </c>
-      <c r="B404" s="8" t="s">
+      <c r="B406" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="C404" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D404" s="9" t="s">
+      <c r="C406" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D406" s="9" t="s">
         <v>5</v>
       </c>
     </row>

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$349</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$350</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1219" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="414">
   <si>
     <t>CUENTA</t>
   </si>
@@ -1261,6 +1261,9 @@
   </si>
   <si>
     <t>FERRETERIA EBER</t>
+  </si>
+  <si>
+    <t>FERRETERIA D3</t>
   </si>
 </sst>
 </file>
@@ -1615,7 +1618,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D406"/>
+  <dimension ref="A1:D407"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -1863,52 +1866,52 @@
     </row>
     <row r="18" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
-        <v>936</v>
-      </c>
-      <c r="B18" t="s">
-        <v>86</v>
+        <v>933</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>413</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="B19" t="s">
-        <v>185</v>
+        <v>86</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>5</v>
+      <c r="D19" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B20" t="s">
-        <v>41</v>
+        <v>185</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>8</v>
+      <c r="D20" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B21" t="s">
-        <v>128</v>
+        <v>41</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>4</v>
@@ -1919,38 +1922,38 @@
     </row>
     <row r="22" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6">
-        <v>946</v>
+        <v>940</v>
       </c>
       <c r="B22" t="s">
-        <v>7</v>
+        <v>128</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D22" t="s">
-        <v>9</v>
+      <c r="D22" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B23" t="s">
-        <v>200</v>
+        <v>7</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>8</v>
+      <c r="D23" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="B24" t="s">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>4</v>
@@ -1961,10 +1964,10 @@
     </row>
     <row r="25" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="B25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>4</v>
@@ -1975,10 +1978,10 @@
     </row>
     <row r="26" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B26" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>4</v>
@@ -1989,38 +1992,38 @@
     </row>
     <row r="27" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="6">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B27" t="s">
-        <v>64</v>
+        <v>147</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D27" t="s">
-        <v>9</v>
+      <c r="D27" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="B28" t="s">
-        <v>129</v>
+        <v>64</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D28" s="1" t="s">
-        <v>8</v>
+      <c r="D28" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="6">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B29" t="s">
-        <v>102</v>
+        <v>129</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>4</v>
@@ -2031,10 +2034,10 @@
     </row>
     <row r="30" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B30" t="s">
-        <v>158</v>
+        <v>102</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>4</v>
@@ -2045,38 +2048,38 @@
     </row>
     <row r="31" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="B31" t="s">
-        <v>6</v>
+        <v>158</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>5</v>
+      <c r="D31" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6">
-        <v>961</v>
+        <v>958</v>
       </c>
       <c r="B32" t="s">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D32" s="1" t="s">
-        <v>8</v>
+      <c r="D32" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="6">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="B33" t="s">
-        <v>140</v>
+        <v>55</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>4</v>
@@ -2087,24 +2090,24 @@
     </row>
     <row r="34" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="6">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B34" t="s">
-        <v>21</v>
+        <v>140</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D34" s="3" t="s">
-        <v>5</v>
+      <c r="D34" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="6">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="B35" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>4</v>
@@ -2115,66 +2118,66 @@
     </row>
     <row r="36" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="B36" t="s">
-        <v>87</v>
+        <v>30</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D36" s="1" t="s">
-        <v>8</v>
+      <c r="D36" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="6">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="B37" t="s">
-        <v>226</v>
+        <v>87</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D37" t="s">
-        <v>9</v>
+      <c r="D37" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="6">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="B38" t="s">
-        <v>174</v>
+        <v>226</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D38" s="3" t="s">
-        <v>5</v>
+      <c r="D38" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="6">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B39" t="s">
-        <v>137</v>
+        <v>174</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D39" s="1" t="s">
-        <v>8</v>
+      <c r="D39" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="6">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B40" t="s">
-        <v>172</v>
+        <v>137</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>4</v>
@@ -2185,10 +2188,10 @@
     </row>
     <row r="41" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="6">
-        <v>980</v>
+        <v>974</v>
       </c>
       <c r="B41" t="s">
-        <v>133</v>
+        <v>172</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>4</v>
@@ -2199,24 +2202,24 @@
     </row>
     <row r="42" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="6">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="B42" t="s">
-        <v>197</v>
+        <v>133</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>5</v>
+      <c r="D42" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="6">
-        <v>987</v>
+        <v>982</v>
       </c>
       <c r="B43" t="s">
-        <v>80</v>
+        <v>197</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>4</v>
@@ -2227,24 +2230,24 @@
     </row>
     <row r="44" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="6">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="B44" t="s">
-        <v>191</v>
+        <v>80</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D44" s="1" t="s">
-        <v>8</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="6">
-        <v>992</v>
+        <v>989</v>
       </c>
       <c r="B45" t="s">
-        <v>66</v>
+        <v>191</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>4</v>
@@ -2255,10 +2258,10 @@
     </row>
     <row r="46" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="6">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="B46" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>4</v>
@@ -2269,10 +2272,10 @@
     </row>
     <row r="47" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="6">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B47" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>4</v>
@@ -2283,10 +2286,10 @@
     </row>
     <row r="48" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="6">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="B48" t="s">
-        <v>44</v>
+        <v>97</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>4</v>
@@ -2297,10 +2300,10 @@
     </row>
     <row r="49" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="6">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B49" t="s">
-        <v>99</v>
+        <v>44</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>4</v>
@@ -2311,38 +2314,38 @@
     </row>
     <row r="50" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="6">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B50" t="s">
-        <v>180</v>
+        <v>99</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D50" t="s">
-        <v>9</v>
+      <c r="D50" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="6">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B51" t="s">
-        <v>222</v>
+        <v>180</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D51" s="1" t="s">
-        <v>8</v>
+      <c r="D51" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="6">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B52" t="s">
-        <v>75</v>
+        <v>222</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>4</v>
@@ -2353,10 +2356,10 @@
     </row>
     <row r="53" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="6">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B53" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>4</v>
@@ -2367,10 +2370,10 @@
     </row>
     <row r="54" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="6">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="B54" t="s">
-        <v>182</v>
+        <v>46</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>4</v>
@@ -2381,38 +2384,38 @@
     </row>
     <row r="55" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B55" t="s">
-        <v>115</v>
+        <v>182</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D55" s="3" t="s">
-        <v>5</v>
+      <c r="D55" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="6">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B56" t="s">
-        <v>214</v>
+        <v>115</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D56" s="1" t="s">
-        <v>8</v>
+      <c r="D56" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="6">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="B57" t="s">
-        <v>74</v>
+        <v>214</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>4</v>
@@ -2423,24 +2426,24 @@
     </row>
     <row r="58" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="6">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B58" t="s">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D58" t="s">
-        <v>9</v>
+      <c r="D58" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="6">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="B59" t="s">
-        <v>189</v>
+        <v>109</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>4</v>
@@ -2451,24 +2454,24 @@
     </row>
     <row r="60" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="6">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B60" t="s">
-        <v>152</v>
+        <v>189</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D60" s="1" t="s">
-        <v>8</v>
+      <c r="D60" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="6">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="B61" t="s">
-        <v>35</v>
+        <v>152</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>4</v>
@@ -2479,10 +2482,10 @@
     </row>
     <row r="62" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="6">
-        <v>1018</v>
-      </c>
-      <c r="B62" s="18" t="s">
-        <v>399</v>
+        <v>1015</v>
+      </c>
+      <c r="B62" t="s">
+        <v>35</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>4</v>
@@ -2493,52 +2496,52 @@
     </row>
     <row r="63" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="6">
-        <v>1020</v>
-      </c>
-      <c r="B63" t="s">
-        <v>362</v>
+        <v>1018</v>
+      </c>
+      <c r="B63" s="18" t="s">
+        <v>399</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D63" s="11" t="s">
-        <v>5</v>
+      <c r="D63" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="6">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B64" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D64" s="14" t="s">
+      <c r="D64" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="6">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="B65" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D65" s="11" t="s">
+      <c r="D65" s="14" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="6">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B66" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>4</v>
@@ -2549,136 +2552,136 @@
     </row>
     <row r="67" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="6">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B67" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="6">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B68" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D68" s="14" t="s">
-        <v>5</v>
+      <c r="D68" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="6">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B69" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D69" s="11" t="s">
+      <c r="D69" s="14" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="6">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B70" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D70" s="14" t="s">
-        <v>8</v>
+      <c r="D70" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="6">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B71" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D71" s="11" t="s">
-        <v>5</v>
+      <c r="D71" s="14" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="6">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B72" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D72" s="14" t="s">
+      <c r="D72" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="6">
-        <v>1031</v>
-      </c>
-      <c r="B73" s="8" t="s">
-        <v>346</v>
+        <v>1030</v>
+      </c>
+      <c r="B73" t="s">
+        <v>356</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D73" s="14" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="6">
-        <v>1032</v>
-      </c>
-      <c r="B74" t="s">
-        <v>369</v>
+        <v>1031</v>
+      </c>
+      <c r="B74" s="8" t="s">
+        <v>346</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D74" s="14" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="6">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B75" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D75" s="11" t="s">
+      <c r="D75" s="14" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="6">
-        <v>1034</v>
-      </c>
-      <c r="B76" s="8" t="s">
-        <v>373</v>
+        <v>1033</v>
+      </c>
+      <c r="B76" t="s">
+        <v>357</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>4</v>
@@ -2689,10 +2692,10 @@
     </row>
     <row r="77" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="6">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>345</v>
+        <v>373</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>4</v>
@@ -2703,10 +2706,10 @@
     </row>
     <row r="78" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="6">
-        <v>1036</v>
-      </c>
-      <c r="B78" t="s">
-        <v>358</v>
+        <v>1035</v>
+      </c>
+      <c r="B78" s="8" t="s">
+        <v>345</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>4</v>
@@ -2717,10 +2720,10 @@
     </row>
     <row r="79" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="6">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="B79" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>4</v>
@@ -2731,10 +2734,10 @@
     </row>
     <row r="80" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="6">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B80" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>4</v>
@@ -2745,10 +2748,10 @@
     </row>
     <row r="81" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="6">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="B81" t="s">
-        <v>371</v>
+        <v>352</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>4</v>
@@ -2759,66 +2762,66 @@
     </row>
     <row r="82" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="6">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="B82" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="6">
-        <v>1044</v>
+        <v>1040</v>
       </c>
       <c r="B83" t="s">
-        <v>394</v>
+        <v>372</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D83" s="11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="6">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="B84" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D84" s="11" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="6">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="B85" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D85" s="11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="6">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="B86" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>4</v>
@@ -2829,66 +2832,66 @@
     </row>
     <row r="87" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="6">
-        <v>1050</v>
-      </c>
-      <c r="B87" s="18" t="s">
-        <v>409</v>
+        <v>1049</v>
+      </c>
+      <c r="B87" t="s">
+        <v>406</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D87" s="11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="6">
-        <v>1416</v>
-      </c>
-      <c r="B88" t="s">
-        <v>217</v>
+        <v>1050</v>
+      </c>
+      <c r="B88" s="18" t="s">
+        <v>409</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D88" s="1" t="s">
-        <v>8</v>
+      <c r="D88" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="6">
-        <v>10107</v>
+        <v>1416</v>
       </c>
       <c r="B89" t="s">
-        <v>96</v>
+        <v>217</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D89" t="s">
-        <v>9</v>
+      <c r="D89" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="6">
-        <v>10137</v>
+        <v>10107</v>
       </c>
       <c r="B90" t="s">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D90" s="1" t="s">
-        <v>8</v>
+      <c r="D90" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="6">
-        <v>10157</v>
+        <v>10137</v>
       </c>
       <c r="B91" t="s">
-        <v>183</v>
+        <v>123</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>4</v>
@@ -2899,10 +2902,10 @@
     </row>
     <row r="92" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="6">
-        <v>10158</v>
+        <v>10157</v>
       </c>
       <c r="B92" t="s">
-        <v>65</v>
+        <v>183</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>4</v>
@@ -2913,108 +2916,108 @@
     </row>
     <row r="93" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="6">
-        <v>10160</v>
+        <v>10158</v>
       </c>
       <c r="B93" t="s">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D93" s="13" t="s">
-        <v>5</v>
+      <c r="D93" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="6">
-        <v>10162</v>
+        <v>10160</v>
       </c>
       <c r="B94" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D94" s="1" t="s">
-        <v>8</v>
+      <c r="D94" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="6">
-        <v>10163</v>
+        <v>10162</v>
       </c>
       <c r="B95" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D95" s="13" t="s">
-        <v>5</v>
+      <c r="D95" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="6">
-        <v>10165</v>
+        <v>10163</v>
       </c>
       <c r="B96" t="s">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D96" s="1" t="s">
-        <v>8</v>
+      <c r="D96" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="6">
-        <v>10166</v>
-      </c>
-      <c r="B97" s="8" t="s">
-        <v>348</v>
+        <v>10165</v>
+      </c>
+      <c r="B97" t="s">
+        <v>19</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D97" s="11" t="s">
+      <c r="D97" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="6">
-        <v>10167</v>
-      </c>
-      <c r="B98" t="s">
-        <v>39</v>
+        <v>10166</v>
+      </c>
+      <c r="B98" s="8" t="s">
+        <v>348</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D98" s="13" t="s">
-        <v>5</v>
+      <c r="D98" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="6">
-        <v>10424</v>
+        <v>10167</v>
       </c>
       <c r="B99" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D99" s="17" t="s">
-        <v>9</v>
+      <c r="D99" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="6">
-        <v>10425</v>
+        <v>10424</v>
       </c>
       <c r="B100" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>4</v>
@@ -3025,24 +3028,24 @@
     </row>
     <row r="101" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="6">
-        <v>20094</v>
+        <v>10425</v>
       </c>
       <c r="B101" t="s">
-        <v>198</v>
+        <v>15</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D101" s="10" t="s">
-        <v>8</v>
+      <c r="D101" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="6">
-        <v>20095</v>
+        <v>20094</v>
       </c>
       <c r="B102" t="s">
-        <v>153</v>
+        <v>198</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>4</v>
@@ -3053,66 +3056,66 @@
     </row>
     <row r="103" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="6">
-        <v>20096</v>
+        <v>20095</v>
       </c>
       <c r="B103" t="s">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D103" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="6">
-        <v>20100</v>
+        <v>20096</v>
       </c>
       <c r="B104" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D104" s="1" t="s">
-        <v>8</v>
+      <c r="D104" s="10" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="6">
-        <v>20101</v>
+        <v>20100</v>
       </c>
       <c r="B105" t="s">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="6">
-        <v>20103</v>
+        <v>20101</v>
       </c>
       <c r="B106" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="6">
-        <v>20106</v>
+        <v>20103</v>
       </c>
       <c r="B107" t="s">
-        <v>155</v>
+        <v>81</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>4</v>
@@ -3123,80 +3126,80 @@
     </row>
     <row r="108" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="6">
-        <v>20108</v>
+        <v>20106</v>
       </c>
       <c r="B108" t="s">
-        <v>219</v>
+        <v>155</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D108" s="10" t="s">
+      <c r="D108" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="6">
-        <v>20109</v>
+        <v>20108</v>
       </c>
       <c r="B109" t="s">
-        <v>53</v>
+        <v>219</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D109" s="1" t="s">
+      <c r="D109" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="6">
-        <v>20110</v>
+        <v>20109</v>
       </c>
       <c r="B110" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D110" s="13" t="s">
-        <v>5</v>
+      <c r="D110" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="6">
-        <v>20113</v>
+        <v>20110</v>
       </c>
       <c r="B111" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D111" s="10" t="s">
-        <v>8</v>
+      <c r="D111" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="6">
-        <v>20114</v>
+        <v>20113</v>
       </c>
       <c r="B112" t="s">
-        <v>126</v>
+        <v>93</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D112" s="1" t="s">
+      <c r="D112" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="6">
-        <v>20116</v>
+        <v>20114</v>
       </c>
       <c r="B113" t="s">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>4</v>
@@ -3207,10 +3210,10 @@
     </row>
     <row r="114" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="6">
-        <v>20117</v>
+        <v>20116</v>
       </c>
       <c r="B114" t="s">
-        <v>186</v>
+        <v>73</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>4</v>
@@ -3221,10 +3224,10 @@
     </row>
     <row r="115" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="6">
-        <v>20118</v>
+        <v>20117</v>
       </c>
       <c r="B115" t="s">
-        <v>160</v>
+        <v>186</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>4</v>
@@ -3235,10 +3238,10 @@
     </row>
     <row r="116" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="6">
-        <v>20120</v>
+        <v>20118</v>
       </c>
       <c r="B116" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>4</v>
@@ -3249,10 +3252,10 @@
     </row>
     <row r="117" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="6">
-        <v>20121</v>
+        <v>20120</v>
       </c>
       <c r="B117" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>4</v>
@@ -3263,38 +3266,38 @@
     </row>
     <row r="118" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="6">
-        <v>20125</v>
+        <v>20121</v>
       </c>
       <c r="B118" t="s">
-        <v>88</v>
+        <v>159</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D118" s="10" t="s">
+      <c r="D118" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="6">
-        <v>20127</v>
+        <v>20125</v>
       </c>
       <c r="B119" t="s">
-        <v>168</v>
+        <v>88</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D119" s="1" t="s">
+      <c r="D119" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="6">
-        <v>20128</v>
+        <v>20127</v>
       </c>
       <c r="B120" t="s">
-        <v>208</v>
+        <v>168</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>4</v>
@@ -3305,52 +3308,52 @@
     </row>
     <row r="121" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="6">
-        <v>20129</v>
+        <v>20128</v>
       </c>
       <c r="B121" t="s">
-        <v>326</v>
+        <v>208</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D121" s="10" t="s">
+      <c r="D121" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="122" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="6">
-        <v>20137</v>
+        <v>20129</v>
       </c>
       <c r="B122" t="s">
-        <v>79</v>
+        <v>326</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D122" s="3" t="s">
-        <v>5</v>
+      <c r="D122" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="6">
-        <v>20138</v>
+        <v>20137</v>
       </c>
       <c r="B123" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D123" s="13" t="s">
+      <c r="D123" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="6">
-        <v>20140</v>
+        <v>20138</v>
       </c>
       <c r="B124" t="s">
-        <v>218</v>
+        <v>113</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>4</v>
@@ -3361,24 +3364,24 @@
     </row>
     <row r="125" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="6">
-        <v>20142</v>
+        <v>20140</v>
       </c>
       <c r="B125" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D125" s="1" t="s">
-        <v>8</v>
+      <c r="D125" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="6">
-        <v>20146</v>
+        <v>20142</v>
       </c>
       <c r="B126" t="s">
-        <v>148</v>
+        <v>193</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>4</v>
@@ -3389,10 +3392,10 @@
     </row>
     <row r="127" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="6">
-        <v>20148</v>
+        <v>20146</v>
       </c>
       <c r="B127" t="s">
-        <v>38</v>
+        <v>148</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>4</v>
@@ -3403,52 +3406,52 @@
     </row>
     <row r="128" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="6">
-        <v>20156</v>
+        <v>20148</v>
       </c>
       <c r="B128" t="s">
-        <v>179</v>
+        <v>38</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D128" s="10" t="s">
+      <c r="D128" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="6">
-        <v>20159</v>
+        <v>20156</v>
       </c>
       <c r="B129" t="s">
-        <v>120</v>
+        <v>179</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D129" s="17" t="s">
-        <v>9</v>
+      <c r="D129" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="6">
-        <v>20160</v>
+        <v>20159</v>
       </c>
       <c r="B130" t="s">
-        <v>224</v>
+        <v>120</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D130" s="10" t="s">
-        <v>8</v>
+      <c r="D130" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="6">
-        <v>20163</v>
+        <v>20160</v>
       </c>
       <c r="B131" t="s">
-        <v>23</v>
+        <v>224</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>4</v>
@@ -3459,52 +3462,52 @@
     </row>
     <row r="132" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="6">
-        <v>20164</v>
+        <v>20163</v>
       </c>
       <c r="B132" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D132" t="s">
-        <v>9</v>
+      <c r="D132" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="6">
-        <v>20165</v>
+        <v>20164</v>
       </c>
       <c r="B133" t="s">
-        <v>131</v>
+        <v>18</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D133" s="10" t="s">
-        <v>8</v>
+      <c r="D133" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="6">
-        <v>20166</v>
+        <v>20165</v>
       </c>
       <c r="B134" t="s">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D134" s="1" t="s">
+      <c r="D134" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="6">
-        <v>20169</v>
+        <v>20166</v>
       </c>
       <c r="B135" t="s">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>4</v>
@@ -3515,38 +3518,38 @@
     </row>
     <row r="136" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="6">
-        <v>20173</v>
+        <v>20169</v>
       </c>
       <c r="B136" t="s">
-        <v>112</v>
+        <v>151</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D136" s="10" t="s">
+      <c r="D136" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="6">
-        <v>20174</v>
+        <v>20173</v>
       </c>
       <c r="B137" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D137" s="1" t="s">
+      <c r="D137" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="6">
-        <v>20178</v>
+        <v>20174</v>
       </c>
       <c r="B138" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>4</v>
@@ -3557,80 +3560,80 @@
     </row>
     <row r="139" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="6">
-        <v>20179</v>
+        <v>20178</v>
       </c>
       <c r="B139" t="s">
-        <v>171</v>
+        <v>117</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D139" t="s">
-        <v>9</v>
+      <c r="D139" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="6">
-        <v>20180</v>
+        <v>20179</v>
       </c>
       <c r="B140" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D140" s="1" t="s">
-        <v>8</v>
+      <c r="D140" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="6">
-        <v>20183</v>
+        <v>20180</v>
       </c>
       <c r="B141" t="s">
-        <v>370</v>
+        <v>149</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D141" s="14" t="s">
-        <v>5</v>
+      <c r="D141" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="6">
-        <v>20189</v>
+        <v>20183</v>
       </c>
       <c r="B142" t="s">
-        <v>329</v>
+        <v>370</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D142" s="1" t="s">
-        <v>8</v>
+      <c r="D142" s="14" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="6">
-        <v>20200</v>
+        <v>20189</v>
       </c>
       <c r="B143" t="s">
-        <v>83</v>
+        <v>329</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D143" s="13" t="s">
-        <v>5</v>
+      <c r="D143" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="6">
-        <v>20201</v>
+        <v>20200</v>
       </c>
       <c r="B144" t="s">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>4</v>
@@ -3641,150 +3644,150 @@
     </row>
     <row r="145" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="6">
-        <v>20204</v>
+        <v>20201</v>
       </c>
       <c r="B145" t="s">
-        <v>57</v>
+        <v>145</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D145" s="10" t="s">
-        <v>8</v>
+      <c r="D145" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="6">
-        <v>20205</v>
+        <v>20204</v>
       </c>
       <c r="B146" t="s">
-        <v>206</v>
+        <v>57</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D146" s="1" t="s">
-        <v>9</v>
+      <c r="D146" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="6">
-        <v>20211</v>
+        <v>20205</v>
       </c>
       <c r="B147" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D147" s="10" t="s">
-        <v>8</v>
+      <c r="D147" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="6">
-        <v>20224</v>
+        <v>20211</v>
       </c>
       <c r="B148" t="s">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D148" s="1" t="s">
+      <c r="D148" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="6">
-        <v>20227</v>
+        <v>20224</v>
       </c>
       <c r="B149" t="s">
-        <v>192</v>
+        <v>85</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D149" s="10" t="s">
+      <c r="D149" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="6">
-        <v>20228</v>
+        <v>20227</v>
       </c>
       <c r="B150" t="s">
-        <v>91</v>
+        <v>192</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D150" s="13" t="s">
-        <v>5</v>
+      <c r="D150" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="6">
-        <v>20230</v>
+        <v>20228</v>
       </c>
       <c r="B151" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D151" s="10" t="s">
-        <v>8</v>
+      <c r="D151" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="6">
-        <v>20234</v>
+        <v>20230</v>
       </c>
       <c r="B152" t="s">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D152" s="13" t="s">
-        <v>5</v>
+      <c r="D152" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="6">
-        <v>20236</v>
+        <v>20234</v>
       </c>
       <c r="B153" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D153" s="3" t="s">
+      <c r="D153" s="13" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="6">
-        <v>20238</v>
+        <v>20236</v>
       </c>
       <c r="B154" t="s">
-        <v>139</v>
+        <v>31</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D154" s="13" t="s">
+      <c r="D154" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="155" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="6">
-        <v>20241</v>
+        <v>20238</v>
       </c>
       <c r="B155" t="s">
-        <v>22</v>
+        <v>139</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>4</v>
@@ -3795,24 +3798,24 @@
     </row>
     <row r="156" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="6">
-        <v>20242</v>
+        <v>20241</v>
       </c>
       <c r="B156" t="s">
-        <v>216</v>
+        <v>22</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D156" s="10" t="s">
-        <v>8</v>
+      <c r="D156" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="6">
-        <v>20244</v>
+        <v>20242</v>
       </c>
       <c r="B157" t="s">
-        <v>124</v>
+        <v>216</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>4</v>
@@ -3823,108 +3826,108 @@
     </row>
     <row r="158" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="6">
-        <v>20246</v>
+        <v>20244</v>
       </c>
       <c r="B158" t="s">
-        <v>14</v>
+        <v>124</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D158" s="13" t="s">
-        <v>5</v>
+      <c r="D158" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="159" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A159" s="6">
-        <v>20249</v>
+        <v>20246</v>
       </c>
       <c r="B159" t="s">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D159" s="10" t="s">
-        <v>8</v>
+      <c r="D159" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="160" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="6">
-        <v>20256</v>
+        <v>20249</v>
       </c>
       <c r="B160" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D160" s="1" t="s">
+      <c r="D160" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="161" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="6">
-        <v>20257</v>
+        <v>20256</v>
       </c>
       <c r="B161" t="s">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D161" s="17" t="s">
-        <v>9</v>
+      <c r="D161" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="6">
-        <v>20258</v>
+        <v>20257</v>
       </c>
       <c r="B162" t="s">
-        <v>199</v>
+        <v>150</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D162" s="1" t="s">
-        <v>8</v>
+      <c r="D162" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="163" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="6">
-        <v>20260</v>
+        <v>20258</v>
       </c>
       <c r="B163" t="s">
-        <v>68</v>
+        <v>199</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D163" s="13" t="s">
-        <v>5</v>
+      <c r="D163" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="6">
-        <v>20261</v>
+        <v>20260</v>
       </c>
       <c r="B164" t="s">
-        <v>207</v>
+        <v>68</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D164" s="10" t="s">
-        <v>8</v>
+      <c r="D164" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="165" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="6">
-        <v>20262</v>
+        <v>20261</v>
       </c>
       <c r="B165" t="s">
-        <v>92</v>
+        <v>207</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>4</v>
@@ -3935,206 +3938,206 @@
     </row>
     <row r="166" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="6">
-        <v>20267</v>
+        <v>20262</v>
       </c>
       <c r="B166" t="s">
-        <v>401</v>
+        <v>92</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D166" s="10" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="6">
-        <v>20268</v>
+        <v>20267</v>
       </c>
       <c r="B167" t="s">
-        <v>201</v>
+        <v>401</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D167" s="1" t="s">
-        <v>8</v>
+      <c r="D167" s="10" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="168" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="6">
-        <v>20271</v>
+        <v>20268</v>
       </c>
       <c r="B168" t="s">
-        <v>34</v>
+        <v>201</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D168" s="13" t="s">
-        <v>5</v>
+      <c r="D168" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="6">
-        <v>20272</v>
+        <v>20271</v>
       </c>
       <c r="B169" t="s">
-        <v>178</v>
+        <v>34</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D169" s="1" t="s">
-        <v>8</v>
+      <c r="D169" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A170" s="6">
-        <v>20275</v>
+        <v>20272</v>
       </c>
       <c r="B170" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D170" s="13" t="s">
-        <v>5</v>
+      <c r="D170" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="171" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="6">
-        <v>20277</v>
+        <v>20275</v>
       </c>
       <c r="B171" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D171" s="1" t="s">
-        <v>8</v>
+      <c r="D171" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="6">
-        <v>20281</v>
+        <v>20277</v>
       </c>
       <c r="B172" t="s">
-        <v>105</v>
+        <v>154</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D172" s="3" t="s">
-        <v>5</v>
+      <c r="D172" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="6">
-        <v>20282</v>
+        <v>20281</v>
       </c>
       <c r="B173" t="s">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D173" s="1" t="s">
-        <v>9</v>
+      <c r="D173" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="174" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="6">
-        <v>20284</v>
+        <v>20282</v>
       </c>
       <c r="B174" t="s">
-        <v>17</v>
+        <v>141</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D174" s="17" t="s">
+      <c r="D174" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="175" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="6">
-        <v>20285</v>
+        <v>20284</v>
       </c>
       <c r="B175" t="s">
-        <v>146</v>
+        <v>17</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D175" s="1" t="s">
-        <v>8</v>
+      <c r="D175" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="6">
-        <v>20289</v>
+        <v>20285</v>
       </c>
       <c r="B176" t="s">
-        <v>52</v>
+        <v>146</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D176" s="3" t="s">
-        <v>5</v>
+      <c r="D176" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="177" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A177" s="6">
-        <v>20290</v>
+        <v>20289</v>
       </c>
       <c r="B177" t="s">
-        <v>103</v>
+        <v>52</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D177" s="1" t="s">
-        <v>8</v>
+      <c r="D177" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="6">
-        <v>20291</v>
+        <v>20290</v>
       </c>
       <c r="B178" t="s">
-        <v>187</v>
+        <v>103</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D178" s="10" t="s">
+      <c r="D178" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="179" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="6">
-        <v>20292</v>
+        <v>20291</v>
       </c>
       <c r="B179" t="s">
-        <v>32</v>
+        <v>187</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D179" s="13" t="s">
-        <v>5</v>
+      <c r="D179" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="6">
-        <v>20293</v>
+        <v>20292</v>
       </c>
       <c r="B180" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>4</v>
@@ -4145,52 +4148,52 @@
     </row>
     <row r="181" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="6">
-        <v>20294</v>
+        <v>20293</v>
       </c>
       <c r="B181" t="s">
-        <v>202</v>
+        <v>43</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D181" s="10" t="s">
-        <v>8</v>
+      <c r="D181" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="182" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="6">
-        <v>20296</v>
+        <v>20294</v>
       </c>
       <c r="B182" t="s">
-        <v>144</v>
+        <v>202</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D182" s="13" t="s">
-        <v>5</v>
+      <c r="D182" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="183" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="6">
-        <v>20298</v>
+        <v>20296</v>
       </c>
       <c r="B183" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D183" s="1" t="s">
-        <v>8</v>
+      <c r="D183" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="184" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="6">
-        <v>20299</v>
+        <v>20298</v>
       </c>
       <c r="B184" t="s">
-        <v>58</v>
+        <v>169</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>4</v>
@@ -4201,10 +4204,10 @@
     </row>
     <row r="185" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="6">
-        <v>20301</v>
+        <v>20299</v>
       </c>
       <c r="B185" t="s">
-        <v>134</v>
+        <v>58</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>4</v>
@@ -4215,10 +4218,10 @@
     </row>
     <row r="186" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="6">
-        <v>20303</v>
+        <v>20301</v>
       </c>
       <c r="B186" t="s">
-        <v>37</v>
+        <v>134</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>4</v>
@@ -4229,24 +4232,24 @@
     </row>
     <row r="187" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="6">
-        <v>20309</v>
+        <v>20303</v>
       </c>
       <c r="B187" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D187" s="13" t="s">
-        <v>5</v>
+      <c r="D187" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="188" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="6">
-        <v>20310</v>
+        <v>20309</v>
       </c>
       <c r="B188" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>4</v>
@@ -4257,52 +4260,52 @@
     </row>
     <row r="189" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="6">
-        <v>20318</v>
+        <v>20310</v>
       </c>
       <c r="B189" t="s">
-        <v>209</v>
+        <v>59</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D189" s="1" t="s">
-        <v>8</v>
+      <c r="D189" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="190" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A190" s="6">
-        <v>20319</v>
+        <v>20318</v>
       </c>
       <c r="B190" t="s">
-        <v>101</v>
+        <v>209</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D190" s="10" t="s">
+      <c r="D190" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="191" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="6">
-        <v>20320</v>
+        <v>20319</v>
       </c>
       <c r="B191" t="s">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D191" s="1" t="s">
+      <c r="D191" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="192" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="6">
-        <v>20324</v>
+        <v>20320</v>
       </c>
       <c r="B192" t="s">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>4</v>
@@ -4313,10 +4316,10 @@
     </row>
     <row r="193" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="6">
-        <v>20331</v>
+        <v>20324</v>
       </c>
       <c r="B193" t="s">
-        <v>51</v>
+        <v>210</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>4</v>
@@ -4327,38 +4330,38 @@
     </row>
     <row r="194" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="6">
-        <v>20333</v>
+        <v>20331</v>
       </c>
       <c r="B194" t="s">
-        <v>136</v>
+        <v>51</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D194" s="13" t="s">
-        <v>5</v>
+      <c r="D194" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="195" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A195" s="6">
-        <v>20337</v>
+        <v>20333</v>
       </c>
       <c r="B195" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D195" s="1" t="s">
-        <v>8</v>
+      <c r="D195" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="196" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="6">
-        <v>20343</v>
+        <v>20337</v>
       </c>
       <c r="B196" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>4</v>
@@ -4369,10 +4372,10 @@
     </row>
     <row r="197" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="6">
-        <v>20344</v>
+        <v>20343</v>
       </c>
       <c r="B197" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>4</v>
@@ -4383,66 +4386,66 @@
     </row>
     <row r="198" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A198" s="6">
-        <v>20351</v>
+        <v>20344</v>
       </c>
       <c r="B198" t="s">
-        <v>26</v>
+        <v>127</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D198" s="13" t="s">
-        <v>5</v>
+      <c r="D198" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="199" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="6">
-        <v>20357</v>
+        <v>20351</v>
       </c>
       <c r="B199" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D199" s="1" t="s">
-        <v>8</v>
+      <c r="D199" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="200" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A200" s="6">
-        <v>20361</v>
+        <v>20357</v>
       </c>
       <c r="B200" t="s">
-        <v>164</v>
+        <v>56</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D200" s="13" t="s">
-        <v>5</v>
+      <c r="D200" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="201" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="6">
-        <v>20362</v>
+        <v>20361</v>
       </c>
       <c r="B201" t="s">
-        <v>45</v>
+        <v>164</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D201" s="10" t="s">
-        <v>8</v>
+      <c r="D201" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="202" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="6">
-        <v>20363</v>
+        <v>20362</v>
       </c>
       <c r="B202" t="s">
-        <v>213</v>
+        <v>45</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>4</v>
@@ -4453,38 +4456,38 @@
     </row>
     <row r="203" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="6">
-        <v>20364</v>
+        <v>20363</v>
       </c>
       <c r="B203" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D203" s="13" t="s">
-        <v>5</v>
+      <c r="D203" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="204" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="6">
-        <v>20366</v>
+        <v>20364</v>
       </c>
       <c r="B204" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D204" s="1" t="s">
-        <v>8</v>
+      <c r="D204" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="205" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A205" s="6">
-        <v>20367</v>
+        <v>20366</v>
       </c>
       <c r="B205" t="s">
-        <v>47</v>
+        <v>220</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>4</v>
@@ -4495,10 +4498,10 @@
     </row>
     <row r="206" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A206" s="6">
-        <v>20369</v>
+        <v>20367</v>
       </c>
       <c r="B206" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>4</v>
@@ -4509,10 +4512,10 @@
     </row>
     <row r="207" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A207" s="6">
-        <v>20371</v>
+        <v>20369</v>
       </c>
       <c r="B207" t="s">
-        <v>223</v>
+        <v>63</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>4</v>
@@ -4523,52 +4526,52 @@
     </row>
     <row r="208" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A208" s="6">
-        <v>20372</v>
+        <v>20371</v>
       </c>
       <c r="B208" t="s">
-        <v>70</v>
+        <v>223</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D208" s="10" t="s">
+      <c r="D208" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="209" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A209" s="6">
-        <v>20374</v>
+        <v>20372</v>
       </c>
       <c r="B209" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D209" s="1" t="s">
+      <c r="D209" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="210" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A210" s="6">
-        <v>20377</v>
+        <v>20374</v>
       </c>
       <c r="B210" t="s">
-        <v>225</v>
+        <v>61</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D210" s="10" t="s">
+      <c r="D210" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="211" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="6">
-        <v>20379</v>
+        <v>20377</v>
       </c>
       <c r="B211" t="s">
-        <v>49</v>
+        <v>225</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>4</v>
@@ -4579,66 +4582,66 @@
     </row>
     <row r="212" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A212" s="6">
-        <v>20380</v>
+        <v>20379</v>
       </c>
       <c r="B212" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D212" s="13" t="s">
-        <v>5</v>
+      <c r="D212" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="213" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A213" s="6">
-        <v>20381</v>
+        <v>20380</v>
       </c>
       <c r="B213" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D213" s="1" t="s">
-        <v>8</v>
+      <c r="D213" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="214" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A214" s="6">
-        <v>20384</v>
+        <v>20381</v>
       </c>
       <c r="B214" t="s">
-        <v>181</v>
+        <v>60</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D214" s="10" t="s">
+      <c r="D214" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="215" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A215" s="6">
-        <v>20385</v>
+        <v>20384</v>
       </c>
       <c r="B215" t="s">
-        <v>36</v>
+        <v>181</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D215" s="1" t="s">
+      <c r="D215" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="216" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A216" s="6">
-        <v>20386</v>
+        <v>20385</v>
       </c>
       <c r="B216" t="s">
-        <v>119</v>
+        <v>36</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>4</v>
@@ -4649,66 +4652,66 @@
     </row>
     <row r="217" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A217" s="6">
-        <v>20388</v>
+        <v>20386</v>
       </c>
       <c r="B217" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D217" s="10" t="s">
+      <c r="D217" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="218" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A218" s="6">
-        <v>20391</v>
+        <v>20388</v>
       </c>
       <c r="B218" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D218" s="1" t="s">
+      <c r="D218" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="219" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A219" s="6">
-        <v>20394</v>
+        <v>20391</v>
       </c>
       <c r="B219" t="s">
-        <v>173</v>
+        <v>106</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D219" s="10" t="s">
+      <c r="D219" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="220" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A220" s="6">
-        <v>20395</v>
+        <v>20394</v>
       </c>
       <c r="B220" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D220" s="1" t="s">
+      <c r="D220" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="221" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A221" s="6">
-        <v>20396</v>
+        <v>20395</v>
       </c>
       <c r="B221" t="s">
-        <v>330</v>
+        <v>161</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>4</v>
@@ -4719,52 +4722,52 @@
     </row>
     <row r="222" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A222" s="6">
-        <v>20397</v>
-      </c>
-      <c r="B222" s="8" t="s">
-        <v>344</v>
+        <v>20396</v>
+      </c>
+      <c r="B222" t="s">
+        <v>330</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D222" s="11" t="s">
-        <v>5</v>
+      <c r="D222" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="223" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223" s="6">
-        <v>30101</v>
-      </c>
-      <c r="B223" t="s">
-        <v>167</v>
+        <v>20397</v>
+      </c>
+      <c r="B223" s="8" t="s">
+        <v>344</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D223" s="1" t="s">
-        <v>8</v>
+      <c r="D223" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="224" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="6">
-        <v>40124</v>
+        <v>30101</v>
       </c>
       <c r="B224" t="s">
-        <v>24</v>
+        <v>167</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D224" s="13" t="s">
-        <v>5</v>
+      <c r="D224" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="225" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A225" s="6">
-        <v>40125</v>
+        <v>40124</v>
       </c>
       <c r="B225" t="s">
-        <v>143</v>
+        <v>24</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>4</v>
@@ -4775,24 +4778,24 @@
     </row>
     <row r="226" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A226" s="6">
-        <v>40127</v>
+        <v>40125</v>
       </c>
       <c r="B226" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D226" s="1" t="s">
-        <v>8</v>
+      <c r="D226" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="227" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A227" s="6">
-        <v>40129</v>
+        <v>40127</v>
       </c>
       <c r="B227" t="s">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>4</v>
@@ -4803,24 +4806,24 @@
     </row>
     <row r="228" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A228" s="6">
-        <v>40137</v>
+        <v>40129</v>
       </c>
       <c r="B228" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D228" s="10" t="s">
+      <c r="D228" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="229" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A229" s="6">
-        <v>40139</v>
+        <v>40137</v>
       </c>
       <c r="B229" t="s">
-        <v>327</v>
+        <v>121</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>4</v>
@@ -4831,66 +4834,66 @@
     </row>
     <row r="230" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A230" s="6">
-        <v>40140</v>
+        <v>40139</v>
       </c>
       <c r="B230" t="s">
-        <v>170</v>
+        <v>327</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D230" s="1" t="s">
+      <c r="D230" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="231" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A231" s="6">
-        <v>40141</v>
+        <v>40140</v>
       </c>
       <c r="B231" t="s">
-        <v>111</v>
+        <v>170</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D231" s="13" t="s">
-        <v>5</v>
+      <c r="D231" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="232" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A232" s="6">
-        <v>40143</v>
+        <v>40141</v>
       </c>
       <c r="B232" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D232" s="10" t="s">
-        <v>8</v>
+      <c r="D232" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="233" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A233" s="6">
-        <v>40144</v>
+        <v>40143</v>
       </c>
       <c r="B233" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D233" s="13" t="s">
-        <v>5</v>
+      <c r="D233" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="234" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A234" s="6">
-        <v>40145</v>
+        <v>40144</v>
       </c>
       <c r="B234" t="s">
-        <v>165</v>
+        <v>107</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>4</v>
@@ -4901,206 +4904,206 @@
     </row>
     <row r="235" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A235" s="6">
-        <v>40147</v>
+        <v>40145</v>
       </c>
       <c r="B235" t="s">
-        <v>405</v>
+        <v>165</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D235" s="19" t="s">
-        <v>8</v>
+      <c r="D235" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="236" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A236" s="6">
-        <v>40150</v>
+        <v>40147</v>
       </c>
       <c r="B236" t="s">
-        <v>221</v>
+        <v>405</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D236" s="10" t="s">
+      <c r="D236" s="19" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="237" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A237" s="6">
-        <v>40151</v>
+        <v>40150</v>
       </c>
       <c r="B237" t="s">
-        <v>54</v>
+        <v>221</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D237" s="1" t="s">
+      <c r="D237" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="238" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A238" s="6">
-        <v>50102</v>
+        <v>40151</v>
       </c>
       <c r="B238" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D238" s="13" t="s">
-        <v>5</v>
+      <c r="D238" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="239" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A239" s="6">
-        <v>50222</v>
+        <v>50102</v>
       </c>
       <c r="B239" t="s">
-        <v>215</v>
+        <v>67</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D239" s="1" t="s">
-        <v>8</v>
+      <c r="D239" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="240" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A240" s="6">
-        <v>50223</v>
+        <v>50222</v>
       </c>
       <c r="B240" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D240" s="10" t="s">
+      <c r="D240" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="241" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="6">
-        <v>50224</v>
+        <v>50223</v>
       </c>
       <c r="B241" t="s">
-        <v>42</v>
+        <v>194</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D241" s="3" t="s">
-        <v>5</v>
+      <c r="D241" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="242" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A242" s="6">
-        <v>50444</v>
+        <v>50224</v>
       </c>
       <c r="B242" t="s">
-        <v>116</v>
+        <v>42</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D242" s="1" t="s">
-        <v>8</v>
+      <c r="D242" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="243" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A243" s="6">
-        <v>50445</v>
+        <v>50444</v>
       </c>
       <c r="B243" t="s">
-        <v>354</v>
+        <v>116</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D243" s="11" t="s">
-        <v>5</v>
+      <c r="D243" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="244" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A244" s="6">
-        <v>50607</v>
+        <v>50445</v>
       </c>
       <c r="B244" t="s">
-        <v>76</v>
+        <v>354</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D244" s="13" t="s">
+      <c r="D244" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="245" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A245" s="6">
-        <v>50608</v>
+        <v>50607</v>
       </c>
       <c r="B245" t="s">
-        <v>177</v>
+        <v>76</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D245" s="1" t="s">
-        <v>8</v>
+      <c r="D245" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="246" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A246" s="6">
-        <v>50611</v>
-      </c>
-      <c r="B246" s="8" t="s">
-        <v>347</v>
+        <v>50608</v>
+      </c>
+      <c r="B246" t="s">
+        <v>177</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D246" s="14" t="s">
+      <c r="D246" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="247" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A247" s="6">
-        <v>50622</v>
-      </c>
-      <c r="B247" t="s">
-        <v>95</v>
+        <v>50611</v>
+      </c>
+      <c r="B247" s="8" t="s">
+        <v>347</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D247" s="16" t="s">
+      <c r="D247" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="248" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A248" s="6">
-        <v>50623</v>
+        <v>50622</v>
       </c>
       <c r="B248" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D248" s="10" t="s">
+      <c r="D248" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="249" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A249" s="6">
-        <v>50625</v>
+        <v>50623</v>
       </c>
       <c r="B249" t="s">
-        <v>204</v>
+        <v>110</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>4</v>
@@ -5111,94 +5114,94 @@
     </row>
     <row r="250" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A250" s="6">
-        <v>50629</v>
+        <v>50625</v>
       </c>
       <c r="B250" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D250" s="1" t="s">
+      <c r="D250" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="251" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A251" s="6">
-        <v>50630</v>
+        <v>50629</v>
       </c>
       <c r="B251" t="s">
-        <v>360</v>
+        <v>188</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D251" s="14" t="s">
+      <c r="D251" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="252" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A252" s="6">
-        <v>50803</v>
+        <v>50630</v>
       </c>
       <c r="B252" t="s">
-        <v>82</v>
+        <v>360</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D252" s="1" t="s">
+      <c r="D252" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="253" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A253" s="6">
-        <v>50805</v>
+        <v>50803</v>
       </c>
       <c r="B253" t="s">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D253" s="10" t="s">
+      <c r="D253" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="254" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="6">
-        <v>50806</v>
+        <v>50805</v>
       </c>
       <c r="B254" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D254" s="1" t="s">
+      <c r="D254" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="255" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A255" s="6">
-        <v>50808</v>
+        <v>50806</v>
       </c>
       <c r="B255" t="s">
-        <v>16</v>
+        <v>156</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D255" s="13" t="s">
-        <v>5</v>
+      <c r="D255" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="256" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A256" s="6">
-        <v>50809</v>
+        <v>50808</v>
       </c>
       <c r="B256" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>4</v>
@@ -5209,24 +5212,24 @@
     </row>
     <row r="257" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A257" s="6">
-        <v>50810</v>
+        <v>50809</v>
       </c>
       <c r="B257" t="s">
-        <v>175</v>
+        <v>98</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D257" s="1" t="s">
-        <v>8</v>
+      <c r="D257" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="258" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A258" s="6">
-        <v>50812</v>
+        <v>50810</v>
       </c>
       <c r="B258" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>4</v>
@@ -5237,80 +5240,80 @@
     </row>
     <row r="259" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A259" s="6">
-        <v>50813</v>
+        <v>50812</v>
       </c>
       <c r="B259" t="s">
-        <v>71</v>
+        <v>184</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D259" s="17" t="s">
-        <v>9</v>
+      <c r="D259" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="260" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A260" s="6">
-        <v>50815</v>
+        <v>50813</v>
       </c>
       <c r="B260" t="s">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D260" s="10" t="s">
-        <v>8</v>
+      <c r="D260" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="261" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A261" s="6">
-        <v>50816</v>
+        <v>50815</v>
       </c>
       <c r="B261" t="s">
-        <v>205</v>
+        <v>114</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D261" s="1" t="s">
+      <c r="D261" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="262" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A262" s="6">
-        <v>50818</v>
+        <v>50816</v>
       </c>
       <c r="B262" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D262" s="13" t="s">
-        <v>5</v>
+      <c r="D262" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="263" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A263" s="6">
-        <v>50819</v>
+        <v>50818</v>
       </c>
       <c r="B263" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D263" s="10" t="s">
-        <v>8</v>
+      <c r="D263" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="264" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A264" s="6">
-        <v>50820</v>
+        <v>50819</v>
       </c>
       <c r="B264" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>4</v>
@@ -5321,66 +5324,66 @@
     </row>
     <row r="265" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A265" s="6">
-        <v>50821</v>
+        <v>50820</v>
       </c>
       <c r="B265" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D265" s="1" t="s">
+      <c r="D265" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="266" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A266" s="6">
-        <v>50823</v>
+        <v>50821</v>
       </c>
       <c r="B266" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D266" s="17" t="s">
-        <v>9</v>
+      <c r="D266" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="267" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A267" s="6">
-        <v>50824</v>
+        <v>50823</v>
       </c>
       <c r="B267" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D267" s="13" t="s">
-        <v>5</v>
+      <c r="D267" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="268" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A268" s="6">
-        <v>50825</v>
+        <v>50824</v>
       </c>
       <c r="B268" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D268" s="10" t="s">
-        <v>8</v>
+      <c r="D268" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="269" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A269" s="6">
-        <v>50826</v>
+        <v>50825</v>
       </c>
       <c r="B269" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>4</v>
@@ -5391,24 +5394,24 @@
     </row>
     <row r="270" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A270" s="6">
-        <v>50827</v>
+        <v>50826</v>
       </c>
       <c r="B270" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D270" s="1" t="s">
+      <c r="D270" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="271" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A271" s="6">
-        <v>50829</v>
+        <v>50827</v>
       </c>
       <c r="B271" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>4</v>
@@ -5419,122 +5422,122 @@
     </row>
     <row r="272" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A272" s="6">
-        <v>50830</v>
+        <v>50829</v>
       </c>
       <c r="B272" t="s">
-        <v>366</v>
+        <v>236</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D272" s="11" t="s">
+      <c r="D272" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="273" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A273" s="6">
-        <v>50831</v>
+        <v>50830</v>
       </c>
       <c r="B273" t="s">
-        <v>351</v>
+        <v>366</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D273" s="11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="274" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A274" s="6">
-        <v>50832</v>
-      </c>
-      <c r="B274" s="8" t="s">
-        <v>349</v>
+        <v>50831</v>
+      </c>
+      <c r="B274" t="s">
+        <v>351</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D274" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="275" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A275" s="6">
-        <v>50833</v>
+        <v>50832</v>
       </c>
       <c r="B275" s="8" t="s">
-        <v>397</v>
+        <v>349</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D275" s="11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="276" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A276" s="6">
-        <v>50230</v>
+        <v>50833</v>
       </c>
       <c r="B276" s="8" t="s">
-        <v>379</v>
+        <v>397</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D276" s="11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="277" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A277" s="6">
-        <v>60103</v>
-      </c>
-      <c r="B277" t="s">
-        <v>237</v>
+        <v>50230</v>
+      </c>
+      <c r="B277" s="8" t="s">
+        <v>379</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D277" s="13" t="s">
+      <c r="D277" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="278" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A278" s="6">
-        <v>60109</v>
+        <v>60103</v>
       </c>
       <c r="B278" t="s">
-        <v>328</v>
+        <v>237</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D278" s="11" t="s">
-        <v>9</v>
+      <c r="D278" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="279" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A279" s="6">
-        <v>60124</v>
+        <v>60109</v>
       </c>
       <c r="B279" t="s">
-        <v>238</v>
+        <v>328</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D279" s="13" t="s">
-        <v>5</v>
+      <c r="D279" s="11" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="280" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A280" s="6">
-        <v>60125</v>
+        <v>60124</v>
       </c>
       <c r="B280" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>4</v>
@@ -5545,80 +5548,80 @@
     </row>
     <row r="281" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A281" s="6">
-        <v>60126</v>
+        <v>60125</v>
       </c>
       <c r="B281" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D281" s="10" t="s">
-        <v>8</v>
+      <c r="D281" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="282" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A282" s="6">
-        <v>60128</v>
+        <v>60126</v>
       </c>
       <c r="B282" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D282" s="3" t="s">
-        <v>5</v>
+      <c r="D282" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="283" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A283" s="6">
-        <v>60130</v>
+        <v>60128</v>
       </c>
       <c r="B283" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D283" s="1" t="s">
-        <v>8</v>
+      <c r="D283" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="284" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A284" s="6">
-        <v>60133</v>
+        <v>60130</v>
       </c>
       <c r="B284" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D284" s="13" t="s">
-        <v>5</v>
+      <c r="D284" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="285" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A285" s="6">
-        <v>60134</v>
+        <v>60133</v>
       </c>
       <c r="B285" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D285" s="1" t="s">
-        <v>8</v>
+      <c r="D285" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="286" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A286" s="6">
-        <v>60137</v>
+        <v>60134</v>
       </c>
       <c r="B286" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>4</v>
@@ -5629,10 +5632,10 @@
     </row>
     <row r="287" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A287" s="6">
-        <v>60139</v>
+        <v>60137</v>
       </c>
       <c r="B287" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>4</v>
@@ -5643,10 +5646,10 @@
     </row>
     <row r="288" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A288" s="6">
-        <v>60142</v>
+        <v>60139</v>
       </c>
       <c r="B288" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>4</v>
@@ -5657,10 +5660,10 @@
     </row>
     <row r="289" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A289" s="6">
-        <v>60148</v>
+        <v>60142</v>
       </c>
       <c r="B289" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>4</v>
@@ -5671,10 +5674,10 @@
     </row>
     <row r="290" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A290" s="6">
-        <v>60149</v>
+        <v>60148</v>
       </c>
       <c r="B290" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>4</v>
@@ -5685,66 +5688,66 @@
     </row>
     <row r="291" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A291" s="6">
-        <v>60150</v>
+        <v>60149</v>
       </c>
       <c r="B291" t="s">
-        <v>332</v>
+        <v>249</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D291" s="13" t="s">
-        <v>5</v>
+      <c r="D291" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="292" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A292" s="6">
-        <v>60158</v>
+        <v>60150</v>
       </c>
       <c r="B292" t="s">
-        <v>250</v>
+        <v>332</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D292" s="10" t="s">
-        <v>8</v>
+      <c r="D292" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="293" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A293" s="6">
-        <v>60159</v>
+        <v>60158</v>
       </c>
       <c r="B293" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D293" s="1" t="s">
+      <c r="D293" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="294" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A294" s="6">
-        <v>60162</v>
+        <v>60159</v>
       </c>
       <c r="B294" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D294" s="13" t="s">
-        <v>5</v>
+      <c r="D294" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="295" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A295" s="6">
-        <v>60163</v>
+        <v>60162</v>
       </c>
       <c r="B295" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>4</v>
@@ -5755,24 +5758,24 @@
     </row>
     <row r="296" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A296" s="6">
-        <v>60165</v>
+        <v>60163</v>
       </c>
       <c r="B296" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D296" s="1" t="s">
-        <v>8</v>
+      <c r="D296" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="297" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A297" s="6">
-        <v>60169</v>
+        <v>60165</v>
       </c>
       <c r="B297" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>4</v>
@@ -5783,52 +5786,52 @@
     </row>
     <row r="298" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A298" s="6">
-        <v>60170</v>
-      </c>
-      <c r="B298" s="8" t="s">
-        <v>337</v>
+        <v>60169</v>
+      </c>
+      <c r="B298" t="s">
+        <v>255</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D298" s="11" t="s">
+      <c r="D298" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="299" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A299" s="6">
-        <v>60172</v>
-      </c>
-      <c r="B299" t="s">
-        <v>256</v>
+        <v>60170</v>
+      </c>
+      <c r="B299" s="8" t="s">
+        <v>337</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D299" s="1" t="s">
+      <c r="D299" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="300" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A300" s="6">
-        <v>60174</v>
+        <v>60172</v>
       </c>
       <c r="B300" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D300" s="13" t="s">
-        <v>5</v>
+      <c r="D300" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="301" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A301" s="6">
-        <v>60176</v>
+        <v>60174</v>
       </c>
       <c r="B301" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>4</v>
@@ -5839,52 +5842,52 @@
     </row>
     <row r="302" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A302" s="6">
-        <v>60178</v>
+        <v>60176</v>
       </c>
       <c r="B302" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D302" s="1" t="s">
-        <v>8</v>
+      <c r="D302" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="303" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A303" s="6">
-        <v>60180</v>
+        <v>60178</v>
       </c>
       <c r="B303" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D303" s="10" t="s">
+      <c r="D303" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="304" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A304" s="6">
-        <v>60184</v>
+        <v>60180</v>
       </c>
       <c r="B304" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D304" s="1" t="s">
+      <c r="D304" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="305" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A305" s="6">
-        <v>60190</v>
+        <v>60184</v>
       </c>
       <c r="B305" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>4</v>
@@ -5895,24 +5898,24 @@
     </row>
     <row r="306" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A306" s="6">
-        <v>60191</v>
+        <v>60190</v>
       </c>
       <c r="B306" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D306" s="10" t="s">
+      <c r="D306" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="307" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A307" s="6">
-        <v>60192</v>
+        <v>60191</v>
       </c>
       <c r="B307" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>4</v>
@@ -5923,10 +5926,10 @@
     </row>
     <row r="308" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A308" s="6">
-        <v>60194</v>
-      </c>
-      <c r="B308" s="18" t="s">
-        <v>410</v>
+        <v>60192</v>
+      </c>
+      <c r="B308" t="s">
+        <v>264</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>4</v>
@@ -5937,10 +5940,10 @@
     </row>
     <row r="309" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A309" s="6">
-        <v>60195</v>
-      </c>
-      <c r="B309" t="s">
-        <v>265</v>
+        <v>60194</v>
+      </c>
+      <c r="B309" s="18" t="s">
+        <v>410</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>4</v>
@@ -5951,10 +5954,10 @@
     </row>
     <row r="310" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A310" s="6">
-        <v>60196</v>
+        <v>60195</v>
       </c>
       <c r="B310" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>4</v>
@@ -5965,10 +5968,10 @@
     </row>
     <row r="311" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A311" s="6">
-        <v>60198</v>
+        <v>60196</v>
       </c>
       <c r="B311" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>4</v>
@@ -5979,52 +5982,52 @@
     </row>
     <row r="312" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A312" s="6">
-        <v>60201</v>
+        <v>60198</v>
       </c>
       <c r="B312" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D312" t="s">
-        <v>9</v>
+      <c r="D312" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="313" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A313" s="6">
-        <v>60202</v>
+        <v>60201</v>
       </c>
       <c r="B313" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D313" s="13" t="s">
-        <v>5</v>
+      <c r="D313" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="314" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A314" s="6">
-        <v>60204</v>
+        <v>60202</v>
       </c>
       <c r="B314" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D314" s="1" t="s">
-        <v>8</v>
+      <c r="D314" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="315" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A315" s="6">
-        <v>60205</v>
+        <v>60204</v>
       </c>
       <c r="B315" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>4</v>
@@ -6035,10 +6038,10 @@
     </row>
     <row r="316" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A316" s="6">
-        <v>60206</v>
+        <v>60205</v>
       </c>
       <c r="B316" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>4</v>
@@ -6049,192 +6052,192 @@
     </row>
     <row r="317" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A317" s="6">
-        <v>60209</v>
+        <v>60206</v>
       </c>
       <c r="B317" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D317" s="10" t="s">
+      <c r="D317" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="318" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A318" s="6">
-        <v>60211</v>
+        <v>60209</v>
       </c>
       <c r="B318" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D318" s="1" t="s">
+      <c r="D318" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="319" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A319" s="6">
-        <v>60215</v>
+        <v>60211</v>
       </c>
       <c r="B319" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D319" s="10" t="s">
+      <c r="D319" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="320" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A320" s="6">
-        <v>60216</v>
+        <v>60215</v>
       </c>
       <c r="B320" t="s">
-        <v>381</v>
+        <v>275</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D320" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="321" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A321" s="6">
-        <v>60217</v>
+        <v>60216</v>
       </c>
       <c r="B321" t="s">
-        <v>276</v>
+        <v>381</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D321" s="10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="322" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A322" s="6">
-        <v>60219</v>
+        <v>60217</v>
       </c>
       <c r="B322" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D322" s="1" t="s">
+      <c r="D322" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="323" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A323" s="6">
-        <v>60222</v>
+        <v>60219</v>
       </c>
       <c r="B323" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D323" s="10" t="s">
+      <c r="D323" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="324" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A324" s="6">
-        <v>60225</v>
+        <v>60222</v>
       </c>
       <c r="B324" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D324" s="17" t="s">
-        <v>9</v>
+      <c r="D324" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="325" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A325" s="6">
-        <v>60230</v>
+        <v>60225</v>
       </c>
       <c r="B325" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D325" s="10" t="s">
-        <v>8</v>
+      <c r="D325" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="326" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A326" s="6">
-        <v>60241</v>
-      </c>
-      <c r="B326" s="8" t="s">
-        <v>338</v>
+        <v>60230</v>
+      </c>
+      <c r="B326" t="s">
+        <v>280</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D326" s="7" t="s">
-        <v>9</v>
+      <c r="D326" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="327" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A327" s="6">
-        <v>60242</v>
+        <v>60241</v>
       </c>
       <c r="B327" s="8" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D327" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="328" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A328" s="6">
-        <v>60243</v>
+        <v>60242</v>
       </c>
       <c r="B328" s="8" t="s">
-        <v>395</v>
+        <v>341</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D328" s="7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="329" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A329" s="6">
-        <v>60245</v>
+        <v>60243</v>
       </c>
       <c r="B329" s="8" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D329" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="330" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A330" s="6">
-        <v>60246</v>
+        <v>60245</v>
       </c>
       <c r="B330" s="8" t="s">
-        <v>407</v>
+        <v>387</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>4</v>
@@ -6245,10 +6248,10 @@
     </row>
     <row r="331" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A331" s="6">
-        <v>60249</v>
-      </c>
-      <c r="B331" s="18" t="s">
-        <v>408</v>
+        <v>60246</v>
+      </c>
+      <c r="B331" s="8" t="s">
+        <v>407</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>4</v>
@@ -6259,38 +6262,38 @@
     </row>
     <row r="332" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A332" s="6">
-        <v>60250</v>
-      </c>
-      <c r="B332" s="8" t="s">
-        <v>339</v>
+        <v>60249</v>
+      </c>
+      <c r="B332" s="18" t="s">
+        <v>408</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D332" s="11" t="s">
-        <v>8</v>
+      <c r="D332" s="7" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="333" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A333" s="6">
-        <v>60253</v>
-      </c>
-      <c r="B333" t="s">
-        <v>281</v>
+        <v>60250</v>
+      </c>
+      <c r="B333" s="8" t="s">
+        <v>339</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D333" s="1" t="s">
+      <c r="D333" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="334" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A334" s="6">
-        <v>60254</v>
+        <v>60253</v>
       </c>
       <c r="B334" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>4</v>
@@ -6301,10 +6304,10 @@
     </row>
     <row r="335" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A335" s="6">
-        <v>60257</v>
+        <v>60254</v>
       </c>
       <c r="B335" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>4</v>
@@ -6315,10 +6318,10 @@
     </row>
     <row r="336" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A336" s="6">
-        <v>60258</v>
+        <v>60257</v>
       </c>
       <c r="B336" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>4</v>
@@ -6329,66 +6332,66 @@
     </row>
     <row r="337" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A337" s="6">
-        <v>60266</v>
-      </c>
-      <c r="B337" s="8" t="s">
-        <v>343</v>
+        <v>60258</v>
+      </c>
+      <c r="B337" t="s">
+        <v>284</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D337" s="11" t="s">
+      <c r="D337" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="338" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A338" s="6">
-        <v>60269</v>
-      </c>
-      <c r="B338" t="s">
-        <v>285</v>
+        <v>60266</v>
+      </c>
+      <c r="B338" s="8" t="s">
+        <v>343</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D338" s="10" t="s">
+      <c r="D338" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="339" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A339" s="6">
-        <v>60270</v>
+        <v>60269</v>
       </c>
       <c r="B339" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D339" s="1" t="s">
-        <v>9</v>
+      <c r="D339" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="340" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A340" s="6">
-        <v>60272</v>
+        <v>60270</v>
       </c>
       <c r="B340" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="341" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A341" s="6">
-        <v>60274</v>
+        <v>60272</v>
       </c>
       <c r="B341" t="s">
-        <v>380</v>
+        <v>287</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>4</v>
@@ -6399,10 +6402,10 @@
     </row>
     <row r="342" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A342" s="6">
-        <v>60275</v>
+        <v>60274</v>
       </c>
       <c r="B342" t="s">
-        <v>288</v>
+        <v>380</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>4</v>
@@ -6413,10 +6416,10 @@
     </row>
     <row r="343" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A343" s="6">
-        <v>60276</v>
+        <v>60275</v>
       </c>
       <c r="B343" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>4</v>
@@ -6427,108 +6430,108 @@
     </row>
     <row r="344" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A344" s="6">
-        <v>60278</v>
+        <v>60276</v>
       </c>
       <c r="B344" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D344" s="13" t="s">
+      <c r="D344" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="345" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A345" s="6">
-        <v>60279</v>
+        <v>60278</v>
       </c>
       <c r="B345" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D345" s="1" t="s">
+      <c r="D345" s="13" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="346" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A346" s="6">
-        <v>60280</v>
+        <v>60279</v>
       </c>
       <c r="B346" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="347" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A347" s="6">
-        <v>60281</v>
-      </c>
-      <c r="B347" s="8" t="s">
-        <v>336</v>
+        <v>60280</v>
+      </c>
+      <c r="B347" t="s">
+        <v>292</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D347" s="11" t="s">
-        <v>9</v>
+      <c r="D347" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="348" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A348" s="6">
-        <v>60282</v>
+        <v>60281</v>
       </c>
       <c r="B348" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D348" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="349" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A349" s="6">
-        <v>60283</v>
-      </c>
-      <c r="B349" t="s">
-        <v>378</v>
+        <v>60282</v>
+      </c>
+      <c r="B349" s="8" t="s">
+        <v>340</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D349" s="1" t="s">
-        <v>8</v>
+      <c r="D349" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="350" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A350" s="6">
-        <v>60284</v>
-      </c>
-      <c r="B350" s="8" t="s">
-        <v>335</v>
+        <v>60283</v>
+      </c>
+      <c r="B350" t="s">
+        <v>378</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D350" s="9" t="s">
-        <v>5</v>
+      <c r="D350" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="351" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A351" s="6">
-        <v>60285</v>
+        <v>60284</v>
       </c>
       <c r="B351" s="8" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>4</v>
@@ -6539,10 +6542,10 @@
     </row>
     <row r="352" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A352" s="6">
-        <v>60286</v>
+        <v>60285</v>
       </c>
       <c r="B352" s="8" t="s">
-        <v>334</v>
+        <v>350</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>4</v>
@@ -6553,52 +6556,52 @@
     </row>
     <row r="353" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A353" s="6">
-        <v>60287</v>
-      </c>
-      <c r="B353" t="s">
-        <v>377</v>
+        <v>60286</v>
+      </c>
+      <c r="B353" s="8" t="s">
+        <v>334</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D353" s="12" t="s">
+      <c r="D353" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="354" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A354" s="6">
-        <v>60289</v>
+        <v>60287</v>
       </c>
       <c r="B354" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D354" s="12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="355" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A355" s="6">
-        <v>60290</v>
+        <v>60289</v>
       </c>
       <c r="B355" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D355" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="356" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A356" s="6">
-        <v>60291</v>
+        <v>60290</v>
       </c>
       <c r="B356" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>4</v>
@@ -6609,24 +6612,24 @@
     </row>
     <row r="357" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A357" s="6">
-        <v>60292</v>
-      </c>
-      <c r="B357" s="18" t="s">
-        <v>400</v>
+        <v>60291</v>
+      </c>
+      <c r="B357" t="s">
+        <v>376</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D357" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="358" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A358" s="6">
-        <v>60296</v>
-      </c>
-      <c r="B358" t="s">
-        <v>391</v>
+        <v>60292</v>
+      </c>
+      <c r="B358" s="18" t="s">
+        <v>400</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>4</v>
@@ -6637,24 +6640,24 @@
     </row>
     <row r="359" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A359" s="6">
-        <v>60297</v>
+        <v>60296</v>
       </c>
       <c r="B359" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D359" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="360" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A360" s="6">
-        <v>60299</v>
+        <v>60297</v>
       </c>
       <c r="B360" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>4</v>
@@ -6665,10 +6668,10 @@
     </row>
     <row r="361" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A361" s="6">
-        <v>60302</v>
-      </c>
-      <c r="B361" s="18" t="s">
-        <v>411</v>
+        <v>60299</v>
+      </c>
+      <c r="B361" t="s">
+        <v>388</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>4</v>
@@ -6679,10 +6682,10 @@
     </row>
     <row r="362" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A362" s="6">
-        <v>60303</v>
+        <v>60302</v>
       </c>
       <c r="B362" s="18" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>4</v>
@@ -6693,52 +6696,52 @@
     </row>
     <row r="363" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A363" s="6">
-        <v>61001</v>
-      </c>
-      <c r="B363" t="s">
-        <v>403</v>
+        <v>60303</v>
+      </c>
+      <c r="B363" s="18" t="s">
+        <v>412</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D363" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="364" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A364" s="6">
-        <v>61004</v>
+        <v>61001</v>
       </c>
       <c r="B364" t="s">
-        <v>293</v>
+        <v>403</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D364" s="15" t="s">
-        <v>5</v>
+      <c r="D364" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="365" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A365" s="6">
-        <v>61009</v>
+        <v>61004</v>
       </c>
       <c r="B365" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D365" s="12" t="s">
-        <v>8</v>
+      <c r="D365" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="366" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A366" s="6">
-        <v>61012</v>
+        <v>61009</v>
       </c>
       <c r="B366" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>4</v>
@@ -6749,10 +6752,10 @@
     </row>
     <row r="367" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A367" s="6">
-        <v>61018</v>
+        <v>61012</v>
       </c>
       <c r="B367" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>4</v>
@@ -6763,10 +6766,10 @@
     </row>
     <row r="368" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A368" s="6">
-        <v>61102</v>
+        <v>61018</v>
       </c>
       <c r="B368" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>4</v>
@@ -6777,52 +6780,52 @@
     </row>
     <row r="369" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A369" s="6">
-        <v>61205</v>
+        <v>61102</v>
       </c>
       <c r="B369" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D369" s="15" t="s">
-        <v>5</v>
+      <c r="D369" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="370" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A370" s="6">
-        <v>70100</v>
+        <v>61205</v>
       </c>
       <c r="B370" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D370" s="12" t="s">
-        <v>8</v>
+      <c r="D370" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="371" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A371" s="6">
-        <v>70101</v>
+        <v>70100</v>
       </c>
       <c r="B371" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D371" s="15" t="s">
-        <v>5</v>
+      <c r="D371" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="372" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A372" s="6">
-        <v>70102</v>
+        <v>70101</v>
       </c>
       <c r="B372" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>4</v>
@@ -6833,80 +6836,80 @@
     </row>
     <row r="373" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A373" s="6">
-        <v>70103</v>
+        <v>70102</v>
       </c>
       <c r="B373" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D373" s="12" t="s">
-        <v>8</v>
+      <c r="D373" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="374" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A374" s="6">
-        <v>70106</v>
+        <v>70103</v>
       </c>
       <c r="B374" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D374" s="15" t="s">
-        <v>5</v>
+      <c r="D374" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="375" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A375" s="6">
-        <v>70109</v>
+        <v>70106</v>
       </c>
       <c r="B375" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D375" s="12" t="s">
-        <v>8</v>
+      <c r="D375" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="376" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A376" s="6">
-        <v>70113</v>
+        <v>70109</v>
       </c>
       <c r="B376" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D376" s="15" t="s">
-        <v>5</v>
+      <c r="D376" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="377" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A377" s="6">
-        <v>70114</v>
+        <v>70113</v>
       </c>
       <c r="B377" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D377" s="9" t="s">
-        <v>9</v>
+      <c r="D377" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="378" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A378" s="6">
-        <v>70115</v>
+        <v>70114</v>
       </c>
       <c r="B378" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>4</v>
@@ -6917,24 +6920,24 @@
     </row>
     <row r="379" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A379" s="6">
-        <v>70638</v>
+        <v>70115</v>
       </c>
       <c r="B379" t="s">
-        <v>306</v>
+        <v>331</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D379" s="12" t="s">
-        <v>8</v>
+      <c r="D379" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="380" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A380" s="6">
-        <v>70639</v>
+        <v>70638</v>
       </c>
       <c r="B380" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>4</v>
@@ -6945,10 +6948,10 @@
     </row>
     <row r="381" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A381" s="6">
-        <v>70640</v>
+        <v>70639</v>
       </c>
       <c r="B381" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>4</v>
@@ -6959,10 +6962,10 @@
     </row>
     <row r="382" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A382" s="6">
-        <v>70642</v>
+        <v>70640</v>
       </c>
       <c r="B382" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>4</v>
@@ -6973,10 +6976,10 @@
     </row>
     <row r="383" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A383" s="6">
-        <v>90504</v>
+        <v>70642</v>
       </c>
       <c r="B383" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>4</v>
@@ -6987,10 +6990,10 @@
     </row>
     <row r="384" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A384" s="6">
-        <v>90509</v>
+        <v>90504</v>
       </c>
       <c r="B384" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>4</v>
@@ -7001,52 +7004,52 @@
     </row>
     <row r="385" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A385" s="6">
-        <v>90602</v>
+        <v>90509</v>
       </c>
       <c r="B385" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D385" s="15" t="s">
-        <v>5</v>
+      <c r="D385" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="386" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A386" s="6">
-        <v>90621</v>
+        <v>90602</v>
       </c>
       <c r="B386" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D386" s="12" t="s">
-        <v>8</v>
+      <c r="D386" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="387" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A387" s="6">
-        <v>90622</v>
+        <v>90621</v>
       </c>
       <c r="B387" t="s">
-        <v>333</v>
+        <v>313</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D387" s="9" t="s">
-        <v>5</v>
+      <c r="D387" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="388" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A388" s="6">
-        <v>90631</v>
-      </c>
-      <c r="B388" s="8" t="s">
-        <v>342</v>
+        <v>90622</v>
+      </c>
+      <c r="B388" t="s">
+        <v>333</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>4</v>
@@ -7057,24 +7060,24 @@
     </row>
     <row r="389" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A389" s="6">
-        <v>90658</v>
-      </c>
-      <c r="B389" t="s">
-        <v>314</v>
+        <v>90631</v>
+      </c>
+      <c r="B389" s="8" t="s">
+        <v>342</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D389" s="12" t="s">
-        <v>8</v>
+      <c r="D389" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="390" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A390" s="6">
-        <v>90660</v>
+        <v>90658</v>
       </c>
       <c r="B390" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>4</v>
@@ -7085,10 +7088,10 @@
     </row>
     <row r="391" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A391" s="6">
-        <v>90668</v>
+        <v>90660</v>
       </c>
       <c r="B391" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>4</v>
@@ -7099,10 +7102,10 @@
     </row>
     <row r="392" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A392" s="6">
-        <v>90671</v>
+        <v>90668</v>
       </c>
       <c r="B392" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>4</v>
@@ -7113,10 +7116,10 @@
     </row>
     <row r="393" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A393" s="6">
-        <v>90679</v>
+        <v>90671</v>
       </c>
       <c r="B393" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>4</v>
@@ -7127,10 +7130,10 @@
     </row>
     <row r="394" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A394" s="6">
-        <v>90683</v>
+        <v>90679</v>
       </c>
       <c r="B394" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>4</v>
@@ -7141,10 +7144,10 @@
     </row>
     <row r="395" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A395" s="6">
-        <v>90705</v>
+        <v>90683</v>
       </c>
       <c r="B395" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>4</v>
@@ -7155,10 +7158,10 @@
     </row>
     <row r="396" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A396" s="6">
-        <v>90706</v>
+        <v>90705</v>
       </c>
       <c r="B396" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>4</v>
@@ -7169,10 +7172,10 @@
     </row>
     <row r="397" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A397" s="6">
-        <v>90708</v>
+        <v>90706</v>
       </c>
       <c r="B397" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>4</v>
@@ -7183,10 +7186,10 @@
     </row>
     <row r="398" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A398" s="6">
-        <v>90709</v>
+        <v>90708</v>
       </c>
       <c r="B398" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>4</v>
@@ -7197,38 +7200,38 @@
     </row>
     <row r="399" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A399" s="6">
-        <v>90713</v>
+        <v>90709</v>
       </c>
       <c r="B399" t="s">
-        <v>402</v>
+        <v>323</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D399" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="400" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A400" s="6">
-        <v>1218</v>
+        <v>90713</v>
       </c>
       <c r="B400" t="s">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="C400" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D400" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="401" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A401" s="6">
-        <v>1959</v>
-      </c>
-      <c r="B401" s="8" t="s">
-        <v>383</v>
+        <v>1218</v>
+      </c>
+      <c r="B401" t="s">
+        <v>382</v>
       </c>
       <c r="C401" s="1" t="s">
         <v>4</v>
@@ -7239,10 +7242,10 @@
     </row>
     <row r="402" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A402" s="6">
-        <v>5625</v>
+        <v>1959</v>
       </c>
       <c r="B402" s="8" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C402" s="1" t="s">
         <v>4</v>
@@ -7253,10 +7256,10 @@
     </row>
     <row r="403" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A403" s="6">
-        <v>1817</v>
+        <v>5625</v>
       </c>
       <c r="B403" s="8" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="C403" s="1" t="s">
         <v>4</v>
@@ -7267,10 +7270,10 @@
     </row>
     <row r="404" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A404" s="6">
-        <v>5737</v>
+        <v>1817</v>
       </c>
       <c r="B404" s="8" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C404" s="1" t="s">
         <v>4</v>
@@ -7281,34 +7284,48 @@
     </row>
     <row r="405" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A405" s="6">
-        <v>60295</v>
+        <v>5737</v>
       </c>
       <c r="B405" s="8" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C405" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D405" s="9" t="s">
-        <v>9</v>
+      <c r="D405" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="406" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A406" s="6">
+        <v>60295</v>
+      </c>
+      <c r="B406" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="C406" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D406" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A407" s="6">
         <v>1045</v>
       </c>
-      <c r="B406" s="8" t="s">
+      <c r="B407" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="C406" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D406" s="9" t="s">
+      <c r="C407" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D407" s="9" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D349"/>
+  <autoFilter ref="A1:D350"/>
   <sortState ref="A2:D374">
     <sortCondition ref="A277"/>
   </sortState>

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -15,14 +15,14 @@
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$350</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hoja 1'!$A$1:$D$351</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1225" uniqueCount="415">
   <si>
     <t>CUENTA</t>
   </si>
@@ -1264,6 +1264,9 @@
   </si>
   <si>
     <t>FERRETERIA D3</t>
+  </si>
+  <si>
+    <t>FERRETERIA BEDINI</t>
   </si>
 </sst>
 </file>
@@ -1618,7 +1621,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D407"/>
+  <dimension ref="A1:D408"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -2258,24 +2261,24 @@
     </row>
     <row r="46" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="6">
-        <v>992</v>
-      </c>
-      <c r="B46" t="s">
-        <v>66</v>
+        <v>990</v>
+      </c>
+      <c r="B46" s="18" t="s">
+        <v>414</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D46" s="1" t="s">
-        <v>8</v>
+      <c r="D46" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="6">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="B47" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>4</v>
@@ -2286,10 +2289,10 @@
     </row>
     <row r="48" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="6">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B48" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>4</v>
@@ -2300,10 +2303,10 @@
     </row>
     <row r="49" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="6">
-        <v>997</v>
+        <v>994</v>
       </c>
       <c r="B49" t="s">
-        <v>44</v>
+        <v>97</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>4</v>
@@ -2314,10 +2317,10 @@
     </row>
     <row r="50" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="6">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B50" t="s">
-        <v>99</v>
+        <v>44</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>4</v>
@@ -2328,38 +2331,38 @@
     </row>
     <row r="51" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="6">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="B51" t="s">
-        <v>180</v>
+        <v>99</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D51" t="s">
-        <v>9</v>
+      <c r="D51" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="6">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B52" t="s">
-        <v>222</v>
+        <v>180</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D52" s="1" t="s">
-        <v>8</v>
+      <c r="D52" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="6">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="B53" t="s">
-        <v>75</v>
+        <v>222</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>4</v>
@@ -2370,10 +2373,10 @@
     </row>
     <row r="54" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="6">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B54" t="s">
-        <v>46</v>
+        <v>75</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>4</v>
@@ -2384,10 +2387,10 @@
     </row>
     <row r="55" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="B55" t="s">
-        <v>182</v>
+        <v>46</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>4</v>
@@ -2398,38 +2401,38 @@
     </row>
     <row r="56" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="6">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B56" t="s">
-        <v>115</v>
+        <v>182</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D56" s="3" t="s">
-        <v>5</v>
+      <c r="D56" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="6">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B57" t="s">
-        <v>214</v>
+        <v>115</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D57" s="1" t="s">
-        <v>8</v>
+      <c r="D57" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="6">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="B58" t="s">
-        <v>74</v>
+        <v>214</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>4</v>
@@ -2440,24 +2443,24 @@
     </row>
     <row r="59" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="6">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B59" t="s">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D59" t="s">
-        <v>9</v>
+      <c r="D59" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="6">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="B60" t="s">
-        <v>189</v>
+        <v>109</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>4</v>
@@ -2468,24 +2471,24 @@
     </row>
     <row r="61" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="6">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B61" t="s">
-        <v>152</v>
+        <v>189</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D61" s="1" t="s">
-        <v>8</v>
+      <c r="D61" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="6">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="B62" t="s">
-        <v>35</v>
+        <v>152</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>4</v>
@@ -2496,10 +2499,10 @@
     </row>
     <row r="63" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="6">
-        <v>1018</v>
-      </c>
-      <c r="B63" s="18" t="s">
-        <v>399</v>
+        <v>1015</v>
+      </c>
+      <c r="B63" t="s">
+        <v>35</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>4</v>
@@ -2510,52 +2513,52 @@
     </row>
     <row r="64" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="6">
-        <v>1020</v>
-      </c>
-      <c r="B64" t="s">
-        <v>362</v>
+        <v>1018</v>
+      </c>
+      <c r="B64" s="18" t="s">
+        <v>399</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D64" s="11" t="s">
-        <v>5</v>
+      <c r="D64" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="6">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B65" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D65" s="14" t="s">
+      <c r="D65" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="6">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="B66" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D66" s="11" t="s">
+      <c r="D66" s="14" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="6">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B67" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>4</v>
@@ -2566,136 +2569,136 @@
     </row>
     <row r="68" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="6">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B68" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="6">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B69" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D69" s="14" t="s">
-        <v>5</v>
+      <c r="D69" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="6">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B70" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D70" s="11" t="s">
+      <c r="D70" s="14" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="6">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B71" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D71" s="14" t="s">
-        <v>8</v>
+      <c r="D71" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="6">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B72" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D72" s="11" t="s">
-        <v>5</v>
+      <c r="D72" s="14" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="6">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B73" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D73" s="14" t="s">
+      <c r="D73" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="6">
-        <v>1031</v>
-      </c>
-      <c r="B74" s="8" t="s">
-        <v>346</v>
+        <v>1030</v>
+      </c>
+      <c r="B74" t="s">
+        <v>356</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D74" s="14" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="6">
-        <v>1032</v>
-      </c>
-      <c r="B75" t="s">
-        <v>369</v>
+        <v>1031</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>346</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D75" s="14" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="6">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B76" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D76" s="11" t="s">
+      <c r="D76" s="14" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="6">
-        <v>1034</v>
-      </c>
-      <c r="B77" s="8" t="s">
-        <v>373</v>
+        <v>1033</v>
+      </c>
+      <c r="B77" t="s">
+        <v>357</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>4</v>
@@ -2706,10 +2709,10 @@
     </row>
     <row r="78" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="6">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>345</v>
+        <v>373</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>4</v>
@@ -2720,10 +2723,10 @@
     </row>
     <row r="79" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="6">
-        <v>1036</v>
-      </c>
-      <c r="B79" t="s">
-        <v>358</v>
+        <v>1035</v>
+      </c>
+      <c r="B79" s="8" t="s">
+        <v>345</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>4</v>
@@ -2734,10 +2737,10 @@
     </row>
     <row r="80" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="6">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="B80" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>4</v>
@@ -2748,10 +2751,10 @@
     </row>
     <row r="81" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="6">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B81" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C81" s="1" t="s">
         <v>4</v>
@@ -2762,10 +2765,10 @@
     </row>
     <row r="82" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="6">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="B82" t="s">
-        <v>371</v>
+        <v>352</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>4</v>
@@ -2776,66 +2779,66 @@
     </row>
     <row r="83" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="6">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="B83" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D83" s="11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="6">
-        <v>1044</v>
+        <v>1040</v>
       </c>
       <c r="B84" t="s">
-        <v>394</v>
+        <v>372</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D84" s="11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="6">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="B85" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D85" s="11" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="6">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="B86" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D86" s="11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="6">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="B87" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>4</v>
@@ -2846,66 +2849,66 @@
     </row>
     <row r="88" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="6">
-        <v>1050</v>
-      </c>
-      <c r="B88" s="18" t="s">
-        <v>409</v>
+        <v>1049</v>
+      </c>
+      <c r="B88" t="s">
+        <v>406</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D88" s="11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="6">
-        <v>1416</v>
-      </c>
-      <c r="B89" t="s">
-        <v>217</v>
+        <v>1050</v>
+      </c>
+      <c r="B89" s="18" t="s">
+        <v>409</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D89" s="1" t="s">
-        <v>8</v>
+      <c r="D89" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="6">
-        <v>10107</v>
+        <v>1416</v>
       </c>
       <c r="B90" t="s">
-        <v>96</v>
+        <v>217</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D90" t="s">
-        <v>9</v>
+      <c r="D90" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="6">
-        <v>10137</v>
+        <v>10107</v>
       </c>
       <c r="B91" t="s">
-        <v>123</v>
+        <v>96</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D91" s="1" t="s">
-        <v>8</v>
+      <c r="D91" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="6">
-        <v>10157</v>
+        <v>10137</v>
       </c>
       <c r="B92" t="s">
-        <v>183</v>
+        <v>123</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>4</v>
@@ -2916,10 +2919,10 @@
     </row>
     <row r="93" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="6">
-        <v>10158</v>
+        <v>10157</v>
       </c>
       <c r="B93" t="s">
-        <v>65</v>
+        <v>183</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>4</v>
@@ -2930,108 +2933,108 @@
     </row>
     <row r="94" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="6">
-        <v>10160</v>
+        <v>10158</v>
       </c>
       <c r="B94" t="s">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D94" s="13" t="s">
-        <v>5</v>
+      <c r="D94" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="6">
-        <v>10162</v>
+        <v>10160</v>
       </c>
       <c r="B95" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D95" s="1" t="s">
-        <v>8</v>
+      <c r="D95" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="6">
-        <v>10163</v>
+        <v>10162</v>
       </c>
       <c r="B96" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D96" s="13" t="s">
-        <v>5</v>
+      <c r="D96" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="6">
-        <v>10165</v>
+        <v>10163</v>
       </c>
       <c r="B97" t="s">
-        <v>19</v>
+        <v>90</v>
       </c>
       <c r="C97" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D97" s="1" t="s">
-        <v>8</v>
+      <c r="D97" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="6">
-        <v>10166</v>
-      </c>
-      <c r="B98" s="8" t="s">
-        <v>348</v>
+        <v>10165</v>
+      </c>
+      <c r="B98" t="s">
+        <v>19</v>
       </c>
       <c r="C98" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D98" s="11" t="s">
+      <c r="D98" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="6">
-        <v>10167</v>
-      </c>
-      <c r="B99" t="s">
-        <v>39</v>
+        <v>10166</v>
+      </c>
+      <c r="B99" s="8" t="s">
+        <v>348</v>
       </c>
       <c r="C99" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D99" s="13" t="s">
-        <v>5</v>
+      <c r="D99" s="11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="6">
-        <v>10424</v>
+        <v>10167</v>
       </c>
       <c r="B100" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D100" s="17" t="s">
-        <v>9</v>
+      <c r="D100" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="6">
-        <v>10425</v>
+        <v>10424</v>
       </c>
       <c r="B101" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>4</v>
@@ -3042,24 +3045,24 @@
     </row>
     <row r="102" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="6">
-        <v>20094</v>
+        <v>10425</v>
       </c>
       <c r="B102" t="s">
-        <v>198</v>
+        <v>15</v>
       </c>
       <c r="C102" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D102" s="10" t="s">
-        <v>8</v>
+      <c r="D102" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="6">
-        <v>20095</v>
+        <v>20094</v>
       </c>
       <c r="B103" t="s">
-        <v>153</v>
+        <v>198</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>4</v>
@@ -3070,66 +3073,66 @@
     </row>
     <row r="104" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="6">
-        <v>20096</v>
+        <v>20095</v>
       </c>
       <c r="B104" t="s">
-        <v>122</v>
+        <v>153</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D104" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="6">
-        <v>20100</v>
+        <v>20096</v>
       </c>
       <c r="B105" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="C105" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D105" s="1" t="s">
-        <v>8</v>
+      <c r="D105" s="10" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="6">
-        <v>20101</v>
+        <v>20100</v>
       </c>
       <c r="B106" t="s">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="C106" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="6">
-        <v>20103</v>
+        <v>20101</v>
       </c>
       <c r="B107" t="s">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="6">
-        <v>20106</v>
+        <v>20103</v>
       </c>
       <c r="B108" t="s">
-        <v>155</v>
+        <v>81</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>4</v>
@@ -3140,80 +3143,80 @@
     </row>
     <row r="109" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="6">
-        <v>20108</v>
+        <v>20106</v>
       </c>
       <c r="B109" t="s">
-        <v>219</v>
+        <v>155</v>
       </c>
       <c r="C109" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D109" s="10" t="s">
+      <c r="D109" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="6">
-        <v>20109</v>
+        <v>20108</v>
       </c>
       <c r="B110" t="s">
-        <v>53</v>
+        <v>219</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D110" s="1" t="s">
+      <c r="D110" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="6">
-        <v>20110</v>
+        <v>20109</v>
       </c>
       <c r="B111" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D111" s="13" t="s">
-        <v>5</v>
+      <c r="D111" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="6">
-        <v>20113</v>
+        <v>20110</v>
       </c>
       <c r="B112" t="s">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D112" s="10" t="s">
-        <v>8</v>
+      <c r="D112" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="6">
-        <v>20114</v>
+        <v>20113</v>
       </c>
       <c r="B113" t="s">
-        <v>126</v>
+        <v>93</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D113" s="1" t="s">
+      <c r="D113" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="6">
-        <v>20116</v>
+        <v>20114</v>
       </c>
       <c r="B114" t="s">
-        <v>73</v>
+        <v>126</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>4</v>
@@ -3224,10 +3227,10 @@
     </row>
     <row r="115" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="6">
-        <v>20117</v>
+        <v>20116</v>
       </c>
       <c r="B115" t="s">
-        <v>186</v>
+        <v>73</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>4</v>
@@ -3238,10 +3241,10 @@
     </row>
     <row r="116" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="6">
-        <v>20118</v>
+        <v>20117</v>
       </c>
       <c r="B116" t="s">
-        <v>160</v>
+        <v>186</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>4</v>
@@ -3252,10 +3255,10 @@
     </row>
     <row r="117" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="6">
-        <v>20120</v>
+        <v>20118</v>
       </c>
       <c r="B117" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>4</v>
@@ -3266,10 +3269,10 @@
     </row>
     <row r="118" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="6">
-        <v>20121</v>
+        <v>20120</v>
       </c>
       <c r="B118" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>4</v>
@@ -3280,38 +3283,38 @@
     </row>
     <row r="119" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="6">
-        <v>20125</v>
+        <v>20121</v>
       </c>
       <c r="B119" t="s">
-        <v>88</v>
+        <v>159</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D119" s="10" t="s">
+      <c r="D119" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="6">
-        <v>20127</v>
+        <v>20125</v>
       </c>
       <c r="B120" t="s">
-        <v>168</v>
+        <v>88</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D120" s="1" t="s">
+      <c r="D120" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="6">
-        <v>20128</v>
+        <v>20127</v>
       </c>
       <c r="B121" t="s">
-        <v>208</v>
+        <v>168</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>4</v>
@@ -3322,52 +3325,52 @@
     </row>
     <row r="122" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="6">
-        <v>20129</v>
+        <v>20128</v>
       </c>
       <c r="B122" t="s">
-        <v>326</v>
+        <v>208</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D122" s="10" t="s">
+      <c r="D122" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="6">
-        <v>20137</v>
+        <v>20129</v>
       </c>
       <c r="B123" t="s">
-        <v>79</v>
+        <v>326</v>
       </c>
       <c r="C123" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D123" s="3" t="s">
-        <v>5</v>
+      <c r="D123" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="6">
-        <v>20138</v>
+        <v>20137</v>
       </c>
       <c r="B124" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="C124" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D124" s="13" t="s">
+      <c r="D124" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="6">
-        <v>20140</v>
+        <v>20138</v>
       </c>
       <c r="B125" t="s">
-        <v>218</v>
+        <v>113</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>4</v>
@@ -3378,24 +3381,24 @@
     </row>
     <row r="126" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="6">
-        <v>20142</v>
+        <v>20140</v>
       </c>
       <c r="B126" t="s">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="C126" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D126" s="1" t="s">
-        <v>8</v>
+      <c r="D126" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="6">
-        <v>20146</v>
+        <v>20142</v>
       </c>
       <c r="B127" t="s">
-        <v>148</v>
+        <v>193</v>
       </c>
       <c r="C127" s="1" t="s">
         <v>4</v>
@@ -3406,10 +3409,10 @@
     </row>
     <row r="128" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="6">
-        <v>20148</v>
+        <v>20146</v>
       </c>
       <c r="B128" t="s">
-        <v>38</v>
+        <v>148</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>4</v>
@@ -3420,52 +3423,52 @@
     </row>
     <row r="129" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="6">
-        <v>20156</v>
+        <v>20148</v>
       </c>
       <c r="B129" t="s">
-        <v>179</v>
+        <v>38</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D129" s="10" t="s">
+      <c r="D129" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="6">
-        <v>20159</v>
+        <v>20156</v>
       </c>
       <c r="B130" t="s">
-        <v>120</v>
+        <v>179</v>
       </c>
       <c r="C130" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D130" s="17" t="s">
-        <v>9</v>
+      <c r="D130" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="6">
-        <v>20160</v>
+        <v>20159</v>
       </c>
       <c r="B131" t="s">
-        <v>224</v>
+        <v>120</v>
       </c>
       <c r="C131" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D131" s="10" t="s">
-        <v>8</v>
+      <c r="D131" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="6">
-        <v>20163</v>
+        <v>20160</v>
       </c>
       <c r="B132" t="s">
-        <v>23</v>
+        <v>224</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>4</v>
@@ -3476,52 +3479,52 @@
     </row>
     <row r="133" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="6">
-        <v>20164</v>
+        <v>20163</v>
       </c>
       <c r="B133" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C133" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D133" t="s">
-        <v>9</v>
+      <c r="D133" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A134" s="6">
-        <v>20165</v>
+        <v>20164</v>
       </c>
       <c r="B134" t="s">
-        <v>131</v>
+        <v>18</v>
       </c>
       <c r="C134" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D134" s="10" t="s">
-        <v>8</v>
+      <c r="D134" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="6">
-        <v>20166</v>
+        <v>20165</v>
       </c>
       <c r="B135" t="s">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D135" s="1" t="s">
+      <c r="D135" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="6">
-        <v>20169</v>
+        <v>20166</v>
       </c>
       <c r="B136" t="s">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="C136" s="1" t="s">
         <v>4</v>
@@ -3532,38 +3535,38 @@
     </row>
     <row r="137" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="6">
-        <v>20173</v>
+        <v>20169</v>
       </c>
       <c r="B137" t="s">
-        <v>112</v>
+        <v>151</v>
       </c>
       <c r="C137" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D137" s="10" t="s">
+      <c r="D137" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="6">
-        <v>20174</v>
+        <v>20173</v>
       </c>
       <c r="B138" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D138" s="1" t="s">
+      <c r="D138" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A139" s="6">
-        <v>20178</v>
+        <v>20174</v>
       </c>
       <c r="B139" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="C139" s="1" t="s">
         <v>4</v>
@@ -3574,80 +3577,80 @@
     </row>
     <row r="140" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="6">
-        <v>20179</v>
+        <v>20178</v>
       </c>
       <c r="B140" t="s">
-        <v>171</v>
+        <v>117</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D140" t="s">
-        <v>9</v>
+      <c r="D140" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="6">
-        <v>20180</v>
+        <v>20179</v>
       </c>
       <c r="B141" t="s">
-        <v>149</v>
+        <v>171</v>
       </c>
       <c r="C141" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D141" s="1" t="s">
-        <v>8</v>
+      <c r="D141" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="6">
-        <v>20183</v>
+        <v>20180</v>
       </c>
       <c r="B142" t="s">
-        <v>370</v>
+        <v>149</v>
       </c>
       <c r="C142" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D142" s="14" t="s">
-        <v>5</v>
+      <c r="D142" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="6">
-        <v>20189</v>
+        <v>20183</v>
       </c>
       <c r="B143" t="s">
-        <v>329</v>
+        <v>370</v>
       </c>
       <c r="C143" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D143" s="1" t="s">
-        <v>8</v>
+      <c r="D143" s="14" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="6">
-        <v>20200</v>
+        <v>20189</v>
       </c>
       <c r="B144" t="s">
-        <v>83</v>
+        <v>329</v>
       </c>
       <c r="C144" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D144" s="13" t="s">
-        <v>5</v>
+      <c r="D144" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="6">
-        <v>20201</v>
+        <v>20200</v>
       </c>
       <c r="B145" t="s">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="C145" s="1" t="s">
         <v>4</v>
@@ -3658,150 +3661,150 @@
     </row>
     <row r="146" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="6">
-        <v>20204</v>
+        <v>20201</v>
       </c>
       <c r="B146" t="s">
-        <v>57</v>
+        <v>145</v>
       </c>
       <c r="C146" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D146" s="10" t="s">
-        <v>8</v>
+      <c r="D146" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="6">
-        <v>20205</v>
+        <v>20204</v>
       </c>
       <c r="B147" t="s">
-        <v>206</v>
+        <v>57</v>
       </c>
       <c r="C147" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D147" s="1" t="s">
-        <v>9</v>
+      <c r="D147" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="6">
-        <v>20211</v>
+        <v>20205</v>
       </c>
       <c r="B148" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D148" s="10" t="s">
-        <v>8</v>
+      <c r="D148" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="6">
-        <v>20224</v>
+        <v>20211</v>
       </c>
       <c r="B149" t="s">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="C149" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D149" s="1" t="s">
+      <c r="D149" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="6">
-        <v>20227</v>
+        <v>20224</v>
       </c>
       <c r="B150" t="s">
-        <v>192</v>
+        <v>85</v>
       </c>
       <c r="C150" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D150" s="10" t="s">
+      <c r="D150" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="6">
-        <v>20228</v>
+        <v>20227</v>
       </c>
       <c r="B151" t="s">
-        <v>91</v>
+        <v>192</v>
       </c>
       <c r="C151" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D151" s="13" t="s">
-        <v>5</v>
+      <c r="D151" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="6">
-        <v>20230</v>
+        <v>20228</v>
       </c>
       <c r="B152" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C152" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D152" s="10" t="s">
-        <v>8</v>
+      <c r="D152" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="6">
-        <v>20234</v>
+        <v>20230</v>
       </c>
       <c r="B153" t="s">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D153" s="13" t="s">
-        <v>5</v>
+      <c r="D153" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="6">
-        <v>20236</v>
+        <v>20234</v>
       </c>
       <c r="B154" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C154" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D154" s="3" t="s">
+      <c r="D154" s="13" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="155" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="6">
-        <v>20238</v>
+        <v>20236</v>
       </c>
       <c r="B155" t="s">
-        <v>139</v>
+        <v>31</v>
       </c>
       <c r="C155" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D155" s="13" t="s">
+      <c r="D155" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="156" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="6">
-        <v>20241</v>
+        <v>20238</v>
       </c>
       <c r="B156" t="s">
-        <v>22</v>
+        <v>139</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>4</v>
@@ -3812,24 +3815,24 @@
     </row>
     <row r="157" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="6">
-        <v>20242</v>
+        <v>20241</v>
       </c>
       <c r="B157" t="s">
-        <v>216</v>
+        <v>22</v>
       </c>
       <c r="C157" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D157" s="10" t="s">
-        <v>8</v>
+      <c r="D157" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="6">
-        <v>20244</v>
+        <v>20242</v>
       </c>
       <c r="B158" t="s">
-        <v>124</v>
+        <v>216</v>
       </c>
       <c r="C158" s="1" t="s">
         <v>4</v>
@@ -3840,108 +3843,108 @@
     </row>
     <row r="159" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A159" s="6">
-        <v>20246</v>
+        <v>20244</v>
       </c>
       <c r="B159" t="s">
-        <v>14</v>
+        <v>124</v>
       </c>
       <c r="C159" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D159" s="13" t="s">
-        <v>5</v>
+      <c r="D159" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="160" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="6">
-        <v>20249</v>
+        <v>20246</v>
       </c>
       <c r="B160" t="s">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="C160" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D160" s="10" t="s">
-        <v>8</v>
+      <c r="D160" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="161" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="6">
-        <v>20256</v>
+        <v>20249</v>
       </c>
       <c r="B161" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="C161" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D161" s="1" t="s">
+      <c r="D161" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="6">
-        <v>20257</v>
+        <v>20256</v>
       </c>
       <c r="B162" t="s">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D162" s="17" t="s">
-        <v>9</v>
+      <c r="D162" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="163" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="6">
-        <v>20258</v>
+        <v>20257</v>
       </c>
       <c r="B163" t="s">
-        <v>199</v>
+        <v>150</v>
       </c>
       <c r="C163" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D163" s="1" t="s">
-        <v>8</v>
+      <c r="D163" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="6">
-        <v>20260</v>
+        <v>20258</v>
       </c>
       <c r="B164" t="s">
-        <v>68</v>
+        <v>199</v>
       </c>
       <c r="C164" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D164" s="13" t="s">
-        <v>5</v>
+      <c r="D164" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="165" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="6">
-        <v>20261</v>
+        <v>20260</v>
       </c>
       <c r="B165" t="s">
-        <v>207</v>
+        <v>68</v>
       </c>
       <c r="C165" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D165" s="10" t="s">
-        <v>8</v>
+      <c r="D165" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="6">
-        <v>20262</v>
+        <v>20261</v>
       </c>
       <c r="B166" t="s">
-        <v>92</v>
+        <v>207</v>
       </c>
       <c r="C166" s="1" t="s">
         <v>4</v>
@@ -3952,206 +3955,206 @@
     </row>
     <row r="167" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="6">
-        <v>20267</v>
+        <v>20262</v>
       </c>
       <c r="B167" t="s">
-        <v>401</v>
+        <v>92</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D167" s="10" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="168" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="6">
-        <v>20268</v>
+        <v>20267</v>
       </c>
       <c r="B168" t="s">
-        <v>201</v>
+        <v>401</v>
       </c>
       <c r="C168" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D168" s="1" t="s">
-        <v>8</v>
+      <c r="D168" s="10" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="6">
-        <v>20271</v>
+        <v>20268</v>
       </c>
       <c r="B169" t="s">
-        <v>34</v>
+        <v>201</v>
       </c>
       <c r="C169" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D169" s="13" t="s">
-        <v>5</v>
+      <c r="D169" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A170" s="6">
-        <v>20272</v>
+        <v>20271</v>
       </c>
       <c r="B170" t="s">
-        <v>178</v>
+        <v>34</v>
       </c>
       <c r="C170" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D170" s="1" t="s">
-        <v>8</v>
+      <c r="D170" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="171" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="6">
-        <v>20275</v>
+        <v>20272</v>
       </c>
       <c r="B171" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D171" s="13" t="s">
-        <v>5</v>
+      <c r="D171" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="6">
-        <v>20277</v>
+        <v>20275</v>
       </c>
       <c r="B172" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="C172" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D172" s="1" t="s">
-        <v>8</v>
+      <c r="D172" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="6">
-        <v>20281</v>
+        <v>20277</v>
       </c>
       <c r="B173" t="s">
-        <v>105</v>
+        <v>154</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D173" s="3" t="s">
-        <v>5</v>
+      <c r="D173" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="174" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="6">
-        <v>20282</v>
+        <v>20281</v>
       </c>
       <c r="B174" t="s">
-        <v>141</v>
+        <v>105</v>
       </c>
       <c r="C174" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D174" s="1" t="s">
-        <v>9</v>
+      <c r="D174" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="175" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="6">
-        <v>20284</v>
+        <v>20282</v>
       </c>
       <c r="B175" t="s">
-        <v>17</v>
+        <v>141</v>
       </c>
       <c r="C175" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D175" s="17" t="s">
+      <c r="D175" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="6">
-        <v>20285</v>
+        <v>20284</v>
       </c>
       <c r="B176" t="s">
-        <v>146</v>
+        <v>17</v>
       </c>
       <c r="C176" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D176" s="1" t="s">
-        <v>8</v>
+      <c r="D176" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="177" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A177" s="6">
-        <v>20289</v>
+        <v>20285</v>
       </c>
       <c r="B177" t="s">
-        <v>52</v>
+        <v>146</v>
       </c>
       <c r="C177" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D177" s="3" t="s">
-        <v>5</v>
+      <c r="D177" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="6">
-        <v>20290</v>
+        <v>20289</v>
       </c>
       <c r="B178" t="s">
-        <v>103</v>
+        <v>52</v>
       </c>
       <c r="C178" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D178" s="1" t="s">
-        <v>8</v>
+      <c r="D178" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="179" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="6">
-        <v>20291</v>
+        <v>20290</v>
       </c>
       <c r="B179" t="s">
-        <v>187</v>
+        <v>103</v>
       </c>
       <c r="C179" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D179" s="10" t="s">
+      <c r="D179" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="6">
-        <v>20292</v>
+        <v>20291</v>
       </c>
       <c r="B180" t="s">
-        <v>32</v>
+        <v>187</v>
       </c>
       <c r="C180" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D180" s="13" t="s">
-        <v>5</v>
+      <c r="D180" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="6">
-        <v>20293</v>
+        <v>20292</v>
       </c>
       <c r="B181" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C181" s="1" t="s">
         <v>4</v>
@@ -4162,52 +4165,52 @@
     </row>
     <row r="182" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="6">
-        <v>20294</v>
+        <v>20293</v>
       </c>
       <c r="B182" t="s">
-        <v>202</v>
+        <v>43</v>
       </c>
       <c r="C182" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D182" s="10" t="s">
-        <v>8</v>
+      <c r="D182" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="183" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="6">
-        <v>20296</v>
+        <v>20294</v>
       </c>
       <c r="B183" t="s">
-        <v>144</v>
+        <v>202</v>
       </c>
       <c r="C183" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D183" s="13" t="s">
-        <v>5</v>
+      <c r="D183" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="184" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="6">
-        <v>20298</v>
+        <v>20296</v>
       </c>
       <c r="B184" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="C184" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D184" s="1" t="s">
-        <v>8</v>
+      <c r="D184" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="185" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="6">
-        <v>20299</v>
+        <v>20298</v>
       </c>
       <c r="B185" t="s">
-        <v>58</v>
+        <v>169</v>
       </c>
       <c r="C185" s="1" t="s">
         <v>4</v>
@@ -4218,10 +4221,10 @@
     </row>
     <row r="186" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="6">
-        <v>20301</v>
+        <v>20299</v>
       </c>
       <c r="B186" t="s">
-        <v>134</v>
+        <v>58</v>
       </c>
       <c r="C186" s="1" t="s">
         <v>4</v>
@@ -4232,10 +4235,10 @@
     </row>
     <row r="187" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="6">
-        <v>20303</v>
+        <v>20301</v>
       </c>
       <c r="B187" t="s">
-        <v>37</v>
+        <v>134</v>
       </c>
       <c r="C187" s="1" t="s">
         <v>4</v>
@@ -4246,24 +4249,24 @@
     </row>
     <row r="188" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="6">
-        <v>20309</v>
+        <v>20303</v>
       </c>
       <c r="B188" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D188" s="13" t="s">
-        <v>5</v>
+      <c r="D188" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="189" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="6">
-        <v>20310</v>
+        <v>20309</v>
       </c>
       <c r="B189" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>4</v>
@@ -4274,52 +4277,52 @@
     </row>
     <row r="190" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A190" s="6">
-        <v>20318</v>
+        <v>20310</v>
       </c>
       <c r="B190" t="s">
-        <v>209</v>
+        <v>59</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D190" s="1" t="s">
-        <v>8</v>
+      <c r="D190" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="191" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="6">
-        <v>20319</v>
+        <v>20318</v>
       </c>
       <c r="B191" t="s">
-        <v>101</v>
+        <v>209</v>
       </c>
       <c r="C191" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D191" s="10" t="s">
+      <c r="D191" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="192" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="6">
-        <v>20320</v>
+        <v>20319</v>
       </c>
       <c r="B192" t="s">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="C192" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D192" s="1" t="s">
+      <c r="D192" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="193" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="6">
-        <v>20324</v>
+        <v>20320</v>
       </c>
       <c r="B193" t="s">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="C193" s="1" t="s">
         <v>4</v>
@@ -4330,10 +4333,10 @@
     </row>
     <row r="194" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A194" s="6">
-        <v>20331</v>
+        <v>20324</v>
       </c>
       <c r="B194" t="s">
-        <v>51</v>
+        <v>210</v>
       </c>
       <c r="C194" s="1" t="s">
         <v>4</v>
@@ -4344,38 +4347,38 @@
     </row>
     <row r="195" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A195" s="6">
-        <v>20333</v>
+        <v>20331</v>
       </c>
       <c r="B195" t="s">
-        <v>136</v>
+        <v>51</v>
       </c>
       <c r="C195" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D195" s="13" t="s">
-        <v>5</v>
+      <c r="D195" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="196" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A196" s="6">
-        <v>20337</v>
+        <v>20333</v>
       </c>
       <c r="B196" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="C196" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D196" s="1" t="s">
-        <v>8</v>
+      <c r="D196" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="197" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A197" s="6">
-        <v>20343</v>
+        <v>20337</v>
       </c>
       <c r="B197" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="C197" s="1" t="s">
         <v>4</v>
@@ -4386,10 +4389,10 @@
     </row>
     <row r="198" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A198" s="6">
-        <v>20344</v>
+        <v>20343</v>
       </c>
       <c r="B198" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="C198" s="1" t="s">
         <v>4</v>
@@ -4400,66 +4403,66 @@
     </row>
     <row r="199" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="6">
-        <v>20351</v>
+        <v>20344</v>
       </c>
       <c r="B199" t="s">
-        <v>26</v>
+        <v>127</v>
       </c>
       <c r="C199" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D199" s="13" t="s">
-        <v>5</v>
+      <c r="D199" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="200" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A200" s="6">
-        <v>20357</v>
+        <v>20351</v>
       </c>
       <c r="B200" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="C200" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D200" s="1" t="s">
-        <v>8</v>
+      <c r="D200" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="201" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="6">
-        <v>20361</v>
+        <v>20357</v>
       </c>
       <c r="B201" t="s">
-        <v>164</v>
+        <v>56</v>
       </c>
       <c r="C201" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D201" s="13" t="s">
-        <v>5</v>
+      <c r="D201" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="202" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="6">
-        <v>20362</v>
+        <v>20361</v>
       </c>
       <c r="B202" t="s">
-        <v>45</v>
+        <v>164</v>
       </c>
       <c r="C202" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D202" s="10" t="s">
-        <v>8</v>
+      <c r="D202" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="203" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A203" s="6">
-        <v>20363</v>
+        <v>20362</v>
       </c>
       <c r="B203" t="s">
-        <v>213</v>
+        <v>45</v>
       </c>
       <c r="C203" s="1" t="s">
         <v>4</v>
@@ -4470,38 +4473,38 @@
     </row>
     <row r="204" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A204" s="6">
-        <v>20364</v>
+        <v>20363</v>
       </c>
       <c r="B204" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D204" s="13" t="s">
-        <v>5</v>
+      <c r="D204" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="205" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A205" s="6">
-        <v>20366</v>
+        <v>20364</v>
       </c>
       <c r="B205" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="C205" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D205" s="1" t="s">
-        <v>8</v>
+      <c r="D205" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="206" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A206" s="6">
-        <v>20367</v>
+        <v>20366</v>
       </c>
       <c r="B206" t="s">
-        <v>47</v>
+        <v>220</v>
       </c>
       <c r="C206" s="1" t="s">
         <v>4</v>
@@ -4512,10 +4515,10 @@
     </row>
     <row r="207" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A207" s="6">
-        <v>20369</v>
+        <v>20367</v>
       </c>
       <c r="B207" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C207" s="1" t="s">
         <v>4</v>
@@ -4526,10 +4529,10 @@
     </row>
     <row r="208" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A208" s="6">
-        <v>20371</v>
+        <v>20369</v>
       </c>
       <c r="B208" t="s">
-        <v>223</v>
+        <v>63</v>
       </c>
       <c r="C208" s="1" t="s">
         <v>4</v>
@@ -4540,52 +4543,52 @@
     </row>
     <row r="209" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A209" s="6">
-        <v>20372</v>
+        <v>20371</v>
       </c>
       <c r="B209" t="s">
-        <v>70</v>
+        <v>223</v>
       </c>
       <c r="C209" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D209" s="10" t="s">
+      <c r="D209" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="210" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A210" s="6">
-        <v>20374</v>
+        <v>20372</v>
       </c>
       <c r="B210" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="C210" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D210" s="1" t="s">
+      <c r="D210" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="211" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A211" s="6">
-        <v>20377</v>
+        <v>20374</v>
       </c>
       <c r="B211" t="s">
-        <v>225</v>
+        <v>61</v>
       </c>
       <c r="C211" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D211" s="10" t="s">
+      <c r="D211" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="212" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A212" s="6">
-        <v>20379</v>
+        <v>20377</v>
       </c>
       <c r="B212" t="s">
-        <v>49</v>
+        <v>225</v>
       </c>
       <c r="C212" s="1" t="s">
         <v>4</v>
@@ -4596,66 +4599,66 @@
     </row>
     <row r="213" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A213" s="6">
-        <v>20380</v>
+        <v>20379</v>
       </c>
       <c r="B213" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="C213" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D213" s="13" t="s">
-        <v>5</v>
+      <c r="D213" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="214" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A214" s="6">
-        <v>20381</v>
+        <v>20380</v>
       </c>
       <c r="B214" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="C214" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D214" s="1" t="s">
-        <v>8</v>
+      <c r="D214" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="215" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A215" s="6">
-        <v>20384</v>
+        <v>20381</v>
       </c>
       <c r="B215" t="s">
-        <v>181</v>
+        <v>60</v>
       </c>
       <c r="C215" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D215" s="10" t="s">
+      <c r="D215" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="216" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A216" s="6">
-        <v>20385</v>
+        <v>20384</v>
       </c>
       <c r="B216" t="s">
-        <v>36</v>
+        <v>181</v>
       </c>
       <c r="C216" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D216" s="1" t="s">
+      <c r="D216" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="217" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A217" s="6">
-        <v>20386</v>
+        <v>20385</v>
       </c>
       <c r="B217" t="s">
-        <v>119</v>
+        <v>36</v>
       </c>
       <c r="C217" s="1" t="s">
         <v>4</v>
@@ -4666,66 +4669,66 @@
     </row>
     <row r="218" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A218" s="6">
-        <v>20388</v>
+        <v>20386</v>
       </c>
       <c r="B218" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D218" s="10" t="s">
+      <c r="D218" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="219" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A219" s="6">
-        <v>20391</v>
+        <v>20388</v>
       </c>
       <c r="B219" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D219" s="1" t="s">
+      <c r="D219" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="220" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A220" s="6">
-        <v>20394</v>
+        <v>20391</v>
       </c>
       <c r="B220" t="s">
-        <v>173</v>
+        <v>106</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D220" s="10" t="s">
+      <c r="D220" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="221" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A221" s="6">
-        <v>20395</v>
+        <v>20394</v>
       </c>
       <c r="B221" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D221" s="1" t="s">
+      <c r="D221" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="222" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A222" s="6">
-        <v>20396</v>
+        <v>20395</v>
       </c>
       <c r="B222" t="s">
-        <v>330</v>
+        <v>161</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>4</v>
@@ -4736,52 +4739,52 @@
     </row>
     <row r="223" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A223" s="6">
-        <v>20397</v>
-      </c>
-      <c r="B223" s="8" t="s">
-        <v>344</v>
+        <v>20396</v>
+      </c>
+      <c r="B223" t="s">
+        <v>330</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D223" s="11" t="s">
-        <v>5</v>
+      <c r="D223" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="224" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A224" s="6">
-        <v>30101</v>
-      </c>
-      <c r="B224" t="s">
-        <v>167</v>
+        <v>20397</v>
+      </c>
+      <c r="B224" s="8" t="s">
+        <v>344</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D224" s="1" t="s">
-        <v>8</v>
+      <c r="D224" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="225" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A225" s="6">
-        <v>40124</v>
+        <v>30101</v>
       </c>
       <c r="B225" t="s">
-        <v>24</v>
+        <v>167</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D225" s="13" t="s">
-        <v>5</v>
+      <c r="D225" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="226" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A226" s="6">
-        <v>40125</v>
+        <v>40124</v>
       </c>
       <c r="B226" t="s">
-        <v>143</v>
+        <v>24</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>4</v>
@@ -4792,24 +4795,24 @@
     </row>
     <row r="227" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A227" s="6">
-        <v>40127</v>
+        <v>40125</v>
       </c>
       <c r="B227" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D227" s="1" t="s">
-        <v>8</v>
+      <c r="D227" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="228" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A228" s="6">
-        <v>40129</v>
+        <v>40127</v>
       </c>
       <c r="B228" t="s">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>4</v>
@@ -4820,24 +4823,24 @@
     </row>
     <row r="229" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A229" s="6">
-        <v>40137</v>
+        <v>40129</v>
       </c>
       <c r="B229" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D229" s="10" t="s">
+      <c r="D229" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="230" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A230" s="6">
-        <v>40139</v>
+        <v>40137</v>
       </c>
       <c r="B230" t="s">
-        <v>327</v>
+        <v>121</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>4</v>
@@ -4848,66 +4851,66 @@
     </row>
     <row r="231" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A231" s="6">
-        <v>40140</v>
+        <v>40139</v>
       </c>
       <c r="B231" t="s">
-        <v>170</v>
+        <v>327</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D231" s="1" t="s">
+      <c r="D231" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="232" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A232" s="6">
-        <v>40141</v>
+        <v>40140</v>
       </c>
       <c r="B232" t="s">
-        <v>111</v>
+        <v>170</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D232" s="13" t="s">
-        <v>5</v>
+      <c r="D232" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="233" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A233" s="6">
-        <v>40143</v>
+        <v>40141</v>
       </c>
       <c r="B233" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D233" s="10" t="s">
-        <v>8</v>
+      <c r="D233" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="234" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A234" s="6">
-        <v>40144</v>
+        <v>40143</v>
       </c>
       <c r="B234" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D234" s="13" t="s">
-        <v>5</v>
+      <c r="D234" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="235" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A235" s="6">
-        <v>40145</v>
+        <v>40144</v>
       </c>
       <c r="B235" t="s">
-        <v>165</v>
+        <v>107</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>4</v>
@@ -4918,206 +4921,206 @@
     </row>
     <row r="236" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A236" s="6">
-        <v>40147</v>
+        <v>40145</v>
       </c>
       <c r="B236" t="s">
-        <v>405</v>
+        <v>165</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D236" s="19" t="s">
-        <v>8</v>
+      <c r="D236" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="237" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A237" s="6">
-        <v>40150</v>
+        <v>40147</v>
       </c>
       <c r="B237" t="s">
-        <v>221</v>
+        <v>405</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D237" s="10" t="s">
+      <c r="D237" s="19" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="238" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A238" s="6">
-        <v>40151</v>
+        <v>40150</v>
       </c>
       <c r="B238" t="s">
-        <v>54</v>
+        <v>221</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D238" s="1" t="s">
+      <c r="D238" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="239" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A239" s="6">
-        <v>50102</v>
+        <v>40151</v>
       </c>
       <c r="B239" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D239" s="13" t="s">
-        <v>5</v>
+      <c r="D239" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="240" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A240" s="6">
-        <v>50222</v>
+        <v>50102</v>
       </c>
       <c r="B240" t="s">
-        <v>215</v>
+        <v>67</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D240" s="1" t="s">
-        <v>8</v>
+      <c r="D240" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="241" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A241" s="6">
-        <v>50223</v>
+        <v>50222</v>
       </c>
       <c r="B241" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D241" s="10" t="s">
+      <c r="D241" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="242" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A242" s="6">
-        <v>50224</v>
+        <v>50223</v>
       </c>
       <c r="B242" t="s">
-        <v>42</v>
+        <v>194</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D242" s="3" t="s">
-        <v>5</v>
+      <c r="D242" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="243" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A243" s="6">
-        <v>50444</v>
+        <v>50224</v>
       </c>
       <c r="B243" t="s">
-        <v>116</v>
+        <v>42</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D243" s="1" t="s">
-        <v>8</v>
+      <c r="D243" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="244" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A244" s="6">
-        <v>50445</v>
+        <v>50444</v>
       </c>
       <c r="B244" t="s">
-        <v>354</v>
+        <v>116</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D244" s="11" t="s">
-        <v>5</v>
+      <c r="D244" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="245" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A245" s="6">
-        <v>50607</v>
+        <v>50445</v>
       </c>
       <c r="B245" t="s">
-        <v>76</v>
+        <v>354</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D245" s="13" t="s">
+      <c r="D245" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="246" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A246" s="6">
-        <v>50608</v>
+        <v>50607</v>
       </c>
       <c r="B246" t="s">
-        <v>177</v>
+        <v>76</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D246" s="1" t="s">
-        <v>8</v>
+      <c r="D246" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="247" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A247" s="6">
-        <v>50611</v>
-      </c>
-      <c r="B247" s="8" t="s">
-        <v>347</v>
+        <v>50608</v>
+      </c>
+      <c r="B247" t="s">
+        <v>177</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D247" s="14" t="s">
+      <c r="D247" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="248" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A248" s="6">
-        <v>50622</v>
-      </c>
-      <c r="B248" t="s">
-        <v>95</v>
+        <v>50611</v>
+      </c>
+      <c r="B248" s="8" t="s">
+        <v>347</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D248" s="16" t="s">
+      <c r="D248" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="249" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A249" s="6">
-        <v>50623</v>
+        <v>50622</v>
       </c>
       <c r="B249" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D249" s="10" t="s">
+      <c r="D249" s="16" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="250" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A250" s="6">
-        <v>50625</v>
+        <v>50623</v>
       </c>
       <c r="B250" t="s">
-        <v>204</v>
+        <v>110</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>4</v>
@@ -5128,94 +5131,94 @@
     </row>
     <row r="251" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A251" s="6">
-        <v>50629</v>
+        <v>50625</v>
       </c>
       <c r="B251" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D251" s="1" t="s">
+      <c r="D251" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="252" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A252" s="6">
-        <v>50630</v>
+        <v>50629</v>
       </c>
       <c r="B252" t="s">
-        <v>360</v>
+        <v>188</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D252" s="14" t="s">
+      <c r="D252" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="253" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A253" s="6">
-        <v>50803</v>
+        <v>50630</v>
       </c>
       <c r="B253" t="s">
-        <v>82</v>
+        <v>360</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D253" s="1" t="s">
+      <c r="D253" s="14" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="254" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A254" s="6">
-        <v>50805</v>
+        <v>50803</v>
       </c>
       <c r="B254" t="s">
-        <v>135</v>
+        <v>82</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D254" s="10" t="s">
+      <c r="D254" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="255" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A255" s="6">
-        <v>50806</v>
+        <v>50805</v>
       </c>
       <c r="B255" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D255" s="1" t="s">
+      <c r="D255" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="256" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A256" s="6">
-        <v>50808</v>
+        <v>50806</v>
       </c>
       <c r="B256" t="s">
-        <v>16</v>
+        <v>156</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D256" s="13" t="s">
-        <v>5</v>
+      <c r="D256" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="257" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A257" s="6">
-        <v>50809</v>
+        <v>50808</v>
       </c>
       <c r="B257" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>4</v>
@@ -5226,24 +5229,24 @@
     </row>
     <row r="258" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A258" s="6">
-        <v>50810</v>
+        <v>50809</v>
       </c>
       <c r="B258" t="s">
-        <v>175</v>
+        <v>98</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D258" s="1" t="s">
-        <v>8</v>
+      <c r="D258" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="259" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A259" s="6">
-        <v>50812</v>
+        <v>50810</v>
       </c>
       <c r="B259" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>4</v>
@@ -5254,80 +5257,80 @@
     </row>
     <row r="260" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A260" s="6">
-        <v>50813</v>
+        <v>50812</v>
       </c>
       <c r="B260" t="s">
-        <v>71</v>
+        <v>184</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D260" s="17" t="s">
-        <v>9</v>
+      <c r="D260" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="261" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A261" s="6">
-        <v>50815</v>
+        <v>50813</v>
       </c>
       <c r="B261" t="s">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D261" s="10" t="s">
-        <v>8</v>
+      <c r="D261" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="262" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A262" s="6">
-        <v>50816</v>
+        <v>50815</v>
       </c>
       <c r="B262" t="s">
-        <v>205</v>
+        <v>114</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D262" s="1" t="s">
+      <c r="D262" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="263" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A263" s="6">
-        <v>50818</v>
+        <v>50816</v>
       </c>
       <c r="B263" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D263" s="13" t="s">
-        <v>5</v>
+      <c r="D263" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="264" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A264" s="6">
-        <v>50819</v>
+        <v>50818</v>
       </c>
       <c r="B264" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D264" s="10" t="s">
-        <v>8</v>
+      <c r="D264" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="265" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A265" s="6">
-        <v>50820</v>
+        <v>50819</v>
       </c>
       <c r="B265" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>4</v>
@@ -5338,66 +5341,66 @@
     </row>
     <row r="266" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A266" s="6">
-        <v>50821</v>
+        <v>50820</v>
       </c>
       <c r="B266" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D266" s="1" t="s">
+      <c r="D266" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="267" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A267" s="6">
-        <v>50823</v>
+        <v>50821</v>
       </c>
       <c r="B267" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D267" s="17" t="s">
-        <v>9</v>
+      <c r="D267" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="268" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A268" s="6">
-        <v>50824</v>
+        <v>50823</v>
       </c>
       <c r="B268" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D268" s="13" t="s">
-        <v>5</v>
+      <c r="D268" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="269" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A269" s="6">
-        <v>50825</v>
+        <v>50824</v>
       </c>
       <c r="B269" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D269" s="10" t="s">
-        <v>8</v>
+      <c r="D269" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="270" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A270" s="6">
-        <v>50826</v>
+        <v>50825</v>
       </c>
       <c r="B270" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>4</v>
@@ -5408,24 +5411,24 @@
     </row>
     <row r="271" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A271" s="6">
-        <v>50827</v>
+        <v>50826</v>
       </c>
       <c r="B271" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D271" s="1" t="s">
+      <c r="D271" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="272" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A272" s="6">
-        <v>50829</v>
+        <v>50827</v>
       </c>
       <c r="B272" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>4</v>
@@ -5436,122 +5439,122 @@
     </row>
     <row r="273" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A273" s="6">
-        <v>50830</v>
+        <v>50829</v>
       </c>
       <c r="B273" t="s">
-        <v>366</v>
+        <v>236</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D273" s="11" t="s">
+      <c r="D273" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="274" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A274" s="6">
-        <v>50831</v>
+        <v>50830</v>
       </c>
       <c r="B274" t="s">
-        <v>351</v>
+        <v>366</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D274" s="11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="275" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A275" s="6">
-        <v>50832</v>
-      </c>
-      <c r="B275" s="8" t="s">
-        <v>349</v>
+        <v>50831</v>
+      </c>
+      <c r="B275" t="s">
+        <v>351</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D275" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="276" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A276" s="6">
-        <v>50833</v>
+        <v>50832</v>
       </c>
       <c r="B276" s="8" t="s">
-        <v>397</v>
+        <v>349</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D276" s="11" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="277" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A277" s="6">
-        <v>50230</v>
+        <v>50833</v>
       </c>
       <c r="B277" s="8" t="s">
-        <v>379</v>
+        <v>397</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D277" s="11" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="278" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A278" s="6">
-        <v>60103</v>
-      </c>
-      <c r="B278" t="s">
-        <v>237</v>
+        <v>50230</v>
+      </c>
+      <c r="B278" s="8" t="s">
+        <v>379</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D278" s="13" t="s">
+      <c r="D278" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="279" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A279" s="6">
-        <v>60109</v>
+        <v>60103</v>
       </c>
       <c r="B279" t="s">
-        <v>328</v>
+        <v>237</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D279" s="11" t="s">
-        <v>9</v>
+      <c r="D279" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="280" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A280" s="6">
-        <v>60124</v>
+        <v>60109</v>
       </c>
       <c r="B280" t="s">
-        <v>238</v>
+        <v>328</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D280" s="13" t="s">
-        <v>5</v>
+      <c r="D280" s="11" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="281" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A281" s="6">
-        <v>60125</v>
+        <v>60124</v>
       </c>
       <c r="B281" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>4</v>
@@ -5562,80 +5565,80 @@
     </row>
     <row r="282" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A282" s="6">
-        <v>60126</v>
+        <v>60125</v>
       </c>
       <c r="B282" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D282" s="10" t="s">
-        <v>8</v>
+      <c r="D282" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="283" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A283" s="6">
-        <v>60128</v>
+        <v>60126</v>
       </c>
       <c r="B283" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D283" s="3" t="s">
-        <v>5</v>
+      <c r="D283" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="284" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A284" s="6">
-        <v>60130</v>
+        <v>60128</v>
       </c>
       <c r="B284" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D284" s="1" t="s">
-        <v>8</v>
+      <c r="D284" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="285" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A285" s="6">
-        <v>60133</v>
+        <v>60130</v>
       </c>
       <c r="B285" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D285" s="13" t="s">
-        <v>5</v>
+      <c r="D285" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="286" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A286" s="6">
-        <v>60134</v>
+        <v>60133</v>
       </c>
       <c r="B286" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D286" s="1" t="s">
-        <v>8</v>
+      <c r="D286" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="287" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A287" s="6">
-        <v>60137</v>
+        <v>60134</v>
       </c>
       <c r="B287" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>4</v>
@@ -5646,10 +5649,10 @@
     </row>
     <row r="288" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A288" s="6">
-        <v>60139</v>
+        <v>60137</v>
       </c>
       <c r="B288" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>4</v>
@@ -5660,10 +5663,10 @@
     </row>
     <row r="289" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A289" s="6">
-        <v>60142</v>
+        <v>60139</v>
       </c>
       <c r="B289" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>4</v>
@@ -5674,10 +5677,10 @@
     </row>
     <row r="290" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A290" s="6">
-        <v>60148</v>
+        <v>60142</v>
       </c>
       <c r="B290" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>4</v>
@@ -5688,10 +5691,10 @@
     </row>
     <row r="291" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A291" s="6">
-        <v>60149</v>
+        <v>60148</v>
       </c>
       <c r="B291" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>4</v>
@@ -5702,66 +5705,66 @@
     </row>
     <row r="292" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A292" s="6">
-        <v>60150</v>
+        <v>60149</v>
       </c>
       <c r="B292" t="s">
-        <v>332</v>
+        <v>249</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D292" s="13" t="s">
-        <v>5</v>
+      <c r="D292" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="293" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A293" s="6">
-        <v>60158</v>
+        <v>60150</v>
       </c>
       <c r="B293" t="s">
-        <v>250</v>
+        <v>332</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D293" s="10" t="s">
-        <v>8</v>
+      <c r="D293" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="294" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A294" s="6">
-        <v>60159</v>
+        <v>60158</v>
       </c>
       <c r="B294" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D294" s="1" t="s">
+      <c r="D294" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="295" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A295" s="6">
-        <v>60162</v>
+        <v>60159</v>
       </c>
       <c r="B295" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D295" s="13" t="s">
-        <v>5</v>
+      <c r="D295" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="296" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A296" s="6">
-        <v>60163</v>
+        <v>60162</v>
       </c>
       <c r="B296" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>4</v>
@@ -5772,24 +5775,24 @@
     </row>
     <row r="297" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A297" s="6">
-        <v>60165</v>
+        <v>60163</v>
       </c>
       <c r="B297" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D297" s="1" t="s">
-        <v>8</v>
+      <c r="D297" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="298" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A298" s="6">
-        <v>60169</v>
+        <v>60165</v>
       </c>
       <c r="B298" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>4</v>
@@ -5800,52 +5803,52 @@
     </row>
     <row r="299" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A299" s="6">
-        <v>60170</v>
-      </c>
-      <c r="B299" s="8" t="s">
-        <v>337</v>
+        <v>60169</v>
+      </c>
+      <c r="B299" t="s">
+        <v>255</v>
       </c>
       <c r="C299" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D299" s="11" t="s">
+      <c r="D299" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="300" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A300" s="6">
-        <v>60172</v>
-      </c>
-      <c r="B300" t="s">
-        <v>256</v>
+        <v>60170</v>
+      </c>
+      <c r="B300" s="8" t="s">
+        <v>337</v>
       </c>
       <c r="C300" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D300" s="1" t="s">
+      <c r="D300" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="301" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A301" s="6">
-        <v>60174</v>
+        <v>60172</v>
       </c>
       <c r="B301" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C301" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D301" s="13" t="s">
-        <v>5</v>
+      <c r="D301" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="302" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A302" s="6">
-        <v>60176</v>
+        <v>60174</v>
       </c>
       <c r="B302" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>4</v>
@@ -5856,52 +5859,52 @@
     </row>
     <row r="303" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A303" s="6">
-        <v>60178</v>
+        <v>60176</v>
       </c>
       <c r="B303" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C303" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D303" s="1" t="s">
-        <v>8</v>
+      <c r="D303" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="304" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A304" s="6">
-        <v>60180</v>
+        <v>60178</v>
       </c>
       <c r="B304" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D304" s="10" t="s">
+      <c r="D304" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="305" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A305" s="6">
-        <v>60184</v>
+        <v>60180</v>
       </c>
       <c r="B305" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C305" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D305" s="1" t="s">
+      <c r="D305" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="306" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A306" s="6">
-        <v>60190</v>
+        <v>60184</v>
       </c>
       <c r="B306" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>4</v>
@@ -5912,24 +5915,24 @@
     </row>
     <row r="307" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A307" s="6">
-        <v>60191</v>
+        <v>60190</v>
       </c>
       <c r="B307" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D307" s="10" t="s">
+      <c r="D307" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="308" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A308" s="6">
-        <v>60192</v>
+        <v>60191</v>
       </c>
       <c r="B308" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>4</v>
@@ -5940,10 +5943,10 @@
     </row>
     <row r="309" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A309" s="6">
-        <v>60194</v>
-      </c>
-      <c r="B309" s="18" t="s">
-        <v>410</v>
+        <v>60192</v>
+      </c>
+      <c r="B309" t="s">
+        <v>264</v>
       </c>
       <c r="C309" s="1" t="s">
         <v>4</v>
@@ -5954,10 +5957,10 @@
     </row>
     <row r="310" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A310" s="6">
-        <v>60195</v>
-      </c>
-      <c r="B310" t="s">
-        <v>265</v>
+        <v>60194</v>
+      </c>
+      <c r="B310" s="18" t="s">
+        <v>410</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>4</v>
@@ -5968,10 +5971,10 @@
     </row>
     <row r="311" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A311" s="6">
-        <v>60196</v>
+        <v>60195</v>
       </c>
       <c r="B311" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>4</v>
@@ -5982,10 +5985,10 @@
     </row>
     <row r="312" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A312" s="6">
-        <v>60198</v>
+        <v>60196</v>
       </c>
       <c r="B312" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>4</v>
@@ -5996,52 +5999,52 @@
     </row>
     <row r="313" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A313" s="6">
-        <v>60201</v>
+        <v>60198</v>
       </c>
       <c r="B313" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D313" t="s">
-        <v>9</v>
+      <c r="D313" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="314" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A314" s="6">
-        <v>60202</v>
+        <v>60201</v>
       </c>
       <c r="B314" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D314" s="13" t="s">
-        <v>5</v>
+      <c r="D314" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="315" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A315" s="6">
-        <v>60204</v>
+        <v>60202</v>
       </c>
       <c r="B315" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D315" s="1" t="s">
-        <v>8</v>
+      <c r="D315" s="13" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="316" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A316" s="6">
-        <v>60205</v>
+        <v>60204</v>
       </c>
       <c r="B316" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>4</v>
@@ -6052,10 +6055,10 @@
     </row>
     <row r="317" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A317" s="6">
-        <v>60206</v>
+        <v>60205</v>
       </c>
       <c r="B317" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>4</v>
@@ -6066,192 +6069,192 @@
     </row>
     <row r="318" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A318" s="6">
-        <v>60209</v>
+        <v>60206</v>
       </c>
       <c r="B318" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D318" s="10" t="s">
+      <c r="D318" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="319" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A319" s="6">
-        <v>60211</v>
+        <v>60209</v>
       </c>
       <c r="B319" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D319" s="1" t="s">
+      <c r="D319" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="320" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A320" s="6">
-        <v>60215</v>
+        <v>60211</v>
       </c>
       <c r="B320" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C320" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D320" s="10" t="s">
+      <c r="D320" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="321" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A321" s="6">
-        <v>60216</v>
+        <v>60215</v>
       </c>
       <c r="B321" t="s">
-        <v>381</v>
+        <v>275</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D321" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="322" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A322" s="6">
-        <v>60217</v>
+        <v>60216</v>
       </c>
       <c r="B322" t="s">
-        <v>276</v>
+        <v>381</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D322" s="10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="323" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A323" s="6">
-        <v>60219</v>
+        <v>60217</v>
       </c>
       <c r="B323" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D323" s="1" t="s">
+      <c r="D323" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="324" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A324" s="6">
-        <v>60222</v>
+        <v>60219</v>
       </c>
       <c r="B324" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D324" s="10" t="s">
+      <c r="D324" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="325" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A325" s="6">
-        <v>60225</v>
+        <v>60222</v>
       </c>
       <c r="B325" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D325" s="17" t="s">
-        <v>9</v>
+      <c r="D325" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="326" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A326" s="6">
-        <v>60230</v>
+        <v>60225</v>
       </c>
       <c r="B326" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D326" s="10" t="s">
-        <v>8</v>
+      <c r="D326" s="17" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="327" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A327" s="6">
-        <v>60241</v>
-      </c>
-      <c r="B327" s="8" t="s">
-        <v>338</v>
+        <v>60230</v>
+      </c>
+      <c r="B327" t="s">
+        <v>280</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D327" s="7" t="s">
-        <v>9</v>
+      <c r="D327" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="328" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A328" s="6">
-        <v>60242</v>
+        <v>60241</v>
       </c>
       <c r="B328" s="8" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D328" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="329" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A329" s="6">
-        <v>60243</v>
+        <v>60242</v>
       </c>
       <c r="B329" s="8" t="s">
-        <v>395</v>
+        <v>341</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D329" s="7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="330" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A330" s="6">
-        <v>60245</v>
+        <v>60243</v>
       </c>
       <c r="B330" s="8" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D330" s="7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="331" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A331" s="6">
-        <v>60246</v>
+        <v>60245</v>
       </c>
       <c r="B331" s="8" t="s">
-        <v>407</v>
+        <v>387</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>4</v>
@@ -6262,10 +6265,10 @@
     </row>
     <row r="332" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A332" s="6">
-        <v>60249</v>
-      </c>
-      <c r="B332" s="18" t="s">
-        <v>408</v>
+        <v>60246</v>
+      </c>
+      <c r="B332" s="8" t="s">
+        <v>407</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>4</v>
@@ -6276,38 +6279,38 @@
     </row>
     <row r="333" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A333" s="6">
-        <v>60250</v>
-      </c>
-      <c r="B333" s="8" t="s">
-        <v>339</v>
+        <v>60249</v>
+      </c>
+      <c r="B333" s="18" t="s">
+        <v>408</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D333" s="11" t="s">
-        <v>8</v>
+      <c r="D333" s="7" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="334" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A334" s="6">
-        <v>60253</v>
-      </c>
-      <c r="B334" t="s">
-        <v>281</v>
+        <v>60250</v>
+      </c>
+      <c r="B334" s="8" t="s">
+        <v>339</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D334" s="1" t="s">
+      <c r="D334" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="335" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A335" s="6">
-        <v>60254</v>
+        <v>60253</v>
       </c>
       <c r="B335" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>4</v>
@@ -6318,10 +6321,10 @@
     </row>
     <row r="336" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A336" s="6">
-        <v>60257</v>
+        <v>60254</v>
       </c>
       <c r="B336" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>4</v>
@@ -6332,10 +6335,10 @@
     </row>
     <row r="337" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A337" s="6">
-        <v>60258</v>
+        <v>60257</v>
       </c>
       <c r="B337" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>4</v>
@@ -6346,66 +6349,66 @@
     </row>
     <row r="338" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A338" s="6">
-        <v>60266</v>
-      </c>
-      <c r="B338" s="8" t="s">
-        <v>343</v>
+        <v>60258</v>
+      </c>
+      <c r="B338" t="s">
+        <v>284</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D338" s="11" t="s">
+      <c r="D338" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="339" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A339" s="6">
-        <v>60269</v>
-      </c>
-      <c r="B339" t="s">
-        <v>285</v>
+        <v>60266</v>
+      </c>
+      <c r="B339" s="8" t="s">
+        <v>343</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D339" s="10" t="s">
+      <c r="D339" s="11" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="340" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A340" s="6">
-        <v>60270</v>
+        <v>60269</v>
       </c>
       <c r="B340" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D340" s="1" t="s">
-        <v>9</v>
+      <c r="D340" s="10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="341" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A341" s="6">
-        <v>60272</v>
+        <v>60270</v>
       </c>
       <c r="B341" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C341" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="342" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A342" s="6">
-        <v>60274</v>
+        <v>60272</v>
       </c>
       <c r="B342" t="s">
-        <v>380</v>
+        <v>287</v>
       </c>
       <c r="C342" s="1" t="s">
         <v>4</v>
@@ -6416,10 +6419,10 @@
     </row>
     <row r="343" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A343" s="6">
-        <v>60275</v>
+        <v>60274</v>
       </c>
       <c r="B343" t="s">
-        <v>288</v>
+        <v>380</v>
       </c>
       <c r="C343" s="1" t="s">
         <v>4</v>
@@ -6430,10 +6433,10 @@
     </row>
     <row r="344" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A344" s="6">
-        <v>60276</v>
+        <v>60275</v>
       </c>
       <c r="B344" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C344" s="1" t="s">
         <v>4</v>
@@ -6444,108 +6447,108 @@
     </row>
     <row r="345" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A345" s="6">
-        <v>60278</v>
+        <v>60276</v>
       </c>
       <c r="B345" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C345" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D345" s="13" t="s">
+      <c r="D345" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="346" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A346" s="6">
-        <v>60279</v>
+        <v>60278</v>
       </c>
       <c r="B346" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C346" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D346" s="1" t="s">
+      <c r="D346" s="13" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="347" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A347" s="6">
-        <v>60280</v>
+        <v>60279</v>
       </c>
       <c r="B347" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C347" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="348" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A348" s="6">
-        <v>60281</v>
-      </c>
-      <c r="B348" s="8" t="s">
-        <v>336</v>
+        <v>60280</v>
+      </c>
+      <c r="B348" t="s">
+        <v>292</v>
       </c>
       <c r="C348" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D348" s="11" t="s">
-        <v>9</v>
+      <c r="D348" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="349" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A349" s="6">
-        <v>60282</v>
+        <v>60281</v>
       </c>
       <c r="B349" s="8" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C349" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D349" s="11" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="350" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A350" s="6">
-        <v>60283</v>
-      </c>
-      <c r="B350" t="s">
-        <v>378</v>
+        <v>60282</v>
+      </c>
+      <c r="B350" s="8" t="s">
+        <v>340</v>
       </c>
       <c r="C350" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D350" s="1" t="s">
-        <v>8</v>
+      <c r="D350" s="11" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="351" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A351" s="6">
-        <v>60284</v>
-      </c>
-      <c r="B351" s="8" t="s">
-        <v>335</v>
+        <v>60283</v>
+      </c>
+      <c r="B351" t="s">
+        <v>378</v>
       </c>
       <c r="C351" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D351" s="9" t="s">
-        <v>5</v>
+      <c r="D351" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="352" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A352" s="6">
-        <v>60285</v>
+        <v>60284</v>
       </c>
       <c r="B352" s="8" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="C352" s="1" t="s">
         <v>4</v>
@@ -6556,10 +6559,10 @@
     </row>
     <row r="353" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A353" s="6">
-        <v>60286</v>
+        <v>60285</v>
       </c>
       <c r="B353" s="8" t="s">
-        <v>334</v>
+        <v>350</v>
       </c>
       <c r="C353" s="1" t="s">
         <v>4</v>
@@ -6570,52 +6573,52 @@
     </row>
     <row r="354" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A354" s="6">
-        <v>60287</v>
-      </c>
-      <c r="B354" t="s">
-        <v>377</v>
+        <v>60286</v>
+      </c>
+      <c r="B354" s="8" t="s">
+        <v>334</v>
       </c>
       <c r="C354" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D354" s="12" t="s">
+      <c r="D354" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="355" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A355" s="6">
-        <v>60289</v>
+        <v>60287</v>
       </c>
       <c r="B355" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D355" s="12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="356" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A356" s="6">
-        <v>60290</v>
+        <v>60289</v>
       </c>
       <c r="B356" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D356" s="12" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="357" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A357" s="6">
-        <v>60291</v>
+        <v>60290</v>
       </c>
       <c r="B357" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>4</v>
@@ -6626,24 +6629,24 @@
     </row>
     <row r="358" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A358" s="6">
-        <v>60292</v>
-      </c>
-      <c r="B358" s="18" t="s">
-        <v>400</v>
+        <v>60291</v>
+      </c>
+      <c r="B358" t="s">
+        <v>376</v>
       </c>
       <c r="C358" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D358" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="359" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A359" s="6">
-        <v>60296</v>
-      </c>
-      <c r="B359" t="s">
-        <v>391</v>
+        <v>60292</v>
+      </c>
+      <c r="B359" s="18" t="s">
+        <v>400</v>
       </c>
       <c r="C359" s="1" t="s">
         <v>4</v>
@@ -6654,24 +6657,24 @@
     </row>
     <row r="360" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A360" s="6">
-        <v>60297</v>
+        <v>60296</v>
       </c>
       <c r="B360" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C360" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D360" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="361" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A361" s="6">
-        <v>60299</v>
+        <v>60297</v>
       </c>
       <c r="B361" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="C361" s="1" t="s">
         <v>4</v>
@@ -6682,10 +6685,10 @@
     </row>
     <row r="362" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A362" s="6">
-        <v>60302</v>
-      </c>
-      <c r="B362" s="18" t="s">
-        <v>411</v>
+        <v>60299</v>
+      </c>
+      <c r="B362" t="s">
+        <v>388</v>
       </c>
       <c r="C362" s="1" t="s">
         <v>4</v>
@@ -6696,10 +6699,10 @@
     </row>
     <row r="363" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A363" s="6">
-        <v>60303</v>
+        <v>60302</v>
       </c>
       <c r="B363" s="18" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C363" s="1" t="s">
         <v>4</v>
@@ -6710,52 +6713,52 @@
     </row>
     <row r="364" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A364" s="6">
-        <v>61001</v>
-      </c>
-      <c r="B364" t="s">
-        <v>403</v>
+        <v>60303</v>
+      </c>
+      <c r="B364" s="18" t="s">
+        <v>412</v>
       </c>
       <c r="C364" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D364" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="365" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A365" s="6">
-        <v>61004</v>
+        <v>61001</v>
       </c>
       <c r="B365" t="s">
-        <v>293</v>
+        <v>403</v>
       </c>
       <c r="C365" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D365" s="15" t="s">
-        <v>5</v>
+      <c r="D365" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="366" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A366" s="6">
-        <v>61009</v>
+        <v>61004</v>
       </c>
       <c r="B366" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C366" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D366" s="12" t="s">
-        <v>8</v>
+      <c r="D366" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="367" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A367" s="6">
-        <v>61012</v>
+        <v>61009</v>
       </c>
       <c r="B367" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C367" s="1" t="s">
         <v>4</v>
@@ -6766,10 +6769,10 @@
     </row>
     <row r="368" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A368" s="6">
-        <v>61018</v>
+        <v>61012</v>
       </c>
       <c r="B368" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C368" s="1" t="s">
         <v>4</v>
@@ -6780,10 +6783,10 @@
     </row>
     <row r="369" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A369" s="6">
-        <v>61102</v>
+        <v>61018</v>
       </c>
       <c r="B369" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C369" s="1" t="s">
         <v>4</v>
@@ -6794,52 +6797,52 @@
     </row>
     <row r="370" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A370" s="6">
-        <v>61205</v>
+        <v>61102</v>
       </c>
       <c r="B370" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C370" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D370" s="15" t="s">
-        <v>5</v>
+      <c r="D370" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="371" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A371" s="6">
-        <v>70100</v>
+        <v>61205</v>
       </c>
       <c r="B371" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C371" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D371" s="12" t="s">
-        <v>8</v>
+      <c r="D371" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="372" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A372" s="6">
-        <v>70101</v>
+        <v>70100</v>
       </c>
       <c r="B372" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C372" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D372" s="15" t="s">
-        <v>5</v>
+      <c r="D372" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="373" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A373" s="6">
-        <v>70102</v>
+        <v>70101</v>
       </c>
       <c r="B373" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C373" s="1" t="s">
         <v>4</v>
@@ -6850,80 +6853,80 @@
     </row>
     <row r="374" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A374" s="6">
-        <v>70103</v>
+        <v>70102</v>
       </c>
       <c r="B374" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C374" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D374" s="12" t="s">
-        <v>8</v>
+      <c r="D374" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="375" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A375" s="6">
-        <v>70106</v>
+        <v>70103</v>
       </c>
       <c r="B375" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C375" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D375" s="15" t="s">
-        <v>5</v>
+      <c r="D375" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="376" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A376" s="6">
-        <v>70109</v>
+        <v>70106</v>
       </c>
       <c r="B376" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C376" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D376" s="12" t="s">
-        <v>8</v>
+      <c r="D376" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="377" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A377" s="6">
-        <v>70113</v>
+        <v>70109</v>
       </c>
       <c r="B377" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C377" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D377" s="15" t="s">
-        <v>5</v>
+      <c r="D377" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="378" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A378" s="6">
-        <v>70114</v>
+        <v>70113</v>
       </c>
       <c r="B378" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
       <c r="C378" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D378" s="9" t="s">
-        <v>9</v>
+      <c r="D378" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="379" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A379" s="6">
-        <v>70115</v>
+        <v>70114</v>
       </c>
       <c r="B379" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="C379" s="1" t="s">
         <v>4</v>
@@ -6934,24 +6937,24 @@
     </row>
     <row r="380" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A380" s="6">
-        <v>70638</v>
+        <v>70115</v>
       </c>
       <c r="B380" t="s">
-        <v>306</v>
+        <v>331</v>
       </c>
       <c r="C380" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D380" s="12" t="s">
-        <v>8</v>
+      <c r="D380" s="9" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="381" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A381" s="6">
-        <v>70639</v>
+        <v>70638</v>
       </c>
       <c r="B381" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C381" s="1" t="s">
         <v>4</v>
@@ -6962,10 +6965,10 @@
     </row>
     <row r="382" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A382" s="6">
-        <v>70640</v>
+        <v>70639</v>
       </c>
       <c r="B382" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C382" s="1" t="s">
         <v>4</v>
@@ -6976,10 +6979,10 @@
     </row>
     <row r="383" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A383" s="6">
-        <v>70642</v>
+        <v>70640</v>
       </c>
       <c r="B383" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C383" s="1" t="s">
         <v>4</v>
@@ -6990,10 +6993,10 @@
     </row>
     <row r="384" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A384" s="6">
-        <v>90504</v>
+        <v>70642</v>
       </c>
       <c r="B384" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C384" s="1" t="s">
         <v>4</v>
@@ -7004,10 +7007,10 @@
     </row>
     <row r="385" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A385" s="6">
-        <v>90509</v>
+        <v>90504</v>
       </c>
       <c r="B385" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C385" s="1" t="s">
         <v>4</v>
@@ -7018,52 +7021,52 @@
     </row>
     <row r="386" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A386" s="6">
-        <v>90602</v>
+        <v>90509</v>
       </c>
       <c r="B386" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C386" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D386" s="15" t="s">
-        <v>5</v>
+      <c r="D386" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="387" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A387" s="6">
-        <v>90621</v>
+        <v>90602</v>
       </c>
       <c r="B387" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C387" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D387" s="12" t="s">
-        <v>8</v>
+      <c r="D387" s="15" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="388" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A388" s="6">
-        <v>90622</v>
+        <v>90621</v>
       </c>
       <c r="B388" t="s">
-        <v>333</v>
+        <v>313</v>
       </c>
       <c r="C388" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D388" s="9" t="s">
-        <v>5</v>
+      <c r="D388" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="389" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A389" s="6">
-        <v>90631</v>
-      </c>
-      <c r="B389" s="8" t="s">
-        <v>342</v>
+        <v>90622</v>
+      </c>
+      <c r="B389" t="s">
+        <v>333</v>
       </c>
       <c r="C389" s="1" t="s">
         <v>4</v>
@@ -7074,24 +7077,24 @@
     </row>
     <row r="390" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A390" s="6">
-        <v>90658</v>
-      </c>
-      <c r="B390" t="s">
-        <v>314</v>
+        <v>90631</v>
+      </c>
+      <c r="B390" s="8" t="s">
+        <v>342</v>
       </c>
       <c r="C390" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D390" s="12" t="s">
-        <v>8</v>
+      <c r="D390" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="391" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A391" s="6">
-        <v>90660</v>
+        <v>90658</v>
       </c>
       <c r="B391" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C391" s="1" t="s">
         <v>4</v>
@@ -7102,10 +7105,10 @@
     </row>
     <row r="392" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A392" s="6">
-        <v>90668</v>
+        <v>90660</v>
       </c>
       <c r="B392" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C392" s="1" t="s">
         <v>4</v>
@@ -7116,10 +7119,10 @@
     </row>
     <row r="393" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A393" s="6">
-        <v>90671</v>
+        <v>90668</v>
       </c>
       <c r="B393" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C393" s="1" t="s">
         <v>4</v>
@@ -7130,10 +7133,10 @@
     </row>
     <row r="394" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A394" s="6">
-        <v>90679</v>
+        <v>90671</v>
       </c>
       <c r="B394" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C394" s="1" t="s">
         <v>4</v>
@@ -7144,10 +7147,10 @@
     </row>
     <row r="395" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A395" s="6">
-        <v>90683</v>
+        <v>90679</v>
       </c>
       <c r="B395" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C395" s="1" t="s">
         <v>4</v>
@@ -7158,10 +7161,10 @@
     </row>
     <row r="396" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A396" s="6">
-        <v>90705</v>
+        <v>90683</v>
       </c>
       <c r="B396" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C396" s="1" t="s">
         <v>4</v>
@@ -7172,10 +7175,10 @@
     </row>
     <row r="397" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A397" s="6">
-        <v>90706</v>
+        <v>90705</v>
       </c>
       <c r="B397" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C397" s="1" t="s">
         <v>4</v>
@@ -7186,10 +7189,10 @@
     </row>
     <row r="398" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A398" s="6">
-        <v>90708</v>
+        <v>90706</v>
       </c>
       <c r="B398" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C398" s="1" t="s">
         <v>4</v>
@@ -7200,10 +7203,10 @@
     </row>
     <row r="399" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A399" s="6">
-        <v>90709</v>
+        <v>90708</v>
       </c>
       <c r="B399" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C399" s="1" t="s">
         <v>4</v>
@@ -7214,38 +7217,38 @@
     </row>
     <row r="400" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A400" s="6">
-        <v>90713</v>
+        <v>90709</v>
       </c>
       <c r="B400" t="s">
-        <v>402</v>
+        <v>323</v>
       </c>
       <c r="C400" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D400" s="12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="401" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A401" s="6">
-        <v>1218</v>
+        <v>90713</v>
       </c>
       <c r="B401" t="s">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="C401" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D401" s="12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="402" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A402" s="6">
-        <v>1959</v>
-      </c>
-      <c r="B402" s="8" t="s">
-        <v>383</v>
+        <v>1218</v>
+      </c>
+      <c r="B402" t="s">
+        <v>382</v>
       </c>
       <c r="C402" s="1" t="s">
         <v>4</v>
@@ -7256,10 +7259,10 @@
     </row>
     <row r="403" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A403" s="6">
-        <v>5625</v>
+        <v>1959</v>
       </c>
       <c r="B403" s="8" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C403" s="1" t="s">
         <v>4</v>
@@ -7270,10 +7273,10 @@
     </row>
     <row r="404" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A404" s="6">
-        <v>1817</v>
+        <v>5625</v>
       </c>
       <c r="B404" s="8" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="C404" s="1" t="s">
         <v>4</v>
@@ -7284,10 +7287,10 @@
     </row>
     <row r="405" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A405" s="6">
-        <v>5737</v>
+        <v>1817</v>
       </c>
       <c r="B405" s="8" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C405" s="1" t="s">
         <v>4</v>
@@ -7298,34 +7301,48 @@
     </row>
     <row r="406" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A406" s="6">
-        <v>60295</v>
+        <v>5737</v>
       </c>
       <c r="B406" s="8" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C406" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D406" s="9" t="s">
-        <v>9</v>
+      <c r="D406" s="12" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="407" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A407" s="6">
+        <v>60295</v>
+      </c>
+      <c r="B407" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="C407" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D407" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A408" s="6">
         <v>1045</v>
       </c>
-      <c r="B407" s="8" t="s">
+      <c r="B408" s="8" t="s">
         <v>386</v>
       </c>
-      <c r="C407" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D407" s="9" t="s">
+      <c r="C408" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D408" s="9" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D350"/>
+  <autoFilter ref="A1:D351"/>
   <sortState ref="A2:D374">
     <sortCondition ref="A277"/>
   </sortState>

--- a/excel/CLIENTES_PERMISOS.xlsx
+++ b/excel/CLIENTES_PERMISOS.xlsx
@@ -2004,7 +2004,7 @@
         <v>4</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2256,7 +2256,7 @@
         <v>4</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -5154,7 +5154,7 @@
         <v>4</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="253" spans="1:4" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
